--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="109" documentId="8_{D3DC1C62-A0A1-41AB-9E62-302D8C909E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0EA3399-3C94-4316-B217-16DDA15115C5}"/>
+  <xr:revisionPtr revIDLastSave="110" documentId="8_{D3DC1C62-A0A1-41AB-9E62-302D8C909E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33640AA6-9F85-4069-B8D2-AE74398987BB}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
@@ -734,10 +734,10 @@
         <v>31</v>
       </c>
       <c r="D12">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E12">
-        <v>1.29</v>
+        <v>1.323</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -768,10 +768,10 @@
         <v>62</v>
       </c>
       <c r="D14">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E14">
-        <v>1.097</v>
+        <v>1.113</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -785,10 +785,10 @@
         <v>40</v>
       </c>
       <c r="D15">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E15">
-        <v>1.0249999999999999</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -819,10 +819,10 @@
         <v>68</v>
       </c>
       <c r="D17">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E17">
-        <v>1.0149999999999999</v>
+        <v>1.0289999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -870,10 +870,10 @@
         <v>85</v>
       </c>
       <c r="D20">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E20">
-        <v>1.0349999999999999</v>
+        <v>1.0469999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -938,10 +938,10 @@
         <v>65</v>
       </c>
       <c r="D24">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E24">
-        <v>1.1850000000000001</v>
+        <v>1.2150000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -955,10 +955,10 @@
         <v>91</v>
       </c>
       <c r="D25">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E25">
-        <v>1.0109999999999999</v>
+        <v>1.022</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -1023,10 +1023,10 @@
         <v>128</v>
       </c>
       <c r="D29">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E29">
-        <v>1.0389999999999999</v>
+        <v>1.0469999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1040,10 +1040,10 @@
         <v>119</v>
       </c>
       <c r="D30">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E30">
-        <v>1.034</v>
+        <v>1.042</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -1057,10 +1057,10 @@
         <v>138</v>
       </c>
       <c r="D31">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E31">
-        <v>1.0289999999999999</v>
+        <v>1.022</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1074,10 +1074,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="E32">
-        <v>1.0329999999999999</v>
+        <v>1.0429999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1091,10 +1091,10 @@
         <v>329</v>
       </c>
       <c r="D33">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E33">
-        <v>1.03</v>
+        <v>1.036</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1142,10 +1142,10 @@
         <v>250</v>
       </c>
       <c r="D36">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="E36">
-        <v>1.008</v>
+        <v>1.024</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1159,10 +1159,10 @@
         <v>217</v>
       </c>
       <c r="D37">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E37">
-        <v>0.96299999999999997</v>
+        <v>0.96799999999999997</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1176,10 +1176,10 @@
         <v>226</v>
       </c>
       <c r="D38">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E38">
-        <v>0.98699999999999999</v>
+        <v>0.99099999999999999</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="110" documentId="8_{D3DC1C62-A0A1-41AB-9E62-302D8C909E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{33640AA6-9F85-4069-B8D2-AE74398987BB}"/>
+  <xr:revisionPtr revIDLastSave="111" documentId="8_{D3DC1C62-A0A1-41AB-9E62-302D8C909E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E725D6E-E8B3-4EB4-ADA3-22E4041DD355}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
@@ -564,10 +564,10 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>1.1579999999999999</v>
+        <v>1.2110000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -615,10 +615,10 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E5">
-        <v>1.206</v>
+        <v>1.2350000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -649,10 +649,10 @@
         <v>61</v>
       </c>
       <c r="D7">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E7">
-        <v>0.95099999999999996</v>
+        <v>0.98399999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -683,10 +683,10 @@
         <v>108</v>
       </c>
       <c r="D9">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E9">
-        <v>1.0369999999999999</v>
+        <v>1.046</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -734,10 +734,10 @@
         <v>31</v>
       </c>
       <c r="D12">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E12">
-        <v>1.323</v>
+        <v>1.355</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -751,10 +751,10 @@
         <v>35</v>
       </c>
       <c r="D13">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E13">
-        <v>0.94299999999999995</v>
+        <v>0.97099999999999997</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -768,10 +768,10 @@
         <v>62</v>
       </c>
       <c r="D14">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E14">
-        <v>1.113</v>
+        <v>1.129</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -802,10 +802,10 @@
         <v>63</v>
       </c>
       <c r="D16">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E16">
-        <v>0.88900000000000001</v>
+        <v>0.90500000000000003</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -819,10 +819,10 @@
         <v>68</v>
       </c>
       <c r="D17">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E17">
-        <v>1.0289999999999999</v>
+        <v>1.044</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -938,10 +938,10 @@
         <v>65</v>
       </c>
       <c r="D24">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E24">
-        <v>1.2150000000000001</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -1006,10 +1006,10 @@
         <v>140</v>
       </c>
       <c r="D28">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E28">
-        <v>1.0069999999999999</v>
+        <v>1.014</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -1074,10 +1074,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="E32">
-        <v>1.0429999999999999</v>
+        <v>1.0529999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1108,10 +1108,10 @@
         <v>323</v>
       </c>
       <c r="D34">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E34">
-        <v>0.97799999999999998</v>
+        <v>0.98499999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1142,10 +1142,10 @@
         <v>250</v>
       </c>
       <c r="D36">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E36">
-        <v>1.024</v>
+        <v>1.032</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1176,10 +1176,10 @@
         <v>226</v>
       </c>
       <c r="D38">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E38">
-        <v>0.99099999999999999</v>
+        <v>0.996</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1193,10 +1193,10 @@
         <v>214</v>
       </c>
       <c r="D39">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E39">
-        <v>0.94399999999999995</v>
+        <v>0.94899999999999995</v>
       </c>
     </row>
   </sheetData>

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="111" documentId="8_{D3DC1C62-A0A1-41AB-9E62-302D8C909E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E725D6E-E8B3-4EB4-ADA3-22E4041DD355}"/>
+  <xr:revisionPtr revIDLastSave="112" documentId="8_{D3DC1C62-A0A1-41AB-9E62-302D8C909E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4244F4B2-1821-4517-9DE2-C945A04F4E83}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="mat_2026" sheetId="1" r:id="rId1"/>
@@ -564,10 +564,10 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2">
-        <v>1.2110000000000001</v>
+        <v>1.2629999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -615,10 +615,10 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E5">
-        <v>1.2350000000000001</v>
+        <v>1.2649999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -649,10 +649,10 @@
         <v>61</v>
       </c>
       <c r="D7">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E7">
-        <v>0.98399999999999999</v>
+        <v>1.016</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -666,10 +666,10 @@
         <v>75</v>
       </c>
       <c r="D8">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E8">
-        <v>1.093</v>
+        <v>1.107</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -683,10 +683,10 @@
         <v>108</v>
       </c>
       <c r="D9">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E9">
-        <v>1.046</v>
+        <v>1.056</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -717,10 +717,10 @@
         <v>88</v>
       </c>
       <c r="D11">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E11">
-        <v>1.0449999999999999</v>
+        <v>1.0569999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -751,10 +751,10 @@
         <v>35</v>
       </c>
       <c r="D13">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E13">
-        <v>0.97099999999999997</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -836,10 +836,10 @@
         <v>75</v>
       </c>
       <c r="D18">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E18">
-        <v>1.04</v>
+        <v>1.0529999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -887,10 +887,10 @@
         <v>88</v>
       </c>
       <c r="D21">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E21">
-        <v>1.0109999999999999</v>
+        <v>1.0229999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -904,10 +904,10 @@
         <v>28</v>
       </c>
       <c r="D22">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E22">
-        <v>1.321</v>
+        <v>1.357</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -921,10 +921,10 @@
         <v>38</v>
       </c>
       <c r="D23">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E23">
-        <v>1.026</v>
+        <v>1.079</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -938,10 +938,10 @@
         <v>65</v>
       </c>
       <c r="D24">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E24">
-        <v>1.2</v>
+        <v>1.1850000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -955,10 +955,10 @@
         <v>91</v>
       </c>
       <c r="D25">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E25">
-        <v>1.022</v>
+        <v>1.044</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -972,10 +972,10 @@
         <v>83</v>
       </c>
       <c r="D26">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>1.012</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -989,10 +989,10 @@
         <v>109</v>
       </c>
       <c r="D27">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E27">
-        <v>0.96299999999999997</v>
+        <v>0.97199999999999998</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -1006,10 +1006,10 @@
         <v>140</v>
       </c>
       <c r="D28">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E28">
-        <v>1.014</v>
+        <v>1.0209999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -1023,10 +1023,10 @@
         <v>128</v>
       </c>
       <c r="D29">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E29">
-        <v>1.0469999999999999</v>
+        <v>1.0549999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1040,10 +1040,10 @@
         <v>119</v>
       </c>
       <c r="D30">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E30">
-        <v>1.042</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -1057,10 +1057,10 @@
         <v>138</v>
       </c>
       <c r="D31">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E31">
-        <v>1.022</v>
+        <v>1.014</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1074,10 +1074,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="E32">
-        <v>1.0529999999999999</v>
+        <v>1.0629999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1091,10 +1091,10 @@
         <v>329</v>
       </c>
       <c r="D33">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E33">
-        <v>1.036</v>
+        <v>1.0329999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1108,10 +1108,10 @@
         <v>323</v>
       </c>
       <c r="D34">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E34">
-        <v>0.98499999999999999</v>
+        <v>0.98799999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1125,10 +1125,10 @@
         <v>218</v>
       </c>
       <c r="D35">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E35">
-        <v>1.0089999999999999</v>
+        <v>1.0049999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1142,10 +1142,10 @@
         <v>250</v>
       </c>
       <c r="D36">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E36">
-        <v>1.032</v>
+        <v>1.036</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1159,10 +1159,10 @@
         <v>217</v>
       </c>
       <c r="D37">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E37">
-        <v>0.96799999999999997</v>
+        <v>0.96299999999999997</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1176,10 +1176,10 @@
         <v>226</v>
       </c>
       <c r="D38">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E38">
-        <v>0.996</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1193,10 +1193,10 @@
         <v>214</v>
       </c>
       <c r="D39">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E39">
-        <v>0.94899999999999995</v>
+        <v>0.94399999999999995</v>
       </c>
     </row>
   </sheetData>

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="112" documentId="8_{D3DC1C62-A0A1-41AB-9E62-302D8C909E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4244F4B2-1821-4517-9DE2-C945A04F4E83}"/>
+  <xr:revisionPtr revIDLastSave="113" documentId="8_{D3DC1C62-A0A1-41AB-9E62-302D8C909E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5D90193-776F-4142-B3BA-482B97DA9E6D}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="mat_2026" sheetId="1" r:id="rId1"/>
@@ -564,10 +564,10 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E2">
-        <v>1.2629999999999999</v>
+        <v>1.3680000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -649,10 +649,10 @@
         <v>61</v>
       </c>
       <c r="D7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E7">
-        <v>1.016</v>
+        <v>1.0329999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -666,10 +666,10 @@
         <v>75</v>
       </c>
       <c r="D8">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E8">
-        <v>1.107</v>
+        <v>1.1200000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -734,10 +734,10 @@
         <v>31</v>
       </c>
       <c r="D12">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E12">
-        <v>1.355</v>
+        <v>1.323</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -870,10 +870,10 @@
         <v>85</v>
       </c>
       <c r="D20">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E20">
-        <v>1.0469999999999999</v>
+        <v>1.0589999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -955,10 +955,10 @@
         <v>91</v>
       </c>
       <c r="D25">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E25">
-        <v>1.044</v>
+        <v>1.0549999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -1023,10 +1023,10 @@
         <v>128</v>
       </c>
       <c r="D29">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E29">
-        <v>1.0549999999999999</v>
+        <v>1.0620000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1040,10 +1040,10 @@
         <v>119</v>
       </c>
       <c r="D30">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E30">
-        <v>1.05</v>
+        <v>1.0669999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -1057,10 +1057,10 @@
         <v>138</v>
       </c>
       <c r="D31">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E31">
-        <v>1.014</v>
+        <v>1.0289999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1074,10 +1074,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E32">
-        <v>1.0629999999999999</v>
+        <v>1.0680000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1091,10 +1091,10 @@
         <v>329</v>
       </c>
       <c r="D33">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E33">
-        <v>1.0329999999999999</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1108,10 +1108,10 @@
         <v>323</v>
       </c>
       <c r="D34">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E34">
-        <v>0.98799999999999999</v>
+        <v>0.98499999999999999</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1142,10 +1142,10 @@
         <v>250</v>
       </c>
       <c r="D36">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="E36">
-        <v>1.036</v>
+        <v>1.048</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1159,10 +1159,10 @@
         <v>217</v>
       </c>
       <c r="D37">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E37">
-        <v>0.96299999999999997</v>
+        <v>0.96799999999999997</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1176,10 +1176,10 @@
         <v>226</v>
       </c>
       <c r="D38">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>1.0129999999999999</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1193,10 +1193,10 @@
         <v>214</v>
       </c>
       <c r="D39">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E39">
-        <v>0.94399999999999995</v>
+        <v>0.94899999999999995</v>
       </c>
     </row>
   </sheetData>

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="113" documentId="8_{D3DC1C62-A0A1-41AB-9E62-302D8C909E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5D90193-776F-4142-B3BA-482B97DA9E6D}"/>
+  <xr:revisionPtr revIDLastSave="114" documentId="8_{D3DC1C62-A0A1-41AB-9E62-302D8C909E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0E30714-B278-4765-AF03-58E6A84C5706}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
@@ -717,10 +717,10 @@
         <v>88</v>
       </c>
       <c r="D11">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E11">
-        <v>1.0569999999999999</v>
+        <v>1.0680000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -734,10 +734,10 @@
         <v>31</v>
       </c>
       <c r="D12">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E12">
-        <v>1.323</v>
+        <v>1.387</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -751,10 +751,10 @@
         <v>35</v>
       </c>
       <c r="D13">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>1.0289999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -768,10 +768,10 @@
         <v>62</v>
       </c>
       <c r="D14">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E14">
-        <v>1.129</v>
+        <v>1.113</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -802,10 +802,10 @@
         <v>63</v>
       </c>
       <c r="D16">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E16">
-        <v>0.90500000000000003</v>
+        <v>0.92100000000000004</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -870,10 +870,10 @@
         <v>85</v>
       </c>
       <c r="D20">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E20">
-        <v>1.0589999999999999</v>
+        <v>1.0349999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -904,10 +904,10 @@
         <v>28</v>
       </c>
       <c r="D22">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E22">
-        <v>1.357</v>
+        <v>1.286</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -938,10 +938,10 @@
         <v>65</v>
       </c>
       <c r="D24">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E24">
-        <v>1.1850000000000001</v>
+        <v>1.169</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -989,10 +989,10 @@
         <v>109</v>
       </c>
       <c r="D27">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E27">
-        <v>0.97199999999999998</v>
+        <v>0.96299999999999997</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -1057,10 +1057,10 @@
         <v>138</v>
       </c>
       <c r="D31">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E31">
-        <v>1.0289999999999999</v>
+        <v>1.0509999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1074,10 +1074,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E32">
-        <v>1.0680000000000001</v>
+        <v>1.071</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1108,10 +1108,10 @@
         <v>323</v>
       </c>
       <c r="D34">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E34">
-        <v>0.98499999999999999</v>
+        <v>0.98099999999999998</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1125,10 +1125,10 @@
         <v>218</v>
       </c>
       <c r="D35">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E35">
-        <v>1.0049999999999999</v>
+        <v>1.0089999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1159,10 +1159,10 @@
         <v>217</v>
       </c>
       <c r="D37">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E37">
-        <v>0.96799999999999997</v>
+        <v>0.96299999999999997</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1176,10 +1176,10 @@
         <v>226</v>
       </c>
       <c r="D38">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E38">
-        <v>1.0129999999999999</v>
+        <v>1.018</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1193,10 +1193,10 @@
         <v>214</v>
       </c>
       <c r="D39">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E39">
-        <v>0.94899999999999995</v>
+        <v>0.95299999999999996</v>
       </c>
     </row>
   </sheetData>

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="114" documentId="8_{D3DC1C62-A0A1-41AB-9E62-302D8C909E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D0E30714-B278-4765-AF03-58E6A84C5706}"/>
+  <xr:revisionPtr revIDLastSave="115" documentId="8_{D3DC1C62-A0A1-41AB-9E62-302D8C909E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4A623AD-9015-4711-8481-BDEB27E4534D}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
@@ -700,10 +700,10 @@
         <v>64</v>
       </c>
       <c r="D10">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E10">
-        <v>1.0780000000000001</v>
+        <v>1.0620000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -734,10 +734,10 @@
         <v>31</v>
       </c>
       <c r="D12">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E12">
-        <v>1.387</v>
+        <v>1.355</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -751,10 +751,10 @@
         <v>35</v>
       </c>
       <c r="D13">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E13">
-        <v>1.0289999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -802,10 +802,10 @@
         <v>63</v>
       </c>
       <c r="D16">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E16">
-        <v>0.92100000000000004</v>
+        <v>0.90500000000000003</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -1023,10 +1023,10 @@
         <v>128</v>
       </c>
       <c r="D29">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E29">
-        <v>1.0620000000000001</v>
+        <v>1.0549999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1057,10 +1057,10 @@
         <v>138</v>
       </c>
       <c r="D31">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E31">
-        <v>1.0509999999999999</v>
+        <v>1.0289999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1091,10 +1091,10 @@
         <v>329</v>
       </c>
       <c r="D33">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E33">
-        <v>1.03</v>
+        <v>1.0269999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1125,10 +1125,10 @@
         <v>218</v>
       </c>
       <c r="D35">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E35">
-        <v>1.0089999999999999</v>
+        <v>1.0049999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="115" documentId="8_{D3DC1C62-A0A1-41AB-9E62-302D8C909E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4A623AD-9015-4711-8481-BDEB27E4534D}"/>
+  <xr:revisionPtr revIDLastSave="118" documentId="8_{D3DC1C62-A0A1-41AB-9E62-302D8C909E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFDE9A86-5766-4FD6-8F9E-30FF641EBD78}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
@@ -179,13 +179,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -537,19 +540,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
@@ -581,10 +584,10 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E3">
-        <v>1.03</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -853,10 +856,10 @@
         <v>89</v>
       </c>
       <c r="D19">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E19">
-        <v>1.0109999999999999</v>
+        <v>0.97799999999999998</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -887,10 +890,10 @@
         <v>88</v>
       </c>
       <c r="D21">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E21">
-        <v>1.0229999999999999</v>
+        <v>1.0109999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -955,10 +958,10 @@
         <v>91</v>
       </c>
       <c r="D25">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E25">
-        <v>1.0549999999999999</v>
+        <v>1.044</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -989,10 +992,10 @@
         <v>109</v>
       </c>
       <c r="D27">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E27">
-        <v>0.96299999999999997</v>
+        <v>0.94499999999999995</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -1006,10 +1009,10 @@
         <v>140</v>
       </c>
       <c r="D28">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E28">
-        <v>1.0209999999999999</v>
+        <v>1.014</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -1023,10 +1026,10 @@
         <v>128</v>
       </c>
       <c r="D29">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E29">
-        <v>1.0549999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1040,10 +1043,10 @@
         <v>119</v>
       </c>
       <c r="D30">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E30">
-        <v>1.0669999999999999</v>
+        <v>1.042</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -1057,10 +1060,10 @@
         <v>138</v>
       </c>
       <c r="D31">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E31">
-        <v>1.0289999999999999</v>
+        <v>1.0509999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1125,10 +1128,10 @@
         <v>218</v>
       </c>
       <c r="D35">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E35">
-        <v>1.0049999999999999</v>
+        <v>1.0089999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1159,10 +1162,10 @@
         <v>217</v>
       </c>
       <c r="D37">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E37">
-        <v>0.96299999999999997</v>
+        <v>0.96799999999999997</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1176,10 +1179,10 @@
         <v>226</v>
       </c>
       <c r="D38">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E38">
-        <v>1.018</v>
+        <v>1.0269999999999999</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="118" documentId="8_{D3DC1C62-A0A1-41AB-9E62-302D8C909E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFDE9A86-5766-4FD6-8F9E-30FF641EBD78}"/>
+  <xr:revisionPtr revIDLastSave="119" documentId="8_{D3DC1C62-A0A1-41AB-9E62-302D8C909E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AB720D0-418E-4553-AEF2-4C8E0608C7BB}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="mat_2026" sheetId="1" r:id="rId1"/>
@@ -771,10 +771,10 @@
         <v>62</v>
       </c>
       <c r="D14">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E14">
-        <v>1.113</v>
+        <v>1.097</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -839,10 +839,10 @@
         <v>75</v>
       </c>
       <c r="D18">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E18">
-        <v>1.0529999999999999</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -873,10 +873,10 @@
         <v>85</v>
       </c>
       <c r="D20">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E20">
-        <v>1.0349999999999999</v>
+        <v>1.024</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -1077,10 +1077,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E32">
-        <v>1.071</v>
+        <v>1.073</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1094,10 +1094,10 @@
         <v>329</v>
       </c>
       <c r="D33">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E33">
-        <v>1.0269999999999999</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1111,10 +1111,10 @@
         <v>323</v>
       </c>
       <c r="D34">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E34">
-        <v>0.98099999999999998</v>
+        <v>0.97799999999999998</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="119" documentId="8_{D3DC1C62-A0A1-41AB-9E62-302D8C909E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AB720D0-418E-4553-AEF2-4C8E0608C7BB}"/>
+  <xr:revisionPtr revIDLastSave="120" documentId="8_{D3DC1C62-A0A1-41AB-9E62-302D8C909E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D53735D1-1DDA-4BC1-9A1D-CE1470F027E6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="mat_2026" sheetId="1" r:id="rId1"/>
@@ -737,10 +737,10 @@
         <v>31</v>
       </c>
       <c r="D12">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E12">
-        <v>1.355</v>
+        <v>1.323</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -1077,10 +1077,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E32">
-        <v>1.073</v>
+        <v>1.0760000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1094,10 +1094,10 @@
         <v>329</v>
       </c>
       <c r="D33">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E33">
-        <v>1.03</v>
+        <v>1.0329999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1111,10 +1111,10 @@
         <v>323</v>
       </c>
       <c r="D34">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E34">
-        <v>0.97799999999999998</v>
+        <v>0.98099999999999998</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1128,10 +1128,10 @@
         <v>218</v>
       </c>
       <c r="D35">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E35">
-        <v>1.0089999999999999</v>
+        <v>1.014</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1179,10 +1179,10 @@
         <v>226</v>
       </c>
       <c r="D38">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E38">
-        <v>1.0269999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1196,10 +1196,10 @@
         <v>214</v>
       </c>
       <c r="D39">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E39">
-        <v>0.95299999999999996</v>
+        <v>0.96299999999999997</v>
       </c>
     </row>
   </sheetData>

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="120" documentId="8_{D3DC1C62-A0A1-41AB-9E62-302D8C909E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D53735D1-1DDA-4BC1-9A1D-CE1470F027E6}"/>
+  <xr:revisionPtr revIDLastSave="121" documentId="8_{D3DC1C62-A0A1-41AB-9E62-302D8C909E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1527510D-6D42-4D58-8011-75595E9F763F}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
@@ -567,10 +567,10 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E2">
-        <v>1.3680000000000001</v>
+        <v>1.3160000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -584,10 +584,10 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -635,10 +635,10 @@
         <v>58</v>
       </c>
       <c r="D6">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E6">
-        <v>1.052</v>
+        <v>1.069</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -652,10 +652,10 @@
         <v>61</v>
       </c>
       <c r="D7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E7">
-        <v>1.0329999999999999</v>
+        <v>1.0489999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -669,10 +669,10 @@
         <v>75</v>
       </c>
       <c r="D8">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E8">
-        <v>1.1200000000000001</v>
+        <v>1.107</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -703,10 +703,10 @@
         <v>64</v>
       </c>
       <c r="D10">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E10">
-        <v>1.0620000000000001</v>
+        <v>1.0780000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -720,10 +720,10 @@
         <v>88</v>
       </c>
       <c r="D11">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E11">
-        <v>1.0680000000000001</v>
+        <v>1.0569999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -754,10 +754,10 @@
         <v>35</v>
       </c>
       <c r="D13">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>1.0289999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -771,10 +771,10 @@
         <v>62</v>
       </c>
       <c r="D14">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E14">
-        <v>1.097</v>
+        <v>1.081</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -788,10 +788,10 @@
         <v>40</v>
       </c>
       <c r="D15">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E15">
-        <v>1.05</v>
+        <v>1.0249999999999999</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -805,10 +805,10 @@
         <v>63</v>
       </c>
       <c r="D16">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E16">
-        <v>0.90500000000000003</v>
+        <v>0.92100000000000004</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -839,10 +839,10 @@
         <v>75</v>
       </c>
       <c r="D18">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E18">
-        <v>1.04</v>
+        <v>1.0669999999999999</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -873,10 +873,10 @@
         <v>85</v>
       </c>
       <c r="D20">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E20">
-        <v>1.024</v>
+        <v>1.0349999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -941,10 +941,10 @@
         <v>65</v>
       </c>
       <c r="D24">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E24">
-        <v>1.169</v>
+        <v>1.1379999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -992,10 +992,10 @@
         <v>109</v>
       </c>
       <c r="D27">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E27">
-        <v>0.94499999999999995</v>
+        <v>0.95399999999999996</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -1026,10 +1026,10 @@
         <v>128</v>
       </c>
       <c r="D29">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E29">
-        <v>1.0309999999999999</v>
+        <v>1.0229999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1060,10 +1060,10 @@
         <v>138</v>
       </c>
       <c r="D31">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E31">
-        <v>1.0509999999999999</v>
+        <v>1.0429999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1077,10 +1077,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E32">
-        <v>1.0760000000000001</v>
+        <v>1.081</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1094,10 +1094,10 @@
         <v>329</v>
       </c>
       <c r="D33">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E33">
-        <v>1.0329999999999999</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1111,10 +1111,10 @@
         <v>323</v>
       </c>
       <c r="D34">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E34">
-        <v>0.98099999999999998</v>
+        <v>0.97799999999999998</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1145,10 +1145,10 @@
         <v>250</v>
       </c>
       <c r="D36">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E36">
-        <v>1.048</v>
+        <v>1.044</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="121" documentId="8_{D3DC1C62-A0A1-41AB-9E62-302D8C909E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1527510D-6D42-4D58-8011-75595E9F763F}"/>
+  <xr:revisionPtr revIDLastSave="122" documentId="8_{D3DC1C62-A0A1-41AB-9E62-302D8C909E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7834D125-3704-47F2-8305-52E957E2B92B}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
@@ -567,10 +567,10 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E2">
-        <v>1.3160000000000001</v>
+        <v>1.2629999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -584,10 +584,10 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E3">
-        <v>1.03</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -618,10 +618,10 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E5">
-        <v>1.2649999999999999</v>
+        <v>1.2350000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -635,10 +635,10 @@
         <v>58</v>
       </c>
       <c r="D6">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E6">
-        <v>1.069</v>
+        <v>1.034</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -652,10 +652,10 @@
         <v>61</v>
       </c>
       <c r="D7">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E7">
-        <v>1.0489999999999999</v>
+        <v>1.016</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -669,10 +669,10 @@
         <v>75</v>
       </c>
       <c r="D8">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E8">
-        <v>1.107</v>
+        <v>1.0669999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -686,10 +686,10 @@
         <v>108</v>
       </c>
       <c r="D9">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E9">
-        <v>1.056</v>
+        <v>1.0189999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -703,10 +703,10 @@
         <v>64</v>
       </c>
       <c r="D10">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E10">
-        <v>1.0780000000000001</v>
+        <v>1.016</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -720,10 +720,10 @@
         <v>88</v>
       </c>
       <c r="D11">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E11">
-        <v>1.0569999999999999</v>
+        <v>1.0229999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -856,10 +856,10 @@
         <v>89</v>
       </c>
       <c r="D19">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E19">
-        <v>0.97799999999999998</v>
+        <v>0.98899999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -907,10 +907,10 @@
         <v>28</v>
       </c>
       <c r="D22">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E22">
-        <v>1.286</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -941,10 +941,10 @@
         <v>65</v>
       </c>
       <c r="D24">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E24">
-        <v>1.1379999999999999</v>
+        <v>1.123</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -1026,10 +1026,10 @@
         <v>128</v>
       </c>
       <c r="D29">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E29">
-        <v>1.0229999999999999</v>
+        <v>1.0389999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1077,10 +1077,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="E32">
-        <v>1.081</v>
+        <v>1.0660000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1094,10 +1094,10 @@
         <v>329</v>
       </c>
       <c r="D33">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E33">
-        <v>1.04</v>
+        <v>1.036</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1111,10 +1111,10 @@
         <v>323</v>
       </c>
       <c r="D34">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="E34">
-        <v>0.97799999999999998</v>
+        <v>0.96899999999999997</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1145,10 +1145,10 @@
         <v>250</v>
       </c>
       <c r="D36">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="E36">
-        <v>1.044</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1162,10 +1162,10 @@
         <v>217</v>
       </c>
       <c r="D37">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E37">
-        <v>0.96799999999999997</v>
+        <v>0.95899999999999996</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1196,10 +1196,10 @@
         <v>214</v>
       </c>
       <c r="D39">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="E39">
-        <v>0.96299999999999997</v>
+        <v>0.96699999999999997</v>
       </c>
     </row>
   </sheetData>

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="122" documentId="8_{D3DC1C62-A0A1-41AB-9E62-302D8C909E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7834D125-3704-47F2-8305-52E957E2B92B}"/>
+  <xr:revisionPtr revIDLastSave="123" documentId="8_{D3DC1C62-A0A1-41AB-9E62-302D8C909E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DDF85A8-231D-4B80-8A8B-822393E38D4E}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
@@ -788,10 +788,10 @@
         <v>40</v>
       </c>
       <c r="D15">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E15">
-        <v>1.0249999999999999</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -839,10 +839,10 @@
         <v>75</v>
       </c>
       <c r="D18">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E18">
-        <v>1.0669999999999999</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -856,10 +856,10 @@
         <v>89</v>
       </c>
       <c r="D19">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E19">
-        <v>0.98899999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1043,10 +1043,10 @@
         <v>119</v>
       </c>
       <c r="D30">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E30">
-        <v>1.042</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -1077,10 +1077,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E32">
-        <v>1.0660000000000001</v>
+        <v>1.071</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1162,10 +1162,10 @@
         <v>217</v>
       </c>
       <c r="D37">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E37">
-        <v>0.95899999999999996</v>
+        <v>0.94899999999999995</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="123" documentId="8_{D3DC1C62-A0A1-41AB-9E62-302D8C909E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DDF85A8-231D-4B80-8A8B-822393E38D4E}"/>
+  <xr:revisionPtr revIDLastSave="124" documentId="8_{D3DC1C62-A0A1-41AB-9E62-302D8C909E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CC5F55F-50D4-45AC-A0B3-A16807694C25}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="mat_2026" sheetId="1" r:id="rId1"/>
@@ -652,10 +652,10 @@
         <v>61</v>
       </c>
       <c r="D7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E7">
-        <v>1.016</v>
+        <v>1.0329999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -669,10 +669,10 @@
         <v>75</v>
       </c>
       <c r="D8">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E8">
-        <v>1.0669999999999999</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -771,10 +771,10 @@
         <v>62</v>
       </c>
       <c r="D14">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E14">
-        <v>1.081</v>
+        <v>1.032</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -805,10 +805,10 @@
         <v>63</v>
       </c>
       <c r="D16">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E16">
-        <v>0.92100000000000004</v>
+        <v>0.90500000000000003</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -873,10 +873,10 @@
         <v>85</v>
       </c>
       <c r="D20">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E20">
-        <v>1.0349999999999999</v>
+        <v>1.024</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -941,10 +941,10 @@
         <v>65</v>
       </c>
       <c r="D24">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E24">
-        <v>1.123</v>
+        <v>1.1080000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -975,10 +975,10 @@
         <v>83</v>
       </c>
       <c r="D26">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E26">
-        <v>1.012</v>
+        <v>1.024</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -992,10 +992,10 @@
         <v>109</v>
       </c>
       <c r="D27">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E27">
-        <v>0.95399999999999996</v>
+        <v>0.96299999999999997</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -1026,10 +1026,10 @@
         <v>128</v>
       </c>
       <c r="D29">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E29">
-        <v>1.0389999999999999</v>
+        <v>1.0309999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1043,10 +1043,10 @@
         <v>119</v>
       </c>
       <c r="D30">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E30">
-        <v>1.05</v>
+        <v>1.042</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -1077,10 +1077,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="E32">
-        <v>1.071</v>
+        <v>1.0780000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1094,10 +1094,10 @@
         <v>329</v>
       </c>
       <c r="D33">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E33">
-        <v>1.036</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1111,10 +1111,10 @@
         <v>323</v>
       </c>
       <c r="D34">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E34">
-        <v>0.96899999999999997</v>
+        <v>0.97499999999999998</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1128,10 +1128,10 @@
         <v>218</v>
       </c>
       <c r="D35">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E35">
-        <v>1.014</v>
+        <v>1.0089999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1162,10 +1162,10 @@
         <v>217</v>
       </c>
       <c r="D37">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="E37">
-        <v>0.94899999999999995</v>
+        <v>0.97699999999999998</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1179,10 +1179,10 @@
         <v>226</v>
       </c>
       <c r="D38">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E38">
-        <v>1.0309999999999999</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1196,10 +1196,10 @@
         <v>214</v>
       </c>
       <c r="D39">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E39">
-        <v>0.96699999999999997</v>
+        <v>0.95799999999999996</v>
       </c>
     </row>
   </sheetData>

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="124" documentId="8_{D3DC1C62-A0A1-41AB-9E62-302D8C909E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CC5F55F-50D4-45AC-A0B3-A16807694C25}"/>
+  <xr:revisionPtr revIDLastSave="125" documentId="8_{D3DC1C62-A0A1-41AB-9E62-302D8C909E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBADE8B7-176A-40B7-8228-9E684F341D9D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="mat_2026" sheetId="1" r:id="rId1"/>
@@ -567,10 +567,10 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2">
-        <v>1.2629999999999999</v>
+        <v>1.3160000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -737,10 +737,10 @@
         <v>31</v>
       </c>
       <c r="D12">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E12">
-        <v>1.323</v>
+        <v>1.355</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -788,10 +788,10 @@
         <v>40</v>
       </c>
       <c r="D15">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E15">
-        <v>1.05</v>
+        <v>1.075</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -822,10 +822,10 @@
         <v>68</v>
       </c>
       <c r="D17">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E17">
-        <v>1.044</v>
+        <v>1.0589999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -924,10 +924,10 @@
         <v>38</v>
       </c>
       <c r="D23">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E23">
-        <v>1.079</v>
+        <v>1.0529999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -992,10 +992,10 @@
         <v>109</v>
       </c>
       <c r="D27">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E27">
-        <v>0.96299999999999997</v>
+        <v>0.97199999999999998</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -1009,10 +1009,10 @@
         <v>140</v>
       </c>
       <c r="D28">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E28">
-        <v>1.014</v>
+        <v>1.0209999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -1026,10 +1026,10 @@
         <v>128</v>
       </c>
       <c r="D29">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E29">
-        <v>1.0309999999999999</v>
+        <v>1.0389999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1077,10 +1077,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="E32">
-        <v>1.0780000000000001</v>
+        <v>1.0880000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1111,10 +1111,10 @@
         <v>323</v>
       </c>
       <c r="D34">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E34">
-        <v>0.97499999999999998</v>
+        <v>0.97199999999999998</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1145,10 +1145,10 @@
         <v>250</v>
       </c>
       <c r="D36">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E36">
-        <v>1.02</v>
+        <v>1.012</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1162,10 +1162,10 @@
         <v>217</v>
       </c>
       <c r="D37">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E37">
-        <v>0.97699999999999998</v>
+        <v>0.98199999999999998</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1179,10 +1179,10 @@
         <v>226</v>
       </c>
       <c r="D38">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E38">
-        <v>1.04</v>
+        <v>1.044</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1196,10 +1196,10 @@
         <v>214</v>
       </c>
       <c r="D39">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E39">
-        <v>0.95799999999999996</v>
+        <v>0.95299999999999996</v>
       </c>
     </row>
   </sheetData>

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Documentos\Proyect_Phyton\Proyect_multi_page\src\pages\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="125" documentId="8_{D3DC1C62-A0A1-41AB-9E62-302D8C909E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBADE8B7-176A-40B7-8228-9E684F341D9D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7248E41D-24BF-48E7-955F-87A06B5DD277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="mat_2026" sheetId="1" r:id="rId1"/>
@@ -206,10 +206,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -788,10 +784,10 @@
         <v>40</v>
       </c>
       <c r="D15">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E15">
-        <v>1.075</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -839,10 +835,10 @@
         <v>75</v>
       </c>
       <c r="D18">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E18">
-        <v>1.08</v>
+        <v>1.093</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -873,10 +869,10 @@
         <v>85</v>
       </c>
       <c r="D20">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E20">
-        <v>1.024</v>
+        <v>1.0349999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -924,10 +920,10 @@
         <v>38</v>
       </c>
       <c r="D23">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E23">
-        <v>1.0529999999999999</v>
+        <v>1.079</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -941,10 +937,10 @@
         <v>65</v>
       </c>
       <c r="D24">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E24">
-        <v>1.1080000000000001</v>
+        <v>1.123</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -1043,10 +1039,10 @@
         <v>119</v>
       </c>
       <c r="D30">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E30">
-        <v>1.042</v>
+        <v>1.0589999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -1077,10 +1073,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E32">
-        <v>1.0880000000000001</v>
+        <v>1.091</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1145,10 +1141,10 @@
         <v>250</v>
       </c>
       <c r="D36">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E36">
-        <v>1.012</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1179,10 +1175,10 @@
         <v>226</v>
       </c>
       <c r="D38">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E38">
-        <v>1.044</v>
+        <v>1.0529999999999999</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Documentos\Proyect_Phyton\Proyect_multi_page\src\pages\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7248E41D-24BF-48E7-955F-87A06B5DD277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{7248E41D-24BF-48E7-955F-87A06B5DD277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D5ED7E9-14A4-4779-917F-EF73AD49EC06}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
@@ -869,10 +869,10 @@
         <v>85</v>
       </c>
       <c r="D20">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E20">
-        <v>1.0349999999999999</v>
+        <v>1.0469999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -903,10 +903,10 @@
         <v>28</v>
       </c>
       <c r="D22">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E22">
-        <v>1.25</v>
+        <v>1.286</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1039,10 +1039,10 @@
         <v>119</v>
       </c>
       <c r="D30">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E30">
-        <v>1.0589999999999999</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -1073,10 +1073,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E32">
-        <v>1.091</v>
+        <v>1.0860000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1124,10 +1124,10 @@
         <v>218</v>
       </c>
       <c r="D35">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E35">
-        <v>1.0089999999999999</v>
+        <v>1.0049999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1141,10 +1141,10 @@
         <v>250</v>
       </c>
       <c r="D36">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E36">
-        <v>1.02</v>
+        <v>1.016</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1175,10 +1175,10 @@
         <v>226</v>
       </c>
       <c r="D38">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E38">
-        <v>1.0529999999999999</v>
+        <v>1.0620000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{7248E41D-24BF-48E7-955F-87A06B5DD277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D5ED7E9-14A4-4779-917F-EF73AD49EC06}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{7248E41D-24BF-48E7-955F-87A06B5DD277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D386E711-AEB0-4A57-BE57-4FB4404CB512}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
@@ -206,6 +206,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -563,10 +567,10 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E2">
-        <v>1.3160000000000001</v>
+        <v>1.2629999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -614,10 +618,10 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E5">
-        <v>1.2350000000000001</v>
+        <v>1.206</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -648,10 +652,10 @@
         <v>61</v>
       </c>
       <c r="D7">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E7">
-        <v>1.0329999999999999</v>
+        <v>1.016</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -699,10 +703,10 @@
         <v>64</v>
       </c>
       <c r="D10">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E10">
-        <v>1.016</v>
+        <v>1.0309999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -716,10 +720,10 @@
         <v>88</v>
       </c>
       <c r="D11">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E11">
-        <v>1.0229999999999999</v>
+        <v>1.0109999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -733,10 +737,10 @@
         <v>31</v>
       </c>
       <c r="D12">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E12">
-        <v>1.355</v>
+        <v>1.419</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -767,10 +771,10 @@
         <v>62</v>
       </c>
       <c r="D14">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E14">
-        <v>1.032</v>
+        <v>1.048</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -801,10 +805,10 @@
         <v>63</v>
       </c>
       <c r="D16">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E16">
-        <v>0.90500000000000003</v>
+        <v>0.92100000000000004</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -835,10 +839,10 @@
         <v>75</v>
       </c>
       <c r="D18">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E18">
-        <v>1.093</v>
+        <v>1.107</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -869,10 +873,10 @@
         <v>85</v>
       </c>
       <c r="D20">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E20">
-        <v>1.0469999999999999</v>
+        <v>1.0589999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -1141,10 +1145,10 @@
         <v>250</v>
       </c>
       <c r="D36">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E36">
-        <v>1.016</v>
+        <v>1.012</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1175,10 +1179,10 @@
         <v>226</v>
       </c>
       <c r="D38">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="E38">
-        <v>1.0620000000000001</v>
+        <v>1.0660000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{7248E41D-24BF-48E7-955F-87A06B5DD277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D386E711-AEB0-4A57-BE57-4FB4404CB512}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{7248E41D-24BF-48E7-955F-87A06B5DD277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D8A0649-CB47-40CF-A03B-8AB573237701}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="mat_2026" sheetId="1" r:id="rId1"/>
@@ -771,10 +771,10 @@
         <v>62</v>
       </c>
       <c r="D14">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E14">
-        <v>1.048</v>
+        <v>1.0649999999999999</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -873,10 +873,10 @@
         <v>85</v>
       </c>
       <c r="D20">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E20">
-        <v>1.0589999999999999</v>
+        <v>1.0469999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -992,10 +992,10 @@
         <v>109</v>
       </c>
       <c r="D27">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E27">
-        <v>0.97199999999999998</v>
+        <v>0.98199999999999998</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -1077,10 +1077,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E32">
-        <v>1.0860000000000001</v>
+        <v>1.0880000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1145,10 +1145,10 @@
         <v>250</v>
       </c>
       <c r="D36">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E36">
-        <v>1.012</v>
+        <v>1.008</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{7248E41D-24BF-48E7-955F-87A06B5DD277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D8A0649-CB47-40CF-A03B-8AB573237701}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{7248E41D-24BF-48E7-955F-87A06B5DD277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{055F4404-566C-4833-B6DD-D8E08F79CB38}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="mat_2026" sheetId="1" r:id="rId1"/>
@@ -669,10 +669,10 @@
         <v>75</v>
       </c>
       <c r="D8">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E8">
-        <v>1.08</v>
+        <v>1.093</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -805,10 +805,10 @@
         <v>63</v>
       </c>
       <c r="D16">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E16">
-        <v>0.92100000000000004</v>
+        <v>0.95199999999999996</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -839,10 +839,10 @@
         <v>75</v>
       </c>
       <c r="D18">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E18">
-        <v>1.107</v>
+        <v>1.1200000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -941,10 +941,10 @@
         <v>65</v>
       </c>
       <c r="D24">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E24">
-        <v>1.123</v>
+        <v>1.1539999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -958,10 +958,10 @@
         <v>91</v>
       </c>
       <c r="D25">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E25">
-        <v>1.044</v>
+        <v>1.0329999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -1026,10 +1026,10 @@
         <v>128</v>
       </c>
       <c r="D29">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E29">
-        <v>1.0389999999999999</v>
+        <v>1.0469999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1060,10 +1060,10 @@
         <v>138</v>
       </c>
       <c r="D31">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E31">
-        <v>1.0429999999999999</v>
+        <v>1.036</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1077,10 +1077,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="E32">
-        <v>1.0880000000000001</v>
+        <v>1.081</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1094,10 +1094,10 @@
         <v>329</v>
       </c>
       <c r="D33">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E33">
-        <v>1.04</v>
+        <v>1.0429999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1111,10 +1111,10 @@
         <v>323</v>
       </c>
       <c r="D34">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E34">
-        <v>0.97199999999999998</v>
+        <v>0.97499999999999998</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1145,10 +1145,10 @@
         <v>250</v>
       </c>
       <c r="D36">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E36">
-        <v>1.008</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1162,10 +1162,10 @@
         <v>217</v>
       </c>
       <c r="D37">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E37">
-        <v>0.98199999999999998</v>
+        <v>0.99099999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1196,10 +1196,10 @@
         <v>214</v>
       </c>
       <c r="D39">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E39">
-        <v>0.95299999999999996</v>
+        <v>0.95799999999999996</v>
       </c>
     </row>
   </sheetData>

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Documentos\Proyect_Phyton\Proyect_multi_page\src\pages\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{7248E41D-24BF-48E7-955F-87A06B5DD277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{055F4404-566C-4833-B6DD-D8E08F79CB38}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
@@ -206,10 +206,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -669,10 +665,10 @@
         <v>75</v>
       </c>
       <c r="D8">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E8">
-        <v>1.093</v>
+        <v>1.1200000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -754,10 +750,10 @@
         <v>35</v>
       </c>
       <c r="D13">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E13">
-        <v>1.0289999999999999</v>
+        <v>1.0569999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -771,10 +767,10 @@
         <v>62</v>
       </c>
       <c r="D14">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E14">
-        <v>1.0649999999999999</v>
+        <v>1.032</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -1043,10 +1039,10 @@
         <v>119</v>
       </c>
       <c r="D30">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E30">
-        <v>1.05</v>
+        <v>1.042</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -1111,10 +1107,10 @@
         <v>323</v>
       </c>
       <c r="D34">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E34">
-        <v>0.97499999999999998</v>
+        <v>0.97199999999999998</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1145,10 +1141,10 @@
         <v>250</v>
       </c>
       <c r="D36">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>1.004</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1162,10 +1158,10 @@
         <v>217</v>
       </c>
       <c r="D37">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E37">
-        <v>0.99099999999999999</v>
+        <v>0.98599999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Documentos\Proyect_Phyton\Proyect_multi_page\src\pages\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA842C35-391A-4C41-983F-20D540D53443}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
@@ -648,10 +648,10 @@
         <v>61</v>
       </c>
       <c r="D7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E7">
-        <v>1.016</v>
+        <v>1.0329999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -682,10 +682,10 @@
         <v>108</v>
       </c>
       <c r="D9">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E9">
-        <v>1.0189999999999999</v>
+        <v>1.0089999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -699,10 +699,10 @@
         <v>64</v>
       </c>
       <c r="D10">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E10">
-        <v>1.0309999999999999</v>
+        <v>1.0620000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -767,10 +767,10 @@
         <v>62</v>
       </c>
       <c r="D14">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E14">
-        <v>1.032</v>
+        <v>1.048</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -818,10 +818,10 @@
         <v>68</v>
       </c>
       <c r="D17">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E17">
-        <v>1.0589999999999999</v>
+        <v>1.0149999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -852,10 +852,10 @@
         <v>89</v>
       </c>
       <c r="D19">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>1.0109999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -869,10 +869,10 @@
         <v>85</v>
       </c>
       <c r="D20">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E20">
-        <v>1.0469999999999999</v>
+        <v>1.024</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -886,10 +886,10 @@
         <v>88</v>
       </c>
       <c r="D21">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E21">
-        <v>1.0109999999999999</v>
+        <v>1.0229999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -971,10 +971,10 @@
         <v>83</v>
       </c>
       <c r="D26">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E26">
-        <v>1.024</v>
+        <v>1.012</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -1005,10 +1005,10 @@
         <v>140</v>
       </c>
       <c r="D28">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E28">
-        <v>1.0209999999999999</v>
+        <v>1.0289999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -1022,10 +1022,10 @@
         <v>128</v>
       </c>
       <c r="D29">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E29">
-        <v>1.0469999999999999</v>
+        <v>1.0549999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1039,10 +1039,10 @@
         <v>119</v>
       </c>
       <c r="D30">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E30">
-        <v>1.042</v>
+        <v>1.034</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -1073,10 +1073,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E32">
-        <v>1.081</v>
+        <v>1.0760000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1124,10 +1124,10 @@
         <v>218</v>
       </c>
       <c r="D35">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E35">
-        <v>1.0049999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1141,10 +1141,10 @@
         <v>250</v>
       </c>
       <c r="D36">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E36">
-        <v>1.004</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1158,10 +1158,10 @@
         <v>217</v>
       </c>
       <c r="D37">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E37">
-        <v>0.98599999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA842C35-391A-4C41-983F-20D540D53443}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8837A9A-FCB5-4119-9AD9-EE068CF52961}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
@@ -631,10 +631,10 @@
         <v>58</v>
       </c>
       <c r="D6">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E6">
-        <v>1.034</v>
+        <v>1.052</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -699,10 +699,10 @@
         <v>64</v>
       </c>
       <c r="D10">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E10">
-        <v>1.0620000000000001</v>
+        <v>1.0780000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -716,10 +716,10 @@
         <v>88</v>
       </c>
       <c r="D11">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E11">
-        <v>1.0109999999999999</v>
+        <v>1.034</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -733,10 +733,10 @@
         <v>31</v>
       </c>
       <c r="D12">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E12">
-        <v>1.419</v>
+        <v>1.387</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -835,10 +835,10 @@
         <v>75</v>
       </c>
       <c r="D18">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E18">
-        <v>1.1200000000000001</v>
+        <v>1.107</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -869,10 +869,10 @@
         <v>85</v>
       </c>
       <c r="D20">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E20">
-        <v>1.024</v>
+        <v>1.012</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -886,10 +886,10 @@
         <v>88</v>
       </c>
       <c r="D21">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E21">
-        <v>1.0229999999999999</v>
+        <v>1.0109999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -1039,10 +1039,10 @@
         <v>119</v>
       </c>
       <c r="D30">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E30">
-        <v>1.034</v>
+        <v>1.0249999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -1073,10 +1073,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="E32">
-        <v>1.0760000000000001</v>
+        <v>1.083</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1090,10 +1090,10 @@
         <v>329</v>
       </c>
       <c r="D33">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E33">
-        <v>1.0429999999999999</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1107,10 +1107,10 @@
         <v>323</v>
       </c>
       <c r="D34">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E34">
-        <v>0.97199999999999998</v>
+        <v>0.96599999999999997</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1158,10 +1158,10 @@
         <v>217</v>
       </c>
       <c r="D37">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>1.0089999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8837A9A-FCB5-4119-9AD9-EE068CF52961}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12D34911-E3B3-4872-A7EF-C51CDD2F7C03}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
@@ -206,6 +206,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -971,10 +975,10 @@
         <v>83</v>
       </c>
       <c r="D26">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E26">
-        <v>1.012</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -1005,10 +1009,10 @@
         <v>140</v>
       </c>
       <c r="D28">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E28">
-        <v>1.0289999999999999</v>
+        <v>1.036</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -1039,10 +1043,10 @@
         <v>119</v>
       </c>
       <c r="D30">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E30">
-        <v>1.0249999999999999</v>
+        <v>1.0169999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12D34911-E3B3-4872-A7EF-C51CDD2F7C03}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{683193B8-8EF0-49B3-BBBF-F2C372EA6D1A}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
@@ -601,10 +601,10 @@
         <v>46</v>
       </c>
       <c r="D4">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E4">
-        <v>1.1519999999999999</v>
+        <v>1.1739999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -669,10 +669,10 @@
         <v>75</v>
       </c>
       <c r="D8">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E8">
-        <v>1.1200000000000001</v>
+        <v>1.107</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -754,10 +754,10 @@
         <v>35</v>
       </c>
       <c r="D13">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E13">
-        <v>1.0569999999999999</v>
+        <v>1.0289999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -839,10 +839,10 @@
         <v>75</v>
       </c>
       <c r="D18">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E18">
-        <v>1.107</v>
+        <v>1.093</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -907,10 +907,10 @@
         <v>28</v>
       </c>
       <c r="D22">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E22">
-        <v>1.286</v>
+        <v>1.321</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1060,10 +1060,10 @@
         <v>138</v>
       </c>
       <c r="D31">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E31">
-        <v>1.036</v>
+        <v>1.0509999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1094,10 +1094,10 @@
         <v>329</v>
       </c>
       <c r="D33">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E33">
-        <v>1.04</v>
+        <v>1.0429999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1145,10 +1145,10 @@
         <v>250</v>
       </c>
       <c r="D36">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>0.996</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1179,10 +1179,10 @@
         <v>226</v>
       </c>
       <c r="D38">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E38">
-        <v>1.0660000000000001</v>
+        <v>1.071</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{683193B8-8EF0-49B3-BBBF-F2C372EA6D1A}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{725895F4-744C-43C7-A8DD-0EACED974466}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
@@ -618,10 +618,10 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E5">
-        <v>1.206</v>
+        <v>1.2649999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -652,10 +652,10 @@
         <v>61</v>
       </c>
       <c r="D7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E7">
-        <v>1.0329999999999999</v>
+        <v>1.0489999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -754,10 +754,10 @@
         <v>35</v>
       </c>
       <c r="D13">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E13">
-        <v>1.0289999999999999</v>
+        <v>1.0569999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -873,10 +873,10 @@
         <v>85</v>
       </c>
       <c r="D20">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E20">
-        <v>1.012</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -1077,10 +1077,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E32">
-        <v>1.083</v>
+        <v>1.0760000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{725895F4-744C-43C7-A8DD-0EACED974466}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{395A80AE-B65F-4731-A91C-B24FBE8322B3}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
@@ -669,10 +669,10 @@
         <v>75</v>
       </c>
       <c r="D8">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E8">
-        <v>1.107</v>
+        <v>1.093</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1043,10 +1043,10 @@
         <v>119</v>
       </c>
       <c r="D30">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E30">
-        <v>1.0169999999999999</v>
+        <v>1.008</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -1077,10 +1077,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E32">
-        <v>1.0760000000000001</v>
+        <v>1.073</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1128,10 +1128,10 @@
         <v>218</v>
       </c>
       <c r="D35">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>1.0049999999999999</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{395A80AE-B65F-4731-A91C-B24FBE8322B3}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B86B45AB-1396-4C4C-B331-C82739A2DA9B}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="mat_2026" sheetId="1" r:id="rId1"/>
@@ -754,10 +754,10 @@
         <v>35</v>
       </c>
       <c r="D13">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E13">
-        <v>1.0569999999999999</v>
+        <v>1.0860000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -822,10 +822,10 @@
         <v>68</v>
       </c>
       <c r="D17">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E17">
-        <v>1.0149999999999999</v>
+        <v>1.0289999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -873,10 +873,10 @@
         <v>85</v>
       </c>
       <c r="D20">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>1.012</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -975,10 +975,10 @@
         <v>83</v>
       </c>
       <c r="D26">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0.98799999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{395A80AE-B65F-4731-A91C-B24FBE8322B3}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{037C98C7-230F-4B6C-9E1B-71EF9DB74B18}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
@@ -754,10 +754,10 @@
         <v>35</v>
       </c>
       <c r="D13">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E13">
-        <v>1.0569999999999999</v>
+        <v>1.0860000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -822,10 +822,10 @@
         <v>68</v>
       </c>
       <c r="D17">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E17">
-        <v>1.0149999999999999</v>
+        <v>1.0289999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -873,10 +873,10 @@
         <v>85</v>
       </c>
       <c r="D20">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>1.012</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -975,10 +975,10 @@
         <v>83</v>
       </c>
       <c r="D26">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>0.98799999999999999</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{037C98C7-230F-4B6C-9E1B-71EF9DB74B18}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8966BD0F-BAA4-4E47-A33A-FBF6CA16C882}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="mat_2026" sheetId="1" r:id="rId1"/>
@@ -703,10 +703,10 @@
         <v>64</v>
       </c>
       <c r="D10">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E10">
-        <v>1.0780000000000001</v>
+        <v>1.0620000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -720,10 +720,10 @@
         <v>88</v>
       </c>
       <c r="D11">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E11">
-        <v>1.034</v>
+        <v>1.0449999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -1077,10 +1077,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E32">
-        <v>1.073</v>
+        <v>1.0780000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1094,10 +1094,10 @@
         <v>329</v>
       </c>
       <c r="D33">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E33">
-        <v>1.0429999999999999</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1111,10 +1111,10 @@
         <v>323</v>
       </c>
       <c r="D34">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E34">
-        <v>0.96599999999999997</v>
+        <v>0.96299999999999997</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1162,10 +1162,10 @@
         <v>217</v>
       </c>
       <c r="D37">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E37">
-        <v>1.0089999999999999</v>
+        <v>1.0049999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8966BD0F-BAA4-4E47-A33A-FBF6CA16C882}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B47AA4D-07C5-4EFF-829B-7AB7BACE42EA}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="mat_2026" sheetId="1" r:id="rId1"/>
@@ -206,10 +206,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -890,10 +886,10 @@
         <v>88</v>
       </c>
       <c r="D21">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E21">
-        <v>1.0109999999999999</v>
+        <v>1.0229999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -907,10 +903,10 @@
         <v>28</v>
       </c>
       <c r="D22">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E22">
-        <v>1.321</v>
+        <v>1.286</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -992,10 +988,10 @@
         <v>109</v>
       </c>
       <c r="D27">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E27">
-        <v>0.98199999999999998</v>
+        <v>0.97199999999999998</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -1026,10 +1022,10 @@
         <v>128</v>
       </c>
       <c r="D29">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E29">
-        <v>1.0549999999999999</v>
+        <v>1.0469999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1043,10 +1039,10 @@
         <v>119</v>
       </c>
       <c r="D30">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E30">
-        <v>1.008</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -1060,10 +1056,10 @@
         <v>138</v>
       </c>
       <c r="D31">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E31">
-        <v>1.0509999999999999</v>
+        <v>1.0580000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1077,10 +1073,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E32">
-        <v>1.0780000000000001</v>
+        <v>1.083</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B47AA4D-07C5-4EFF-829B-7AB7BACE42EA}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46372787-35E8-427F-B5E2-1C5D123F4DD7}"/>
   <bookViews>
     <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
@@ -206,6 +206,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -682,10 +686,10 @@
         <v>108</v>
       </c>
       <c r="D9">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E9">
-        <v>1.0089999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -716,10 +720,10 @@
         <v>88</v>
       </c>
       <c r="D11">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E11">
-        <v>1.0449999999999999</v>
+        <v>1.0569999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -750,10 +754,10 @@
         <v>35</v>
       </c>
       <c r="D13">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E13">
-        <v>1.0860000000000001</v>
+        <v>1.1140000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -801,10 +805,10 @@
         <v>63</v>
       </c>
       <c r="D16">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E16">
-        <v>0.95199999999999996</v>
+        <v>0.96799999999999997</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -835,10 +839,10 @@
         <v>75</v>
       </c>
       <c r="D18">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E18">
-        <v>1.093</v>
+        <v>1.107</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -903,10 +907,10 @@
         <v>28</v>
       </c>
       <c r="D22">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E22">
-        <v>1.286</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -937,10 +941,10 @@
         <v>65</v>
       </c>
       <c r="D24">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E24">
-        <v>1.1539999999999999</v>
+        <v>1.1379999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -1073,10 +1077,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="E32">
-        <v>1.083</v>
+        <v>1.081</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1090,10 +1094,10 @@
         <v>329</v>
       </c>
       <c r="D33">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E33">
-        <v>1.04</v>
+        <v>1.0429999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1141,10 +1145,10 @@
         <v>250</v>
       </c>
       <c r="D36">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E36">
-        <v>0.996</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1158,10 +1162,10 @@
         <v>217</v>
       </c>
       <c r="D37">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E37">
-        <v>1.0049999999999999</v>
+        <v>1.0089999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1175,10 +1179,10 @@
         <v>226</v>
       </c>
       <c r="D38">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E38">
-        <v>1.071</v>
+        <v>1.0840000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1192,10 +1196,10 @@
         <v>214</v>
       </c>
       <c r="D39">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E39">
-        <v>0.95799999999999996</v>
+        <v>0.95299999999999996</v>
       </c>
     </row>
   </sheetData>

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46372787-35E8-427F-B5E2-1C5D123F4DD7}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48EA67D6-54B8-4120-A206-DEE64ADF7599}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="mat_2026" sheetId="1" r:id="rId1"/>
     <sheet name="proyeccion_2026" sheetId="2" r:id="rId2"/>
+    <sheet name="genero" sheetId="3" r:id="rId3"/>
+    <sheet name="mat_time" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">mat_2026!$A$1:$E$39</definedName>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="39">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -137,6 +139,27 @@
   <si>
     <t>% ALCANZADO PROYECCIÓN</t>
   </si>
+  <si>
+    <t>Sexo</t>
+  </si>
+  <si>
+    <t>RECUENTO</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>ESTUDIANTES</t>
+  </si>
+  <si>
+    <t>UE</t>
+  </si>
+  <si>
+    <t>MATRICULA</t>
+  </si>
 </sst>
 </file>
 
@@ -179,7 +202,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -190,6 +213,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -720,10 +744,10 @@
         <v>88</v>
       </c>
       <c r="D11">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E11">
-        <v>1.0569999999999999</v>
+        <v>1.0680000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -907,10 +931,10 @@
         <v>28</v>
       </c>
       <c r="D22">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E22">
-        <v>1.25</v>
+        <v>1.286</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1375,4 +1399,2617 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AA5CF5E-5BFB-4AEA-AE46-C69F6039886F}">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11">
+        <v>430</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD19485A-0629-47F9-A5AD-80ABA7A6E076}">
+  <dimension ref="A1:C224"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="4">
+        <v>46009</v>
+      </c>
+      <c r="C2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="4">
+        <v>46008</v>
+      </c>
+      <c r="C3">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C4">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="4">
+        <v>46001</v>
+      </c>
+      <c r="C5">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="4">
+        <v>46002</v>
+      </c>
+      <c r="C6">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="4">
+        <v>46014</v>
+      </c>
+      <c r="C7">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="4">
+        <v>46006</v>
+      </c>
+      <c r="C8">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="4">
+        <v>46013</v>
+      </c>
+      <c r="C9">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="4">
+        <v>46007</v>
+      </c>
+      <c r="C10">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="4">
+        <v>46147</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="4">
+        <v>46077</v>
+      </c>
+      <c r="C12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="4">
+        <v>46003</v>
+      </c>
+      <c r="C13">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="4">
+        <v>46010</v>
+      </c>
+      <c r="C14">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="4">
+        <v>46079</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="4">
+        <v>46020</v>
+      </c>
+      <c r="C16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4">
+        <v>46015</v>
+      </c>
+      <c r="C17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="4">
+        <v>46083</v>
+      </c>
+      <c r="C18">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="4">
+        <v>46097</v>
+      </c>
+      <c r="C19">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="4">
+        <v>46021</v>
+      </c>
+      <c r="C20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="4">
+        <v>46080</v>
+      </c>
+      <c r="C21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="4">
+        <v>46087</v>
+      </c>
+      <c r="C22">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="4">
+        <v>46022</v>
+      </c>
+      <c r="C23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" s="4">
+        <v>46086</v>
+      </c>
+      <c r="C24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" s="4">
+        <v>46076</v>
+      </c>
+      <c r="C25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" s="4">
+        <v>46136</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" s="4">
+        <v>46078</v>
+      </c>
+      <c r="C27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" s="4">
+        <v>46098</v>
+      </c>
+      <c r="C28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" s="4">
+        <v>46084</v>
+      </c>
+      <c r="C29">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" s="4">
+        <v>46099</v>
+      </c>
+      <c r="C30">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31" s="4">
+        <v>46128</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" s="4">
+        <v>46141</v>
+      </c>
+      <c r="C32">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33" s="4">
+        <v>46132</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>16</v>
+      </c>
+      <c r="B34" s="4">
+        <v>46127</v>
+      </c>
+      <c r="C34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B35" s="4">
+        <v>46091</v>
+      </c>
+      <c r="C35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>16</v>
+      </c>
+      <c r="B36" s="4">
+        <v>46104</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>16</v>
+      </c>
+      <c r="B37" s="4">
+        <v>46140</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>16</v>
+      </c>
+      <c r="B38" s="4">
+        <v>46106</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>16</v>
+      </c>
+      <c r="B39" s="4">
+        <v>46113</v>
+      </c>
+      <c r="C39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>16</v>
+      </c>
+      <c r="B40" s="4">
+        <v>46090</v>
+      </c>
+      <c r="C40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>16</v>
+      </c>
+      <c r="B41" s="4">
+        <v>46148</v>
+      </c>
+      <c r="C41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>16</v>
+      </c>
+      <c r="B42" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>16</v>
+      </c>
+      <c r="B43" s="4">
+        <v>46125</v>
+      </c>
+      <c r="C43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>16</v>
+      </c>
+      <c r="B44" s="4">
+        <v>46093</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>16</v>
+      </c>
+      <c r="B45" s="4">
+        <v>46092</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>16</v>
+      </c>
+      <c r="B46" s="4">
+        <v>46101</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>14</v>
+      </c>
+      <c r="B47" s="4">
+        <v>46007</v>
+      </c>
+      <c r="C47">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>14</v>
+      </c>
+      <c r="B48" s="4">
+        <v>46009</v>
+      </c>
+      <c r="C48">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>14</v>
+      </c>
+      <c r="B49" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C49">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>14</v>
+      </c>
+      <c r="B50" s="4">
+        <v>46001</v>
+      </c>
+      <c r="C50">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B51" s="4">
+        <v>46006</v>
+      </c>
+      <c r="C51">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>14</v>
+      </c>
+      <c r="B52" s="4">
+        <v>46010</v>
+      </c>
+      <c r="C52">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>14</v>
+      </c>
+      <c r="B53" s="4">
+        <v>46014</v>
+      </c>
+      <c r="C53">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>14</v>
+      </c>
+      <c r="B54" s="4">
+        <v>46002</v>
+      </c>
+      <c r="C54">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>14</v>
+      </c>
+      <c r="B55" s="4">
+        <v>46008</v>
+      </c>
+      <c r="C55">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>14</v>
+      </c>
+      <c r="B56" s="4">
+        <v>46003</v>
+      </c>
+      <c r="C56">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>14</v>
+      </c>
+      <c r="B57" s="4">
+        <v>46013</v>
+      </c>
+      <c r="C57">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>14</v>
+      </c>
+      <c r="B58" s="4">
+        <v>46022</v>
+      </c>
+      <c r="C58">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>14</v>
+      </c>
+      <c r="B59" s="4">
+        <v>46080</v>
+      </c>
+      <c r="C59">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>14</v>
+      </c>
+      <c r="B60" s="4">
+        <v>46084</v>
+      </c>
+      <c r="C60">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>14</v>
+      </c>
+      <c r="B61" s="4">
+        <v>46125</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>14</v>
+      </c>
+      <c r="B62" s="4">
+        <v>46091</v>
+      </c>
+      <c r="C62">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>14</v>
+      </c>
+      <c r="B63" s="4">
+        <v>46083</v>
+      </c>
+      <c r="C63">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>14</v>
+      </c>
+      <c r="B64" s="4">
+        <v>46105</v>
+      </c>
+      <c r="C64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>14</v>
+      </c>
+      <c r="B65" s="4">
+        <v>46077</v>
+      </c>
+      <c r="C65">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>14</v>
+      </c>
+      <c r="B66" s="4">
+        <v>46118</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>14</v>
+      </c>
+      <c r="B67" s="4">
+        <v>46078</v>
+      </c>
+      <c r="C67">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>14</v>
+      </c>
+      <c r="B68" s="4">
+        <v>46099</v>
+      </c>
+      <c r="C68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>14</v>
+      </c>
+      <c r="B69" s="4">
+        <v>46104</v>
+      </c>
+      <c r="C69">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>14</v>
+      </c>
+      <c r="B70" s="4">
+        <v>46107</v>
+      </c>
+      <c r="C70">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>14</v>
+      </c>
+      <c r="B71" s="4">
+        <v>46020</v>
+      </c>
+      <c r="C71">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>14</v>
+      </c>
+      <c r="B72" s="4">
+        <v>46076</v>
+      </c>
+      <c r="C72">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>14</v>
+      </c>
+      <c r="B73" s="4">
+        <v>46111</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>14</v>
+      </c>
+      <c r="B74" s="4">
+        <v>46087</v>
+      </c>
+      <c r="C74">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>14</v>
+      </c>
+      <c r="B75" s="4">
+        <v>46140</v>
+      </c>
+      <c r="C75">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>14</v>
+      </c>
+      <c r="B76" s="4">
+        <v>46113</v>
+      </c>
+      <c r="C76">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>14</v>
+      </c>
+      <c r="B77" s="4">
+        <v>46119</v>
+      </c>
+      <c r="C77">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>14</v>
+      </c>
+      <c r="B78" s="4">
+        <v>46108</v>
+      </c>
+      <c r="C78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>14</v>
+      </c>
+      <c r="B79" s="4">
+        <v>46098</v>
+      </c>
+      <c r="C79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>14</v>
+      </c>
+      <c r="B80" s="4">
+        <v>46141</v>
+      </c>
+      <c r="C80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>14</v>
+      </c>
+      <c r="B81" s="4">
+        <v>46114</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>14</v>
+      </c>
+      <c r="B82" s="4">
+        <v>46079</v>
+      </c>
+      <c r="C82">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>14</v>
+      </c>
+      <c r="B83" s="4">
+        <v>46139</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>14</v>
+      </c>
+      <c r="B84" s="4">
+        <v>46148</v>
+      </c>
+      <c r="C84">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>14</v>
+      </c>
+      <c r="B85" s="4">
+        <v>46092</v>
+      </c>
+      <c r="C85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>14</v>
+      </c>
+      <c r="B86" s="4">
+        <v>46021</v>
+      </c>
+      <c r="C86">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>14</v>
+      </c>
+      <c r="B87" s="4">
+        <v>46086</v>
+      </c>
+      <c r="C87">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>14</v>
+      </c>
+      <c r="B88" s="4">
+        <v>46147</v>
+      </c>
+      <c r="C88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>14</v>
+      </c>
+      <c r="B89" s="4">
+        <v>46134</v>
+      </c>
+      <c r="C89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>3</v>
+      </c>
+      <c r="B90" s="4">
+        <v>46003</v>
+      </c>
+      <c r="C90">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>3</v>
+      </c>
+      <c r="B91" s="4">
+        <v>46002</v>
+      </c>
+      <c r="C91">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>3</v>
+      </c>
+      <c r="B92" s="4">
+        <v>46008</v>
+      </c>
+      <c r="C92">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>3</v>
+      </c>
+      <c r="B93" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C93">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>3</v>
+      </c>
+      <c r="B94" s="4">
+        <v>46007</v>
+      </c>
+      <c r="C94">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>3</v>
+      </c>
+      <c r="B95" s="4">
+        <v>46001</v>
+      </c>
+      <c r="C95">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>3</v>
+      </c>
+      <c r="B96" s="4">
+        <v>46010</v>
+      </c>
+      <c r="C96">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>3</v>
+      </c>
+      <c r="B97" s="4">
+        <v>46006</v>
+      </c>
+      <c r="C97">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>3</v>
+      </c>
+      <c r="B98" s="4">
+        <v>46009</v>
+      </c>
+      <c r="C98">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>3</v>
+      </c>
+      <c r="B99" s="4">
+        <v>46015</v>
+      </c>
+      <c r="C99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>3</v>
+      </c>
+      <c r="B100" s="4">
+        <v>46014</v>
+      </c>
+      <c r="C100">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>3</v>
+      </c>
+      <c r="B101" s="4">
+        <v>46013</v>
+      </c>
+      <c r="C101">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>3</v>
+      </c>
+      <c r="B102" s="4">
+        <v>46021</v>
+      </c>
+      <c r="C102">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>3</v>
+      </c>
+      <c r="B103" s="4">
+        <v>46077</v>
+      </c>
+      <c r="C103">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>3</v>
+      </c>
+      <c r="B104" s="4">
+        <v>46090</v>
+      </c>
+      <c r="C104">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>3</v>
+      </c>
+      <c r="B105" s="4">
+        <v>46093</v>
+      </c>
+      <c r="C105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>3</v>
+      </c>
+      <c r="B106" s="4">
+        <v>46078</v>
+      </c>
+      <c r="C106">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>3</v>
+      </c>
+      <c r="B107" s="4">
+        <v>46084</v>
+      </c>
+      <c r="C107">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>3</v>
+      </c>
+      <c r="B108" s="4">
+        <v>46134</v>
+      </c>
+      <c r="C108">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>3</v>
+      </c>
+      <c r="B109" s="4">
+        <v>46083</v>
+      </c>
+      <c r="C109">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>3</v>
+      </c>
+      <c r="B110" s="4">
+        <v>46022</v>
+      </c>
+      <c r="C110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>3</v>
+      </c>
+      <c r="B111" s="4">
+        <v>46114</v>
+      </c>
+      <c r="C111">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>3</v>
+      </c>
+      <c r="B112" s="4">
+        <v>46135</v>
+      </c>
+      <c r="C112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>3</v>
+      </c>
+      <c r="B113" s="4">
+        <v>46126</v>
+      </c>
+      <c r="C113">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>3</v>
+      </c>
+      <c r="B114" s="4">
+        <v>46120</v>
+      </c>
+      <c r="C114">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>3</v>
+      </c>
+      <c r="B115" s="4">
+        <v>46127</v>
+      </c>
+      <c r="C115">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>3</v>
+      </c>
+      <c r="B116" s="4">
+        <v>46087</v>
+      </c>
+      <c r="C116">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>3</v>
+      </c>
+      <c r="B117" s="4">
+        <v>46108</v>
+      </c>
+      <c r="C117">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>3</v>
+      </c>
+      <c r="B118" s="4">
+        <v>46020</v>
+      </c>
+      <c r="C118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>3</v>
+      </c>
+      <c r="B119" s="4">
+        <v>46097</v>
+      </c>
+      <c r="C119">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>3</v>
+      </c>
+      <c r="B120" s="4">
+        <v>46129</v>
+      </c>
+      <c r="C120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>3</v>
+      </c>
+      <c r="B121" s="4">
+        <v>46080</v>
+      </c>
+      <c r="C121">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>3</v>
+      </c>
+      <c r="B122" s="4">
+        <v>46101</v>
+      </c>
+      <c r="C122">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>3</v>
+      </c>
+      <c r="B123" s="4">
+        <v>46150</v>
+      </c>
+      <c r="C123">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>3</v>
+      </c>
+      <c r="B124" s="4">
+        <v>46141</v>
+      </c>
+      <c r="C124">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>3</v>
+      </c>
+      <c r="B125" s="4">
+        <v>46085</v>
+      </c>
+      <c r="C125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>3</v>
+      </c>
+      <c r="B126" s="4">
+        <v>46148</v>
+      </c>
+      <c r="C126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>3</v>
+      </c>
+      <c r="B127" s="4">
+        <v>46118</v>
+      </c>
+      <c r="C127">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>3</v>
+      </c>
+      <c r="B128" s="4">
+        <v>46079</v>
+      </c>
+      <c r="C128">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" s="4">
+        <v>46003</v>
+      </c>
+      <c r="C129">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C130">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" s="4">
+        <v>46006</v>
+      </c>
+      <c r="C131">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" s="4">
+        <v>46001</v>
+      </c>
+      <c r="C132">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" s="4">
+        <v>46014</v>
+      </c>
+      <c r="C133">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" s="4">
+        <v>46002</v>
+      </c>
+      <c r="C134">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" s="4">
+        <v>46009</v>
+      </c>
+      <c r="C135">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" s="4">
+        <v>46010</v>
+      </c>
+      <c r="C136">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" s="4">
+        <v>46008</v>
+      </c>
+      <c r="C137">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" s="4">
+        <v>46007</v>
+      </c>
+      <c r="C138">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" s="4">
+        <v>46013</v>
+      </c>
+      <c r="C139">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" s="4">
+        <v>46080</v>
+      </c>
+      <c r="C140">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" s="4">
+        <v>46090</v>
+      </c>
+      <c r="C141">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" s="4">
+        <v>46079</v>
+      </c>
+      <c r="C142">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" s="4">
+        <v>46015</v>
+      </c>
+      <c r="C143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" s="4">
+        <v>46085</v>
+      </c>
+      <c r="C144">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" s="4">
+        <v>46098</v>
+      </c>
+      <c r="C145">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" s="4">
+        <v>46021</v>
+      </c>
+      <c r="C146">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" s="4">
+        <v>46078</v>
+      </c>
+      <c r="C147">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" s="4">
+        <v>46084</v>
+      </c>
+      <c r="C148">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" s="4">
+        <v>46128</v>
+      </c>
+      <c r="C149">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" s="4">
+        <v>46083</v>
+      </c>
+      <c r="C150">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" s="4">
+        <v>46076</v>
+      </c>
+      <c r="C151">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" s="4">
+        <v>46099</v>
+      </c>
+      <c r="C152">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" s="4">
+        <v>46092</v>
+      </c>
+      <c r="C153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" s="4">
+        <v>46031</v>
+      </c>
+      <c r="C154">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" s="4">
+        <v>46120</v>
+      </c>
+      <c r="C155">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" s="4">
+        <v>46077</v>
+      </c>
+      <c r="C156">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" s="4">
+        <v>46114</v>
+      </c>
+      <c r="C157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" s="4">
+        <v>46037</v>
+      </c>
+      <c r="C158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" s="4">
+        <v>46020</v>
+      </c>
+      <c r="C159">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" s="4">
+        <v>46106</v>
+      </c>
+      <c r="C160">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" s="4">
+        <v>46112</v>
+      </c>
+      <c r="C161">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" s="4">
+        <v>46132</v>
+      </c>
+      <c r="C162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" s="4">
+        <v>46108</v>
+      </c>
+      <c r="C163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" s="4">
+        <v>46148</v>
+      </c>
+      <c r="C164">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" s="4">
+        <v>46118</v>
+      </c>
+      <c r="C165">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" s="4">
+        <v>46035</v>
+      </c>
+      <c r="C166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" s="4">
+        <v>46093</v>
+      </c>
+      <c r="C167">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" s="4">
+        <v>46022</v>
+      </c>
+      <c r="C168">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" s="4">
+        <v>46087</v>
+      </c>
+      <c r="C169">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" s="4">
+        <v>46030</v>
+      </c>
+      <c r="C170">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" s="4">
+        <v>46101</v>
+      </c>
+      <c r="C171">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" s="4">
+        <v>46142</v>
+      </c>
+      <c r="C172">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>21</v>
+      </c>
+      <c r="B173" s="4">
+        <v>46001</v>
+      </c>
+      <c r="C173">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>21</v>
+      </c>
+      <c r="B174" s="4">
+        <v>46008</v>
+      </c>
+      <c r="C174">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>21</v>
+      </c>
+      <c r="B175" s="4">
+        <v>46003</v>
+      </c>
+      <c r="C175">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>21</v>
+      </c>
+      <c r="B176" s="4">
+        <v>46002</v>
+      </c>
+      <c r="C176">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>21</v>
+      </c>
+      <c r="B177" s="4">
+        <v>46006</v>
+      </c>
+      <c r="C177">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>21</v>
+      </c>
+      <c r="B178" s="4">
+        <v>46007</v>
+      </c>
+      <c r="C178">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>21</v>
+      </c>
+      <c r="B179" s="4">
+        <v>46000</v>
+      </c>
+      <c r="C179">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>21</v>
+      </c>
+      <c r="B180" s="4">
+        <v>46084</v>
+      </c>
+      <c r="C180">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>21</v>
+      </c>
+      <c r="B181" s="4">
+        <v>46014</v>
+      </c>
+      <c r="C181">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>21</v>
+      </c>
+      <c r="B182" s="4">
+        <v>46013</v>
+      </c>
+      <c r="C182">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>21</v>
+      </c>
+      <c r="B183" s="4">
+        <v>46010</v>
+      </c>
+      <c r="C183">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>21</v>
+      </c>
+      <c r="B184" s="4">
+        <v>46021</v>
+      </c>
+      <c r="C184">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>21</v>
+      </c>
+      <c r="B185" s="4">
+        <v>46009</v>
+      </c>
+      <c r="C185">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>21</v>
+      </c>
+      <c r="B186" s="4">
+        <v>46083</v>
+      </c>
+      <c r="C186">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>21</v>
+      </c>
+      <c r="B187" s="4">
+        <v>46079</v>
+      </c>
+      <c r="C187">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>21</v>
+      </c>
+      <c r="B188" s="4">
+        <v>46077</v>
+      </c>
+      <c r="C188">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>21</v>
+      </c>
+      <c r="B189" s="4">
+        <v>46035</v>
+      </c>
+      <c r="C189">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>21</v>
+      </c>
+      <c r="B190" s="4">
+        <v>46085</v>
+      </c>
+      <c r="C190">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>21</v>
+      </c>
+      <c r="B191" s="4">
+        <v>46120</v>
+      </c>
+      <c r="C191">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>21</v>
+      </c>
+      <c r="B192" s="4">
+        <v>46114</v>
+      </c>
+      <c r="C192">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>21</v>
+      </c>
+      <c r="B193" s="4">
+        <v>46094</v>
+      </c>
+      <c r="C193">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>21</v>
+      </c>
+      <c r="B194" s="4">
+        <v>46080</v>
+      </c>
+      <c r="C194">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>21</v>
+      </c>
+      <c r="B195" s="4">
+        <v>46127</v>
+      </c>
+      <c r="C195">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>21</v>
+      </c>
+      <c r="B196" s="4">
+        <v>46091</v>
+      </c>
+      <c r="C196">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>21</v>
+      </c>
+      <c r="B197" s="4">
+        <v>46090</v>
+      </c>
+      <c r="C197">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>21</v>
+      </c>
+      <c r="B198" s="4">
+        <v>46020</v>
+      </c>
+      <c r="C198">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>21</v>
+      </c>
+      <c r="B199" s="4">
+        <v>46015</v>
+      </c>
+      <c r="C199">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>21</v>
+      </c>
+      <c r="B200" s="4">
+        <v>46113</v>
+      </c>
+      <c r="C200">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>21</v>
+      </c>
+      <c r="B201" s="4">
+        <v>46078</v>
+      </c>
+      <c r="C201">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>21</v>
+      </c>
+      <c r="B202" s="4">
+        <v>46148</v>
+      </c>
+      <c r="C202">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>21</v>
+      </c>
+      <c r="B203" s="4">
+        <v>46105</v>
+      </c>
+      <c r="C203">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>21</v>
+      </c>
+      <c r="B204" s="4">
+        <v>46087</v>
+      </c>
+      <c r="C204">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>21</v>
+      </c>
+      <c r="B205" s="4">
+        <v>46107</v>
+      </c>
+      <c r="C205">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>21</v>
+      </c>
+      <c r="B206" s="4">
+        <v>46086</v>
+      </c>
+      <c r="C206">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>21</v>
+      </c>
+      <c r="B207" s="4">
+        <v>46106</v>
+      </c>
+      <c r="C207">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>21</v>
+      </c>
+      <c r="B208" s="4">
+        <v>46150</v>
+      </c>
+      <c r="C208">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>21</v>
+      </c>
+      <c r="B209" s="4">
+        <v>46104</v>
+      </c>
+      <c r="C209">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>21</v>
+      </c>
+      <c r="B210" s="4">
+        <v>46118</v>
+      </c>
+      <c r="C210">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>21</v>
+      </c>
+      <c r="B211" s="4">
+        <v>46076</v>
+      </c>
+      <c r="C211">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>21</v>
+      </c>
+      <c r="B212" s="4">
+        <v>46093</v>
+      </c>
+      <c r="C212">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>21</v>
+      </c>
+      <c r="B213" s="4">
+        <v>46122</v>
+      </c>
+      <c r="C213">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>21</v>
+      </c>
+      <c r="B214" s="4">
+        <v>46092</v>
+      </c>
+      <c r="C214">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>21</v>
+      </c>
+      <c r="B215" s="4">
+        <v>46133</v>
+      </c>
+      <c r="C215">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>21</v>
+      </c>
+      <c r="B216" s="4">
+        <v>46126</v>
+      </c>
+      <c r="C216">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>21</v>
+      </c>
+      <c r="B217" s="4">
+        <v>46022</v>
+      </c>
+      <c r="C217">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>21</v>
+      </c>
+      <c r="B218" s="4">
+        <v>46100</v>
+      </c>
+      <c r="C218">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>21</v>
+      </c>
+      <c r="B219" s="4">
+        <v>46101</v>
+      </c>
+      <c r="C219">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>21</v>
+      </c>
+      <c r="B220" s="4">
+        <v>46097</v>
+      </c>
+      <c r="C220">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>21</v>
+      </c>
+      <c r="B221" s="4">
+        <v>46108</v>
+      </c>
+      <c r="C221">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>21</v>
+      </c>
+      <c r="B222" s="4">
+        <v>46098</v>
+      </c>
+      <c r="C222">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>21</v>
+      </c>
+      <c r="B223">
+        <v>46142</v>
+      </c>
+      <c r="C223">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>21</v>
+      </c>
+      <c r="B224">
+        <v>46031</v>
+      </c>
+      <c r="C224">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48EA67D6-54B8-4120-A206-DEE64ADF7599}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A180E8F-D2AB-459A-97D6-BB607D0CC07B}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" activeTab="3" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="mat_2026" sheetId="1" r:id="rId1"/>
@@ -3991,7 +3991,7 @@
       <c r="A223" t="s">
         <v>21</v>
       </c>
-      <c r="B223">
+      <c r="B223" s="4">
         <v>46142</v>
       </c>
       <c r="C223">
@@ -4002,7 +4002,7 @@
       <c r="A224" t="s">
         <v>21</v>
       </c>
-      <c r="B224">
+      <c r="B224" s="4">
         <v>46031</v>
       </c>
       <c r="C224">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A180E8F-D2AB-459A-97D6-BB607D0CC07B}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE517BC8-012A-48C6-A15D-0F970796DFBA}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" activeTab="3" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="mat_2026" sheetId="1" r:id="rId1"/>

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE517BC8-012A-48C6-A15D-0F970796DFBA}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65510C09-4A46-4D8D-B15E-68D7160F9804}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="mat_2026" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="39">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -181,15 +181,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -197,12 +203,49 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -213,7 +256,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -625,10 +673,10 @@
         <v>46</v>
       </c>
       <c r="D4">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E4">
-        <v>1.1739999999999999</v>
+        <v>1.1519999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -1016,10 +1064,10 @@
         <v>109</v>
       </c>
       <c r="D27">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E27">
-        <v>0.97199999999999998</v>
+        <v>0.98199999999999998</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -1101,10 +1149,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E32">
-        <v>1.081</v>
+        <v>1.0780000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1169,10 +1217,10 @@
         <v>250</v>
       </c>
       <c r="D36">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>1.004</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1203,10 +1251,10 @@
         <v>226</v>
       </c>
       <c r="D38">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E38">
-        <v>1.0840000000000001</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -1220,10 +1268,10 @@
         <v>214</v>
       </c>
       <c r="D39">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E39">
-        <v>0.95299999999999996</v>
+        <v>0.94899999999999995</v>
       </c>
     </row>
   </sheetData>
@@ -1439,7 +1487,7 @@
         <v>35</v>
       </c>
       <c r="C3">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1483,7 +1531,7 @@
         <v>34</v>
       </c>
       <c r="C7">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1505,7 +1553,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1516,7 +1564,7 @@
         <v>35</v>
       </c>
       <c r="C10">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1527,7 +1575,7 @@
         <v>34</v>
       </c>
       <c r="C11">
-        <v>430</v>
+        <v>428</v>
       </c>
     </row>
   </sheetData>
@@ -1537,7 +1585,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD19485A-0629-47F9-A5AD-80ABA7A6E076}">
-  <dimension ref="A1:C224"/>
+  <dimension ref="A1:C226"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -1557,2455 +1605,2477 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="4">
+      <c r="A2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="5">
         <v>46009</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="6">
         <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="4">
+      <c r="A3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="8">
         <v>46008</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="9">
         <v>302</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="4">
+      <c r="A4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="5">
         <v>46000</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="6">
         <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="4">
+      <c r="A5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="8">
         <v>46001</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="9">
         <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="4">
+      <c r="A6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="5">
         <v>46002</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="6">
         <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="4">
+      <c r="A7" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="8">
         <v>46014</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="9">
         <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="4">
+      <c r="A8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="5">
         <v>46006</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="6">
         <v>228</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="4">
+      <c r="A9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="8">
         <v>46013</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="9">
         <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="4">
+      <c r="A10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="5">
         <v>46007</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="6">
         <v>329</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="4">
+      <c r="A11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="8">
         <v>46147</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="4">
+      <c r="A12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" s="5">
         <v>46077</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="6">
         <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="4">
+      <c r="A13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="8">
         <v>46003</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="9">
         <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="4">
+      <c r="A14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="5">
         <v>46010</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="6">
         <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" s="4">
+      <c r="A15" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="8">
         <v>46079</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="9">
         <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="4">
+      <c r="A16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="5">
         <v>46020</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="6">
         <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" s="4">
+      <c r="A17" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" s="8">
         <v>46015</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="9">
         <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="4">
+      <c r="A18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="5">
         <v>46083</v>
       </c>
-      <c r="C18">
-        <v>14</v>
+      <c r="C18" s="6">
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" s="4">
+      <c r="A19" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="8">
         <v>46097</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="9">
         <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>16</v>
-      </c>
-      <c r="B20" s="4">
+      <c r="A20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" s="5">
         <v>46021</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="6">
         <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>16</v>
-      </c>
-      <c r="B21" s="4">
+      <c r="A21" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="8">
         <v>46080</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="9">
         <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>16</v>
-      </c>
-      <c r="B22" s="4">
+      <c r="A22" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="5">
         <v>46087</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="6">
         <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>16</v>
-      </c>
-      <c r="B23" s="4">
+      <c r="A23" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" s="8">
         <v>46022</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="9">
         <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>16</v>
-      </c>
-      <c r="B24" s="4">
+      <c r="A24" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" s="5">
         <v>46086</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="6">
         <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>16</v>
-      </c>
-      <c r="B25" s="4">
+      <c r="A25" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" s="8">
         <v>46076</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="9">
         <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>16</v>
-      </c>
-      <c r="B26" s="4">
+      <c r="A26" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" s="5">
         <v>46136</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>16</v>
-      </c>
-      <c r="B27" s="4">
+      <c r="A27" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" s="8">
         <v>46078</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="9">
         <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>16</v>
-      </c>
-      <c r="B28" s="4">
+      <c r="A28" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" s="5">
         <v>46098</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="6">
         <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>16</v>
-      </c>
-      <c r="B29" s="4">
+      <c r="A29" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" s="8">
         <v>46084</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>16</v>
-      </c>
-      <c r="B30" s="4">
+      <c r="A30" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" s="5">
         <v>46099</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="6">
         <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>16</v>
-      </c>
-      <c r="B31" s="4">
+      <c r="A31" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31" s="8">
         <v>46128</v>
       </c>
-      <c r="C31">
+      <c r="C31" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>16</v>
-      </c>
-      <c r="B32" s="4">
+      <c r="A32" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" s="5">
         <v>46141</v>
       </c>
-      <c r="C32">
+      <c r="C32" s="6">
         <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>16</v>
-      </c>
-      <c r="B33" s="4">
+      <c r="A33" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33" s="8">
         <v>46132</v>
       </c>
-      <c r="C33">
+      <c r="C33" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>16</v>
-      </c>
-      <c r="B34" s="4">
+      <c r="A34" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B34" s="5">
         <v>46127</v>
       </c>
-      <c r="C34">
+      <c r="C34" s="6">
         <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>16</v>
-      </c>
-      <c r="B35" s="4">
+      <c r="A35" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B35" s="8">
         <v>46091</v>
       </c>
-      <c r="C35">
+      <c r="C35" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>16</v>
-      </c>
-      <c r="B36" s="4">
+      <c r="A36" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B36" s="5">
         <v>46104</v>
       </c>
-      <c r="C36">
+      <c r="C36" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>16</v>
-      </c>
-      <c r="B37" s="4">
+      <c r="A37" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B37" s="8">
         <v>46140</v>
       </c>
-      <c r="C37">
+      <c r="C37" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>16</v>
-      </c>
-      <c r="B38" s="4">
+      <c r="A38" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B38" s="5">
         <v>46106</v>
       </c>
-      <c r="C38">
+      <c r="C38" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>16</v>
-      </c>
-      <c r="B39" s="4">
+      <c r="A39" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B39" s="8">
         <v>46113</v>
       </c>
-      <c r="C39">
+      <c r="C39" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>16</v>
-      </c>
-      <c r="B40" s="4">
+      <c r="A40" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B40" s="5">
         <v>46090</v>
       </c>
-      <c r="C40">
+      <c r="C40" s="6">
         <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>16</v>
-      </c>
-      <c r="B41" s="4">
+      <c r="A41" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B41" s="8">
         <v>46148</v>
       </c>
-      <c r="C41">
+      <c r="C41" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>16</v>
-      </c>
-      <c r="B42" s="4">
+      <c r="A42" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B42" s="5">
         <v>46139</v>
       </c>
-      <c r="C42">
+      <c r="C42" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>16</v>
-      </c>
-      <c r="B43" s="4">
+      <c r="A43" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B43" s="8">
         <v>46125</v>
       </c>
-      <c r="C43">
+      <c r="C43" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>16</v>
-      </c>
-      <c r="B44" s="4">
+      <c r="A44" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B44" s="5">
         <v>46093</v>
       </c>
-      <c r="C44">
+      <c r="C44" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>16</v>
-      </c>
-      <c r="B45" s="4">
+      <c r="A45" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B45" s="8">
         <v>46092</v>
       </c>
-      <c r="C45">
+      <c r="C45" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>16</v>
-      </c>
-      <c r="B46" s="4">
+      <c r="A46" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B46" s="5">
         <v>46101</v>
       </c>
-      <c r="C46">
+      <c r="C46" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>14</v>
-      </c>
-      <c r="B47" s="4">
+      <c r="A47" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B47" s="8">
         <v>46007</v>
       </c>
-      <c r="C47">
+      <c r="C47" s="9">
         <v>79</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>14</v>
-      </c>
-      <c r="B48" s="4">
+      <c r="A48" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B48" s="5">
         <v>46009</v>
       </c>
-      <c r="C48">
+      <c r="C48" s="6">
         <v>34</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>14</v>
-      </c>
-      <c r="B49" s="4">
+      <c r="A49" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B49" s="8">
         <v>46000</v>
       </c>
-      <c r="C49">
+      <c r="C49" s="9">
         <v>82</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>14</v>
-      </c>
-      <c r="B50" s="4">
+      <c r="A50" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B50" s="5">
         <v>46001</v>
       </c>
-      <c r="C50">
+      <c r="C50" s="6">
         <v>83</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>14</v>
-      </c>
-      <c r="B51" s="4">
+      <c r="A51" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B51" s="8">
         <v>46006</v>
       </c>
-      <c r="C51">
+      <c r="C51" s="9">
         <v>79</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>14</v>
-      </c>
-      <c r="B52" s="4">
+      <c r="A52" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B52" s="5">
         <v>46010</v>
       </c>
-      <c r="C52">
+      <c r="C52" s="6">
         <v>24</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>14</v>
-      </c>
-      <c r="B53" s="4">
+      <c r="A53" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B53" s="8">
         <v>46014</v>
       </c>
-      <c r="C53">
+      <c r="C53" s="9">
         <v>20</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>14</v>
-      </c>
-      <c r="B54" s="4">
+      <c r="A54" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B54" s="5">
         <v>46002</v>
       </c>
-      <c r="C54">
+      <c r="C54" s="6">
         <v>47</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>14</v>
-      </c>
-      <c r="B55" s="4">
+      <c r="A55" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B55" s="8">
         <v>46008</v>
       </c>
-      <c r="C55">
+      <c r="C55" s="9">
         <v>58</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>14</v>
-      </c>
-      <c r="B56" s="4">
+      <c r="A56" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B56" s="5">
         <v>46003</v>
       </c>
-      <c r="C56">
+      <c r="C56" s="6">
         <v>47</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>14</v>
-      </c>
-      <c r="B57" s="4">
+      <c r="A57" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B57" s="8">
         <v>46013</v>
       </c>
-      <c r="C57">
+      <c r="C57" s="9">
         <v>30</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>14</v>
-      </c>
-      <c r="B58" s="4">
+      <c r="A58" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B58" s="5">
         <v>46022</v>
       </c>
-      <c r="C58">
+      <c r="C58" s="6">
         <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>14</v>
-      </c>
-      <c r="B59" s="4">
+      <c r="A59" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B59" s="8">
         <v>46080</v>
       </c>
-      <c r="C59">
+      <c r="C59" s="9">
         <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>14</v>
-      </c>
-      <c r="B60" s="4">
+      <c r="A60" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B60" s="5">
         <v>46084</v>
       </c>
-      <c r="C60">
+      <c r="C60" s="6">
         <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>14</v>
-      </c>
-      <c r="B61" s="4">
+      <c r="A61" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B61" s="8">
         <v>46125</v>
       </c>
-      <c r="C61">
+      <c r="C61" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>14</v>
-      </c>
-      <c r="B62" s="4">
+      <c r="A62" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B62" s="5">
         <v>46091</v>
       </c>
-      <c r="C62">
+      <c r="C62" s="6">
         <v>3</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>14</v>
-      </c>
-      <c r="B63" s="4">
+      <c r="A63" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B63" s="8">
         <v>46083</v>
       </c>
-      <c r="C63">
+      <c r="C63" s="9">
         <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>14</v>
-      </c>
-      <c r="B64" s="4">
+      <c r="A64" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B64" s="5">
         <v>46105</v>
       </c>
-      <c r="C64">
+      <c r="C64" s="6">
         <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>14</v>
-      </c>
-      <c r="B65" s="4">
+      <c r="A65" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B65" s="8">
         <v>46077</v>
       </c>
-      <c r="C65">
+      <c r="C65" s="9">
         <v>9</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>14</v>
-      </c>
-      <c r="B66" s="4">
+      <c r="A66" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B66" s="5">
         <v>46118</v>
       </c>
-      <c r="C66">
+      <c r="C66" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>14</v>
-      </c>
-      <c r="B67" s="4">
+      <c r="A67" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B67" s="8">
         <v>46078</v>
       </c>
-      <c r="C67">
+      <c r="C67" s="9">
         <v>6</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>14</v>
-      </c>
-      <c r="B68" s="4">
+      <c r="A68" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B68" s="5">
         <v>46099</v>
       </c>
-      <c r="C68">
+      <c r="C68" s="6">
         <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>14</v>
-      </c>
-      <c r="B69" s="4">
+      <c r="A69" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B69" s="8">
         <v>46104</v>
       </c>
-      <c r="C69">
+      <c r="C69" s="9">
         <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>14</v>
-      </c>
-      <c r="B70" s="4">
+      <c r="A70" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B70" s="5">
         <v>46107</v>
       </c>
-      <c r="C70">
+      <c r="C70" s="6">
         <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>14</v>
-      </c>
-      <c r="B71" s="4">
+      <c r="A71" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B71" s="8">
         <v>46020</v>
       </c>
-      <c r="C71">
+      <c r="C71" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>14</v>
-      </c>
-      <c r="B72" s="4">
+      <c r="A72" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B72" s="5">
         <v>46076</v>
       </c>
-      <c r="C72">
+      <c r="C72" s="6">
         <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>14</v>
-      </c>
-      <c r="B73" s="4">
+      <c r="A73" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B73" s="8">
         <v>46111</v>
       </c>
-      <c r="C73">
+      <c r="C73" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>14</v>
-      </c>
-      <c r="B74" s="4">
+      <c r="A74" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B74" s="5">
         <v>46087</v>
       </c>
-      <c r="C74">
+      <c r="C74" s="6">
         <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>14</v>
-      </c>
-      <c r="B75" s="4">
+      <c r="A75" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B75" s="8">
         <v>46140</v>
       </c>
-      <c r="C75">
+      <c r="C75" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>14</v>
-      </c>
-      <c r="B76" s="4">
+      <c r="A76" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B76" s="5">
         <v>46113</v>
       </c>
-      <c r="C76">
+      <c r="C76" s="6">
         <v>3</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>14</v>
-      </c>
-      <c r="B77" s="4">
+      <c r="A77" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B77" s="8">
         <v>46119</v>
       </c>
-      <c r="C77">
+      <c r="C77" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>14</v>
-      </c>
-      <c r="B78" s="4">
+      <c r="A78" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B78" s="5">
         <v>46108</v>
       </c>
-      <c r="C78">
+      <c r="C78" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>14</v>
-      </c>
-      <c r="B79" s="4">
+      <c r="A79" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B79" s="8">
         <v>46098</v>
       </c>
-      <c r="C79">
+      <c r="C79" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>14</v>
-      </c>
-      <c r="B80" s="4">
+      <c r="A80" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B80" s="5">
         <v>46141</v>
       </c>
-      <c r="C80">
+      <c r="C80" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>14</v>
-      </c>
-      <c r="B81" s="4">
+      <c r="A81" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B81" s="8">
         <v>46114</v>
       </c>
-      <c r="C81">
+      <c r="C81" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>14</v>
-      </c>
-      <c r="B82" s="4">
+      <c r="A82" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B82" s="5">
         <v>46079</v>
       </c>
-      <c r="C82">
+      <c r="C82" s="6">
         <v>3</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>14</v>
-      </c>
-      <c r="B83" s="4">
+      <c r="A83" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B83" s="8">
         <v>46139</v>
       </c>
-      <c r="C83">
+      <c r="C83" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>14</v>
-      </c>
-      <c r="B84" s="4">
+      <c r="A84" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B84" s="5">
         <v>46148</v>
       </c>
-      <c r="C84">
+      <c r="C84" s="6">
         <v>2</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>14</v>
-      </c>
-      <c r="B85" s="4">
+      <c r="A85" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B85" s="8">
         <v>46092</v>
       </c>
-      <c r="C85">
+      <c r="C85" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>14</v>
-      </c>
-      <c r="B86" s="4">
+      <c r="A86" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B86" s="5">
         <v>46021</v>
       </c>
-      <c r="C86">
+      <c r="C86" s="6">
         <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>14</v>
-      </c>
-      <c r="B87" s="4">
+      <c r="A87" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B87" s="8">
         <v>46086</v>
       </c>
-      <c r="C87">
+      <c r="C87" s="9">
         <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>14</v>
-      </c>
-      <c r="B88" s="4">
+      <c r="A88" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B88" s="5">
         <v>46147</v>
       </c>
-      <c r="C88">
+      <c r="C88" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>14</v>
-      </c>
-      <c r="B89" s="4">
+      <c r="A89" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B89" s="8">
         <v>46134</v>
       </c>
-      <c r="C89">
+      <c r="C89" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>3</v>
-      </c>
-      <c r="B90" s="4">
+      <c r="A90" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B90" s="5">
         <v>46003</v>
       </c>
-      <c r="C90">
+      <c r="C90" s="6">
         <v>95</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>3</v>
-      </c>
-      <c r="B91" s="4">
+      <c r="A91" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B91" s="8">
         <v>46002</v>
       </c>
-      <c r="C91">
-        <v>117</v>
+      <c r="C91" s="9">
+        <v>116</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>3</v>
-      </c>
-      <c r="B92" s="4">
+      <c r="A92" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B92" s="5">
         <v>46008</v>
       </c>
-      <c r="C92">
+      <c r="C92" s="6">
         <v>15</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>3</v>
-      </c>
-      <c r="B93" s="4">
+      <c r="A93" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B93" s="8">
         <v>46000</v>
       </c>
-      <c r="C93">
+      <c r="C93" s="9">
         <v>99</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>3</v>
-      </c>
-      <c r="B94" s="4">
+      <c r="A94" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B94" s="5">
         <v>46007</v>
       </c>
-      <c r="C94">
+      <c r="C94" s="6">
         <v>43</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>3</v>
-      </c>
-      <c r="B95" s="4">
+      <c r="A95" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B95" s="8">
         <v>46001</v>
       </c>
-      <c r="C95">
+      <c r="C95" s="9">
         <v>91</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>3</v>
-      </c>
-      <c r="B96" s="4">
+      <c r="A96" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B96" s="5">
         <v>46010</v>
       </c>
-      <c r="C96">
+      <c r="C96" s="6">
         <v>9</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>3</v>
-      </c>
-      <c r="B97" s="4">
+      <c r="A97" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B97" s="8">
         <v>46006</v>
       </c>
-      <c r="C97">
+      <c r="C97" s="9">
         <v>84</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>3</v>
-      </c>
-      <c r="B98" s="4">
+      <c r="A98" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B98" s="5">
         <v>46009</v>
       </c>
-      <c r="C98">
+      <c r="C98" s="6">
         <v>2</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>3</v>
-      </c>
-      <c r="B99" s="4">
+      <c r="A99" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B99" s="8">
         <v>46015</v>
       </c>
-      <c r="C99">
+      <c r="C99" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>3</v>
-      </c>
-      <c r="B100" s="4">
+      <c r="A100" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B100" s="5">
         <v>46014</v>
       </c>
-      <c r="C100">
+      <c r="C100" s="6">
         <v>8</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>3</v>
-      </c>
-      <c r="B101" s="4">
+      <c r="A101" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B101" s="8">
         <v>46013</v>
       </c>
-      <c r="C101">
+      <c r="C101" s="9">
         <v>3</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>3</v>
-      </c>
-      <c r="B102" s="4">
+      <c r="A102" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B102" s="5">
         <v>46021</v>
       </c>
-      <c r="C102">
+      <c r="C102" s="6">
         <v>2</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>3</v>
-      </c>
-      <c r="B103" s="4">
+      <c r="A103" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B103" s="8">
         <v>46077</v>
       </c>
-      <c r="C103">
+      <c r="C103" s="9">
         <v>8</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>3</v>
-      </c>
-      <c r="B104" s="4">
+      <c r="A104" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B104" s="5">
         <v>46090</v>
       </c>
-      <c r="C104">
+      <c r="C104" s="6">
         <v>5</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>3</v>
-      </c>
-      <c r="B105" s="4">
+      <c r="A105" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B105" s="8">
         <v>46093</v>
       </c>
-      <c r="C105">
+      <c r="C105" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>3</v>
-      </c>
-      <c r="B106" s="4">
+      <c r="A106" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B106" s="5">
         <v>46078</v>
       </c>
-      <c r="C106">
+      <c r="C106" s="6">
         <v>7</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>3</v>
-      </c>
-      <c r="B107" s="4">
+      <c r="A107" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B107" s="8">
         <v>46084</v>
       </c>
-      <c r="C107">
+      <c r="C107" s="9">
         <v>9</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>3</v>
-      </c>
-      <c r="B108" s="4">
+      <c r="A108" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B108" s="5">
         <v>46134</v>
       </c>
-      <c r="C108">
+      <c r="C108" s="6">
         <v>2</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>3</v>
-      </c>
-      <c r="B109" s="4">
+      <c r="A109" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B109" s="8">
         <v>46083</v>
       </c>
-      <c r="C109">
+      <c r="C109" s="9">
         <v>4</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>3</v>
-      </c>
-      <c r="B110" s="4">
+      <c r="A110" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B110" s="5">
         <v>46022</v>
       </c>
-      <c r="C110">
+      <c r="C110" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>3</v>
-      </c>
-      <c r="B111" s="4">
+      <c r="A111" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B111" s="8">
         <v>46114</v>
       </c>
-      <c r="C111">
+      <c r="C111" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>3</v>
-      </c>
-      <c r="B112" s="4">
+      <c r="A112" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B112" s="5">
         <v>46135</v>
       </c>
-      <c r="C112">
+      <c r="C112" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>3</v>
-      </c>
-      <c r="B113" s="4">
+      <c r="A113" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B113" s="8">
         <v>46126</v>
       </c>
-      <c r="C113">
+      <c r="C113" s="9">
         <v>3</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>3</v>
-      </c>
-      <c r="B114" s="4">
+      <c r="A114" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B114" s="5">
         <v>46120</v>
       </c>
-      <c r="C114">
+      <c r="C114" s="6">
         <v>3</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>3</v>
-      </c>
-      <c r="B115" s="4">
+      <c r="A115" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B115" s="8">
         <v>46127</v>
       </c>
-      <c r="C115">
+      <c r="C115" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>3</v>
-      </c>
-      <c r="B116" s="4">
+      <c r="A116" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B116" s="5">
         <v>46087</v>
       </c>
-      <c r="C116">
+      <c r="C116" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>3</v>
-      </c>
-      <c r="B117" s="4">
+      <c r="A117" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B117" s="8">
         <v>46108</v>
       </c>
-      <c r="C117">
+      <c r="C117" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>3</v>
-      </c>
-      <c r="B118" s="4">
+      <c r="A118" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B118" s="5">
         <v>46020</v>
       </c>
-      <c r="C118">
+      <c r="C118" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>3</v>
-      </c>
-      <c r="B119" s="4">
+      <c r="A119" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B119" s="8">
         <v>46097</v>
       </c>
-      <c r="C119">
+      <c r="C119" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>3</v>
-      </c>
-      <c r="B120" s="4">
+      <c r="A120" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B120" s="5">
         <v>46129</v>
       </c>
-      <c r="C120">
+      <c r="C120" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>3</v>
-      </c>
-      <c r="B121" s="4">
+      <c r="A121" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B121" s="8">
         <v>46080</v>
       </c>
-      <c r="C121">
+      <c r="C121" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>3</v>
-      </c>
-      <c r="B122" s="4">
+      <c r="A122" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B122" s="5">
         <v>46101</v>
       </c>
-      <c r="C122">
+      <c r="C122" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123" t="s">
-        <v>3</v>
-      </c>
-      <c r="B123" s="4">
+      <c r="A123" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B123" s="8">
         <v>46150</v>
       </c>
-      <c r="C123">
+      <c r="C123" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A124" t="s">
-        <v>3</v>
-      </c>
-      <c r="B124" s="4">
+      <c r="A124" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B124" s="5">
         <v>46141</v>
       </c>
-      <c r="C124">
+      <c r="C124" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A125" t="s">
-        <v>3</v>
-      </c>
-      <c r="B125" s="4">
+      <c r="A125" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B125" s="8">
         <v>46085</v>
       </c>
-      <c r="C125">
+      <c r="C125" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>3</v>
-      </c>
-      <c r="B126" s="4">
+      <c r="A126" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B126" s="5">
         <v>46148</v>
       </c>
-      <c r="C126">
+      <c r="C126" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>3</v>
-      </c>
-      <c r="B127" s="4">
+      <c r="A127" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B127" s="8">
         <v>46118</v>
       </c>
-      <c r="C127">
+      <c r="C127" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>3</v>
-      </c>
-      <c r="B128" s="4">
+      <c r="A128" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B128" s="5">
         <v>46079</v>
       </c>
-      <c r="C128">
+      <c r="C128" s="6">
         <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" s="4">
+      <c r="A129" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" s="8">
         <v>46003</v>
       </c>
-      <c r="C129">
+      <c r="C129" s="9">
         <v>92</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" s="4">
+      <c r="A130" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" s="5">
         <v>46000</v>
       </c>
-      <c r="C130">
+      <c r="C130" s="6">
         <v>133</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" s="4">
+      <c r="A131" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" s="8">
         <v>46006</v>
       </c>
-      <c r="C131">
+      <c r="C131" s="9">
         <v>175</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" s="4">
+      <c r="A132" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" s="5">
         <v>46001</v>
       </c>
-      <c r="C132">
+      <c r="C132" s="6">
         <v>174</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" s="4">
+      <c r="A133" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" s="8">
         <v>46014</v>
       </c>
-      <c r="C133">
+      <c r="C133" s="9">
         <v>16</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" s="4">
+      <c r="A134" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" s="5">
         <v>46002</v>
       </c>
-      <c r="C134">
+      <c r="C134" s="6">
         <v>171</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" s="4">
+      <c r="A135" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" s="8">
         <v>46009</v>
       </c>
-      <c r="C135">
+      <c r="C135" s="9">
         <v>20</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" s="4">
+      <c r="A136" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" s="5">
         <v>46010</v>
       </c>
-      <c r="C136">
+      <c r="C136" s="6">
         <v>19</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" s="4">
+      <c r="A137" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" s="8">
         <v>46008</v>
       </c>
-      <c r="C137">
+      <c r="C137" s="9">
         <v>25</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" s="4">
+      <c r="A138" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" s="5">
         <v>46007</v>
       </c>
-      <c r="C138">
+      <c r="C138" s="6">
         <v>43</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" s="4">
+      <c r="A139" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" s="8">
         <v>46013</v>
       </c>
-      <c r="C139">
+      <c r="C139" s="9">
         <v>12</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" s="4">
+      <c r="A140" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" s="5">
         <v>46080</v>
       </c>
-      <c r="C140">
+      <c r="C140" s="6">
         <v>2</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" s="4">
+      <c r="A141" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" s="8">
         <v>46090</v>
       </c>
-      <c r="C141">
+      <c r="C141" s="9">
         <v>7</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" s="4">
+      <c r="A142" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" s="5">
         <v>46079</v>
       </c>
-      <c r="C142">
+      <c r="C142" s="6">
         <v>4</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" s="4">
+      <c r="A143" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" s="8">
         <v>46015</v>
       </c>
-      <c r="C143">
+      <c r="C143" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" s="4">
+      <c r="A144" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" s="5">
         <v>46085</v>
       </c>
-      <c r="C144">
+      <c r="C144" s="6">
         <v>6</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" s="4">
+      <c r="A145" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" s="8">
         <v>46098</v>
       </c>
-      <c r="C145">
+      <c r="C145" s="9">
         <v>2</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" s="4">
+      <c r="A146" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" s="5">
         <v>46021</v>
       </c>
-      <c r="C146">
+      <c r="C146" s="6">
         <v>10</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" s="4">
+      <c r="A147" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" s="8">
         <v>46078</v>
       </c>
-      <c r="C147">
+      <c r="C147" s="9">
         <v>7</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" s="4">
+      <c r="A148" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" s="5">
         <v>46084</v>
       </c>
-      <c r="C148">
+      <c r="C148" s="6">
         <v>9</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" s="4">
+      <c r="A149" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" s="8">
         <v>46128</v>
       </c>
-      <c r="C149">
+      <c r="C149" s="9">
         <v>3</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" s="4">
+      <c r="A150" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" s="5">
         <v>46083</v>
       </c>
-      <c r="C150">
+      <c r="C150" s="6">
         <v>8</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" s="4">
+      <c r="A151" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" s="8">
+        <v>46153</v>
+      </c>
+      <c r="C151" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" s="5">
         <v>46076</v>
       </c>
-      <c r="C151">
+      <c r="C152" s="6">
         <v>7</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" s="4">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" s="8">
         <v>46099</v>
       </c>
-      <c r="C152">
+      <c r="C153" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" s="4">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" s="5">
         <v>46092</v>
       </c>
-      <c r="C153">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" s="4">
+      <c r="C154" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" s="8">
         <v>46031</v>
       </c>
-      <c r="C154">
+      <c r="C155" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" s="4">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" s="5">
         <v>46120</v>
       </c>
-      <c r="C155">
+      <c r="C156" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" s="4">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" s="8">
         <v>46077</v>
       </c>
-      <c r="C156">
+      <c r="C157" s="9">
         <v>5</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" s="4">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" s="5">
         <v>46114</v>
       </c>
-      <c r="C157">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" s="4">
+      <c r="C158" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" s="8">
         <v>46037</v>
       </c>
-      <c r="C158">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" s="4">
+      <c r="C159" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" s="5">
         <v>46020</v>
       </c>
-      <c r="C159">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" s="4">
+      <c r="C160" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" s="8">
         <v>46106</v>
       </c>
-      <c r="C160">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" s="4">
+      <c r="C161" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" s="5">
         <v>46112</v>
       </c>
-      <c r="C161">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" s="4">
+      <c r="C162" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" s="8">
         <v>46132</v>
       </c>
-      <c r="C162">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" s="4">
+      <c r="C163" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" s="5">
         <v>46108</v>
       </c>
-      <c r="C163">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" s="4">
+      <c r="C164" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" s="8">
         <v>46148</v>
       </c>
-      <c r="C164">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" s="4">
+      <c r="C165" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" s="5">
         <v>46118</v>
       </c>
-      <c r="C165">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" s="4">
+      <c r="C166" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" s="8">
         <v>46035</v>
       </c>
-      <c r="C166">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
-        <v>15</v>
-      </c>
-      <c r="B167" s="4">
+      <c r="C167" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" s="5">
         <v>46093</v>
       </c>
-      <c r="C167">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" s="4">
+      <c r="C168" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" s="8">
         <v>46022</v>
       </c>
-      <c r="C168">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" s="4">
+      <c r="C169" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" s="5">
         <v>46087</v>
       </c>
-      <c r="C169">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" s="4">
+      <c r="C170" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" s="8">
         <v>46030</v>
       </c>
-      <c r="C170">
+      <c r="C171" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" s="4">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" s="5">
         <v>46101</v>
       </c>
-      <c r="C171">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" s="4">
+      <c r="C172" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" s="8">
         <v>46142</v>
       </c>
-      <c r="C172">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
-        <v>21</v>
-      </c>
-      <c r="B173" s="4">
+      <c r="C173" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B174" s="5">
         <v>46001</v>
       </c>
-      <c r="C173">
+      <c r="C174" s="6">
         <v>154</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
-        <v>21</v>
-      </c>
-      <c r="B174" s="4">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B175" s="8">
         <v>46008</v>
       </c>
-      <c r="C174">
+      <c r="C175" s="9">
         <v>38</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
-        <v>21</v>
-      </c>
-      <c r="B175" s="4">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B176" s="5">
         <v>46003</v>
       </c>
-      <c r="C175">
+      <c r="C176" s="6">
         <v>70</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
-        <v>21</v>
-      </c>
-      <c r="B176" s="4">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B177" s="8">
         <v>46002</v>
       </c>
-      <c r="C176">
+      <c r="C177" s="9">
         <v>111</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
-        <v>21</v>
-      </c>
-      <c r="B177" s="4">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B178" s="5">
         <v>46006</v>
       </c>
-      <c r="C177">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A178" t="s">
-        <v>21</v>
-      </c>
-      <c r="B178" s="4">
+      <c r="C178" s="6">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B179" s="8">
         <v>46007</v>
       </c>
-      <c r="C178">
+      <c r="C179" s="9">
         <v>45</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A179" t="s">
-        <v>21</v>
-      </c>
-      <c r="B179" s="4">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B180" s="5">
         <v>46000</v>
       </c>
-      <c r="C179">
+      <c r="C180" s="6">
         <v>129</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
-        <v>21</v>
-      </c>
-      <c r="B180" s="4">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B181" s="8">
         <v>46084</v>
       </c>
-      <c r="C180">
+      <c r="C181" s="9">
         <v>10</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
-        <v>21</v>
-      </c>
-      <c r="B181" s="4">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B182" s="5">
         <v>46014</v>
       </c>
-      <c r="C181">
+      <c r="C182" s="6">
         <v>22</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
-        <v>21</v>
-      </c>
-      <c r="B182" s="4">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B183" s="8">
         <v>46013</v>
       </c>
-      <c r="C182">
+      <c r="C183" s="9">
         <v>29</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
-        <v>21</v>
-      </c>
-      <c r="B183" s="4">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B184" s="5">
         <v>46010</v>
       </c>
-      <c r="C183">
+      <c r="C184" s="6">
         <v>19</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
-        <v>21</v>
-      </c>
-      <c r="B184" s="4">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B185" s="8">
         <v>46021</v>
       </c>
-      <c r="C184">
+      <c r="C185" s="9">
         <v>6</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
-        <v>21</v>
-      </c>
-      <c r="B185" s="4">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B186" s="5">
         <v>46009</v>
       </c>
-      <c r="C185">
+      <c r="C186" s="6">
         <v>25</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
-        <v>21</v>
-      </c>
-      <c r="B186" s="4">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B187" s="8">
         <v>46083</v>
       </c>
-      <c r="C186">
+      <c r="C187" s="9">
         <v>8</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
-        <v>21</v>
-      </c>
-      <c r="B187" s="4">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B188" s="5">
         <v>46079</v>
       </c>
-      <c r="C187">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
-        <v>21</v>
-      </c>
-      <c r="B188" s="4">
+      <c r="C188" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B189" s="8">
         <v>46077</v>
       </c>
-      <c r="C188">
+      <c r="C189" s="9">
         <v>5</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
-        <v>21</v>
-      </c>
-      <c r="B189" s="4">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B190" s="5">
         <v>46035</v>
       </c>
-      <c r="C189">
+      <c r="C190" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
-        <v>21</v>
-      </c>
-      <c r="B190" s="4">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B191" s="8">
         <v>46085</v>
       </c>
-      <c r="C190">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A191" t="s">
-        <v>21</v>
-      </c>
-      <c r="B191" s="4">
+      <c r="C191" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B192" s="5">
         <v>46120</v>
       </c>
-      <c r="C191">
+      <c r="C192" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A192" t="s">
-        <v>21</v>
-      </c>
-      <c r="B192" s="4">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B193" s="8">
         <v>46114</v>
       </c>
-      <c r="C192">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A193" t="s">
-        <v>21</v>
-      </c>
-      <c r="B193" s="4">
+      <c r="C193" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B194" s="5">
         <v>46094</v>
       </c>
-      <c r="C193">
+      <c r="C194" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A194" t="s">
-        <v>21</v>
-      </c>
-      <c r="B194" s="4">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B195" s="8">
         <v>46080</v>
       </c>
-      <c r="C194">
+      <c r="C195" s="9">
         <v>7</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A195" t="s">
-        <v>21</v>
-      </c>
-      <c r="B195" s="4">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B196" s="5">
         <v>46127</v>
       </c>
-      <c r="C195">
+      <c r="C196" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
-        <v>21</v>
-      </c>
-      <c r="B196" s="4">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B197" s="8">
         <v>46091</v>
       </c>
-      <c r="C196">
+      <c r="C197" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
-        <v>21</v>
-      </c>
-      <c r="B197" s="4">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B198" s="5">
         <v>46090</v>
       </c>
-      <c r="C197">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A198" t="s">
-        <v>21</v>
-      </c>
-      <c r="B198" s="4">
+      <c r="C198" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B199" s="8">
         <v>46020</v>
       </c>
-      <c r="C198">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
-        <v>21</v>
-      </c>
-      <c r="B199" s="4">
+      <c r="C199" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B200" s="5">
         <v>46015</v>
       </c>
-      <c r="C199">
+      <c r="C200" s="6">
         <v>6</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
-        <v>21</v>
-      </c>
-      <c r="B200" s="4">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B201" s="8">
         <v>46113</v>
       </c>
-      <c r="C200">
+      <c r="C201" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
-        <v>21</v>
-      </c>
-      <c r="B201" s="4">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B202" s="5">
         <v>46078</v>
       </c>
-      <c r="C201">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A202" t="s">
-        <v>21</v>
-      </c>
-      <c r="B202" s="4">
+      <c r="C202" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B203" s="8">
         <v>46148</v>
       </c>
-      <c r="C202">
+      <c r="C203" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A203" t="s">
-        <v>21</v>
-      </c>
-      <c r="B203" s="4">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B204" s="5">
         <v>46105</v>
       </c>
-      <c r="C203">
+      <c r="C204" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
-        <v>21</v>
-      </c>
-      <c r="B204" s="4">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B205" s="8">
         <v>46087</v>
       </c>
-      <c r="C204">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A205" t="s">
-        <v>21</v>
-      </c>
-      <c r="B205" s="4">
+      <c r="C205" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B206" s="5">
         <v>46107</v>
       </c>
-      <c r="C205">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A206" t="s">
-        <v>21</v>
-      </c>
-      <c r="B206" s="4">
+      <c r="C206" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B207" s="8">
         <v>46086</v>
       </c>
-      <c r="C206">
+      <c r="C207" s="9">
         <v>4</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A207" t="s">
-        <v>21</v>
-      </c>
-      <c r="B207" s="4">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B208" s="5">
         <v>46106</v>
       </c>
-      <c r="C207">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A208" t="s">
-        <v>21</v>
-      </c>
-      <c r="B208" s="4">
+      <c r="C208" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B209" s="8">
         <v>46150</v>
       </c>
-      <c r="C208">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A209" t="s">
-        <v>21</v>
-      </c>
-      <c r="B209" s="4">
+      <c r="C209" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B210" s="5">
         <v>46104</v>
       </c>
-      <c r="C209">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A210" t="s">
-        <v>21</v>
-      </c>
-      <c r="B210" s="4">
+      <c r="C210" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B211" s="8">
         <v>46118</v>
       </c>
-      <c r="C210">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A211" t="s">
-        <v>21</v>
-      </c>
-      <c r="B211" s="4">
+      <c r="C211" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B212" s="5">
         <v>46076</v>
       </c>
-      <c r="C211">
+      <c r="C212" s="6">
         <v>11</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A212" t="s">
-        <v>21</v>
-      </c>
-      <c r="B212" s="4">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B213" s="8">
         <v>46093</v>
       </c>
-      <c r="C212">
+      <c r="C213" s="9">
         <v>4</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
-        <v>21</v>
-      </c>
-      <c r="B213" s="4">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B214" s="5">
         <v>46122</v>
       </c>
-      <c r="C213">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A214" t="s">
-        <v>21</v>
-      </c>
-      <c r="B214" s="4">
+      <c r="C214" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B215" s="8">
         <v>46092</v>
       </c>
-      <c r="C214">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A215" t="s">
-        <v>21</v>
-      </c>
-      <c r="B215" s="4">
+      <c r="C215" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B216" s="5">
         <v>46133</v>
       </c>
-      <c r="C215">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A216" t="s">
-        <v>21</v>
-      </c>
-      <c r="B216" s="4">
+      <c r="C216" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B217" s="8">
         <v>46126</v>
       </c>
-      <c r="C216">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A217" t="s">
-        <v>21</v>
-      </c>
-      <c r="B217" s="4">
+      <c r="C217" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B218" s="5">
         <v>46022</v>
       </c>
-      <c r="C217">
+      <c r="C218" s="6">
         <v>2</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A218" t="s">
-        <v>21</v>
-      </c>
-      <c r="B218" s="4">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B219" s="8">
         <v>46100</v>
       </c>
-      <c r="C218">
+      <c r="C219" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A219" t="s">
-        <v>21</v>
-      </c>
-      <c r="B219" s="4">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B220" s="5">
         <v>46101</v>
       </c>
-      <c r="C219">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A220" t="s">
-        <v>21</v>
-      </c>
-      <c r="B220" s="4">
+      <c r="C220" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B221" s="8">
         <v>46097</v>
       </c>
-      <c r="C220">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A221" t="s">
-        <v>21</v>
-      </c>
-      <c r="B221" s="4">
+      <c r="C221" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B222" s="5">
         <v>46108</v>
       </c>
-      <c r="C221">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A222" t="s">
-        <v>21</v>
-      </c>
-      <c r="B222" s="4">
+      <c r="C222" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B223" s="8">
         <v>46098</v>
       </c>
-      <c r="C222">
+      <c r="C223" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
-        <v>21</v>
-      </c>
-      <c r="B223" s="4">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B224" s="5">
         <v>46142</v>
       </c>
-      <c r="C223">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
-        <v>21</v>
-      </c>
-      <c r="B224" s="4">
+      <c r="C224" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B225" s="8">
+        <v>46153</v>
+      </c>
+      <c r="C225" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B226" s="5">
         <v>46031</v>
       </c>
-      <c r="C224">
+      <c r="C226" s="6">
         <v>1</v>
       </c>
     </row>

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65510C09-4A46-4D8D-B15E-68D7160F9804}"/>
+  <xr:revisionPtr revIDLastSave="69" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5131E768-AA99-4E87-AC4D-33B6FE5EF4F4}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="mat_2026" sheetId="1" r:id="rId1"/>
     <sheet name="proyeccion_2026" sheetId="2" r:id="rId2"/>
     <sheet name="genero" sheetId="3" r:id="rId3"/>
     <sheet name="mat_time" sheetId="4" r:id="rId4"/>
+    <sheet name="origen_estudiantes" sheetId="5" r:id="rId5"/>
+    <sheet name="origen_colegios" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">mat_2026!$A$1:$E$39</definedName>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="286">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -159,6 +161,747 @@
   </si>
   <si>
     <t>MATRICULA</t>
+  </si>
+  <si>
+    <t>INTERNO</t>
+  </si>
+  <si>
+    <t>NUEVO-SAE</t>
+  </si>
+  <si>
+    <t>ANOTATE-LISTA</t>
+  </si>
+  <si>
+    <t>Jardín Infantil Carrusel (Integra)</t>
+  </si>
+  <si>
+    <t>Escuela España</t>
+  </si>
+  <si>
+    <t>Colegio María Auxiliadora</t>
+  </si>
+  <si>
+    <t>Escuela Ferroviaria</t>
+  </si>
+  <si>
+    <t>Escuela Claudio Gay</t>
+  </si>
+  <si>
+    <t>Liceo Bicentenario San Esteban</t>
+  </si>
+  <si>
+    <t>Escuela Capitán Ignacio Carrera Pinto</t>
+  </si>
+  <si>
+    <t>Colegio San José</t>
+  </si>
+  <si>
+    <t>Colegio Alcázar</t>
+  </si>
+  <si>
+    <t>Escuela de Lenguaje Rayito de Luz</t>
+  </si>
+  <si>
+    <t>Colegio San Sebastián</t>
+  </si>
+  <si>
+    <t>Centro de Lenguaje Paicaví</t>
+  </si>
+  <si>
+    <t>Escuela Perfecto de la Fuente del Villar</t>
+  </si>
+  <si>
+    <t>CORPORACION EDUCACION HUMBERTO CASARINO</t>
+  </si>
+  <si>
+    <t>Escuela Aurora Velasco Pérez</t>
+  </si>
+  <si>
+    <t>Escuela Carmela Carvajal de Prat</t>
+  </si>
+  <si>
+    <t>Escuela María Isabel de Brown</t>
+  </si>
+  <si>
+    <t>Escuela Gabriela Mistral</t>
+  </si>
+  <si>
+    <t>Escuela Básica Lo Calvo</t>
+  </si>
+  <si>
+    <t>Colegio Alto Gabriela</t>
+  </si>
+  <si>
+    <t>Escuela John F. Kennedy</t>
+  </si>
+  <si>
+    <t>C. Educ. Prof. Guillermo González Heinrich</t>
+  </si>
+  <si>
+    <t>Escuela Básica La Pampilla</t>
+  </si>
+  <si>
+    <t>Colegio Educenter</t>
+  </si>
+  <si>
+    <t>Liceo Santa Clara</t>
+  </si>
+  <si>
+    <t>Escuela de Lenguaje Cumbres de Aconcagua</t>
+  </si>
+  <si>
+    <t>Escuela General José Miguel Carrera</t>
+  </si>
+  <si>
+    <t>Colegio Genesare</t>
+  </si>
+  <si>
+    <t>Escuela John Kennedy</t>
+  </si>
+  <si>
+    <t>Escuela El Corazón</t>
+  </si>
+  <si>
+    <t>Escuela Particular Jean Piaget</t>
+  </si>
+  <si>
+    <t>Escuela El Sauce</t>
+  </si>
+  <si>
+    <t>Escuela República de Argentina (ex Liceo)</t>
+  </si>
+  <si>
+    <t>Escuela Emigdio Galdames Robles</t>
+  </si>
+  <si>
+    <t>Escuela Básica Pablo Neruda</t>
+  </si>
+  <si>
+    <t>Colegio 21 de Mayo</t>
+  </si>
+  <si>
+    <t>Escuela Básica Río Blanco</t>
+  </si>
+  <si>
+    <t>Escuela Básica Cristo Redentor</t>
+  </si>
+  <si>
+    <t>EXTRANJERO</t>
+  </si>
+  <si>
+    <t>Escuela General Bernardo O'Higgins</t>
+  </si>
+  <si>
+    <t>Escuela Silvio Zenteno Valenzuela</t>
+  </si>
+  <si>
+    <t>Escuela Juan Gómez Millas</t>
+  </si>
+  <si>
+    <t>Colegio Villa Aconcagua</t>
+  </si>
+  <si>
+    <t>Colegio Metodista Edén del Niño</t>
+  </si>
+  <si>
+    <t>Escuela Kamac Mayu</t>
+  </si>
+  <si>
+    <t>Colegio San Luis</t>
+  </si>
+  <si>
+    <t>Liceo Bicentenario Corina Urbina</t>
+  </si>
+  <si>
+    <t>Jardín Infantil Pasitos Andinos</t>
+  </si>
+  <si>
+    <t>Escuela de Párvulos Kids Place</t>
+  </si>
+  <si>
+    <t>Jardín Infantil Pampanitos</t>
+  </si>
+  <si>
+    <t>Escuela Bucalemu</t>
+  </si>
+  <si>
+    <t>Jardín Infantil Carrusel (VTF)</t>
+  </si>
+  <si>
+    <t>Colegio Aconcagua</t>
+  </si>
+  <si>
+    <t>Liceo José Domingo Cañas</t>
+  </si>
+  <si>
+    <t>Escuela Especial de Lenguaje Ariki Mau</t>
+  </si>
+  <si>
+    <t>Escuela Ribera Sur</t>
+  </si>
+  <si>
+    <t>Escuela Especial de Lenguaje Curimón</t>
+  </si>
+  <si>
+    <t>Escuela de Lenguaje Mundo de Colores</t>
+  </si>
+  <si>
+    <t>Escuela Especial de Lenguaje Makiato</t>
+  </si>
+  <si>
+    <t>Jardín Infantil Gotita de Luna</t>
+  </si>
+  <si>
+    <t>Liceo Bicentenario Cordillera</t>
+  </si>
+  <si>
+    <t>Colegio Curimón</t>
+  </si>
+  <si>
+    <t>Colegio Sunnyland School</t>
+  </si>
+  <si>
+    <t>Escuela San Rafael</t>
+  </si>
+  <si>
+    <t>Escuela Guillermo Bañados Honorato</t>
+  </si>
+  <si>
+    <t>Escuela Sol de Medio Día</t>
+  </si>
+  <si>
+    <t>Escuela Inclusiva San Lorenzo</t>
+  </si>
+  <si>
+    <t>Colegio Inglés de Los Andes</t>
+  </si>
+  <si>
+    <t>Colegio Teodoro Lowey</t>
+  </si>
+  <si>
+    <t>Jardín Infantil El Portalito de Daniela</t>
+  </si>
+  <si>
+    <t>Escuela Básica Rucapequén</t>
+  </si>
+  <si>
+    <t>Jardín Infantil Montañita</t>
+  </si>
+  <si>
+    <t>Escuela Manuel León Salinas</t>
+  </si>
+  <si>
+    <t>Escuela Mixta Lo Calvo</t>
+  </si>
+  <si>
+    <t>Colegio San Pablo</t>
+  </si>
+  <si>
+    <t>Liceo Maximiliano Salas Marchán</t>
+  </si>
+  <si>
+    <t>Escuela Paso Histórico</t>
+  </si>
+  <si>
+    <t>Escuela Pedro Aguirre Cerda</t>
+  </si>
+  <si>
+    <t>Escuela Bolivia</t>
+  </si>
+  <si>
+    <t>Liceo San Felipe</t>
+  </si>
+  <si>
+    <t>Escuela José de San Martín</t>
+  </si>
+  <si>
+    <t>Jardín Infantil El Peneca</t>
+  </si>
+  <si>
+    <t>Escuela de Lenguaje Ote Moana</t>
+  </si>
+  <si>
+    <t>Escuela de Lenguaje Sembrando Palabras</t>
+  </si>
+  <si>
+    <t>Colegio Santa Juana de Arco</t>
+  </si>
+  <si>
+    <t>Colegio Alonso de Ercilla</t>
+  </si>
+  <si>
+    <t>Escuela José Manso de Velasco</t>
+  </si>
+  <si>
+    <t>Liceo Bicentenario Cordillera (ex-Alonso de Ercilla)</t>
+  </si>
+  <si>
+    <t>Escuela de Lenguaje Burbujitas de Colores</t>
+  </si>
+  <si>
+    <t>Escuela Esp. de Lenguaje Sembrando Palabras</t>
+  </si>
+  <si>
+    <t>Escuela Esp. de Lenguaje Hormiguitas de Aconcagua</t>
+  </si>
+  <si>
+    <t>Liceo Bicentenario Corina Urbina Villanueva</t>
+  </si>
+  <si>
+    <t>Escuela El Buen Pastor</t>
+  </si>
+  <si>
+    <t>Jardín Infantil Sol Naciente</t>
+  </si>
+  <si>
+    <t>Escuela Silvio Zenteno (Rinconada de Silva)</t>
+  </si>
+  <si>
+    <t>Colegio Pirámide</t>
+  </si>
+  <si>
+    <t>Escuela Básica Las Palmas</t>
+  </si>
+  <si>
+    <t>Colegio Marie Poussepin</t>
+  </si>
+  <si>
+    <t>Escuela de Lenguaje Magrace</t>
+  </si>
+  <si>
+    <t>Escuela María Angélica Elizondo Briceño</t>
+  </si>
+  <si>
+    <t>Escuela Santa Filomena</t>
+  </si>
+  <si>
+    <t>Liceo Bicentenario Oriente</t>
+  </si>
+  <si>
+    <t>Escuela Presidente Roosevelt</t>
+  </si>
+  <si>
+    <t>JI Hormiguitas de Aconcagua</t>
+  </si>
+  <si>
+    <t>Escuela Daniel Rivero Ochoa</t>
+  </si>
+  <si>
+    <t>Escuela de Lenguaje El Trigal</t>
+  </si>
+  <si>
+    <t>Escuela Julio Tejedor Zúñiga</t>
+  </si>
+  <si>
+    <t>Colegio Renacer</t>
+  </si>
+  <si>
+    <t>Escuela Chile</t>
+  </si>
+  <si>
+    <t>Colegio Lorenzo Sazie</t>
+  </si>
+  <si>
+    <t>Jardín Infantil Nicanor Parra</t>
+  </si>
+  <si>
+    <t>Colegio San Pedro Nolasco</t>
+  </si>
+  <si>
+    <t>Escuela de Lenguaje Voces del Valle</t>
+  </si>
+  <si>
+    <t>Escuela María Leiva de Ibáñez</t>
+  </si>
+  <si>
+    <t>Escuela de Lenguaje Yamanqui</t>
+  </si>
+  <si>
+    <t>Escuela República del Ecuador</t>
+  </si>
+  <si>
+    <t>Colegio Madres Dominicas</t>
+  </si>
+  <si>
+    <t>Jardín El Rincón de los Angelitos</t>
+  </si>
+  <si>
+    <t>Escuela Eliecer Pérez Vargas</t>
+  </si>
+  <si>
+    <t>Jardín Infantil Las Cuncunitas</t>
+  </si>
+  <si>
+    <t>Escuela Esp. de Lenguaje Aringa Poki</t>
+  </si>
+  <si>
+    <t>Escuela de Lenguaje Aneley</t>
+  </si>
+  <si>
+    <t>Colegio Santa María College</t>
+  </si>
+  <si>
+    <t>Escuela de Lenguaje Conejito Saltarin</t>
+  </si>
+  <si>
+    <t>Colegio Maese Da Vinci</t>
+  </si>
+  <si>
+    <t>Liceo Bicentenario María Mazzarello</t>
+  </si>
+  <si>
+    <t>Colegio Huillón</t>
+  </si>
+  <si>
+    <t>Colegio Araucarias</t>
+  </si>
+  <si>
+    <t>Escuela Particular Elsa Ramírez</t>
+  </si>
+  <si>
+    <t>Escuela Especial de Lenguaje Caicura</t>
+  </si>
+  <si>
+    <t>Escuela República de Argentina</t>
+  </si>
+  <si>
+    <t>Escuela Carolina Ocampo García</t>
+  </si>
+  <si>
+    <t>Colegio Vedruna</t>
+  </si>
+  <si>
+    <t>Escuela Valdivia de Paine</t>
+  </si>
+  <si>
+    <t>Jardín Infantil Campanitas de Jahuel</t>
+  </si>
+  <si>
+    <t>Escuela Guardiamarina Guillermo Zañartu</t>
+  </si>
+  <si>
+    <t>Jardín Infantil La Mazorquita</t>
+  </si>
+  <si>
+    <t>Escuela Jesús Fernández Hidalgo</t>
+  </si>
+  <si>
+    <t>Jardín Infantil Los Pingüinitos</t>
+  </si>
+  <si>
+    <t>Escuela Adelaida Miguieles Soto</t>
+  </si>
+  <si>
+    <t>Jardín Infantil Renacer</t>
+  </si>
+  <si>
+    <t>Jardín Infantil Terranova</t>
+  </si>
+  <si>
+    <t>Colegio Charles Darwin</t>
+  </si>
+  <si>
+    <t>Colegio Poeta de Chile</t>
+  </si>
+  <si>
+    <t>Escuela José de San Martín (Ex E-62)</t>
+  </si>
+  <si>
+    <t>Escuela José Ibáñez</t>
+  </si>
+  <si>
+    <t>Escuela de Lenguaje Curimón</t>
+  </si>
+  <si>
+    <t>Escuela Básica Pablo Neruda (Ex-Rep. de Brasil)</t>
+  </si>
+  <si>
+    <t>Liceo Doctor Roberto Humeres Oyaneder</t>
+  </si>
+  <si>
+    <t>Colegio Albert Einstein</t>
+  </si>
+  <si>
+    <t>Escuela Esp. de Lenguaje Yamanqui</t>
+  </si>
+  <si>
+    <t>Escuela Especial de Lenguaje Aringa Poki</t>
+  </si>
+  <si>
+    <t>Instituto Agrícola Pascual Baburizza</t>
+  </si>
+  <si>
+    <t>Escuela Particular San José</t>
+  </si>
+  <si>
+    <t>Liceo Comercial Particular Los Andes</t>
+  </si>
+  <si>
+    <t>Colegio Assunta Pallota</t>
+  </si>
+  <si>
+    <t>Escuela Pablo Neruda</t>
+  </si>
+  <si>
+    <t>Liceo Bicentenario Técnico Amancay</t>
+  </si>
+  <si>
+    <t>Liceo Politécnico América</t>
+  </si>
+  <si>
+    <t>Liceo Técnico Profesional Pedro Aguirre Cerda</t>
+  </si>
+  <si>
+    <t>Colegio Brega College</t>
+  </si>
+  <si>
+    <t>Escuela Agrícola de San Felipe</t>
+  </si>
+  <si>
+    <t>Escuela Víctor Koerner</t>
+  </si>
+  <si>
+    <t>Escuela Básica Silvio Zenteno Vergara</t>
+  </si>
+  <si>
+    <t>Colegio Altos del Huerto</t>
+  </si>
+  <si>
+    <t>Escuela España (frecuente confusión como "Nueva")</t>
+  </si>
+  <si>
+    <t>Escuela Particular La Merced</t>
+  </si>
+  <si>
+    <t>Liceo Neandro Schilling</t>
+  </si>
+  <si>
+    <t>Centro Educacional Principado de Asturias</t>
+  </si>
+  <si>
+    <t>Proyecto Virtual (sin RBD tradicional)</t>
+  </si>
+  <si>
+    <t>Colegio Excelsior</t>
+  </si>
+  <si>
+    <t>Liceo Huertos Familiares</t>
+  </si>
+  <si>
+    <t>Liceo Técnico Prof. Juan Bautista de la Salle</t>
+  </si>
+  <si>
+    <t>Escuela Básica Libertad</t>
+  </si>
+  <si>
+    <t>Liceo Valentín Letelier Madariaga</t>
+  </si>
+  <si>
+    <t>Proyecto Online (sin RBD físico)</t>
+  </si>
+  <si>
+    <t>Escuela Mil Paisajes</t>
+  </si>
+  <si>
+    <t>Colegio Compañía de María</t>
+  </si>
+  <si>
+    <t>Liceo Polivalente Manuel Rodríguez</t>
+  </si>
+  <si>
+    <t>Liceo Polivalente Rigoberto Fontt</t>
+  </si>
+  <si>
+    <t>Colegio Dalmacia</t>
+  </si>
+  <si>
+    <t>Colegio Chillán</t>
+  </si>
+  <si>
+    <t>Escuela Parroquial Domingo Savio</t>
+  </si>
+  <si>
+    <t>Colegio La Merced</t>
+  </si>
+  <si>
+    <t>Colegio Portaliano</t>
+  </si>
+  <si>
+    <t>Liceo Bicentenario Vicente Pérez Rosales</t>
+  </si>
+  <si>
+    <t>Liceo Parroquial Teresita de Los Andes</t>
+  </si>
+  <si>
+    <t>Centro Educacional Joao de Oliveira Botas</t>
+  </si>
+  <si>
+    <t>Colegio San Pedro</t>
+  </si>
+  <si>
+    <t>Liceo José Manuel Borgoño Núñez</t>
+  </si>
+  <si>
+    <t>Colegio Lonquén</t>
+  </si>
+  <si>
+    <t>Liceo Melinka</t>
+  </si>
+  <si>
+    <t>Escuela Paulo Freire (ex 422)</t>
+  </si>
+  <si>
+    <t>Colegio Terraustral Oeste</t>
+  </si>
+  <si>
+    <t>Colegio Andes Chile</t>
+  </si>
+  <si>
+    <t>Liceo Politécnico El Señor de Renca</t>
+  </si>
+  <si>
+    <t>Colegio San Gregorio de La Salle</t>
+  </si>
+  <si>
+    <t>Escuela Patricio Lynch</t>
+  </si>
+  <si>
+    <t>Liceo San Gerónimo</t>
+  </si>
+  <si>
+    <t>Escuela Nuestra Señora de Andacollo</t>
+  </si>
+  <si>
+    <t>Colegio Nuevo Horizonte</t>
+  </si>
+  <si>
+    <t>OTRO</t>
+  </si>
+  <si>
+    <t>Colegio Adventista de San Felipe</t>
+  </si>
+  <si>
+    <t>Escuela Francisco Petrinovich</t>
+  </si>
+  <si>
+    <t>Escuela Almendral</t>
+  </si>
+  <si>
+    <t>Escuela Industrial Guillermo Richards Cuevas</t>
+  </si>
+  <si>
+    <t>Liceo Bicentenario Industrial G. Richards Cuevas</t>
+  </si>
+  <si>
+    <t>Liceo Manuel Marín Fritis</t>
+  </si>
+  <si>
+    <t>Liceo Darío Salas</t>
+  </si>
+  <si>
+    <t>Colegio Particular Pumanque</t>
+  </si>
+  <si>
+    <t>Escuela Manuel Rodríguez Erdoíza</t>
+  </si>
+  <si>
+    <t>Escuela José Bernardo Suárez</t>
+  </si>
+  <si>
+    <t>Colegio Santa María de Aconcagua</t>
+  </si>
+  <si>
+    <t>CEIA Juan Francisco González</t>
+  </si>
+  <si>
+    <t>Escuela Independencia (ex F-80)</t>
+  </si>
+  <si>
+    <t>Liceo Bicentenario Panquehue</t>
+  </si>
+  <si>
+    <t>Escuela Básica El Buen Pastor</t>
+  </si>
+  <si>
+    <t>Escuela Herminia Ortega de Croxatto</t>
+  </si>
+  <si>
+    <t>Liceo Dr. John Kennedy</t>
+  </si>
+  <si>
+    <t>Colegio Inmaculada Concepción</t>
+  </si>
+  <si>
+    <t>Colegio Saint George School</t>
+  </si>
+  <si>
+    <t>Liceo Brígida Walker</t>
+  </si>
+  <si>
+    <t>Colegio Sendero del Saber</t>
+  </si>
+  <si>
+    <t>Colegio San Alberto Magno</t>
+  </si>
+  <si>
+    <t>Colegio San Andrés de Colina</t>
+  </si>
+  <si>
+    <t>Liceo Bicentenario Santa María de Aconcagua</t>
+  </si>
+  <si>
+    <t>Colegio Polivalente Francisco Ramírez</t>
+  </si>
+  <si>
+    <t>Colegio Verdoyham School</t>
+  </si>
+  <si>
+    <t>Escuela Ema Lobos Reyes</t>
+  </si>
+  <si>
+    <t>Liceo Bicentenario Cumbres de Cóndores</t>
+  </si>
+  <si>
+    <t>Escuela Agrícola Salesiana Fundación Huidobro</t>
+  </si>
+  <si>
+    <t>Liceo Bicentenario Llay Llay</t>
+  </si>
+  <si>
+    <t>Colegio Aconcagua Educa</t>
+  </si>
+  <si>
+    <t>Escuela María Teresa del Canto</t>
+  </si>
+  <si>
+    <t>Escuela Mateo Cokljat Knippe</t>
+  </si>
+  <si>
+    <t>Liceo Cap. de Corbeta Pedro González P.</t>
+  </si>
+  <si>
+    <t>Escuela Básica Carolina Ocampo García</t>
+  </si>
+  <si>
+    <t>Escuela Profesora Aurelia Rojas Burgos</t>
+  </si>
+  <si>
+    <t>Liceo Panquehue</t>
+  </si>
+  <si>
+    <t>Liceo Salvador González</t>
+  </si>
+  <si>
+    <t>Colegio Cumbres de Llay Llay</t>
+  </si>
+  <si>
+    <t>Colegio Genesaret</t>
+  </si>
+  <si>
+    <t>Escuela Jorge Alessandri Rodríguez</t>
+  </si>
+  <si>
+    <t>PROCEDENCIA</t>
   </si>
 </sst>
 </file>
@@ -707,10 +1450,10 @@
         <v>58</v>
       </c>
       <c r="D6">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E6">
-        <v>1.052</v>
+        <v>1.034</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -724,10 +1467,10 @@
         <v>61</v>
       </c>
       <c r="D7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E7">
-        <v>1.0489999999999999</v>
+        <v>1.0660000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1149,10 +1892,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="E32">
-        <v>1.0780000000000001</v>
+        <v>1.071</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1166,10 +1909,10 @@
         <v>329</v>
       </c>
       <c r="D33">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="E33">
-        <v>1.0429999999999999</v>
+        <v>1.0269999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1183,10 +1926,10 @@
         <v>323</v>
       </c>
       <c r="D34">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E34">
-        <v>0.96299999999999997</v>
+        <v>0.95699999999999996</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1217,10 +1960,10 @@
         <v>250</v>
       </c>
       <c r="D36">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E36">
-        <v>1.004</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1234,10 +1977,10 @@
         <v>217</v>
       </c>
       <c r="D37">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E37">
-        <v>1.0089999999999999</v>
+        <v>1.0049999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1268,10 +2011,10 @@
         <v>214</v>
       </c>
       <c r="D39">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E39">
-        <v>0.94899999999999995</v>
+        <v>0.94399999999999995</v>
       </c>
     </row>
   </sheetData>
@@ -1542,7 +2285,7 @@
         <v>34</v>
       </c>
       <c r="C8">
-        <v>599</v>
+        <v>592</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1553,7 +2296,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>701</v>
+        <v>698</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1575,7 +2318,7 @@
         <v>34</v>
       </c>
       <c r="C11">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
   </sheetData>
@@ -1585,7 +2328,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD19485A-0629-47F9-A5AD-80ABA7A6E076}">
-  <dimension ref="A1:C226"/>
+  <dimension ref="A1:C231"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -1612,7 +2355,7 @@
         <v>46009</v>
       </c>
       <c r="C2" s="6">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1623,7 +2366,7 @@
         <v>46008</v>
       </c>
       <c r="C3" s="9">
-        <v>302</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1667,7 +2410,7 @@
         <v>46014</v>
       </c>
       <c r="C7" s="9">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1700,7 +2443,7 @@
         <v>46007</v>
       </c>
       <c r="C10" s="6">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -2082,7 +2825,7 @@
         <v>16</v>
       </c>
       <c r="B45" s="8">
-        <v>46092</v>
+        <v>46156</v>
       </c>
       <c r="C45" s="9">
         <v>1</v>
@@ -2093,7 +2836,7 @@
         <v>16</v>
       </c>
       <c r="B46" s="5">
-        <v>46101</v>
+        <v>46092</v>
       </c>
       <c r="C46" s="6">
         <v>1</v>
@@ -2101,13 +2844,13 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B47" s="8">
-        <v>46007</v>
+        <v>46101</v>
       </c>
       <c r="C47" s="9">
-        <v>79</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -2115,10 +2858,10 @@
         <v>14</v>
       </c>
       <c r="B48" s="5">
-        <v>46009</v>
+        <v>46007</v>
       </c>
       <c r="C48" s="6">
-        <v>34</v>
+        <v>79</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -2126,10 +2869,10 @@
         <v>14</v>
       </c>
       <c r="B49" s="8">
-        <v>46000</v>
+        <v>46009</v>
       </c>
       <c r="C49" s="9">
-        <v>82</v>
+        <v>34</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -2137,10 +2880,10 @@
         <v>14</v>
       </c>
       <c r="B50" s="5">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C50" s="6">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -2148,10 +2891,10 @@
         <v>14</v>
       </c>
       <c r="B51" s="8">
-        <v>46006</v>
+        <v>46001</v>
       </c>
       <c r="C51" s="9">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -2159,10 +2902,10 @@
         <v>14</v>
       </c>
       <c r="B52" s="5">
-        <v>46010</v>
+        <v>46006</v>
       </c>
       <c r="C52" s="6">
-        <v>24</v>
+        <v>79</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -2170,10 +2913,10 @@
         <v>14</v>
       </c>
       <c r="B53" s="8">
-        <v>46014</v>
+        <v>46010</v>
       </c>
       <c r="C53" s="9">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -2181,10 +2924,10 @@
         <v>14</v>
       </c>
       <c r="B54" s="5">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="C54" s="6">
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -2192,10 +2935,10 @@
         <v>14</v>
       </c>
       <c r="B55" s="8">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C55" s="9">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -2203,10 +2946,10 @@
         <v>14</v>
       </c>
       <c r="B56" s="5">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="C56" s="6">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -2214,10 +2957,10 @@
         <v>14</v>
       </c>
       <c r="B57" s="8">
-        <v>46013</v>
+        <v>46003</v>
       </c>
       <c r="C57" s="9">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -2225,10 +2968,10 @@
         <v>14</v>
       </c>
       <c r="B58" s="5">
-        <v>46022</v>
+        <v>46013</v>
       </c>
       <c r="C58" s="6">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -2236,10 +2979,10 @@
         <v>14</v>
       </c>
       <c r="B59" s="8">
-        <v>46080</v>
+        <v>46022</v>
       </c>
       <c r="C59" s="9">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -2247,10 +2990,10 @@
         <v>14</v>
       </c>
       <c r="B60" s="5">
-        <v>46084</v>
+        <v>46080</v>
       </c>
       <c r="C60" s="6">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -2258,10 +3001,10 @@
         <v>14</v>
       </c>
       <c r="B61" s="8">
-        <v>46125</v>
+        <v>46084</v>
       </c>
       <c r="C61" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -2269,10 +3012,10 @@
         <v>14</v>
       </c>
       <c r="B62" s="5">
-        <v>46091</v>
+        <v>46125</v>
       </c>
       <c r="C62" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -2280,10 +3023,10 @@
         <v>14</v>
       </c>
       <c r="B63" s="8">
-        <v>46083</v>
+        <v>46091</v>
       </c>
       <c r="C63" s="9">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -2291,10 +3034,10 @@
         <v>14</v>
       </c>
       <c r="B64" s="5">
-        <v>46105</v>
+        <v>46083</v>
       </c>
       <c r="C64" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -2302,10 +3045,10 @@
         <v>14</v>
       </c>
       <c r="B65" s="8">
-        <v>46077</v>
+        <v>46105</v>
       </c>
       <c r="C65" s="9">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -2313,10 +3056,10 @@
         <v>14</v>
       </c>
       <c r="B66" s="5">
-        <v>46118</v>
+        <v>46077</v>
       </c>
       <c r="C66" s="6">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -2324,10 +3067,10 @@
         <v>14</v>
       </c>
       <c r="B67" s="8">
-        <v>46078</v>
+        <v>46118</v>
       </c>
       <c r="C67" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -2335,10 +3078,10 @@
         <v>14</v>
       </c>
       <c r="B68" s="5">
-        <v>46099</v>
+        <v>46078</v>
       </c>
       <c r="C68" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -2346,10 +3089,10 @@
         <v>14</v>
       </c>
       <c r="B69" s="8">
-        <v>46104</v>
+        <v>46099</v>
       </c>
       <c r="C69" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -2357,10 +3100,10 @@
         <v>14</v>
       </c>
       <c r="B70" s="5">
-        <v>46107</v>
+        <v>46104</v>
       </c>
       <c r="C70" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -2368,7 +3111,7 @@
         <v>14</v>
       </c>
       <c r="B71" s="8">
-        <v>46020</v>
+        <v>46107</v>
       </c>
       <c r="C71" s="9">
         <v>2</v>
@@ -2379,10 +3122,10 @@
         <v>14</v>
       </c>
       <c r="B72" s="5">
-        <v>46076</v>
+        <v>46020</v>
       </c>
       <c r="C72" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -2390,10 +3133,10 @@
         <v>14</v>
       </c>
       <c r="B73" s="8">
-        <v>46111</v>
+        <v>46076</v>
       </c>
       <c r="C73" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -2401,10 +3144,10 @@
         <v>14</v>
       </c>
       <c r="B74" s="5">
-        <v>46087</v>
+        <v>46111</v>
       </c>
       <c r="C74" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -2412,7 +3155,7 @@
         <v>14</v>
       </c>
       <c r="B75" s="8">
-        <v>46140</v>
+        <v>46087</v>
       </c>
       <c r="C75" s="9">
         <v>2</v>
@@ -2423,10 +3166,10 @@
         <v>14</v>
       </c>
       <c r="B76" s="5">
-        <v>46113</v>
+        <v>46140</v>
       </c>
       <c r="C76" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -2434,10 +3177,10 @@
         <v>14</v>
       </c>
       <c r="B77" s="8">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="C77" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -2445,10 +3188,10 @@
         <v>14</v>
       </c>
       <c r="B78" s="5">
-        <v>46108</v>
+        <v>46119</v>
       </c>
       <c r="C78" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -2456,7 +3199,7 @@
         <v>14</v>
       </c>
       <c r="B79" s="8">
-        <v>46098</v>
+        <v>46108</v>
       </c>
       <c r="C79" s="9">
         <v>1</v>
@@ -2467,7 +3210,7 @@
         <v>14</v>
       </c>
       <c r="B80" s="5">
-        <v>46141</v>
+        <v>46098</v>
       </c>
       <c r="C80" s="6">
         <v>1</v>
@@ -2478,7 +3221,7 @@
         <v>14</v>
       </c>
       <c r="B81" s="8">
-        <v>46114</v>
+        <v>46141</v>
       </c>
       <c r="C81" s="9">
         <v>1</v>
@@ -2489,10 +3232,10 @@
         <v>14</v>
       </c>
       <c r="B82" s="5">
-        <v>46079</v>
+        <v>46114</v>
       </c>
       <c r="C82" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -2500,10 +3243,10 @@
         <v>14</v>
       </c>
       <c r="B83" s="8">
-        <v>46139</v>
+        <v>46079</v>
       </c>
       <c r="C83" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -2511,10 +3254,10 @@
         <v>14</v>
       </c>
       <c r="B84" s="5">
-        <v>46148</v>
+        <v>46139</v>
       </c>
       <c r="C84" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -2522,10 +3265,10 @@
         <v>14</v>
       </c>
       <c r="B85" s="8">
-        <v>46092</v>
+        <v>46148</v>
       </c>
       <c r="C85" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -2533,10 +3276,10 @@
         <v>14</v>
       </c>
       <c r="B86" s="5">
-        <v>46021</v>
+        <v>46092</v>
       </c>
       <c r="C86" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -2544,10 +3287,10 @@
         <v>14</v>
       </c>
       <c r="B87" s="8">
-        <v>46086</v>
+        <v>46021</v>
       </c>
       <c r="C87" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -2555,10 +3298,10 @@
         <v>14</v>
       </c>
       <c r="B88" s="5">
-        <v>46147</v>
+        <v>46086</v>
       </c>
       <c r="C88" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -2566,7 +3309,7 @@
         <v>14</v>
       </c>
       <c r="B89" s="8">
-        <v>46134</v>
+        <v>46147</v>
       </c>
       <c r="C89" s="9">
         <v>1</v>
@@ -2574,13 +3317,13 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B90" s="5">
-        <v>46003</v>
+        <v>46134</v>
       </c>
       <c r="C90" s="6">
-        <v>95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -2588,10 +3331,10 @@
         <v>3</v>
       </c>
       <c r="B91" s="8">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="C91" s="9">
-        <v>116</v>
+        <v>95</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -2599,10 +3342,10 @@
         <v>3</v>
       </c>
       <c r="B92" s="5">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C92" s="6">
-        <v>15</v>
+        <v>116</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -2610,10 +3353,10 @@
         <v>3</v>
       </c>
       <c r="B93" s="8">
-        <v>46000</v>
+        <v>46008</v>
       </c>
       <c r="C93" s="9">
-        <v>99</v>
+        <v>15</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -2621,10 +3364,10 @@
         <v>3</v>
       </c>
       <c r="B94" s="5">
-        <v>46007</v>
+        <v>46000</v>
       </c>
       <c r="C94" s="6">
-        <v>43</v>
+        <v>98</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -2632,10 +3375,10 @@
         <v>3</v>
       </c>
       <c r="B95" s="8">
-        <v>46001</v>
+        <v>46007</v>
       </c>
       <c r="C95" s="9">
-        <v>91</v>
+        <v>43</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -2643,10 +3386,10 @@
         <v>3</v>
       </c>
       <c r="B96" s="5">
-        <v>46010</v>
+        <v>46001</v>
       </c>
       <c r="C96" s="6">
-        <v>9</v>
+        <v>91</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -2654,10 +3397,10 @@
         <v>3</v>
       </c>
       <c r="B97" s="8">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="C97" s="9">
-        <v>84</v>
+        <v>9</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -2665,10 +3408,10 @@
         <v>3</v>
       </c>
       <c r="B98" s="5">
-        <v>46009</v>
+        <v>46006</v>
       </c>
       <c r="C98" s="6">
-        <v>2</v>
+        <v>84</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -2676,10 +3419,10 @@
         <v>3</v>
       </c>
       <c r="B99" s="8">
-        <v>46015</v>
+        <v>46009</v>
       </c>
       <c r="C99" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -2687,10 +3430,10 @@
         <v>3</v>
       </c>
       <c r="B100" s="5">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="C100" s="6">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -2698,10 +3441,10 @@
         <v>3</v>
       </c>
       <c r="B101" s="8">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="C101" s="9">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -2709,10 +3452,10 @@
         <v>3</v>
       </c>
       <c r="B102" s="5">
-        <v>46021</v>
+        <v>46013</v>
       </c>
       <c r="C102" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -2720,10 +3463,10 @@
         <v>3</v>
       </c>
       <c r="B103" s="8">
-        <v>46077</v>
+        <v>46021</v>
       </c>
       <c r="C103" s="9">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -2731,10 +3474,10 @@
         <v>3</v>
       </c>
       <c r="B104" s="5">
-        <v>46090</v>
+        <v>46077</v>
       </c>
       <c r="C104" s="6">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -2742,10 +3485,10 @@
         <v>3</v>
       </c>
       <c r="B105" s="8">
-        <v>46093</v>
+        <v>46090</v>
       </c>
       <c r="C105" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -2753,10 +3496,10 @@
         <v>3</v>
       </c>
       <c r="B106" s="5">
-        <v>46078</v>
+        <v>46093</v>
       </c>
       <c r="C106" s="6">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -2764,10 +3507,10 @@
         <v>3</v>
       </c>
       <c r="B107" s="8">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="C107" s="9">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -2775,10 +3518,10 @@
         <v>3</v>
       </c>
       <c r="B108" s="5">
-        <v>46134</v>
+        <v>46084</v>
       </c>
       <c r="C108" s="6">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -2786,10 +3529,10 @@
         <v>3</v>
       </c>
       <c r="B109" s="8">
-        <v>46083</v>
+        <v>46134</v>
       </c>
       <c r="C109" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -2797,10 +3540,10 @@
         <v>3</v>
       </c>
       <c r="B110" s="5">
-        <v>46022</v>
+        <v>46083</v>
       </c>
       <c r="C110" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -2808,10 +3551,10 @@
         <v>3</v>
       </c>
       <c r="B111" s="8">
-        <v>46114</v>
+        <v>46022</v>
       </c>
       <c r="C111" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -2819,10 +3562,10 @@
         <v>3</v>
       </c>
       <c r="B112" s="5">
-        <v>46135</v>
+        <v>46114</v>
       </c>
       <c r="C112" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -2830,10 +3573,10 @@
         <v>3</v>
       </c>
       <c r="B113" s="8">
-        <v>46126</v>
+        <v>46135</v>
       </c>
       <c r="C113" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -2841,7 +3584,7 @@
         <v>3</v>
       </c>
       <c r="B114" s="5">
-        <v>46120</v>
+        <v>46126</v>
       </c>
       <c r="C114" s="6">
         <v>3</v>
@@ -2852,10 +3595,10 @@
         <v>3</v>
       </c>
       <c r="B115" s="8">
-        <v>46127</v>
+        <v>46120</v>
       </c>
       <c r="C115" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -2863,7 +3606,7 @@
         <v>3</v>
       </c>
       <c r="B116" s="5">
-        <v>46087</v>
+        <v>46127</v>
       </c>
       <c r="C116" s="6">
         <v>1</v>
@@ -2874,7 +3617,7 @@
         <v>3</v>
       </c>
       <c r="B117" s="8">
-        <v>46108</v>
+        <v>46087</v>
       </c>
       <c r="C117" s="9">
         <v>1</v>
@@ -2885,7 +3628,7 @@
         <v>3</v>
       </c>
       <c r="B118" s="5">
-        <v>46020</v>
+        <v>46108</v>
       </c>
       <c r="C118" s="6">
         <v>1</v>
@@ -2896,7 +3639,7 @@
         <v>3</v>
       </c>
       <c r="B119" s="8">
-        <v>46097</v>
+        <v>46020</v>
       </c>
       <c r="C119" s="9">
         <v>1</v>
@@ -2907,7 +3650,7 @@
         <v>3</v>
       </c>
       <c r="B120" s="5">
-        <v>46129</v>
+        <v>46097</v>
       </c>
       <c r="C120" s="6">
         <v>1</v>
@@ -2918,7 +3661,7 @@
         <v>3</v>
       </c>
       <c r="B121" s="8">
-        <v>46080</v>
+        <v>46129</v>
       </c>
       <c r="C121" s="9">
         <v>1</v>
@@ -2929,7 +3672,7 @@
         <v>3</v>
       </c>
       <c r="B122" s="5">
-        <v>46101</v>
+        <v>46080</v>
       </c>
       <c r="C122" s="6">
         <v>1</v>
@@ -2940,7 +3683,7 @@
         <v>3</v>
       </c>
       <c r="B123" s="8">
-        <v>46150</v>
+        <v>46101</v>
       </c>
       <c r="C123" s="9">
         <v>1</v>
@@ -2951,7 +3694,7 @@
         <v>3</v>
       </c>
       <c r="B124" s="5">
-        <v>46141</v>
+        <v>46155</v>
       </c>
       <c r="C124" s="6">
         <v>1</v>
@@ -2962,7 +3705,7 @@
         <v>3</v>
       </c>
       <c r="B125" s="8">
-        <v>46085</v>
+        <v>46150</v>
       </c>
       <c r="C125" s="9">
         <v>1</v>
@@ -2973,7 +3716,7 @@
         <v>3</v>
       </c>
       <c r="B126" s="5">
-        <v>46148</v>
+        <v>46141</v>
       </c>
       <c r="C126" s="6">
         <v>1</v>
@@ -2984,10 +3727,10 @@
         <v>3</v>
       </c>
       <c r="B127" s="8">
-        <v>46118</v>
+        <v>46085</v>
       </c>
       <c r="C127" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -2995,7 +3738,7 @@
         <v>3</v>
       </c>
       <c r="B128" s="5">
-        <v>46079</v>
+        <v>46148</v>
       </c>
       <c r="C128" s="6">
         <v>1</v>
@@ -3003,24 +3746,24 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B129" s="8">
-        <v>46003</v>
+        <v>46118</v>
       </c>
       <c r="C129" s="9">
-        <v>92</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B130" s="5">
-        <v>46000</v>
+        <v>46079</v>
       </c>
       <c r="C130" s="6">
-        <v>133</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -3028,10 +3771,10 @@
         <v>15</v>
       </c>
       <c r="B131" s="8">
-        <v>46006</v>
+        <v>46003</v>
       </c>
       <c r="C131" s="9">
-        <v>175</v>
+        <v>92</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -3039,10 +3782,10 @@
         <v>15</v>
       </c>
       <c r="B132" s="5">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C132" s="6">
-        <v>174</v>
+        <v>133</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -3050,10 +3793,10 @@
         <v>15</v>
       </c>
       <c r="B133" s="8">
-        <v>46014</v>
+        <v>46006</v>
       </c>
       <c r="C133" s="9">
-        <v>16</v>
+        <v>175</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -3061,10 +3804,10 @@
         <v>15</v>
       </c>
       <c r="B134" s="5">
-        <v>46002</v>
+        <v>46001</v>
       </c>
       <c r="C134" s="6">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -3072,10 +3815,10 @@
         <v>15</v>
       </c>
       <c r="B135" s="8">
-        <v>46009</v>
+        <v>46014</v>
       </c>
       <c r="C135" s="9">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -3083,10 +3826,10 @@
         <v>15</v>
       </c>
       <c r="B136" s="5">
-        <v>46010</v>
+        <v>46002</v>
       </c>
       <c r="C136" s="6">
-        <v>19</v>
+        <v>171</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -3094,10 +3837,10 @@
         <v>15</v>
       </c>
       <c r="B137" s="8">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="C137" s="9">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -3105,10 +3848,10 @@
         <v>15</v>
       </c>
       <c r="B138" s="5">
-        <v>46007</v>
+        <v>46010</v>
       </c>
       <c r="C138" s="6">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -3116,10 +3859,10 @@
         <v>15</v>
       </c>
       <c r="B139" s="8">
-        <v>46013</v>
+        <v>46008</v>
       </c>
       <c r="C139" s="9">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -3127,10 +3870,10 @@
         <v>15</v>
       </c>
       <c r="B140" s="5">
-        <v>46080</v>
+        <v>46007</v>
       </c>
       <c r="C140" s="6">
-        <v>2</v>
+        <v>43</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -3138,10 +3881,10 @@
         <v>15</v>
       </c>
       <c r="B141" s="8">
-        <v>46090</v>
+        <v>46013</v>
       </c>
       <c r="C141" s="9">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -3149,10 +3892,10 @@
         <v>15</v>
       </c>
       <c r="B142" s="5">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="C142" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -3160,10 +3903,10 @@
         <v>15</v>
       </c>
       <c r="B143" s="8">
-        <v>46015</v>
+        <v>46090</v>
       </c>
       <c r="C143" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -3171,10 +3914,10 @@
         <v>15</v>
       </c>
       <c r="B144" s="5">
-        <v>46085</v>
+        <v>46079</v>
       </c>
       <c r="C144" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -3182,10 +3925,10 @@
         <v>15</v>
       </c>
       <c r="B145" s="8">
-        <v>46098</v>
+        <v>46015</v>
       </c>
       <c r="C145" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -3193,10 +3936,10 @@
         <v>15</v>
       </c>
       <c r="B146" s="5">
-        <v>46021</v>
+        <v>46085</v>
       </c>
       <c r="C146" s="6">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -3204,10 +3947,10 @@
         <v>15</v>
       </c>
       <c r="B147" s="8">
-        <v>46078</v>
+        <v>46098</v>
       </c>
       <c r="C147" s="9">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -3215,10 +3958,10 @@
         <v>15</v>
       </c>
       <c r="B148" s="5">
-        <v>46084</v>
+        <v>46021</v>
       </c>
       <c r="C148" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -3226,10 +3969,10 @@
         <v>15</v>
       </c>
       <c r="B149" s="8">
-        <v>46128</v>
+        <v>46078</v>
       </c>
       <c r="C149" s="9">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -3237,10 +3980,10 @@
         <v>15</v>
       </c>
       <c r="B150" s="5">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="C150" s="6">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -3248,10 +3991,10 @@
         <v>15</v>
       </c>
       <c r="B151" s="8">
-        <v>46153</v>
+        <v>46128</v>
       </c>
       <c r="C151" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -3259,10 +4002,10 @@
         <v>15</v>
       </c>
       <c r="B152" s="5">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="C152" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -3270,10 +4013,10 @@
         <v>15</v>
       </c>
       <c r="B153" s="8">
-        <v>46099</v>
+        <v>46153</v>
       </c>
       <c r="C153" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -3281,10 +4024,10 @@
         <v>15</v>
       </c>
       <c r="B154" s="5">
-        <v>46092</v>
+        <v>46076</v>
       </c>
       <c r="C154" s="6">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -3292,7 +4035,7 @@
         <v>15</v>
       </c>
       <c r="B155" s="8">
-        <v>46031</v>
+        <v>46099</v>
       </c>
       <c r="C155" s="9">
         <v>2</v>
@@ -3303,10 +4046,10 @@
         <v>15</v>
       </c>
       <c r="B156" s="5">
-        <v>46120</v>
+        <v>46092</v>
       </c>
       <c r="C156" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -3314,10 +4057,10 @@
         <v>15</v>
       </c>
       <c r="B157" s="8">
-        <v>46077</v>
+        <v>46031</v>
       </c>
       <c r="C157" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -3325,10 +4068,10 @@
         <v>15</v>
       </c>
       <c r="B158" s="5">
-        <v>46114</v>
+        <v>46120</v>
       </c>
       <c r="C158" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -3336,10 +4079,10 @@
         <v>15</v>
       </c>
       <c r="B159" s="8">
-        <v>46037</v>
+        <v>46077</v>
       </c>
       <c r="C159" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -3347,10 +4090,10 @@
         <v>15</v>
       </c>
       <c r="B160" s="5">
-        <v>46020</v>
+        <v>46114</v>
       </c>
       <c r="C160" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -3358,7 +4101,7 @@
         <v>15</v>
       </c>
       <c r="B161" s="8">
-        <v>46106</v>
+        <v>46037</v>
       </c>
       <c r="C161" s="9">
         <v>1</v>
@@ -3369,10 +4112,10 @@
         <v>15</v>
       </c>
       <c r="B162" s="5">
-        <v>46112</v>
+        <v>46020</v>
       </c>
       <c r="C162" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -3380,7 +4123,7 @@
         <v>15</v>
       </c>
       <c r="B163" s="8">
-        <v>46132</v>
+        <v>46106</v>
       </c>
       <c r="C163" s="9">
         <v>1</v>
@@ -3391,7 +4134,7 @@
         <v>15</v>
       </c>
       <c r="B164" s="5">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="C164" s="6">
         <v>1</v>
@@ -3402,7 +4145,7 @@
         <v>15</v>
       </c>
       <c r="B165" s="8">
-        <v>46148</v>
+        <v>46132</v>
       </c>
       <c r="C165" s="9">
         <v>1</v>
@@ -3413,7 +4156,7 @@
         <v>15</v>
       </c>
       <c r="B166" s="5">
-        <v>46118</v>
+        <v>46108</v>
       </c>
       <c r="C166" s="6">
         <v>1</v>
@@ -3424,7 +4167,7 @@
         <v>15</v>
       </c>
       <c r="B167" s="8">
-        <v>46035</v>
+        <v>46148</v>
       </c>
       <c r="C167" s="9">
         <v>1</v>
@@ -3435,7 +4178,7 @@
         <v>15</v>
       </c>
       <c r="B168" s="5">
-        <v>46093</v>
+        <v>46118</v>
       </c>
       <c r="C168" s="6">
         <v>1</v>
@@ -3446,7 +4189,7 @@
         <v>15</v>
       </c>
       <c r="B169" s="8">
-        <v>46022</v>
+        <v>46035</v>
       </c>
       <c r="C169" s="9">
         <v>1</v>
@@ -3457,7 +4200,7 @@
         <v>15</v>
       </c>
       <c r="B170" s="5">
-        <v>46087</v>
+        <v>46093</v>
       </c>
       <c r="C170" s="6">
         <v>1</v>
@@ -3468,10 +4211,10 @@
         <v>15</v>
       </c>
       <c r="B171" s="8">
-        <v>46030</v>
+        <v>46022</v>
       </c>
       <c r="C171" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -3479,7 +4222,7 @@
         <v>15</v>
       </c>
       <c r="B172" s="5">
-        <v>46101</v>
+        <v>46087</v>
       </c>
       <c r="C172" s="6">
         <v>1</v>
@@ -3490,32 +4233,32 @@
         <v>15</v>
       </c>
       <c r="B173" s="8">
-        <v>46142</v>
+        <v>46030</v>
       </c>
       <c r="C173" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B174" s="5">
-        <v>46001</v>
+        <v>46101</v>
       </c>
       <c r="C174" s="6">
-        <v>154</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B175" s="8">
-        <v>46008</v>
+        <v>46142</v>
       </c>
       <c r="C175" s="9">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -3523,10 +4266,10 @@
         <v>21</v>
       </c>
       <c r="B176" s="5">
-        <v>46003</v>
+        <v>46001</v>
       </c>
       <c r="C176" s="6">
-        <v>70</v>
+        <v>153</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -3534,10 +4277,10 @@
         <v>21</v>
       </c>
       <c r="B177" s="8">
-        <v>46002</v>
+        <v>46008</v>
       </c>
       <c r="C177" s="9">
-        <v>111</v>
+        <v>38</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -3545,10 +4288,10 @@
         <v>21</v>
       </c>
       <c r="B178" s="5">
-        <v>46006</v>
+        <v>46003</v>
       </c>
       <c r="C178" s="6">
-        <v>147</v>
+        <v>70</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -3556,10 +4299,10 @@
         <v>21</v>
       </c>
       <c r="B179" s="8">
-        <v>46007</v>
+        <v>46002</v>
       </c>
       <c r="C179" s="9">
-        <v>45</v>
+        <v>111</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -3567,10 +4310,10 @@
         <v>21</v>
       </c>
       <c r="B180" s="5">
-        <v>46000</v>
+        <v>46006</v>
       </c>
       <c r="C180" s="6">
-        <v>129</v>
+        <v>147</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -3578,10 +4321,10 @@
         <v>21</v>
       </c>
       <c r="B181" s="8">
-        <v>46084</v>
+        <v>46007</v>
       </c>
       <c r="C181" s="9">
-        <v>10</v>
+        <v>45</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -3589,10 +4332,10 @@
         <v>21</v>
       </c>
       <c r="B182" s="5">
-        <v>46014</v>
+        <v>46000</v>
       </c>
       <c r="C182" s="6">
-        <v>22</v>
+        <v>129</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -3600,10 +4343,10 @@
         <v>21</v>
       </c>
       <c r="B183" s="8">
-        <v>46013</v>
+        <v>46084</v>
       </c>
       <c r="C183" s="9">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -3611,10 +4354,10 @@
         <v>21</v>
       </c>
       <c r="B184" s="5">
-        <v>46010</v>
+        <v>46014</v>
       </c>
       <c r="C184" s="6">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -3622,10 +4365,10 @@
         <v>21</v>
       </c>
       <c r="B185" s="8">
-        <v>46021</v>
+        <v>46013</v>
       </c>
       <c r="C185" s="9">
-        <v>6</v>
+        <v>29</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -3633,10 +4376,10 @@
         <v>21</v>
       </c>
       <c r="B186" s="5">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="C186" s="6">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -3644,10 +4387,10 @@
         <v>21</v>
       </c>
       <c r="B187" s="8">
-        <v>46083</v>
+        <v>46021</v>
       </c>
       <c r="C187" s="9">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -3655,10 +4398,10 @@
         <v>21</v>
       </c>
       <c r="B188" s="5">
-        <v>46079</v>
+        <v>46009</v>
       </c>
       <c r="C188" s="6">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -3666,10 +4409,10 @@
         <v>21</v>
       </c>
       <c r="B189" s="8">
-        <v>46077</v>
+        <v>46083</v>
       </c>
       <c r="C189" s="9">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -3677,10 +4420,10 @@
         <v>21</v>
       </c>
       <c r="B190" s="5">
-        <v>46035</v>
+        <v>46079</v>
       </c>
       <c r="C190" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -3688,10 +4431,10 @@
         <v>21</v>
       </c>
       <c r="B191" s="8">
-        <v>46085</v>
+        <v>46077</v>
       </c>
       <c r="C191" s="9">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -3699,7 +4442,7 @@
         <v>21</v>
       </c>
       <c r="B192" s="5">
-        <v>46120</v>
+        <v>46035</v>
       </c>
       <c r="C192" s="6">
         <v>2</v>
@@ -3710,10 +4453,10 @@
         <v>21</v>
       </c>
       <c r="B193" s="8">
-        <v>46114</v>
+        <v>46085</v>
       </c>
       <c r="C193" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -3721,10 +4464,10 @@
         <v>21</v>
       </c>
       <c r="B194" s="5">
-        <v>46094</v>
+        <v>46120</v>
       </c>
       <c r="C194" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -3732,10 +4475,10 @@
         <v>21</v>
       </c>
       <c r="B195" s="8">
-        <v>46080</v>
+        <v>46114</v>
       </c>
       <c r="C195" s="9">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -3743,10 +4486,10 @@
         <v>21</v>
       </c>
       <c r="B196" s="5">
-        <v>46127</v>
+        <v>46094</v>
       </c>
       <c r="C196" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -3754,10 +4497,10 @@
         <v>21</v>
       </c>
       <c r="B197" s="8">
-        <v>46091</v>
+        <v>46080</v>
       </c>
       <c r="C197" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -3765,10 +4508,10 @@
         <v>21</v>
       </c>
       <c r="B198" s="5">
-        <v>46090</v>
+        <v>46127</v>
       </c>
       <c r="C198" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -3776,10 +4519,10 @@
         <v>21</v>
       </c>
       <c r="B199" s="8">
-        <v>46020</v>
+        <v>46091</v>
       </c>
       <c r="C199" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -3787,10 +4530,10 @@
         <v>21</v>
       </c>
       <c r="B200" s="5">
-        <v>46015</v>
+        <v>46090</v>
       </c>
       <c r="C200" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -3798,10 +4541,10 @@
         <v>21</v>
       </c>
       <c r="B201" s="8">
-        <v>46113</v>
+        <v>46020</v>
       </c>
       <c r="C201" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -3809,10 +4552,10 @@
         <v>21</v>
       </c>
       <c r="B202" s="5">
-        <v>46078</v>
+        <v>46015</v>
       </c>
       <c r="C202" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -3820,10 +4563,10 @@
         <v>21</v>
       </c>
       <c r="B203" s="8">
-        <v>46148</v>
+        <v>46078</v>
       </c>
       <c r="C203" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -3831,7 +4574,7 @@
         <v>21</v>
       </c>
       <c r="B204" s="5">
-        <v>46105</v>
+        <v>46148</v>
       </c>
       <c r="C204" s="6">
         <v>2</v>
@@ -3842,10 +4585,10 @@
         <v>21</v>
       </c>
       <c r="B205" s="8">
-        <v>46087</v>
+        <v>46105</v>
       </c>
       <c r="C205" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -3853,7 +4596,7 @@
         <v>21</v>
       </c>
       <c r="B206" s="5">
-        <v>46107</v>
+        <v>46087</v>
       </c>
       <c r="C206" s="6">
         <v>3</v>
@@ -3864,10 +4607,10 @@
         <v>21</v>
       </c>
       <c r="B207" s="8">
-        <v>46086</v>
+        <v>46107</v>
       </c>
       <c r="C207" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -3875,10 +4618,10 @@
         <v>21</v>
       </c>
       <c r="B208" s="5">
-        <v>46106</v>
+        <v>46086</v>
       </c>
       <c r="C208" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -3886,10 +4629,10 @@
         <v>21</v>
       </c>
       <c r="B209" s="8">
-        <v>46150</v>
+        <v>46106</v>
       </c>
       <c r="C209" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -3897,7 +4640,7 @@
         <v>21</v>
       </c>
       <c r="B210" s="5">
-        <v>46104</v>
+        <v>46150</v>
       </c>
       <c r="C210" s="6">
         <v>3</v>
@@ -3908,10 +4651,10 @@
         <v>21</v>
       </c>
       <c r="B211" s="8">
-        <v>46118</v>
+        <v>46104</v>
       </c>
       <c r="C211" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -3919,10 +4662,10 @@
         <v>21</v>
       </c>
       <c r="B212" s="5">
-        <v>46076</v>
+        <v>46118</v>
       </c>
       <c r="C212" s="6">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -3930,10 +4673,10 @@
         <v>21</v>
       </c>
       <c r="B213" s="8">
-        <v>46093</v>
+        <v>46076</v>
       </c>
       <c r="C213" s="9">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -3941,7 +4684,7 @@
         <v>21</v>
       </c>
       <c r="B214" s="5">
-        <v>46122</v>
+        <v>46154</v>
       </c>
       <c r="C214" s="6">
         <v>1</v>
@@ -3952,10 +4695,10 @@
         <v>21</v>
       </c>
       <c r="B215" s="8">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="C215" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -3963,7 +4706,7 @@
         <v>21</v>
       </c>
       <c r="B216" s="5">
-        <v>46133</v>
+        <v>46122</v>
       </c>
       <c r="C216" s="6">
         <v>1</v>
@@ -3974,10 +4717,10 @@
         <v>21</v>
       </c>
       <c r="B217" s="8">
-        <v>46126</v>
+        <v>46092</v>
       </c>
       <c r="C217" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -3985,7 +4728,7 @@
         <v>21</v>
       </c>
       <c r="B218" s="5">
-        <v>46022</v>
+        <v>46156</v>
       </c>
       <c r="C218" s="6">
         <v>2</v>
@@ -3996,10 +4739,10 @@
         <v>21</v>
       </c>
       <c r="B219" s="8">
-        <v>46100</v>
+        <v>46133</v>
       </c>
       <c r="C219" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4007,7 +4750,7 @@
         <v>21</v>
       </c>
       <c r="B220" s="5">
-        <v>46101</v>
+        <v>46126</v>
       </c>
       <c r="C220" s="6">
         <v>1</v>
@@ -4018,10 +4761,10 @@
         <v>21</v>
       </c>
       <c r="B221" s="8">
-        <v>46097</v>
+        <v>46022</v>
       </c>
       <c r="C221" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -4029,10 +4772,10 @@
         <v>21</v>
       </c>
       <c r="B222" s="5">
-        <v>46108</v>
+        <v>46100</v>
       </c>
       <c r="C222" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -4040,10 +4783,10 @@
         <v>21</v>
       </c>
       <c r="B223" s="8">
-        <v>46098</v>
+        <v>46101</v>
       </c>
       <c r="C223" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -4051,10 +4794,10 @@
         <v>21</v>
       </c>
       <c r="B224" s="5">
-        <v>46142</v>
+        <v>46097</v>
       </c>
       <c r="C224" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -4062,7 +4805,7 @@
         <v>21</v>
       </c>
       <c r="B225" s="8">
-        <v>46153</v>
+        <v>46108</v>
       </c>
       <c r="C225" s="9">
         <v>1</v>
@@ -4073,9 +4816,4684 @@
         <v>21</v>
       </c>
       <c r="B226" s="5">
+        <v>46098</v>
+      </c>
+      <c r="C226" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B227" s="8">
+        <v>46113</v>
+      </c>
+      <c r="C227" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B228" s="5">
+        <v>46142</v>
+      </c>
+      <c r="C228" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B229" s="8">
+        <v>46153</v>
+      </c>
+      <c r="C229" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B230" s="5">
         <v>46031</v>
       </c>
-      <c r="C226" s="6">
+      <c r="C230" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B231" s="8">
+        <v>46155</v>
+      </c>
+      <c r="C231" s="9">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF41E2F3-2E0F-49EB-BAE8-83F2CBABFF5B}">
+  <dimension ref="A1:E39"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>14</v>
+      </c>
+      <c r="E2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>26</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>36</v>
+      </c>
+      <c r="D4">
+        <v>9</v>
+      </c>
+      <c r="E4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>36</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <v>50</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>53</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>69</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9">
+        <v>91</v>
+      </c>
+      <c r="D9">
+        <v>5</v>
+      </c>
+      <c r="E9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>58</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11">
+        <v>78</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>27</v>
+      </c>
+      <c r="E12">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13">
+        <v>29</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14">
+        <v>46</v>
+      </c>
+      <c r="D14">
+        <v>6</v>
+      </c>
+      <c r="E14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15">
+        <v>36</v>
+      </c>
+      <c r="D15">
+        <v>5</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16">
+        <v>51</v>
+      </c>
+      <c r="D16">
+        <v>3</v>
+      </c>
+      <c r="E16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17">
+        <v>58</v>
+      </c>
+      <c r="D17">
+        <v>3</v>
+      </c>
+      <c r="E17">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18">
+        <v>68</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19">
+        <v>77</v>
+      </c>
+      <c r="D19">
+        <v>6</v>
+      </c>
+      <c r="E19">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20">
+        <v>64</v>
+      </c>
+      <c r="D20">
+        <v>9</v>
+      </c>
+      <c r="E20">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21">
+        <v>73</v>
+      </c>
+      <c r="D21">
+        <v>6</v>
+      </c>
+      <c r="E21">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>25</v>
+      </c>
+      <c r="E22">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>31</v>
+      </c>
+      <c r="D23">
+        <v>5</v>
+      </c>
+      <c r="E23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24">
+        <v>52</v>
+      </c>
+      <c r="D24">
+        <v>12</v>
+      </c>
+      <c r="E24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25">
+        <v>82</v>
+      </c>
+      <c r="D25">
+        <v>3</v>
+      </c>
+      <c r="E25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26">
+        <v>74</v>
+      </c>
+      <c r="D26">
+        <v>3</v>
+      </c>
+      <c r="E26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27">
+        <v>92</v>
+      </c>
+      <c r="D27">
+        <v>3</v>
+      </c>
+      <c r="E27">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28">
+        <v>123</v>
+      </c>
+      <c r="D28">
+        <v>8</v>
+      </c>
+      <c r="E28">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29">
+        <v>118</v>
+      </c>
+      <c r="D29">
+        <v>3</v>
+      </c>
+      <c r="E29">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30">
+        <v>99</v>
+      </c>
+      <c r="D30">
+        <v>8</v>
+      </c>
+      <c r="E30">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31">
+        <v>118</v>
+      </c>
+      <c r="D31">
+        <v>4</v>
+      </c>
+      <c r="E31">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32">
+        <v>83</v>
+      </c>
+      <c r="D32">
+        <v>254</v>
+      </c>
+      <c r="E32">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33">
+        <v>296</v>
+      </c>
+      <c r="D33">
+        <v>8</v>
+      </c>
+      <c r="E33">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>16</v>
+      </c>
+      <c r="B34" t="s">
+        <v>19</v>
+      </c>
+      <c r="C34">
+        <v>289</v>
+      </c>
+      <c r="D34">
+        <v>8</v>
+      </c>
+      <c r="E34">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B35" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35">
+        <v>210</v>
+      </c>
+      <c r="D35">
+        <v>4</v>
+      </c>
+      <c r="E35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>21</v>
+      </c>
+      <c r="B36" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36">
+        <v>108</v>
+      </c>
+      <c r="D36">
+        <v>86</v>
+      </c>
+      <c r="E36">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37">
+        <v>178</v>
+      </c>
+      <c r="D37">
+        <v>12</v>
+      </c>
+      <c r="E37">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>21</v>
+      </c>
+      <c r="B38" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38">
+        <v>202</v>
+      </c>
+      <c r="D38">
+        <v>10</v>
+      </c>
+      <c r="E38">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39">
+        <v>190</v>
+      </c>
+      <c r="D39">
+        <v>3</v>
+      </c>
+      <c r="E39">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0916EAC6-1E7F-4924-9D0E-33749FD3E143}">
+  <dimension ref="A1:C357"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" t="s">
+        <v>77</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>3</v>
+      </c>
+      <c r="B31" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B32" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>3</v>
+      </c>
+      <c r="B33" t="s">
+        <v>79</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>3</v>
+      </c>
+      <c r="B34" t="s">
+        <v>73</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>3</v>
+      </c>
+      <c r="B35" t="s">
+        <v>64</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>3</v>
+      </c>
+      <c r="B36" t="s">
+        <v>75</v>
+      </c>
+      <c r="C36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>3</v>
+      </c>
+      <c r="B37" t="s">
+        <v>66</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>3</v>
+      </c>
+      <c r="B38" t="s">
+        <v>65</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>3</v>
+      </c>
+      <c r="B39" t="s">
+        <v>69</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>14</v>
+      </c>
+      <c r="B40" t="s">
+        <v>80</v>
+      </c>
+      <c r="C40">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>14</v>
+      </c>
+      <c r="B41" t="s">
+        <v>43</v>
+      </c>
+      <c r="C41">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>14</v>
+      </c>
+      <c r="B42" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>14</v>
+      </c>
+      <c r="B43" t="s">
+        <v>42</v>
+      </c>
+      <c r="C43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>14</v>
+      </c>
+      <c r="B44" t="s">
+        <v>53</v>
+      </c>
+      <c r="C44">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>14</v>
+      </c>
+      <c r="B45" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>14</v>
+      </c>
+      <c r="B46" t="s">
+        <v>64</v>
+      </c>
+      <c r="C46">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>14</v>
+      </c>
+      <c r="B47" t="s">
+        <v>82</v>
+      </c>
+      <c r="C47">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>14</v>
+      </c>
+      <c r="B48" t="s">
+        <v>52</v>
+      </c>
+      <c r="C48">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>14</v>
+      </c>
+      <c r="B49" t="s">
+        <v>65</v>
+      </c>
+      <c r="C49">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>14</v>
+      </c>
+      <c r="B50" t="s">
+        <v>83</v>
+      </c>
+      <c r="C50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>14</v>
+      </c>
+      <c r="B51" t="s">
+        <v>50</v>
+      </c>
+      <c r="C51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>14</v>
+      </c>
+      <c r="B52" t="s">
+        <v>84</v>
+      </c>
+      <c r="C52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>14</v>
+      </c>
+      <c r="B53" t="s">
+        <v>49</v>
+      </c>
+      <c r="C53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>14</v>
+      </c>
+      <c r="B54" t="s">
+        <v>85</v>
+      </c>
+      <c r="C54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>14</v>
+      </c>
+      <c r="B55" t="s">
+        <v>54</v>
+      </c>
+      <c r="C55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>14</v>
+      </c>
+      <c r="B56" t="s">
+        <v>86</v>
+      </c>
+      <c r="C56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>14</v>
+      </c>
+      <c r="B57" t="s">
+        <v>87</v>
+      </c>
+      <c r="C57">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>14</v>
+      </c>
+      <c r="B58" t="s">
+        <v>88</v>
+      </c>
+      <c r="C58">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>14</v>
+      </c>
+      <c r="B59" t="s">
+        <v>78</v>
+      </c>
+      <c r="C59">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>14</v>
+      </c>
+      <c r="B60" t="s">
+        <v>89</v>
+      </c>
+      <c r="C60">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>14</v>
+      </c>
+      <c r="B61" t="s">
+        <v>90</v>
+      </c>
+      <c r="C61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>14</v>
+      </c>
+      <c r="B62" t="s">
+        <v>73</v>
+      </c>
+      <c r="C62">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>14</v>
+      </c>
+      <c r="B63" t="s">
+        <v>68</v>
+      </c>
+      <c r="C63">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>14</v>
+      </c>
+      <c r="B64" t="s">
+        <v>91</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>14</v>
+      </c>
+      <c r="B65" t="s">
+        <v>57</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>14</v>
+      </c>
+      <c r="B66" t="s">
+        <v>92</v>
+      </c>
+      <c r="C66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>14</v>
+      </c>
+      <c r="B67" t="s">
+        <v>55</v>
+      </c>
+      <c r="C67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>14</v>
+      </c>
+      <c r="B68" t="s">
+        <v>93</v>
+      </c>
+      <c r="C68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>14</v>
+      </c>
+      <c r="B69" t="s">
+        <v>94</v>
+      </c>
+      <c r="C69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>14</v>
+      </c>
+      <c r="B70" t="s">
+        <v>95</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>14</v>
+      </c>
+      <c r="B71" t="s">
+        <v>96</v>
+      </c>
+      <c r="C71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>14</v>
+      </c>
+      <c r="B72" t="s">
+        <v>97</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>14</v>
+      </c>
+      <c r="B73" t="s">
+        <v>98</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>14</v>
+      </c>
+      <c r="B74" t="s">
+        <v>99</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>14</v>
+      </c>
+      <c r="B75" t="s">
+        <v>100</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>14</v>
+      </c>
+      <c r="B76" t="s">
+        <v>101</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>14</v>
+      </c>
+      <c r="B77" t="s">
+        <v>79</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>14</v>
+      </c>
+      <c r="B78" t="s">
+        <v>102</v>
+      </c>
+      <c r="C78">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>14</v>
+      </c>
+      <c r="B79" t="s">
+        <v>59</v>
+      </c>
+      <c r="C79">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>14</v>
+      </c>
+      <c r="B80" t="s">
+        <v>66</v>
+      </c>
+      <c r="C80">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>14</v>
+      </c>
+      <c r="B81" t="s">
+        <v>103</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>14</v>
+      </c>
+      <c r="B82" t="s">
+        <v>74</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>14</v>
+      </c>
+      <c r="B83" t="s">
+        <v>104</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>14</v>
+      </c>
+      <c r="B84" t="s">
+        <v>105</v>
+      </c>
+      <c r="C84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>14</v>
+      </c>
+      <c r="B85" t="s">
+        <v>106</v>
+      </c>
+      <c r="C85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>14</v>
+      </c>
+      <c r="B86" t="s">
+        <v>107</v>
+      </c>
+      <c r="C86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>14</v>
+      </c>
+      <c r="B87" t="s">
+        <v>108</v>
+      </c>
+      <c r="C87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>14</v>
+      </c>
+      <c r="B88" t="s">
+        <v>109</v>
+      </c>
+      <c r="C88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>14</v>
+      </c>
+      <c r="B89" t="s">
+        <v>110</v>
+      </c>
+      <c r="C89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>14</v>
+      </c>
+      <c r="B90" t="s">
+        <v>111</v>
+      </c>
+      <c r="C90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>14</v>
+      </c>
+      <c r="B91" t="s">
+        <v>112</v>
+      </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>14</v>
+      </c>
+      <c r="B92" t="s">
+        <v>113</v>
+      </c>
+      <c r="C92">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>14</v>
+      </c>
+      <c r="B93" t="s">
+        <v>114</v>
+      </c>
+      <c r="C93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>14</v>
+      </c>
+      <c r="B94" t="s">
+        <v>51</v>
+      </c>
+      <c r="C94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>14</v>
+      </c>
+      <c r="B95" t="s">
+        <v>115</v>
+      </c>
+      <c r="C95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>14</v>
+      </c>
+      <c r="B96" t="s">
+        <v>116</v>
+      </c>
+      <c r="C96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>14</v>
+      </c>
+      <c r="B97" t="s">
+        <v>72</v>
+      </c>
+      <c r="C97">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>14</v>
+      </c>
+      <c r="B98" t="s">
+        <v>117</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>14</v>
+      </c>
+      <c r="B99" t="s">
+        <v>118</v>
+      </c>
+      <c r="C99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>14</v>
+      </c>
+      <c r="B100" t="s">
+        <v>71</v>
+      </c>
+      <c r="C100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>14</v>
+      </c>
+      <c r="B101" t="s">
+        <v>119</v>
+      </c>
+      <c r="C101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>120</v>
+      </c>
+      <c r="C102">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>121</v>
+      </c>
+      <c r="C103">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>122</v>
+      </c>
+      <c r="C104">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>123</v>
+      </c>
+      <c r="C105">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>124</v>
+      </c>
+      <c r="C106">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>125</v>
+      </c>
+      <c r="C107">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>104</v>
+      </c>
+      <c r="C108">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>102</v>
+      </c>
+      <c r="C109">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>126</v>
+      </c>
+      <c r="C110">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>127</v>
+      </c>
+      <c r="C111">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>128</v>
+      </c>
+      <c r="C112">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>129</v>
+      </c>
+      <c r="C113">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>130</v>
+      </c>
+      <c r="C114">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>81</v>
+      </c>
+      <c r="C115">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>131</v>
+      </c>
+      <c r="C116">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>132</v>
+      </c>
+      <c r="C117">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>133</v>
+      </c>
+      <c r="C118">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>134</v>
+      </c>
+      <c r="C119">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>135</v>
+      </c>
+      <c r="C120">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>136</v>
+      </c>
+      <c r="C121">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>137</v>
+      </c>
+      <c r="C122">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>138</v>
+      </c>
+      <c r="C123">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>139</v>
+      </c>
+      <c r="C124">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>49</v>
+      </c>
+      <c r="C125">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>140</v>
+      </c>
+      <c r="C126">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>141</v>
+      </c>
+      <c r="C127">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>62</v>
+      </c>
+      <c r="C128">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>142</v>
+      </c>
+      <c r="C129">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>143</v>
+      </c>
+      <c r="C130">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>144</v>
+      </c>
+      <c r="C131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>145</v>
+      </c>
+      <c r="C132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>146</v>
+      </c>
+      <c r="C133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>147</v>
+      </c>
+      <c r="C134">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>148</v>
+      </c>
+      <c r="C135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>149</v>
+      </c>
+      <c r="C136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>150</v>
+      </c>
+      <c r="C137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>151</v>
+      </c>
+      <c r="C138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>152</v>
+      </c>
+      <c r="C139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>153</v>
+      </c>
+      <c r="C140">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>67</v>
+      </c>
+      <c r="C141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>154</v>
+      </c>
+      <c r="C142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>155</v>
+      </c>
+      <c r="C143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>156</v>
+      </c>
+      <c r="C144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>157</v>
+      </c>
+      <c r="C145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>158</v>
+      </c>
+      <c r="C146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>159</v>
+      </c>
+      <c r="C147">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>160</v>
+      </c>
+      <c r="C148">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>161</v>
+      </c>
+      <c r="C149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>162</v>
+      </c>
+      <c r="C150">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>163</v>
+      </c>
+      <c r="C151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>164</v>
+      </c>
+      <c r="C152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>165</v>
+      </c>
+      <c r="C153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>166</v>
+      </c>
+      <c r="C154">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>83</v>
+      </c>
+      <c r="C155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>167</v>
+      </c>
+      <c r="C156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>168</v>
+      </c>
+      <c r="C157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>169</v>
+      </c>
+      <c r="C158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>170</v>
+      </c>
+      <c r="C159">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>171</v>
+      </c>
+      <c r="C160">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>172</v>
+      </c>
+      <c r="C161">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>98</v>
+      </c>
+      <c r="C162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>173</v>
+      </c>
+      <c r="C163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>174</v>
+      </c>
+      <c r="C164">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>175</v>
+      </c>
+      <c r="C165">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>68</v>
+      </c>
+      <c r="C166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>176</v>
+      </c>
+      <c r="C167">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>177</v>
+      </c>
+      <c r="C168">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>178</v>
+      </c>
+      <c r="C169">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>179</v>
+      </c>
+      <c r="C170">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>180</v>
+      </c>
+      <c r="C171">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>181</v>
+      </c>
+      <c r="C172">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>182</v>
+      </c>
+      <c r="C173">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>70</v>
+      </c>
+      <c r="C174">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>183</v>
+      </c>
+      <c r="C175">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>184</v>
+      </c>
+      <c r="C176">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>185</v>
+      </c>
+      <c r="C177">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>186</v>
+      </c>
+      <c r="C178">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>88</v>
+      </c>
+      <c r="C179">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>187</v>
+      </c>
+      <c r="C180">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>188</v>
+      </c>
+      <c r="C181">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>189</v>
+      </c>
+      <c r="C182">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>190</v>
+      </c>
+      <c r="C183">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>191</v>
+      </c>
+      <c r="C184">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>192</v>
+      </c>
+      <c r="C185">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>193</v>
+      </c>
+      <c r="C186">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>16</v>
+      </c>
+      <c r="B187" t="s">
+        <v>49</v>
+      </c>
+      <c r="C187">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>16</v>
+      </c>
+      <c r="B188" t="s">
+        <v>43</v>
+      </c>
+      <c r="C188">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>16</v>
+      </c>
+      <c r="B189" t="s">
+        <v>54</v>
+      </c>
+      <c r="C189">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>16</v>
+      </c>
+      <c r="B190" t="s">
+        <v>66</v>
+      </c>
+      <c r="C190">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>16</v>
+      </c>
+      <c r="B191" t="s">
+        <v>195</v>
+      </c>
+      <c r="C191">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>16</v>
+      </c>
+      <c r="B192" t="s">
+        <v>194</v>
+      </c>
+      <c r="C192">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>16</v>
+      </c>
+      <c r="B193" t="s">
+        <v>50</v>
+      </c>
+      <c r="C193">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>16</v>
+      </c>
+      <c r="B194" t="s">
+        <v>65</v>
+      </c>
+      <c r="C194">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>16</v>
+      </c>
+      <c r="B195" t="s">
+        <v>117</v>
+      </c>
+      <c r="C195">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>16</v>
+      </c>
+      <c r="B196" t="s">
+        <v>46</v>
+      </c>
+      <c r="C196">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>16</v>
+      </c>
+      <c r="B197" t="s">
+        <v>55</v>
+      </c>
+      <c r="C197">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>16</v>
+      </c>
+      <c r="B198" t="s">
+        <v>45</v>
+      </c>
+      <c r="C198">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>16</v>
+      </c>
+      <c r="B199" t="s">
+        <v>72</v>
+      </c>
+      <c r="C199">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>16</v>
+      </c>
+      <c r="B200" t="s">
+        <v>196</v>
+      </c>
+      <c r="C200">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>16</v>
+      </c>
+      <c r="B201" t="s">
+        <v>85</v>
+      </c>
+      <c r="C201">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>16</v>
+      </c>
+      <c r="B202" t="s">
+        <v>48</v>
+      </c>
+      <c r="C202">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>16</v>
+      </c>
+      <c r="B203" t="s">
+        <v>197</v>
+      </c>
+      <c r="C203">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>16</v>
+      </c>
+      <c r="B204" t="s">
+        <v>52</v>
+      </c>
+      <c r="C204">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>16</v>
+      </c>
+      <c r="B205" t="s">
+        <v>57</v>
+      </c>
+      <c r="C205">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>16</v>
+      </c>
+      <c r="B206" t="s">
+        <v>201</v>
+      </c>
+      <c r="C206">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>16</v>
+      </c>
+      <c r="B207" t="s">
+        <v>200</v>
+      </c>
+      <c r="C207">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>16</v>
+      </c>
+      <c r="B208" t="s">
+        <v>199</v>
+      </c>
+      <c r="C208">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>16</v>
+      </c>
+      <c r="B209" t="s">
+        <v>71</v>
+      </c>
+      <c r="C209">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>16</v>
+      </c>
+      <c r="B210" t="s">
+        <v>73</v>
+      </c>
+      <c r="C210">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>16</v>
+      </c>
+      <c r="B211" t="s">
+        <v>60</v>
+      </c>
+      <c r="C211">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>16</v>
+      </c>
+      <c r="B212" t="s">
+        <v>198</v>
+      </c>
+      <c r="C212">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>16</v>
+      </c>
+      <c r="B213" t="s">
+        <v>47</v>
+      </c>
+      <c r="C213">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>16</v>
+      </c>
+      <c r="B214" t="s">
+        <v>78</v>
+      </c>
+      <c r="C214">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>16</v>
+      </c>
+      <c r="B215" t="s">
+        <v>92</v>
+      </c>
+      <c r="C215">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>16</v>
+      </c>
+      <c r="B216" t="s">
+        <v>115</v>
+      </c>
+      <c r="C216">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>16</v>
+      </c>
+      <c r="B217" t="s">
+        <v>59</v>
+      </c>
+      <c r="C217">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>16</v>
+      </c>
+      <c r="B218" t="s">
+        <v>74</v>
+      </c>
+      <c r="C218">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>16</v>
+      </c>
+      <c r="B219" t="s">
+        <v>76</v>
+      </c>
+      <c r="C219">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>16</v>
+      </c>
+      <c r="B220" t="s">
+        <v>203</v>
+      </c>
+      <c r="C220">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>16</v>
+      </c>
+      <c r="B221" t="s">
+        <v>119</v>
+      </c>
+      <c r="C221">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>16</v>
+      </c>
+      <c r="B222" t="s">
+        <v>202</v>
+      </c>
+      <c r="C222">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>16</v>
+      </c>
+      <c r="B223" t="s">
+        <v>44</v>
+      </c>
+      <c r="C223">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>16</v>
+      </c>
+      <c r="B224" t="s">
+        <v>68</v>
+      </c>
+      <c r="C224">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>16</v>
+      </c>
+      <c r="B225" t="s">
+        <v>190</v>
+      </c>
+      <c r="C225">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>16</v>
+      </c>
+      <c r="B226" t="s">
+        <v>80</v>
+      </c>
+      <c r="C226">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>16</v>
+      </c>
+      <c r="B227" t="s">
+        <v>204</v>
+      </c>
+      <c r="C227">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>16</v>
+      </c>
+      <c r="B228" t="s">
+        <v>206</v>
+      </c>
+      <c r="C228">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>16</v>
+      </c>
+      <c r="B229" t="s">
+        <v>205</v>
+      </c>
+      <c r="C229">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>16</v>
+      </c>
+      <c r="B230" t="s">
+        <v>207</v>
+      </c>
+      <c r="C230">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>16</v>
+      </c>
+      <c r="B231" t="s">
+        <v>208</v>
+      </c>
+      <c r="C231">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>16</v>
+      </c>
+      <c r="B232" t="s">
+        <v>64</v>
+      </c>
+      <c r="C232">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>16</v>
+      </c>
+      <c r="B233" t="s">
+        <v>209</v>
+      </c>
+      <c r="C233">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>16</v>
+      </c>
+      <c r="B234" t="s">
+        <v>238</v>
+      </c>
+      <c r="C234">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>16</v>
+      </c>
+      <c r="B235" t="s">
+        <v>116</v>
+      </c>
+      <c r="C235">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>16</v>
+      </c>
+      <c r="B236" t="s">
+        <v>230</v>
+      </c>
+      <c r="C236">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>16</v>
+      </c>
+      <c r="B237" t="s">
+        <v>213</v>
+      </c>
+      <c r="C237">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>16</v>
+      </c>
+      <c r="B238" t="s">
+        <v>225</v>
+      </c>
+      <c r="C238">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>16</v>
+      </c>
+      <c r="B239" t="s">
+        <v>220</v>
+      </c>
+      <c r="C239">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>16</v>
+      </c>
+      <c r="B240" t="s">
+        <v>216</v>
+      </c>
+      <c r="C240">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>16</v>
+      </c>
+      <c r="B241" t="s">
+        <v>223</v>
+      </c>
+      <c r="C241">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>16</v>
+      </c>
+      <c r="B242" t="s">
+        <v>217</v>
+      </c>
+      <c r="C242">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>16</v>
+      </c>
+      <c r="B243" t="s">
+        <v>120</v>
+      </c>
+      <c r="C243">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>16</v>
+      </c>
+      <c r="B244" t="s">
+        <v>244</v>
+      </c>
+      <c r="C244">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>16</v>
+      </c>
+      <c r="B245" t="s">
+        <v>219</v>
+      </c>
+      <c r="C245">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>16</v>
+      </c>
+      <c r="B246" t="s">
+        <v>218</v>
+      </c>
+      <c r="C246">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>16</v>
+      </c>
+      <c r="B247" t="s">
+        <v>251</v>
+      </c>
+      <c r="C247">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>16</v>
+      </c>
+      <c r="B248" t="s">
+        <v>235</v>
+      </c>
+      <c r="C248">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>16</v>
+      </c>
+      <c r="B249" t="s">
+        <v>69</v>
+      </c>
+      <c r="C249">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>16</v>
+      </c>
+      <c r="B250" t="s">
+        <v>241</v>
+      </c>
+      <c r="C250">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>16</v>
+      </c>
+      <c r="B251" t="s">
+        <v>236</v>
+      </c>
+      <c r="C251">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>16</v>
+      </c>
+      <c r="B252" t="s">
+        <v>127</v>
+      </c>
+      <c r="C252">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>16</v>
+      </c>
+      <c r="B253" t="s">
+        <v>242</v>
+      </c>
+      <c r="C253">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>16</v>
+      </c>
+      <c r="B254" t="s">
+        <v>224</v>
+      </c>
+      <c r="C254">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>16</v>
+      </c>
+      <c r="B255" t="s">
+        <v>227</v>
+      </c>
+      <c r="C255">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>16</v>
+      </c>
+      <c r="B256" t="s">
+        <v>232</v>
+      </c>
+      <c r="C256">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>16</v>
+      </c>
+      <c r="B257" t="s">
+        <v>229</v>
+      </c>
+      <c r="C257">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>16</v>
+      </c>
+      <c r="B258" t="s">
+        <v>210</v>
+      </c>
+      <c r="C258">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>16</v>
+      </c>
+      <c r="B259" t="s">
+        <v>231</v>
+      </c>
+      <c r="C259">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>16</v>
+      </c>
+      <c r="B260" t="s">
+        <v>221</v>
+      </c>
+      <c r="C260">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>16</v>
+      </c>
+      <c r="B261" t="s">
+        <v>233</v>
+      </c>
+      <c r="C261">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>16</v>
+      </c>
+      <c r="B262" t="s">
+        <v>240</v>
+      </c>
+      <c r="C262">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>16</v>
+      </c>
+      <c r="B263" t="s">
+        <v>228</v>
+      </c>
+      <c r="C263">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>16</v>
+      </c>
+      <c r="B264" t="s">
+        <v>214</v>
+      </c>
+      <c r="C264">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>16</v>
+      </c>
+      <c r="B265" t="s">
+        <v>237</v>
+      </c>
+      <c r="C265">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>16</v>
+      </c>
+      <c r="B266" t="s">
+        <v>215</v>
+      </c>
+      <c r="C266">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>16</v>
+      </c>
+      <c r="B267" t="s">
+        <v>245</v>
+      </c>
+      <c r="C267">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>16</v>
+      </c>
+      <c r="B268" t="s">
+        <v>212</v>
+      </c>
+      <c r="C268">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>16</v>
+      </c>
+      <c r="B269" t="s">
+        <v>222</v>
+      </c>
+      <c r="C269">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>16</v>
+      </c>
+      <c r="B270" t="s">
+        <v>239</v>
+      </c>
+      <c r="C270">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>16</v>
+      </c>
+      <c r="B271" t="s">
+        <v>226</v>
+      </c>
+      <c r="C271">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>16</v>
+      </c>
+      <c r="B272" t="s">
+        <v>234</v>
+      </c>
+      <c r="C272">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>16</v>
+      </c>
+      <c r="B273" t="s">
+        <v>243</v>
+      </c>
+      <c r="C273">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>16</v>
+      </c>
+      <c r="B274" t="s">
+        <v>70</v>
+      </c>
+      <c r="C274">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>16</v>
+      </c>
+      <c r="B275" t="s">
+        <v>211</v>
+      </c>
+      <c r="C275">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>16</v>
+      </c>
+      <c r="B276" t="s">
+        <v>122</v>
+      </c>
+      <c r="C276">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>16</v>
+      </c>
+      <c r="B277" t="s">
+        <v>58</v>
+      </c>
+      <c r="C277">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>21</v>
+      </c>
+      <c r="B278" t="s">
+        <v>122</v>
+      </c>
+      <c r="C278">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>21</v>
+      </c>
+      <c r="B279" t="s">
+        <v>190</v>
+      </c>
+      <c r="C279">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>21</v>
+      </c>
+      <c r="B280" t="s">
+        <v>133</v>
+      </c>
+      <c r="C280">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>21</v>
+      </c>
+      <c r="B281" t="s">
+        <v>104</v>
+      </c>
+      <c r="C281">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>21</v>
+      </c>
+      <c r="B282" t="s">
+        <v>203</v>
+      </c>
+      <c r="C282">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>21</v>
+      </c>
+      <c r="B283" t="s">
+        <v>246</v>
+      </c>
+      <c r="C283">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>21</v>
+      </c>
+      <c r="B284" t="s">
+        <v>121</v>
+      </c>
+      <c r="C284">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>21</v>
+      </c>
+      <c r="B285" t="s">
+        <v>247</v>
+      </c>
+      <c r="C285">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>21</v>
+      </c>
+      <c r="B286" t="s">
+        <v>143</v>
+      </c>
+      <c r="C286">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>21</v>
+      </c>
+      <c r="B287" t="s">
+        <v>248</v>
+      </c>
+      <c r="C287">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>21</v>
+      </c>
+      <c r="B288" t="s">
+        <v>129</v>
+      </c>
+      <c r="C288">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>21</v>
+      </c>
+      <c r="B289" t="s">
+        <v>249</v>
+      </c>
+      <c r="C289">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>21</v>
+      </c>
+      <c r="B290" t="s">
+        <v>250</v>
+      </c>
+      <c r="C290">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>21</v>
+      </c>
+      <c r="B291" t="s">
+        <v>102</v>
+      </c>
+      <c r="C291">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>21</v>
+      </c>
+      <c r="B292" t="s">
+        <v>134</v>
+      </c>
+      <c r="C292">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>21</v>
+      </c>
+      <c r="B293" t="s">
+        <v>197</v>
+      </c>
+      <c r="C293">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>21</v>
+      </c>
+      <c r="B294" t="s">
+        <v>251</v>
+      </c>
+      <c r="C294">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>21</v>
+      </c>
+      <c r="B295" t="s">
+        <v>252</v>
+      </c>
+      <c r="C295">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>21</v>
+      </c>
+      <c r="B296" t="s">
+        <v>164</v>
+      </c>
+      <c r="C296">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>21</v>
+      </c>
+      <c r="B297" t="s">
+        <v>253</v>
+      </c>
+      <c r="C297">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>21</v>
+      </c>
+      <c r="B298" t="s">
+        <v>254</v>
+      </c>
+      <c r="C298">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>21</v>
+      </c>
+      <c r="B299" t="s">
+        <v>128</v>
+      </c>
+      <c r="C299">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>21</v>
+      </c>
+      <c r="B300" t="s">
+        <v>255</v>
+      </c>
+      <c r="C300">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>21</v>
+      </c>
+      <c r="B301" t="s">
+        <v>44</v>
+      </c>
+      <c r="C301">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>21</v>
+      </c>
+      <c r="B302" t="s">
+        <v>81</v>
+      </c>
+      <c r="C302">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>21</v>
+      </c>
+      <c r="B303" t="s">
+        <v>127</v>
+      </c>
+      <c r="C303">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>21</v>
+      </c>
+      <c r="B304" t="s">
+        <v>54</v>
+      </c>
+      <c r="C304">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>21</v>
+      </c>
+      <c r="B305" t="s">
+        <v>257</v>
+      </c>
+      <c r="C305">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>21</v>
+      </c>
+      <c r="B306" t="s">
+        <v>273</v>
+      </c>
+      <c r="C306">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>21</v>
+      </c>
+      <c r="B307" t="s">
+        <v>174</v>
+      </c>
+      <c r="C307">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>21</v>
+      </c>
+      <c r="B308" t="s">
+        <v>85</v>
+      </c>
+      <c r="C308">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>21</v>
+      </c>
+      <c r="B309" t="s">
+        <v>200</v>
+      </c>
+      <c r="C309">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>21</v>
+      </c>
+      <c r="B310" t="s">
+        <v>172</v>
+      </c>
+      <c r="C310">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>21</v>
+      </c>
+      <c r="B311" t="s">
+        <v>77</v>
+      </c>
+      <c r="C311">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>21</v>
+      </c>
+      <c r="B312" t="s">
+        <v>256</v>
+      </c>
+      <c r="C312">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>21</v>
+      </c>
+      <c r="B313" t="s">
+        <v>258</v>
+      </c>
+      <c r="C313">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>21</v>
+      </c>
+      <c r="B314" t="s">
+        <v>199</v>
+      </c>
+      <c r="C314">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>21</v>
+      </c>
+      <c r="B315" t="s">
+        <v>226</v>
+      </c>
+      <c r="C315">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>21</v>
+      </c>
+      <c r="B316" t="s">
+        <v>259</v>
+      </c>
+      <c r="C316">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>21</v>
+      </c>
+      <c r="B317" t="s">
+        <v>117</v>
+      </c>
+      <c r="C317">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>21</v>
+      </c>
+      <c r="B318" t="s">
+        <v>62</v>
+      </c>
+      <c r="C318">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>21</v>
+      </c>
+      <c r="B319" t="s">
+        <v>137</v>
+      </c>
+      <c r="C319">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>21</v>
+      </c>
+      <c r="B320" t="s">
+        <v>70</v>
+      </c>
+      <c r="C320">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>21</v>
+      </c>
+      <c r="B321" t="s">
+        <v>270</v>
+      </c>
+      <c r="C321">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" t="s">
+        <v>21</v>
+      </c>
+      <c r="B322" t="s">
+        <v>92</v>
+      </c>
+      <c r="C322">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" t="s">
+        <v>21</v>
+      </c>
+      <c r="B323" t="s">
+        <v>271</v>
+      </c>
+      <c r="C323">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A324" t="s">
+        <v>21</v>
+      </c>
+      <c r="B324" t="s">
+        <v>264</v>
+      </c>
+      <c r="C324">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" t="s">
+        <v>21</v>
+      </c>
+      <c r="B325" t="s">
+        <v>277</v>
+      </c>
+      <c r="C325">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" t="s">
+        <v>21</v>
+      </c>
+      <c r="B326" t="s">
+        <v>265</v>
+      </c>
+      <c r="C326">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A327" t="s">
+        <v>21</v>
+      </c>
+      <c r="B327" t="s">
+        <v>281</v>
+      </c>
+      <c r="C327">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" t="s">
+        <v>21</v>
+      </c>
+      <c r="B328" t="s">
+        <v>266</v>
+      </c>
+      <c r="C328">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" t="s">
+        <v>21</v>
+      </c>
+      <c r="B329" t="s">
+        <v>138</v>
+      </c>
+      <c r="C329">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A330" t="s">
+        <v>21</v>
+      </c>
+      <c r="B330" t="s">
+        <v>268</v>
+      </c>
+      <c r="C330">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" t="s">
+        <v>21</v>
+      </c>
+      <c r="B331" t="s">
+        <v>173</v>
+      </c>
+      <c r="C331">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" t="s">
+        <v>21</v>
+      </c>
+      <c r="B332" t="s">
+        <v>269</v>
+      </c>
+      <c r="C332">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A333" t="s">
+        <v>21</v>
+      </c>
+      <c r="B333" t="s">
+        <v>63</v>
+      </c>
+      <c r="C333">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" t="s">
+        <v>21</v>
+      </c>
+      <c r="B334" t="s">
+        <v>49</v>
+      </c>
+      <c r="C334">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" t="s">
+        <v>21</v>
+      </c>
+      <c r="B335" t="s">
+        <v>280</v>
+      </c>
+      <c r="C335">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A336" t="s">
+        <v>21</v>
+      </c>
+      <c r="B336" t="s">
+        <v>186</v>
+      </c>
+      <c r="C336">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>21</v>
+      </c>
+      <c r="B337" t="s">
+        <v>261</v>
+      </c>
+      <c r="C337">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
+        <v>21</v>
+      </c>
+      <c r="B338" t="s">
+        <v>272</v>
+      </c>
+      <c r="C338">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>21</v>
+      </c>
+      <c r="B339" t="s">
+        <v>166</v>
+      </c>
+      <c r="C339">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
+        <v>21</v>
+      </c>
+      <c r="B340" t="s">
+        <v>274</v>
+      </c>
+      <c r="C340">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A341" t="s">
+        <v>21</v>
+      </c>
+      <c r="B341" t="s">
+        <v>215</v>
+      </c>
+      <c r="C341">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A342" t="s">
+        <v>21</v>
+      </c>
+      <c r="B342" t="s">
+        <v>275</v>
+      </c>
+      <c r="C342">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A343" t="s">
+        <v>21</v>
+      </c>
+      <c r="B343" t="s">
+        <v>267</v>
+      </c>
+      <c r="C343">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A344" t="s">
+        <v>21</v>
+      </c>
+      <c r="B344" t="s">
+        <v>276</v>
+      </c>
+      <c r="C344">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A345" t="s">
+        <v>21</v>
+      </c>
+      <c r="B345" t="s">
+        <v>263</v>
+      </c>
+      <c r="C345">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A346" t="s">
+        <v>21</v>
+      </c>
+      <c r="B346" t="s">
+        <v>278</v>
+      </c>
+      <c r="C346">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A347" t="s">
+        <v>21</v>
+      </c>
+      <c r="B347" t="s">
+        <v>139</v>
+      </c>
+      <c r="C347">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A348" t="s">
+        <v>21</v>
+      </c>
+      <c r="B348" t="s">
+        <v>279</v>
+      </c>
+      <c r="C348">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>21</v>
+      </c>
+      <c r="B349" t="s">
+        <v>260</v>
+      </c>
+      <c r="C349">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>21</v>
+      </c>
+      <c r="B350" t="s">
+        <v>116</v>
+      </c>
+      <c r="C350">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>21</v>
+      </c>
+      <c r="B351" t="s">
+        <v>126</v>
+      </c>
+      <c r="C351">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
+        <v>21</v>
+      </c>
+      <c r="B352" t="s">
+        <v>175</v>
+      </c>
+      <c r="C352">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>21</v>
+      </c>
+      <c r="B353" t="s">
+        <v>149</v>
+      </c>
+      <c r="C353">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>21</v>
+      </c>
+      <c r="B354" t="s">
+        <v>282</v>
+      </c>
+      <c r="C354">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A355" t="s">
+        <v>21</v>
+      </c>
+      <c r="B355" t="s">
+        <v>262</v>
+      </c>
+      <c r="C355">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A356" t="s">
+        <v>21</v>
+      </c>
+      <c r="B356" t="s">
+        <v>283</v>
+      </c>
+      <c r="C356">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A357" t="s">
+        <v>21</v>
+      </c>
+      <c r="B357" t="s">
+        <v>284</v>
+      </c>
+      <c r="C357">
         <v>1</v>
       </c>
     </row>

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="69" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5131E768-AA99-4E87-AC4D-33B6FE5EF4F4}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17D3294F-DA32-4565-9151-2A36A443EAD3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
@@ -22,6 +22,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">mat_2026!$A$1:$E$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">origen_colegios!$A$1:$C$357</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1145" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="286">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -1344,7 +1345,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8FC1322-F2C4-4535-882A-673ED2A7B0F2}">
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -1354,7 +1355,7 @@
     <col min="5" max="5" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -1370,8 +1371,9 @@
       <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1388,7 +1390,7 @@
         <v>1.2629999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1405,7 +1407,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1422,7 +1424,7 @@
         <v>1.1519999999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1439,7 +1441,7 @@
         <v>1.2649999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1456,7 +1458,7 @@
         <v>1.034</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -1473,7 +1475,7 @@
         <v>1.0660000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1490,7 +1492,7 @@
         <v>1.093</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -1507,7 +1509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -1524,7 +1526,7 @@
         <v>1.0620000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -1541,7 +1543,7 @@
         <v>1.0680000000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1558,7 +1560,7 @@
         <v>1.387</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1575,7 +1577,7 @@
         <v>1.1140000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -1592,7 +1594,7 @@
         <v>1.048</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>14</v>
       </c>
@@ -1609,7 +1611,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -1824,10 +1826,10 @@
         <v>140</v>
       </c>
       <c r="D28">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E28">
-        <v>1.036</v>
+        <v>1.0429999999999999</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -1875,10 +1877,10 @@
         <v>138</v>
       </c>
       <c r="D31">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E31">
-        <v>1.0580000000000001</v>
+        <v>1.0649999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1960,10 +1962,10 @@
         <v>250</v>
       </c>
       <c r="D36">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E36">
-        <v>1.02</v>
+        <v>1.028</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2263,7 +2265,7 @@
         <v>35</v>
       </c>
       <c r="C6">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2274,7 +2276,7 @@
         <v>34</v>
       </c>
       <c r="C7">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -2307,7 +2309,7 @@
         <v>35</v>
       </c>
       <c r="C10">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -2318,7 +2320,7 @@
         <v>34</v>
       </c>
       <c r="C11">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -2328,7 +2330,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD19485A-0629-47F9-A5AD-80ABA7A6E076}">
-  <dimension ref="A1:C231"/>
+  <dimension ref="A1:C234"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -4046,7 +4048,7 @@
         <v>15</v>
       </c>
       <c r="B156" s="5">
-        <v>46092</v>
+        <v>46154</v>
       </c>
       <c r="C156" s="6">
         <v>1</v>
@@ -4057,10 +4059,10 @@
         <v>15</v>
       </c>
       <c r="B157" s="8">
-        <v>46031</v>
+        <v>46092</v>
       </c>
       <c r="C157" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -4068,7 +4070,7 @@
         <v>15</v>
       </c>
       <c r="B158" s="5">
-        <v>46120</v>
+        <v>46031</v>
       </c>
       <c r="C158" s="6">
         <v>2</v>
@@ -4079,10 +4081,10 @@
         <v>15</v>
       </c>
       <c r="B159" s="8">
-        <v>46077</v>
+        <v>46120</v>
       </c>
       <c r="C159" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -4090,10 +4092,10 @@
         <v>15</v>
       </c>
       <c r="B160" s="5">
-        <v>46114</v>
+        <v>46077</v>
       </c>
       <c r="C160" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -4101,7 +4103,7 @@
         <v>15</v>
       </c>
       <c r="B161" s="8">
-        <v>46037</v>
+        <v>46114</v>
       </c>
       <c r="C161" s="9">
         <v>1</v>
@@ -4112,10 +4114,10 @@
         <v>15</v>
       </c>
       <c r="B162" s="5">
-        <v>46020</v>
+        <v>46037</v>
       </c>
       <c r="C162" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -4123,10 +4125,10 @@
         <v>15</v>
       </c>
       <c r="B163" s="8">
-        <v>46106</v>
+        <v>46020</v>
       </c>
       <c r="C163" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -4134,7 +4136,7 @@
         <v>15</v>
       </c>
       <c r="B164" s="5">
-        <v>46112</v>
+        <v>46106</v>
       </c>
       <c r="C164" s="6">
         <v>1</v>
@@ -4145,7 +4147,7 @@
         <v>15</v>
       </c>
       <c r="B165" s="8">
-        <v>46132</v>
+        <v>46155</v>
       </c>
       <c r="C165" s="9">
         <v>1</v>
@@ -4156,7 +4158,7 @@
         <v>15</v>
       </c>
       <c r="B166" s="5">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="C166" s="6">
         <v>1</v>
@@ -4167,7 +4169,7 @@
         <v>15</v>
       </c>
       <c r="B167" s="8">
-        <v>46148</v>
+        <v>46132</v>
       </c>
       <c r="C167" s="9">
         <v>1</v>
@@ -4178,7 +4180,7 @@
         <v>15</v>
       </c>
       <c r="B168" s="5">
-        <v>46118</v>
+        <v>46108</v>
       </c>
       <c r="C168" s="6">
         <v>1</v>
@@ -4189,7 +4191,7 @@
         <v>15</v>
       </c>
       <c r="B169" s="8">
-        <v>46035</v>
+        <v>46148</v>
       </c>
       <c r="C169" s="9">
         <v>1</v>
@@ -4200,7 +4202,7 @@
         <v>15</v>
       </c>
       <c r="B170" s="5">
-        <v>46093</v>
+        <v>46118</v>
       </c>
       <c r="C170" s="6">
         <v>1</v>
@@ -4211,7 +4213,7 @@
         <v>15</v>
       </c>
       <c r="B171" s="8">
-        <v>46022</v>
+        <v>46035</v>
       </c>
       <c r="C171" s="9">
         <v>1</v>
@@ -4222,7 +4224,7 @@
         <v>15</v>
       </c>
       <c r="B172" s="5">
-        <v>46087</v>
+        <v>46093</v>
       </c>
       <c r="C172" s="6">
         <v>1</v>
@@ -4233,10 +4235,10 @@
         <v>15</v>
       </c>
       <c r="B173" s="8">
-        <v>46030</v>
+        <v>46022</v>
       </c>
       <c r="C173" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -4244,7 +4246,7 @@
         <v>15</v>
       </c>
       <c r="B174" s="5">
-        <v>46101</v>
+        <v>46087</v>
       </c>
       <c r="C174" s="6">
         <v>1</v>
@@ -4255,32 +4257,32 @@
         <v>15</v>
       </c>
       <c r="B175" s="8">
-        <v>46142</v>
+        <v>46030</v>
       </c>
       <c r="C175" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B176" s="5">
-        <v>46001</v>
+        <v>46101</v>
       </c>
       <c r="C176" s="6">
-        <v>153</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B177" s="8">
-        <v>46008</v>
+        <v>46142</v>
       </c>
       <c r="C177" s="9">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -4288,10 +4290,10 @@
         <v>21</v>
       </c>
       <c r="B178" s="5">
-        <v>46003</v>
+        <v>46001</v>
       </c>
       <c r="C178" s="6">
-        <v>70</v>
+        <v>153</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -4299,10 +4301,10 @@
         <v>21</v>
       </c>
       <c r="B179" s="8">
-        <v>46002</v>
+        <v>46008</v>
       </c>
       <c r="C179" s="9">
-        <v>111</v>
+        <v>38</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -4310,10 +4312,10 @@
         <v>21</v>
       </c>
       <c r="B180" s="5">
-        <v>46006</v>
+        <v>46003</v>
       </c>
       <c r="C180" s="6">
-        <v>147</v>
+        <v>70</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -4321,10 +4323,10 @@
         <v>21</v>
       </c>
       <c r="B181" s="8">
-        <v>46007</v>
+        <v>46002</v>
       </c>
       <c r="C181" s="9">
-        <v>45</v>
+        <v>111</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -4332,10 +4334,10 @@
         <v>21</v>
       </c>
       <c r="B182" s="5">
-        <v>46000</v>
+        <v>46006</v>
       </c>
       <c r="C182" s="6">
-        <v>129</v>
+        <v>147</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -4343,10 +4345,10 @@
         <v>21</v>
       </c>
       <c r="B183" s="8">
-        <v>46084</v>
+        <v>46007</v>
       </c>
       <c r="C183" s="9">
-        <v>10</v>
+        <v>45</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -4354,10 +4356,10 @@
         <v>21</v>
       </c>
       <c r="B184" s="5">
-        <v>46014</v>
+        <v>46000</v>
       </c>
       <c r="C184" s="6">
-        <v>22</v>
+        <v>129</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -4365,10 +4367,10 @@
         <v>21</v>
       </c>
       <c r="B185" s="8">
-        <v>46013</v>
+        <v>46084</v>
       </c>
       <c r="C185" s="9">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -4376,10 +4378,10 @@
         <v>21</v>
       </c>
       <c r="B186" s="5">
-        <v>46010</v>
+        <v>46014</v>
       </c>
       <c r="C186" s="6">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -4387,10 +4389,10 @@
         <v>21</v>
       </c>
       <c r="B187" s="8">
-        <v>46021</v>
+        <v>46013</v>
       </c>
       <c r="C187" s="9">
-        <v>6</v>
+        <v>29</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -4398,10 +4400,10 @@
         <v>21</v>
       </c>
       <c r="B188" s="5">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="C188" s="6">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -4409,10 +4411,10 @@
         <v>21</v>
       </c>
       <c r="B189" s="8">
-        <v>46083</v>
+        <v>46021</v>
       </c>
       <c r="C189" s="9">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -4420,10 +4422,10 @@
         <v>21</v>
       </c>
       <c r="B190" s="5">
-        <v>46079</v>
+        <v>46009</v>
       </c>
       <c r="C190" s="6">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -4431,10 +4433,10 @@
         <v>21</v>
       </c>
       <c r="B191" s="8">
-        <v>46077</v>
+        <v>46083</v>
       </c>
       <c r="C191" s="9">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -4442,7 +4444,7 @@
         <v>21</v>
       </c>
       <c r="B192" s="5">
-        <v>46035</v>
+        <v>46157</v>
       </c>
       <c r="C192" s="6">
         <v>2</v>
@@ -4453,7 +4455,7 @@
         <v>21</v>
       </c>
       <c r="B193" s="8">
-        <v>46085</v>
+        <v>46079</v>
       </c>
       <c r="C193" s="9">
         <v>3</v>
@@ -4464,10 +4466,10 @@
         <v>21</v>
       </c>
       <c r="B194" s="5">
-        <v>46120</v>
+        <v>46077</v>
       </c>
       <c r="C194" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -4475,10 +4477,10 @@
         <v>21</v>
       </c>
       <c r="B195" s="8">
-        <v>46114</v>
+        <v>46035</v>
       </c>
       <c r="C195" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -4486,10 +4488,10 @@
         <v>21</v>
       </c>
       <c r="B196" s="5">
-        <v>46094</v>
+        <v>46085</v>
       </c>
       <c r="C196" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -4497,10 +4499,10 @@
         <v>21</v>
       </c>
       <c r="B197" s="8">
-        <v>46080</v>
+        <v>46120</v>
       </c>
       <c r="C197" s="9">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -4508,10 +4510,10 @@
         <v>21</v>
       </c>
       <c r="B198" s="5">
-        <v>46127</v>
+        <v>46114</v>
       </c>
       <c r="C198" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -4519,10 +4521,10 @@
         <v>21</v>
       </c>
       <c r="B199" s="8">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="C199" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -4530,10 +4532,10 @@
         <v>21</v>
       </c>
       <c r="B200" s="5">
-        <v>46090</v>
+        <v>46080</v>
       </c>
       <c r="C200" s="6">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -4541,10 +4543,10 @@
         <v>21</v>
       </c>
       <c r="B201" s="8">
-        <v>46020</v>
+        <v>46127</v>
       </c>
       <c r="C201" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -4552,10 +4554,10 @@
         <v>21</v>
       </c>
       <c r="B202" s="5">
-        <v>46015</v>
+        <v>46091</v>
       </c>
       <c r="C202" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -4563,10 +4565,10 @@
         <v>21</v>
       </c>
       <c r="B203" s="8">
-        <v>46078</v>
+        <v>46090</v>
       </c>
       <c r="C203" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -4574,10 +4576,10 @@
         <v>21</v>
       </c>
       <c r="B204" s="5">
-        <v>46148</v>
+        <v>46020</v>
       </c>
       <c r="C204" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -4585,10 +4587,10 @@
         <v>21</v>
       </c>
       <c r="B205" s="8">
-        <v>46105</v>
+        <v>46015</v>
       </c>
       <c r="C205" s="9">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -4596,10 +4598,10 @@
         <v>21</v>
       </c>
       <c r="B206" s="5">
-        <v>46087</v>
+        <v>46078</v>
       </c>
       <c r="C206" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -4607,10 +4609,10 @@
         <v>21</v>
       </c>
       <c r="B207" s="8">
-        <v>46107</v>
+        <v>46148</v>
       </c>
       <c r="C207" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4618,10 +4620,10 @@
         <v>21</v>
       </c>
       <c r="B208" s="5">
-        <v>46086</v>
+        <v>46105</v>
       </c>
       <c r="C208" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4629,10 +4631,10 @@
         <v>21</v>
       </c>
       <c r="B209" s="8">
-        <v>46106</v>
+        <v>46087</v>
       </c>
       <c r="C209" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4640,7 +4642,7 @@
         <v>21</v>
       </c>
       <c r="B210" s="5">
-        <v>46150</v>
+        <v>46107</v>
       </c>
       <c r="C210" s="6">
         <v>3</v>
@@ -4651,10 +4653,10 @@
         <v>21</v>
       </c>
       <c r="B211" s="8">
-        <v>46104</v>
+        <v>46086</v>
       </c>
       <c r="C211" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -4662,7 +4664,7 @@
         <v>21</v>
       </c>
       <c r="B212" s="5">
-        <v>46118</v>
+        <v>46106</v>
       </c>
       <c r="C212" s="6">
         <v>1</v>
@@ -4673,10 +4675,10 @@
         <v>21</v>
       </c>
       <c r="B213" s="8">
-        <v>46076</v>
+        <v>46150</v>
       </c>
       <c r="C213" s="9">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4684,10 +4686,10 @@
         <v>21</v>
       </c>
       <c r="B214" s="5">
-        <v>46154</v>
+        <v>46104</v>
       </c>
       <c r="C214" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4695,10 +4697,10 @@
         <v>21</v>
       </c>
       <c r="B215" s="8">
-        <v>46093</v>
+        <v>46118</v>
       </c>
       <c r="C215" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4706,10 +4708,10 @@
         <v>21</v>
       </c>
       <c r="B216" s="5">
-        <v>46122</v>
+        <v>46076</v>
       </c>
       <c r="C216" s="6">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4717,10 +4719,10 @@
         <v>21</v>
       </c>
       <c r="B217" s="8">
-        <v>46092</v>
+        <v>46154</v>
       </c>
       <c r="C217" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -4728,10 +4730,10 @@
         <v>21</v>
       </c>
       <c r="B218" s="5">
-        <v>46156</v>
+        <v>46093</v>
       </c>
       <c r="C218" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -4739,7 +4741,7 @@
         <v>21</v>
       </c>
       <c r="B219" s="8">
-        <v>46133</v>
+        <v>46122</v>
       </c>
       <c r="C219" s="9">
         <v>1</v>
@@ -4750,10 +4752,10 @@
         <v>21</v>
       </c>
       <c r="B220" s="5">
-        <v>46126</v>
+        <v>46092</v>
       </c>
       <c r="C220" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -4761,7 +4763,7 @@
         <v>21</v>
       </c>
       <c r="B221" s="8">
-        <v>46022</v>
+        <v>46156</v>
       </c>
       <c r="C221" s="9">
         <v>2</v>
@@ -4772,10 +4774,10 @@
         <v>21</v>
       </c>
       <c r="B222" s="5">
-        <v>46100</v>
+        <v>46133</v>
       </c>
       <c r="C222" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -4783,7 +4785,7 @@
         <v>21</v>
       </c>
       <c r="B223" s="8">
-        <v>46101</v>
+        <v>46126</v>
       </c>
       <c r="C223" s="9">
         <v>1</v>
@@ -4794,10 +4796,10 @@
         <v>21</v>
       </c>
       <c r="B224" s="5">
-        <v>46097</v>
+        <v>46022</v>
       </c>
       <c r="C224" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -4805,10 +4807,10 @@
         <v>21</v>
       </c>
       <c r="B225" s="8">
-        <v>46108</v>
+        <v>46100</v>
       </c>
       <c r="C225" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -4816,10 +4818,10 @@
         <v>21</v>
       </c>
       <c r="B226" s="5">
-        <v>46098</v>
+        <v>46101</v>
       </c>
       <c r="C226" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -4827,10 +4829,10 @@
         <v>21</v>
       </c>
       <c r="B227" s="8">
-        <v>46113</v>
+        <v>46097</v>
       </c>
       <c r="C227" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -4838,7 +4840,7 @@
         <v>21</v>
       </c>
       <c r="B228" s="5">
-        <v>46142</v>
+        <v>46108</v>
       </c>
       <c r="C228" s="6">
         <v>1</v>
@@ -4849,10 +4851,10 @@
         <v>21</v>
       </c>
       <c r="B229" s="8">
-        <v>46153</v>
+        <v>46098</v>
       </c>
       <c r="C229" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -4860,7 +4862,7 @@
         <v>21</v>
       </c>
       <c r="B230" s="5">
-        <v>46031</v>
+        <v>46113</v>
       </c>
       <c r="C230" s="6">
         <v>1</v>
@@ -4871,9 +4873,42 @@
         <v>21</v>
       </c>
       <c r="B231" s="8">
+        <v>46142</v>
+      </c>
+      <c r="C231" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B232" s="5">
+        <v>46153</v>
+      </c>
+      <c r="C232" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B233" s="8">
+        <v>46031</v>
+      </c>
+      <c r="C233" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B234" s="5">
         <v>46155</v>
       </c>
-      <c r="C231" s="9">
+      <c r="C234" s="6">
         <v>1</v>
       </c>
     </row>
@@ -5365,7 +5400,7 @@
         <v>8</v>
       </c>
       <c r="E28">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -5416,7 +5451,7 @@
         <v>4</v>
       </c>
       <c r="E31">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -5498,10 +5533,10 @@
         <v>108</v>
       </c>
       <c r="D36">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E36">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -5562,6 +5597,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0916EAC6-1E7F-4924-9D0E-33749FD3E143}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:C357"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5581,7 +5617,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -5592,7 +5628,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -5603,7 +5639,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -5614,7 +5650,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -5625,7 +5661,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -5636,7 +5672,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -5647,7 +5683,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -5658,7 +5694,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -5669,7 +5705,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -5680,7 +5716,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>3</v>
       </c>
@@ -5691,7 +5727,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>3</v>
       </c>
@@ -5702,7 +5738,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>3</v>
       </c>
@@ -5713,7 +5749,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -5724,7 +5760,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>3</v>
       </c>
@@ -5735,7 +5771,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -5746,7 +5782,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>3</v>
       </c>
@@ -5757,7 +5793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -5768,7 +5804,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>3</v>
       </c>
@@ -5779,7 +5815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -5790,7 +5826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -5801,7 +5837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -5812,7 +5848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>3</v>
       </c>
@@ -5823,7 +5859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>3</v>
       </c>
@@ -5834,7 +5870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>3</v>
       </c>
@@ -5845,7 +5881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>3</v>
       </c>
@@ -5856,7 +5892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -5867,7 +5903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>3</v>
       </c>
@@ -5878,7 +5914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>3</v>
       </c>
@@ -5889,7 +5925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>3</v>
       </c>
@@ -5900,7 +5936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>3</v>
       </c>
@@ -5911,7 +5947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>3</v>
       </c>
@@ -5922,7 +5958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>3</v>
       </c>
@@ -5933,7 +5969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>3</v>
       </c>
@@ -5944,7 +5980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>3</v>
       </c>
@@ -5955,7 +5991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>3</v>
       </c>
@@ -5966,7 +6002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>3</v>
       </c>
@@ -5977,7 +6013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>3</v>
       </c>
@@ -5988,7 +6024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>3</v>
       </c>
@@ -5999,7 +6035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>14</v>
       </c>
@@ -6010,7 +6046,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>14</v>
       </c>
@@ -6021,7 +6057,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>14</v>
       </c>
@@ -6032,7 +6068,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>14</v>
       </c>
@@ -6043,7 +6079,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>14</v>
       </c>
@@ -6054,7 +6090,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>14</v>
       </c>
@@ -6065,7 +6101,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>14</v>
       </c>
@@ -6076,7 +6112,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>14</v>
       </c>
@@ -6087,7 +6123,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>14</v>
       </c>
@@ -6098,7 +6134,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>14</v>
       </c>
@@ -6109,7 +6145,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>14</v>
       </c>
@@ -6120,7 +6156,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>14</v>
       </c>
@@ -6131,7 +6167,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>14</v>
       </c>
@@ -6142,7 +6178,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>14</v>
       </c>
@@ -6153,7 +6189,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>14</v>
       </c>
@@ -6164,7 +6200,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>14</v>
       </c>
@@ -6175,7 +6211,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>14</v>
       </c>
@@ -6186,7 +6222,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>14</v>
       </c>
@@ -6197,7 +6233,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>14</v>
       </c>
@@ -6208,7 +6244,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>14</v>
       </c>
@@ -6219,7 +6255,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>14</v>
       </c>
@@ -6230,7 +6266,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>14</v>
       </c>
@@ -6241,7 +6277,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>14</v>
       </c>
@@ -6252,7 +6288,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>14</v>
       </c>
@@ -6263,7 +6299,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>14</v>
       </c>
@@ -6274,7 +6310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>14</v>
       </c>
@@ -6285,7 +6321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>14</v>
       </c>
@@ -6296,7 +6332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>14</v>
       </c>
@@ -6307,7 +6343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>14</v>
       </c>
@@ -6318,7 +6354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>14</v>
       </c>
@@ -6329,7 +6365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>14</v>
       </c>
@@ -6340,7 +6376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>14</v>
       </c>
@@ -6351,7 +6387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>14</v>
       </c>
@@ -6362,7 +6398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>14</v>
       </c>
@@ -6373,7 +6409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>14</v>
       </c>
@@ -6384,7 +6420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>14</v>
       </c>
@@ -6395,7 +6431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>14</v>
       </c>
@@ -6406,7 +6442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>14</v>
       </c>
@@ -6417,7 +6453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>14</v>
       </c>
@@ -6428,7 +6464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>14</v>
       </c>
@@ -6439,7 +6475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>14</v>
       </c>
@@ -6450,7 +6486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>14</v>
       </c>
@@ -6461,7 +6497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>14</v>
       </c>
@@ -6472,7 +6508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>14</v>
       </c>
@@ -6483,7 +6519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>14</v>
       </c>
@@ -6494,7 +6530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>14</v>
       </c>
@@ -6505,7 +6541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>14</v>
       </c>
@@ -6516,7 +6552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>14</v>
       </c>
@@ -6527,7 +6563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>14</v>
       </c>
@@ -6538,7 +6574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>14</v>
       </c>
@@ -6549,7 +6585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>14</v>
       </c>
@@ -6560,7 +6596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>14</v>
       </c>
@@ -6571,7 +6607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>14</v>
       </c>
@@ -6582,7 +6618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>14</v>
       </c>
@@ -6593,7 +6629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>14</v>
       </c>
@@ -6604,7 +6640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>14</v>
       </c>
@@ -6615,7 +6651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>14</v>
       </c>
@@ -6626,7 +6662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>14</v>
       </c>
@@ -6637,7 +6673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>14</v>
       </c>
@@ -6648,7 +6684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>14</v>
       </c>
@@ -6659,7 +6695,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>14</v>
       </c>
@@ -6670,7 +6706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>14</v>
       </c>
@@ -6714,7 +6750,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>15</v>
       </c>
@@ -6725,7 +6761,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>15</v>
       </c>
@@ -6736,7 +6772,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>15</v>
       </c>
@@ -6747,7 +6783,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>15</v>
       </c>
@@ -6758,7 +6794,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>15</v>
       </c>
@@ -6769,7 +6805,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>15</v>
       </c>
@@ -6780,7 +6816,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>15</v>
       </c>
@@ -6791,7 +6827,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>15</v>
       </c>
@@ -6802,7 +6838,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>15</v>
       </c>
@@ -6813,7 +6849,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>15</v>
       </c>
@@ -6824,7 +6860,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>15</v>
       </c>
@@ -6835,7 +6871,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>15</v>
       </c>
@@ -6846,7 +6882,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>15</v>
       </c>
@@ -6857,7 +6893,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>15</v>
       </c>
@@ -6868,7 +6904,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>15</v>
       </c>
@@ -6879,7 +6915,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>15</v>
       </c>
@@ -6890,7 +6926,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>15</v>
       </c>
@@ -6901,7 +6937,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>15</v>
       </c>
@@ -6912,7 +6948,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>15</v>
       </c>
@@ -6923,7 +6959,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>15</v>
       </c>
@@ -6934,7 +6970,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>15</v>
       </c>
@@ -6945,7 +6981,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>15</v>
       </c>
@@ -6956,7 +6992,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>15</v>
       </c>
@@ -6967,7 +7003,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>15</v>
       </c>
@@ -6978,7 +7014,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>15</v>
       </c>
@@ -6989,7 +7025,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>15</v>
       </c>
@@ -7000,7 +7036,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>15</v>
       </c>
@@ -7011,7 +7047,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>15</v>
       </c>
@@ -7022,7 +7058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>15</v>
       </c>
@@ -7033,7 +7069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>15</v>
       </c>
@@ -7044,7 +7080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>15</v>
       </c>
@@ -7055,7 +7091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>15</v>
       </c>
@@ -7066,7 +7102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>15</v>
       </c>
@@ -7077,7 +7113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>15</v>
       </c>
@@ -7088,7 +7124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>15</v>
       </c>
@@ -7099,7 +7135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>15</v>
       </c>
@@ -7110,7 +7146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>15</v>
       </c>
@@ -7121,7 +7157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>15</v>
       </c>
@@ -7132,7 +7168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>15</v>
       </c>
@@ -7143,7 +7179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>15</v>
       </c>
@@ -7154,7 +7190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>15</v>
       </c>
@@ -7165,7 +7201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>15</v>
       </c>
@@ -7176,7 +7212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>15</v>
       </c>
@@ -7187,7 +7223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>15</v>
       </c>
@@ -7198,7 +7234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>15</v>
       </c>
@@ -7209,7 +7245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>15</v>
       </c>
@@ -7220,7 +7256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>15</v>
       </c>
@@ -7231,7 +7267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>15</v>
       </c>
@@ -7242,7 +7278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>15</v>
       </c>
@@ -7253,7 +7289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>15</v>
       </c>
@@ -7264,7 +7300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>15</v>
       </c>
@@ -7275,7 +7311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>15</v>
       </c>
@@ -7286,7 +7322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>15</v>
       </c>
@@ -7297,7 +7333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>15</v>
       </c>
@@ -7308,7 +7344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>15</v>
       </c>
@@ -7319,7 +7355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>15</v>
       </c>
@@ -7330,7 +7366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>15</v>
       </c>
@@ -7341,7 +7377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>15</v>
       </c>
@@ -7352,7 +7388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>15</v>
       </c>
@@ -7363,7 +7399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>15</v>
       </c>
@@ -7374,7 +7410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>15</v>
       </c>
@@ -7385,7 +7421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>15</v>
       </c>
@@ -7396,7 +7432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>15</v>
       </c>
@@ -7407,7 +7443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>15</v>
       </c>
@@ -7418,7 +7454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>15</v>
       </c>
@@ -7429,7 +7465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>15</v>
       </c>
@@ -7440,7 +7476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>15</v>
       </c>
@@ -7451,7 +7487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>15</v>
       </c>
@@ -7462,7 +7498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>15</v>
       </c>
@@ -7473,7 +7509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>15</v>
       </c>
@@ -7484,7 +7520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>15</v>
       </c>
@@ -7495,7 +7531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>15</v>
       </c>
@@ -7506,7 +7542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>15</v>
       </c>
@@ -7517,7 +7553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>15</v>
       </c>
@@ -7528,7 +7564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>15</v>
       </c>
@@ -7539,7 +7575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>15</v>
       </c>
@@ -7550,7 +7586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>15</v>
       </c>
@@ -7561,7 +7597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>15</v>
       </c>
@@ -7572,7 +7608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>15</v>
       </c>
@@ -7583,7 +7619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>15</v>
       </c>
@@ -7594,7 +7630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>15</v>
       </c>
@@ -7605,7 +7641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>15</v>
       </c>
@@ -7748,7 +7784,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>16</v>
       </c>
@@ -7759,7 +7795,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>16</v>
       </c>
@@ -7770,7 +7806,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>16</v>
       </c>
@@ -7781,7 +7817,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>16</v>
       </c>
@@ -7792,7 +7828,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>16</v>
       </c>
@@ -7803,7 +7839,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>16</v>
       </c>
@@ -7814,7 +7850,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>16</v>
       </c>
@@ -7825,7 +7861,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>16</v>
       </c>
@@ -7836,7 +7872,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>16</v>
       </c>
@@ -7847,7 +7883,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>16</v>
       </c>
@@ -7858,7 +7894,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>16</v>
       </c>
@@ -7869,7 +7905,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>16</v>
       </c>
@@ -7880,7 +7916,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>16</v>
       </c>
@@ -7891,7 +7927,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>16</v>
       </c>
@@ -7902,7 +7938,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>16</v>
       </c>
@@ -7913,7 +7949,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>16</v>
       </c>
@@ -7924,7 +7960,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>16</v>
       </c>
@@ -7935,7 +7971,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>16</v>
       </c>
@@ -7946,7 +7982,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>16</v>
       </c>
@@ -7957,7 +7993,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>16</v>
       </c>
@@ -7968,7 +8004,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>16</v>
       </c>
@@ -7979,7 +8015,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>16</v>
       </c>
@@ -7990,7 +8026,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>16</v>
       </c>
@@ -8001,7 +8037,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>16</v>
       </c>
@@ -8012,7 +8048,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>16</v>
       </c>
@@ -8023,7 +8059,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>16</v>
       </c>
@@ -8034,7 +8070,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>16</v>
       </c>
@@ -8045,7 +8081,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>16</v>
       </c>
@@ -8056,7 +8092,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>16</v>
       </c>
@@ -8067,7 +8103,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>16</v>
       </c>
@@ -8078,7 +8114,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>16</v>
       </c>
@@ -8089,7 +8125,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>16</v>
       </c>
@@ -8100,7 +8136,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>16</v>
       </c>
@@ -8111,7 +8147,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>16</v>
       </c>
@@ -8122,7 +8158,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>16</v>
       </c>
@@ -8133,7 +8169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>16</v>
       </c>
@@ -8144,7 +8180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>16</v>
       </c>
@@ -8155,7 +8191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>16</v>
       </c>
@@ -8166,7 +8202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>16</v>
       </c>
@@ -8177,7 +8213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>16</v>
       </c>
@@ -8188,7 +8224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>16</v>
       </c>
@@ -8199,7 +8235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>16</v>
       </c>
@@ -8210,7 +8246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>16</v>
       </c>
@@ -8221,7 +8257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>16</v>
       </c>
@@ -8232,7 +8268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>16</v>
       </c>
@@ -8243,7 +8279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>16</v>
       </c>
@@ -8254,7 +8290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>16</v>
       </c>
@@ -8265,7 +8301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>16</v>
       </c>
@@ -8276,7 +8312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>16</v>
       </c>
@@ -8287,7 +8323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>16</v>
       </c>
@@ -8298,7 +8334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>16</v>
       </c>
@@ -8309,7 +8345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>16</v>
       </c>
@@ -8320,7 +8356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>16</v>
       </c>
@@ -8331,7 +8367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>16</v>
       </c>
@@ -8342,7 +8378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>16</v>
       </c>
@@ -8353,7 +8389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>16</v>
       </c>
@@ -8364,7 +8400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>16</v>
       </c>
@@ -8375,7 +8411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>16</v>
       </c>
@@ -8386,7 +8422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>16</v>
       </c>
@@ -8397,7 +8433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>16</v>
       </c>
@@ -8408,7 +8444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>16</v>
       </c>
@@ -8419,7 +8455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>16</v>
       </c>
@@ -8430,7 +8466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>16</v>
       </c>
@@ -8441,7 +8477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>16</v>
       </c>
@@ -8452,7 +8488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>16</v>
       </c>
@@ -8463,7 +8499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>16</v>
       </c>
@@ -8474,7 +8510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>16</v>
       </c>
@@ -8485,7 +8521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>16</v>
       </c>
@@ -8496,7 +8532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>16</v>
       </c>
@@ -8507,7 +8543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>16</v>
       </c>
@@ -8518,7 +8554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>16</v>
       </c>
@@ -8529,7 +8565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>16</v>
       </c>
@@ -8540,7 +8576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>16</v>
       </c>
@@ -8551,7 +8587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>16</v>
       </c>
@@ -8562,7 +8598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>16</v>
       </c>
@@ -8573,7 +8609,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>16</v>
       </c>
@@ -8584,7 +8620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>16</v>
       </c>
@@ -8595,7 +8631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>16</v>
       </c>
@@ -8606,7 +8642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>16</v>
       </c>
@@ -8650,7 +8686,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>21</v>
       </c>
@@ -8661,7 +8697,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>21</v>
       </c>
@@ -8672,7 +8708,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>21</v>
       </c>
@@ -8683,7 +8719,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>21</v>
       </c>
@@ -8694,7 +8730,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>21</v>
       </c>
@@ -8705,7 +8741,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>21</v>
       </c>
@@ -8716,7 +8752,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>21</v>
       </c>
@@ -8727,7 +8763,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>21</v>
       </c>
@@ -8738,7 +8774,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>21</v>
       </c>
@@ -8749,7 +8785,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>21</v>
       </c>
@@ -8760,7 +8796,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>21</v>
       </c>
@@ -8771,7 +8807,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>21</v>
       </c>
@@ -8782,7 +8818,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>21</v>
       </c>
@@ -8793,7 +8829,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>21</v>
       </c>
@@ -8804,7 +8840,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>21</v>
       </c>
@@ -8815,7 +8851,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>21</v>
       </c>
@@ -8826,7 +8862,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>21</v>
       </c>
@@ -8837,7 +8873,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>21</v>
       </c>
@@ -8848,7 +8884,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>21</v>
       </c>
@@ -8859,7 +8895,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>21</v>
       </c>
@@ -8870,7 +8906,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>21</v>
       </c>
@@ -8881,7 +8917,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>21</v>
       </c>
@@ -8892,7 +8928,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>21</v>
       </c>
@@ -8903,7 +8939,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>21</v>
       </c>
@@ -8914,7 +8950,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>21</v>
       </c>
@@ -8925,7 +8961,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>21</v>
       </c>
@@ -8936,7 +8972,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>21</v>
       </c>
@@ -8947,7 +8983,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>21</v>
       </c>
@@ -8958,7 +8994,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>21</v>
       </c>
@@ -8969,7 +9005,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>21</v>
       </c>
@@ -8980,7 +9016,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>21</v>
       </c>
@@ -8991,7 +9027,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>21</v>
       </c>
@@ -9002,7 +9038,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>21</v>
       </c>
@@ -9013,7 +9049,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>21</v>
       </c>
@@ -9024,7 +9060,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>21</v>
       </c>
@@ -9035,7 +9071,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>21</v>
       </c>
@@ -9046,7 +9082,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>21</v>
       </c>
@@ -9057,7 +9093,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>21</v>
       </c>
@@ -9068,7 +9104,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>21</v>
       </c>
@@ -9079,7 +9115,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>21</v>
       </c>
@@ -9090,7 +9126,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>21</v>
       </c>
@@ -9101,7 +9137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>21</v>
       </c>
@@ -9112,7 +9148,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>21</v>
       </c>
@@ -9123,7 +9159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>21</v>
       </c>
@@ -9134,7 +9170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>21</v>
       </c>
@@ -9145,7 +9181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>21</v>
       </c>
@@ -9156,7 +9192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>21</v>
       </c>
@@ -9167,7 +9203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>21</v>
       </c>
@@ -9178,7 +9214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>21</v>
       </c>
@@ -9189,7 +9225,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>21</v>
       </c>
@@ -9200,7 +9236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>21</v>
       </c>
@@ -9211,7 +9247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>21</v>
       </c>
@@ -9222,7 +9258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>21</v>
       </c>
@@ -9233,7 +9269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>21</v>
       </c>
@@ -9244,7 +9280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>21</v>
       </c>
@@ -9255,7 +9291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>21</v>
       </c>
@@ -9266,7 +9302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>21</v>
       </c>
@@ -9277,7 +9313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>21</v>
       </c>
@@ -9288,7 +9324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>21</v>
       </c>
@@ -9299,7 +9335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>21</v>
       </c>
@@ -9310,7 +9346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>21</v>
       </c>
@@ -9321,7 +9357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>21</v>
       </c>
@@ -9332,7 +9368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>21</v>
       </c>
@@ -9343,7 +9379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>21</v>
       </c>
@@ -9354,7 +9390,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>21</v>
       </c>
@@ -9365,7 +9401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>21</v>
       </c>
@@ -9376,7 +9412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>21</v>
       </c>
@@ -9387,7 +9423,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>21</v>
       </c>
@@ -9398,7 +9434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>21</v>
       </c>
@@ -9409,7 +9445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>21</v>
       </c>
@@ -9420,7 +9456,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>21</v>
       </c>
@@ -9431,7 +9467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>21</v>
       </c>
@@ -9442,7 +9478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>21</v>
       </c>
@@ -9453,7 +9489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>21</v>
       </c>
@@ -9464,7 +9500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>21</v>
       </c>
@@ -9475,7 +9511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>21</v>
       </c>
@@ -9486,7 +9522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>21</v>
       </c>
@@ -9498,6 +9534,22 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C357" xr:uid="{0916EAC6-1E7F-4924-9D0E-33749FD3E143}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="10"/>
+        <filter val="11"/>
+        <filter val="12"/>
+        <filter val="13"/>
+        <filter val="14"/>
+        <filter val="15"/>
+        <filter val="16"/>
+        <filter val="22"/>
+        <filter val="28"/>
+        <filter val="39"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17D3294F-DA32-4565-9151-2A36A443EAD3}"/>
+  <xr:revisionPtr revIDLastSave="87" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{703055C9-2199-4AB3-91CC-C80D5686EFF6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="5" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="mat_2026" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="286">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -1401,10 +1401,10 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E3">
-        <v>0.97</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1452,10 +1452,10 @@
         <v>58</v>
       </c>
       <c r="D6">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E6">
-        <v>1.034</v>
+        <v>1.052</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1469,10 +1469,10 @@
         <v>61</v>
       </c>
       <c r="D7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E7">
-        <v>1.0660000000000001</v>
+        <v>1.0820000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -1486,10 +1486,10 @@
         <v>75</v>
       </c>
       <c r="D8">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E8">
-        <v>1.093</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1520,10 +1520,10 @@
         <v>64</v>
       </c>
       <c r="D10">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E10">
-        <v>1.0620000000000001</v>
+        <v>1.0940000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1877,10 +1877,10 @@
         <v>138</v>
       </c>
       <c r="D31">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E31">
-        <v>1.0649999999999999</v>
+        <v>1.0580000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1894,10 +1894,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E32">
-        <v>1.071</v>
+        <v>1.0680000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1911,10 +1911,10 @@
         <v>329</v>
       </c>
       <c r="D33">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E33">
-        <v>1.0269999999999999</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1928,10 +1928,10 @@
         <v>323</v>
       </c>
       <c r="D34">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E34">
-        <v>0.95699999999999996</v>
+        <v>0.96299999999999997</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1962,10 +1962,10 @@
         <v>250</v>
       </c>
       <c r="D36">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E36">
-        <v>1.028</v>
+        <v>1.024</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2221,7 +2221,7 @@
         <v>34</v>
       </c>
       <c r="C2">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2232,7 +2232,7 @@
         <v>35</v>
       </c>
       <c r="C3">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2265,7 +2265,7 @@
         <v>35</v>
       </c>
       <c r="C6">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2298,7 +2298,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>698</v>
+        <v>700</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2309,7 +2309,7 @@
         <v>35</v>
       </c>
       <c r="C10">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -2330,7 +2330,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD19485A-0629-47F9-A5AD-80ABA7A6E076}">
-  <dimension ref="A1:C234"/>
+  <dimension ref="A1:C237"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -2434,7 +2434,7 @@
         <v>46013</v>
       </c>
       <c r="C9" s="9">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2533,7 +2533,7 @@
         <v>46083</v>
       </c>
       <c r="C18" s="6">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -2596,10 +2596,10 @@
         <v>16</v>
       </c>
       <c r="B24" s="5">
-        <v>46086</v>
+        <v>46161</v>
       </c>
       <c r="C24" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -2607,10 +2607,10 @@
         <v>16</v>
       </c>
       <c r="B25" s="8">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="C25" s="9">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -2618,10 +2618,10 @@
         <v>16</v>
       </c>
       <c r="B26" s="5">
-        <v>46136</v>
+        <v>46076</v>
       </c>
       <c r="C26" s="6">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -2629,10 +2629,10 @@
         <v>16</v>
       </c>
       <c r="B27" s="8">
-        <v>46078</v>
+        <v>46136</v>
       </c>
       <c r="C27" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -2640,7 +2640,7 @@
         <v>16</v>
       </c>
       <c r="B28" s="5">
-        <v>46098</v>
+        <v>46078</v>
       </c>
       <c r="C28" s="6">
         <v>3</v>
@@ -2651,10 +2651,10 @@
         <v>16</v>
       </c>
       <c r="B29" s="8">
-        <v>46084</v>
+        <v>46098</v>
       </c>
       <c r="C29" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -2662,10 +2662,10 @@
         <v>16</v>
       </c>
       <c r="B30" s="5">
-        <v>46099</v>
+        <v>46084</v>
       </c>
       <c r="C30" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -2673,10 +2673,10 @@
         <v>16</v>
       </c>
       <c r="B31" s="8">
-        <v>46128</v>
+        <v>46160</v>
       </c>
       <c r="C31" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -2684,10 +2684,10 @@
         <v>16</v>
       </c>
       <c r="B32" s="5">
-        <v>46141</v>
+        <v>46099</v>
       </c>
       <c r="C32" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -2695,7 +2695,7 @@
         <v>16</v>
       </c>
       <c r="B33" s="8">
-        <v>46132</v>
+        <v>46128</v>
       </c>
       <c r="C33" s="9">
         <v>1</v>
@@ -2706,10 +2706,10 @@
         <v>16</v>
       </c>
       <c r="B34" s="5">
-        <v>46127</v>
+        <v>46141</v>
       </c>
       <c r="C34" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -2717,10 +2717,10 @@
         <v>16</v>
       </c>
       <c r="B35" s="8">
-        <v>46091</v>
+        <v>46132</v>
       </c>
       <c r="C35" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -2728,10 +2728,10 @@
         <v>16</v>
       </c>
       <c r="B36" s="5">
-        <v>46104</v>
+        <v>46127</v>
       </c>
       <c r="C36" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -2739,10 +2739,10 @@
         <v>16</v>
       </c>
       <c r="B37" s="8">
-        <v>46140</v>
+        <v>46091</v>
       </c>
       <c r="C37" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -2750,7 +2750,7 @@
         <v>16</v>
       </c>
       <c r="B38" s="5">
-        <v>46106</v>
+        <v>46104</v>
       </c>
       <c r="C38" s="6">
         <v>1</v>
@@ -2761,10 +2761,10 @@
         <v>16</v>
       </c>
       <c r="B39" s="8">
-        <v>46113</v>
+        <v>46140</v>
       </c>
       <c r="C39" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -2772,10 +2772,10 @@
         <v>16</v>
       </c>
       <c r="B40" s="5">
-        <v>46090</v>
+        <v>46106</v>
       </c>
       <c r="C40" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -2783,7 +2783,7 @@
         <v>16</v>
       </c>
       <c r="B41" s="8">
-        <v>46148</v>
+        <v>46113</v>
       </c>
       <c r="C41" s="9">
         <v>2</v>
@@ -2794,10 +2794,10 @@
         <v>16</v>
       </c>
       <c r="B42" s="5">
-        <v>46139</v>
+        <v>46090</v>
       </c>
       <c r="C42" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -2805,10 +2805,10 @@
         <v>16</v>
       </c>
       <c r="B43" s="8">
-        <v>46125</v>
+        <v>46148</v>
       </c>
       <c r="C43" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -2816,7 +2816,7 @@
         <v>16</v>
       </c>
       <c r="B44" s="5">
-        <v>46093</v>
+        <v>46139</v>
       </c>
       <c r="C44" s="6">
         <v>1</v>
@@ -2827,7 +2827,7 @@
         <v>16</v>
       </c>
       <c r="B45" s="8">
-        <v>46156</v>
+        <v>46125</v>
       </c>
       <c r="C45" s="9">
         <v>1</v>
@@ -2838,7 +2838,7 @@
         <v>16</v>
       </c>
       <c r="B46" s="5">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="C46" s="6">
         <v>1</v>
@@ -2849,7 +2849,7 @@
         <v>16</v>
       </c>
       <c r="B47" s="8">
-        <v>46101</v>
+        <v>46156</v>
       </c>
       <c r="C47" s="9">
         <v>1</v>
@@ -2857,24 +2857,24 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B48" s="5">
-        <v>46007</v>
+        <v>46092</v>
       </c>
       <c r="C48" s="6">
-        <v>79</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B49" s="8">
-        <v>46009</v>
+        <v>46101</v>
       </c>
       <c r="C49" s="9">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -2882,10 +2882,10 @@
         <v>14</v>
       </c>
       <c r="B50" s="5">
-        <v>46000</v>
+        <v>46007</v>
       </c>
       <c r="C50" s="6">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -2893,10 +2893,10 @@
         <v>14</v>
       </c>
       <c r="B51" s="8">
-        <v>46001</v>
+        <v>46009</v>
       </c>
       <c r="C51" s="9">
-        <v>83</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -2904,10 +2904,10 @@
         <v>14</v>
       </c>
       <c r="B52" s="5">
-        <v>46006</v>
+        <v>46000</v>
       </c>
       <c r="C52" s="6">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -2915,10 +2915,10 @@
         <v>14</v>
       </c>
       <c r="B53" s="8">
-        <v>46010</v>
+        <v>46001</v>
       </c>
       <c r="C53" s="9">
-        <v>24</v>
+        <v>83</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -2926,10 +2926,10 @@
         <v>14</v>
       </c>
       <c r="B54" s="5">
-        <v>46014</v>
+        <v>46006</v>
       </c>
       <c r="C54" s="6">
-        <v>20</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -2937,10 +2937,10 @@
         <v>14</v>
       </c>
       <c r="B55" s="8">
-        <v>46002</v>
+        <v>46010</v>
       </c>
       <c r="C55" s="9">
-        <v>47</v>
+        <v>24</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -2948,10 +2948,10 @@
         <v>14</v>
       </c>
       <c r="B56" s="5">
-        <v>46008</v>
+        <v>46014</v>
       </c>
       <c r="C56" s="6">
-        <v>58</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -2959,7 +2959,7 @@
         <v>14</v>
       </c>
       <c r="B57" s="8">
-        <v>46003</v>
+        <v>46002</v>
       </c>
       <c r="C57" s="9">
         <v>47</v>
@@ -2970,10 +2970,10 @@
         <v>14</v>
       </c>
       <c r="B58" s="5">
-        <v>46013</v>
+        <v>46008</v>
       </c>
       <c r="C58" s="6">
-        <v>30</v>
+        <v>58</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -2981,10 +2981,10 @@
         <v>14</v>
       </c>
       <c r="B59" s="8">
-        <v>46022</v>
+        <v>46003</v>
       </c>
       <c r="C59" s="9">
-        <v>2</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -2992,10 +2992,10 @@
         <v>14</v>
       </c>
       <c r="B60" s="5">
-        <v>46080</v>
+        <v>46013</v>
       </c>
       <c r="C60" s="6">
-        <v>8</v>
+        <v>30</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -3003,10 +3003,10 @@
         <v>14</v>
       </c>
       <c r="B61" s="8">
-        <v>46084</v>
+        <v>46022</v>
       </c>
       <c r="C61" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -3014,10 +3014,10 @@
         <v>14</v>
       </c>
       <c r="B62" s="5">
-        <v>46125</v>
+        <v>46080</v>
       </c>
       <c r="C62" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -3025,7 +3025,7 @@
         <v>14</v>
       </c>
       <c r="B63" s="8">
-        <v>46091</v>
+        <v>46084</v>
       </c>
       <c r="C63" s="9">
         <v>3</v>
@@ -3036,10 +3036,10 @@
         <v>14</v>
       </c>
       <c r="B64" s="5">
-        <v>46083</v>
+        <v>46125</v>
       </c>
       <c r="C64" s="6">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -3047,10 +3047,10 @@
         <v>14</v>
       </c>
       <c r="B65" s="8">
-        <v>46105</v>
+        <v>46091</v>
       </c>
       <c r="C65" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -3058,10 +3058,10 @@
         <v>14</v>
       </c>
       <c r="B66" s="5">
-        <v>46077</v>
+        <v>46083</v>
       </c>
       <c r="C66" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -3069,10 +3069,10 @@
         <v>14</v>
       </c>
       <c r="B67" s="8">
-        <v>46118</v>
+        <v>46105</v>
       </c>
       <c r="C67" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -3080,10 +3080,10 @@
         <v>14</v>
       </c>
       <c r="B68" s="5">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="C68" s="6">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -3091,10 +3091,10 @@
         <v>14</v>
       </c>
       <c r="B69" s="8">
-        <v>46099</v>
+        <v>46118</v>
       </c>
       <c r="C69" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -3102,10 +3102,10 @@
         <v>14</v>
       </c>
       <c r="B70" s="5">
-        <v>46104</v>
+        <v>46078</v>
       </c>
       <c r="C70" s="6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -3113,7 +3113,7 @@
         <v>14</v>
       </c>
       <c r="B71" s="8">
-        <v>46107</v>
+        <v>46099</v>
       </c>
       <c r="C71" s="9">
         <v>2</v>
@@ -3124,10 +3124,10 @@
         <v>14</v>
       </c>
       <c r="B72" s="5">
-        <v>46020</v>
+        <v>46104</v>
       </c>
       <c r="C72" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -3135,10 +3135,10 @@
         <v>14</v>
       </c>
       <c r="B73" s="8">
-        <v>46076</v>
+        <v>46107</v>
       </c>
       <c r="C73" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -3146,10 +3146,10 @@
         <v>14</v>
       </c>
       <c r="B74" s="5">
-        <v>46111</v>
+        <v>46020</v>
       </c>
       <c r="C74" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -3157,10 +3157,10 @@
         <v>14</v>
       </c>
       <c r="B75" s="8">
-        <v>46087</v>
+        <v>46076</v>
       </c>
       <c r="C75" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -3168,10 +3168,10 @@
         <v>14</v>
       </c>
       <c r="B76" s="5">
-        <v>46140</v>
+        <v>46111</v>
       </c>
       <c r="C76" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -3179,10 +3179,10 @@
         <v>14</v>
       </c>
       <c r="B77" s="8">
-        <v>46113</v>
+        <v>46087</v>
       </c>
       <c r="C77" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -3190,7 +3190,7 @@
         <v>14</v>
       </c>
       <c r="B78" s="5">
-        <v>46119</v>
+        <v>46140</v>
       </c>
       <c r="C78" s="6">
         <v>2</v>
@@ -3201,10 +3201,10 @@
         <v>14</v>
       </c>
       <c r="B79" s="8">
-        <v>46108</v>
+        <v>46113</v>
       </c>
       <c r="C79" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -3212,10 +3212,10 @@
         <v>14</v>
       </c>
       <c r="B80" s="5">
-        <v>46098</v>
+        <v>46119</v>
       </c>
       <c r="C80" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -3223,7 +3223,7 @@
         <v>14</v>
       </c>
       <c r="B81" s="8">
-        <v>46141</v>
+        <v>46108</v>
       </c>
       <c r="C81" s="9">
         <v>1</v>
@@ -3234,7 +3234,7 @@
         <v>14</v>
       </c>
       <c r="B82" s="5">
-        <v>46114</v>
+        <v>46098</v>
       </c>
       <c r="C82" s="6">
         <v>1</v>
@@ -3245,10 +3245,10 @@
         <v>14</v>
       </c>
       <c r="B83" s="8">
-        <v>46079</v>
+        <v>46141</v>
       </c>
       <c r="C83" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -3256,7 +3256,7 @@
         <v>14</v>
       </c>
       <c r="B84" s="5">
-        <v>46139</v>
+        <v>46114</v>
       </c>
       <c r="C84" s="6">
         <v>1</v>
@@ -3267,10 +3267,10 @@
         <v>14</v>
       </c>
       <c r="B85" s="8">
-        <v>46148</v>
+        <v>46079</v>
       </c>
       <c r="C85" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -3278,7 +3278,7 @@
         <v>14</v>
       </c>
       <c r="B86" s="5">
-        <v>46092</v>
+        <v>46139</v>
       </c>
       <c r="C86" s="6">
         <v>1</v>
@@ -3289,7 +3289,7 @@
         <v>14</v>
       </c>
       <c r="B87" s="8">
-        <v>46021</v>
+        <v>46148</v>
       </c>
       <c r="C87" s="9">
         <v>2</v>
@@ -3300,10 +3300,10 @@
         <v>14</v>
       </c>
       <c r="B88" s="5">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="C88" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -3311,10 +3311,10 @@
         <v>14</v>
       </c>
       <c r="B89" s="8">
-        <v>46147</v>
+        <v>46021</v>
       </c>
       <c r="C89" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -3322,32 +3322,32 @@
         <v>14</v>
       </c>
       <c r="B90" s="5">
-        <v>46134</v>
+        <v>46086</v>
       </c>
       <c r="C90" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B91" s="8">
-        <v>46003</v>
+        <v>46147</v>
       </c>
       <c r="C91" s="9">
-        <v>95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B92" s="5">
-        <v>46002</v>
+        <v>46134</v>
       </c>
       <c r="C92" s="6">
-        <v>116</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -3355,10 +3355,10 @@
         <v>3</v>
       </c>
       <c r="B93" s="8">
-        <v>46008</v>
+        <v>46003</v>
       </c>
       <c r="C93" s="9">
-        <v>15</v>
+        <v>95</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -3366,10 +3366,10 @@
         <v>3</v>
       </c>
       <c r="B94" s="5">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="C94" s="6">
-        <v>98</v>
+        <v>115</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -3377,10 +3377,10 @@
         <v>3</v>
       </c>
       <c r="B95" s="8">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="C95" s="9">
-        <v>43</v>
+        <v>15</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -3388,10 +3388,10 @@
         <v>3</v>
       </c>
       <c r="B96" s="5">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C96" s="6">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -3399,10 +3399,10 @@
         <v>3</v>
       </c>
       <c r="B97" s="8">
-        <v>46010</v>
+        <v>46007</v>
       </c>
       <c r="C97" s="9">
-        <v>9</v>
+        <v>43</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -3410,10 +3410,10 @@
         <v>3</v>
       </c>
       <c r="B98" s="5">
-        <v>46006</v>
+        <v>46001</v>
       </c>
       <c r="C98" s="6">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -3421,10 +3421,10 @@
         <v>3</v>
       </c>
       <c r="B99" s="8">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="C99" s="9">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -3432,10 +3432,10 @@
         <v>3</v>
       </c>
       <c r="B100" s="5">
-        <v>46015</v>
+        <v>46006</v>
       </c>
       <c r="C100" s="6">
-        <v>1</v>
+        <v>84</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -3443,10 +3443,10 @@
         <v>3</v>
       </c>
       <c r="B101" s="8">
-        <v>46014</v>
+        <v>46009</v>
       </c>
       <c r="C101" s="9">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -3454,10 +3454,10 @@
         <v>3</v>
       </c>
       <c r="B102" s="5">
-        <v>46013</v>
+        <v>46015</v>
       </c>
       <c r="C102" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -3465,10 +3465,10 @@
         <v>3</v>
       </c>
       <c r="B103" s="8">
-        <v>46021</v>
+        <v>46014</v>
       </c>
       <c r="C103" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -3476,10 +3476,10 @@
         <v>3</v>
       </c>
       <c r="B104" s="5">
-        <v>46077</v>
+        <v>46013</v>
       </c>
       <c r="C104" s="6">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -3487,10 +3487,10 @@
         <v>3</v>
       </c>
       <c r="B105" s="8">
-        <v>46090</v>
+        <v>46021</v>
       </c>
       <c r="C105" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -3498,10 +3498,10 @@
         <v>3</v>
       </c>
       <c r="B106" s="5">
-        <v>46093</v>
+        <v>46077</v>
       </c>
       <c r="C106" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -3509,10 +3509,10 @@
         <v>3</v>
       </c>
       <c r="B107" s="8">
-        <v>46078</v>
+        <v>46090</v>
       </c>
       <c r="C107" s="9">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -3520,10 +3520,10 @@
         <v>3</v>
       </c>
       <c r="B108" s="5">
-        <v>46084</v>
+        <v>46093</v>
       </c>
       <c r="C108" s="6">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -3531,10 +3531,10 @@
         <v>3</v>
       </c>
       <c r="B109" s="8">
-        <v>46134</v>
+        <v>46078</v>
       </c>
       <c r="C109" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -3542,10 +3542,10 @@
         <v>3</v>
       </c>
       <c r="B110" s="5">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="C110" s="6">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -3553,10 +3553,10 @@
         <v>3</v>
       </c>
       <c r="B111" s="8">
-        <v>46022</v>
+        <v>46134</v>
       </c>
       <c r="C111" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -3564,10 +3564,10 @@
         <v>3</v>
       </c>
       <c r="B112" s="5">
-        <v>46114</v>
+        <v>46083</v>
       </c>
       <c r="C112" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -3575,7 +3575,7 @@
         <v>3</v>
       </c>
       <c r="B113" s="8">
-        <v>46135</v>
+        <v>46022</v>
       </c>
       <c r="C113" s="9">
         <v>1</v>
@@ -3586,10 +3586,10 @@
         <v>3</v>
       </c>
       <c r="B114" s="5">
-        <v>46126</v>
+        <v>46114</v>
       </c>
       <c r="C114" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -3597,10 +3597,10 @@
         <v>3</v>
       </c>
       <c r="B115" s="8">
-        <v>46120</v>
+        <v>46135</v>
       </c>
       <c r="C115" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -3608,10 +3608,10 @@
         <v>3</v>
       </c>
       <c r="B116" s="5">
-        <v>46127</v>
+        <v>46126</v>
       </c>
       <c r="C116" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -3619,10 +3619,10 @@
         <v>3</v>
       </c>
       <c r="B117" s="8">
-        <v>46087</v>
+        <v>46120</v>
       </c>
       <c r="C117" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -3630,7 +3630,7 @@
         <v>3</v>
       </c>
       <c r="B118" s="5">
-        <v>46108</v>
+        <v>46127</v>
       </c>
       <c r="C118" s="6">
         <v>1</v>
@@ -3641,7 +3641,7 @@
         <v>3</v>
       </c>
       <c r="B119" s="8">
-        <v>46020</v>
+        <v>46087</v>
       </c>
       <c r="C119" s="9">
         <v>1</v>
@@ -3652,7 +3652,7 @@
         <v>3</v>
       </c>
       <c r="B120" s="5">
-        <v>46097</v>
+        <v>46108</v>
       </c>
       <c r="C120" s="6">
         <v>1</v>
@@ -3663,7 +3663,7 @@
         <v>3</v>
       </c>
       <c r="B121" s="8">
-        <v>46129</v>
+        <v>46020</v>
       </c>
       <c r="C121" s="9">
         <v>1</v>
@@ -3674,7 +3674,7 @@
         <v>3</v>
       </c>
       <c r="B122" s="5">
-        <v>46080</v>
+        <v>46097</v>
       </c>
       <c r="C122" s="6">
         <v>1</v>
@@ -3685,10 +3685,10 @@
         <v>3</v>
       </c>
       <c r="B123" s="8">
-        <v>46101</v>
+        <v>46161</v>
       </c>
       <c r="C123" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -3696,7 +3696,7 @@
         <v>3</v>
       </c>
       <c r="B124" s="5">
-        <v>46155</v>
+        <v>46129</v>
       </c>
       <c r="C124" s="6">
         <v>1</v>
@@ -3707,7 +3707,7 @@
         <v>3</v>
       </c>
       <c r="B125" s="8">
-        <v>46150</v>
+        <v>46080</v>
       </c>
       <c r="C125" s="9">
         <v>1</v>
@@ -3718,7 +3718,7 @@
         <v>3</v>
       </c>
       <c r="B126" s="5">
-        <v>46141</v>
+        <v>46101</v>
       </c>
       <c r="C126" s="6">
         <v>1</v>
@@ -3729,7 +3729,7 @@
         <v>3</v>
       </c>
       <c r="B127" s="8">
-        <v>46085</v>
+        <v>46155</v>
       </c>
       <c r="C127" s="9">
         <v>1</v>
@@ -3740,7 +3740,7 @@
         <v>3</v>
       </c>
       <c r="B128" s="5">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="C128" s="6">
         <v>1</v>
@@ -3751,10 +3751,10 @@
         <v>3</v>
       </c>
       <c r="B129" s="8">
-        <v>46118</v>
+        <v>46141</v>
       </c>
       <c r="C129" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -3762,7 +3762,7 @@
         <v>3</v>
       </c>
       <c r="B130" s="5">
-        <v>46079</v>
+        <v>46085</v>
       </c>
       <c r="C130" s="6">
         <v>1</v>
@@ -3770,35 +3770,35 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B131" s="8">
-        <v>46003</v>
+        <v>46148</v>
       </c>
       <c r="C131" s="9">
-        <v>92</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B132" s="5">
-        <v>46000</v>
+        <v>46118</v>
       </c>
       <c r="C132" s="6">
-        <v>133</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B133" s="8">
-        <v>46006</v>
+        <v>46079</v>
       </c>
       <c r="C133" s="9">
-        <v>175</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -3806,10 +3806,10 @@
         <v>15</v>
       </c>
       <c r="B134" s="5">
-        <v>46001</v>
+        <v>46003</v>
       </c>
       <c r="C134" s="6">
-        <v>174</v>
+        <v>92</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -3817,10 +3817,10 @@
         <v>15</v>
       </c>
       <c r="B135" s="8">
-        <v>46014</v>
+        <v>46000</v>
       </c>
       <c r="C135" s="9">
-        <v>16</v>
+        <v>133</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -3828,10 +3828,10 @@
         <v>15</v>
       </c>
       <c r="B136" s="5">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="C136" s="6">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -3839,10 +3839,10 @@
         <v>15</v>
       </c>
       <c r="B137" s="8">
-        <v>46009</v>
+        <v>46001</v>
       </c>
       <c r="C137" s="9">
-        <v>20</v>
+        <v>174</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -3850,10 +3850,10 @@
         <v>15</v>
       </c>
       <c r="B138" s="5">
-        <v>46010</v>
+        <v>46014</v>
       </c>
       <c r="C138" s="6">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -3861,10 +3861,10 @@
         <v>15</v>
       </c>
       <c r="B139" s="8">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C139" s="9">
-        <v>25</v>
+        <v>171</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -3872,10 +3872,10 @@
         <v>15</v>
       </c>
       <c r="B140" s="5">
-        <v>46007</v>
+        <v>46009</v>
       </c>
       <c r="C140" s="6">
-        <v>43</v>
+        <v>20</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -3883,10 +3883,10 @@
         <v>15</v>
       </c>
       <c r="B141" s="8">
-        <v>46013</v>
+        <v>46010</v>
       </c>
       <c r="C141" s="9">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -3894,10 +3894,10 @@
         <v>15</v>
       </c>
       <c r="B142" s="5">
-        <v>46080</v>
+        <v>46008</v>
       </c>
       <c r="C142" s="6">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -3905,10 +3905,10 @@
         <v>15</v>
       </c>
       <c r="B143" s="8">
-        <v>46090</v>
+        <v>46007</v>
       </c>
       <c r="C143" s="9">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -3916,10 +3916,10 @@
         <v>15</v>
       </c>
       <c r="B144" s="5">
-        <v>46079</v>
+        <v>46013</v>
       </c>
       <c r="C144" s="6">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -3927,10 +3927,10 @@
         <v>15</v>
       </c>
       <c r="B145" s="8">
-        <v>46015</v>
+        <v>46080</v>
       </c>
       <c r="C145" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -3938,10 +3938,10 @@
         <v>15</v>
       </c>
       <c r="B146" s="5">
-        <v>46085</v>
+        <v>46090</v>
       </c>
       <c r="C146" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -3949,10 +3949,10 @@
         <v>15</v>
       </c>
       <c r="B147" s="8">
-        <v>46098</v>
+        <v>46079</v>
       </c>
       <c r="C147" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -3960,10 +3960,10 @@
         <v>15</v>
       </c>
       <c r="B148" s="5">
-        <v>46021</v>
+        <v>46015</v>
       </c>
       <c r="C148" s="6">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -3971,10 +3971,10 @@
         <v>15</v>
       </c>
       <c r="B149" s="8">
-        <v>46078</v>
+        <v>46085</v>
       </c>
       <c r="C149" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -3982,10 +3982,10 @@
         <v>15</v>
       </c>
       <c r="B150" s="5">
-        <v>46084</v>
+        <v>46098</v>
       </c>
       <c r="C150" s="6">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -3993,10 +3993,10 @@
         <v>15</v>
       </c>
       <c r="B151" s="8">
-        <v>46128</v>
+        <v>46021</v>
       </c>
       <c r="C151" s="9">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -4004,10 +4004,10 @@
         <v>15</v>
       </c>
       <c r="B152" s="5">
-        <v>46083</v>
+        <v>46078</v>
       </c>
       <c r="C152" s="6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -4015,10 +4015,10 @@
         <v>15</v>
       </c>
       <c r="B153" s="8">
-        <v>46153</v>
+        <v>46084</v>
       </c>
       <c r="C153" s="9">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -4026,10 +4026,10 @@
         <v>15</v>
       </c>
       <c r="B154" s="5">
-        <v>46076</v>
+        <v>46128</v>
       </c>
       <c r="C154" s="6">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -4037,10 +4037,10 @@
         <v>15</v>
       </c>
       <c r="B155" s="8">
-        <v>46099</v>
+        <v>46083</v>
       </c>
       <c r="C155" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -4048,7 +4048,7 @@
         <v>15</v>
       </c>
       <c r="B156" s="5">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="C156" s="6">
         <v>1</v>
@@ -4059,10 +4059,10 @@
         <v>15</v>
       </c>
       <c r="B157" s="8">
-        <v>46092</v>
+        <v>46076</v>
       </c>
       <c r="C157" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -4070,7 +4070,7 @@
         <v>15</v>
       </c>
       <c r="B158" s="5">
-        <v>46031</v>
+        <v>46099</v>
       </c>
       <c r="C158" s="6">
         <v>2</v>
@@ -4081,10 +4081,10 @@
         <v>15</v>
       </c>
       <c r="B159" s="8">
-        <v>46120</v>
+        <v>46154</v>
       </c>
       <c r="C159" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -4092,10 +4092,10 @@
         <v>15</v>
       </c>
       <c r="B160" s="5">
-        <v>46077</v>
+        <v>46092</v>
       </c>
       <c r="C160" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -4103,10 +4103,10 @@
         <v>15</v>
       </c>
       <c r="B161" s="8">
-        <v>46114</v>
+        <v>46031</v>
       </c>
       <c r="C161" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -4114,10 +4114,10 @@
         <v>15</v>
       </c>
       <c r="B162" s="5">
-        <v>46037</v>
+        <v>46120</v>
       </c>
       <c r="C162" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -4125,10 +4125,10 @@
         <v>15</v>
       </c>
       <c r="B163" s="8">
-        <v>46020</v>
+        <v>46077</v>
       </c>
       <c r="C163" s="9">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -4136,7 +4136,7 @@
         <v>15</v>
       </c>
       <c r="B164" s="5">
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="C164" s="6">
         <v>1</v>
@@ -4147,7 +4147,7 @@
         <v>15</v>
       </c>
       <c r="B165" s="8">
-        <v>46155</v>
+        <v>46037</v>
       </c>
       <c r="C165" s="9">
         <v>1</v>
@@ -4158,10 +4158,10 @@
         <v>15</v>
       </c>
       <c r="B166" s="5">
-        <v>46112</v>
+        <v>46020</v>
       </c>
       <c r="C166" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -4169,7 +4169,7 @@
         <v>15</v>
       </c>
       <c r="B167" s="8">
-        <v>46132</v>
+        <v>46106</v>
       </c>
       <c r="C167" s="9">
         <v>1</v>
@@ -4180,7 +4180,7 @@
         <v>15</v>
       </c>
       <c r="B168" s="5">
-        <v>46108</v>
+        <v>46155</v>
       </c>
       <c r="C168" s="6">
         <v>1</v>
@@ -4191,7 +4191,7 @@
         <v>15</v>
       </c>
       <c r="B169" s="8">
-        <v>46148</v>
+        <v>46112</v>
       </c>
       <c r="C169" s="9">
         <v>1</v>
@@ -4202,7 +4202,7 @@
         <v>15</v>
       </c>
       <c r="B170" s="5">
-        <v>46118</v>
+        <v>46132</v>
       </c>
       <c r="C170" s="6">
         <v>1</v>
@@ -4213,7 +4213,7 @@
         <v>15</v>
       </c>
       <c r="B171" s="8">
-        <v>46035</v>
+        <v>46108</v>
       </c>
       <c r="C171" s="9">
         <v>1</v>
@@ -4224,7 +4224,7 @@
         <v>15</v>
       </c>
       <c r="B172" s="5">
-        <v>46093</v>
+        <v>46148</v>
       </c>
       <c r="C172" s="6">
         <v>1</v>
@@ -4235,7 +4235,7 @@
         <v>15</v>
       </c>
       <c r="B173" s="8">
-        <v>46022</v>
+        <v>46118</v>
       </c>
       <c r="C173" s="9">
         <v>1</v>
@@ -4246,7 +4246,7 @@
         <v>15</v>
       </c>
       <c r="B174" s="5">
-        <v>46087</v>
+        <v>46035</v>
       </c>
       <c r="C174" s="6">
         <v>1</v>
@@ -4257,10 +4257,10 @@
         <v>15</v>
       </c>
       <c r="B175" s="8">
-        <v>46030</v>
+        <v>46093</v>
       </c>
       <c r="C175" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -4268,7 +4268,7 @@
         <v>15</v>
       </c>
       <c r="B176" s="5">
-        <v>46101</v>
+        <v>46022</v>
       </c>
       <c r="C176" s="6">
         <v>1</v>
@@ -4279,7 +4279,7 @@
         <v>15</v>
       </c>
       <c r="B177" s="8">
-        <v>46142</v>
+        <v>46087</v>
       </c>
       <c r="C177" s="9">
         <v>1</v>
@@ -4287,35 +4287,35 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B178" s="5">
-        <v>46001</v>
+        <v>46030</v>
       </c>
       <c r="C178" s="6">
-        <v>153</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B179" s="8">
-        <v>46008</v>
+        <v>46101</v>
       </c>
       <c r="C179" s="9">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B180" s="5">
-        <v>46003</v>
+        <v>46142</v>
       </c>
       <c r="C180" s="6">
-        <v>70</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -4323,10 +4323,10 @@
         <v>21</v>
       </c>
       <c r="B181" s="8">
-        <v>46002</v>
+        <v>46001</v>
       </c>
       <c r="C181" s="9">
-        <v>111</v>
+        <v>153</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -4334,10 +4334,10 @@
         <v>21</v>
       </c>
       <c r="B182" s="5">
-        <v>46006</v>
+        <v>46008</v>
       </c>
       <c r="C182" s="6">
-        <v>147</v>
+        <v>38</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -4345,10 +4345,10 @@
         <v>21</v>
       </c>
       <c r="B183" s="8">
-        <v>46007</v>
+        <v>46003</v>
       </c>
       <c r="C183" s="9">
-        <v>45</v>
+        <v>70</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -4356,10 +4356,10 @@
         <v>21</v>
       </c>
       <c r="B184" s="5">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="C184" s="6">
-        <v>129</v>
+        <v>111</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -4367,10 +4367,10 @@
         <v>21</v>
       </c>
       <c r="B185" s="8">
-        <v>46084</v>
+        <v>46006</v>
       </c>
       <c r="C185" s="9">
-        <v>10</v>
+        <v>147</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -4378,10 +4378,10 @@
         <v>21</v>
       </c>
       <c r="B186" s="5">
-        <v>46014</v>
+        <v>46007</v>
       </c>
       <c r="C186" s="6">
-        <v>22</v>
+        <v>45</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -4389,10 +4389,10 @@
         <v>21</v>
       </c>
       <c r="B187" s="8">
-        <v>46013</v>
+        <v>46000</v>
       </c>
       <c r="C187" s="9">
-        <v>29</v>
+        <v>129</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -4400,10 +4400,10 @@
         <v>21</v>
       </c>
       <c r="B188" s="5">
-        <v>46010</v>
+        <v>46084</v>
       </c>
       <c r="C188" s="6">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -4411,10 +4411,10 @@
         <v>21</v>
       </c>
       <c r="B189" s="8">
-        <v>46021</v>
+        <v>46014</v>
       </c>
       <c r="C189" s="9">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -4422,10 +4422,10 @@
         <v>21</v>
       </c>
       <c r="B190" s="5">
-        <v>46009</v>
+        <v>46013</v>
       </c>
       <c r="C190" s="6">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -4433,10 +4433,10 @@
         <v>21</v>
       </c>
       <c r="B191" s="8">
-        <v>46083</v>
+        <v>46010</v>
       </c>
       <c r="C191" s="9">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -4444,10 +4444,10 @@
         <v>21</v>
       </c>
       <c r="B192" s="5">
-        <v>46157</v>
+        <v>46021</v>
       </c>
       <c r="C192" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -4455,10 +4455,10 @@
         <v>21</v>
       </c>
       <c r="B193" s="8">
-        <v>46079</v>
+        <v>46009</v>
       </c>
       <c r="C193" s="9">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -4466,10 +4466,10 @@
         <v>21</v>
       </c>
       <c r="B194" s="5">
-        <v>46077</v>
+        <v>46083</v>
       </c>
       <c r="C194" s="6">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -4477,7 +4477,7 @@
         <v>21</v>
       </c>
       <c r="B195" s="8">
-        <v>46035</v>
+        <v>46157</v>
       </c>
       <c r="C195" s="9">
         <v>2</v>
@@ -4488,7 +4488,7 @@
         <v>21</v>
       </c>
       <c r="B196" s="5">
-        <v>46085</v>
+        <v>46079</v>
       </c>
       <c r="C196" s="6">
         <v>3</v>
@@ -4499,10 +4499,10 @@
         <v>21</v>
       </c>
       <c r="B197" s="8">
-        <v>46120</v>
+        <v>46077</v>
       </c>
       <c r="C197" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -4510,10 +4510,10 @@
         <v>21</v>
       </c>
       <c r="B198" s="5">
-        <v>46114</v>
+        <v>46035</v>
       </c>
       <c r="C198" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -4521,10 +4521,10 @@
         <v>21</v>
       </c>
       <c r="B199" s="8">
-        <v>46094</v>
+        <v>46085</v>
       </c>
       <c r="C199" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -4532,10 +4532,10 @@
         <v>21</v>
       </c>
       <c r="B200" s="5">
-        <v>46080</v>
+        <v>46120</v>
       </c>
       <c r="C200" s="6">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -4543,10 +4543,10 @@
         <v>21</v>
       </c>
       <c r="B201" s="8">
-        <v>46127</v>
+        <v>46114</v>
       </c>
       <c r="C201" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -4554,10 +4554,10 @@
         <v>21</v>
       </c>
       <c r="B202" s="5">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="C202" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -4565,10 +4565,10 @@
         <v>21</v>
       </c>
       <c r="B203" s="8">
-        <v>46090</v>
+        <v>46080</v>
       </c>
       <c r="C203" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -4576,10 +4576,10 @@
         <v>21</v>
       </c>
       <c r="B204" s="5">
-        <v>46020</v>
+        <v>46127</v>
       </c>
       <c r="C204" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -4587,10 +4587,10 @@
         <v>21</v>
       </c>
       <c r="B205" s="8">
-        <v>46015</v>
+        <v>46091</v>
       </c>
       <c r="C205" s="9">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -4598,10 +4598,10 @@
         <v>21</v>
       </c>
       <c r="B206" s="5">
-        <v>46078</v>
+        <v>46090</v>
       </c>
       <c r="C206" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -4609,10 +4609,10 @@
         <v>21</v>
       </c>
       <c r="B207" s="8">
-        <v>46148</v>
+        <v>46020</v>
       </c>
       <c r="C207" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4620,10 +4620,10 @@
         <v>21</v>
       </c>
       <c r="B208" s="5">
-        <v>46105</v>
+        <v>46015</v>
       </c>
       <c r="C208" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4631,10 +4631,10 @@
         <v>21</v>
       </c>
       <c r="B209" s="8">
-        <v>46087</v>
+        <v>46078</v>
       </c>
       <c r="C209" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4642,10 +4642,10 @@
         <v>21</v>
       </c>
       <c r="B210" s="5">
-        <v>46107</v>
+        <v>46148</v>
       </c>
       <c r="C210" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -4653,10 +4653,10 @@
         <v>21</v>
       </c>
       <c r="B211" s="8">
-        <v>46086</v>
+        <v>46105</v>
       </c>
       <c r="C211" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -4664,10 +4664,10 @@
         <v>21</v>
       </c>
       <c r="B212" s="5">
-        <v>46106</v>
+        <v>46087</v>
       </c>
       <c r="C212" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4675,7 +4675,7 @@
         <v>21</v>
       </c>
       <c r="B213" s="8">
-        <v>46150</v>
+        <v>46107</v>
       </c>
       <c r="C213" s="9">
         <v>3</v>
@@ -4686,10 +4686,10 @@
         <v>21</v>
       </c>
       <c r="B214" s="5">
-        <v>46104</v>
+        <v>46086</v>
       </c>
       <c r="C214" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4697,7 +4697,7 @@
         <v>21</v>
       </c>
       <c r="B215" s="8">
-        <v>46118</v>
+        <v>46106</v>
       </c>
       <c r="C215" s="9">
         <v>1</v>
@@ -4708,10 +4708,10 @@
         <v>21</v>
       </c>
       <c r="B216" s="5">
-        <v>46076</v>
+        <v>46150</v>
       </c>
       <c r="C216" s="6">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4719,10 +4719,10 @@
         <v>21</v>
       </c>
       <c r="B217" s="8">
-        <v>46154</v>
+        <v>46104</v>
       </c>
       <c r="C217" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -4730,10 +4730,10 @@
         <v>21</v>
       </c>
       <c r="B218" s="5">
-        <v>46093</v>
+        <v>46118</v>
       </c>
       <c r="C218" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -4741,10 +4741,10 @@
         <v>21</v>
       </c>
       <c r="B219" s="8">
-        <v>46122</v>
+        <v>46076</v>
       </c>
       <c r="C219" s="9">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4752,10 +4752,10 @@
         <v>21</v>
       </c>
       <c r="B220" s="5">
-        <v>46092</v>
+        <v>46154</v>
       </c>
       <c r="C220" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -4763,10 +4763,10 @@
         <v>21</v>
       </c>
       <c r="B221" s="8">
-        <v>46156</v>
+        <v>46093</v>
       </c>
       <c r="C221" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -4774,7 +4774,7 @@
         <v>21</v>
       </c>
       <c r="B222" s="5">
-        <v>46133</v>
+        <v>46122</v>
       </c>
       <c r="C222" s="6">
         <v>1</v>
@@ -4785,10 +4785,10 @@
         <v>21</v>
       </c>
       <c r="B223" s="8">
-        <v>46126</v>
+        <v>46092</v>
       </c>
       <c r="C223" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -4796,7 +4796,7 @@
         <v>21</v>
       </c>
       <c r="B224" s="5">
-        <v>46022</v>
+        <v>46156</v>
       </c>
       <c r="C224" s="6">
         <v>2</v>
@@ -4807,10 +4807,10 @@
         <v>21</v>
       </c>
       <c r="B225" s="8">
-        <v>46100</v>
+        <v>46133</v>
       </c>
       <c r="C225" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -4818,7 +4818,7 @@
         <v>21</v>
       </c>
       <c r="B226" s="5">
-        <v>46101</v>
+        <v>46126</v>
       </c>
       <c r="C226" s="6">
         <v>1</v>
@@ -4829,10 +4829,10 @@
         <v>21</v>
       </c>
       <c r="B227" s="8">
-        <v>46097</v>
+        <v>46022</v>
       </c>
       <c r="C227" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -4840,10 +4840,10 @@
         <v>21</v>
       </c>
       <c r="B228" s="5">
-        <v>46108</v>
+        <v>46100</v>
       </c>
       <c r="C228" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -4851,10 +4851,10 @@
         <v>21</v>
       </c>
       <c r="B229" s="8">
-        <v>46098</v>
+        <v>46101</v>
       </c>
       <c r="C229" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -4862,10 +4862,10 @@
         <v>21</v>
       </c>
       <c r="B230" s="5">
-        <v>46113</v>
+        <v>46097</v>
       </c>
       <c r="C230" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -4873,7 +4873,7 @@
         <v>21</v>
       </c>
       <c r="B231" s="8">
-        <v>46142</v>
+        <v>46108</v>
       </c>
       <c r="C231" s="9">
         <v>1</v>
@@ -4884,10 +4884,10 @@
         <v>21</v>
       </c>
       <c r="B232" s="5">
-        <v>46153</v>
+        <v>46098</v>
       </c>
       <c r="C232" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -4895,7 +4895,7 @@
         <v>21</v>
       </c>
       <c r="B233" s="8">
-        <v>46031</v>
+        <v>46113</v>
       </c>
       <c r="C233" s="9">
         <v>1</v>
@@ -4906,9 +4906,42 @@
         <v>21</v>
       </c>
       <c r="B234" s="5">
+        <v>46142</v>
+      </c>
+      <c r="C234" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B235" s="8">
+        <v>46153</v>
+      </c>
+      <c r="C235" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B236" s="5">
+        <v>46031</v>
+      </c>
+      <c r="C236" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B237" s="8">
         <v>46155</v>
       </c>
-      <c r="C234" s="6">
+      <c r="C237" s="9">
         <v>1</v>
       </c>
     </row>
@@ -4975,7 +5008,7 @@
         <v>4</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -5020,13 +5053,13 @@
         <v>11</v>
       </c>
       <c r="C6">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -5043,7 +5076,7 @@
         <v>1</v>
       </c>
       <c r="E7">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -5054,7 +5087,7 @@
         <v>10</v>
       </c>
       <c r="C8">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D8">
         <v>4</v>
@@ -5094,7 +5127,7 @@
         <v>1</v>
       </c>
       <c r="E10">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -5445,7 +5478,7 @@
         <v>7</v>
       </c>
       <c r="C31">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D31">
         <v>4</v>
@@ -5465,7 +5498,7 @@
         <v>83</v>
       </c>
       <c r="D32">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E32">
         <v>87</v>
@@ -5485,7 +5518,7 @@
         <v>8</v>
       </c>
       <c r="E33">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -5496,13 +5529,13 @@
         <v>19</v>
       </c>
       <c r="C34">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D34">
         <v>8</v>
       </c>
       <c r="E34">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -5536,7 +5569,7 @@
         <v>87</v>
       </c>
       <c r="E36">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -5597,7 +5630,6 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0916EAC6-1E7F-4924-9D0E-33749FD3E143}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:C357"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5617,7 +5649,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -5628,7 +5660,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -5639,403 +5671,403 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
         <v>44</v>
       </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
         <v>53</v>
       </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
         <v>50</v>
       </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" t="s">
         <v>46</v>
       </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>52</v>
-      </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" t="s">
-        <v>54</v>
-      </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>3</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="C15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" t="s">
         <v>56</v>
       </c>
-      <c r="C15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="C16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" t="s">
         <v>57</v>
       </c>
-      <c r="C16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>3</v>
-      </c>
-      <c r="B17" t="s">
+      <c r="C17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" t="s">
+        <v>62</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>3</v>
+      </c>
+      <c r="B24" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25" t="s">
+        <v>77</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>3</v>
+      </c>
+      <c r="B28" t="s">
+        <v>68</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30" t="s">
         <v>70</v>
       </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="C30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>3</v>
+      </c>
+      <c r="B31" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B32" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>3</v>
+      </c>
+      <c r="B33" t="s">
+        <v>73</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>3</v>
+      </c>
+      <c r="B34" t="s">
+        <v>74</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>3</v>
+      </c>
+      <c r="B35" t="s">
+        <v>75</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>3</v>
+      </c>
+      <c r="B36" t="s">
         <v>76</v>
       </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>3</v>
-      </c>
-      <c r="B19" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>3</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="C36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>3</v>
+      </c>
+      <c r="B37" t="s">
+        <v>61</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>3</v>
+      </c>
+      <c r="B38" t="s">
         <v>78</v>
       </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>3</v>
-      </c>
-      <c r="B21" t="s">
-        <v>68</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B22" t="s">
-        <v>77</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>3</v>
-      </c>
-      <c r="B23" t="s">
-        <v>72</v>
-      </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>3</v>
-      </c>
-      <c r="B24" t="s">
-        <v>63</v>
-      </c>
-      <c r="C24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>3</v>
-      </c>
-      <c r="B25" t="s">
-        <v>60</v>
-      </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>3</v>
-      </c>
-      <c r="B26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>3</v>
-      </c>
-      <c r="B27" t="s">
-        <v>59</v>
-      </c>
-      <c r="C27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>3</v>
-      </c>
-      <c r="B28" t="s">
-        <v>67</v>
-      </c>
-      <c r="C28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>3</v>
-      </c>
-      <c r="B29" t="s">
-        <v>62</v>
-      </c>
-      <c r="C29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>3</v>
-      </c>
-      <c r="B30" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>3</v>
-      </c>
-      <c r="B31" t="s">
-        <v>58</v>
-      </c>
-      <c r="C31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>3</v>
-      </c>
-      <c r="B32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>3</v>
-      </c>
-      <c r="B33" t="s">
+      <c r="C38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>3</v>
+      </c>
+      <c r="B39" t="s">
         <v>79</v>
       </c>
-      <c r="C33">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>3</v>
-      </c>
-      <c r="B34" t="s">
-        <v>73</v>
-      </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>3</v>
-      </c>
-      <c r="B35" t="s">
-        <v>64</v>
-      </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>3</v>
-      </c>
-      <c r="B36" t="s">
-        <v>75</v>
-      </c>
-      <c r="C36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>3</v>
-      </c>
-      <c r="B37" t="s">
-        <v>66</v>
-      </c>
-      <c r="C37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>3</v>
-      </c>
-      <c r="B38" t="s">
-        <v>65</v>
-      </c>
-      <c r="C38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>3</v>
-      </c>
-      <c r="B39" t="s">
-        <v>69</v>
-      </c>
       <c r="C39">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>14</v>
       </c>
@@ -6046,7 +6078,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>14</v>
       </c>
@@ -6057,7 +6089,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>14</v>
       </c>
@@ -6068,7 +6100,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>14</v>
       </c>
@@ -6079,7 +6111,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>14</v>
       </c>
@@ -6090,7 +6122,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>14</v>
       </c>
@@ -6101,7 +6133,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>14</v>
       </c>
@@ -6112,7 +6144,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>14</v>
       </c>
@@ -6123,7 +6155,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>14</v>
       </c>
@@ -6134,7 +6166,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>14</v>
       </c>
@@ -6145,7 +6177,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>14</v>
       </c>
@@ -6156,7 +6188,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>14</v>
       </c>
@@ -6167,7 +6199,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>14</v>
       </c>
@@ -6178,7 +6210,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>14</v>
       </c>
@@ -6189,7 +6221,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>14</v>
       </c>
@@ -6200,7 +6232,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>14</v>
       </c>
@@ -6211,7 +6243,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>14</v>
       </c>
@@ -6222,7 +6254,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>14</v>
       </c>
@@ -6233,7 +6265,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>14</v>
       </c>
@@ -6244,7 +6276,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>14</v>
       </c>
@@ -6255,7 +6287,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>14</v>
       </c>
@@ -6266,7 +6298,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>14</v>
       </c>
@@ -6277,7 +6309,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>14</v>
       </c>
@@ -6288,7 +6320,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>14</v>
       </c>
@@ -6299,7 +6331,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>14</v>
       </c>
@@ -6310,7 +6342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>14</v>
       </c>
@@ -6321,7 +6353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>14</v>
       </c>
@@ -6332,7 +6364,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>14</v>
       </c>
@@ -6343,7 +6375,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>14</v>
       </c>
@@ -6354,7 +6386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>14</v>
       </c>
@@ -6365,7 +6397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>14</v>
       </c>
@@ -6376,7 +6408,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>14</v>
       </c>
@@ -6387,7 +6419,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>14</v>
       </c>
@@ -6398,7 +6430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>14</v>
       </c>
@@ -6409,7 +6441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>14</v>
       </c>
@@ -6420,7 +6452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>14</v>
       </c>
@@ -6431,7 +6463,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>14</v>
       </c>
@@ -6442,7 +6474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>14</v>
       </c>
@@ -6453,7 +6485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>14</v>
       </c>
@@ -6464,7 +6496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>14</v>
       </c>
@@ -6475,7 +6507,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>14</v>
       </c>
@@ -6486,7 +6518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>14</v>
       </c>
@@ -6497,7 +6529,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>14</v>
       </c>
@@ -6508,7 +6540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>14</v>
       </c>
@@ -6519,7 +6551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>14</v>
       </c>
@@ -6530,7 +6562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>14</v>
       </c>
@@ -6541,7 +6573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>14</v>
       </c>
@@ -6552,7 +6584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>14</v>
       </c>
@@ -6563,7 +6595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>14</v>
       </c>
@@ -6574,7 +6606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>14</v>
       </c>
@@ -6585,7 +6617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>14</v>
       </c>
@@ -6596,7 +6628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>14</v>
       </c>
@@ -6607,7 +6639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>14</v>
       </c>
@@ -6618,7 +6650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>14</v>
       </c>
@@ -6629,7 +6661,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>14</v>
       </c>
@@ -6640,7 +6672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>14</v>
       </c>
@@ -6651,7 +6683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>14</v>
       </c>
@@ -6662,7 +6694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>14</v>
       </c>
@@ -6673,7 +6705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>14</v>
       </c>
@@ -6684,7 +6716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>14</v>
       </c>
@@ -6695,7 +6727,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>14</v>
       </c>
@@ -6706,7 +6738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>14</v>
       </c>
@@ -6725,7 +6757,7 @@
         <v>120</v>
       </c>
       <c r="C102">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -6750,7 +6782,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="105" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>15</v>
       </c>
@@ -6761,7 +6793,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="106" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>15</v>
       </c>
@@ -6772,7 +6804,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="107" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>15</v>
       </c>
@@ -6783,7 +6815,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="108" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>15</v>
       </c>
@@ -6794,7 +6826,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="109" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>15</v>
       </c>
@@ -6805,7 +6837,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="110" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>15</v>
       </c>
@@ -6816,7 +6848,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="111" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>15</v>
       </c>
@@ -6827,7 +6859,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="112" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>15</v>
       </c>
@@ -6838,7 +6870,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="113" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>15</v>
       </c>
@@ -6849,7 +6881,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="114" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>15</v>
       </c>
@@ -6860,7 +6892,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="115" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>15</v>
       </c>
@@ -6871,7 +6903,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="116" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>15</v>
       </c>
@@ -6882,7 +6914,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="117" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>15</v>
       </c>
@@ -6893,7 +6925,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="118" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>15</v>
       </c>
@@ -6904,7 +6936,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="119" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>15</v>
       </c>
@@ -6915,7 +6947,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="120" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>15</v>
       </c>
@@ -6926,7 +6958,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>15</v>
       </c>
@@ -6937,7 +6969,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>15</v>
       </c>
@@ -6948,7 +6980,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>15</v>
       </c>
@@ -6959,7 +6991,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>15</v>
       </c>
@@ -6970,7 +7002,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>15</v>
       </c>
@@ -6981,7 +7013,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>15</v>
       </c>
@@ -6992,7 +7024,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>15</v>
       </c>
@@ -7003,7 +7035,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>15</v>
       </c>
@@ -7014,7 +7046,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>15</v>
       </c>
@@ -7025,7 +7057,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>15</v>
       </c>
@@ -7036,7 +7068,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>15</v>
       </c>
@@ -7047,7 +7079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>15</v>
       </c>
@@ -7058,7 +7090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>15</v>
       </c>
@@ -7069,7 +7101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>15</v>
       </c>
@@ -7080,7 +7112,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>15</v>
       </c>
@@ -7091,7 +7123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>15</v>
       </c>
@@ -7102,7 +7134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>15</v>
       </c>
@@ -7113,7 +7145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>15</v>
       </c>
@@ -7124,7 +7156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>15</v>
       </c>
@@ -7135,7 +7167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>15</v>
       </c>
@@ -7146,7 +7178,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>15</v>
       </c>
@@ -7157,7 +7189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>15</v>
       </c>
@@ -7168,7 +7200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>15</v>
       </c>
@@ -7179,7 +7211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>15</v>
       </c>
@@ -7190,7 +7222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>15</v>
       </c>
@@ -7201,7 +7233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>15</v>
       </c>
@@ -7212,7 +7244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>15</v>
       </c>
@@ -7223,7 +7255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>15</v>
       </c>
@@ -7234,7 +7266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>15</v>
       </c>
@@ -7245,7 +7277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>15</v>
       </c>
@@ -7256,7 +7288,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>15</v>
       </c>
@@ -7267,7 +7299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>15</v>
       </c>
@@ -7278,7 +7310,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>15</v>
       </c>
@@ -7289,7 +7321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>15</v>
       </c>
@@ -7300,7 +7332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>15</v>
       </c>
@@ -7311,7 +7343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>15</v>
       </c>
@@ -7322,7 +7354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>15</v>
       </c>
@@ -7333,7 +7365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>15</v>
       </c>
@@ -7344,7 +7376,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>15</v>
       </c>
@@ -7355,7 +7387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>15</v>
       </c>
@@ -7366,7 +7398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>15</v>
       </c>
@@ -7377,7 +7409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>15</v>
       </c>
@@ -7388,7 +7420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>15</v>
       </c>
@@ -7399,7 +7431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>15</v>
       </c>
@@ -7410,7 +7442,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>15</v>
       </c>
@@ -7421,7 +7453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>15</v>
       </c>
@@ -7432,7 +7464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>15</v>
       </c>
@@ -7443,7 +7475,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>15</v>
       </c>
@@ -7454,7 +7486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>15</v>
       </c>
@@ -7465,7 +7497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>15</v>
       </c>
@@ -7476,7 +7508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>15</v>
       </c>
@@ -7487,7 +7519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>15</v>
       </c>
@@ -7498,7 +7530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>15</v>
       </c>
@@ -7509,7 +7541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>15</v>
       </c>
@@ -7520,7 +7552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>15</v>
       </c>
@@ -7531,7 +7563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>15</v>
       </c>
@@ -7542,7 +7574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>15</v>
       </c>
@@ -7553,7 +7585,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>15</v>
       </c>
@@ -7564,7 +7596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>15</v>
       </c>
@@ -7575,7 +7607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>15</v>
       </c>
@@ -7586,7 +7618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>15</v>
       </c>
@@ -7597,7 +7629,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>15</v>
       </c>
@@ -7608,7 +7640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>15</v>
       </c>
@@ -7619,7 +7651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>15</v>
       </c>
@@ -7630,7 +7662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>15</v>
       </c>
@@ -7641,7 +7673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>15</v>
       </c>
@@ -7701,10 +7733,10 @@
         <v>16</v>
       </c>
       <c r="B191" t="s">
-        <v>195</v>
+        <v>117</v>
       </c>
       <c r="C191">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -7712,10 +7744,10 @@
         <v>16</v>
       </c>
       <c r="B192" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C192">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -7723,7 +7755,7 @@
         <v>16</v>
       </c>
       <c r="B193" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C193">
         <v>12</v>
@@ -7734,7 +7766,7 @@
         <v>16</v>
       </c>
       <c r="B194" t="s">
-        <v>65</v>
+        <v>194</v>
       </c>
       <c r="C194">
         <v>12</v>
@@ -7745,7 +7777,7 @@
         <v>16</v>
       </c>
       <c r="B195" t="s">
-        <v>117</v>
+        <v>50</v>
       </c>
       <c r="C195">
         <v>12</v>
@@ -7784,29 +7816,29 @@
         <v>10</v>
       </c>
     </row>
-    <row r="199" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>16</v>
       </c>
       <c r="B199" t="s">
-        <v>72</v>
+        <v>196</v>
       </c>
       <c r="C199">
         <v>9</v>
       </c>
     </row>
-    <row r="200" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>16</v>
       </c>
       <c r="B200" t="s">
-        <v>196</v>
+        <v>72</v>
       </c>
       <c r="C200">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="201" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>16</v>
       </c>
@@ -7817,7 +7849,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="202" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>16</v>
       </c>
@@ -7828,7 +7860,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="203" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>16</v>
       </c>
@@ -7839,7 +7871,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="204" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>16</v>
       </c>
@@ -7850,7 +7882,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="205" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>16</v>
       </c>
@@ -7861,7 +7893,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="206" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>16</v>
       </c>
@@ -7872,7 +7904,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="207" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>16</v>
       </c>
@@ -7883,7 +7915,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="208" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>16</v>
       </c>
@@ -7894,7 +7926,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="209" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>16</v>
       </c>
@@ -7905,7 +7937,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="210" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>16</v>
       </c>
@@ -7916,7 +7948,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="211" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>16</v>
       </c>
@@ -7927,7 +7959,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="212" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>16</v>
       </c>
@@ -7938,7 +7970,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="213" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>16</v>
       </c>
@@ -7949,7 +7981,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="214" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>16</v>
       </c>
@@ -7960,7 +7992,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="215" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>16</v>
       </c>
@@ -7971,7 +8003,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="216" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>16</v>
       </c>
@@ -7982,7 +8014,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="217" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>16</v>
       </c>
@@ -7993,7 +8025,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="218" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>16</v>
       </c>
@@ -8004,7 +8036,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="219" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>16</v>
       </c>
@@ -8015,7 +8047,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="220" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>16</v>
       </c>
@@ -8026,7 +8058,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="221" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>16</v>
       </c>
@@ -8037,7 +8069,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="222" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>16</v>
       </c>
@@ -8048,7 +8080,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="223" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>16</v>
       </c>
@@ -8059,7 +8091,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="224" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>16</v>
       </c>
@@ -8070,7 +8102,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="225" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>16</v>
       </c>
@@ -8081,7 +8113,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="226" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>16</v>
       </c>
@@ -8092,7 +8124,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="227" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>16</v>
       </c>
@@ -8103,7 +8135,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="228" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>16</v>
       </c>
@@ -8114,7 +8146,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="229" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>16</v>
       </c>
@@ -8125,7 +8157,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="230" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>16</v>
       </c>
@@ -8136,7 +8168,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="231" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>16</v>
       </c>
@@ -8147,7 +8179,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="232" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>16</v>
       </c>
@@ -8158,7 +8190,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="233" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>16</v>
       </c>
@@ -8169,7 +8201,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>16</v>
       </c>
@@ -8180,7 +8212,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>16</v>
       </c>
@@ -8191,7 +8223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>16</v>
       </c>
@@ -8202,7 +8234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="237" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>16</v>
       </c>
@@ -8213,7 +8245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>16</v>
       </c>
@@ -8224,7 +8256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>16</v>
       </c>
@@ -8235,7 +8267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>16</v>
       </c>
@@ -8246,7 +8278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>16</v>
       </c>
@@ -8257,7 +8289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>16</v>
       </c>
@@ -8268,7 +8300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>16</v>
       </c>
@@ -8279,7 +8311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>16</v>
       </c>
@@ -8290,7 +8322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>16</v>
       </c>
@@ -8301,7 +8333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>16</v>
       </c>
@@ -8312,7 +8344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>16</v>
       </c>
@@ -8323,7 +8355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>16</v>
       </c>
@@ -8334,7 +8366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>16</v>
       </c>
@@ -8345,7 +8377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>16</v>
       </c>
@@ -8356,7 +8388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>16</v>
       </c>
@@ -8367,7 +8399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>16</v>
       </c>
@@ -8378,7 +8410,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>16</v>
       </c>
@@ -8389,7 +8421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>16</v>
       </c>
@@ -8400,7 +8432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>16</v>
       </c>
@@ -8411,7 +8443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>16</v>
       </c>
@@ -8422,7 +8454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>16</v>
       </c>
@@ -8433,7 +8465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>16</v>
       </c>
@@ -8444,7 +8476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>16</v>
       </c>
@@ -8455,7 +8487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>16</v>
       </c>
@@ -8466,7 +8498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>16</v>
       </c>
@@ -8477,7 +8509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>16</v>
       </c>
@@ -8488,7 +8520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>16</v>
       </c>
@@ -8499,7 +8531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>16</v>
       </c>
@@ -8510,7 +8542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>16</v>
       </c>
@@ -8521,7 +8553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>16</v>
       </c>
@@ -8532,7 +8564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>16</v>
       </c>
@@ -8543,7 +8575,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>16</v>
       </c>
@@ -8554,7 +8586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>16</v>
       </c>
@@ -8565,7 +8597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>16</v>
       </c>
@@ -8576,7 +8608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>16</v>
       </c>
@@ -8587,7 +8619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>16</v>
       </c>
@@ -8598,7 +8630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>16</v>
       </c>
@@ -8609,7 +8641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="274" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>16</v>
       </c>
@@ -8620,7 +8652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>16</v>
       </c>
@@ -8631,7 +8663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>16</v>
       </c>
@@ -8642,7 +8674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>16</v>
       </c>
@@ -8686,7 +8718,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="281" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>21</v>
       </c>
@@ -8697,7 +8729,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="282" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>21</v>
       </c>
@@ -8708,7 +8740,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="283" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>21</v>
       </c>
@@ -8719,7 +8751,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="284" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>21</v>
       </c>
@@ -8730,18 +8762,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="285" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>21</v>
       </c>
       <c r="B285" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C285">
         <v>5</v>
       </c>
     </row>
-    <row r="286" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>21</v>
       </c>
@@ -8752,40 +8784,40 @@
         <v>5</v>
       </c>
     </row>
-    <row r="287" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>21</v>
       </c>
       <c r="B287" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C287">
         <v>5</v>
       </c>
     </row>
-    <row r="288" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>21</v>
       </c>
       <c r="B288" t="s">
+        <v>248</v>
+      </c>
+      <c r="C288">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>21</v>
+      </c>
+      <c r="B289" t="s">
         <v>129</v>
-      </c>
-      <c r="C288">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="289" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A289" t="s">
-        <v>21</v>
-      </c>
-      <c r="B289" t="s">
-        <v>249</v>
       </c>
       <c r="C289">
         <v>4</v>
       </c>
     </row>
-    <row r="290" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>21</v>
       </c>
@@ -8796,7 +8828,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="291" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>21</v>
       </c>
@@ -8807,7 +8839,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="292" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>21</v>
       </c>
@@ -8818,7 +8850,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="293" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>21</v>
       </c>
@@ -8829,7 +8861,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="294" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>21</v>
       </c>
@@ -8840,18 +8872,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="295" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>21</v>
       </c>
       <c r="B295" t="s">
-        <v>252</v>
+        <v>44</v>
       </c>
       <c r="C295">
         <v>3</v>
       </c>
     </row>
-    <row r="296" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>21</v>
       </c>
@@ -8862,7 +8894,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="297" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>21</v>
       </c>
@@ -8873,7 +8905,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="298" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>21</v>
       </c>
@@ -8884,7 +8916,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="299" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>21</v>
       </c>
@@ -8895,7 +8927,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="300" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>21</v>
       </c>
@@ -8906,183 +8938,183 @@
         <v>3</v>
       </c>
     </row>
-    <row r="301" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>21</v>
       </c>
       <c r="B301" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="C301">
         <v>3</v>
       </c>
     </row>
-    <row r="302" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>21</v>
       </c>
       <c r="B302" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="C302">
         <v>3</v>
       </c>
     </row>
-    <row r="303" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>21</v>
       </c>
       <c r="B303" t="s">
-        <v>127</v>
+        <v>252</v>
       </c>
       <c r="C303">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="304" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>21</v>
       </c>
       <c r="B304" t="s">
+        <v>259</v>
+      </c>
+      <c r="C304">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>21</v>
+      </c>
+      <c r="B305" t="s">
+        <v>172</v>
+      </c>
+      <c r="C305">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>21</v>
+      </c>
+      <c r="B306" t="s">
+        <v>85</v>
+      </c>
+      <c r="C306">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>21</v>
+      </c>
+      <c r="B307" t="s">
+        <v>199</v>
+      </c>
+      <c r="C307">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>21</v>
+      </c>
+      <c r="B308" t="s">
+        <v>174</v>
+      </c>
+      <c r="C308">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>21</v>
+      </c>
+      <c r="B309" t="s">
         <v>54</v>
       </c>
-      <c r="C304">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="305" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A305" t="s">
-        <v>21</v>
-      </c>
-      <c r="B305" t="s">
+      <c r="C309">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>21</v>
+      </c>
+      <c r="B310" t="s">
+        <v>200</v>
+      </c>
+      <c r="C310">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>21</v>
+      </c>
+      <c r="B311" t="s">
+        <v>273</v>
+      </c>
+      <c r="C311">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>21</v>
+      </c>
+      <c r="B312" t="s">
+        <v>77</v>
+      </c>
+      <c r="C312">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>21</v>
+      </c>
+      <c r="B313" t="s">
         <v>257</v>
       </c>
-      <c r="C305">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="306" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A306" t="s">
-        <v>21</v>
-      </c>
-      <c r="B306" t="s">
-        <v>273</v>
-      </c>
-      <c r="C306">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="307" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A307" t="s">
-        <v>21</v>
-      </c>
-      <c r="B307" t="s">
-        <v>174</v>
-      </c>
-      <c r="C307">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="308" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A308" t="s">
-        <v>21</v>
-      </c>
-      <c r="B308" t="s">
-        <v>85</v>
-      </c>
-      <c r="C308">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="309" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A309" t="s">
-        <v>21</v>
-      </c>
-      <c r="B309" t="s">
-        <v>200</v>
-      </c>
-      <c r="C309">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="310" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A310" t="s">
-        <v>21</v>
-      </c>
-      <c r="B310" t="s">
-        <v>172</v>
-      </c>
-      <c r="C310">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="311" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A311" t="s">
-        <v>21</v>
-      </c>
-      <c r="B311" t="s">
-        <v>77</v>
-      </c>
-      <c r="C311">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="312" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A312" t="s">
-        <v>21</v>
-      </c>
-      <c r="B312" t="s">
+      <c r="C313">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>21</v>
+      </c>
+      <c r="B314" t="s">
+        <v>258</v>
+      </c>
+      <c r="C314">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>21</v>
+      </c>
+      <c r="B315" t="s">
         <v>256</v>
       </c>
-      <c r="C312">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="313" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A313" t="s">
-        <v>21</v>
-      </c>
-      <c r="B313" t="s">
-        <v>258</v>
-      </c>
-      <c r="C313">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="314" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A314" t="s">
-        <v>21</v>
-      </c>
-      <c r="B314" t="s">
-        <v>199</v>
-      </c>
-      <c r="C314">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="315" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A315" t="s">
-        <v>21</v>
-      </c>
-      <c r="B315" t="s">
+      <c r="C315">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>21</v>
+      </c>
+      <c r="B316" t="s">
         <v>226</v>
       </c>
-      <c r="C315">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="316" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A316" t="s">
-        <v>21</v>
-      </c>
-      <c r="B316" t="s">
-        <v>259</v>
-      </c>
       <c r="C316">
         <v>2</v>
       </c>
     </row>
-    <row r="317" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>21</v>
       </c>
@@ -9093,7 +9125,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="318" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>21</v>
       </c>
@@ -9104,7 +9136,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="319" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>21</v>
       </c>
@@ -9115,7 +9147,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="320" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>21</v>
       </c>
@@ -9126,7 +9158,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="321" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>21</v>
       </c>
@@ -9137,7 +9169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>21</v>
       </c>
@@ -9148,7 +9180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="323" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>21</v>
       </c>
@@ -9159,7 +9191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>21</v>
       </c>
@@ -9170,7 +9202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>21</v>
       </c>
@@ -9181,7 +9213,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>21</v>
       </c>
@@ -9192,7 +9224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>21</v>
       </c>
@@ -9203,7 +9235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="328" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>21</v>
       </c>
@@ -9214,7 +9246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>21</v>
       </c>
@@ -9225,7 +9257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>21</v>
       </c>
@@ -9236,7 +9268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="331" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>21</v>
       </c>
@@ -9247,7 +9279,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="332" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>21</v>
       </c>
@@ -9258,7 +9290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>21</v>
       </c>
@@ -9269,7 +9301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="334" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>21</v>
       </c>
@@ -9280,7 +9312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="335" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>21</v>
       </c>
@@ -9291,7 +9323,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="336" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>21</v>
       </c>
@@ -9302,7 +9334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="337" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>21</v>
       </c>
@@ -9313,7 +9345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="338" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>21</v>
       </c>
@@ -9324,7 +9356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="339" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>21</v>
       </c>
@@ -9335,7 +9367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="340" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>21</v>
       </c>
@@ -9346,7 +9378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="341" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>21</v>
       </c>
@@ -9357,7 +9389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="342" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>21</v>
       </c>
@@ -9368,7 +9400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="343" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>21</v>
       </c>
@@ -9379,7 +9411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="344" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>21</v>
       </c>
@@ -9390,7 +9422,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="345" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>21</v>
       </c>
@@ -9401,7 +9433,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="346" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>21</v>
       </c>
@@ -9412,7 +9444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="347" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>21</v>
       </c>
@@ -9423,7 +9455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="348" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>21</v>
       </c>
@@ -9434,7 +9466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="349" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>21</v>
       </c>
@@ -9445,7 +9477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="350" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>21</v>
       </c>
@@ -9456,7 +9488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="351" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>21</v>
       </c>
@@ -9467,7 +9499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="352" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>21</v>
       </c>
@@ -9478,7 +9510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="353" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>21</v>
       </c>
@@ -9489,7 +9521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="354" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>21</v>
       </c>
@@ -9500,7 +9532,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="355" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>21</v>
       </c>
@@ -9511,7 +9543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="356" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>21</v>
       </c>
@@ -9522,7 +9554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="357" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>21</v>
       </c>
@@ -9534,22 +9566,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C357" xr:uid="{0916EAC6-1E7F-4924-9D0E-33749FD3E143}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="10"/>
-        <filter val="11"/>
-        <filter val="12"/>
-        <filter val="13"/>
-        <filter val="14"/>
-        <filter val="15"/>
-        <filter val="16"/>
-        <filter val="22"/>
-        <filter val="28"/>
-        <filter val="39"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="87" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{703055C9-2199-4AB3-91CC-C80D5686EFF6}"/>
+  <xr:revisionPtr revIDLastSave="93" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C1F3DBA-D00E-4EA1-AAF3-82982472E9B2}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="5" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="667" firstSheet="1" activeTab="6" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="mat_2026" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="mat_time" sheetId="4" r:id="rId4"/>
     <sheet name="origen_estudiantes" sheetId="5" r:id="rId5"/>
     <sheet name="origen_colegios" sheetId="6" r:id="rId6"/>
+    <sheet name="com_est" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">mat_2026!$A$1:$E$39</definedName>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="301">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -903,6 +904,51 @@
   </si>
   <si>
     <t>PROCEDENCIA</t>
+  </si>
+  <si>
+    <t>Comuna</t>
+  </si>
+  <si>
+    <t>Estudiantes</t>
+  </si>
+  <si>
+    <t>Calle Larga</t>
+  </si>
+  <si>
+    <t>Los Andes</t>
+  </si>
+  <si>
+    <t>San Esteban</t>
+  </si>
+  <si>
+    <t>Rinconada</t>
+  </si>
+  <si>
+    <t>San Felipe</t>
+  </si>
+  <si>
+    <t>Santa Maria</t>
+  </si>
+  <si>
+    <t>Santiago</t>
+  </si>
+  <si>
+    <t>Catemu</t>
+  </si>
+  <si>
+    <t>Putaendo</t>
+  </si>
+  <si>
+    <t>Panquehue</t>
+  </si>
+  <si>
+    <t>Llay Llay</t>
+  </si>
+  <si>
+    <t>Tiltil</t>
+  </si>
+  <si>
+    <t>Colina</t>
   </si>
 </sst>
 </file>
@@ -9568,4 +9614,490 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23700CF0-069F-497B-B50D-FB3ED3120196}">
+  <dimension ref="A1:C43"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" t="s">
+        <v>286</v>
+      </c>
+      <c r="C1" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C3">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C4">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>291</v>
+      </c>
+      <c r="C5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>292</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>293</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>294</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>288</v>
+      </c>
+      <c r="C9">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>289</v>
+      </c>
+      <c r="C10">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>291</v>
+      </c>
+      <c r="C11">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>290</v>
+      </c>
+      <c r="C12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>292</v>
+      </c>
+      <c r="C13">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>292</v>
+      </c>
+      <c r="C14">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>295</v>
+      </c>
+      <c r="C15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>289</v>
+      </c>
+      <c r="C16">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>296</v>
+      </c>
+      <c r="C17">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>293</v>
+      </c>
+      <c r="C18">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>297</v>
+      </c>
+      <c r="C19">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>290</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>298</v>
+      </c>
+      <c r="C21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>291</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>288</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" t="s">
+        <v>292</v>
+      </c>
+      <c r="C24">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" t="s">
+        <v>289</v>
+      </c>
+      <c r="C25">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" t="s">
+        <v>299</v>
+      </c>
+      <c r="C26">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" t="s">
+        <v>288</v>
+      </c>
+      <c r="C27">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" t="s">
+        <v>290</v>
+      </c>
+      <c r="C28">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" t="s">
+        <v>291</v>
+      </c>
+      <c r="C29">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" t="s">
+        <v>300</v>
+      </c>
+      <c r="C30">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31" t="s">
+        <v>296</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" t="s">
+        <v>293</v>
+      </c>
+      <c r="C32">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33" t="s">
+        <v>297</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>21</v>
+      </c>
+      <c r="B34" t="s">
+        <v>292</v>
+      </c>
+      <c r="C34">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>21</v>
+      </c>
+      <c r="B35" t="s">
+        <v>290</v>
+      </c>
+      <c r="C35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>21</v>
+      </c>
+      <c r="B36" t="s">
+        <v>297</v>
+      </c>
+      <c r="C36">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" t="s">
+        <v>296</v>
+      </c>
+      <c r="C37">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>21</v>
+      </c>
+      <c r="B38" t="s">
+        <v>298</v>
+      </c>
+      <c r="C38">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" t="s">
+        <v>293</v>
+      </c>
+      <c r="C39">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>21</v>
+      </c>
+      <c r="B40" t="s">
+        <v>288</v>
+      </c>
+      <c r="C40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>21</v>
+      </c>
+      <c r="B41" t="s">
+        <v>295</v>
+      </c>
+      <c r="C41">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>21</v>
+      </c>
+      <c r="B42" t="s">
+        <v>289</v>
+      </c>
+      <c r="C42">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>21</v>
+      </c>
+      <c r="B43" t="s">
+        <v>291</v>
+      </c>
+      <c r="C43">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="93" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C1F3DBA-D00E-4EA1-AAF3-82982472E9B2}"/>
+  <xr:revisionPtr revIDLastSave="95" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47CC1CAC-893F-4D6D-A8F8-3C8786FE9C3F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="667" firstSheet="1" activeTab="6" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" tabRatio="667" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="mat_2026" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1239" uniqueCount="300">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -928,9 +928,6 @@
   </si>
   <si>
     <t>Santa Maria</t>
-  </si>
-  <si>
-    <t>Santiago</t>
   </si>
   <si>
     <t>Catemu</t>
@@ -2376,7 +2373,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD19485A-0629-47F9-A5AD-80ABA7A6E076}">
-  <dimension ref="A1:C237"/>
+  <dimension ref="A1:C238"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -2414,7 +2411,7 @@
         <v>46008</v>
       </c>
       <c r="C3" s="9">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2587,10 +2584,10 @@
         <v>16</v>
       </c>
       <c r="B19" s="8">
-        <v>46097</v>
+        <v>46162</v>
       </c>
       <c r="C19" s="9">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -2598,10 +2595,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="5">
-        <v>46021</v>
+        <v>46097</v>
       </c>
       <c r="C20" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -2609,10 +2606,10 @@
         <v>16</v>
       </c>
       <c r="B21" s="8">
-        <v>46080</v>
+        <v>46021</v>
       </c>
       <c r="C21" s="9">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -2620,10 +2617,10 @@
         <v>16</v>
       </c>
       <c r="B22" s="5">
-        <v>46087</v>
+        <v>46080</v>
       </c>
       <c r="C22" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -2631,10 +2628,10 @@
         <v>16</v>
       </c>
       <c r="B23" s="8">
-        <v>46022</v>
+        <v>46087</v>
       </c>
       <c r="C23" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -2642,10 +2639,10 @@
         <v>16</v>
       </c>
       <c r="B24" s="5">
-        <v>46161</v>
+        <v>46022</v>
       </c>
       <c r="C24" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -2653,10 +2650,10 @@
         <v>16</v>
       </c>
       <c r="B25" s="8">
-        <v>46086</v>
+        <v>46161</v>
       </c>
       <c r="C25" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -2664,10 +2661,10 @@
         <v>16</v>
       </c>
       <c r="B26" s="5">
-        <v>46076</v>
+        <v>46086</v>
       </c>
       <c r="C26" s="6">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -2675,10 +2672,10 @@
         <v>16</v>
       </c>
       <c r="B27" s="8">
-        <v>46136</v>
+        <v>46076</v>
       </c>
       <c r="C27" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -2686,10 +2683,10 @@
         <v>16</v>
       </c>
       <c r="B28" s="5">
-        <v>46078</v>
+        <v>46136</v>
       </c>
       <c r="C28" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -2697,7 +2694,7 @@
         <v>16</v>
       </c>
       <c r="B29" s="8">
-        <v>46098</v>
+        <v>46078</v>
       </c>
       <c r="C29" s="9">
         <v>3</v>
@@ -2708,10 +2705,10 @@
         <v>16</v>
       </c>
       <c r="B30" s="5">
-        <v>46084</v>
+        <v>46098</v>
       </c>
       <c r="C30" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -2719,10 +2716,10 @@
         <v>16</v>
       </c>
       <c r="B31" s="8">
-        <v>46160</v>
+        <v>46084</v>
       </c>
       <c r="C31" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -2730,7 +2727,7 @@
         <v>16</v>
       </c>
       <c r="B32" s="5">
-        <v>46099</v>
+        <v>46160</v>
       </c>
       <c r="C32" s="6">
         <v>3</v>
@@ -2741,10 +2738,10 @@
         <v>16</v>
       </c>
       <c r="B33" s="8">
-        <v>46128</v>
+        <v>46099</v>
       </c>
       <c r="C33" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -2752,10 +2749,10 @@
         <v>16</v>
       </c>
       <c r="B34" s="5">
-        <v>46141</v>
+        <v>46128</v>
       </c>
       <c r="C34" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -2763,10 +2760,10 @@
         <v>16</v>
       </c>
       <c r="B35" s="8">
-        <v>46132</v>
+        <v>46141</v>
       </c>
       <c r="C35" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -2774,10 +2771,10 @@
         <v>16</v>
       </c>
       <c r="B36" s="5">
-        <v>46127</v>
+        <v>46132</v>
       </c>
       <c r="C36" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -2785,7 +2782,7 @@
         <v>16</v>
       </c>
       <c r="B37" s="8">
-        <v>46091</v>
+        <v>46127</v>
       </c>
       <c r="C37" s="9">
         <v>2</v>
@@ -2796,10 +2793,10 @@
         <v>16</v>
       </c>
       <c r="B38" s="5">
-        <v>46104</v>
+        <v>46091</v>
       </c>
       <c r="C38" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -2807,7 +2804,7 @@
         <v>16</v>
       </c>
       <c r="B39" s="8">
-        <v>46140</v>
+        <v>46104</v>
       </c>
       <c r="C39" s="9">
         <v>1</v>
@@ -2818,7 +2815,7 @@
         <v>16</v>
       </c>
       <c r="B40" s="5">
-        <v>46106</v>
+        <v>46140</v>
       </c>
       <c r="C40" s="6">
         <v>1</v>
@@ -2829,10 +2826,10 @@
         <v>16</v>
       </c>
       <c r="B41" s="8">
-        <v>46113</v>
+        <v>46106</v>
       </c>
       <c r="C41" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -2840,10 +2837,10 @@
         <v>16</v>
       </c>
       <c r="B42" s="5">
-        <v>46090</v>
+        <v>46113</v>
       </c>
       <c r="C42" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -2851,10 +2848,10 @@
         <v>16</v>
       </c>
       <c r="B43" s="8">
-        <v>46148</v>
+        <v>46090</v>
       </c>
       <c r="C43" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -2862,10 +2859,10 @@
         <v>16</v>
       </c>
       <c r="B44" s="5">
-        <v>46139</v>
+        <v>46148</v>
       </c>
       <c r="C44" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -2873,7 +2870,7 @@
         <v>16</v>
       </c>
       <c r="B45" s="8">
-        <v>46125</v>
+        <v>46139</v>
       </c>
       <c r="C45" s="9">
         <v>1</v>
@@ -2884,7 +2881,7 @@
         <v>16</v>
       </c>
       <c r="B46" s="5">
-        <v>46093</v>
+        <v>46125</v>
       </c>
       <c r="C46" s="6">
         <v>1</v>
@@ -2895,7 +2892,7 @@
         <v>16</v>
       </c>
       <c r="B47" s="8">
-        <v>46156</v>
+        <v>46093</v>
       </c>
       <c r="C47" s="9">
         <v>1</v>
@@ -2906,7 +2903,7 @@
         <v>16</v>
       </c>
       <c r="B48" s="5">
-        <v>46092</v>
+        <v>46156</v>
       </c>
       <c r="C48" s="6">
         <v>1</v>
@@ -2917,7 +2914,7 @@
         <v>16</v>
       </c>
       <c r="B49" s="8">
-        <v>46101</v>
+        <v>46092</v>
       </c>
       <c r="C49" s="9">
         <v>1</v>
@@ -2925,13 +2922,13 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B50" s="5">
-        <v>46007</v>
+        <v>46101</v>
       </c>
       <c r="C50" s="6">
-        <v>79</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -2939,10 +2936,10 @@
         <v>14</v>
       </c>
       <c r="B51" s="8">
-        <v>46009</v>
+        <v>46007</v>
       </c>
       <c r="C51" s="9">
-        <v>34</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -2950,10 +2947,10 @@
         <v>14</v>
       </c>
       <c r="B52" s="5">
-        <v>46000</v>
+        <v>46009</v>
       </c>
       <c r="C52" s="6">
-        <v>82</v>
+        <v>34</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -2961,10 +2958,10 @@
         <v>14</v>
       </c>
       <c r="B53" s="8">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C53" s="9">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -2972,10 +2969,10 @@
         <v>14</v>
       </c>
       <c r="B54" s="5">
-        <v>46006</v>
+        <v>46001</v>
       </c>
       <c r="C54" s="6">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -2983,10 +2980,10 @@
         <v>14</v>
       </c>
       <c r="B55" s="8">
-        <v>46010</v>
+        <v>46006</v>
       </c>
       <c r="C55" s="9">
-        <v>24</v>
+        <v>79</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -2994,10 +2991,10 @@
         <v>14</v>
       </c>
       <c r="B56" s="5">
-        <v>46014</v>
+        <v>46010</v>
       </c>
       <c r="C56" s="6">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -3005,10 +3002,10 @@
         <v>14</v>
       </c>
       <c r="B57" s="8">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="C57" s="9">
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -3016,10 +3013,10 @@
         <v>14</v>
       </c>
       <c r="B58" s="5">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C58" s="6">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -3027,10 +3024,10 @@
         <v>14</v>
       </c>
       <c r="B59" s="8">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="C59" s="9">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -3038,10 +3035,10 @@
         <v>14</v>
       </c>
       <c r="B60" s="5">
-        <v>46013</v>
+        <v>46003</v>
       </c>
       <c r="C60" s="6">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -3049,10 +3046,10 @@
         <v>14</v>
       </c>
       <c r="B61" s="8">
-        <v>46022</v>
+        <v>46013</v>
       </c>
       <c r="C61" s="9">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -3060,10 +3057,10 @@
         <v>14</v>
       </c>
       <c r="B62" s="5">
-        <v>46080</v>
+        <v>46022</v>
       </c>
       <c r="C62" s="6">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -3071,10 +3068,10 @@
         <v>14</v>
       </c>
       <c r="B63" s="8">
-        <v>46084</v>
+        <v>46080</v>
       </c>
       <c r="C63" s="9">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -3082,10 +3079,10 @@
         <v>14</v>
       </c>
       <c r="B64" s="5">
-        <v>46125</v>
+        <v>46084</v>
       </c>
       <c r="C64" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -3093,10 +3090,10 @@
         <v>14</v>
       </c>
       <c r="B65" s="8">
-        <v>46091</v>
+        <v>46125</v>
       </c>
       <c r="C65" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -3104,10 +3101,10 @@
         <v>14</v>
       </c>
       <c r="B66" s="5">
-        <v>46083</v>
+        <v>46091</v>
       </c>
       <c r="C66" s="6">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -3115,10 +3112,10 @@
         <v>14</v>
       </c>
       <c r="B67" s="8">
-        <v>46105</v>
+        <v>46083</v>
       </c>
       <c r="C67" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -3126,10 +3123,10 @@
         <v>14</v>
       </c>
       <c r="B68" s="5">
-        <v>46077</v>
+        <v>46105</v>
       </c>
       <c r="C68" s="6">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -3137,10 +3134,10 @@
         <v>14</v>
       </c>
       <c r="B69" s="8">
-        <v>46118</v>
+        <v>46077</v>
       </c>
       <c r="C69" s="9">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -3148,10 +3145,10 @@
         <v>14</v>
       </c>
       <c r="B70" s="5">
-        <v>46078</v>
+        <v>46118</v>
       </c>
       <c r="C70" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -3159,10 +3156,10 @@
         <v>14</v>
       </c>
       <c r="B71" s="8">
-        <v>46099</v>
+        <v>46078</v>
       </c>
       <c r="C71" s="9">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -3170,10 +3167,10 @@
         <v>14</v>
       </c>
       <c r="B72" s="5">
-        <v>46104</v>
+        <v>46099</v>
       </c>
       <c r="C72" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -3181,10 +3178,10 @@
         <v>14</v>
       </c>
       <c r="B73" s="8">
-        <v>46107</v>
+        <v>46104</v>
       </c>
       <c r="C73" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -3192,7 +3189,7 @@
         <v>14</v>
       </c>
       <c r="B74" s="5">
-        <v>46020</v>
+        <v>46107</v>
       </c>
       <c r="C74" s="6">
         <v>2</v>
@@ -3203,10 +3200,10 @@
         <v>14</v>
       </c>
       <c r="B75" s="8">
-        <v>46076</v>
+        <v>46020</v>
       </c>
       <c r="C75" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -3214,10 +3211,10 @@
         <v>14</v>
       </c>
       <c r="B76" s="5">
-        <v>46111</v>
+        <v>46076</v>
       </c>
       <c r="C76" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -3225,10 +3222,10 @@
         <v>14</v>
       </c>
       <c r="B77" s="8">
-        <v>46087</v>
+        <v>46111</v>
       </c>
       <c r="C77" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -3236,7 +3233,7 @@
         <v>14</v>
       </c>
       <c r="B78" s="5">
-        <v>46140</v>
+        <v>46087</v>
       </c>
       <c r="C78" s="6">
         <v>2</v>
@@ -3247,10 +3244,10 @@
         <v>14</v>
       </c>
       <c r="B79" s="8">
-        <v>46113</v>
+        <v>46140</v>
       </c>
       <c r="C79" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -3258,10 +3255,10 @@
         <v>14</v>
       </c>
       <c r="B80" s="5">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="C80" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -3269,10 +3266,10 @@
         <v>14</v>
       </c>
       <c r="B81" s="8">
-        <v>46108</v>
+        <v>46119</v>
       </c>
       <c r="C81" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -3280,7 +3277,7 @@
         <v>14</v>
       </c>
       <c r="B82" s="5">
-        <v>46098</v>
+        <v>46108</v>
       </c>
       <c r="C82" s="6">
         <v>1</v>
@@ -3291,7 +3288,7 @@
         <v>14</v>
       </c>
       <c r="B83" s="8">
-        <v>46141</v>
+        <v>46098</v>
       </c>
       <c r="C83" s="9">
         <v>1</v>
@@ -3302,7 +3299,7 @@
         <v>14</v>
       </c>
       <c r="B84" s="5">
-        <v>46114</v>
+        <v>46141</v>
       </c>
       <c r="C84" s="6">
         <v>1</v>
@@ -3313,10 +3310,10 @@
         <v>14</v>
       </c>
       <c r="B85" s="8">
-        <v>46079</v>
+        <v>46114</v>
       </c>
       <c r="C85" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -3324,10 +3321,10 @@
         <v>14</v>
       </c>
       <c r="B86" s="5">
-        <v>46139</v>
+        <v>46079</v>
       </c>
       <c r="C86" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -3335,10 +3332,10 @@
         <v>14</v>
       </c>
       <c r="B87" s="8">
-        <v>46148</v>
+        <v>46139</v>
       </c>
       <c r="C87" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -3346,10 +3343,10 @@
         <v>14</v>
       </c>
       <c r="B88" s="5">
-        <v>46092</v>
+        <v>46148</v>
       </c>
       <c r="C88" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -3357,10 +3354,10 @@
         <v>14</v>
       </c>
       <c r="B89" s="8">
-        <v>46021</v>
+        <v>46092</v>
       </c>
       <c r="C89" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -3368,10 +3365,10 @@
         <v>14</v>
       </c>
       <c r="B90" s="5">
-        <v>46086</v>
+        <v>46021</v>
       </c>
       <c r="C90" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -3379,10 +3376,10 @@
         <v>14</v>
       </c>
       <c r="B91" s="8">
-        <v>46147</v>
+        <v>46086</v>
       </c>
       <c r="C91" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -3390,7 +3387,7 @@
         <v>14</v>
       </c>
       <c r="B92" s="5">
-        <v>46134</v>
+        <v>46147</v>
       </c>
       <c r="C92" s="6">
         <v>1</v>
@@ -3398,13 +3395,13 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B93" s="8">
-        <v>46003</v>
+        <v>46134</v>
       </c>
       <c r="C93" s="9">
-        <v>95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -3412,10 +3409,10 @@
         <v>3</v>
       </c>
       <c r="B94" s="5">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="C94" s="6">
-        <v>115</v>
+        <v>95</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -3423,10 +3420,10 @@
         <v>3</v>
       </c>
       <c r="B95" s="8">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C95" s="9">
-        <v>15</v>
+        <v>115</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -3434,10 +3431,10 @@
         <v>3</v>
       </c>
       <c r="B96" s="5">
-        <v>46000</v>
+        <v>46008</v>
       </c>
       <c r="C96" s="6">
-        <v>98</v>
+        <v>15</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -3445,10 +3442,10 @@
         <v>3</v>
       </c>
       <c r="B97" s="8">
-        <v>46007</v>
+        <v>46000</v>
       </c>
       <c r="C97" s="9">
-        <v>43</v>
+        <v>98</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -3456,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="B98" s="5">
-        <v>46001</v>
+        <v>46007</v>
       </c>
       <c r="C98" s="6">
-        <v>91</v>
+        <v>43</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -3467,10 +3464,10 @@
         <v>3</v>
       </c>
       <c r="B99" s="8">
-        <v>46010</v>
+        <v>46001</v>
       </c>
       <c r="C99" s="9">
-        <v>9</v>
+        <v>91</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -3478,10 +3475,10 @@
         <v>3</v>
       </c>
       <c r="B100" s="5">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="C100" s="6">
-        <v>84</v>
+        <v>9</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -3489,10 +3486,10 @@
         <v>3</v>
       </c>
       <c r="B101" s="8">
-        <v>46009</v>
+        <v>46006</v>
       </c>
       <c r="C101" s="9">
-        <v>2</v>
+        <v>84</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -3500,10 +3497,10 @@
         <v>3</v>
       </c>
       <c r="B102" s="5">
-        <v>46015</v>
+        <v>46009</v>
       </c>
       <c r="C102" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -3511,10 +3508,10 @@
         <v>3</v>
       </c>
       <c r="B103" s="8">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="C103" s="9">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -3522,10 +3519,10 @@
         <v>3</v>
       </c>
       <c r="B104" s="5">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="C104" s="6">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -3533,10 +3530,10 @@
         <v>3</v>
       </c>
       <c r="B105" s="8">
-        <v>46021</v>
+        <v>46013</v>
       </c>
       <c r="C105" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -3544,10 +3541,10 @@
         <v>3</v>
       </c>
       <c r="B106" s="5">
-        <v>46077</v>
+        <v>46021</v>
       </c>
       <c r="C106" s="6">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -3555,10 +3552,10 @@
         <v>3</v>
       </c>
       <c r="B107" s="8">
-        <v>46090</v>
+        <v>46077</v>
       </c>
       <c r="C107" s="9">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -3566,10 +3563,10 @@
         <v>3</v>
       </c>
       <c r="B108" s="5">
-        <v>46093</v>
+        <v>46090</v>
       </c>
       <c r="C108" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -3577,10 +3574,10 @@
         <v>3</v>
       </c>
       <c r="B109" s="8">
-        <v>46078</v>
+        <v>46093</v>
       </c>
       <c r="C109" s="9">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -3588,10 +3585,10 @@
         <v>3</v>
       </c>
       <c r="B110" s="5">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="C110" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -3599,10 +3596,10 @@
         <v>3</v>
       </c>
       <c r="B111" s="8">
-        <v>46134</v>
+        <v>46084</v>
       </c>
       <c r="C111" s="9">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -3610,10 +3607,10 @@
         <v>3</v>
       </c>
       <c r="B112" s="5">
-        <v>46083</v>
+        <v>46134</v>
       </c>
       <c r="C112" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -3621,10 +3618,10 @@
         <v>3</v>
       </c>
       <c r="B113" s="8">
-        <v>46022</v>
+        <v>46083</v>
       </c>
       <c r="C113" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -3632,10 +3629,10 @@
         <v>3</v>
       </c>
       <c r="B114" s="5">
-        <v>46114</v>
+        <v>46022</v>
       </c>
       <c r="C114" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -3643,10 +3640,10 @@
         <v>3</v>
       </c>
       <c r="B115" s="8">
-        <v>46135</v>
+        <v>46114</v>
       </c>
       <c r="C115" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -3654,10 +3651,10 @@
         <v>3</v>
       </c>
       <c r="B116" s="5">
-        <v>46126</v>
+        <v>46135</v>
       </c>
       <c r="C116" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -3665,7 +3662,7 @@
         <v>3</v>
       </c>
       <c r="B117" s="8">
-        <v>46120</v>
+        <v>46126</v>
       </c>
       <c r="C117" s="9">
         <v>3</v>
@@ -3676,10 +3673,10 @@
         <v>3</v>
       </c>
       <c r="B118" s="5">
-        <v>46127</v>
+        <v>46120</v>
       </c>
       <c r="C118" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -3687,7 +3684,7 @@
         <v>3</v>
       </c>
       <c r="B119" s="8">
-        <v>46087</v>
+        <v>46127</v>
       </c>
       <c r="C119" s="9">
         <v>1</v>
@@ -3698,7 +3695,7 @@
         <v>3</v>
       </c>
       <c r="B120" s="5">
-        <v>46108</v>
+        <v>46087</v>
       </c>
       <c r="C120" s="6">
         <v>1</v>
@@ -3709,7 +3706,7 @@
         <v>3</v>
       </c>
       <c r="B121" s="8">
-        <v>46020</v>
+        <v>46108</v>
       </c>
       <c r="C121" s="9">
         <v>1</v>
@@ -3720,7 +3717,7 @@
         <v>3</v>
       </c>
       <c r="B122" s="5">
-        <v>46097</v>
+        <v>46020</v>
       </c>
       <c r="C122" s="6">
         <v>1</v>
@@ -3731,10 +3728,10 @@
         <v>3</v>
       </c>
       <c r="B123" s="8">
-        <v>46161</v>
+        <v>46097</v>
       </c>
       <c r="C123" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -3742,10 +3739,10 @@
         <v>3</v>
       </c>
       <c r="B124" s="5">
-        <v>46129</v>
+        <v>46161</v>
       </c>
       <c r="C124" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -3753,7 +3750,7 @@
         <v>3</v>
       </c>
       <c r="B125" s="8">
-        <v>46080</v>
+        <v>46129</v>
       </c>
       <c r="C125" s="9">
         <v>1</v>
@@ -3764,7 +3761,7 @@
         <v>3</v>
       </c>
       <c r="B126" s="5">
-        <v>46101</v>
+        <v>46080</v>
       </c>
       <c r="C126" s="6">
         <v>1</v>
@@ -3775,7 +3772,7 @@
         <v>3</v>
       </c>
       <c r="B127" s="8">
-        <v>46155</v>
+        <v>46101</v>
       </c>
       <c r="C127" s="9">
         <v>1</v>
@@ -3786,7 +3783,7 @@
         <v>3</v>
       </c>
       <c r="B128" s="5">
-        <v>46150</v>
+        <v>46155</v>
       </c>
       <c r="C128" s="6">
         <v>1</v>
@@ -3797,7 +3794,7 @@
         <v>3</v>
       </c>
       <c r="B129" s="8">
-        <v>46141</v>
+        <v>46150</v>
       </c>
       <c r="C129" s="9">
         <v>1</v>
@@ -3808,7 +3805,7 @@
         <v>3</v>
       </c>
       <c r="B130" s="5">
-        <v>46085</v>
+        <v>46141</v>
       </c>
       <c r="C130" s="6">
         <v>1</v>
@@ -3819,7 +3816,7 @@
         <v>3</v>
       </c>
       <c r="B131" s="8">
-        <v>46148</v>
+        <v>46085</v>
       </c>
       <c r="C131" s="9">
         <v>1</v>
@@ -3830,10 +3827,10 @@
         <v>3</v>
       </c>
       <c r="B132" s="5">
-        <v>46118</v>
+        <v>46148</v>
       </c>
       <c r="C132" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -3841,21 +3838,21 @@
         <v>3</v>
       </c>
       <c r="B133" s="8">
-        <v>46079</v>
+        <v>46118</v>
       </c>
       <c r="C133" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B134" s="5">
-        <v>46003</v>
+        <v>46079</v>
       </c>
       <c r="C134" s="6">
-        <v>92</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -3863,10 +3860,10 @@
         <v>15</v>
       </c>
       <c r="B135" s="8">
-        <v>46000</v>
+        <v>46003</v>
       </c>
       <c r="C135" s="9">
-        <v>133</v>
+        <v>92</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -3874,10 +3871,10 @@
         <v>15</v>
       </c>
       <c r="B136" s="5">
-        <v>46006</v>
+        <v>46000</v>
       </c>
       <c r="C136" s="6">
-        <v>174</v>
+        <v>133</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -3885,7 +3882,7 @@
         <v>15</v>
       </c>
       <c r="B137" s="8">
-        <v>46001</v>
+        <v>46006</v>
       </c>
       <c r="C137" s="9">
         <v>174</v>
@@ -3896,10 +3893,10 @@
         <v>15</v>
       </c>
       <c r="B138" s="5">
-        <v>46014</v>
+        <v>46001</v>
       </c>
       <c r="C138" s="6">
-        <v>16</v>
+        <v>174</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -3907,10 +3904,10 @@
         <v>15</v>
       </c>
       <c r="B139" s="8">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="C139" s="9">
-        <v>171</v>
+        <v>16</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -3918,10 +3915,10 @@
         <v>15</v>
       </c>
       <c r="B140" s="5">
-        <v>46009</v>
+        <v>46002</v>
       </c>
       <c r="C140" s="6">
-        <v>20</v>
+        <v>171</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -3929,10 +3926,10 @@
         <v>15</v>
       </c>
       <c r="B141" s="8">
-        <v>46010</v>
+        <v>46009</v>
       </c>
       <c r="C141" s="9">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -3940,10 +3937,10 @@
         <v>15</v>
       </c>
       <c r="B142" s="5">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="C142" s="6">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -3951,10 +3948,10 @@
         <v>15</v>
       </c>
       <c r="B143" s="8">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="C143" s="9">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -3962,10 +3959,10 @@
         <v>15</v>
       </c>
       <c r="B144" s="5">
-        <v>46013</v>
+        <v>46007</v>
       </c>
       <c r="C144" s="6">
-        <v>12</v>
+        <v>43</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -3973,10 +3970,10 @@
         <v>15</v>
       </c>
       <c r="B145" s="8">
-        <v>46080</v>
+        <v>46013</v>
       </c>
       <c r="C145" s="9">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -3984,10 +3981,10 @@
         <v>15</v>
       </c>
       <c r="B146" s="5">
-        <v>46090</v>
+        <v>46080</v>
       </c>
       <c r="C146" s="6">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -3995,10 +3992,10 @@
         <v>15</v>
       </c>
       <c r="B147" s="8">
-        <v>46079</v>
+        <v>46090</v>
       </c>
       <c r="C147" s="9">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -4006,10 +4003,10 @@
         <v>15</v>
       </c>
       <c r="B148" s="5">
-        <v>46015</v>
+        <v>46079</v>
       </c>
       <c r="C148" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -4017,10 +4014,10 @@
         <v>15</v>
       </c>
       <c r="B149" s="8">
-        <v>46085</v>
+        <v>46015</v>
       </c>
       <c r="C149" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -4028,10 +4025,10 @@
         <v>15</v>
       </c>
       <c r="B150" s="5">
-        <v>46098</v>
+        <v>46085</v>
       </c>
       <c r="C150" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -4039,10 +4036,10 @@
         <v>15</v>
       </c>
       <c r="B151" s="8">
-        <v>46021</v>
+        <v>46098</v>
       </c>
       <c r="C151" s="9">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -4050,10 +4047,10 @@
         <v>15</v>
       </c>
       <c r="B152" s="5">
-        <v>46078</v>
+        <v>46021</v>
       </c>
       <c r="C152" s="6">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -4061,10 +4058,10 @@
         <v>15</v>
       </c>
       <c r="B153" s="8">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="C153" s="9">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -4072,10 +4069,10 @@
         <v>15</v>
       </c>
       <c r="B154" s="5">
-        <v>46128</v>
+        <v>46084</v>
       </c>
       <c r="C154" s="6">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -4083,10 +4080,10 @@
         <v>15</v>
       </c>
       <c r="B155" s="8">
-        <v>46083</v>
+        <v>46128</v>
       </c>
       <c r="C155" s="9">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -4094,10 +4091,10 @@
         <v>15</v>
       </c>
       <c r="B156" s="5">
-        <v>46153</v>
+        <v>46083</v>
       </c>
       <c r="C156" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -4105,10 +4102,10 @@
         <v>15</v>
       </c>
       <c r="B157" s="8">
-        <v>46076</v>
+        <v>46153</v>
       </c>
       <c r="C157" s="9">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -4116,10 +4113,10 @@
         <v>15</v>
       </c>
       <c r="B158" s="5">
-        <v>46099</v>
+        <v>46076</v>
       </c>
       <c r="C158" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -4127,10 +4124,10 @@
         <v>15</v>
       </c>
       <c r="B159" s="8">
-        <v>46154</v>
+        <v>46099</v>
       </c>
       <c r="C159" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -4138,7 +4135,7 @@
         <v>15</v>
       </c>
       <c r="B160" s="5">
-        <v>46092</v>
+        <v>46154</v>
       </c>
       <c r="C160" s="6">
         <v>1</v>
@@ -4149,10 +4146,10 @@
         <v>15</v>
       </c>
       <c r="B161" s="8">
-        <v>46031</v>
+        <v>46092</v>
       </c>
       <c r="C161" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -4160,7 +4157,7 @@
         <v>15</v>
       </c>
       <c r="B162" s="5">
-        <v>46120</v>
+        <v>46031</v>
       </c>
       <c r="C162" s="6">
         <v>2</v>
@@ -4171,10 +4168,10 @@
         <v>15</v>
       </c>
       <c r="B163" s="8">
-        <v>46077</v>
+        <v>46120</v>
       </c>
       <c r="C163" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -4182,10 +4179,10 @@
         <v>15</v>
       </c>
       <c r="B164" s="5">
-        <v>46114</v>
+        <v>46077</v>
       </c>
       <c r="C164" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -4193,7 +4190,7 @@
         <v>15</v>
       </c>
       <c r="B165" s="8">
-        <v>46037</v>
+        <v>46114</v>
       </c>
       <c r="C165" s="9">
         <v>1</v>
@@ -4204,10 +4201,10 @@
         <v>15</v>
       </c>
       <c r="B166" s="5">
-        <v>46020</v>
+        <v>46037</v>
       </c>
       <c r="C166" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -4215,10 +4212,10 @@
         <v>15</v>
       </c>
       <c r="B167" s="8">
-        <v>46106</v>
+        <v>46020</v>
       </c>
       <c r="C167" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -4226,7 +4223,7 @@
         <v>15</v>
       </c>
       <c r="B168" s="5">
-        <v>46155</v>
+        <v>46106</v>
       </c>
       <c r="C168" s="6">
         <v>1</v>
@@ -4237,7 +4234,7 @@
         <v>15</v>
       </c>
       <c r="B169" s="8">
-        <v>46112</v>
+        <v>46155</v>
       </c>
       <c r="C169" s="9">
         <v>1</v>
@@ -4248,7 +4245,7 @@
         <v>15</v>
       </c>
       <c r="B170" s="5">
-        <v>46132</v>
+        <v>46112</v>
       </c>
       <c r="C170" s="6">
         <v>1</v>
@@ -4259,7 +4256,7 @@
         <v>15</v>
       </c>
       <c r="B171" s="8">
-        <v>46108</v>
+        <v>46132</v>
       </c>
       <c r="C171" s="9">
         <v>1</v>
@@ -4270,7 +4267,7 @@
         <v>15</v>
       </c>
       <c r="B172" s="5">
-        <v>46148</v>
+        <v>46108</v>
       </c>
       <c r="C172" s="6">
         <v>1</v>
@@ -4281,7 +4278,7 @@
         <v>15</v>
       </c>
       <c r="B173" s="8">
-        <v>46118</v>
+        <v>46148</v>
       </c>
       <c r="C173" s="9">
         <v>1</v>
@@ -4292,7 +4289,7 @@
         <v>15</v>
       </c>
       <c r="B174" s="5">
-        <v>46035</v>
+        <v>46118</v>
       </c>
       <c r="C174" s="6">
         <v>1</v>
@@ -4303,7 +4300,7 @@
         <v>15</v>
       </c>
       <c r="B175" s="8">
-        <v>46093</v>
+        <v>46035</v>
       </c>
       <c r="C175" s="9">
         <v>1</v>
@@ -4314,7 +4311,7 @@
         <v>15</v>
       </c>
       <c r="B176" s="5">
-        <v>46022</v>
+        <v>46093</v>
       </c>
       <c r="C176" s="6">
         <v>1</v>
@@ -4325,7 +4322,7 @@
         <v>15</v>
       </c>
       <c r="B177" s="8">
-        <v>46087</v>
+        <v>46022</v>
       </c>
       <c r="C177" s="9">
         <v>1</v>
@@ -4336,10 +4333,10 @@
         <v>15</v>
       </c>
       <c r="B178" s="5">
-        <v>46030</v>
+        <v>46087</v>
       </c>
       <c r="C178" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -4347,10 +4344,10 @@
         <v>15</v>
       </c>
       <c r="B179" s="8">
-        <v>46101</v>
+        <v>46030</v>
       </c>
       <c r="C179" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -4358,7 +4355,7 @@
         <v>15</v>
       </c>
       <c r="B180" s="5">
-        <v>46142</v>
+        <v>46101</v>
       </c>
       <c r="C180" s="6">
         <v>1</v>
@@ -4366,13 +4363,13 @@
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B181" s="8">
-        <v>46001</v>
+        <v>46142</v>
       </c>
       <c r="C181" s="9">
-        <v>153</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -4380,10 +4377,10 @@
         <v>21</v>
       </c>
       <c r="B182" s="5">
-        <v>46008</v>
+        <v>46001</v>
       </c>
       <c r="C182" s="6">
-        <v>38</v>
+        <v>153</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -4391,10 +4388,10 @@
         <v>21</v>
       </c>
       <c r="B183" s="8">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="C183" s="9">
-        <v>70</v>
+        <v>38</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -4402,10 +4399,10 @@
         <v>21</v>
       </c>
       <c r="B184" s="5">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="C184" s="6">
-        <v>111</v>
+        <v>70</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -4413,10 +4410,10 @@
         <v>21</v>
       </c>
       <c r="B185" s="8">
-        <v>46006</v>
+        <v>46002</v>
       </c>
       <c r="C185" s="9">
-        <v>147</v>
+        <v>111</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -4424,10 +4421,10 @@
         <v>21</v>
       </c>
       <c r="B186" s="5">
-        <v>46007</v>
+        <v>46006</v>
       </c>
       <c r="C186" s="6">
-        <v>45</v>
+        <v>147</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -4435,10 +4432,10 @@
         <v>21</v>
       </c>
       <c r="B187" s="8">
-        <v>46000</v>
+        <v>46007</v>
       </c>
       <c r="C187" s="9">
-        <v>129</v>
+        <v>45</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -4446,10 +4443,10 @@
         <v>21</v>
       </c>
       <c r="B188" s="5">
-        <v>46084</v>
+        <v>46000</v>
       </c>
       <c r="C188" s="6">
-        <v>10</v>
+        <v>129</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -4457,10 +4454,10 @@
         <v>21</v>
       </c>
       <c r="B189" s="8">
-        <v>46014</v>
+        <v>46084</v>
       </c>
       <c r="C189" s="9">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -4468,10 +4465,10 @@
         <v>21</v>
       </c>
       <c r="B190" s="5">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="C190" s="6">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -4479,10 +4476,10 @@
         <v>21</v>
       </c>
       <c r="B191" s="8">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="C191" s="9">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -4490,10 +4487,10 @@
         <v>21</v>
       </c>
       <c r="B192" s="5">
-        <v>46021</v>
+        <v>46010</v>
       </c>
       <c r="C192" s="6">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -4501,10 +4498,10 @@
         <v>21</v>
       </c>
       <c r="B193" s="8">
-        <v>46009</v>
+        <v>46021</v>
       </c>
       <c r="C193" s="9">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -4512,10 +4509,10 @@
         <v>21</v>
       </c>
       <c r="B194" s="5">
-        <v>46083</v>
+        <v>46009</v>
       </c>
       <c r="C194" s="6">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -4523,10 +4520,10 @@
         <v>21</v>
       </c>
       <c r="B195" s="8">
-        <v>46157</v>
+        <v>46083</v>
       </c>
       <c r="C195" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -4534,10 +4531,10 @@
         <v>21</v>
       </c>
       <c r="B196" s="5">
-        <v>46079</v>
+        <v>46157</v>
       </c>
       <c r="C196" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -4545,10 +4542,10 @@
         <v>21</v>
       </c>
       <c r="B197" s="8">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="C197" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -4556,10 +4553,10 @@
         <v>21</v>
       </c>
       <c r="B198" s="5">
-        <v>46035</v>
+        <v>46077</v>
       </c>
       <c r="C198" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -4567,10 +4564,10 @@
         <v>21</v>
       </c>
       <c r="B199" s="8">
-        <v>46085</v>
+        <v>46035</v>
       </c>
       <c r="C199" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -4578,10 +4575,10 @@
         <v>21</v>
       </c>
       <c r="B200" s="5">
-        <v>46120</v>
+        <v>46085</v>
       </c>
       <c r="C200" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -4589,10 +4586,10 @@
         <v>21</v>
       </c>
       <c r="B201" s="8">
-        <v>46114</v>
+        <v>46120</v>
       </c>
       <c r="C201" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -4600,10 +4597,10 @@
         <v>21</v>
       </c>
       <c r="B202" s="5">
-        <v>46094</v>
+        <v>46114</v>
       </c>
       <c r="C202" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -4611,10 +4608,10 @@
         <v>21</v>
       </c>
       <c r="B203" s="8">
-        <v>46080</v>
+        <v>46094</v>
       </c>
       <c r="C203" s="9">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -4622,10 +4619,10 @@
         <v>21</v>
       </c>
       <c r="B204" s="5">
-        <v>46127</v>
+        <v>46080</v>
       </c>
       <c r="C204" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -4633,7 +4630,7 @@
         <v>21</v>
       </c>
       <c r="B205" s="8">
-        <v>46091</v>
+        <v>46127</v>
       </c>
       <c r="C205" s="9">
         <v>2</v>
@@ -4644,10 +4641,10 @@
         <v>21</v>
       </c>
       <c r="B206" s="5">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="C206" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -4655,10 +4652,10 @@
         <v>21</v>
       </c>
       <c r="B207" s="8">
-        <v>46020</v>
+        <v>46090</v>
       </c>
       <c r="C207" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4666,10 +4663,10 @@
         <v>21</v>
       </c>
       <c r="B208" s="5">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="C208" s="6">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4677,10 +4674,10 @@
         <v>21</v>
       </c>
       <c r="B209" s="8">
-        <v>46078</v>
+        <v>46015</v>
       </c>
       <c r="C209" s="9">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4688,10 +4685,10 @@
         <v>21</v>
       </c>
       <c r="B210" s="5">
-        <v>46148</v>
+        <v>46078</v>
       </c>
       <c r="C210" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -4699,7 +4696,7 @@
         <v>21</v>
       </c>
       <c r="B211" s="8">
-        <v>46105</v>
+        <v>46148</v>
       </c>
       <c r="C211" s="9">
         <v>2</v>
@@ -4710,10 +4707,10 @@
         <v>21</v>
       </c>
       <c r="B212" s="5">
-        <v>46087</v>
+        <v>46105</v>
       </c>
       <c r="C212" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4721,7 +4718,7 @@
         <v>21</v>
       </c>
       <c r="B213" s="8">
-        <v>46107</v>
+        <v>46087</v>
       </c>
       <c r="C213" s="9">
         <v>3</v>
@@ -4732,10 +4729,10 @@
         <v>21</v>
       </c>
       <c r="B214" s="5">
-        <v>46086</v>
+        <v>46107</v>
       </c>
       <c r="C214" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4743,10 +4740,10 @@
         <v>21</v>
       </c>
       <c r="B215" s="8">
-        <v>46106</v>
+        <v>46086</v>
       </c>
       <c r="C215" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4754,10 +4751,10 @@
         <v>21</v>
       </c>
       <c r="B216" s="5">
-        <v>46150</v>
+        <v>46106</v>
       </c>
       <c r="C216" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4765,7 +4762,7 @@
         <v>21</v>
       </c>
       <c r="B217" s="8">
-        <v>46104</v>
+        <v>46150</v>
       </c>
       <c r="C217" s="9">
         <v>3</v>
@@ -4776,10 +4773,10 @@
         <v>21</v>
       </c>
       <c r="B218" s="5">
-        <v>46118</v>
+        <v>46104</v>
       </c>
       <c r="C218" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -4787,10 +4784,10 @@
         <v>21</v>
       </c>
       <c r="B219" s="8">
-        <v>46076</v>
+        <v>46118</v>
       </c>
       <c r="C219" s="9">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4798,10 +4795,10 @@
         <v>21</v>
       </c>
       <c r="B220" s="5">
-        <v>46154</v>
+        <v>46076</v>
       </c>
       <c r="C220" s="6">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -4809,10 +4806,10 @@
         <v>21</v>
       </c>
       <c r="B221" s="8">
-        <v>46093</v>
+        <v>46154</v>
       </c>
       <c r="C221" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -4820,10 +4817,10 @@
         <v>21</v>
       </c>
       <c r="B222" s="5">
-        <v>46122</v>
+        <v>46093</v>
       </c>
       <c r="C222" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -4831,10 +4828,10 @@
         <v>21</v>
       </c>
       <c r="B223" s="8">
-        <v>46092</v>
+        <v>46122</v>
       </c>
       <c r="C223" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -4842,10 +4839,10 @@
         <v>21</v>
       </c>
       <c r="B224" s="5">
-        <v>46156</v>
+        <v>46092</v>
       </c>
       <c r="C224" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -4853,10 +4850,10 @@
         <v>21</v>
       </c>
       <c r="B225" s="8">
-        <v>46133</v>
+        <v>46156</v>
       </c>
       <c r="C225" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -4864,7 +4861,7 @@
         <v>21</v>
       </c>
       <c r="B226" s="5">
-        <v>46126</v>
+        <v>46133</v>
       </c>
       <c r="C226" s="6">
         <v>1</v>
@@ -4875,10 +4872,10 @@
         <v>21</v>
       </c>
       <c r="B227" s="8">
-        <v>46022</v>
+        <v>46126</v>
       </c>
       <c r="C227" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -4886,7 +4883,7 @@
         <v>21</v>
       </c>
       <c r="B228" s="5">
-        <v>46100</v>
+        <v>46022</v>
       </c>
       <c r="C228" s="6">
         <v>2</v>
@@ -4897,10 +4894,10 @@
         <v>21</v>
       </c>
       <c r="B229" s="8">
-        <v>46101</v>
+        <v>46100</v>
       </c>
       <c r="C229" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -4908,10 +4905,10 @@
         <v>21</v>
       </c>
       <c r="B230" s="5">
-        <v>46097</v>
+        <v>46101</v>
       </c>
       <c r="C230" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -4919,10 +4916,10 @@
         <v>21</v>
       </c>
       <c r="B231" s="8">
-        <v>46108</v>
+        <v>46097</v>
       </c>
       <c r="C231" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -4930,10 +4927,10 @@
         <v>21</v>
       </c>
       <c r="B232" s="5">
-        <v>46098</v>
+        <v>46108</v>
       </c>
       <c r="C232" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -4941,10 +4938,10 @@
         <v>21</v>
       </c>
       <c r="B233" s="8">
-        <v>46113</v>
+        <v>46098</v>
       </c>
       <c r="C233" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -4952,7 +4949,7 @@
         <v>21</v>
       </c>
       <c r="B234" s="5">
-        <v>46142</v>
+        <v>46113</v>
       </c>
       <c r="C234" s="6">
         <v>1</v>
@@ -4963,7 +4960,7 @@
         <v>21</v>
       </c>
       <c r="B235" s="8">
-        <v>46153</v>
+        <v>46142</v>
       </c>
       <c r="C235" s="9">
         <v>1</v>
@@ -4974,7 +4971,7 @@
         <v>21</v>
       </c>
       <c r="B236" s="5">
-        <v>46031</v>
+        <v>46153</v>
       </c>
       <c r="C236" s="6">
         <v>1</v>
@@ -4985,9 +4982,20 @@
         <v>21</v>
       </c>
       <c r="B237" s="8">
+        <v>46031</v>
+      </c>
+      <c r="C237" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B238" s="5">
         <v>46155</v>
       </c>
-      <c r="C237" s="9">
+      <c r="C238" s="6">
         <v>1</v>
       </c>
     </row>
@@ -9706,7 +9714,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -9783,7 +9791,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C15">
         <v>4</v>
@@ -9805,7 +9813,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C17">
         <v>23</v>
@@ -9827,7 +9835,7 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C19">
         <v>11</v>
@@ -9849,7 +9857,7 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C21">
         <v>4</v>
@@ -9885,7 +9893,7 @@
         <v>292</v>
       </c>
       <c r="C24">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -9896,7 +9904,7 @@
         <v>289</v>
       </c>
       <c r="C25">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -9904,7 +9912,7 @@
         <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -9918,7 +9926,7 @@
         <v>288</v>
       </c>
       <c r="C27">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -9940,7 +9948,7 @@
         <v>291</v>
       </c>
       <c r="C29">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -9948,7 +9956,7 @@
         <v>16</v>
       </c>
       <c r="B30" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C30">
         <v>10</v>
@@ -9959,7 +9967,7 @@
         <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -9981,7 +9989,7 @@
         <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -10014,7 +10022,7 @@
         <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C36">
         <v>24</v>
@@ -10025,7 +10033,7 @@
         <v>21</v>
       </c>
       <c r="B37" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C37">
         <v>61</v>
@@ -10036,7 +10044,7 @@
         <v>21</v>
       </c>
       <c r="B38" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C38">
         <v>24</v>
@@ -10069,7 +10077,7 @@
         <v>21</v>
       </c>
       <c r="B41" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C41">
         <v>14</v>

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="95" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47CC1CAC-893F-4D6D-A8F8-3C8786FE9C3F}"/>
+  <xr:revisionPtr revIDLastSave="103" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F43598EA-D6BF-4954-B274-4663362D5914}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" tabRatio="667" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" tabRatio="667" activeTab="6" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="mat_2026" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">mat_2026!$A$1:$E$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">origen_colegios!$A$1:$C$357</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">origen_colegios!$A$1:$C$354</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1239" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1237" uniqueCount="299">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -331,9 +331,6 @@
   </si>
   <si>
     <t>Colegio Aconcagua</t>
-  </si>
-  <si>
-    <t>Liceo José Domingo Cañas</t>
   </si>
   <si>
     <t>Escuela Especial de Lenguaje Ariki Mau</t>
@@ -1444,10 +1441,10 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1461,10 +1458,10 @@
         <v>46</v>
       </c>
       <c r="D4">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E4">
-        <v>1.1519999999999999</v>
+        <v>1.1299999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -1478,10 +1475,10 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E5">
-        <v>1.2649999999999999</v>
+        <v>1.294</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1495,10 +1492,10 @@
         <v>58</v>
       </c>
       <c r="D6">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E6">
-        <v>1.052</v>
+        <v>1.069</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1580,10 +1577,10 @@
         <v>88</v>
       </c>
       <c r="D11">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E11">
-        <v>1.0680000000000001</v>
+        <v>1.0569999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -1716,10 +1713,10 @@
         <v>89</v>
       </c>
       <c r="D19">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E19">
-        <v>1.0109999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1733,10 +1730,10 @@
         <v>85</v>
       </c>
       <c r="D20">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E20">
-        <v>1.012</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -1852,10 +1849,10 @@
         <v>109</v>
       </c>
       <c r="D27">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E27">
-        <v>0.98199999999999998</v>
+        <v>0.97199999999999998</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -1903,10 +1900,10 @@
         <v>119</v>
       </c>
       <c r="D30">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>0.99199999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -1937,10 +1934,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E32">
-        <v>1.0680000000000001</v>
+        <v>1.071</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1971,10 +1968,10 @@
         <v>323</v>
       </c>
       <c r="D34">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E34">
-        <v>0.96299999999999997</v>
+        <v>0.95699999999999996</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -2005,10 +2002,10 @@
         <v>250</v>
       </c>
       <c r="D36">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="E36">
-        <v>1.024</v>
+        <v>1.028</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2056,10 +2053,10 @@
         <v>214</v>
       </c>
       <c r="D39">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E39">
-        <v>0.94399999999999995</v>
+        <v>0.93500000000000005</v>
       </c>
     </row>
   </sheetData>
@@ -2373,7 +2370,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD19485A-0629-47F9-A5AD-80ABA7A6E076}">
-  <dimension ref="A1:C238"/>
+  <dimension ref="A1:C242"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -2411,7 +2408,7 @@
         <v>46008</v>
       </c>
       <c r="C3" s="9">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2422,7 +2419,7 @@
         <v>46000</v>
       </c>
       <c r="C4" s="6">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2738,10 +2735,10 @@
         <v>16</v>
       </c>
       <c r="B33" s="8">
-        <v>46099</v>
+        <v>46167</v>
       </c>
       <c r="C33" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -2749,10 +2746,10 @@
         <v>16</v>
       </c>
       <c r="B34" s="5">
-        <v>46128</v>
+        <v>46099</v>
       </c>
       <c r="C34" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -2760,10 +2757,10 @@
         <v>16</v>
       </c>
       <c r="B35" s="8">
-        <v>46141</v>
+        <v>46128</v>
       </c>
       <c r="C35" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -2771,10 +2768,10 @@
         <v>16</v>
       </c>
       <c r="B36" s="5">
-        <v>46132</v>
+        <v>46141</v>
       </c>
       <c r="C36" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -2782,10 +2779,10 @@
         <v>16</v>
       </c>
       <c r="B37" s="8">
-        <v>46127</v>
+        <v>46132</v>
       </c>
       <c r="C37" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -2793,7 +2790,7 @@
         <v>16</v>
       </c>
       <c r="B38" s="5">
-        <v>46091</v>
+        <v>46127</v>
       </c>
       <c r="C38" s="6">
         <v>2</v>
@@ -2804,10 +2801,10 @@
         <v>16</v>
       </c>
       <c r="B39" s="8">
-        <v>46104</v>
+        <v>46091</v>
       </c>
       <c r="C39" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -2815,7 +2812,7 @@
         <v>16</v>
       </c>
       <c r="B40" s="5">
-        <v>46140</v>
+        <v>46104</v>
       </c>
       <c r="C40" s="6">
         <v>1</v>
@@ -2826,7 +2823,7 @@
         <v>16</v>
       </c>
       <c r="B41" s="8">
-        <v>46106</v>
+        <v>46140</v>
       </c>
       <c r="C41" s="9">
         <v>1</v>
@@ -2837,10 +2834,10 @@
         <v>16</v>
       </c>
       <c r="B42" s="5">
-        <v>46113</v>
+        <v>46106</v>
       </c>
       <c r="C42" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -2848,10 +2845,10 @@
         <v>16</v>
       </c>
       <c r="B43" s="8">
-        <v>46090</v>
+        <v>46113</v>
       </c>
       <c r="C43" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -2859,10 +2856,10 @@
         <v>16</v>
       </c>
       <c r="B44" s="5">
-        <v>46148</v>
+        <v>46090</v>
       </c>
       <c r="C44" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -2881,7 +2878,7 @@
         <v>16</v>
       </c>
       <c r="B46" s="5">
-        <v>46125</v>
+        <v>46148</v>
       </c>
       <c r="C46" s="6">
         <v>1</v>
@@ -2892,7 +2889,7 @@
         <v>16</v>
       </c>
       <c r="B47" s="8">
-        <v>46093</v>
+        <v>46125</v>
       </c>
       <c r="C47" s="9">
         <v>1</v>
@@ -2903,7 +2900,7 @@
         <v>16</v>
       </c>
       <c r="B48" s="5">
-        <v>46156</v>
+        <v>46093</v>
       </c>
       <c r="C48" s="6">
         <v>1</v>
@@ -2914,7 +2911,7 @@
         <v>16</v>
       </c>
       <c r="B49" s="8">
-        <v>46092</v>
+        <v>46156</v>
       </c>
       <c r="C49" s="9">
         <v>1</v>
@@ -2925,7 +2922,7 @@
         <v>16</v>
       </c>
       <c r="B50" s="5">
-        <v>46101</v>
+        <v>46092</v>
       </c>
       <c r="C50" s="6">
         <v>1</v>
@@ -2933,13 +2930,13 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B51" s="8">
-        <v>46007</v>
+        <v>46101</v>
       </c>
       <c r="C51" s="9">
-        <v>79</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -2947,10 +2944,10 @@
         <v>14</v>
       </c>
       <c r="B52" s="5">
-        <v>46009</v>
+        <v>46007</v>
       </c>
       <c r="C52" s="6">
-        <v>34</v>
+        <v>78</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -2958,10 +2955,10 @@
         <v>14</v>
       </c>
       <c r="B53" s="8">
-        <v>46000</v>
+        <v>46009</v>
       </c>
       <c r="C53" s="9">
-        <v>82</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -2969,10 +2966,10 @@
         <v>14</v>
       </c>
       <c r="B54" s="5">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C54" s="6">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -2980,10 +2977,10 @@
         <v>14</v>
       </c>
       <c r="B55" s="8">
-        <v>46006</v>
+        <v>46001</v>
       </c>
       <c r="C55" s="9">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -2991,10 +2988,10 @@
         <v>14</v>
       </c>
       <c r="B56" s="5">
-        <v>46010</v>
+        <v>46006</v>
       </c>
       <c r="C56" s="6">
-        <v>24</v>
+        <v>79</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -3002,10 +2999,10 @@
         <v>14</v>
       </c>
       <c r="B57" s="8">
-        <v>46014</v>
+        <v>46010</v>
       </c>
       <c r="C57" s="9">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -3013,10 +3010,10 @@
         <v>14</v>
       </c>
       <c r="B58" s="5">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="C58" s="6">
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -3024,10 +3021,10 @@
         <v>14</v>
       </c>
       <c r="B59" s="8">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C59" s="9">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -3035,10 +3032,10 @@
         <v>14</v>
       </c>
       <c r="B60" s="5">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="C60" s="6">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -3046,10 +3043,10 @@
         <v>14</v>
       </c>
       <c r="B61" s="8">
-        <v>46013</v>
+        <v>46003</v>
       </c>
       <c r="C61" s="9">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -3057,10 +3054,10 @@
         <v>14</v>
       </c>
       <c r="B62" s="5">
-        <v>46022</v>
+        <v>46013</v>
       </c>
       <c r="C62" s="6">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -3068,10 +3065,10 @@
         <v>14</v>
       </c>
       <c r="B63" s="8">
-        <v>46080</v>
+        <v>46022</v>
       </c>
       <c r="C63" s="9">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -3079,10 +3076,10 @@
         <v>14</v>
       </c>
       <c r="B64" s="5">
-        <v>46084</v>
+        <v>46080</v>
       </c>
       <c r="C64" s="6">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -3090,10 +3087,10 @@
         <v>14</v>
       </c>
       <c r="B65" s="8">
-        <v>46125</v>
+        <v>46084</v>
       </c>
       <c r="C65" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -3101,10 +3098,10 @@
         <v>14</v>
       </c>
       <c r="B66" s="5">
-        <v>46091</v>
+        <v>46125</v>
       </c>
       <c r="C66" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -3112,10 +3109,10 @@
         <v>14</v>
       </c>
       <c r="B67" s="8">
-        <v>46083</v>
+        <v>46091</v>
       </c>
       <c r="C67" s="9">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -3123,10 +3120,10 @@
         <v>14</v>
       </c>
       <c r="B68" s="5">
-        <v>46105</v>
+        <v>46083</v>
       </c>
       <c r="C68" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -3134,10 +3131,10 @@
         <v>14</v>
       </c>
       <c r="B69" s="8">
-        <v>46077</v>
+        <v>46105</v>
       </c>
       <c r="C69" s="9">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -3145,10 +3142,10 @@
         <v>14</v>
       </c>
       <c r="B70" s="5">
-        <v>46118</v>
+        <v>46077</v>
       </c>
       <c r="C70" s="6">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -3156,10 +3153,10 @@
         <v>14</v>
       </c>
       <c r="B71" s="8">
-        <v>46078</v>
+        <v>46118</v>
       </c>
       <c r="C71" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -3167,10 +3164,10 @@
         <v>14</v>
       </c>
       <c r="B72" s="5">
-        <v>46099</v>
+        <v>46078</v>
       </c>
       <c r="C72" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -3178,10 +3175,10 @@
         <v>14</v>
       </c>
       <c r="B73" s="8">
-        <v>46104</v>
+        <v>46099</v>
       </c>
       <c r="C73" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -3189,10 +3186,10 @@
         <v>14</v>
       </c>
       <c r="B74" s="5">
-        <v>46107</v>
+        <v>46104</v>
       </c>
       <c r="C74" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -3200,7 +3197,7 @@
         <v>14</v>
       </c>
       <c r="B75" s="8">
-        <v>46020</v>
+        <v>46107</v>
       </c>
       <c r="C75" s="9">
         <v>2</v>
@@ -3211,10 +3208,10 @@
         <v>14</v>
       </c>
       <c r="B76" s="5">
-        <v>46076</v>
+        <v>46020</v>
       </c>
       <c r="C76" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -3222,10 +3219,10 @@
         <v>14</v>
       </c>
       <c r="B77" s="8">
-        <v>46111</v>
+        <v>46076</v>
       </c>
       <c r="C77" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -3233,10 +3230,10 @@
         <v>14</v>
       </c>
       <c r="B78" s="5">
-        <v>46087</v>
+        <v>46111</v>
       </c>
       <c r="C78" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -3244,7 +3241,7 @@
         <v>14</v>
       </c>
       <c r="B79" s="8">
-        <v>46140</v>
+        <v>46087</v>
       </c>
       <c r="C79" s="9">
         <v>2</v>
@@ -3255,10 +3252,10 @@
         <v>14</v>
       </c>
       <c r="B80" s="5">
-        <v>46113</v>
+        <v>46140</v>
       </c>
       <c r="C80" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -3266,10 +3263,10 @@
         <v>14</v>
       </c>
       <c r="B81" s="8">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="C81" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -3277,10 +3274,10 @@
         <v>14</v>
       </c>
       <c r="B82" s="5">
-        <v>46108</v>
+        <v>46119</v>
       </c>
       <c r="C82" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -3288,7 +3285,7 @@
         <v>14</v>
       </c>
       <c r="B83" s="8">
-        <v>46098</v>
+        <v>46108</v>
       </c>
       <c r="C83" s="9">
         <v>1</v>
@@ -3299,7 +3296,7 @@
         <v>14</v>
       </c>
       <c r="B84" s="5">
-        <v>46141</v>
+        <v>46098</v>
       </c>
       <c r="C84" s="6">
         <v>1</v>
@@ -3310,7 +3307,7 @@
         <v>14</v>
       </c>
       <c r="B85" s="8">
-        <v>46114</v>
+        <v>46141</v>
       </c>
       <c r="C85" s="9">
         <v>1</v>
@@ -3321,10 +3318,10 @@
         <v>14</v>
       </c>
       <c r="B86" s="5">
-        <v>46079</v>
+        <v>46114</v>
       </c>
       <c r="C86" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -3332,10 +3329,10 @@
         <v>14</v>
       </c>
       <c r="B87" s="8">
-        <v>46139</v>
+        <v>46079</v>
       </c>
       <c r="C87" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -3343,10 +3340,10 @@
         <v>14</v>
       </c>
       <c r="B88" s="5">
-        <v>46148</v>
+        <v>46139</v>
       </c>
       <c r="C88" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -3354,10 +3351,10 @@
         <v>14</v>
       </c>
       <c r="B89" s="8">
-        <v>46092</v>
+        <v>46148</v>
       </c>
       <c r="C89" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -3365,10 +3362,10 @@
         <v>14</v>
       </c>
       <c r="B90" s="5">
-        <v>46021</v>
+        <v>46092</v>
       </c>
       <c r="C90" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -3376,10 +3373,10 @@
         <v>14</v>
       </c>
       <c r="B91" s="8">
-        <v>46086</v>
+        <v>46021</v>
       </c>
       <c r="C91" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -3387,10 +3384,10 @@
         <v>14</v>
       </c>
       <c r="B92" s="5">
-        <v>46147</v>
+        <v>46086</v>
       </c>
       <c r="C92" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -3398,7 +3395,7 @@
         <v>14</v>
       </c>
       <c r="B93" s="8">
-        <v>46134</v>
+        <v>46147</v>
       </c>
       <c r="C93" s="9">
         <v>1</v>
@@ -3406,13 +3403,13 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B94" s="5">
-        <v>46003</v>
+        <v>46134</v>
       </c>
       <c r="C94" s="6">
-        <v>95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -3420,10 +3417,10 @@
         <v>3</v>
       </c>
       <c r="B95" s="8">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="C95" s="9">
-        <v>115</v>
+        <v>95</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -3431,10 +3428,10 @@
         <v>3</v>
       </c>
       <c r="B96" s="5">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C96" s="6">
-        <v>15</v>
+        <v>115</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -3442,10 +3439,10 @@
         <v>3</v>
       </c>
       <c r="B97" s="8">
-        <v>46000</v>
+        <v>46008</v>
       </c>
       <c r="C97" s="9">
-        <v>98</v>
+        <v>15</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -3453,10 +3450,10 @@
         <v>3</v>
       </c>
       <c r="B98" s="5">
-        <v>46007</v>
+        <v>46000</v>
       </c>
       <c r="C98" s="6">
-        <v>43</v>
+        <v>98</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -3464,10 +3461,10 @@
         <v>3</v>
       </c>
       <c r="B99" s="8">
-        <v>46001</v>
+        <v>46007</v>
       </c>
       <c r="C99" s="9">
-        <v>91</v>
+        <v>41</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -3475,10 +3472,10 @@
         <v>3</v>
       </c>
       <c r="B100" s="5">
-        <v>46010</v>
+        <v>46001</v>
       </c>
       <c r="C100" s="6">
-        <v>9</v>
+        <v>91</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -3486,10 +3483,10 @@
         <v>3</v>
       </c>
       <c r="B101" s="8">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="C101" s="9">
-        <v>84</v>
+        <v>9</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -3497,10 +3494,10 @@
         <v>3</v>
       </c>
       <c r="B102" s="5">
-        <v>46009</v>
+        <v>46006</v>
       </c>
       <c r="C102" s="6">
-        <v>2</v>
+        <v>84</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -3508,10 +3505,10 @@
         <v>3</v>
       </c>
       <c r="B103" s="8">
-        <v>46015</v>
+        <v>46009</v>
       </c>
       <c r="C103" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -3519,10 +3516,10 @@
         <v>3</v>
       </c>
       <c r="B104" s="5">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="C104" s="6">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -3530,10 +3527,10 @@
         <v>3</v>
       </c>
       <c r="B105" s="8">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="C105" s="9">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -3541,10 +3538,10 @@
         <v>3</v>
       </c>
       <c r="B106" s="5">
-        <v>46021</v>
+        <v>46013</v>
       </c>
       <c r="C106" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -3552,10 +3549,10 @@
         <v>3</v>
       </c>
       <c r="B107" s="8">
-        <v>46077</v>
+        <v>46021</v>
       </c>
       <c r="C107" s="9">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -3563,10 +3560,10 @@
         <v>3</v>
       </c>
       <c r="B108" s="5">
-        <v>46090</v>
+        <v>46077</v>
       </c>
       <c r="C108" s="6">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -3574,7 +3571,7 @@
         <v>3</v>
       </c>
       <c r="B109" s="8">
-        <v>46093</v>
+        <v>46167</v>
       </c>
       <c r="C109" s="9">
         <v>1</v>
@@ -3585,10 +3582,10 @@
         <v>3</v>
       </c>
       <c r="B110" s="5">
-        <v>46078</v>
+        <v>46090</v>
       </c>
       <c r="C110" s="6">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -3596,10 +3593,10 @@
         <v>3</v>
       </c>
       <c r="B111" s="8">
-        <v>46084</v>
+        <v>46093</v>
       </c>
       <c r="C111" s="9">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -3607,10 +3604,10 @@
         <v>3</v>
       </c>
       <c r="B112" s="5">
-        <v>46134</v>
+        <v>46078</v>
       </c>
       <c r="C112" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -3618,10 +3615,10 @@
         <v>3</v>
       </c>
       <c r="B113" s="8">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="C113" s="9">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -3629,10 +3626,10 @@
         <v>3</v>
       </c>
       <c r="B114" s="5">
-        <v>46022</v>
+        <v>46134</v>
       </c>
       <c r="C114" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -3640,10 +3637,10 @@
         <v>3</v>
       </c>
       <c r="B115" s="8">
-        <v>46114</v>
+        <v>46083</v>
       </c>
       <c r="C115" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -3651,7 +3648,7 @@
         <v>3</v>
       </c>
       <c r="B116" s="5">
-        <v>46135</v>
+        <v>46022</v>
       </c>
       <c r="C116" s="6">
         <v>1</v>
@@ -3662,10 +3659,10 @@
         <v>3</v>
       </c>
       <c r="B117" s="8">
-        <v>46126</v>
+        <v>46114</v>
       </c>
       <c r="C117" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -3673,10 +3670,10 @@
         <v>3</v>
       </c>
       <c r="B118" s="5">
-        <v>46120</v>
+        <v>46135</v>
       </c>
       <c r="C118" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -3684,10 +3681,10 @@
         <v>3</v>
       </c>
       <c r="B119" s="8">
-        <v>46127</v>
+        <v>46168</v>
       </c>
       <c r="C119" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -3695,10 +3692,10 @@
         <v>3</v>
       </c>
       <c r="B120" s="5">
-        <v>46087</v>
+        <v>46126</v>
       </c>
       <c r="C120" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -3706,10 +3703,10 @@
         <v>3</v>
       </c>
       <c r="B121" s="8">
-        <v>46108</v>
+        <v>46120</v>
       </c>
       <c r="C121" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -3717,7 +3714,7 @@
         <v>3</v>
       </c>
       <c r="B122" s="5">
-        <v>46020</v>
+        <v>46127</v>
       </c>
       <c r="C122" s="6">
         <v>1</v>
@@ -3728,7 +3725,7 @@
         <v>3</v>
       </c>
       <c r="B123" s="8">
-        <v>46097</v>
+        <v>46087</v>
       </c>
       <c r="C123" s="9">
         <v>1</v>
@@ -3739,10 +3736,10 @@
         <v>3</v>
       </c>
       <c r="B124" s="5">
-        <v>46161</v>
+        <v>46108</v>
       </c>
       <c r="C124" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -3750,7 +3747,7 @@
         <v>3</v>
       </c>
       <c r="B125" s="8">
-        <v>46129</v>
+        <v>46020</v>
       </c>
       <c r="C125" s="9">
         <v>1</v>
@@ -3761,7 +3758,7 @@
         <v>3</v>
       </c>
       <c r="B126" s="5">
-        <v>46080</v>
+        <v>46097</v>
       </c>
       <c r="C126" s="6">
         <v>1</v>
@@ -3772,10 +3769,10 @@
         <v>3</v>
       </c>
       <c r="B127" s="8">
-        <v>46101</v>
+        <v>46161</v>
       </c>
       <c r="C127" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -3783,7 +3780,7 @@
         <v>3</v>
       </c>
       <c r="B128" s="5">
-        <v>46155</v>
+        <v>46129</v>
       </c>
       <c r="C128" s="6">
         <v>1</v>
@@ -3794,7 +3791,7 @@
         <v>3</v>
       </c>
       <c r="B129" s="8">
-        <v>46150</v>
+        <v>46080</v>
       </c>
       <c r="C129" s="9">
         <v>1</v>
@@ -3805,7 +3802,7 @@
         <v>3</v>
       </c>
       <c r="B130" s="5">
-        <v>46141</v>
+        <v>46101</v>
       </c>
       <c r="C130" s="6">
         <v>1</v>
@@ -3816,7 +3813,7 @@
         <v>3</v>
       </c>
       <c r="B131" s="8">
-        <v>46085</v>
+        <v>46155</v>
       </c>
       <c r="C131" s="9">
         <v>1</v>
@@ -3827,7 +3824,7 @@
         <v>3</v>
       </c>
       <c r="B132" s="5">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="C132" s="6">
         <v>1</v>
@@ -3838,10 +3835,10 @@
         <v>3</v>
       </c>
       <c r="B133" s="8">
-        <v>46118</v>
+        <v>46141</v>
       </c>
       <c r="C133" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -3849,7 +3846,7 @@
         <v>3</v>
       </c>
       <c r="B134" s="5">
-        <v>46079</v>
+        <v>46085</v>
       </c>
       <c r="C134" s="6">
         <v>1</v>
@@ -3857,35 +3854,35 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B135" s="8">
-        <v>46003</v>
+        <v>46148</v>
       </c>
       <c r="C135" s="9">
-        <v>92</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B136" s="5">
-        <v>46000</v>
+        <v>46118</v>
       </c>
       <c r="C136" s="6">
-        <v>133</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B137" s="8">
-        <v>46006</v>
+        <v>46079</v>
       </c>
       <c r="C137" s="9">
-        <v>174</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -3893,10 +3890,10 @@
         <v>15</v>
       </c>
       <c r="B138" s="5">
-        <v>46001</v>
+        <v>46003</v>
       </c>
       <c r="C138" s="6">
-        <v>174</v>
+        <v>92</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -3904,10 +3901,10 @@
         <v>15</v>
       </c>
       <c r="B139" s="8">
-        <v>46014</v>
+        <v>46000</v>
       </c>
       <c r="C139" s="9">
-        <v>16</v>
+        <v>132</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -3915,10 +3912,10 @@
         <v>15</v>
       </c>
       <c r="B140" s="5">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="C140" s="6">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -3926,10 +3923,10 @@
         <v>15</v>
       </c>
       <c r="B141" s="8">
-        <v>46009</v>
+        <v>46001</v>
       </c>
       <c r="C141" s="9">
-        <v>20</v>
+        <v>174</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -3937,10 +3934,10 @@
         <v>15</v>
       </c>
       <c r="B142" s="5">
-        <v>46010</v>
+        <v>46014</v>
       </c>
       <c r="C142" s="6">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -3948,10 +3945,10 @@
         <v>15</v>
       </c>
       <c r="B143" s="8">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C143" s="9">
-        <v>25</v>
+        <v>171</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -3959,10 +3956,10 @@
         <v>15</v>
       </c>
       <c r="B144" s="5">
-        <v>46007</v>
+        <v>46009</v>
       </c>
       <c r="C144" s="6">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -3970,10 +3967,10 @@
         <v>15</v>
       </c>
       <c r="B145" s="8">
-        <v>46013</v>
+        <v>46010</v>
       </c>
       <c r="C145" s="9">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -3981,10 +3978,10 @@
         <v>15</v>
       </c>
       <c r="B146" s="5">
-        <v>46080</v>
+        <v>46008</v>
       </c>
       <c r="C146" s="6">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -3992,10 +3989,10 @@
         <v>15</v>
       </c>
       <c r="B147" s="8">
-        <v>46090</v>
+        <v>46007</v>
       </c>
       <c r="C147" s="9">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -4003,10 +4000,10 @@
         <v>15</v>
       </c>
       <c r="B148" s="5">
-        <v>46079</v>
+        <v>46013</v>
       </c>
       <c r="C148" s="6">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -4014,10 +4011,10 @@
         <v>15</v>
       </c>
       <c r="B149" s="8">
-        <v>46015</v>
+        <v>46080</v>
       </c>
       <c r="C149" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -4025,10 +4022,10 @@
         <v>15</v>
       </c>
       <c r="B150" s="5">
-        <v>46085</v>
+        <v>46090</v>
       </c>
       <c r="C150" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -4036,10 +4033,10 @@
         <v>15</v>
       </c>
       <c r="B151" s="8">
-        <v>46098</v>
+        <v>46079</v>
       </c>
       <c r="C151" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -4047,10 +4044,10 @@
         <v>15</v>
       </c>
       <c r="B152" s="5">
-        <v>46021</v>
+        <v>46015</v>
       </c>
       <c r="C152" s="6">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -4058,10 +4055,10 @@
         <v>15</v>
       </c>
       <c r="B153" s="8">
-        <v>46078</v>
+        <v>46085</v>
       </c>
       <c r="C153" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -4069,10 +4066,10 @@
         <v>15</v>
       </c>
       <c r="B154" s="5">
-        <v>46084</v>
+        <v>46098</v>
       </c>
       <c r="C154" s="6">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -4080,10 +4077,10 @@
         <v>15</v>
       </c>
       <c r="B155" s="8">
-        <v>46128</v>
+        <v>46021</v>
       </c>
       <c r="C155" s="9">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -4091,10 +4088,10 @@
         <v>15</v>
       </c>
       <c r="B156" s="5">
-        <v>46083</v>
+        <v>46078</v>
       </c>
       <c r="C156" s="6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -4102,10 +4099,10 @@
         <v>15</v>
       </c>
       <c r="B157" s="8">
-        <v>46153</v>
+        <v>46084</v>
       </c>
       <c r="C157" s="9">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -4113,10 +4110,10 @@
         <v>15</v>
       </c>
       <c r="B158" s="5">
-        <v>46076</v>
+        <v>46128</v>
       </c>
       <c r="C158" s="6">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -4124,10 +4121,10 @@
         <v>15</v>
       </c>
       <c r="B159" s="8">
-        <v>46099</v>
+        <v>46083</v>
       </c>
       <c r="C159" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -4135,7 +4132,7 @@
         <v>15</v>
       </c>
       <c r="B160" s="5">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="C160" s="6">
         <v>1</v>
@@ -4146,10 +4143,10 @@
         <v>15</v>
       </c>
       <c r="B161" s="8">
-        <v>46092</v>
+        <v>46076</v>
       </c>
       <c r="C161" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -4157,7 +4154,7 @@
         <v>15</v>
       </c>
       <c r="B162" s="5">
-        <v>46031</v>
+        <v>46099</v>
       </c>
       <c r="C162" s="6">
         <v>2</v>
@@ -4168,10 +4165,10 @@
         <v>15</v>
       </c>
       <c r="B163" s="8">
-        <v>46120</v>
+        <v>46154</v>
       </c>
       <c r="C163" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -4179,10 +4176,10 @@
         <v>15</v>
       </c>
       <c r="B164" s="5">
-        <v>46077</v>
+        <v>46092</v>
       </c>
       <c r="C164" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -4190,10 +4187,10 @@
         <v>15</v>
       </c>
       <c r="B165" s="8">
-        <v>46114</v>
+        <v>46031</v>
       </c>
       <c r="C165" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -4201,10 +4198,10 @@
         <v>15</v>
       </c>
       <c r="B166" s="5">
-        <v>46037</v>
+        <v>46120</v>
       </c>
       <c r="C166" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -4212,10 +4209,10 @@
         <v>15</v>
       </c>
       <c r="B167" s="8">
-        <v>46020</v>
+        <v>46077</v>
       </c>
       <c r="C167" s="9">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -4223,7 +4220,7 @@
         <v>15</v>
       </c>
       <c r="B168" s="5">
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="C168" s="6">
         <v>1</v>
@@ -4234,7 +4231,7 @@
         <v>15</v>
       </c>
       <c r="B169" s="8">
-        <v>46155</v>
+        <v>46037</v>
       </c>
       <c r="C169" s="9">
         <v>1</v>
@@ -4245,10 +4242,10 @@
         <v>15</v>
       </c>
       <c r="B170" s="5">
-        <v>46112</v>
+        <v>46020</v>
       </c>
       <c r="C170" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -4256,7 +4253,7 @@
         <v>15</v>
       </c>
       <c r="B171" s="8">
-        <v>46132</v>
+        <v>46106</v>
       </c>
       <c r="C171" s="9">
         <v>1</v>
@@ -4267,7 +4264,7 @@
         <v>15</v>
       </c>
       <c r="B172" s="5">
-        <v>46108</v>
+        <v>46155</v>
       </c>
       <c r="C172" s="6">
         <v>1</v>
@@ -4278,7 +4275,7 @@
         <v>15</v>
       </c>
       <c r="B173" s="8">
-        <v>46148</v>
+        <v>46112</v>
       </c>
       <c r="C173" s="9">
         <v>1</v>
@@ -4289,7 +4286,7 @@
         <v>15</v>
       </c>
       <c r="B174" s="5">
-        <v>46118</v>
+        <v>46132</v>
       </c>
       <c r="C174" s="6">
         <v>1</v>
@@ -4300,7 +4297,7 @@
         <v>15</v>
       </c>
       <c r="B175" s="8">
-        <v>46035</v>
+        <v>46108</v>
       </c>
       <c r="C175" s="9">
         <v>1</v>
@@ -4311,7 +4308,7 @@
         <v>15</v>
       </c>
       <c r="B176" s="5">
-        <v>46093</v>
+        <v>46148</v>
       </c>
       <c r="C176" s="6">
         <v>1</v>
@@ -4322,7 +4319,7 @@
         <v>15</v>
       </c>
       <c r="B177" s="8">
-        <v>46022</v>
+        <v>46118</v>
       </c>
       <c r="C177" s="9">
         <v>1</v>
@@ -4333,7 +4330,7 @@
         <v>15</v>
       </c>
       <c r="B178" s="5">
-        <v>46087</v>
+        <v>46035</v>
       </c>
       <c r="C178" s="6">
         <v>1</v>
@@ -4344,10 +4341,10 @@
         <v>15</v>
       </c>
       <c r="B179" s="8">
-        <v>46030</v>
+        <v>46093</v>
       </c>
       <c r="C179" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -4355,7 +4352,7 @@
         <v>15</v>
       </c>
       <c r="B180" s="5">
-        <v>46101</v>
+        <v>46022</v>
       </c>
       <c r="C180" s="6">
         <v>1</v>
@@ -4366,7 +4363,7 @@
         <v>15</v>
       </c>
       <c r="B181" s="8">
-        <v>46142</v>
+        <v>46087</v>
       </c>
       <c r="C181" s="9">
         <v>1</v>
@@ -4374,35 +4371,35 @@
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B182" s="5">
-        <v>46001</v>
+        <v>46030</v>
       </c>
       <c r="C182" s="6">
-        <v>153</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B183" s="8">
-        <v>46008</v>
+        <v>46101</v>
       </c>
       <c r="C183" s="9">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B184" s="5">
-        <v>46003</v>
+        <v>46142</v>
       </c>
       <c r="C184" s="6">
-        <v>70</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -4410,10 +4407,10 @@
         <v>21</v>
       </c>
       <c r="B185" s="8">
-        <v>46002</v>
+        <v>46001</v>
       </c>
       <c r="C185" s="9">
-        <v>111</v>
+        <v>153</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -4421,10 +4418,10 @@
         <v>21</v>
       </c>
       <c r="B186" s="5">
-        <v>46006</v>
+        <v>46008</v>
       </c>
       <c r="C186" s="6">
-        <v>147</v>
+        <v>38</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -4432,10 +4429,10 @@
         <v>21</v>
       </c>
       <c r="B187" s="8">
-        <v>46007</v>
+        <v>46003</v>
       </c>
       <c r="C187" s="9">
-        <v>45</v>
+        <v>70</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -4443,10 +4440,10 @@
         <v>21</v>
       </c>
       <c r="B188" s="5">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="C188" s="6">
-        <v>129</v>
+        <v>111</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -4454,10 +4451,10 @@
         <v>21</v>
       </c>
       <c r="B189" s="8">
-        <v>46084</v>
+        <v>46006</v>
       </c>
       <c r="C189" s="9">
-        <v>10</v>
+        <v>147</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -4465,10 +4462,10 @@
         <v>21</v>
       </c>
       <c r="B190" s="5">
-        <v>46014</v>
+        <v>46007</v>
       </c>
       <c r="C190" s="6">
-        <v>22</v>
+        <v>45</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -4476,10 +4473,10 @@
         <v>21</v>
       </c>
       <c r="B191" s="8">
-        <v>46013</v>
+        <v>46000</v>
       </c>
       <c r="C191" s="9">
-        <v>29</v>
+        <v>129</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -4487,10 +4484,10 @@
         <v>21</v>
       </c>
       <c r="B192" s="5">
-        <v>46010</v>
+        <v>46084</v>
       </c>
       <c r="C192" s="6">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -4498,10 +4495,10 @@
         <v>21</v>
       </c>
       <c r="B193" s="8">
-        <v>46021</v>
+        <v>46014</v>
       </c>
       <c r="C193" s="9">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -4509,10 +4506,10 @@
         <v>21</v>
       </c>
       <c r="B194" s="5">
-        <v>46009</v>
+        <v>46013</v>
       </c>
       <c r="C194" s="6">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -4520,10 +4517,10 @@
         <v>21</v>
       </c>
       <c r="B195" s="8">
-        <v>46083</v>
+        <v>46010</v>
       </c>
       <c r="C195" s="9">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -4531,10 +4528,10 @@
         <v>21</v>
       </c>
       <c r="B196" s="5">
-        <v>46157</v>
+        <v>46021</v>
       </c>
       <c r="C196" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -4542,10 +4539,10 @@
         <v>21</v>
       </c>
       <c r="B197" s="8">
-        <v>46079</v>
+        <v>46009</v>
       </c>
       <c r="C197" s="9">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -4553,10 +4550,10 @@
         <v>21</v>
       </c>
       <c r="B198" s="5">
-        <v>46077</v>
+        <v>46083</v>
       </c>
       <c r="C198" s="6">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -4564,7 +4561,7 @@
         <v>21</v>
       </c>
       <c r="B199" s="8">
-        <v>46035</v>
+        <v>46157</v>
       </c>
       <c r="C199" s="9">
         <v>2</v>
@@ -4575,7 +4572,7 @@
         <v>21</v>
       </c>
       <c r="B200" s="5">
-        <v>46085</v>
+        <v>46079</v>
       </c>
       <c r="C200" s="6">
         <v>3</v>
@@ -4586,10 +4583,10 @@
         <v>21</v>
       </c>
       <c r="B201" s="8">
-        <v>46120</v>
+        <v>46167</v>
       </c>
       <c r="C201" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -4597,10 +4594,10 @@
         <v>21</v>
       </c>
       <c r="B202" s="5">
-        <v>46114</v>
+        <v>46077</v>
       </c>
       <c r="C202" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -4608,10 +4605,10 @@
         <v>21</v>
       </c>
       <c r="B203" s="8">
-        <v>46094</v>
+        <v>46035</v>
       </c>
       <c r="C203" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -4619,10 +4616,10 @@
         <v>21</v>
       </c>
       <c r="B204" s="5">
-        <v>46080</v>
+        <v>46085</v>
       </c>
       <c r="C204" s="6">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -4630,7 +4627,7 @@
         <v>21</v>
       </c>
       <c r="B205" s="8">
-        <v>46127</v>
+        <v>46120</v>
       </c>
       <c r="C205" s="9">
         <v>2</v>
@@ -4641,10 +4638,10 @@
         <v>21</v>
       </c>
       <c r="B206" s="5">
-        <v>46091</v>
+        <v>46114</v>
       </c>
       <c r="C206" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -4652,10 +4649,10 @@
         <v>21</v>
       </c>
       <c r="B207" s="8">
-        <v>46090</v>
+        <v>46094</v>
       </c>
       <c r="C207" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4663,10 +4660,10 @@
         <v>21</v>
       </c>
       <c r="B208" s="5">
-        <v>46020</v>
+        <v>46080</v>
       </c>
       <c r="C208" s="6">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4674,10 +4671,10 @@
         <v>21</v>
       </c>
       <c r="B209" s="8">
-        <v>46015</v>
+        <v>46127</v>
       </c>
       <c r="C209" s="9">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4685,10 +4682,10 @@
         <v>21</v>
       </c>
       <c r="B210" s="5">
-        <v>46078</v>
+        <v>46091</v>
       </c>
       <c r="C210" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -4696,10 +4693,10 @@
         <v>21</v>
       </c>
       <c r="B211" s="8">
-        <v>46148</v>
+        <v>46090</v>
       </c>
       <c r="C211" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -4707,10 +4704,10 @@
         <v>21</v>
       </c>
       <c r="B212" s="5">
-        <v>46105</v>
+        <v>46020</v>
       </c>
       <c r="C212" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4718,10 +4715,10 @@
         <v>21</v>
       </c>
       <c r="B213" s="8">
-        <v>46087</v>
+        <v>46015</v>
       </c>
       <c r="C213" s="9">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4729,10 +4726,10 @@
         <v>21</v>
       </c>
       <c r="B214" s="5">
-        <v>46107</v>
+        <v>46078</v>
       </c>
       <c r="C214" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4740,10 +4737,10 @@
         <v>21</v>
       </c>
       <c r="B215" s="8">
-        <v>46086</v>
+        <v>46148</v>
       </c>
       <c r="C215" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4751,10 +4748,10 @@
         <v>21</v>
       </c>
       <c r="B216" s="5">
-        <v>46106</v>
+        <v>46105</v>
       </c>
       <c r="C216" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4762,7 +4759,7 @@
         <v>21</v>
       </c>
       <c r="B217" s="8">
-        <v>46150</v>
+        <v>46087</v>
       </c>
       <c r="C217" s="9">
         <v>3</v>
@@ -4773,7 +4770,7 @@
         <v>21</v>
       </c>
       <c r="B218" s="5">
-        <v>46104</v>
+        <v>46107</v>
       </c>
       <c r="C218" s="6">
         <v>3</v>
@@ -4784,10 +4781,10 @@
         <v>21</v>
       </c>
       <c r="B219" s="8">
-        <v>46118</v>
+        <v>46086</v>
       </c>
       <c r="C219" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4795,10 +4792,10 @@
         <v>21</v>
       </c>
       <c r="B220" s="5">
-        <v>46076</v>
+        <v>46106</v>
       </c>
       <c r="C220" s="6">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -4806,10 +4803,10 @@
         <v>21</v>
       </c>
       <c r="B221" s="8">
-        <v>46154</v>
+        <v>46150</v>
       </c>
       <c r="C221" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -4817,7 +4814,7 @@
         <v>21</v>
       </c>
       <c r="B222" s="5">
-        <v>46093</v>
+        <v>46104</v>
       </c>
       <c r="C222" s="6">
         <v>3</v>
@@ -4828,7 +4825,7 @@
         <v>21</v>
       </c>
       <c r="B223" s="8">
-        <v>46122</v>
+        <v>46118</v>
       </c>
       <c r="C223" s="9">
         <v>1</v>
@@ -4839,10 +4836,10 @@
         <v>21</v>
       </c>
       <c r="B224" s="5">
-        <v>46092</v>
+        <v>46076</v>
       </c>
       <c r="C224" s="6">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -4850,10 +4847,10 @@
         <v>21</v>
       </c>
       <c r="B225" s="8">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="C225" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -4861,10 +4858,10 @@
         <v>21</v>
       </c>
       <c r="B226" s="5">
-        <v>46133</v>
+        <v>46093</v>
       </c>
       <c r="C226" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -4872,7 +4869,7 @@
         <v>21</v>
       </c>
       <c r="B227" s="8">
-        <v>46126</v>
+        <v>46122</v>
       </c>
       <c r="C227" s="9">
         <v>1</v>
@@ -4883,10 +4880,10 @@
         <v>21</v>
       </c>
       <c r="B228" s="5">
-        <v>46022</v>
+        <v>46092</v>
       </c>
       <c r="C228" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -4894,7 +4891,7 @@
         <v>21</v>
       </c>
       <c r="B229" s="8">
-        <v>46100</v>
+        <v>46156</v>
       </c>
       <c r="C229" s="9">
         <v>2</v>
@@ -4905,7 +4902,7 @@
         <v>21</v>
       </c>
       <c r="B230" s="5">
-        <v>46101</v>
+        <v>46133</v>
       </c>
       <c r="C230" s="6">
         <v>1</v>
@@ -4916,10 +4913,10 @@
         <v>21</v>
       </c>
       <c r="B231" s="8">
-        <v>46097</v>
+        <v>46126</v>
       </c>
       <c r="C231" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -4927,10 +4924,10 @@
         <v>21</v>
       </c>
       <c r="B232" s="5">
-        <v>46108</v>
+        <v>46022</v>
       </c>
       <c r="C232" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -4938,7 +4935,7 @@
         <v>21</v>
       </c>
       <c r="B233" s="8">
-        <v>46098</v>
+        <v>46100</v>
       </c>
       <c r="C233" s="9">
         <v>2</v>
@@ -4949,7 +4946,7 @@
         <v>21</v>
       </c>
       <c r="B234" s="5">
-        <v>46113</v>
+        <v>46101</v>
       </c>
       <c r="C234" s="6">
         <v>1</v>
@@ -4960,10 +4957,10 @@
         <v>21</v>
       </c>
       <c r="B235" s="8">
-        <v>46142</v>
+        <v>46097</v>
       </c>
       <c r="C235" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -4971,7 +4968,7 @@
         <v>21</v>
       </c>
       <c r="B236" s="5">
-        <v>46153</v>
+        <v>46108</v>
       </c>
       <c r="C236" s="6">
         <v>1</v>
@@ -4982,10 +4979,10 @@
         <v>21</v>
       </c>
       <c r="B237" s="8">
-        <v>46031</v>
+        <v>46098</v>
       </c>
       <c r="C237" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -4993,9 +4990,53 @@
         <v>21</v>
       </c>
       <c r="B238" s="5">
+        <v>46113</v>
+      </c>
+      <c r="C238" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B239" s="8">
+        <v>46142</v>
+      </c>
+      <c r="C239" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B240" s="5">
+        <v>46153</v>
+      </c>
+      <c r="C240" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B241" s="8">
+        <v>46031</v>
+      </c>
+      <c r="C241" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B242" s="5">
         <v>46155</v>
       </c>
-      <c r="C238" s="6">
+      <c r="C242" s="6">
         <v>1</v>
       </c>
     </row>
@@ -5062,7 +5103,7 @@
         <v>4</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -5079,7 +5120,7 @@
         <v>9</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -5096,7 +5137,7 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -5113,7 +5154,7 @@
         <v>1</v>
       </c>
       <c r="E6">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -5198,7 +5239,7 @@
         <v>1</v>
       </c>
       <c r="E11">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -5331,7 +5372,7 @@
         <v>77</v>
       </c>
       <c r="D19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19">
         <v>7</v>
@@ -5345,7 +5386,7 @@
         <v>9</v>
       </c>
       <c r="C20">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D20">
         <v>9</v>
@@ -5467,7 +5508,7 @@
         <v>92</v>
       </c>
       <c r="D27">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E27">
         <v>12</v>
@@ -5515,7 +5556,7 @@
         <v>9</v>
       </c>
       <c r="C30">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D30">
         <v>8</v>
@@ -5549,13 +5590,13 @@
         <v>17</v>
       </c>
       <c r="C32">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D32">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E32">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -5583,7 +5624,7 @@
         <v>19</v>
       </c>
       <c r="C34">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D34">
         <v>8</v>
@@ -5617,7 +5658,7 @@
         <v>17</v>
       </c>
       <c r="C36">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D36">
         <v>87</v>
@@ -5671,7 +5712,7 @@
         <v>190</v>
       </c>
       <c r="D39">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E39">
         <v>9</v>
@@ -5684,7 +5725,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0916EAC6-1E7F-4924-9D0E-33749FD3E143}">
-  <dimension ref="A1:C357"/>
+  <dimension ref="A1:C354"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
@@ -5697,7 +5738,7 @@
         <v>37</v>
       </c>
       <c r="B1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C1" t="s">
         <v>36</v>
@@ -5730,10 +5771,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -5741,7 +5782,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -5862,7 +5903,7 @@
         <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C16">
         <v>2</v>
@@ -5950,7 +5991,7 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -6093,7 +6134,7 @@
         <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -6390,7 +6431,7 @@
         <v>14</v>
       </c>
       <c r="B64" t="s">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -6401,7 +6442,7 @@
         <v>14</v>
       </c>
       <c r="B65" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -6412,7 +6453,7 @@
         <v>14</v>
       </c>
       <c r="B66" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -6423,7 +6464,7 @@
         <v>14</v>
       </c>
       <c r="B67" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -6434,7 +6475,7 @@
         <v>14</v>
       </c>
       <c r="B68" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -6445,7 +6486,7 @@
         <v>14</v>
       </c>
       <c r="B69" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -6456,7 +6497,7 @@
         <v>14</v>
       </c>
       <c r="B70" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -6467,7 +6508,7 @@
         <v>14</v>
       </c>
       <c r="B71" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -6478,7 +6519,7 @@
         <v>14</v>
       </c>
       <c r="B72" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -6489,7 +6530,7 @@
         <v>14</v>
       </c>
       <c r="B73" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -6500,7 +6541,7 @@
         <v>14</v>
       </c>
       <c r="B74" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -6511,7 +6552,7 @@
         <v>14</v>
       </c>
       <c r="B75" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -6522,7 +6563,7 @@
         <v>14</v>
       </c>
       <c r="B76" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="C76">
         <v>1</v>
@@ -6533,7 +6574,7 @@
         <v>14</v>
       </c>
       <c r="B77" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="C77">
         <v>1</v>
@@ -6544,7 +6585,7 @@
         <v>14</v>
       </c>
       <c r="B78" t="s">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="C78">
         <v>1</v>
@@ -6555,7 +6596,7 @@
         <v>14</v>
       </c>
       <c r="B79" t="s">
-        <v>59</v>
+        <v>102</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -6566,7 +6607,7 @@
         <v>14</v>
       </c>
       <c r="B80" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="C80">
         <v>1</v>
@@ -6577,7 +6618,7 @@
         <v>14</v>
       </c>
       <c r="B81" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -6588,7 +6629,7 @@
         <v>14</v>
       </c>
       <c r="B82" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="C82">
         <v>1</v>
@@ -6599,7 +6640,7 @@
         <v>14</v>
       </c>
       <c r="B83" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -6610,7 +6651,7 @@
         <v>14</v>
       </c>
       <c r="B84" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C84">
         <v>1</v>
@@ -6621,7 +6662,7 @@
         <v>14</v>
       </c>
       <c r="B85" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -6632,7 +6673,7 @@
         <v>14</v>
       </c>
       <c r="B86" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
       <c r="C86">
         <v>1</v>
@@ -6643,7 +6684,7 @@
         <v>14</v>
       </c>
       <c r="B87" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C87">
         <v>1</v>
@@ -6654,7 +6695,7 @@
         <v>14</v>
       </c>
       <c r="B88" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -6665,7 +6706,7 @@
         <v>14</v>
       </c>
       <c r="B89" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -6676,7 +6717,7 @@
         <v>14</v>
       </c>
       <c r="B90" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="C90">
         <v>1</v>
@@ -6687,7 +6728,7 @@
         <v>14</v>
       </c>
       <c r="B91" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C91">
         <v>1</v>
@@ -6698,7 +6739,7 @@
         <v>14</v>
       </c>
       <c r="B92" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="C92">
         <v>1</v>
@@ -6720,7 +6761,7 @@
         <v>14</v>
       </c>
       <c r="B94" t="s">
-        <v>51</v>
+        <v>101</v>
       </c>
       <c r="C94">
         <v>1</v>
@@ -6731,7 +6772,7 @@
         <v>14</v>
       </c>
       <c r="B95" t="s">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="C95">
         <v>1</v>
@@ -6753,7 +6794,7 @@
         <v>14</v>
       </c>
       <c r="B97" t="s">
-        <v>72</v>
+        <v>117</v>
       </c>
       <c r="C97">
         <v>1</v>
@@ -6764,7 +6805,7 @@
         <v>14</v>
       </c>
       <c r="B98" t="s">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -6783,24 +6824,24 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B100" t="s">
-        <v>71</v>
+        <v>119</v>
       </c>
       <c r="C100">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B101" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C101">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -6808,10 +6849,10 @@
         <v>15</v>
       </c>
       <c r="B102" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C102">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -6819,10 +6860,10 @@
         <v>15</v>
       </c>
       <c r="B103" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C103">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -6830,10 +6871,10 @@
         <v>15</v>
       </c>
       <c r="B104" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C104">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -6841,10 +6882,10 @@
         <v>15</v>
       </c>
       <c r="B105" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C105">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -6852,10 +6893,10 @@
         <v>15</v>
       </c>
       <c r="B106" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="C106">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -6863,10 +6904,10 @@
         <v>15</v>
       </c>
       <c r="B107" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="C107">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -6874,10 +6915,10 @@
         <v>15</v>
       </c>
       <c r="B108" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="C108">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -6885,10 +6926,10 @@
         <v>15</v>
       </c>
       <c r="B109" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="C109">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -6896,7 +6937,7 @@
         <v>15</v>
       </c>
       <c r="B110" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C110">
         <v>4</v>
@@ -6907,7 +6948,7 @@
         <v>15</v>
       </c>
       <c r="B111" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C111">
         <v>4</v>
@@ -6918,7 +6959,7 @@
         <v>15</v>
       </c>
       <c r="B112" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C112">
         <v>4</v>
@@ -6929,10 +6970,10 @@
         <v>15</v>
       </c>
       <c r="B113" t="s">
-        <v>129</v>
+        <v>81</v>
       </c>
       <c r="C113">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -6940,10 +6981,10 @@
         <v>15</v>
       </c>
       <c r="B114" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C114">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -6951,7 +6992,7 @@
         <v>15</v>
       </c>
       <c r="B115" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="C115">
         <v>3</v>
@@ -6962,7 +7003,7 @@
         <v>15</v>
       </c>
       <c r="B116" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C116">
         <v>3</v>
@@ -6973,7 +7014,7 @@
         <v>15</v>
       </c>
       <c r="B117" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C117">
         <v>3</v>
@@ -6984,10 +7025,10 @@
         <v>15</v>
       </c>
       <c r="B118" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C118">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -6998,7 +7039,7 @@
         <v>134</v>
       </c>
       <c r="C119">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -7017,7 +7058,7 @@
         <v>15</v>
       </c>
       <c r="B121" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C121">
         <v>2</v>
@@ -7028,7 +7069,7 @@
         <v>15</v>
       </c>
       <c r="B122" t="s">
-        <v>137</v>
+        <v>62</v>
       </c>
       <c r="C122">
         <v>2</v>
@@ -7039,7 +7080,7 @@
         <v>15</v>
       </c>
       <c r="B123" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C123">
         <v>2</v>
@@ -7050,7 +7091,7 @@
         <v>15</v>
       </c>
       <c r="B124" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C124">
         <v>2</v>
@@ -7061,7 +7102,7 @@
         <v>15</v>
       </c>
       <c r="B125" t="s">
-        <v>49</v>
+        <v>138</v>
       </c>
       <c r="C125">
         <v>2</v>
@@ -7072,7 +7113,7 @@
         <v>15</v>
       </c>
       <c r="B126" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C126">
         <v>2</v>
@@ -7083,7 +7124,7 @@
         <v>15</v>
       </c>
       <c r="B127" t="s">
-        <v>141</v>
+        <v>49</v>
       </c>
       <c r="C127">
         <v>2</v>
@@ -7094,10 +7135,10 @@
         <v>15</v>
       </c>
       <c r="B128" t="s">
-        <v>62</v>
+        <v>169</v>
       </c>
       <c r="C128">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -7105,10 +7146,10 @@
         <v>15</v>
       </c>
       <c r="B129" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="C129">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -7116,10 +7157,10 @@
         <v>15</v>
       </c>
       <c r="B130" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
       <c r="C130">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -7127,7 +7168,7 @@
         <v>15</v>
       </c>
       <c r="B131" t="s">
-        <v>144</v>
+        <v>187</v>
       </c>
       <c r="C131">
         <v>1</v>
@@ -7138,7 +7179,7 @@
         <v>15</v>
       </c>
       <c r="B132" t="s">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="C132">
         <v>1</v>
@@ -7160,7 +7201,7 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="C134">
         <v>1</v>
@@ -7171,7 +7212,7 @@
         <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>148</v>
+        <v>188</v>
       </c>
       <c r="C135">
         <v>1</v>
@@ -7182,7 +7223,7 @@
         <v>15</v>
       </c>
       <c r="B136" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="C136">
         <v>1</v>
@@ -7193,7 +7234,7 @@
         <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="C137">
         <v>1</v>
@@ -7204,7 +7245,7 @@
         <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>151</v>
+        <v>186</v>
       </c>
       <c r="C138">
         <v>1</v>
@@ -7215,7 +7256,7 @@
         <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C139">
         <v>1</v>
@@ -7226,7 +7267,7 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="C140">
         <v>1</v>
@@ -7237,7 +7278,7 @@
         <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>67</v>
+        <v>153</v>
       </c>
       <c r="C141">
         <v>1</v>
@@ -7248,7 +7289,7 @@
         <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="C142">
         <v>1</v>
@@ -7270,7 +7311,7 @@
         <v>15</v>
       </c>
       <c r="B144" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="C144">
         <v>1</v>
@@ -7281,7 +7322,7 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="C145">
         <v>1</v>
@@ -7292,7 +7333,7 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="C146">
         <v>1</v>
@@ -7314,7 +7355,7 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="C148">
         <v>1</v>
@@ -7336,7 +7377,7 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
       <c r="C150">
         <v>1</v>
@@ -7347,7 +7388,7 @@
         <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="C151">
         <v>1</v>
@@ -7358,7 +7399,7 @@
         <v>15</v>
       </c>
       <c r="B152" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="C152">
         <v>1</v>
@@ -7369,7 +7410,7 @@
         <v>15</v>
       </c>
       <c r="B153" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="C153">
         <v>1</v>
@@ -7380,7 +7421,7 @@
         <v>15</v>
       </c>
       <c r="B154" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="C154">
         <v>1</v>
@@ -7391,7 +7432,7 @@
         <v>15</v>
       </c>
       <c r="B155" t="s">
-        <v>83</v>
+        <v>166</v>
       </c>
       <c r="C155">
         <v>1</v>
@@ -7402,7 +7443,7 @@
         <v>15</v>
       </c>
       <c r="B156" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="C156">
         <v>1</v>
@@ -7424,7 +7465,7 @@
         <v>15</v>
       </c>
       <c r="B158" t="s">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="C158">
         <v>1</v>
@@ -7446,7 +7487,7 @@
         <v>15</v>
       </c>
       <c r="B160" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="C160">
         <v>1</v>
@@ -7457,7 +7498,7 @@
         <v>15</v>
       </c>
       <c r="B161" t="s">
-        <v>172</v>
+        <v>97</v>
       </c>
       <c r="C161">
         <v>1</v>
@@ -7468,7 +7509,7 @@
         <v>15</v>
       </c>
       <c r="B162" t="s">
-        <v>98</v>
+        <v>164</v>
       </c>
       <c r="C162">
         <v>1</v>
@@ -7479,7 +7520,7 @@
         <v>15</v>
       </c>
       <c r="B163" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -7490,7 +7531,7 @@
         <v>15</v>
       </c>
       <c r="B164" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="C164">
         <v>1</v>
@@ -7501,7 +7542,7 @@
         <v>15</v>
       </c>
       <c r="B165" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C165">
         <v>1</v>
@@ -7512,7 +7553,7 @@
         <v>15</v>
       </c>
       <c r="B166" t="s">
-        <v>68</v>
+        <v>163</v>
       </c>
       <c r="C166">
         <v>1</v>
@@ -7523,7 +7564,7 @@
         <v>15</v>
       </c>
       <c r="B167" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -7534,7 +7575,7 @@
         <v>15</v>
       </c>
       <c r="B168" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="C168">
         <v>1</v>
@@ -7545,7 +7586,7 @@
         <v>15</v>
       </c>
       <c r="B169" t="s">
-        <v>178</v>
+        <v>88</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -7556,7 +7597,7 @@
         <v>15</v>
       </c>
       <c r="B170" t="s">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -7567,7 +7608,7 @@
         <v>15</v>
       </c>
       <c r="B171" t="s">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="C171">
         <v>1</v>
@@ -7578,7 +7619,7 @@
         <v>15</v>
       </c>
       <c r="B172" t="s">
-        <v>181</v>
+        <v>67</v>
       </c>
       <c r="C172">
         <v>1</v>
@@ -7589,7 +7630,7 @@
         <v>15</v>
       </c>
       <c r="B173" t="s">
-        <v>182</v>
+        <v>70</v>
       </c>
       <c r="C173">
         <v>1</v>
@@ -7600,7 +7641,7 @@
         <v>15</v>
       </c>
       <c r="B174" t="s">
-        <v>70</v>
+        <v>144</v>
       </c>
       <c r="C174">
         <v>1</v>
@@ -7611,7 +7652,7 @@
         <v>15</v>
       </c>
       <c r="B175" t="s">
-        <v>183</v>
+        <v>68</v>
       </c>
       <c r="C175">
         <v>1</v>
@@ -7622,7 +7663,7 @@
         <v>15</v>
       </c>
       <c r="B176" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -7633,7 +7674,7 @@
         <v>15</v>
       </c>
       <c r="B177" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -7644,7 +7685,7 @@
         <v>15</v>
       </c>
       <c r="B178" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -7655,7 +7696,7 @@
         <v>15</v>
       </c>
       <c r="B179" t="s">
-        <v>88</v>
+        <v>178</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -7666,7 +7707,7 @@
         <v>15</v>
       </c>
       <c r="B180" t="s">
-        <v>187</v>
+        <v>142</v>
       </c>
       <c r="C180">
         <v>1</v>
@@ -7677,7 +7718,7 @@
         <v>15</v>
       </c>
       <c r="B181" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C181">
         <v>1</v>
@@ -7688,7 +7729,7 @@
         <v>15</v>
       </c>
       <c r="B182" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C182">
         <v>1</v>
@@ -7699,7 +7740,7 @@
         <v>15</v>
       </c>
       <c r="B183" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C183">
         <v>1</v>
@@ -7710,7 +7751,7 @@
         <v>15</v>
       </c>
       <c r="B184" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C184">
         <v>1</v>
@@ -7718,24 +7759,24 @@
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B185" t="s">
-        <v>192</v>
+        <v>49</v>
       </c>
       <c r="C185">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B186" t="s">
-        <v>193</v>
+        <v>43</v>
       </c>
       <c r="C186">
-        <v>1</v>
+        <v>22</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -7743,10 +7784,10 @@
         <v>16</v>
       </c>
       <c r="B187" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C187">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -7754,10 +7795,10 @@
         <v>16</v>
       </c>
       <c r="B188" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="C188">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -7765,10 +7806,10 @@
         <v>16</v>
       </c>
       <c r="B189" t="s">
-        <v>54</v>
+        <v>116</v>
       </c>
       <c r="C189">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -7776,10 +7817,10 @@
         <v>16</v>
       </c>
       <c r="B190" t="s">
-        <v>66</v>
+        <v>194</v>
       </c>
       <c r="C190">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -7787,10 +7828,10 @@
         <v>16</v>
       </c>
       <c r="B191" t="s">
-        <v>117</v>
+        <v>65</v>
       </c>
       <c r="C191">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -7798,10 +7839,10 @@
         <v>16</v>
       </c>
       <c r="B192" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C192">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -7809,7 +7850,7 @@
         <v>16</v>
       </c>
       <c r="B193" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="C193">
         <v>12</v>
@@ -7820,10 +7861,10 @@
         <v>16</v>
       </c>
       <c r="B194" t="s">
-        <v>194</v>
+        <v>46</v>
       </c>
       <c r="C194">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -7831,10 +7872,10 @@
         <v>16</v>
       </c>
       <c r="B195" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C195">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -7842,10 +7883,10 @@
         <v>16</v>
       </c>
       <c r="B196" t="s">
-        <v>46</v>
+        <v>195</v>
       </c>
       <c r="C196">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -7853,7 +7894,7 @@
         <v>16</v>
       </c>
       <c r="B197" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C197">
         <v>10</v>
@@ -7864,10 +7905,10 @@
         <v>16</v>
       </c>
       <c r="B198" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="C198">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -7878,7 +7919,7 @@
         <v>196</v>
       </c>
       <c r="C199">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -7886,10 +7927,10 @@
         <v>16</v>
       </c>
       <c r="B200" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="C200">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -7897,7 +7938,7 @@
         <v>16</v>
       </c>
       <c r="B201" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="C201">
         <v>7</v>
@@ -7919,7 +7960,7 @@
         <v>16</v>
       </c>
       <c r="B203" t="s">
-        <v>197</v>
+        <v>57</v>
       </c>
       <c r="C203">
         <v>6</v>
@@ -7930,10 +7971,10 @@
         <v>16</v>
       </c>
       <c r="B204" t="s">
-        <v>52</v>
+        <v>200</v>
       </c>
       <c r="C204">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -7941,10 +7982,10 @@
         <v>16</v>
       </c>
       <c r="B205" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="C205">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -7952,7 +7993,7 @@
         <v>16</v>
       </c>
       <c r="B206" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C206">
         <v>5</v>
@@ -7963,7 +8004,7 @@
         <v>16</v>
       </c>
       <c r="B207" t="s">
-        <v>200</v>
+        <v>73</v>
       </c>
       <c r="C207">
         <v>5</v>
@@ -7974,10 +8015,10 @@
         <v>16</v>
       </c>
       <c r="B208" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C208">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -7985,10 +8026,10 @@
         <v>16</v>
       </c>
       <c r="B209" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="C209">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -7996,10 +8037,10 @@
         <v>16</v>
       </c>
       <c r="B210" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="C210">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -8007,7 +8048,7 @@
         <v>16</v>
       </c>
       <c r="B211" t="s">
-        <v>60</v>
+        <v>199</v>
       </c>
       <c r="C211">
         <v>4</v>
@@ -8018,7 +8059,7 @@
         <v>16</v>
       </c>
       <c r="B212" t="s">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="C212">
         <v>4</v>
@@ -8029,7 +8070,7 @@
         <v>16</v>
       </c>
       <c r="B213" t="s">
-        <v>47</v>
+        <v>92</v>
       </c>
       <c r="C213">
         <v>4</v>
@@ -8040,10 +8081,10 @@
         <v>16</v>
       </c>
       <c r="B214" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C214">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -8051,10 +8092,10 @@
         <v>16</v>
       </c>
       <c r="B215" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
       <c r="C215">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -8062,7 +8103,7 @@
         <v>16</v>
       </c>
       <c r="B216" t="s">
-        <v>115</v>
+        <v>74</v>
       </c>
       <c r="C216">
         <v>3</v>
@@ -8073,7 +8114,7 @@
         <v>16</v>
       </c>
       <c r="B217" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="C217">
         <v>3</v>
@@ -8084,7 +8125,7 @@
         <v>16</v>
       </c>
       <c r="B218" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="C218">
         <v>3</v>
@@ -8095,7 +8136,7 @@
         <v>16</v>
       </c>
       <c r="B219" t="s">
-        <v>76</v>
+        <v>118</v>
       </c>
       <c r="C219">
         <v>3</v>
@@ -8106,7 +8147,7 @@
         <v>16</v>
       </c>
       <c r="B220" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C220">
         <v>3</v>
@@ -8117,7 +8158,7 @@
         <v>16</v>
       </c>
       <c r="B221" t="s">
-        <v>119</v>
+        <v>68</v>
       </c>
       <c r="C221">
         <v>3</v>
@@ -8128,10 +8169,10 @@
         <v>16</v>
       </c>
       <c r="B222" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C222">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -8139,10 +8180,10 @@
         <v>16</v>
       </c>
       <c r="B223" t="s">
-        <v>44</v>
+        <v>203</v>
       </c>
       <c r="C223">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -8150,10 +8191,10 @@
         <v>16</v>
       </c>
       <c r="B224" t="s">
-        <v>68</v>
+        <v>207</v>
       </c>
       <c r="C224">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -8161,7 +8202,7 @@
         <v>16</v>
       </c>
       <c r="B225" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="C225">
         <v>2</v>
@@ -8183,7 +8224,7 @@
         <v>16</v>
       </c>
       <c r="B227" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C227">
         <v>2</v>
@@ -8194,7 +8235,7 @@
         <v>16</v>
       </c>
       <c r="B228" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="C228">
         <v>2</v>
@@ -8205,7 +8246,7 @@
         <v>16</v>
       </c>
       <c r="B229" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C229">
         <v>2</v>
@@ -8216,7 +8257,7 @@
         <v>16</v>
       </c>
       <c r="B230" t="s">
-        <v>207</v>
+        <v>64</v>
       </c>
       <c r="C230">
         <v>2</v>
@@ -8230,7 +8271,7 @@
         <v>208</v>
       </c>
       <c r="C231">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -8238,10 +8279,10 @@
         <v>16</v>
       </c>
       <c r="B232" t="s">
-        <v>64</v>
+        <v>237</v>
       </c>
       <c r="C232">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -8249,7 +8290,7 @@
         <v>16</v>
       </c>
       <c r="B233" t="s">
-        <v>209</v>
+        <v>115</v>
       </c>
       <c r="C233">
         <v>1</v>
@@ -8260,7 +8301,7 @@
         <v>16</v>
       </c>
       <c r="B234" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="C234">
         <v>1</v>
@@ -8271,7 +8312,7 @@
         <v>16</v>
       </c>
       <c r="B235" t="s">
-        <v>116</v>
+        <v>212</v>
       </c>
       <c r="C235">
         <v>1</v>
@@ -8282,7 +8323,7 @@
         <v>16</v>
       </c>
       <c r="B236" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="C236">
         <v>1</v>
@@ -8293,7 +8334,7 @@
         <v>16</v>
       </c>
       <c r="B237" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -8304,7 +8345,7 @@
         <v>16</v>
       </c>
       <c r="B238" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -8315,7 +8356,7 @@
         <v>16</v>
       </c>
       <c r="B239" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -8326,7 +8367,7 @@
         <v>16</v>
       </c>
       <c r="B240" t="s">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="C240">
         <v>1</v>
@@ -8337,7 +8378,7 @@
         <v>16</v>
       </c>
       <c r="B241" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -8348,7 +8389,7 @@
         <v>16</v>
       </c>
       <c r="B242" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -8359,7 +8400,7 @@
         <v>16</v>
       </c>
       <c r="B243" t="s">
-        <v>120</v>
+        <v>221</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -8370,7 +8411,7 @@
         <v>16</v>
       </c>
       <c r="B244" t="s">
-        <v>244</v>
+        <v>217</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -8381,7 +8422,7 @@
         <v>16</v>
       </c>
       <c r="B245" t="s">
-        <v>219</v>
+        <v>119</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -8392,7 +8433,7 @@
         <v>16</v>
       </c>
       <c r="B246" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="C246">
         <v>1</v>
@@ -8403,7 +8444,7 @@
         <v>16</v>
       </c>
       <c r="B247" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="C247">
         <v>1</v>
@@ -8414,7 +8455,7 @@
         <v>16</v>
       </c>
       <c r="B248" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C248">
         <v>1</v>
@@ -8425,7 +8466,7 @@
         <v>16</v>
       </c>
       <c r="B249" t="s">
-        <v>69</v>
+        <v>235</v>
       </c>
       <c r="C249">
         <v>1</v>
@@ -8436,7 +8477,7 @@
         <v>16</v>
       </c>
       <c r="B250" t="s">
-        <v>241</v>
+        <v>126</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -8447,7 +8488,7 @@
         <v>16</v>
       </c>
       <c r="B251" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="C251">
         <v>1</v>
@@ -8458,7 +8499,7 @@
         <v>16</v>
       </c>
       <c r="B252" t="s">
-        <v>127</v>
+        <v>223</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -8469,7 +8510,7 @@
         <v>16</v>
       </c>
       <c r="B253" t="s">
-        <v>242</v>
+        <v>226</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -8480,7 +8521,7 @@
         <v>16</v>
       </c>
       <c r="B254" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -8491,7 +8532,7 @@
         <v>16</v>
       </c>
       <c r="B255" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -8502,7 +8543,7 @@
         <v>16</v>
       </c>
       <c r="B256" t="s">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -8513,7 +8554,7 @@
         <v>16</v>
       </c>
       <c r="B257" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -8524,7 +8565,7 @@
         <v>16</v>
       </c>
       <c r="B258" t="s">
-        <v>210</v>
+        <v>239</v>
       </c>
       <c r="C258">
         <v>1</v>
@@ -8535,7 +8576,7 @@
         <v>16</v>
       </c>
       <c r="B259" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C259">
         <v>1</v>
@@ -8546,7 +8587,7 @@
         <v>16</v>
       </c>
       <c r="B260" t="s">
-        <v>221</v>
+        <v>243</v>
       </c>
       <c r="C260">
         <v>1</v>
@@ -8557,7 +8598,7 @@
         <v>16</v>
       </c>
       <c r="B261" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C261">
         <v>1</v>
@@ -8568,7 +8609,7 @@
         <v>16</v>
       </c>
       <c r="B262" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="C262">
         <v>1</v>
@@ -8579,7 +8620,7 @@
         <v>16</v>
       </c>
       <c r="B263" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="C263">
         <v>1</v>
@@ -8601,7 +8642,7 @@
         <v>16</v>
       </c>
       <c r="B265" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="C265">
         <v>1</v>
@@ -8612,7 +8653,7 @@
         <v>16</v>
       </c>
       <c r="B266" t="s">
-        <v>215</v>
+        <v>69</v>
       </c>
       <c r="C266">
         <v>1</v>
@@ -8623,7 +8664,7 @@
         <v>16</v>
       </c>
       <c r="B267" t="s">
-        <v>245</v>
+        <v>224</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -8634,7 +8675,7 @@
         <v>16</v>
       </c>
       <c r="B268" t="s">
-        <v>212</v>
+        <v>250</v>
       </c>
       <c r="C268">
         <v>1</v>
@@ -8645,7 +8686,7 @@
         <v>16</v>
       </c>
       <c r="B269" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="C269">
         <v>1</v>
@@ -8656,7 +8697,7 @@
         <v>16</v>
       </c>
       <c r="B270" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="C270">
         <v>1</v>
@@ -8667,7 +8708,7 @@
         <v>16</v>
       </c>
       <c r="B271" t="s">
-        <v>226</v>
+        <v>70</v>
       </c>
       <c r="C271">
         <v>1</v>
@@ -8678,7 +8719,7 @@
         <v>16</v>
       </c>
       <c r="B272" t="s">
-        <v>234</v>
+        <v>216</v>
       </c>
       <c r="C272">
         <v>1</v>
@@ -8689,7 +8730,7 @@
         <v>16</v>
       </c>
       <c r="B273" t="s">
-        <v>243</v>
+        <v>121</v>
       </c>
       <c r="C273">
         <v>1</v>
@@ -8700,7 +8741,7 @@
         <v>16</v>
       </c>
       <c r="B274" t="s">
-        <v>70</v>
+        <v>211</v>
       </c>
       <c r="C274">
         <v>1</v>
@@ -8711,7 +8752,7 @@
         <v>16</v>
       </c>
       <c r="B275" t="s">
-        <v>211</v>
+        <v>58</v>
       </c>
       <c r="C275">
         <v>1</v>
@@ -8719,24 +8760,24 @@
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B276" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C276">
-        <v>1</v>
+        <v>39</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B277" t="s">
-        <v>58</v>
+        <v>189</v>
       </c>
       <c r="C277">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -8744,10 +8785,10 @@
         <v>21</v>
       </c>
       <c r="B278" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="C278">
-        <v>39</v>
+        <v>10</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -8755,10 +8796,10 @@
         <v>21</v>
       </c>
       <c r="B279" t="s">
-        <v>190</v>
+        <v>103</v>
       </c>
       <c r="C279">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -8766,10 +8807,10 @@
         <v>21</v>
       </c>
       <c r="B280" t="s">
-        <v>133</v>
+        <v>202</v>
       </c>
       <c r="C280">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -8777,10 +8818,10 @@
         <v>21</v>
       </c>
       <c r="B281" t="s">
-        <v>104</v>
+        <v>245</v>
       </c>
       <c r="C281">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -8788,10 +8829,10 @@
         <v>21</v>
       </c>
       <c r="B282" t="s">
-        <v>203</v>
+        <v>120</v>
       </c>
       <c r="C282">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -8799,10 +8840,10 @@
         <v>21</v>
       </c>
       <c r="B283" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C283">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -8810,10 +8851,10 @@
         <v>21</v>
       </c>
       <c r="B284" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="C284">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
@@ -8821,7 +8862,7 @@
         <v>21</v>
       </c>
       <c r="B285" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C285">
         <v>5</v>
@@ -8832,7 +8873,7 @@
         <v>21</v>
       </c>
       <c r="B286" t="s">
-        <v>143</v>
+        <v>248</v>
       </c>
       <c r="C286">
         <v>5</v>
@@ -8843,10 +8884,10 @@
         <v>21</v>
       </c>
       <c r="B287" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C287">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
@@ -8854,10 +8895,10 @@
         <v>21</v>
       </c>
       <c r="B288" t="s">
-        <v>248</v>
+        <v>128</v>
       </c>
       <c r="C288">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -8865,7 +8906,7 @@
         <v>21</v>
       </c>
       <c r="B289" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="C289">
         <v>4</v>
@@ -8876,7 +8917,7 @@
         <v>21</v>
       </c>
       <c r="B290" t="s">
-        <v>250</v>
+        <v>133</v>
       </c>
       <c r="C290">
         <v>4</v>
@@ -8887,10 +8928,10 @@
         <v>21</v>
       </c>
       <c r="B291" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="C291">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
@@ -8898,10 +8939,10 @@
         <v>21</v>
       </c>
       <c r="B292" t="s">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="C292">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
@@ -8909,7 +8950,7 @@
         <v>21</v>
       </c>
       <c r="B293" t="s">
-        <v>197</v>
+        <v>250</v>
       </c>
       <c r="C293">
         <v>3</v>
@@ -8920,7 +8961,7 @@
         <v>21</v>
       </c>
       <c r="B294" t="s">
-        <v>251</v>
+        <v>163</v>
       </c>
       <c r="C294">
         <v>3</v>
@@ -8931,7 +8972,7 @@
         <v>21</v>
       </c>
       <c r="B295" t="s">
-        <v>44</v>
+        <v>252</v>
       </c>
       <c r="C295">
         <v>3</v>
@@ -8942,7 +8983,7 @@
         <v>21</v>
       </c>
       <c r="B296" t="s">
-        <v>164</v>
+        <v>253</v>
       </c>
       <c r="C296">
         <v>3</v>
@@ -8953,7 +8994,7 @@
         <v>21</v>
       </c>
       <c r="B297" t="s">
-        <v>253</v>
+        <v>44</v>
       </c>
       <c r="C297">
         <v>3</v>
@@ -8975,7 +9016,7 @@
         <v>21</v>
       </c>
       <c r="B299" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C299">
         <v>3</v>
@@ -8986,7 +9027,7 @@
         <v>21</v>
       </c>
       <c r="B300" t="s">
-        <v>255</v>
+        <v>196</v>
       </c>
       <c r="C300">
         <v>3</v>
@@ -8997,10 +9038,10 @@
         <v>21</v>
       </c>
       <c r="B301" t="s">
-        <v>81</v>
+        <v>171</v>
       </c>
       <c r="C301">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
@@ -9008,10 +9049,10 @@
         <v>21</v>
       </c>
       <c r="B302" t="s">
-        <v>127</v>
+        <v>198</v>
       </c>
       <c r="C302">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -9019,7 +9060,7 @@
         <v>21</v>
       </c>
       <c r="B303" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="C303">
         <v>2</v>
@@ -9030,7 +9071,7 @@
         <v>21</v>
       </c>
       <c r="B304" t="s">
-        <v>259</v>
+        <v>136</v>
       </c>
       <c r="C304">
         <v>2</v>
@@ -9041,7 +9082,7 @@
         <v>21</v>
       </c>
       <c r="B305" t="s">
-        <v>172</v>
+        <v>258</v>
       </c>
       <c r="C305">
         <v>2</v>
@@ -9052,7 +9093,7 @@
         <v>21</v>
       </c>
       <c r="B306" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="C306">
         <v>2</v>
@@ -9063,7 +9104,7 @@
         <v>21</v>
       </c>
       <c r="B307" t="s">
-        <v>199</v>
+        <v>77</v>
       </c>
       <c r="C307">
         <v>2</v>
@@ -9074,7 +9115,7 @@
         <v>21</v>
       </c>
       <c r="B308" t="s">
-        <v>174</v>
+        <v>257</v>
       </c>
       <c r="C308">
         <v>2</v>
@@ -9085,7 +9126,7 @@
         <v>21</v>
       </c>
       <c r="B309" t="s">
-        <v>54</v>
+        <v>256</v>
       </c>
       <c r="C309">
         <v>2</v>
@@ -9096,7 +9137,7 @@
         <v>21</v>
       </c>
       <c r="B310" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="C310">
         <v>2</v>
@@ -9107,7 +9148,7 @@
         <v>21</v>
       </c>
       <c r="B311" t="s">
-        <v>273</v>
+        <v>85</v>
       </c>
       <c r="C311">
         <v>2</v>
@@ -9118,7 +9159,7 @@
         <v>21</v>
       </c>
       <c r="B312" t="s">
-        <v>77</v>
+        <v>251</v>
       </c>
       <c r="C312">
         <v>2</v>
@@ -9129,7 +9170,7 @@
         <v>21</v>
       </c>
       <c r="B313" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C313">
         <v>2</v>
@@ -9140,7 +9181,7 @@
         <v>21</v>
       </c>
       <c r="B314" t="s">
-        <v>258</v>
+        <v>54</v>
       </c>
       <c r="C314">
         <v>2</v>
@@ -9151,7 +9192,7 @@
         <v>21</v>
       </c>
       <c r="B315" t="s">
-        <v>256</v>
+        <v>199</v>
       </c>
       <c r="C315">
         <v>2</v>
@@ -9162,7 +9203,7 @@
         <v>21</v>
       </c>
       <c r="B316" t="s">
-        <v>226</v>
+        <v>62</v>
       </c>
       <c r="C316">
         <v>2</v>
@@ -9173,7 +9214,7 @@
         <v>21</v>
       </c>
       <c r="B317" t="s">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="C317">
         <v>2</v>
@@ -9184,10 +9225,10 @@
         <v>21</v>
       </c>
       <c r="B318" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C318">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
@@ -9195,10 +9236,10 @@
         <v>21</v>
       </c>
       <c r="B319" t="s">
-        <v>137</v>
+        <v>214</v>
       </c>
       <c r="C319">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
@@ -9206,10 +9247,10 @@
         <v>21</v>
       </c>
       <c r="B320" t="s">
-        <v>70</v>
+        <v>270</v>
       </c>
       <c r="C320">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
@@ -9217,7 +9258,7 @@
         <v>21</v>
       </c>
       <c r="B321" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C321">
         <v>1</v>
@@ -9228,7 +9269,7 @@
         <v>21</v>
       </c>
       <c r="B322" t="s">
-        <v>92</v>
+        <v>276</v>
       </c>
       <c r="C322">
         <v>1</v>
@@ -9239,7 +9280,7 @@
         <v>21</v>
       </c>
       <c r="B323" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="C323">
         <v>1</v>
@@ -9250,7 +9291,7 @@
         <v>21</v>
       </c>
       <c r="B324" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C324">
         <v>1</v>
@@ -9261,7 +9302,7 @@
         <v>21</v>
       </c>
       <c r="B325" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -9272,7 +9313,7 @@
         <v>21</v>
       </c>
       <c r="B326" t="s">
-        <v>265</v>
+        <v>137</v>
       </c>
       <c r="C326">
         <v>1</v>
@@ -9283,7 +9324,7 @@
         <v>21</v>
       </c>
       <c r="B327" t="s">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="C327">
         <v>1</v>
@@ -9294,7 +9335,7 @@
         <v>21</v>
       </c>
       <c r="B328" t="s">
-        <v>266</v>
+        <v>92</v>
       </c>
       <c r="C328">
         <v>1</v>
@@ -9305,7 +9346,7 @@
         <v>21</v>
       </c>
       <c r="B329" t="s">
-        <v>138</v>
+        <v>268</v>
       </c>
       <c r="C329">
         <v>1</v>
@@ -9316,7 +9357,7 @@
         <v>21</v>
       </c>
       <c r="B330" t="s">
-        <v>268</v>
+        <v>125</v>
       </c>
       <c r="C330">
         <v>1</v>
@@ -9327,7 +9368,7 @@
         <v>21</v>
       </c>
       <c r="B331" t="s">
-        <v>173</v>
+        <v>281</v>
       </c>
       <c r="C331">
         <v>1</v>
@@ -9338,7 +9379,7 @@
         <v>21</v>
       </c>
       <c r="B332" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="C332">
         <v>1</v>
@@ -9349,7 +9390,7 @@
         <v>21</v>
       </c>
       <c r="B333" t="s">
-        <v>63</v>
+        <v>185</v>
       </c>
       <c r="C333">
         <v>1</v>
@@ -9360,7 +9401,7 @@
         <v>21</v>
       </c>
       <c r="B334" t="s">
-        <v>49</v>
+        <v>165</v>
       </c>
       <c r="C334">
         <v>1</v>
@@ -9371,7 +9412,7 @@
         <v>21</v>
       </c>
       <c r="B335" t="s">
-        <v>280</v>
+        <v>49</v>
       </c>
       <c r="C335">
         <v>1</v>
@@ -9382,7 +9423,7 @@
         <v>21</v>
       </c>
       <c r="B336" t="s">
-        <v>186</v>
+        <v>115</v>
       </c>
       <c r="C336">
         <v>1</v>
@@ -9393,7 +9434,7 @@
         <v>21</v>
       </c>
       <c r="B337" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="C337">
         <v>1</v>
@@ -9404,7 +9445,7 @@
         <v>21</v>
       </c>
       <c r="B338" t="s">
-        <v>272</v>
+        <v>138</v>
       </c>
       <c r="C338">
         <v>1</v>
@@ -9415,7 +9456,7 @@
         <v>21</v>
       </c>
       <c r="B339" t="s">
-        <v>166</v>
+        <v>274</v>
       </c>
       <c r="C339">
         <v>1</v>
@@ -9426,7 +9467,7 @@
         <v>21</v>
       </c>
       <c r="B340" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="C340">
         <v>1</v>
@@ -9437,7 +9478,7 @@
         <v>21</v>
       </c>
       <c r="B341" t="s">
-        <v>215</v>
+        <v>275</v>
       </c>
       <c r="C341">
         <v>1</v>
@@ -9448,7 +9489,7 @@
         <v>21</v>
       </c>
       <c r="B342" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="C342">
         <v>1</v>
@@ -9459,7 +9500,7 @@
         <v>21</v>
       </c>
       <c r="B343" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="C343">
         <v>1</v>
@@ -9470,7 +9511,7 @@
         <v>21</v>
       </c>
       <c r="B344" t="s">
-        <v>276</v>
+        <v>172</v>
       </c>
       <c r="C344">
         <v>1</v>
@@ -9481,7 +9522,7 @@
         <v>21</v>
       </c>
       <c r="B345" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
       <c r="C345">
         <v>1</v>
@@ -9492,7 +9533,7 @@
         <v>21</v>
       </c>
       <c r="B346" t="s">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="C346">
         <v>1</v>
@@ -9503,7 +9544,7 @@
         <v>21</v>
       </c>
       <c r="B347" t="s">
-        <v>139</v>
+        <v>277</v>
       </c>
       <c r="C347">
         <v>1</v>
@@ -9514,7 +9555,7 @@
         <v>21</v>
       </c>
       <c r="B348" t="s">
-        <v>279</v>
+        <v>148</v>
       </c>
       <c r="C348">
         <v>1</v>
@@ -9525,7 +9566,7 @@
         <v>21</v>
       </c>
       <c r="B349" t="s">
-        <v>260</v>
+        <v>174</v>
       </c>
       <c r="C349">
         <v>1</v>
@@ -9536,7 +9577,7 @@
         <v>21</v>
       </c>
       <c r="B350" t="s">
-        <v>116</v>
+        <v>261</v>
       </c>
       <c r="C350">
         <v>1</v>
@@ -9547,7 +9588,7 @@
         <v>21</v>
       </c>
       <c r="B351" t="s">
-        <v>126</v>
+        <v>282</v>
       </c>
       <c r="C351">
         <v>1</v>
@@ -9558,7 +9599,7 @@
         <v>21</v>
       </c>
       <c r="B352" t="s">
-        <v>175</v>
+        <v>260</v>
       </c>
       <c r="C352">
         <v>1</v>
@@ -9569,7 +9610,7 @@
         <v>21</v>
       </c>
       <c r="B353" t="s">
-        <v>149</v>
+        <v>283</v>
       </c>
       <c r="C353">
         <v>1</v>
@@ -9580,42 +9621,9 @@
         <v>21</v>
       </c>
       <c r="B354" t="s">
-        <v>282</v>
+        <v>269</v>
       </c>
       <c r="C354">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A355" t="s">
-        <v>21</v>
-      </c>
-      <c r="B355" t="s">
-        <v>262</v>
-      </c>
-      <c r="C355">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A356" t="s">
-        <v>21</v>
-      </c>
-      <c r="B356" t="s">
-        <v>283</v>
-      </c>
-      <c r="C356">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A357" t="s">
-        <v>21</v>
-      </c>
-      <c r="B357" t="s">
-        <v>284</v>
-      </c>
-      <c r="C357">
         <v>1</v>
       </c>
     </row>
@@ -9637,10 +9645,10 @@
         <v>37</v>
       </c>
       <c r="B1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C1" t="s">
         <v>286</v>
-      </c>
-      <c r="C1" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -9648,10 +9656,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C2">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -9659,10 +9667,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C3">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -9670,7 +9678,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C4">
         <v>36</v>
@@ -9681,7 +9689,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C5">
         <v>11</v>
@@ -9692,7 +9700,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C6">
         <v>7</v>
@@ -9703,7 +9711,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -9714,7 +9722,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -9725,7 +9733,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C9">
         <v>29</v>
@@ -9736,10 +9744,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C10">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -9747,7 +9755,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C11">
         <v>23</v>
@@ -9758,7 +9766,7 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C12">
         <v>30</v>
@@ -9769,7 +9777,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C13">
         <v>26</v>
@@ -9780,10 +9788,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C14">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -9791,7 +9799,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C15">
         <v>4</v>
@@ -9802,7 +9810,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C16">
         <v>13</v>
@@ -9813,10 +9821,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C17">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -9824,7 +9832,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C18">
         <v>33</v>
@@ -9835,7 +9843,7 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C19">
         <v>11</v>
@@ -9846,7 +9854,7 @@
         <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C20">
         <v>2</v>
@@ -9857,7 +9865,7 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C21">
         <v>4</v>
@@ -9868,7 +9876,7 @@
         <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C22">
         <v>2</v>
@@ -9879,7 +9887,7 @@
         <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C23">
         <v>2</v>
@@ -9890,7 +9898,7 @@
         <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C24">
         <v>42</v>
@@ -9901,10 +9909,10 @@
         <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C25">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -9912,7 +9920,7 @@
         <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -9923,7 +9931,7 @@
         <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C27">
         <v>111</v>
@@ -9934,7 +9942,7 @@
         <v>16</v>
       </c>
       <c r="B28" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C28">
         <v>140</v>
@@ -9945,7 +9953,7 @@
         <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C29">
         <v>77</v>
@@ -9956,7 +9964,7 @@
         <v>16</v>
       </c>
       <c r="B30" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C30">
         <v>10</v>
@@ -9967,7 +9975,7 @@
         <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -9978,7 +9986,7 @@
         <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C32">
         <v>7</v>
@@ -9989,7 +9997,7 @@
         <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -10000,10 +10008,10 @@
         <v>21</v>
       </c>
       <c r="B34" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C34">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -10011,7 +10019,7 @@
         <v>21</v>
       </c>
       <c r="B35" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C35">
         <v>9</v>
@@ -10022,10 +10030,10 @@
         <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C36">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -10033,7 +10041,7 @@
         <v>21</v>
       </c>
       <c r="B37" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C37">
         <v>61</v>
@@ -10044,7 +10052,7 @@
         <v>21</v>
       </c>
       <c r="B38" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C38">
         <v>24</v>
@@ -10055,7 +10063,7 @@
         <v>21</v>
       </c>
       <c r="B39" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C39">
         <v>55</v>
@@ -10066,7 +10074,7 @@
         <v>21</v>
       </c>
       <c r="B40" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C40">
         <v>3</v>
@@ -10077,7 +10085,7 @@
         <v>21</v>
       </c>
       <c r="B41" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C41">
         <v>14</v>
@@ -10088,7 +10096,7 @@
         <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C42">
         <v>14</v>
@@ -10099,7 +10107,7 @@
         <v>21</v>
       </c>
       <c r="B43" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C43">
         <v>6</v>

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="103" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F43598EA-D6BF-4954-B274-4663362D5914}"/>
+  <xr:revisionPtr revIDLastSave="104" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6190DAF-664A-4163-9865-F19B4E0C087F}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" tabRatio="667" activeTab="6" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" tabRatio="667" activeTab="2" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="mat_2026" sheetId="1" r:id="rId1"/>
@@ -2261,7 +2261,7 @@
         <v>34</v>
       </c>
       <c r="C2">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2272,7 +2272,7 @@
         <v>35</v>
       </c>
       <c r="C3">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2283,7 +2283,7 @@
         <v>34</v>
       </c>
       <c r="C4">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2294,7 +2294,7 @@
         <v>35</v>
       </c>
       <c r="C5">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2305,7 +2305,7 @@
         <v>35</v>
       </c>
       <c r="C6">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2316,7 +2316,7 @@
         <v>34</v>
       </c>
       <c r="C7">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -2338,7 +2338,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2360,7 +2360,7 @@
         <v>34</v>
       </c>
       <c r="C11">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
   </sheetData>

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="104" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6190DAF-664A-4163-9865-F19B4E0C087F}"/>
+  <xr:revisionPtr revIDLastSave="112" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6FFC419-9C79-4D8E-B42D-72BE3557323A}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" tabRatio="667" activeTab="2" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="667" activeTab="6" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="mat_2026" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1237" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1235" uniqueCount="298">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -715,9 +715,6 @@
   </si>
   <si>
     <t>Colegio Chillán</t>
-  </si>
-  <si>
-    <t>Escuela Parroquial Domingo Savio</t>
   </si>
   <si>
     <t>Colegio La Merced</t>
@@ -1062,10 +1059,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1815,10 +1808,10 @@
         <v>91</v>
       </c>
       <c r="D25">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E25">
-        <v>1.0329999999999999</v>
+        <v>1.022</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -1934,10 +1927,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E32">
-        <v>1.071</v>
+        <v>1.0680000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1951,10 +1944,10 @@
         <v>329</v>
       </c>
       <c r="D33">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E33">
-        <v>1.03</v>
+        <v>1.0269999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -1985,10 +1978,10 @@
         <v>218</v>
       </c>
       <c r="D35">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E35">
-        <v>1.0049999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -2305,7 +2298,7 @@
         <v>35</v>
       </c>
       <c r="C6">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2338,7 +2331,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>699</v>
+        <v>696</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2463,7 +2456,7 @@
         <v>46006</v>
       </c>
       <c r="C8" s="6">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2474,7 +2467,7 @@
         <v>46013</v>
       </c>
       <c r="C9" s="9">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2848,7 +2841,7 @@
         <v>46113</v>
       </c>
       <c r="C43" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -4102,7 +4095,7 @@
         <v>46084</v>
       </c>
       <c r="C157" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -5477,7 +5470,7 @@
         <v>3</v>
       </c>
       <c r="E25">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -5596,7 +5589,7 @@
         <v>251</v>
       </c>
       <c r="E32">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -5613,7 +5606,7 @@
         <v>8</v>
       </c>
       <c r="E33">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -5641,7 +5634,7 @@
         <v>20</v>
       </c>
       <c r="C35">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D35">
         <v>4</v>
@@ -5725,7 +5718,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0916EAC6-1E7F-4924-9D0E-33749FD3E143}">
-  <dimension ref="A1:C354"/>
+  <dimension ref="A1:C353"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
@@ -5738,7 +5731,7 @@
         <v>37</v>
       </c>
       <c r="B1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C1" t="s">
         <v>36</v>
@@ -6937,7 +6930,7 @@
         <v>15</v>
       </c>
       <c r="B110" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C110">
         <v>4</v>
@@ -6948,7 +6941,7 @@
         <v>15</v>
       </c>
       <c r="B111" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C111">
         <v>4</v>
@@ -6959,10 +6952,10 @@
         <v>15</v>
       </c>
       <c r="B112" t="s">
-        <v>129</v>
+        <v>81</v>
       </c>
       <c r="C112">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -6970,7 +6963,7 @@
         <v>15</v>
       </c>
       <c r="B113" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="C113">
         <v>3</v>
@@ -7828,7 +7821,7 @@
         <v>16</v>
       </c>
       <c r="B191" t="s">
-        <v>65</v>
+        <v>193</v>
       </c>
       <c r="C191">
         <v>12</v>
@@ -7839,7 +7832,7 @@
         <v>16</v>
       </c>
       <c r="B192" t="s">
-        <v>193</v>
+        <v>50</v>
       </c>
       <c r="C192">
         <v>12</v>
@@ -7850,10 +7843,10 @@
         <v>16</v>
       </c>
       <c r="B193" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C193">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -7872,7 +7865,7 @@
         <v>16</v>
       </c>
       <c r="B195" t="s">
-        <v>55</v>
+        <v>195</v>
       </c>
       <c r="C195">
         <v>10</v>
@@ -7883,7 +7876,7 @@
         <v>16</v>
       </c>
       <c r="B196" t="s">
-        <v>195</v>
+        <v>55</v>
       </c>
       <c r="C196">
         <v>10</v>
@@ -7916,7 +7909,7 @@
         <v>16</v>
       </c>
       <c r="B199" t="s">
-        <v>196</v>
+        <v>85</v>
       </c>
       <c r="C199">
         <v>7</v>
@@ -7927,7 +7920,7 @@
         <v>16</v>
       </c>
       <c r="B200" t="s">
-        <v>85</v>
+        <v>196</v>
       </c>
       <c r="C200">
         <v>7</v>
@@ -7949,7 +7942,7 @@
         <v>16</v>
       </c>
       <c r="B202" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C202">
         <v>6</v>
@@ -7960,7 +7953,7 @@
         <v>16</v>
       </c>
       <c r="B203" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C203">
         <v>6</v>
@@ -7971,7 +7964,7 @@
         <v>16</v>
       </c>
       <c r="B204" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C204">
         <v>5</v>
@@ -7993,7 +7986,7 @@
         <v>16</v>
       </c>
       <c r="B206" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C206">
         <v>5</v>
@@ -8015,7 +8008,7 @@
         <v>16</v>
       </c>
       <c r="B208" t="s">
-        <v>197</v>
+        <v>60</v>
       </c>
       <c r="C208">
         <v>4</v>
@@ -8026,7 +8019,7 @@
         <v>16</v>
       </c>
       <c r="B209" t="s">
-        <v>60</v>
+        <v>199</v>
       </c>
       <c r="C209">
         <v>4</v>
@@ -8048,7 +8041,7 @@
         <v>16</v>
       </c>
       <c r="B211" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C211">
         <v>4</v>
@@ -8092,7 +8085,7 @@
         <v>16</v>
       </c>
       <c r="B215" t="s">
-        <v>114</v>
+        <v>44</v>
       </c>
       <c r="C215">
         <v>3</v>
@@ -8103,7 +8096,7 @@
         <v>16</v>
       </c>
       <c r="B216" t="s">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="C216">
         <v>3</v>
@@ -8114,7 +8107,7 @@
         <v>16</v>
       </c>
       <c r="B217" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="C217">
         <v>3</v>
@@ -8125,7 +8118,7 @@
         <v>16</v>
       </c>
       <c r="B218" t="s">
-        <v>59</v>
+        <v>201</v>
       </c>
       <c r="C218">
         <v>3</v>
@@ -8136,7 +8129,7 @@
         <v>16</v>
       </c>
       <c r="B219" t="s">
-        <v>118</v>
+        <v>68</v>
       </c>
       <c r="C219">
         <v>3</v>
@@ -8147,7 +8140,7 @@
         <v>16</v>
       </c>
       <c r="B220" t="s">
-        <v>201</v>
+        <v>74</v>
       </c>
       <c r="C220">
         <v>3</v>
@@ -8158,7 +8151,7 @@
         <v>16</v>
       </c>
       <c r="B221" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C221">
         <v>3</v>
@@ -8169,7 +8162,7 @@
         <v>16</v>
       </c>
       <c r="B222" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C222">
         <v>2</v>
@@ -8180,7 +8173,7 @@
         <v>16</v>
       </c>
       <c r="B223" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C223">
         <v>2</v>
@@ -8191,7 +8184,7 @@
         <v>16</v>
       </c>
       <c r="B224" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="C224">
         <v>2</v>
@@ -8202,7 +8195,7 @@
         <v>16</v>
       </c>
       <c r="B225" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C225">
         <v>2</v>
@@ -8213,7 +8206,7 @@
         <v>16</v>
       </c>
       <c r="B226" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="C226">
         <v>2</v>
@@ -8224,7 +8217,7 @@
         <v>16</v>
       </c>
       <c r="B227" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C227">
         <v>2</v>
@@ -8235,7 +8228,7 @@
         <v>16</v>
       </c>
       <c r="B228" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="C228">
         <v>2</v>
@@ -8246,7 +8239,7 @@
         <v>16</v>
       </c>
       <c r="B229" t="s">
-        <v>202</v>
+        <v>80</v>
       </c>
       <c r="C229">
         <v>2</v>
@@ -8257,7 +8250,7 @@
         <v>16</v>
       </c>
       <c r="B230" t="s">
-        <v>64</v>
+        <v>206</v>
       </c>
       <c r="C230">
         <v>2</v>
@@ -8268,7 +8261,7 @@
         <v>16</v>
       </c>
       <c r="B231" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="C231">
         <v>1</v>
@@ -8279,7 +8272,7 @@
         <v>16</v>
       </c>
       <c r="B232" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="C232">
         <v>1</v>
@@ -8301,7 +8294,7 @@
         <v>16</v>
       </c>
       <c r="B234" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C234">
         <v>1</v>
@@ -8312,7 +8305,7 @@
         <v>16</v>
       </c>
       <c r="B235" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="C235">
         <v>1</v>
@@ -8323,7 +8316,7 @@
         <v>16</v>
       </c>
       <c r="B236" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="C236">
         <v>1</v>
@@ -8334,7 +8327,7 @@
         <v>16</v>
       </c>
       <c r="B237" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -8345,7 +8338,7 @@
         <v>16</v>
       </c>
       <c r="B238" t="s">
-        <v>231</v>
+        <v>70</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -8356,7 +8349,7 @@
         <v>16</v>
       </c>
       <c r="B239" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -8367,7 +8360,7 @@
         <v>16</v>
       </c>
       <c r="B240" t="s">
-        <v>242</v>
+        <v>121</v>
       </c>
       <c r="C240">
         <v>1</v>
@@ -8378,7 +8371,7 @@
         <v>16</v>
       </c>
       <c r="B241" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -8389,7 +8382,7 @@
         <v>16</v>
       </c>
       <c r="B242" t="s">
-        <v>210</v>
+        <v>58</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -8400,7 +8393,7 @@
         <v>16</v>
       </c>
       <c r="B243" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -8422,7 +8415,7 @@
         <v>16</v>
       </c>
       <c r="B245" t="s">
-        <v>119</v>
+        <v>235</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -8433,7 +8426,7 @@
         <v>16</v>
       </c>
       <c r="B246" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C246">
         <v>1</v>
@@ -8444,7 +8437,7 @@
         <v>16</v>
       </c>
       <c r="B247" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="C247">
         <v>1</v>
@@ -8455,7 +8448,7 @@
         <v>16</v>
       </c>
       <c r="B248" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C248">
         <v>1</v>
@@ -8466,7 +8459,7 @@
         <v>16</v>
       </c>
       <c r="B249" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C249">
         <v>1</v>
@@ -8477,7 +8470,7 @@
         <v>16</v>
       </c>
       <c r="B250" t="s">
-        <v>126</v>
+        <v>218</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -8488,7 +8481,7 @@
         <v>16</v>
       </c>
       <c r="B251" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C251">
         <v>1</v>
@@ -8499,7 +8492,7 @@
         <v>16</v>
       </c>
       <c r="B252" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -8510,7 +8503,7 @@
         <v>16</v>
       </c>
       <c r="B253" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -8521,7 +8514,7 @@
         <v>16</v>
       </c>
       <c r="B254" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -8532,7 +8525,7 @@
         <v>16</v>
       </c>
       <c r="B255" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -8543,7 +8536,7 @@
         <v>16</v>
       </c>
       <c r="B256" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -8554,7 +8547,7 @@
         <v>16</v>
       </c>
       <c r="B257" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -8565,7 +8558,7 @@
         <v>16</v>
       </c>
       <c r="B258" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C258">
         <v>1</v>
@@ -8576,7 +8569,7 @@
         <v>16</v>
       </c>
       <c r="B259" t="s">
-        <v>232</v>
+        <v>208</v>
       </c>
       <c r="C259">
         <v>1</v>
@@ -8587,7 +8580,7 @@
         <v>16</v>
       </c>
       <c r="B260" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="C260">
         <v>1</v>
@@ -8598,7 +8591,7 @@
         <v>16</v>
       </c>
       <c r="B261" t="s">
-        <v>227</v>
+        <v>126</v>
       </c>
       <c r="C261">
         <v>1</v>
@@ -8609,7 +8602,7 @@
         <v>16</v>
       </c>
       <c r="B262" t="s">
-        <v>233</v>
+        <v>211</v>
       </c>
       <c r="C262">
         <v>1</v>
@@ -8620,7 +8613,7 @@
         <v>16</v>
       </c>
       <c r="B263" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="C263">
         <v>1</v>
@@ -8631,7 +8624,7 @@
         <v>16</v>
       </c>
       <c r="B264" t="s">
-        <v>214</v>
+        <v>69</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -8642,7 +8635,7 @@
         <v>16</v>
       </c>
       <c r="B265" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="C265">
         <v>1</v>
@@ -8653,7 +8646,7 @@
         <v>16</v>
       </c>
       <c r="B266" t="s">
-        <v>69</v>
+        <v>223</v>
       </c>
       <c r="C266">
         <v>1</v>
@@ -8664,7 +8657,7 @@
         <v>16</v>
       </c>
       <c r="B267" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -8675,7 +8668,7 @@
         <v>16</v>
       </c>
       <c r="B268" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="C268">
         <v>1</v>
@@ -8686,7 +8679,7 @@
         <v>16</v>
       </c>
       <c r="B269" t="s">
-        <v>238</v>
+        <v>215</v>
       </c>
       <c r="C269">
         <v>1</v>
@@ -8697,7 +8690,7 @@
         <v>16</v>
       </c>
       <c r="B270" t="s">
-        <v>215</v>
+        <v>119</v>
       </c>
       <c r="C270">
         <v>1</v>
@@ -8708,7 +8701,7 @@
         <v>16</v>
       </c>
       <c r="B271" t="s">
-        <v>70</v>
+        <v>216</v>
       </c>
       <c r="C271">
         <v>1</v>
@@ -8719,7 +8712,7 @@
         <v>16</v>
       </c>
       <c r="B272" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="C272">
         <v>1</v>
@@ -8730,7 +8723,7 @@
         <v>16</v>
       </c>
       <c r="B273" t="s">
-        <v>121</v>
+        <v>243</v>
       </c>
       <c r="C273">
         <v>1</v>
@@ -8741,7 +8734,7 @@
         <v>16</v>
       </c>
       <c r="B274" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C274">
         <v>1</v>
@@ -8749,13 +8742,13 @@
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B275" t="s">
-        <v>58</v>
+        <v>121</v>
       </c>
       <c r="C275">
-        <v>1</v>
+        <v>39</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -8763,10 +8756,10 @@
         <v>21</v>
       </c>
       <c r="B276" t="s">
-        <v>121</v>
+        <v>189</v>
       </c>
       <c r="C276">
-        <v>39</v>
+        <v>11</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -8774,10 +8767,10 @@
         <v>21</v>
       </c>
       <c r="B277" t="s">
-        <v>189</v>
+        <v>132</v>
       </c>
       <c r="C277">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -8785,10 +8778,10 @@
         <v>21</v>
       </c>
       <c r="B278" t="s">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="C278">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -8796,7 +8789,7 @@
         <v>21</v>
       </c>
       <c r="B279" t="s">
-        <v>103</v>
+        <v>202</v>
       </c>
       <c r="C279">
         <v>7</v>
@@ -8807,10 +8800,10 @@
         <v>21</v>
       </c>
       <c r="B280" t="s">
-        <v>202</v>
+        <v>244</v>
       </c>
       <c r="C280">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -8818,7 +8811,7 @@
         <v>21</v>
       </c>
       <c r="B281" t="s">
-        <v>245</v>
+        <v>120</v>
       </c>
       <c r="C281">
         <v>6</v>
@@ -8829,10 +8822,10 @@
         <v>21</v>
       </c>
       <c r="B282" t="s">
-        <v>120</v>
+        <v>246</v>
       </c>
       <c r="C282">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -8840,7 +8833,7 @@
         <v>21</v>
       </c>
       <c r="B283" t="s">
-        <v>247</v>
+        <v>142</v>
       </c>
       <c r="C283">
         <v>5</v>
@@ -8851,7 +8844,7 @@
         <v>21</v>
       </c>
       <c r="B284" t="s">
-        <v>142</v>
+        <v>245</v>
       </c>
       <c r="C284">
         <v>5</v>
@@ -8862,7 +8855,7 @@
         <v>21</v>
       </c>
       <c r="B285" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C285">
         <v>5</v>
@@ -8876,7 +8869,7 @@
         <v>248</v>
       </c>
       <c r="C286">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -8884,7 +8877,7 @@
         <v>21</v>
       </c>
       <c r="B287" t="s">
-        <v>249</v>
+        <v>128</v>
       </c>
       <c r="C287">
         <v>4</v>
@@ -8895,7 +8888,7 @@
         <v>21</v>
       </c>
       <c r="B288" t="s">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="C288">
         <v>4</v>
@@ -8906,7 +8899,7 @@
         <v>21</v>
       </c>
       <c r="B289" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="C289">
         <v>4</v>
@@ -8917,10 +8910,10 @@
         <v>21</v>
       </c>
       <c r="B290" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C290">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -8928,7 +8921,7 @@
         <v>21</v>
       </c>
       <c r="B291" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="C291">
         <v>3</v>
@@ -8939,7 +8932,7 @@
         <v>21</v>
       </c>
       <c r="B292" t="s">
-        <v>81</v>
+        <v>249</v>
       </c>
       <c r="C292">
         <v>3</v>
@@ -8950,7 +8943,7 @@
         <v>21</v>
       </c>
       <c r="B293" t="s">
-        <v>250</v>
+        <v>163</v>
       </c>
       <c r="C293">
         <v>3</v>
@@ -8961,7 +8954,7 @@
         <v>21</v>
       </c>
       <c r="B294" t="s">
-        <v>163</v>
+        <v>251</v>
       </c>
       <c r="C294">
         <v>3</v>
@@ -8983,7 +8976,7 @@
         <v>21</v>
       </c>
       <c r="B296" t="s">
-        <v>253</v>
+        <v>44</v>
       </c>
       <c r="C296">
         <v>3</v>
@@ -8994,7 +8987,7 @@
         <v>21</v>
       </c>
       <c r="B297" t="s">
-        <v>44</v>
+        <v>253</v>
       </c>
       <c r="C297">
         <v>3</v>
@@ -9005,7 +8998,7 @@
         <v>21</v>
       </c>
       <c r="B298" t="s">
-        <v>254</v>
+        <v>126</v>
       </c>
       <c r="C298">
         <v>3</v>
@@ -9016,7 +9009,7 @@
         <v>21</v>
       </c>
       <c r="B299" t="s">
-        <v>126</v>
+        <v>196</v>
       </c>
       <c r="C299">
         <v>3</v>
@@ -9027,10 +9020,10 @@
         <v>21</v>
       </c>
       <c r="B300" t="s">
-        <v>196</v>
+        <v>171</v>
       </c>
       <c r="C300">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -9038,7 +9031,7 @@
         <v>21</v>
       </c>
       <c r="B301" t="s">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="C301">
         <v>2</v>
@@ -9049,7 +9042,7 @@
         <v>21</v>
       </c>
       <c r="B302" t="s">
-        <v>198</v>
+        <v>271</v>
       </c>
       <c r="C302">
         <v>2</v>
@@ -9060,7 +9053,7 @@
         <v>21</v>
       </c>
       <c r="B303" t="s">
-        <v>272</v>
+        <v>136</v>
       </c>
       <c r="C303">
         <v>2</v>
@@ -9071,7 +9064,7 @@
         <v>21</v>
       </c>
       <c r="B304" t="s">
-        <v>136</v>
+        <v>257</v>
       </c>
       <c r="C304">
         <v>2</v>
@@ -9082,7 +9075,7 @@
         <v>21</v>
       </c>
       <c r="B305" t="s">
-        <v>258</v>
+        <v>116</v>
       </c>
       <c r="C305">
         <v>2</v>
@@ -9093,7 +9086,7 @@
         <v>21</v>
       </c>
       <c r="B306" t="s">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="C306">
         <v>2</v>
@@ -9104,7 +9097,7 @@
         <v>21</v>
       </c>
       <c r="B307" t="s">
-        <v>77</v>
+        <v>256</v>
       </c>
       <c r="C307">
         <v>2</v>
@@ -9115,7 +9108,7 @@
         <v>21</v>
       </c>
       <c r="B308" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C308">
         <v>2</v>
@@ -9126,7 +9119,7 @@
         <v>21</v>
       </c>
       <c r="B309" t="s">
-        <v>256</v>
+        <v>173</v>
       </c>
       <c r="C309">
         <v>2</v>
@@ -9137,7 +9130,7 @@
         <v>21</v>
       </c>
       <c r="B310" t="s">
-        <v>173</v>
+        <v>85</v>
       </c>
       <c r="C310">
         <v>2</v>
@@ -9148,7 +9141,7 @@
         <v>21</v>
       </c>
       <c r="B311" t="s">
-        <v>85</v>
+        <v>250</v>
       </c>
       <c r="C311">
         <v>2</v>
@@ -9159,7 +9152,7 @@
         <v>21</v>
       </c>
       <c r="B312" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="C312">
         <v>2</v>
@@ -9170,7 +9163,7 @@
         <v>21</v>
       </c>
       <c r="B313" t="s">
-        <v>255</v>
+        <v>54</v>
       </c>
       <c r="C313">
         <v>2</v>
@@ -9181,7 +9174,7 @@
         <v>21</v>
       </c>
       <c r="B314" t="s">
-        <v>54</v>
+        <v>199</v>
       </c>
       <c r="C314">
         <v>2</v>
@@ -9192,7 +9185,7 @@
         <v>21</v>
       </c>
       <c r="B315" t="s">
-        <v>199</v>
+        <v>62</v>
       </c>
       <c r="C315">
         <v>2</v>
@@ -9203,7 +9196,7 @@
         <v>21</v>
       </c>
       <c r="B316" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C316">
         <v>2</v>
@@ -9214,10 +9207,10 @@
         <v>21</v>
       </c>
       <c r="B317" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C317">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
@@ -9225,7 +9218,7 @@
         <v>21</v>
       </c>
       <c r="B318" t="s">
-        <v>63</v>
+        <v>214</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -9236,7 +9229,7 @@
         <v>21</v>
       </c>
       <c r="B319" t="s">
-        <v>214</v>
+        <v>269</v>
       </c>
       <c r="C319">
         <v>1</v>
@@ -9247,7 +9240,7 @@
         <v>21</v>
       </c>
       <c r="B320" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="C320">
         <v>1</v>
@@ -9258,7 +9251,7 @@
         <v>21</v>
       </c>
       <c r="B321" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="C321">
         <v>1</v>
@@ -9269,7 +9262,7 @@
         <v>21</v>
       </c>
       <c r="B322" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="C322">
         <v>1</v>
@@ -9280,7 +9273,7 @@
         <v>21</v>
       </c>
       <c r="B323" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C323">
         <v>1</v>
@@ -9291,7 +9284,7 @@
         <v>21</v>
       </c>
       <c r="B324" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="C324">
         <v>1</v>
@@ -9302,7 +9295,7 @@
         <v>21</v>
       </c>
       <c r="B325" t="s">
-        <v>280</v>
+        <v>137</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -9313,7 +9306,7 @@
         <v>21</v>
       </c>
       <c r="B326" t="s">
-        <v>137</v>
+        <v>266</v>
       </c>
       <c r="C326">
         <v>1</v>
@@ -9324,7 +9317,7 @@
         <v>21</v>
       </c>
       <c r="B327" t="s">
-        <v>267</v>
+        <v>92</v>
       </c>
       <c r="C327">
         <v>1</v>
@@ -9335,7 +9328,7 @@
         <v>21</v>
       </c>
       <c r="B328" t="s">
-        <v>92</v>
+        <v>267</v>
       </c>
       <c r="C328">
         <v>1</v>
@@ -9346,7 +9339,7 @@
         <v>21</v>
       </c>
       <c r="B329" t="s">
-        <v>268</v>
+        <v>125</v>
       </c>
       <c r="C329">
         <v>1</v>
@@ -9357,7 +9350,7 @@
         <v>21</v>
       </c>
       <c r="B330" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="C330">
         <v>1</v>
@@ -9368,7 +9361,7 @@
         <v>21</v>
       </c>
       <c r="B331" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C331">
         <v>1</v>
@@ -9379,7 +9372,7 @@
         <v>21</v>
       </c>
       <c r="B332" t="s">
-        <v>279</v>
+        <v>185</v>
       </c>
       <c r="C332">
         <v>1</v>
@@ -9390,7 +9383,7 @@
         <v>21</v>
       </c>
       <c r="B333" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="C333">
         <v>1</v>
@@ -9401,7 +9394,7 @@
         <v>21</v>
       </c>
       <c r="B334" t="s">
-        <v>165</v>
+        <v>49</v>
       </c>
       <c r="C334">
         <v>1</v>
@@ -9412,7 +9405,7 @@
         <v>21</v>
       </c>
       <c r="B335" t="s">
-        <v>49</v>
+        <v>115</v>
       </c>
       <c r="C335">
         <v>1</v>
@@ -9423,7 +9416,7 @@
         <v>21</v>
       </c>
       <c r="B336" t="s">
-        <v>115</v>
+        <v>270</v>
       </c>
       <c r="C336">
         <v>1</v>
@@ -9434,7 +9427,7 @@
         <v>21</v>
       </c>
       <c r="B337" t="s">
-        <v>271</v>
+        <v>138</v>
       </c>
       <c r="C337">
         <v>1</v>
@@ -9445,7 +9438,7 @@
         <v>21</v>
       </c>
       <c r="B338" t="s">
-        <v>138</v>
+        <v>273</v>
       </c>
       <c r="C338">
         <v>1</v>
@@ -9456,7 +9449,7 @@
         <v>21</v>
       </c>
       <c r="B339" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="C339">
         <v>1</v>
@@ -9467,7 +9460,7 @@
         <v>21</v>
       </c>
       <c r="B340" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="C340">
         <v>1</v>
@@ -9478,7 +9471,7 @@
         <v>21</v>
       </c>
       <c r="B341" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="C341">
         <v>1</v>
@@ -9489,7 +9482,7 @@
         <v>21</v>
       </c>
       <c r="B342" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="C342">
         <v>1</v>
@@ -9500,7 +9493,7 @@
         <v>21</v>
       </c>
       <c r="B343" t="s">
-        <v>273</v>
+        <v>172</v>
       </c>
       <c r="C343">
         <v>1</v>
@@ -9511,7 +9504,7 @@
         <v>21</v>
       </c>
       <c r="B344" t="s">
-        <v>172</v>
+        <v>277</v>
       </c>
       <c r="C344">
         <v>1</v>
@@ -9522,7 +9515,7 @@
         <v>21</v>
       </c>
       <c r="B345" t="s">
-        <v>278</v>
+        <v>258</v>
       </c>
       <c r="C345">
         <v>1</v>
@@ -9533,7 +9526,7 @@
         <v>21</v>
       </c>
       <c r="B346" t="s">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="C346">
         <v>1</v>
@@ -9544,7 +9537,7 @@
         <v>21</v>
       </c>
       <c r="B347" t="s">
-        <v>277</v>
+        <v>148</v>
       </c>
       <c r="C347">
         <v>1</v>
@@ -9555,7 +9548,7 @@
         <v>21</v>
       </c>
       <c r="B348" t="s">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="C348">
         <v>1</v>
@@ -9566,7 +9559,7 @@
         <v>21</v>
       </c>
       <c r="B349" t="s">
-        <v>174</v>
+        <v>260</v>
       </c>
       <c r="C349">
         <v>1</v>
@@ -9577,7 +9570,7 @@
         <v>21</v>
       </c>
       <c r="B350" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="C350">
         <v>1</v>
@@ -9588,7 +9581,7 @@
         <v>21</v>
       </c>
       <c r="B351" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="C351">
         <v>1</v>
@@ -9599,7 +9592,7 @@
         <v>21</v>
       </c>
       <c r="B352" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="C352">
         <v>1</v>
@@ -9610,20 +9603,9 @@
         <v>21</v>
       </c>
       <c r="B353" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="C353">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A354" t="s">
-        <v>21</v>
-      </c>
-      <c r="B354" t="s">
-        <v>269</v>
-      </c>
-      <c r="C354">
         <v>1</v>
       </c>
     </row>
@@ -9645,10 +9627,10 @@
         <v>37</v>
       </c>
       <c r="B1" t="s">
+        <v>284</v>
+      </c>
+      <c r="C1" t="s">
         <v>285</v>
-      </c>
-      <c r="C1" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -9656,7 +9638,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C2">
         <v>63</v>
@@ -9667,7 +9649,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C3">
         <v>513</v>
@@ -9678,7 +9660,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C4">
         <v>36</v>
@@ -9689,7 +9671,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C5">
         <v>11</v>
@@ -9700,7 +9682,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C6">
         <v>7</v>
@@ -9711,7 +9693,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -9722,7 +9704,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -9733,7 +9715,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C9">
         <v>29</v>
@@ -9744,7 +9726,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C10">
         <v>559</v>
@@ -9755,7 +9737,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C11">
         <v>23</v>
@@ -9766,7 +9748,7 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C12">
         <v>30</v>
@@ -9777,7 +9759,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C13">
         <v>26</v>
@@ -9788,10 +9770,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C14">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -9799,7 +9781,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C15">
         <v>4</v>
@@ -9810,7 +9792,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C16">
         <v>13</v>
@@ -9821,7 +9803,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C17">
         <v>22</v>
@@ -9832,7 +9814,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C18">
         <v>33</v>
@@ -9843,7 +9825,7 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C19">
         <v>11</v>
@@ -9854,7 +9836,7 @@
         <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C20">
         <v>2</v>
@@ -9865,7 +9847,7 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C21">
         <v>4</v>
@@ -9876,7 +9858,7 @@
         <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C22">
         <v>2</v>
@@ -9887,7 +9869,7 @@
         <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C23">
         <v>2</v>
@@ -9898,10 +9880,10 @@
         <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C24">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -9909,10 +9891,10 @@
         <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C25">
-        <v>877</v>
+        <v>875</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -9920,7 +9902,7 @@
         <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -9931,7 +9913,7 @@
         <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C27">
         <v>111</v>
@@ -9942,7 +9924,7 @@
         <v>16</v>
       </c>
       <c r="B28" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C28">
         <v>140</v>
@@ -9953,7 +9935,7 @@
         <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C29">
         <v>77</v>
@@ -9964,7 +9946,7 @@
         <v>16</v>
       </c>
       <c r="B30" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C30">
         <v>10</v>
@@ -9975,7 +9957,7 @@
         <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -9986,7 +9968,7 @@
         <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C32">
         <v>7</v>
@@ -9997,7 +9979,7 @@
         <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -10008,7 +9990,7 @@
         <v>21</v>
       </c>
       <c r="B34" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C34">
         <v>711</v>
@@ -10019,7 +10001,7 @@
         <v>21</v>
       </c>
       <c r="B35" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C35">
         <v>9</v>
@@ -10030,7 +10012,7 @@
         <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C36">
         <v>22</v>
@@ -10041,7 +10023,7 @@
         <v>21</v>
       </c>
       <c r="B37" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C37">
         <v>61</v>
@@ -10052,7 +10034,7 @@
         <v>21</v>
       </c>
       <c r="B38" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C38">
         <v>24</v>
@@ -10063,7 +10045,7 @@
         <v>21</v>
       </c>
       <c r="B39" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C39">
         <v>55</v>
@@ -10074,7 +10056,7 @@
         <v>21</v>
       </c>
       <c r="B40" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C40">
         <v>3</v>
@@ -10085,7 +10067,7 @@
         <v>21</v>
       </c>
       <c r="B41" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C41">
         <v>14</v>
@@ -10096,7 +10078,7 @@
         <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C42">
         <v>14</v>
@@ -10107,7 +10089,7 @@
         <v>21</v>
       </c>
       <c r="B43" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C43">
         <v>6</v>

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="112" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6FFC419-9C79-4D8E-B42D-72BE3557323A}"/>
+  <xr:revisionPtr revIDLastSave="118" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39B7227F-CD69-4888-8833-0B91B1920956}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="667" activeTab="6" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1235" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="298">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -1059,6 +1059,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1536,10 +1540,10 @@
         <v>108</v>
       </c>
       <c r="D9">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>1.0089999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1893,10 +1897,10 @@
         <v>119</v>
       </c>
       <c r="D30">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E30">
-        <v>0.99199999999999999</v>
+        <v>0.98299999999999998</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -1927,10 +1931,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E32">
-        <v>1.0680000000000001</v>
+        <v>1.0660000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2265,7 +2269,7 @@
         <v>35</v>
       </c>
       <c r="C3">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2298,7 +2302,7 @@
         <v>35</v>
       </c>
       <c r="C6">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2331,7 +2335,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2363,7 +2367,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD19485A-0629-47F9-A5AD-80ABA7A6E076}">
-  <dimension ref="A1:C242"/>
+  <dimension ref="A1:C243"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -2522,7 +2526,7 @@
         <v>46010</v>
       </c>
       <c r="C14" s="6">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -3586,7 +3590,7 @@
         <v>3</v>
       </c>
       <c r="B111" s="8">
-        <v>46093</v>
+        <v>46170</v>
       </c>
       <c r="C111" s="9">
         <v>1</v>
@@ -3597,10 +3601,10 @@
         <v>3</v>
       </c>
       <c r="B112" s="5">
-        <v>46078</v>
+        <v>46093</v>
       </c>
       <c r="C112" s="6">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -3608,10 +3612,10 @@
         <v>3</v>
       </c>
       <c r="B113" s="8">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="C113" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -3619,10 +3623,10 @@
         <v>3</v>
       </c>
       <c r="B114" s="5">
-        <v>46134</v>
+        <v>46084</v>
       </c>
       <c r="C114" s="6">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -3630,10 +3634,10 @@
         <v>3</v>
       </c>
       <c r="B115" s="8">
-        <v>46083</v>
+        <v>46134</v>
       </c>
       <c r="C115" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -3641,10 +3645,10 @@
         <v>3</v>
       </c>
       <c r="B116" s="5">
-        <v>46022</v>
+        <v>46083</v>
       </c>
       <c r="C116" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -3652,10 +3656,10 @@
         <v>3</v>
       </c>
       <c r="B117" s="8">
-        <v>46114</v>
+        <v>46022</v>
       </c>
       <c r="C117" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -3663,10 +3667,10 @@
         <v>3</v>
       </c>
       <c r="B118" s="5">
-        <v>46135</v>
+        <v>46114</v>
       </c>
       <c r="C118" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -3674,10 +3678,10 @@
         <v>3</v>
       </c>
       <c r="B119" s="8">
-        <v>46168</v>
+        <v>46135</v>
       </c>
       <c r="C119" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -3685,7 +3689,7 @@
         <v>3</v>
       </c>
       <c r="B120" s="5">
-        <v>46126</v>
+        <v>46168</v>
       </c>
       <c r="C120" s="6">
         <v>3</v>
@@ -3696,7 +3700,7 @@
         <v>3</v>
       </c>
       <c r="B121" s="8">
-        <v>46120</v>
+        <v>46126</v>
       </c>
       <c r="C121" s="9">
         <v>3</v>
@@ -3707,10 +3711,10 @@
         <v>3</v>
       </c>
       <c r="B122" s="5">
-        <v>46127</v>
+        <v>46120</v>
       </c>
       <c r="C122" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -3718,7 +3722,7 @@
         <v>3</v>
       </c>
       <c r="B123" s="8">
-        <v>46087</v>
+        <v>46127</v>
       </c>
       <c r="C123" s="9">
         <v>1</v>
@@ -3729,7 +3733,7 @@
         <v>3</v>
       </c>
       <c r="B124" s="5">
-        <v>46108</v>
+        <v>46087</v>
       </c>
       <c r="C124" s="6">
         <v>1</v>
@@ -3740,7 +3744,7 @@
         <v>3</v>
       </c>
       <c r="B125" s="8">
-        <v>46020</v>
+        <v>46108</v>
       </c>
       <c r="C125" s="9">
         <v>1</v>
@@ -3751,7 +3755,7 @@
         <v>3</v>
       </c>
       <c r="B126" s="5">
-        <v>46097</v>
+        <v>46020</v>
       </c>
       <c r="C126" s="6">
         <v>1</v>
@@ -3762,10 +3766,10 @@
         <v>3</v>
       </c>
       <c r="B127" s="8">
-        <v>46161</v>
+        <v>46097</v>
       </c>
       <c r="C127" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -3773,10 +3777,10 @@
         <v>3</v>
       </c>
       <c r="B128" s="5">
-        <v>46129</v>
+        <v>46161</v>
       </c>
       <c r="C128" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -3784,7 +3788,7 @@
         <v>3</v>
       </c>
       <c r="B129" s="8">
-        <v>46080</v>
+        <v>46129</v>
       </c>
       <c r="C129" s="9">
         <v>1</v>
@@ -3795,7 +3799,7 @@
         <v>3</v>
       </c>
       <c r="B130" s="5">
-        <v>46101</v>
+        <v>46080</v>
       </c>
       <c r="C130" s="6">
         <v>1</v>
@@ -3806,7 +3810,7 @@
         <v>3</v>
       </c>
       <c r="B131" s="8">
-        <v>46155</v>
+        <v>46101</v>
       </c>
       <c r="C131" s="9">
         <v>1</v>
@@ -3817,7 +3821,7 @@
         <v>3</v>
       </c>
       <c r="B132" s="5">
-        <v>46150</v>
+        <v>46155</v>
       </c>
       <c r="C132" s="6">
         <v>1</v>
@@ -3828,7 +3832,7 @@
         <v>3</v>
       </c>
       <c r="B133" s="8">
-        <v>46141</v>
+        <v>46150</v>
       </c>
       <c r="C133" s="9">
         <v>1</v>
@@ -3839,7 +3843,7 @@
         <v>3</v>
       </c>
       <c r="B134" s="5">
-        <v>46085</v>
+        <v>46141</v>
       </c>
       <c r="C134" s="6">
         <v>1</v>
@@ -3850,7 +3854,7 @@
         <v>3</v>
       </c>
       <c r="B135" s="8">
-        <v>46148</v>
+        <v>46085</v>
       </c>
       <c r="C135" s="9">
         <v>1</v>
@@ -3861,10 +3865,10 @@
         <v>3</v>
       </c>
       <c r="B136" s="5">
-        <v>46118</v>
+        <v>46148</v>
       </c>
       <c r="C136" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -3872,21 +3876,21 @@
         <v>3</v>
       </c>
       <c r="B137" s="8">
-        <v>46079</v>
+        <v>46118</v>
       </c>
       <c r="C137" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B138" s="5">
-        <v>46003</v>
+        <v>46079</v>
       </c>
       <c r="C138" s="6">
-        <v>92</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -3894,10 +3898,10 @@
         <v>15</v>
       </c>
       <c r="B139" s="8">
-        <v>46000</v>
+        <v>46003</v>
       </c>
       <c r="C139" s="9">
-        <v>132</v>
+        <v>92</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -3905,10 +3909,10 @@
         <v>15</v>
       </c>
       <c r="B140" s="5">
-        <v>46006</v>
+        <v>46000</v>
       </c>
       <c r="C140" s="6">
-        <v>174</v>
+        <v>132</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -3916,10 +3920,10 @@
         <v>15</v>
       </c>
       <c r="B141" s="8">
-        <v>46001</v>
+        <v>46006</v>
       </c>
       <c r="C141" s="9">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -3927,10 +3931,10 @@
         <v>15</v>
       </c>
       <c r="B142" s="5">
-        <v>46014</v>
+        <v>46001</v>
       </c>
       <c r="C142" s="6">
-        <v>16</v>
+        <v>174</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -3938,10 +3942,10 @@
         <v>15</v>
       </c>
       <c r="B143" s="8">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="C143" s="9">
-        <v>171</v>
+        <v>16</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -3949,10 +3953,10 @@
         <v>15</v>
       </c>
       <c r="B144" s="5">
-        <v>46009</v>
+        <v>46002</v>
       </c>
       <c r="C144" s="6">
-        <v>19</v>
+        <v>171</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -3960,7 +3964,7 @@
         <v>15</v>
       </c>
       <c r="B145" s="8">
-        <v>46010</v>
+        <v>46009</v>
       </c>
       <c r="C145" s="9">
         <v>19</v>
@@ -3971,10 +3975,10 @@
         <v>15</v>
       </c>
       <c r="B146" s="5">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="C146" s="6">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -3982,10 +3986,10 @@
         <v>15</v>
       </c>
       <c r="B147" s="8">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="C147" s="9">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -3993,10 +3997,10 @@
         <v>15</v>
       </c>
       <c r="B148" s="5">
-        <v>46013</v>
+        <v>46007</v>
       </c>
       <c r="C148" s="6">
-        <v>12</v>
+        <v>43</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -4004,10 +4008,10 @@
         <v>15</v>
       </c>
       <c r="B149" s="8">
-        <v>46080</v>
+        <v>46013</v>
       </c>
       <c r="C149" s="9">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -4015,10 +4019,10 @@
         <v>15</v>
       </c>
       <c r="B150" s="5">
-        <v>46090</v>
+        <v>46080</v>
       </c>
       <c r="C150" s="6">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -4026,10 +4030,10 @@
         <v>15</v>
       </c>
       <c r="B151" s="8">
-        <v>46079</v>
+        <v>46090</v>
       </c>
       <c r="C151" s="9">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -4037,10 +4041,10 @@
         <v>15</v>
       </c>
       <c r="B152" s="5">
-        <v>46015</v>
+        <v>46079</v>
       </c>
       <c r="C152" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -4048,10 +4052,10 @@
         <v>15</v>
       </c>
       <c r="B153" s="8">
-        <v>46085</v>
+        <v>46015</v>
       </c>
       <c r="C153" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -4059,10 +4063,10 @@
         <v>15</v>
       </c>
       <c r="B154" s="5">
-        <v>46098</v>
+        <v>46085</v>
       </c>
       <c r="C154" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -4070,10 +4074,10 @@
         <v>15</v>
       </c>
       <c r="B155" s="8">
-        <v>46021</v>
+        <v>46098</v>
       </c>
       <c r="C155" s="9">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -4081,10 +4085,10 @@
         <v>15</v>
       </c>
       <c r="B156" s="5">
-        <v>46078</v>
+        <v>46021</v>
       </c>
       <c r="C156" s="6">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -4092,10 +4096,10 @@
         <v>15</v>
       </c>
       <c r="B157" s="8">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="C157" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -4103,10 +4107,10 @@
         <v>15</v>
       </c>
       <c r="B158" s="5">
-        <v>46128</v>
+        <v>46084</v>
       </c>
       <c r="C158" s="6">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -4114,10 +4118,10 @@
         <v>15</v>
       </c>
       <c r="B159" s="8">
-        <v>46083</v>
+        <v>46128</v>
       </c>
       <c r="C159" s="9">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -4125,10 +4129,10 @@
         <v>15</v>
       </c>
       <c r="B160" s="5">
-        <v>46153</v>
+        <v>46083</v>
       </c>
       <c r="C160" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -4136,10 +4140,10 @@
         <v>15</v>
       </c>
       <c r="B161" s="8">
-        <v>46076</v>
+        <v>46153</v>
       </c>
       <c r="C161" s="9">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -4147,10 +4151,10 @@
         <v>15</v>
       </c>
       <c r="B162" s="5">
-        <v>46099</v>
+        <v>46076</v>
       </c>
       <c r="C162" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -4158,10 +4162,10 @@
         <v>15</v>
       </c>
       <c r="B163" s="8">
-        <v>46154</v>
+        <v>46099</v>
       </c>
       <c r="C163" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -4169,7 +4173,7 @@
         <v>15</v>
       </c>
       <c r="B164" s="5">
-        <v>46092</v>
+        <v>46154</v>
       </c>
       <c r="C164" s="6">
         <v>1</v>
@@ -4180,10 +4184,10 @@
         <v>15</v>
       </c>
       <c r="B165" s="8">
-        <v>46031</v>
+        <v>46092</v>
       </c>
       <c r="C165" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -4191,7 +4195,7 @@
         <v>15</v>
       </c>
       <c r="B166" s="5">
-        <v>46120</v>
+        <v>46031</v>
       </c>
       <c r="C166" s="6">
         <v>2</v>
@@ -4202,10 +4206,10 @@
         <v>15</v>
       </c>
       <c r="B167" s="8">
-        <v>46077</v>
+        <v>46120</v>
       </c>
       <c r="C167" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -4213,10 +4217,10 @@
         <v>15</v>
       </c>
       <c r="B168" s="5">
-        <v>46114</v>
+        <v>46077</v>
       </c>
       <c r="C168" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -4224,7 +4228,7 @@
         <v>15</v>
       </c>
       <c r="B169" s="8">
-        <v>46037</v>
+        <v>46114</v>
       </c>
       <c r="C169" s="9">
         <v>1</v>
@@ -4235,10 +4239,10 @@
         <v>15</v>
       </c>
       <c r="B170" s="5">
-        <v>46020</v>
+        <v>46037</v>
       </c>
       <c r="C170" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -4246,10 +4250,10 @@
         <v>15</v>
       </c>
       <c r="B171" s="8">
-        <v>46106</v>
+        <v>46020</v>
       </c>
       <c r="C171" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -4257,7 +4261,7 @@
         <v>15</v>
       </c>
       <c r="B172" s="5">
-        <v>46155</v>
+        <v>46106</v>
       </c>
       <c r="C172" s="6">
         <v>1</v>
@@ -4268,7 +4272,7 @@
         <v>15</v>
       </c>
       <c r="B173" s="8">
-        <v>46112</v>
+        <v>46155</v>
       </c>
       <c r="C173" s="9">
         <v>1</v>
@@ -4279,7 +4283,7 @@
         <v>15</v>
       </c>
       <c r="B174" s="5">
-        <v>46132</v>
+        <v>46112</v>
       </c>
       <c r="C174" s="6">
         <v>1</v>
@@ -4290,7 +4294,7 @@
         <v>15</v>
       </c>
       <c r="B175" s="8">
-        <v>46108</v>
+        <v>46132</v>
       </c>
       <c r="C175" s="9">
         <v>1</v>
@@ -4301,7 +4305,7 @@
         <v>15</v>
       </c>
       <c r="B176" s="5">
-        <v>46148</v>
+        <v>46108</v>
       </c>
       <c r="C176" s="6">
         <v>1</v>
@@ -4312,7 +4316,7 @@
         <v>15</v>
       </c>
       <c r="B177" s="8">
-        <v>46118</v>
+        <v>46148</v>
       </c>
       <c r="C177" s="9">
         <v>1</v>
@@ -4323,7 +4327,7 @@
         <v>15</v>
       </c>
       <c r="B178" s="5">
-        <v>46035</v>
+        <v>46118</v>
       </c>
       <c r="C178" s="6">
         <v>1</v>
@@ -4334,7 +4338,7 @@
         <v>15</v>
       </c>
       <c r="B179" s="8">
-        <v>46093</v>
+        <v>46035</v>
       </c>
       <c r="C179" s="9">
         <v>1</v>
@@ -4345,7 +4349,7 @@
         <v>15</v>
       </c>
       <c r="B180" s="5">
-        <v>46022</v>
+        <v>46093</v>
       </c>
       <c r="C180" s="6">
         <v>1</v>
@@ -4356,7 +4360,7 @@
         <v>15</v>
       </c>
       <c r="B181" s="8">
-        <v>46087</v>
+        <v>46022</v>
       </c>
       <c r="C181" s="9">
         <v>1</v>
@@ -4367,10 +4371,10 @@
         <v>15</v>
       </c>
       <c r="B182" s="5">
-        <v>46030</v>
+        <v>46087</v>
       </c>
       <c r="C182" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -4378,10 +4382,10 @@
         <v>15</v>
       </c>
       <c r="B183" s="8">
-        <v>46101</v>
+        <v>46030</v>
       </c>
       <c r="C183" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -4389,7 +4393,7 @@
         <v>15</v>
       </c>
       <c r="B184" s="5">
-        <v>46142</v>
+        <v>46101</v>
       </c>
       <c r="C184" s="6">
         <v>1</v>
@@ -4397,13 +4401,13 @@
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B185" s="8">
-        <v>46001</v>
+        <v>46142</v>
       </c>
       <c r="C185" s="9">
-        <v>153</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -4411,10 +4415,10 @@
         <v>21</v>
       </c>
       <c r="B186" s="5">
-        <v>46008</v>
+        <v>46001</v>
       </c>
       <c r="C186" s="6">
-        <v>38</v>
+        <v>153</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -4422,10 +4426,10 @@
         <v>21</v>
       </c>
       <c r="B187" s="8">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="C187" s="9">
-        <v>70</v>
+        <v>38</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -4433,10 +4437,10 @@
         <v>21</v>
       </c>
       <c r="B188" s="5">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="C188" s="6">
-        <v>111</v>
+        <v>70</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -4444,10 +4448,10 @@
         <v>21</v>
       </c>
       <c r="B189" s="8">
-        <v>46006</v>
+        <v>46002</v>
       </c>
       <c r="C189" s="9">
-        <v>147</v>
+        <v>111</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -4455,10 +4459,10 @@
         <v>21</v>
       </c>
       <c r="B190" s="5">
-        <v>46007</v>
+        <v>46006</v>
       </c>
       <c r="C190" s="6">
-        <v>45</v>
+        <v>147</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -4466,10 +4470,10 @@
         <v>21</v>
       </c>
       <c r="B191" s="8">
-        <v>46000</v>
+        <v>46007</v>
       </c>
       <c r="C191" s="9">
-        <v>129</v>
+        <v>45</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -4477,10 +4481,10 @@
         <v>21</v>
       </c>
       <c r="B192" s="5">
-        <v>46084</v>
+        <v>46000</v>
       </c>
       <c r="C192" s="6">
-        <v>10</v>
+        <v>129</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -4488,10 +4492,10 @@
         <v>21</v>
       </c>
       <c r="B193" s="8">
-        <v>46014</v>
+        <v>46084</v>
       </c>
       <c r="C193" s="9">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -4499,10 +4503,10 @@
         <v>21</v>
       </c>
       <c r="B194" s="5">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="C194" s="6">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -4510,10 +4514,10 @@
         <v>21</v>
       </c>
       <c r="B195" s="8">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="C195" s="9">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -4521,10 +4525,10 @@
         <v>21</v>
       </c>
       <c r="B196" s="5">
-        <v>46021</v>
+        <v>46010</v>
       </c>
       <c r="C196" s="6">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -4532,10 +4536,10 @@
         <v>21</v>
       </c>
       <c r="B197" s="8">
-        <v>46009</v>
+        <v>46021</v>
       </c>
       <c r="C197" s="9">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -4543,10 +4547,10 @@
         <v>21</v>
       </c>
       <c r="B198" s="5">
-        <v>46083</v>
+        <v>46009</v>
       </c>
       <c r="C198" s="6">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -4554,10 +4558,10 @@
         <v>21</v>
       </c>
       <c r="B199" s="8">
-        <v>46157</v>
+        <v>46083</v>
       </c>
       <c r="C199" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -4565,10 +4569,10 @@
         <v>21</v>
       </c>
       <c r="B200" s="5">
-        <v>46079</v>
+        <v>46157</v>
       </c>
       <c r="C200" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -4576,10 +4580,10 @@
         <v>21</v>
       </c>
       <c r="B201" s="8">
-        <v>46167</v>
+        <v>46079</v>
       </c>
       <c r="C201" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -4587,10 +4591,10 @@
         <v>21</v>
       </c>
       <c r="B202" s="5">
-        <v>46077</v>
+        <v>46167</v>
       </c>
       <c r="C202" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -4598,10 +4602,10 @@
         <v>21</v>
       </c>
       <c r="B203" s="8">
-        <v>46035</v>
+        <v>46077</v>
       </c>
       <c r="C203" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -4609,10 +4613,10 @@
         <v>21</v>
       </c>
       <c r="B204" s="5">
-        <v>46085</v>
+        <v>46035</v>
       </c>
       <c r="C204" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -4620,10 +4624,10 @@
         <v>21</v>
       </c>
       <c r="B205" s="8">
-        <v>46120</v>
+        <v>46085</v>
       </c>
       <c r="C205" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -4631,10 +4635,10 @@
         <v>21</v>
       </c>
       <c r="B206" s="5">
-        <v>46114</v>
+        <v>46120</v>
       </c>
       <c r="C206" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -4642,10 +4646,10 @@
         <v>21</v>
       </c>
       <c r="B207" s="8">
-        <v>46094</v>
+        <v>46114</v>
       </c>
       <c r="C207" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4653,10 +4657,10 @@
         <v>21</v>
       </c>
       <c r="B208" s="5">
-        <v>46080</v>
+        <v>46094</v>
       </c>
       <c r="C208" s="6">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4664,10 +4668,10 @@
         <v>21</v>
       </c>
       <c r="B209" s="8">
-        <v>46127</v>
+        <v>46080</v>
       </c>
       <c r="C209" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4675,7 +4679,7 @@
         <v>21</v>
       </c>
       <c r="B210" s="5">
-        <v>46091</v>
+        <v>46127</v>
       </c>
       <c r="C210" s="6">
         <v>2</v>
@@ -4686,10 +4690,10 @@
         <v>21</v>
       </c>
       <c r="B211" s="8">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="C211" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -4697,10 +4701,10 @@
         <v>21</v>
       </c>
       <c r="B212" s="5">
-        <v>46020</v>
+        <v>46090</v>
       </c>
       <c r="C212" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4708,10 +4712,10 @@
         <v>21</v>
       </c>
       <c r="B213" s="8">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="C213" s="9">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4719,10 +4723,10 @@
         <v>21</v>
       </c>
       <c r="B214" s="5">
-        <v>46078</v>
+        <v>46015</v>
       </c>
       <c r="C214" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4730,10 +4734,10 @@
         <v>21</v>
       </c>
       <c r="B215" s="8">
-        <v>46148</v>
+        <v>46078</v>
       </c>
       <c r="C215" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4741,7 +4745,7 @@
         <v>21</v>
       </c>
       <c r="B216" s="5">
-        <v>46105</v>
+        <v>46148</v>
       </c>
       <c r="C216" s="6">
         <v>2</v>
@@ -4752,10 +4756,10 @@
         <v>21</v>
       </c>
       <c r="B217" s="8">
-        <v>46087</v>
+        <v>46105</v>
       </c>
       <c r="C217" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -4763,7 +4767,7 @@
         <v>21</v>
       </c>
       <c r="B218" s="5">
-        <v>46107</v>
+        <v>46087</v>
       </c>
       <c r="C218" s="6">
         <v>3</v>
@@ -4774,10 +4778,10 @@
         <v>21</v>
       </c>
       <c r="B219" s="8">
-        <v>46086</v>
+        <v>46107</v>
       </c>
       <c r="C219" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4785,10 +4789,10 @@
         <v>21</v>
       </c>
       <c r="B220" s="5">
-        <v>46106</v>
+        <v>46086</v>
       </c>
       <c r="C220" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -4796,10 +4800,10 @@
         <v>21</v>
       </c>
       <c r="B221" s="8">
-        <v>46150</v>
+        <v>46106</v>
       </c>
       <c r="C221" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -4807,7 +4811,7 @@
         <v>21</v>
       </c>
       <c r="B222" s="5">
-        <v>46104</v>
+        <v>46150</v>
       </c>
       <c r="C222" s="6">
         <v>3</v>
@@ -4818,10 +4822,10 @@
         <v>21</v>
       </c>
       <c r="B223" s="8">
-        <v>46118</v>
+        <v>46104</v>
       </c>
       <c r="C223" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -4829,10 +4833,10 @@
         <v>21</v>
       </c>
       <c r="B224" s="5">
-        <v>46076</v>
+        <v>46118</v>
       </c>
       <c r="C224" s="6">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -4840,10 +4844,10 @@
         <v>21</v>
       </c>
       <c r="B225" s="8">
-        <v>46154</v>
+        <v>46076</v>
       </c>
       <c r="C225" s="9">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -4851,10 +4855,10 @@
         <v>21</v>
       </c>
       <c r="B226" s="5">
-        <v>46093</v>
+        <v>46154</v>
       </c>
       <c r="C226" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -4862,10 +4866,10 @@
         <v>21</v>
       </c>
       <c r="B227" s="8">
-        <v>46122</v>
+        <v>46093</v>
       </c>
       <c r="C227" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -4873,10 +4877,10 @@
         <v>21</v>
       </c>
       <c r="B228" s="5">
-        <v>46092</v>
+        <v>46122</v>
       </c>
       <c r="C228" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -4884,10 +4888,10 @@
         <v>21</v>
       </c>
       <c r="B229" s="8">
-        <v>46156</v>
+        <v>46092</v>
       </c>
       <c r="C229" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -4895,10 +4899,10 @@
         <v>21</v>
       </c>
       <c r="B230" s="5">
-        <v>46133</v>
+        <v>46156</v>
       </c>
       <c r="C230" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -4906,7 +4910,7 @@
         <v>21</v>
       </c>
       <c r="B231" s="8">
-        <v>46126</v>
+        <v>46133</v>
       </c>
       <c r="C231" s="9">
         <v>1</v>
@@ -4917,10 +4921,10 @@
         <v>21</v>
       </c>
       <c r="B232" s="5">
-        <v>46022</v>
+        <v>46126</v>
       </c>
       <c r="C232" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -4928,7 +4932,7 @@
         <v>21</v>
       </c>
       <c r="B233" s="8">
-        <v>46100</v>
+        <v>46022</v>
       </c>
       <c r="C233" s="9">
         <v>2</v>
@@ -4939,10 +4943,10 @@
         <v>21</v>
       </c>
       <c r="B234" s="5">
-        <v>46101</v>
+        <v>46100</v>
       </c>
       <c r="C234" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -4950,10 +4954,10 @@
         <v>21</v>
       </c>
       <c r="B235" s="8">
-        <v>46097</v>
+        <v>46101</v>
       </c>
       <c r="C235" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -4961,10 +4965,10 @@
         <v>21</v>
       </c>
       <c r="B236" s="5">
-        <v>46108</v>
+        <v>46097</v>
       </c>
       <c r="C236" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -4972,10 +4976,10 @@
         <v>21</v>
       </c>
       <c r="B237" s="8">
-        <v>46098</v>
+        <v>46108</v>
       </c>
       <c r="C237" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -4983,10 +4987,10 @@
         <v>21</v>
       </c>
       <c r="B238" s="5">
-        <v>46113</v>
+        <v>46098</v>
       </c>
       <c r="C238" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -4994,7 +4998,7 @@
         <v>21</v>
       </c>
       <c r="B239" s="8">
-        <v>46142</v>
+        <v>46113</v>
       </c>
       <c r="C239" s="9">
         <v>1</v>
@@ -5005,7 +5009,7 @@
         <v>21</v>
       </c>
       <c r="B240" s="5">
-        <v>46153</v>
+        <v>46142</v>
       </c>
       <c r="C240" s="6">
         <v>1</v>
@@ -5016,7 +5020,7 @@
         <v>21</v>
       </c>
       <c r="B241" s="8">
-        <v>46031</v>
+        <v>46153</v>
       </c>
       <c r="C241" s="9">
         <v>1</v>
@@ -5027,9 +5031,20 @@
         <v>21</v>
       </c>
       <c r="B242" s="5">
+        <v>46031</v>
+      </c>
+      <c r="C242" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B243" s="8">
         <v>46155</v>
       </c>
-      <c r="C242" s="6">
+      <c r="C243" s="9">
         <v>1</v>
       </c>
     </row>
@@ -5198,7 +5213,7 @@
         <v>5</v>
       </c>
       <c r="E9">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -5552,7 +5567,7 @@
         <v>98</v>
       </c>
       <c r="D30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E30">
         <v>12</v>
@@ -5586,7 +5601,7 @@
         <v>84</v>
       </c>
       <c r="D32">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E32">
         <v>88</v>
@@ -5756,7 +5771,7 @@
         <v>43</v>
       </c>
       <c r="C3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -6897,10 +6912,10 @@
         <v>15</v>
       </c>
       <c r="B107" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="C107">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -6908,7 +6923,7 @@
         <v>15</v>
       </c>
       <c r="B108" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C108">
         <v>4</v>
@@ -6919,7 +6934,7 @@
         <v>15</v>
       </c>
       <c r="B109" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C109">
         <v>4</v>
@@ -6930,7 +6945,7 @@
         <v>15</v>
       </c>
       <c r="B110" t="s">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="C110">
         <v>4</v>
@@ -7832,10 +7847,10 @@
         <v>16</v>
       </c>
       <c r="B192" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C192">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -7843,7 +7858,7 @@
         <v>16</v>
       </c>
       <c r="B193" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="C193">
         <v>11</v>
@@ -9652,7 +9667,7 @@
         <v>287</v>
       </c>
       <c r="C3">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -9773,7 +9788,7 @@
         <v>290</v>
       </c>
       <c r="C14">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -9894,7 +9909,7 @@
         <v>287</v>
       </c>
       <c r="C25">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="118" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39B7227F-CD69-4888-8833-0B91B1920956}"/>
+  <xr:revisionPtr revIDLastSave="131" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{233474BD-2F56-4F32-8FEB-CA6D64773B22}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="667" activeTab="6" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" tabRatio="667" activeTab="7" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="mat_2026" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="origen_estudiantes" sheetId="5" r:id="rId5"/>
     <sheet name="origen_colegios" sheetId="6" r:id="rId6"/>
     <sheet name="com_est" sheetId="7" r:id="rId7"/>
+    <sheet name="cantidad_cursos" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">mat_2026!$A$1:$E$39</definedName>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1236" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1315" uniqueCount="300">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -940,6 +941,12 @@
   </si>
   <si>
     <t>Colina</t>
+  </si>
+  <si>
+    <t>PRE-KINDER</t>
+  </si>
+  <si>
+    <t>CURSOS</t>
   </si>
 </sst>
 </file>
@@ -10113,4 +10120,448 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A394073B-D687-4CC9-855F-76C313D18351}">
+  <dimension ref="A1:C39"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" customWidth="1"/>
+    <col min="3" max="3" width="20.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>298</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>298</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>298</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>16</v>
+      </c>
+      <c r="B34" t="s">
+        <v>19</v>
+      </c>
+      <c r="C34">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B35" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>21</v>
+      </c>
+      <c r="B36" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>21</v>
+      </c>
+      <c r="B38" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="131" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{233474BD-2F56-4F32-8FEB-CA6D64773B22}"/>
+  <xr:revisionPtr revIDLastSave="140" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17178297-3EDB-4DB5-BD1F-E10B1FA6D658}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" tabRatio="667" activeTab="7" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" tabRatio="731" firstSheet="2" activeTab="7" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="mat_2026" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1315" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1317" uniqueCount="300">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -1033,7 +1033,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1050,6 +1050,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1530,10 +1532,10 @@
         <v>75</v>
       </c>
       <c r="D8">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E8">
-        <v>1.08</v>
+        <v>1.0669999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -1751,10 +1753,10 @@
         <v>88</v>
       </c>
       <c r="D21">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E21">
-        <v>1.0229999999999999</v>
+        <v>1.0109999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -1921,10 +1923,10 @@
         <v>138</v>
       </c>
       <c r="D31">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E31">
-        <v>1.0580000000000001</v>
+        <v>1.0509999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1938,10 +1940,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E32">
-        <v>1.0660000000000001</v>
+        <v>1.0629999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1955,10 +1957,10 @@
         <v>329</v>
       </c>
       <c r="D33">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E33">
-        <v>1.0269999999999999</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2023,10 +2025,10 @@
         <v>217</v>
       </c>
       <c r="D37">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E37">
-        <v>1.0049999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -2040,10 +2042,10 @@
         <v>226</v>
       </c>
       <c r="D38">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E38">
-        <v>1.08</v>
+        <v>1.075</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -2057,10 +2059,10 @@
         <v>214</v>
       </c>
       <c r="D39">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E39">
-        <v>0.93500000000000005</v>
+        <v>0.93</v>
       </c>
     </row>
   </sheetData>
@@ -2276,7 +2278,7 @@
         <v>35</v>
       </c>
       <c r="C3">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2287,7 +2289,7 @@
         <v>34</v>
       </c>
       <c r="C4">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2298,7 +2300,7 @@
         <v>35</v>
       </c>
       <c r="C5">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2320,7 +2322,7 @@
         <v>34</v>
       </c>
       <c r="C7">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -2331,7 +2333,7 @@
         <v>34</v>
       </c>
       <c r="C8">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2364,7 +2366,7 @@
         <v>34</v>
       </c>
       <c r="C11">
-        <v>430</v>
+        <v>427</v>
       </c>
     </row>
   </sheetData>
@@ -2374,7 +2376,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD19485A-0629-47F9-A5AD-80ABA7A6E076}">
-  <dimension ref="A1:C243"/>
+  <dimension ref="A1:C245"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -2467,7 +2469,7 @@
         <v>46006</v>
       </c>
       <c r="C8" s="6">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2552,10 +2554,10 @@
         <v>16</v>
       </c>
       <c r="B16" s="5">
-        <v>46020</v>
+        <v>46015</v>
       </c>
       <c r="C16" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -2563,10 +2565,10 @@
         <v>16</v>
       </c>
       <c r="B17" s="8">
-        <v>46015</v>
+        <v>46083</v>
       </c>
       <c r="C17" s="9">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -2574,10 +2576,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="5">
-        <v>46083</v>
+        <v>46162</v>
       </c>
       <c r="C18" s="6">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -2585,10 +2587,10 @@
         <v>16</v>
       </c>
       <c r="B19" s="8">
-        <v>46162</v>
+        <v>46097</v>
       </c>
       <c r="C19" s="9">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -2596,10 +2598,10 @@
         <v>16</v>
       </c>
       <c r="B20" s="5">
-        <v>46097</v>
+        <v>46021</v>
       </c>
       <c r="C20" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -2607,10 +2609,10 @@
         <v>16</v>
       </c>
       <c r="B21" s="8">
-        <v>46021</v>
+        <v>46080</v>
       </c>
       <c r="C21" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -2618,10 +2620,10 @@
         <v>16</v>
       </c>
       <c r="B22" s="5">
-        <v>46080</v>
+        <v>46087</v>
       </c>
       <c r="C22" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -2629,10 +2631,10 @@
         <v>16</v>
       </c>
       <c r="B23" s="8">
-        <v>46087</v>
+        <v>46022</v>
       </c>
       <c r="C23" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -2640,10 +2642,10 @@
         <v>16</v>
       </c>
       <c r="B24" s="5">
-        <v>46022</v>
+        <v>46161</v>
       </c>
       <c r="C24" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -2651,10 +2653,10 @@
         <v>16</v>
       </c>
       <c r="B25" s="8">
-        <v>46161</v>
+        <v>46086</v>
       </c>
       <c r="C25" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -2662,10 +2664,10 @@
         <v>16</v>
       </c>
       <c r="B26" s="5">
-        <v>46086</v>
+        <v>46020</v>
       </c>
       <c r="C26" s="6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -2893,7 +2895,7 @@
         <v>16</v>
       </c>
       <c r="B47" s="8">
-        <v>46125</v>
+        <v>46175</v>
       </c>
       <c r="C47" s="9">
         <v>1</v>
@@ -2904,7 +2906,7 @@
         <v>16</v>
       </c>
       <c r="B48" s="5">
-        <v>46093</v>
+        <v>46125</v>
       </c>
       <c r="C48" s="6">
         <v>1</v>
@@ -2915,7 +2917,7 @@
         <v>16</v>
       </c>
       <c r="B49" s="8">
-        <v>46156</v>
+        <v>46176</v>
       </c>
       <c r="C49" s="9">
         <v>1</v>
@@ -2926,7 +2928,7 @@
         <v>16</v>
       </c>
       <c r="B50" s="5">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="C50" s="6">
         <v>1</v>
@@ -2937,7 +2939,7 @@
         <v>16</v>
       </c>
       <c r="B51" s="8">
-        <v>46101</v>
+        <v>46156</v>
       </c>
       <c r="C51" s="9">
         <v>1</v>
@@ -2945,24 +2947,24 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B52" s="5">
-        <v>46007</v>
+        <v>46092</v>
       </c>
       <c r="C52" s="6">
-        <v>78</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B53" s="8">
-        <v>46009</v>
+        <v>46101</v>
       </c>
       <c r="C53" s="9">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -2970,10 +2972,10 @@
         <v>14</v>
       </c>
       <c r="B54" s="5">
-        <v>46000</v>
+        <v>46007</v>
       </c>
       <c r="C54" s="6">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -2981,10 +2983,10 @@
         <v>14</v>
       </c>
       <c r="B55" s="8">
-        <v>46001</v>
+        <v>46009</v>
       </c>
       <c r="C55" s="9">
-        <v>83</v>
+        <v>34</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -2992,10 +2994,10 @@
         <v>14</v>
       </c>
       <c r="B56" s="5">
-        <v>46006</v>
+        <v>46000</v>
       </c>
       <c r="C56" s="6">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -3003,10 +3005,10 @@
         <v>14</v>
       </c>
       <c r="B57" s="8">
-        <v>46010</v>
+        <v>46001</v>
       </c>
       <c r="C57" s="9">
-        <v>24</v>
+        <v>83</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -3014,10 +3016,10 @@
         <v>14</v>
       </c>
       <c r="B58" s="5">
-        <v>46014</v>
+        <v>46006</v>
       </c>
       <c r="C58" s="6">
-        <v>20</v>
+        <v>79</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -3025,10 +3027,10 @@
         <v>14</v>
       </c>
       <c r="B59" s="8">
-        <v>46002</v>
+        <v>46010</v>
       </c>
       <c r="C59" s="9">
-        <v>47</v>
+        <v>24</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -3036,10 +3038,10 @@
         <v>14</v>
       </c>
       <c r="B60" s="5">
-        <v>46008</v>
+        <v>46014</v>
       </c>
       <c r="C60" s="6">
-        <v>58</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -3047,7 +3049,7 @@
         <v>14</v>
       </c>
       <c r="B61" s="8">
-        <v>46003</v>
+        <v>46002</v>
       </c>
       <c r="C61" s="9">
         <v>47</v>
@@ -3058,10 +3060,10 @@
         <v>14</v>
       </c>
       <c r="B62" s="5">
-        <v>46013</v>
+        <v>46008</v>
       </c>
       <c r="C62" s="6">
-        <v>30</v>
+        <v>58</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -3069,10 +3071,10 @@
         <v>14</v>
       </c>
       <c r="B63" s="8">
-        <v>46022</v>
+        <v>46003</v>
       </c>
       <c r="C63" s="9">
-        <v>2</v>
+        <v>47</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -3080,10 +3082,10 @@
         <v>14</v>
       </c>
       <c r="B64" s="5">
-        <v>46080</v>
+        <v>46013</v>
       </c>
       <c r="C64" s="6">
-        <v>8</v>
+        <v>30</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -3091,10 +3093,10 @@
         <v>14</v>
       </c>
       <c r="B65" s="8">
-        <v>46084</v>
+        <v>46022</v>
       </c>
       <c r="C65" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -3102,10 +3104,10 @@
         <v>14</v>
       </c>
       <c r="B66" s="5">
-        <v>46125</v>
+        <v>46080</v>
       </c>
       <c r="C66" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -3113,7 +3115,7 @@
         <v>14</v>
       </c>
       <c r="B67" s="8">
-        <v>46091</v>
+        <v>46084</v>
       </c>
       <c r="C67" s="9">
         <v>3</v>
@@ -3124,10 +3126,10 @@
         <v>14</v>
       </c>
       <c r="B68" s="5">
-        <v>46083</v>
+        <v>46125</v>
       </c>
       <c r="C68" s="6">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -3135,10 +3137,10 @@
         <v>14</v>
       </c>
       <c r="B69" s="8">
-        <v>46105</v>
+        <v>46091</v>
       </c>
       <c r="C69" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -3146,10 +3148,10 @@
         <v>14</v>
       </c>
       <c r="B70" s="5">
-        <v>46077</v>
+        <v>46083</v>
       </c>
       <c r="C70" s="6">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -3157,10 +3159,10 @@
         <v>14</v>
       </c>
       <c r="B71" s="8">
-        <v>46118</v>
+        <v>46105</v>
       </c>
       <c r="C71" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -3168,10 +3170,10 @@
         <v>14</v>
       </c>
       <c r="B72" s="5">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="C72" s="6">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -3179,10 +3181,10 @@
         <v>14</v>
       </c>
       <c r="B73" s="8">
-        <v>46099</v>
+        <v>46118</v>
       </c>
       <c r="C73" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -3190,10 +3192,10 @@
         <v>14</v>
       </c>
       <c r="B74" s="5">
-        <v>46104</v>
+        <v>46078</v>
       </c>
       <c r="C74" s="6">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -3201,7 +3203,7 @@
         <v>14</v>
       </c>
       <c r="B75" s="8">
-        <v>46107</v>
+        <v>46099</v>
       </c>
       <c r="C75" s="9">
         <v>2</v>
@@ -3212,10 +3214,10 @@
         <v>14</v>
       </c>
       <c r="B76" s="5">
-        <v>46020</v>
+        <v>46104</v>
       </c>
       <c r="C76" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -3223,10 +3225,10 @@
         <v>14</v>
       </c>
       <c r="B77" s="8">
-        <v>46076</v>
+        <v>46107</v>
       </c>
       <c r="C77" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -3234,10 +3236,10 @@
         <v>14</v>
       </c>
       <c r="B78" s="5">
-        <v>46111</v>
+        <v>46020</v>
       </c>
       <c r="C78" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -3245,10 +3247,10 @@
         <v>14</v>
       </c>
       <c r="B79" s="8">
-        <v>46087</v>
+        <v>46076</v>
       </c>
       <c r="C79" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -3256,10 +3258,10 @@
         <v>14</v>
       </c>
       <c r="B80" s="5">
-        <v>46140</v>
+        <v>46111</v>
       </c>
       <c r="C80" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -3267,10 +3269,10 @@
         <v>14</v>
       </c>
       <c r="B81" s="8">
-        <v>46113</v>
+        <v>46087</v>
       </c>
       <c r="C81" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -3278,7 +3280,7 @@
         <v>14</v>
       </c>
       <c r="B82" s="5">
-        <v>46119</v>
+        <v>46140</v>
       </c>
       <c r="C82" s="6">
         <v>2</v>
@@ -3289,10 +3291,10 @@
         <v>14</v>
       </c>
       <c r="B83" s="8">
-        <v>46108</v>
+        <v>46113</v>
       </c>
       <c r="C83" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -3300,10 +3302,10 @@
         <v>14</v>
       </c>
       <c r="B84" s="5">
-        <v>46098</v>
+        <v>46119</v>
       </c>
       <c r="C84" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -3311,7 +3313,7 @@
         <v>14</v>
       </c>
       <c r="B85" s="8">
-        <v>46141</v>
+        <v>46108</v>
       </c>
       <c r="C85" s="9">
         <v>1</v>
@@ -3322,7 +3324,7 @@
         <v>14</v>
       </c>
       <c r="B86" s="5">
-        <v>46114</v>
+        <v>46098</v>
       </c>
       <c r="C86" s="6">
         <v>1</v>
@@ -3333,10 +3335,10 @@
         <v>14</v>
       </c>
       <c r="B87" s="8">
-        <v>46079</v>
+        <v>46141</v>
       </c>
       <c r="C87" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -3344,7 +3346,7 @@
         <v>14</v>
       </c>
       <c r="B88" s="5">
-        <v>46139</v>
+        <v>46114</v>
       </c>
       <c r="C88" s="6">
         <v>1</v>
@@ -3355,10 +3357,10 @@
         <v>14</v>
       </c>
       <c r="B89" s="8">
-        <v>46148</v>
+        <v>46079</v>
       </c>
       <c r="C89" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -3366,7 +3368,7 @@
         <v>14</v>
       </c>
       <c r="B90" s="5">
-        <v>46092</v>
+        <v>46139</v>
       </c>
       <c r="C90" s="6">
         <v>1</v>
@@ -3377,7 +3379,7 @@
         <v>14</v>
       </c>
       <c r="B91" s="8">
-        <v>46021</v>
+        <v>46148</v>
       </c>
       <c r="C91" s="9">
         <v>2</v>
@@ -3388,10 +3390,10 @@
         <v>14</v>
       </c>
       <c r="B92" s="5">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="C92" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -3399,10 +3401,10 @@
         <v>14</v>
       </c>
       <c r="B93" s="8">
-        <v>46147</v>
+        <v>46021</v>
       </c>
       <c r="C93" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -3410,32 +3412,32 @@
         <v>14</v>
       </c>
       <c r="B94" s="5">
-        <v>46134</v>
+        <v>46086</v>
       </c>
       <c r="C94" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B95" s="8">
-        <v>46003</v>
+        <v>46147</v>
       </c>
       <c r="C95" s="9">
-        <v>95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B96" s="5">
-        <v>46002</v>
+        <v>46134</v>
       </c>
       <c r="C96" s="6">
-        <v>115</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -3443,10 +3445,10 @@
         <v>3</v>
       </c>
       <c r="B97" s="8">
-        <v>46008</v>
+        <v>46003</v>
       </c>
       <c r="C97" s="9">
-        <v>15</v>
+        <v>95</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -3454,10 +3456,10 @@
         <v>3</v>
       </c>
       <c r="B98" s="5">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="C98" s="6">
-        <v>98</v>
+        <v>115</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -3465,10 +3467,10 @@
         <v>3</v>
       </c>
       <c r="B99" s="8">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="C99" s="9">
-        <v>41</v>
+        <v>15</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -3476,10 +3478,10 @@
         <v>3</v>
       </c>
       <c r="B100" s="5">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C100" s="6">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -3487,10 +3489,10 @@
         <v>3</v>
       </c>
       <c r="B101" s="8">
-        <v>46010</v>
+        <v>46007</v>
       </c>
       <c r="C101" s="9">
-        <v>9</v>
+        <v>40</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -3498,10 +3500,10 @@
         <v>3</v>
       </c>
       <c r="B102" s="5">
-        <v>46006</v>
+        <v>46001</v>
       </c>
       <c r="C102" s="6">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -3509,10 +3511,10 @@
         <v>3</v>
       </c>
       <c r="B103" s="8">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="C103" s="9">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -3520,10 +3522,10 @@
         <v>3</v>
       </c>
       <c r="B104" s="5">
-        <v>46015</v>
+        <v>46006</v>
       </c>
       <c r="C104" s="6">
-        <v>1</v>
+        <v>84</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -3531,10 +3533,10 @@
         <v>3</v>
       </c>
       <c r="B105" s="8">
-        <v>46014</v>
+        <v>46009</v>
       </c>
       <c r="C105" s="9">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -3542,10 +3544,10 @@
         <v>3</v>
       </c>
       <c r="B106" s="5">
-        <v>46013</v>
+        <v>46015</v>
       </c>
       <c r="C106" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -3553,10 +3555,10 @@
         <v>3</v>
       </c>
       <c r="B107" s="8">
-        <v>46021</v>
+        <v>46014</v>
       </c>
       <c r="C107" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -3564,10 +3566,10 @@
         <v>3</v>
       </c>
       <c r="B108" s="5">
-        <v>46077</v>
+        <v>46013</v>
       </c>
       <c r="C108" s="6">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -3575,10 +3577,10 @@
         <v>3</v>
       </c>
       <c r="B109" s="8">
-        <v>46167</v>
+        <v>46021</v>
       </c>
       <c r="C109" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -3586,10 +3588,10 @@
         <v>3</v>
       </c>
       <c r="B110" s="5">
-        <v>46090</v>
+        <v>46077</v>
       </c>
       <c r="C110" s="6">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -3597,7 +3599,7 @@
         <v>3</v>
       </c>
       <c r="B111" s="8">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="C111" s="9">
         <v>1</v>
@@ -3608,10 +3610,10 @@
         <v>3</v>
       </c>
       <c r="B112" s="5">
-        <v>46093</v>
+        <v>46090</v>
       </c>
       <c r="C112" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -3619,10 +3621,10 @@
         <v>3</v>
       </c>
       <c r="B113" s="8">
-        <v>46078</v>
+        <v>46170</v>
       </c>
       <c r="C113" s="9">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -3630,10 +3632,10 @@
         <v>3</v>
       </c>
       <c r="B114" s="5">
-        <v>46084</v>
+        <v>46093</v>
       </c>
       <c r="C114" s="6">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -3641,10 +3643,10 @@
         <v>3</v>
       </c>
       <c r="B115" s="8">
-        <v>46134</v>
+        <v>46078</v>
       </c>
       <c r="C115" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -3652,10 +3654,10 @@
         <v>3</v>
       </c>
       <c r="B116" s="5">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="C116" s="6">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -3663,10 +3665,10 @@
         <v>3</v>
       </c>
       <c r="B117" s="8">
-        <v>46022</v>
+        <v>46134</v>
       </c>
       <c r="C117" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -3674,10 +3676,10 @@
         <v>3</v>
       </c>
       <c r="B118" s="5">
-        <v>46114</v>
+        <v>46083</v>
       </c>
       <c r="C118" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -3685,7 +3687,7 @@
         <v>3</v>
       </c>
       <c r="B119" s="8">
-        <v>46135</v>
+        <v>46022</v>
       </c>
       <c r="C119" s="9">
         <v>1</v>
@@ -3696,10 +3698,10 @@
         <v>3</v>
       </c>
       <c r="B120" s="5">
-        <v>46168</v>
+        <v>46114</v>
       </c>
       <c r="C120" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -3707,10 +3709,10 @@
         <v>3</v>
       </c>
       <c r="B121" s="8">
-        <v>46126</v>
+        <v>46135</v>
       </c>
       <c r="C121" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -3718,7 +3720,7 @@
         <v>3</v>
       </c>
       <c r="B122" s="5">
-        <v>46120</v>
+        <v>46168</v>
       </c>
       <c r="C122" s="6">
         <v>3</v>
@@ -3729,10 +3731,10 @@
         <v>3</v>
       </c>
       <c r="B123" s="8">
-        <v>46127</v>
+        <v>46126</v>
       </c>
       <c r="C123" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -3740,10 +3742,10 @@
         <v>3</v>
       </c>
       <c r="B124" s="5">
-        <v>46087</v>
+        <v>46120</v>
       </c>
       <c r="C124" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -3751,7 +3753,7 @@
         <v>3</v>
       </c>
       <c r="B125" s="8">
-        <v>46108</v>
+        <v>46127</v>
       </c>
       <c r="C125" s="9">
         <v>1</v>
@@ -3762,7 +3764,7 @@
         <v>3</v>
       </c>
       <c r="B126" s="5">
-        <v>46020</v>
+        <v>46087</v>
       </c>
       <c r="C126" s="6">
         <v>1</v>
@@ -3773,7 +3775,7 @@
         <v>3</v>
       </c>
       <c r="B127" s="8">
-        <v>46097</v>
+        <v>46108</v>
       </c>
       <c r="C127" s="9">
         <v>1</v>
@@ -3784,10 +3786,10 @@
         <v>3</v>
       </c>
       <c r="B128" s="5">
-        <v>46161</v>
+        <v>46020</v>
       </c>
       <c r="C128" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -3795,7 +3797,7 @@
         <v>3</v>
       </c>
       <c r="B129" s="8">
-        <v>46129</v>
+        <v>46097</v>
       </c>
       <c r="C129" s="9">
         <v>1</v>
@@ -3806,10 +3808,10 @@
         <v>3</v>
       </c>
       <c r="B130" s="5">
-        <v>46080</v>
+        <v>46161</v>
       </c>
       <c r="C130" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -3817,7 +3819,7 @@
         <v>3</v>
       </c>
       <c r="B131" s="8">
-        <v>46101</v>
+        <v>46129</v>
       </c>
       <c r="C131" s="9">
         <v>1</v>
@@ -3828,7 +3830,7 @@
         <v>3</v>
       </c>
       <c r="B132" s="5">
-        <v>46155</v>
+        <v>46080</v>
       </c>
       <c r="C132" s="6">
         <v>1</v>
@@ -3839,7 +3841,7 @@
         <v>3</v>
       </c>
       <c r="B133" s="8">
-        <v>46150</v>
+        <v>46101</v>
       </c>
       <c r="C133" s="9">
         <v>1</v>
@@ -3850,7 +3852,7 @@
         <v>3</v>
       </c>
       <c r="B134" s="5">
-        <v>46141</v>
+        <v>46155</v>
       </c>
       <c r="C134" s="6">
         <v>1</v>
@@ -3861,7 +3863,7 @@
         <v>3</v>
       </c>
       <c r="B135" s="8">
-        <v>46085</v>
+        <v>46150</v>
       </c>
       <c r="C135" s="9">
         <v>1</v>
@@ -3872,7 +3874,7 @@
         <v>3</v>
       </c>
       <c r="B136" s="5">
-        <v>46148</v>
+        <v>46141</v>
       </c>
       <c r="C136" s="6">
         <v>1</v>
@@ -3883,10 +3885,10 @@
         <v>3</v>
       </c>
       <c r="B137" s="8">
-        <v>46118</v>
+        <v>46085</v>
       </c>
       <c r="C137" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -3894,7 +3896,7 @@
         <v>3</v>
       </c>
       <c r="B138" s="5">
-        <v>46079</v>
+        <v>46148</v>
       </c>
       <c r="C138" s="6">
         <v>1</v>
@@ -3902,24 +3904,24 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B139" s="8">
-        <v>46003</v>
+        <v>46118</v>
       </c>
       <c r="C139" s="9">
-        <v>92</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B140" s="5">
-        <v>46000</v>
+        <v>46079</v>
       </c>
       <c r="C140" s="6">
-        <v>132</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -3927,10 +3929,10 @@
         <v>15</v>
       </c>
       <c r="B141" s="8">
-        <v>46006</v>
+        <v>46003</v>
       </c>
       <c r="C141" s="9">
-        <v>173</v>
+        <v>92</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -3938,10 +3940,10 @@
         <v>15</v>
       </c>
       <c r="B142" s="5">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C142" s="6">
-        <v>174</v>
+        <v>132</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -3949,10 +3951,10 @@
         <v>15</v>
       </c>
       <c r="B143" s="8">
-        <v>46014</v>
+        <v>46006</v>
       </c>
       <c r="C143" s="9">
-        <v>16</v>
+        <v>173</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -3960,10 +3962,10 @@
         <v>15</v>
       </c>
       <c r="B144" s="5">
-        <v>46002</v>
+        <v>46001</v>
       </c>
       <c r="C144" s="6">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -3971,10 +3973,10 @@
         <v>15</v>
       </c>
       <c r="B145" s="8">
-        <v>46009</v>
+        <v>46014</v>
       </c>
       <c r="C145" s="9">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -3982,10 +3984,10 @@
         <v>15</v>
       </c>
       <c r="B146" s="5">
-        <v>46010</v>
+        <v>46002</v>
       </c>
       <c r="C146" s="6">
-        <v>19</v>
+        <v>171</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -3993,10 +3995,10 @@
         <v>15</v>
       </c>
       <c r="B147" s="8">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="C147" s="9">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -4004,10 +4006,10 @@
         <v>15</v>
       </c>
       <c r="B148" s="5">
-        <v>46007</v>
+        <v>46010</v>
       </c>
       <c r="C148" s="6">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -4015,10 +4017,10 @@
         <v>15</v>
       </c>
       <c r="B149" s="8">
-        <v>46013</v>
+        <v>46008</v>
       </c>
       <c r="C149" s="9">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -4026,10 +4028,10 @@
         <v>15</v>
       </c>
       <c r="B150" s="5">
-        <v>46080</v>
+        <v>46007</v>
       </c>
       <c r="C150" s="6">
-        <v>2</v>
+        <v>43</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -4037,10 +4039,10 @@
         <v>15</v>
       </c>
       <c r="B151" s="8">
-        <v>46090</v>
+        <v>46013</v>
       </c>
       <c r="C151" s="9">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -4048,10 +4050,10 @@
         <v>15</v>
       </c>
       <c r="B152" s="5">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="C152" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -4059,10 +4061,10 @@
         <v>15</v>
       </c>
       <c r="B153" s="8">
-        <v>46015</v>
+        <v>46090</v>
       </c>
       <c r="C153" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -4070,10 +4072,10 @@
         <v>15</v>
       </c>
       <c r="B154" s="5">
-        <v>46085</v>
+        <v>46079</v>
       </c>
       <c r="C154" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -4081,10 +4083,10 @@
         <v>15</v>
       </c>
       <c r="B155" s="8">
-        <v>46098</v>
+        <v>46015</v>
       </c>
       <c r="C155" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -4092,10 +4094,10 @@
         <v>15</v>
       </c>
       <c r="B156" s="5">
-        <v>46021</v>
+        <v>46085</v>
       </c>
       <c r="C156" s="6">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -4103,10 +4105,10 @@
         <v>15</v>
       </c>
       <c r="B157" s="8">
-        <v>46078</v>
+        <v>46098</v>
       </c>
       <c r="C157" s="9">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -4114,10 +4116,10 @@
         <v>15</v>
       </c>
       <c r="B158" s="5">
-        <v>46084</v>
+        <v>46021</v>
       </c>
       <c r="C158" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -4125,10 +4127,10 @@
         <v>15</v>
       </c>
       <c r="B159" s="8">
-        <v>46128</v>
+        <v>46078</v>
       </c>
       <c r="C159" s="9">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -4136,7 +4138,7 @@
         <v>15</v>
       </c>
       <c r="B160" s="5">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="C160" s="6">
         <v>8</v>
@@ -4147,10 +4149,10 @@
         <v>15</v>
       </c>
       <c r="B161" s="8">
-        <v>46153</v>
+        <v>46128</v>
       </c>
       <c r="C161" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -4158,10 +4160,10 @@
         <v>15</v>
       </c>
       <c r="B162" s="5">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="C162" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -4169,10 +4171,10 @@
         <v>15</v>
       </c>
       <c r="B163" s="8">
-        <v>46099</v>
+        <v>46153</v>
       </c>
       <c r="C163" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -4180,10 +4182,10 @@
         <v>15</v>
       </c>
       <c r="B164" s="5">
-        <v>46154</v>
+        <v>46076</v>
       </c>
       <c r="C164" s="6">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -4191,10 +4193,10 @@
         <v>15</v>
       </c>
       <c r="B165" s="8">
-        <v>46092</v>
+        <v>46099</v>
       </c>
       <c r="C165" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -4202,10 +4204,10 @@
         <v>15</v>
       </c>
       <c r="B166" s="5">
-        <v>46031</v>
+        <v>46154</v>
       </c>
       <c r="C166" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -4213,10 +4215,10 @@
         <v>15</v>
       </c>
       <c r="B167" s="8">
-        <v>46120</v>
+        <v>46092</v>
       </c>
       <c r="C167" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -4224,10 +4226,10 @@
         <v>15</v>
       </c>
       <c r="B168" s="5">
-        <v>46077</v>
+        <v>46031</v>
       </c>
       <c r="C168" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -4235,10 +4237,10 @@
         <v>15</v>
       </c>
       <c r="B169" s="8">
-        <v>46114</v>
+        <v>46120</v>
       </c>
       <c r="C169" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -4246,10 +4248,10 @@
         <v>15</v>
       </c>
       <c r="B170" s="5">
-        <v>46037</v>
+        <v>46077</v>
       </c>
       <c r="C170" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -4257,10 +4259,10 @@
         <v>15</v>
       </c>
       <c r="B171" s="8">
-        <v>46020</v>
+        <v>46114</v>
       </c>
       <c r="C171" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -4268,7 +4270,7 @@
         <v>15</v>
       </c>
       <c r="B172" s="5">
-        <v>46106</v>
+        <v>46037</v>
       </c>
       <c r="C172" s="6">
         <v>1</v>
@@ -4279,10 +4281,10 @@
         <v>15</v>
       </c>
       <c r="B173" s="8">
-        <v>46155</v>
+        <v>46020</v>
       </c>
       <c r="C173" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -4290,7 +4292,7 @@
         <v>15</v>
       </c>
       <c r="B174" s="5">
-        <v>46112</v>
+        <v>46106</v>
       </c>
       <c r="C174" s="6">
         <v>1</v>
@@ -4301,7 +4303,7 @@
         <v>15</v>
       </c>
       <c r="B175" s="8">
-        <v>46132</v>
+        <v>46155</v>
       </c>
       <c r="C175" s="9">
         <v>1</v>
@@ -4312,7 +4314,7 @@
         <v>15</v>
       </c>
       <c r="B176" s="5">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="C176" s="6">
         <v>1</v>
@@ -4323,7 +4325,7 @@
         <v>15</v>
       </c>
       <c r="B177" s="8">
-        <v>46148</v>
+        <v>46132</v>
       </c>
       <c r="C177" s="9">
         <v>1</v>
@@ -4334,7 +4336,7 @@
         <v>15</v>
       </c>
       <c r="B178" s="5">
-        <v>46118</v>
+        <v>46108</v>
       </c>
       <c r="C178" s="6">
         <v>1</v>
@@ -4345,7 +4347,7 @@
         <v>15</v>
       </c>
       <c r="B179" s="8">
-        <v>46035</v>
+        <v>46148</v>
       </c>
       <c r="C179" s="9">
         <v>1</v>
@@ -4356,7 +4358,7 @@
         <v>15</v>
       </c>
       <c r="B180" s="5">
-        <v>46093</v>
+        <v>46118</v>
       </c>
       <c r="C180" s="6">
         <v>1</v>
@@ -4367,7 +4369,7 @@
         <v>15</v>
       </c>
       <c r="B181" s="8">
-        <v>46022</v>
+        <v>46035</v>
       </c>
       <c r="C181" s="9">
         <v>1</v>
@@ -4378,7 +4380,7 @@
         <v>15</v>
       </c>
       <c r="B182" s="5">
-        <v>46087</v>
+        <v>46093</v>
       </c>
       <c r="C182" s="6">
         <v>1</v>
@@ -4389,10 +4391,10 @@
         <v>15</v>
       </c>
       <c r="B183" s="8">
-        <v>46030</v>
+        <v>46022</v>
       </c>
       <c r="C183" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -4400,7 +4402,7 @@
         <v>15</v>
       </c>
       <c r="B184" s="5">
-        <v>46101</v>
+        <v>46087</v>
       </c>
       <c r="C184" s="6">
         <v>1</v>
@@ -4411,32 +4413,32 @@
         <v>15</v>
       </c>
       <c r="B185" s="8">
-        <v>46142</v>
+        <v>46030</v>
       </c>
       <c r="C185" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B186" s="5">
-        <v>46001</v>
+        <v>46101</v>
       </c>
       <c r="C186" s="6">
-        <v>153</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B187" s="8">
-        <v>46008</v>
+        <v>46142</v>
       </c>
       <c r="C187" s="9">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -4444,10 +4446,10 @@
         <v>21</v>
       </c>
       <c r="B188" s="5">
-        <v>46003</v>
+        <v>46001</v>
       </c>
       <c r="C188" s="6">
-        <v>70</v>
+        <v>153</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -4455,10 +4457,10 @@
         <v>21</v>
       </c>
       <c r="B189" s="8">
-        <v>46002</v>
+        <v>46008</v>
       </c>
       <c r="C189" s="9">
-        <v>111</v>
+        <v>38</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -4466,10 +4468,10 @@
         <v>21</v>
       </c>
       <c r="B190" s="5">
-        <v>46006</v>
+        <v>46003</v>
       </c>
       <c r="C190" s="6">
-        <v>147</v>
+        <v>70</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -4477,10 +4479,10 @@
         <v>21</v>
       </c>
       <c r="B191" s="8">
-        <v>46007</v>
+        <v>46002</v>
       </c>
       <c r="C191" s="9">
-        <v>45</v>
+        <v>111</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -4488,10 +4490,10 @@
         <v>21</v>
       </c>
       <c r="B192" s="5">
-        <v>46000</v>
+        <v>46006</v>
       </c>
       <c r="C192" s="6">
-        <v>129</v>
+        <v>147</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -4499,10 +4501,10 @@
         <v>21</v>
       </c>
       <c r="B193" s="8">
-        <v>46084</v>
+        <v>46007</v>
       </c>
       <c r="C193" s="9">
-        <v>10</v>
+        <v>45</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -4510,10 +4512,10 @@
         <v>21</v>
       </c>
       <c r="B194" s="5">
-        <v>46014</v>
+        <v>46000</v>
       </c>
       <c r="C194" s="6">
-        <v>22</v>
+        <v>127</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -4521,10 +4523,10 @@
         <v>21</v>
       </c>
       <c r="B195" s="8">
-        <v>46013</v>
+        <v>46084</v>
       </c>
       <c r="C195" s="9">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -4532,10 +4534,10 @@
         <v>21</v>
       </c>
       <c r="B196" s="5">
-        <v>46010</v>
+        <v>46014</v>
       </c>
       <c r="C196" s="6">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -4543,10 +4545,10 @@
         <v>21</v>
       </c>
       <c r="B197" s="8">
-        <v>46021</v>
+        <v>46013</v>
       </c>
       <c r="C197" s="9">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -4554,10 +4556,10 @@
         <v>21</v>
       </c>
       <c r="B198" s="5">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="C198" s="6">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -4565,10 +4567,10 @@
         <v>21</v>
       </c>
       <c r="B199" s="8">
-        <v>46083</v>
+        <v>46021</v>
       </c>
       <c r="C199" s="9">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -4576,10 +4578,10 @@
         <v>21</v>
       </c>
       <c r="B200" s="5">
-        <v>46157</v>
+        <v>46009</v>
       </c>
       <c r="C200" s="6">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -4587,10 +4589,10 @@
         <v>21</v>
       </c>
       <c r="B201" s="8">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="C201" s="9">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -4598,10 +4600,10 @@
         <v>21</v>
       </c>
       <c r="B202" s="5">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="C202" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -4609,10 +4611,10 @@
         <v>21</v>
       </c>
       <c r="B203" s="8">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="C203" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -4620,10 +4622,10 @@
         <v>21</v>
       </c>
       <c r="B204" s="5">
-        <v>46035</v>
+        <v>46167</v>
       </c>
       <c r="C204" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -4631,10 +4633,10 @@
         <v>21</v>
       </c>
       <c r="B205" s="8">
-        <v>46085</v>
+        <v>46077</v>
       </c>
       <c r="C205" s="9">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -4642,7 +4644,7 @@
         <v>21</v>
       </c>
       <c r="B206" s="5">
-        <v>46120</v>
+        <v>46035</v>
       </c>
       <c r="C206" s="6">
         <v>2</v>
@@ -4653,10 +4655,10 @@
         <v>21</v>
       </c>
       <c r="B207" s="8">
-        <v>46114</v>
+        <v>46085</v>
       </c>
       <c r="C207" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4664,10 +4666,10 @@
         <v>21</v>
       </c>
       <c r="B208" s="5">
-        <v>46094</v>
+        <v>46120</v>
       </c>
       <c r="C208" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4675,10 +4677,10 @@
         <v>21</v>
       </c>
       <c r="B209" s="8">
-        <v>46080</v>
+        <v>46114</v>
       </c>
       <c r="C209" s="9">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4686,10 +4688,10 @@
         <v>21</v>
       </c>
       <c r="B210" s="5">
-        <v>46127</v>
+        <v>46094</v>
       </c>
       <c r="C210" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -4697,10 +4699,10 @@
         <v>21</v>
       </c>
       <c r="B211" s="8">
-        <v>46091</v>
+        <v>46080</v>
       </c>
       <c r="C211" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -4708,10 +4710,10 @@
         <v>21</v>
       </c>
       <c r="B212" s="5">
-        <v>46090</v>
+        <v>46127</v>
       </c>
       <c r="C212" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4719,10 +4721,10 @@
         <v>21</v>
       </c>
       <c r="B213" s="8">
-        <v>46020</v>
+        <v>46091</v>
       </c>
       <c r="C213" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4730,10 +4732,10 @@
         <v>21</v>
       </c>
       <c r="B214" s="5">
-        <v>46015</v>
+        <v>46090</v>
       </c>
       <c r="C214" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4741,10 +4743,10 @@
         <v>21</v>
       </c>
       <c r="B215" s="8">
-        <v>46078</v>
+        <v>46020</v>
       </c>
       <c r="C215" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4752,10 +4754,10 @@
         <v>21</v>
       </c>
       <c r="B216" s="5">
-        <v>46148</v>
+        <v>46015</v>
       </c>
       <c r="C216" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4763,10 +4765,10 @@
         <v>21</v>
       </c>
       <c r="B217" s="8">
-        <v>46105</v>
+        <v>46078</v>
       </c>
       <c r="C217" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -4774,10 +4776,10 @@
         <v>21</v>
       </c>
       <c r="B218" s="5">
-        <v>46087</v>
+        <v>46148</v>
       </c>
       <c r="C218" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -4785,10 +4787,10 @@
         <v>21</v>
       </c>
       <c r="B219" s="8">
-        <v>46107</v>
+        <v>46105</v>
       </c>
       <c r="C219" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4796,10 +4798,10 @@
         <v>21</v>
       </c>
       <c r="B220" s="5">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="C220" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -4807,10 +4809,10 @@
         <v>21</v>
       </c>
       <c r="B221" s="8">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C221" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -4818,10 +4820,10 @@
         <v>21</v>
       </c>
       <c r="B222" s="5">
-        <v>46150</v>
+        <v>46086</v>
       </c>
       <c r="C222" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -4829,10 +4831,10 @@
         <v>21</v>
       </c>
       <c r="B223" s="8">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="C223" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -4840,10 +4842,10 @@
         <v>21</v>
       </c>
       <c r="B224" s="5">
-        <v>46118</v>
+        <v>46150</v>
       </c>
       <c r="C224" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -4851,10 +4853,10 @@
         <v>21</v>
       </c>
       <c r="B225" s="8">
-        <v>46076</v>
+        <v>46104</v>
       </c>
       <c r="C225" s="9">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -4862,7 +4864,7 @@
         <v>21</v>
       </c>
       <c r="B226" s="5">
-        <v>46154</v>
+        <v>46118</v>
       </c>
       <c r="C226" s="6">
         <v>1</v>
@@ -4873,10 +4875,10 @@
         <v>21</v>
       </c>
       <c r="B227" s="8">
-        <v>46093</v>
+        <v>46076</v>
       </c>
       <c r="C227" s="9">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -4884,7 +4886,7 @@
         <v>21</v>
       </c>
       <c r="B228" s="5">
-        <v>46122</v>
+        <v>46154</v>
       </c>
       <c r="C228" s="6">
         <v>1</v>
@@ -4895,7 +4897,7 @@
         <v>21</v>
       </c>
       <c r="B229" s="8">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="C229" s="9">
         <v>3</v>
@@ -4906,10 +4908,10 @@
         <v>21</v>
       </c>
       <c r="B230" s="5">
-        <v>46156</v>
+        <v>46122</v>
       </c>
       <c r="C230" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -4917,10 +4919,10 @@
         <v>21</v>
       </c>
       <c r="B231" s="8">
-        <v>46133</v>
+        <v>46092</v>
       </c>
       <c r="C231" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -4928,10 +4930,10 @@
         <v>21</v>
       </c>
       <c r="B232" s="5">
-        <v>46126</v>
+        <v>46156</v>
       </c>
       <c r="C232" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -4939,10 +4941,10 @@
         <v>21</v>
       </c>
       <c r="B233" s="8">
-        <v>46022</v>
+        <v>46133</v>
       </c>
       <c r="C233" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -4950,10 +4952,10 @@
         <v>21</v>
       </c>
       <c r="B234" s="5">
-        <v>46100</v>
+        <v>46126</v>
       </c>
       <c r="C234" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -4961,10 +4963,10 @@
         <v>21</v>
       </c>
       <c r="B235" s="8">
-        <v>46101</v>
+        <v>46022</v>
       </c>
       <c r="C235" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -4972,10 +4974,10 @@
         <v>21</v>
       </c>
       <c r="B236" s="5">
-        <v>46097</v>
+        <v>46100</v>
       </c>
       <c r="C236" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -4983,7 +4985,7 @@
         <v>21</v>
       </c>
       <c r="B237" s="8">
-        <v>46108</v>
+        <v>46101</v>
       </c>
       <c r="C237" s="9">
         <v>1</v>
@@ -4994,10 +4996,10 @@
         <v>21</v>
       </c>
       <c r="B238" s="5">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="C238" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -5005,7 +5007,7 @@
         <v>21</v>
       </c>
       <c r="B239" s="8">
-        <v>46113</v>
+        <v>46108</v>
       </c>
       <c r="C239" s="9">
         <v>1</v>
@@ -5016,10 +5018,10 @@
         <v>21</v>
       </c>
       <c r="B240" s="5">
-        <v>46142</v>
+        <v>46098</v>
       </c>
       <c r="C240" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -5027,7 +5029,7 @@
         <v>21</v>
       </c>
       <c r="B241" s="8">
-        <v>46153</v>
+        <v>46113</v>
       </c>
       <c r="C241" s="9">
         <v>1</v>
@@ -5038,7 +5040,7 @@
         <v>21</v>
       </c>
       <c r="B242" s="5">
-        <v>46031</v>
+        <v>46142</v>
       </c>
       <c r="C242" s="6">
         <v>1</v>
@@ -5049,9 +5051,31 @@
         <v>21</v>
       </c>
       <c r="B243" s="8">
+        <v>46153</v>
+      </c>
+      <c r="C243" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B244" s="5">
+        <v>46031</v>
+      </c>
+      <c r="C244" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B245" s="8">
         <v>46155</v>
       </c>
-      <c r="C243" s="9">
+      <c r="C245" s="9">
         <v>1</v>
       </c>
     </row>
@@ -5203,7 +5227,7 @@
         <v>4</v>
       </c>
       <c r="E8">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -5418,7 +5442,7 @@
         <v>7</v>
       </c>
       <c r="C21">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D21">
         <v>6</v>
@@ -5594,7 +5618,7 @@
         <v>4</v>
       </c>
       <c r="E31">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -5608,10 +5632,10 @@
         <v>84</v>
       </c>
       <c r="D32">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E32">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -5628,7 +5652,7 @@
         <v>8</v>
       </c>
       <c r="E33">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -5690,7 +5714,7 @@
         <v>18</v>
       </c>
       <c r="C37">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D37">
         <v>12</v>
@@ -5707,7 +5731,7 @@
         <v>19</v>
       </c>
       <c r="C38">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D38">
         <v>10</v>
@@ -5724,7 +5748,7 @@
         <v>20</v>
       </c>
       <c r="C39">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -6845,7 +6869,7 @@
         <v>119</v>
       </c>
       <c r="C100">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -7832,10 +7856,10 @@
         <v>16</v>
       </c>
       <c r="B190" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C190">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -7843,7 +7867,7 @@
         <v>16</v>
       </c>
       <c r="B191" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C191">
         <v>12</v>
@@ -7898,7 +7922,7 @@
         <v>16</v>
       </c>
       <c r="B196" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C196">
         <v>10</v>
@@ -7909,10 +7933,10 @@
         <v>16</v>
       </c>
       <c r="B197" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C197">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -7931,10 +7955,10 @@
         <v>16</v>
       </c>
       <c r="B199" t="s">
-        <v>85</v>
+        <v>196</v>
       </c>
       <c r="C199">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -7942,7 +7966,7 @@
         <v>16</v>
       </c>
       <c r="B200" t="s">
-        <v>196</v>
+        <v>85</v>
       </c>
       <c r="C200">
         <v>7</v>
@@ -8096,7 +8120,7 @@
         <v>16</v>
       </c>
       <c r="B214" t="s">
-        <v>76</v>
+        <v>201</v>
       </c>
       <c r="C214">
         <v>3</v>
@@ -8107,7 +8131,7 @@
         <v>16</v>
       </c>
       <c r="B215" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="C215">
         <v>3</v>
@@ -8118,7 +8142,7 @@
         <v>16</v>
       </c>
       <c r="B216" t="s">
-        <v>114</v>
+        <v>59</v>
       </c>
       <c r="C216">
         <v>3</v>
@@ -8140,7 +8164,7 @@
         <v>16</v>
       </c>
       <c r="B218" t="s">
-        <v>201</v>
+        <v>44</v>
       </c>
       <c r="C218">
         <v>3</v>
@@ -8162,7 +8186,7 @@
         <v>16</v>
       </c>
       <c r="B220" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C220">
         <v>3</v>
@@ -8173,7 +8197,7 @@
         <v>16</v>
       </c>
       <c r="B221" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="C221">
         <v>3</v>
@@ -8184,10 +8208,10 @@
         <v>16</v>
       </c>
       <c r="B222" t="s">
-        <v>205</v>
+        <v>80</v>
       </c>
       <c r="C222">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -8195,7 +8219,7 @@
         <v>16</v>
       </c>
       <c r="B223" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C223">
         <v>2</v>
@@ -8206,7 +8230,7 @@
         <v>16</v>
       </c>
       <c r="B224" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="C224">
         <v>2</v>
@@ -8217,7 +8241,7 @@
         <v>16</v>
       </c>
       <c r="B225" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C225">
         <v>2</v>
@@ -8228,7 +8252,7 @@
         <v>16</v>
       </c>
       <c r="B226" t="s">
-        <v>64</v>
+        <v>203</v>
       </c>
       <c r="C226">
         <v>2</v>
@@ -8239,7 +8263,7 @@
         <v>16</v>
       </c>
       <c r="B227" t="s">
-        <v>207</v>
+        <v>64</v>
       </c>
       <c r="C227">
         <v>2</v>
@@ -8250,7 +8274,7 @@
         <v>16</v>
       </c>
       <c r="B228" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C228">
         <v>2</v>
@@ -8261,7 +8285,7 @@
         <v>16</v>
       </c>
       <c r="B229" t="s">
-        <v>80</v>
+        <v>189</v>
       </c>
       <c r="C229">
         <v>2</v>
@@ -9674,7 +9698,7 @@
         <v>287</v>
       </c>
       <c r="C3">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -9795,7 +9819,7 @@
         <v>290</v>
       </c>
       <c r="C14">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -9916,7 +9940,7 @@
         <v>287</v>
       </c>
       <c r="C25">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -10015,7 +10039,7 @@
         <v>290</v>
       </c>
       <c r="C34">
-        <v>711</v>
+        <v>708</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -10144,420 +10168,420 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>298</v>
       </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C11" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C20" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>298</v>
+      </c>
+      <c r="C21" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="C22" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="C23" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="C24" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="C25" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="C8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
+      <c r="C26" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="C27" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C28" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="C29" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" s="11" t="s">
         <v>298</v>
       </c>
-      <c r="C12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="C31" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" s="6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C34" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="9">
         <v>6</v>
       </c>
-      <c r="C13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" t="s">
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38" s="6">
         <v>7</v>
       </c>
-      <c r="C21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>298</v>
-      </c>
-      <c r="C22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>5</v>
-      </c>
-      <c r="C25">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>12</v>
-      </c>
-      <c r="C27">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>16</v>
-      </c>
-      <c r="B32" t="s">
-        <v>17</v>
-      </c>
-      <c r="C32">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>16</v>
-      </c>
-      <c r="B33" t="s">
-        <v>18</v>
-      </c>
-      <c r="C33">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>16</v>
-      </c>
-      <c r="B34" t="s">
-        <v>19</v>
-      </c>
-      <c r="C34">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>16</v>
-      </c>
-      <c r="B35" t="s">
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C35">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>21</v>
-      </c>
-      <c r="B36" t="s">
-        <v>17</v>
-      </c>
-      <c r="C36">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>21</v>
-      </c>
-      <c r="B37" t="s">
-        <v>18</v>
-      </c>
-      <c r="C37">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>21</v>
-      </c>
-      <c r="B38" t="s">
-        <v>19</v>
-      </c>
-      <c r="C38">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>21</v>
-      </c>
-      <c r="B39" t="s">
-        <v>20</v>
-      </c>
-      <c r="C39">
+      <c r="C39" s="9">
         <v>7</v>
       </c>
     </row>

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="140" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17178297-3EDB-4DB5-BD1F-E10B1FA6D658}"/>
+  <xr:revisionPtr revIDLastSave="150" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95AF4B72-74CA-4F31-9868-91B2ADF691C9}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" tabRatio="731" firstSheet="2" activeTab="7" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" tabRatio="731" firstSheet="1" activeTab="7" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="mat_2026" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1317" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1320" uniqueCount="300">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -1685,10 +1685,10 @@
         <v>68</v>
       </c>
       <c r="D17">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E17">
-        <v>1.0289999999999999</v>
+        <v>1.044</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -1940,10 +1940,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E32">
-        <v>1.0629999999999999</v>
+        <v>1.0660000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1974,10 +1974,10 @@
         <v>323</v>
       </c>
       <c r="D34">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E34">
-        <v>0.95699999999999996</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -2333,7 +2333,7 @@
         <v>34</v>
       </c>
       <c r="C8">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2344,7 +2344,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2376,7 +2376,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD19485A-0629-47F9-A5AD-80ABA7A6E076}">
-  <dimension ref="A1:C245"/>
+  <dimension ref="A1:C246"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -2708,7 +2708,7 @@
         <v>16</v>
       </c>
       <c r="B30" s="5">
-        <v>46098</v>
+        <v>46176</v>
       </c>
       <c r="C30" s="6">
         <v>3</v>
@@ -2719,10 +2719,10 @@
         <v>16</v>
       </c>
       <c r="B31" s="8">
-        <v>46084</v>
+        <v>46098</v>
       </c>
       <c r="C31" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -2730,10 +2730,10 @@
         <v>16</v>
       </c>
       <c r="B32" s="5">
-        <v>46160</v>
+        <v>46084</v>
       </c>
       <c r="C32" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -2741,10 +2741,10 @@
         <v>16</v>
       </c>
       <c r="B33" s="8">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="C33" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -2752,10 +2752,10 @@
         <v>16</v>
       </c>
       <c r="B34" s="5">
-        <v>46099</v>
+        <v>46167</v>
       </c>
       <c r="C34" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -2763,10 +2763,10 @@
         <v>16</v>
       </c>
       <c r="B35" s="8">
-        <v>46128</v>
+        <v>46099</v>
       </c>
       <c r="C35" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -2774,10 +2774,10 @@
         <v>16</v>
       </c>
       <c r="B36" s="5">
-        <v>46141</v>
+        <v>46128</v>
       </c>
       <c r="C36" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -2785,10 +2785,10 @@
         <v>16</v>
       </c>
       <c r="B37" s="8">
-        <v>46132</v>
+        <v>46141</v>
       </c>
       <c r="C37" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -2796,10 +2796,10 @@
         <v>16</v>
       </c>
       <c r="B38" s="5">
-        <v>46127</v>
+        <v>46132</v>
       </c>
       <c r="C38" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -2807,7 +2807,7 @@
         <v>16</v>
       </c>
       <c r="B39" s="8">
-        <v>46091</v>
+        <v>46127</v>
       </c>
       <c r="C39" s="9">
         <v>2</v>
@@ -2818,10 +2818,10 @@
         <v>16</v>
       </c>
       <c r="B40" s="5">
-        <v>46104</v>
+        <v>46091</v>
       </c>
       <c r="C40" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -2829,7 +2829,7 @@
         <v>16</v>
       </c>
       <c r="B41" s="8">
-        <v>46140</v>
+        <v>46104</v>
       </c>
       <c r="C41" s="9">
         <v>1</v>
@@ -2840,7 +2840,7 @@
         <v>16</v>
       </c>
       <c r="B42" s="5">
-        <v>46106</v>
+        <v>46140</v>
       </c>
       <c r="C42" s="6">
         <v>1</v>
@@ -2851,7 +2851,7 @@
         <v>16</v>
       </c>
       <c r="B43" s="8">
-        <v>46113</v>
+        <v>46106</v>
       </c>
       <c r="C43" s="9">
         <v>1</v>
@@ -2862,10 +2862,10 @@
         <v>16</v>
       </c>
       <c r="B44" s="5">
-        <v>46090</v>
+        <v>46113</v>
       </c>
       <c r="C44" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -2873,10 +2873,10 @@
         <v>16</v>
       </c>
       <c r="B45" s="8">
-        <v>46139</v>
+        <v>46090</v>
       </c>
       <c r="C45" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -2884,7 +2884,7 @@
         <v>16</v>
       </c>
       <c r="B46" s="5">
-        <v>46148</v>
+        <v>46139</v>
       </c>
       <c r="C46" s="6">
         <v>1</v>
@@ -2895,7 +2895,7 @@
         <v>16</v>
       </c>
       <c r="B47" s="8">
-        <v>46175</v>
+        <v>46148</v>
       </c>
       <c r="C47" s="9">
         <v>1</v>
@@ -2906,7 +2906,7 @@
         <v>16</v>
       </c>
       <c r="B48" s="5">
-        <v>46125</v>
+        <v>46175</v>
       </c>
       <c r="C48" s="6">
         <v>1</v>
@@ -2917,7 +2917,7 @@
         <v>16</v>
       </c>
       <c r="B49" s="8">
-        <v>46176</v>
+        <v>46125</v>
       </c>
       <c r="C49" s="9">
         <v>1</v>
@@ -3390,7 +3390,7 @@
         <v>14</v>
       </c>
       <c r="B92" s="5">
-        <v>46092</v>
+        <v>46174</v>
       </c>
       <c r="C92" s="6">
         <v>1</v>
@@ -3401,10 +3401,10 @@
         <v>14</v>
       </c>
       <c r="B93" s="8">
-        <v>46021</v>
+        <v>46092</v>
       </c>
       <c r="C93" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -3412,10 +3412,10 @@
         <v>14</v>
       </c>
       <c r="B94" s="5">
-        <v>46086</v>
+        <v>46021</v>
       </c>
       <c r="C94" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -3423,10 +3423,10 @@
         <v>14</v>
       </c>
       <c r="B95" s="8">
-        <v>46147</v>
+        <v>46086</v>
       </c>
       <c r="C95" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -3434,7 +3434,7 @@
         <v>14</v>
       </c>
       <c r="B96" s="5">
-        <v>46134</v>
+        <v>46147</v>
       </c>
       <c r="C96" s="6">
         <v>1</v>
@@ -3442,13 +3442,13 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B97" s="8">
-        <v>46003</v>
+        <v>46134</v>
       </c>
       <c r="C97" s="9">
-        <v>95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -3456,10 +3456,10 @@
         <v>3</v>
       </c>
       <c r="B98" s="5">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="C98" s="6">
-        <v>115</v>
+        <v>95</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -3467,10 +3467,10 @@
         <v>3</v>
       </c>
       <c r="B99" s="8">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C99" s="9">
-        <v>15</v>
+        <v>115</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -3478,10 +3478,10 @@
         <v>3</v>
       </c>
       <c r="B100" s="5">
-        <v>46000</v>
+        <v>46008</v>
       </c>
       <c r="C100" s="6">
-        <v>98</v>
+        <v>15</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -3489,10 +3489,10 @@
         <v>3</v>
       </c>
       <c r="B101" s="8">
-        <v>46007</v>
+        <v>46000</v>
       </c>
       <c r="C101" s="9">
-        <v>40</v>
+        <v>98</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -3500,10 +3500,10 @@
         <v>3</v>
       </c>
       <c r="B102" s="5">
-        <v>46001</v>
+        <v>46007</v>
       </c>
       <c r="C102" s="6">
-        <v>91</v>
+        <v>40</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -3511,10 +3511,10 @@
         <v>3</v>
       </c>
       <c r="B103" s="8">
-        <v>46010</v>
+        <v>46001</v>
       </c>
       <c r="C103" s="9">
-        <v>9</v>
+        <v>91</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -3522,10 +3522,10 @@
         <v>3</v>
       </c>
       <c r="B104" s="5">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="C104" s="6">
-        <v>84</v>
+        <v>9</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -3533,10 +3533,10 @@
         <v>3</v>
       </c>
       <c r="B105" s="8">
-        <v>46009</v>
+        <v>46006</v>
       </c>
       <c r="C105" s="9">
-        <v>2</v>
+        <v>84</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -3544,10 +3544,10 @@
         <v>3</v>
       </c>
       <c r="B106" s="5">
-        <v>46015</v>
+        <v>46009</v>
       </c>
       <c r="C106" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -3555,10 +3555,10 @@
         <v>3</v>
       </c>
       <c r="B107" s="8">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="C107" s="9">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -3566,10 +3566,10 @@
         <v>3</v>
       </c>
       <c r="B108" s="5">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="C108" s="6">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -3577,10 +3577,10 @@
         <v>3</v>
       </c>
       <c r="B109" s="8">
-        <v>46021</v>
+        <v>46013</v>
       </c>
       <c r="C109" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -3588,10 +3588,10 @@
         <v>3</v>
       </c>
       <c r="B110" s="5">
-        <v>46077</v>
+        <v>46021</v>
       </c>
       <c r="C110" s="6">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -3599,10 +3599,10 @@
         <v>3</v>
       </c>
       <c r="B111" s="8">
-        <v>46167</v>
+        <v>46077</v>
       </c>
       <c r="C111" s="9">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -3610,10 +3610,10 @@
         <v>3</v>
       </c>
       <c r="B112" s="5">
-        <v>46090</v>
+        <v>46167</v>
       </c>
       <c r="C112" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -3621,10 +3621,10 @@
         <v>3</v>
       </c>
       <c r="B113" s="8">
-        <v>46170</v>
+        <v>46090</v>
       </c>
       <c r="C113" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -3632,7 +3632,7 @@
         <v>3</v>
       </c>
       <c r="B114" s="5">
-        <v>46093</v>
+        <v>46170</v>
       </c>
       <c r="C114" s="6">
         <v>1</v>
@@ -3643,10 +3643,10 @@
         <v>3</v>
       </c>
       <c r="B115" s="8">
-        <v>46078</v>
+        <v>46093</v>
       </c>
       <c r="C115" s="9">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -3654,10 +3654,10 @@
         <v>3</v>
       </c>
       <c r="B116" s="5">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="C116" s="6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -3665,10 +3665,10 @@
         <v>3</v>
       </c>
       <c r="B117" s="8">
-        <v>46134</v>
+        <v>46084</v>
       </c>
       <c r="C117" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -3676,10 +3676,10 @@
         <v>3</v>
       </c>
       <c r="B118" s="5">
-        <v>46083</v>
+        <v>46134</v>
       </c>
       <c r="C118" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -3687,10 +3687,10 @@
         <v>3</v>
       </c>
       <c r="B119" s="8">
-        <v>46022</v>
+        <v>46083</v>
       </c>
       <c r="C119" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -3698,10 +3698,10 @@
         <v>3</v>
       </c>
       <c r="B120" s="5">
-        <v>46114</v>
+        <v>46022</v>
       </c>
       <c r="C120" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -3709,10 +3709,10 @@
         <v>3</v>
       </c>
       <c r="B121" s="8">
-        <v>46135</v>
+        <v>46114</v>
       </c>
       <c r="C121" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -3720,10 +3720,10 @@
         <v>3</v>
       </c>
       <c r="B122" s="5">
-        <v>46168</v>
+        <v>46135</v>
       </c>
       <c r="C122" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -3731,7 +3731,7 @@
         <v>3</v>
       </c>
       <c r="B123" s="8">
-        <v>46126</v>
+        <v>46168</v>
       </c>
       <c r="C123" s="9">
         <v>3</v>
@@ -3742,7 +3742,7 @@
         <v>3</v>
       </c>
       <c r="B124" s="5">
-        <v>46120</v>
+        <v>46126</v>
       </c>
       <c r="C124" s="6">
         <v>3</v>
@@ -3753,10 +3753,10 @@
         <v>3</v>
       </c>
       <c r="B125" s="8">
-        <v>46127</v>
+        <v>46120</v>
       </c>
       <c r="C125" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
@@ -3764,7 +3764,7 @@
         <v>3</v>
       </c>
       <c r="B126" s="5">
-        <v>46087</v>
+        <v>46127</v>
       </c>
       <c r="C126" s="6">
         <v>1</v>
@@ -3775,7 +3775,7 @@
         <v>3</v>
       </c>
       <c r="B127" s="8">
-        <v>46108</v>
+        <v>46087</v>
       </c>
       <c r="C127" s="9">
         <v>1</v>
@@ -3786,7 +3786,7 @@
         <v>3</v>
       </c>
       <c r="B128" s="5">
-        <v>46020</v>
+        <v>46108</v>
       </c>
       <c r="C128" s="6">
         <v>1</v>
@@ -3797,7 +3797,7 @@
         <v>3</v>
       </c>
       <c r="B129" s="8">
-        <v>46097</v>
+        <v>46020</v>
       </c>
       <c r="C129" s="9">
         <v>1</v>
@@ -3808,10 +3808,10 @@
         <v>3</v>
       </c>
       <c r="B130" s="5">
-        <v>46161</v>
+        <v>46097</v>
       </c>
       <c r="C130" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -3819,10 +3819,10 @@
         <v>3</v>
       </c>
       <c r="B131" s="8">
-        <v>46129</v>
+        <v>46161</v>
       </c>
       <c r="C131" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -3830,7 +3830,7 @@
         <v>3</v>
       </c>
       <c r="B132" s="5">
-        <v>46080</v>
+        <v>46129</v>
       </c>
       <c r="C132" s="6">
         <v>1</v>
@@ -3841,7 +3841,7 @@
         <v>3</v>
       </c>
       <c r="B133" s="8">
-        <v>46101</v>
+        <v>46080</v>
       </c>
       <c r="C133" s="9">
         <v>1</v>
@@ -3852,7 +3852,7 @@
         <v>3</v>
       </c>
       <c r="B134" s="5">
-        <v>46155</v>
+        <v>46101</v>
       </c>
       <c r="C134" s="6">
         <v>1</v>
@@ -3863,7 +3863,7 @@
         <v>3</v>
       </c>
       <c r="B135" s="8">
-        <v>46150</v>
+        <v>46155</v>
       </c>
       <c r="C135" s="9">
         <v>1</v>
@@ -3874,7 +3874,7 @@
         <v>3</v>
       </c>
       <c r="B136" s="5">
-        <v>46141</v>
+        <v>46150</v>
       </c>
       <c r="C136" s="6">
         <v>1</v>
@@ -3885,7 +3885,7 @@
         <v>3</v>
       </c>
       <c r="B137" s="8">
-        <v>46085</v>
+        <v>46141</v>
       </c>
       <c r="C137" s="9">
         <v>1</v>
@@ -3896,7 +3896,7 @@
         <v>3</v>
       </c>
       <c r="B138" s="5">
-        <v>46148</v>
+        <v>46085</v>
       </c>
       <c r="C138" s="6">
         <v>1</v>
@@ -3907,10 +3907,10 @@
         <v>3</v>
       </c>
       <c r="B139" s="8">
-        <v>46118</v>
+        <v>46148</v>
       </c>
       <c r="C139" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -3918,21 +3918,21 @@
         <v>3</v>
       </c>
       <c r="B140" s="5">
-        <v>46079</v>
+        <v>46118</v>
       </c>
       <c r="C140" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B141" s="8">
-        <v>46003</v>
+        <v>46079</v>
       </c>
       <c r="C141" s="9">
-        <v>92</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -3940,10 +3940,10 @@
         <v>15</v>
       </c>
       <c r="B142" s="5">
-        <v>46000</v>
+        <v>46003</v>
       </c>
       <c r="C142" s="6">
-        <v>132</v>
+        <v>92</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -3951,10 +3951,10 @@
         <v>15</v>
       </c>
       <c r="B143" s="8">
-        <v>46006</v>
+        <v>46000</v>
       </c>
       <c r="C143" s="9">
-        <v>173</v>
+        <v>132</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -3962,10 +3962,10 @@
         <v>15</v>
       </c>
       <c r="B144" s="5">
-        <v>46001</v>
+        <v>46006</v>
       </c>
       <c r="C144" s="6">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -3973,10 +3973,10 @@
         <v>15</v>
       </c>
       <c r="B145" s="8">
-        <v>46014</v>
+        <v>46001</v>
       </c>
       <c r="C145" s="9">
-        <v>16</v>
+        <v>174</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -3984,10 +3984,10 @@
         <v>15</v>
       </c>
       <c r="B146" s="5">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="C146" s="6">
-        <v>171</v>
+        <v>16</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -3995,10 +3995,10 @@
         <v>15</v>
       </c>
       <c r="B147" s="8">
-        <v>46009</v>
+        <v>46002</v>
       </c>
       <c r="C147" s="9">
-        <v>19</v>
+        <v>171</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -4006,7 +4006,7 @@
         <v>15</v>
       </c>
       <c r="B148" s="5">
-        <v>46010</v>
+        <v>46009</v>
       </c>
       <c r="C148" s="6">
         <v>19</v>
@@ -4017,10 +4017,10 @@
         <v>15</v>
       </c>
       <c r="B149" s="8">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="C149" s="9">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -4028,10 +4028,10 @@
         <v>15</v>
       </c>
       <c r="B150" s="5">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="C150" s="6">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -4039,10 +4039,10 @@
         <v>15</v>
       </c>
       <c r="B151" s="8">
-        <v>46013</v>
+        <v>46007</v>
       </c>
       <c r="C151" s="9">
-        <v>12</v>
+        <v>43</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -4050,10 +4050,10 @@
         <v>15</v>
       </c>
       <c r="B152" s="5">
-        <v>46080</v>
+        <v>46013</v>
       </c>
       <c r="C152" s="6">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -4061,10 +4061,10 @@
         <v>15</v>
       </c>
       <c r="B153" s="8">
-        <v>46090</v>
+        <v>46080</v>
       </c>
       <c r="C153" s="9">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -4072,10 +4072,10 @@
         <v>15</v>
       </c>
       <c r="B154" s="5">
-        <v>46079</v>
+        <v>46090</v>
       </c>
       <c r="C154" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -4083,10 +4083,10 @@
         <v>15</v>
       </c>
       <c r="B155" s="8">
-        <v>46015</v>
+        <v>46079</v>
       </c>
       <c r="C155" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -4094,10 +4094,10 @@
         <v>15</v>
       </c>
       <c r="B156" s="5">
-        <v>46085</v>
+        <v>46015</v>
       </c>
       <c r="C156" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -4105,10 +4105,10 @@
         <v>15</v>
       </c>
       <c r="B157" s="8">
-        <v>46098</v>
+        <v>46085</v>
       </c>
       <c r="C157" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -4116,10 +4116,10 @@
         <v>15</v>
       </c>
       <c r="B158" s="5">
-        <v>46021</v>
+        <v>46098</v>
       </c>
       <c r="C158" s="6">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -4127,10 +4127,10 @@
         <v>15</v>
       </c>
       <c r="B159" s="8">
-        <v>46078</v>
+        <v>46021</v>
       </c>
       <c r="C159" s="9">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -4138,10 +4138,10 @@
         <v>15</v>
       </c>
       <c r="B160" s="5">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="C160" s="6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -4149,10 +4149,10 @@
         <v>15</v>
       </c>
       <c r="B161" s="8">
-        <v>46128</v>
+        <v>46084</v>
       </c>
       <c r="C161" s="9">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -4160,10 +4160,10 @@
         <v>15</v>
       </c>
       <c r="B162" s="5">
-        <v>46083</v>
+        <v>46128</v>
       </c>
       <c r="C162" s="6">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -4171,10 +4171,10 @@
         <v>15</v>
       </c>
       <c r="B163" s="8">
-        <v>46153</v>
+        <v>46083</v>
       </c>
       <c r="C163" s="9">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -4182,10 +4182,10 @@
         <v>15</v>
       </c>
       <c r="B164" s="5">
-        <v>46076</v>
+        <v>46153</v>
       </c>
       <c r="C164" s="6">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -4193,10 +4193,10 @@
         <v>15</v>
       </c>
       <c r="B165" s="8">
-        <v>46099</v>
+        <v>46076</v>
       </c>
       <c r="C165" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -4204,10 +4204,10 @@
         <v>15</v>
       </c>
       <c r="B166" s="5">
-        <v>46154</v>
+        <v>46099</v>
       </c>
       <c r="C166" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -4215,7 +4215,7 @@
         <v>15</v>
       </c>
       <c r="B167" s="8">
-        <v>46092</v>
+        <v>46154</v>
       </c>
       <c r="C167" s="9">
         <v>1</v>
@@ -4226,10 +4226,10 @@
         <v>15</v>
       </c>
       <c r="B168" s="5">
-        <v>46031</v>
+        <v>46092</v>
       </c>
       <c r="C168" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -4237,7 +4237,7 @@
         <v>15</v>
       </c>
       <c r="B169" s="8">
-        <v>46120</v>
+        <v>46031</v>
       </c>
       <c r="C169" s="9">
         <v>2</v>
@@ -4248,10 +4248,10 @@
         <v>15</v>
       </c>
       <c r="B170" s="5">
-        <v>46077</v>
+        <v>46120</v>
       </c>
       <c r="C170" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -4259,10 +4259,10 @@
         <v>15</v>
       </c>
       <c r="B171" s="8">
-        <v>46114</v>
+        <v>46077</v>
       </c>
       <c r="C171" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -4270,7 +4270,7 @@
         <v>15</v>
       </c>
       <c r="B172" s="5">
-        <v>46037</v>
+        <v>46114</v>
       </c>
       <c r="C172" s="6">
         <v>1</v>
@@ -4281,10 +4281,10 @@
         <v>15</v>
       </c>
       <c r="B173" s="8">
-        <v>46020</v>
+        <v>46037</v>
       </c>
       <c r="C173" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -4292,10 +4292,10 @@
         <v>15</v>
       </c>
       <c r="B174" s="5">
-        <v>46106</v>
+        <v>46020</v>
       </c>
       <c r="C174" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -4303,7 +4303,7 @@
         <v>15</v>
       </c>
       <c r="B175" s="8">
-        <v>46155</v>
+        <v>46106</v>
       </c>
       <c r="C175" s="9">
         <v>1</v>
@@ -4314,7 +4314,7 @@
         <v>15</v>
       </c>
       <c r="B176" s="5">
-        <v>46112</v>
+        <v>46155</v>
       </c>
       <c r="C176" s="6">
         <v>1</v>
@@ -4325,7 +4325,7 @@
         <v>15</v>
       </c>
       <c r="B177" s="8">
-        <v>46132</v>
+        <v>46112</v>
       </c>
       <c r="C177" s="9">
         <v>1</v>
@@ -4336,7 +4336,7 @@
         <v>15</v>
       </c>
       <c r="B178" s="5">
-        <v>46108</v>
+        <v>46132</v>
       </c>
       <c r="C178" s="6">
         <v>1</v>
@@ -4347,7 +4347,7 @@
         <v>15</v>
       </c>
       <c r="B179" s="8">
-        <v>46148</v>
+        <v>46108</v>
       </c>
       <c r="C179" s="9">
         <v>1</v>
@@ -4358,7 +4358,7 @@
         <v>15</v>
       </c>
       <c r="B180" s="5">
-        <v>46118</v>
+        <v>46148</v>
       </c>
       <c r="C180" s="6">
         <v>1</v>
@@ -4369,7 +4369,7 @@
         <v>15</v>
       </c>
       <c r="B181" s="8">
-        <v>46035</v>
+        <v>46118</v>
       </c>
       <c r="C181" s="9">
         <v>1</v>
@@ -4380,7 +4380,7 @@
         <v>15</v>
       </c>
       <c r="B182" s="5">
-        <v>46093</v>
+        <v>46035</v>
       </c>
       <c r="C182" s="6">
         <v>1</v>
@@ -4391,7 +4391,7 @@
         <v>15</v>
       </c>
       <c r="B183" s="8">
-        <v>46022</v>
+        <v>46093</v>
       </c>
       <c r="C183" s="9">
         <v>1</v>
@@ -4402,7 +4402,7 @@
         <v>15</v>
       </c>
       <c r="B184" s="5">
-        <v>46087</v>
+        <v>46022</v>
       </c>
       <c r="C184" s="6">
         <v>1</v>
@@ -4413,10 +4413,10 @@
         <v>15</v>
       </c>
       <c r="B185" s="8">
-        <v>46030</v>
+        <v>46087</v>
       </c>
       <c r="C185" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -4424,10 +4424,10 @@
         <v>15</v>
       </c>
       <c r="B186" s="5">
-        <v>46101</v>
+        <v>46030</v>
       </c>
       <c r="C186" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -4435,7 +4435,7 @@
         <v>15</v>
       </c>
       <c r="B187" s="8">
-        <v>46142</v>
+        <v>46101</v>
       </c>
       <c r="C187" s="9">
         <v>1</v>
@@ -4443,13 +4443,13 @@
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B188" s="5">
-        <v>46001</v>
+        <v>46142</v>
       </c>
       <c r="C188" s="6">
-        <v>153</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -4457,10 +4457,10 @@
         <v>21</v>
       </c>
       <c r="B189" s="8">
-        <v>46008</v>
+        <v>46001</v>
       </c>
       <c r="C189" s="9">
-        <v>38</v>
+        <v>153</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -4468,10 +4468,10 @@
         <v>21</v>
       </c>
       <c r="B190" s="5">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="C190" s="6">
-        <v>70</v>
+        <v>38</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -4479,10 +4479,10 @@
         <v>21</v>
       </c>
       <c r="B191" s="8">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="C191" s="9">
-        <v>111</v>
+        <v>70</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -4490,10 +4490,10 @@
         <v>21</v>
       </c>
       <c r="B192" s="5">
-        <v>46006</v>
+        <v>46002</v>
       </c>
       <c r="C192" s="6">
-        <v>147</v>
+        <v>111</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -4501,10 +4501,10 @@
         <v>21</v>
       </c>
       <c r="B193" s="8">
-        <v>46007</v>
+        <v>46006</v>
       </c>
       <c r="C193" s="9">
-        <v>45</v>
+        <v>147</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -4512,10 +4512,10 @@
         <v>21</v>
       </c>
       <c r="B194" s="5">
-        <v>46000</v>
+        <v>46007</v>
       </c>
       <c r="C194" s="6">
-        <v>127</v>
+        <v>45</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -4523,10 +4523,10 @@
         <v>21</v>
       </c>
       <c r="B195" s="8">
-        <v>46084</v>
+        <v>46000</v>
       </c>
       <c r="C195" s="9">
-        <v>10</v>
+        <v>127</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -4534,10 +4534,10 @@
         <v>21</v>
       </c>
       <c r="B196" s="5">
-        <v>46014</v>
+        <v>46084</v>
       </c>
       <c r="C196" s="6">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -4545,10 +4545,10 @@
         <v>21</v>
       </c>
       <c r="B197" s="8">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="C197" s="9">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -4556,10 +4556,10 @@
         <v>21</v>
       </c>
       <c r="B198" s="5">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="C198" s="6">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -4567,10 +4567,10 @@
         <v>21</v>
       </c>
       <c r="B199" s="8">
-        <v>46021</v>
+        <v>46010</v>
       </c>
       <c r="C199" s="9">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -4578,10 +4578,10 @@
         <v>21</v>
       </c>
       <c r="B200" s="5">
-        <v>46009</v>
+        <v>46021</v>
       </c>
       <c r="C200" s="6">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -4589,10 +4589,10 @@
         <v>21</v>
       </c>
       <c r="B201" s="8">
-        <v>46083</v>
+        <v>46009</v>
       </c>
       <c r="C201" s="9">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -4600,10 +4600,10 @@
         <v>21</v>
       </c>
       <c r="B202" s="5">
-        <v>46157</v>
+        <v>46083</v>
       </c>
       <c r="C202" s="6">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -4611,10 +4611,10 @@
         <v>21</v>
       </c>
       <c r="B203" s="8">
-        <v>46079</v>
+        <v>46157</v>
       </c>
       <c r="C203" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -4622,10 +4622,10 @@
         <v>21</v>
       </c>
       <c r="B204" s="5">
-        <v>46167</v>
+        <v>46079</v>
       </c>
       <c r="C204" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -4633,10 +4633,10 @@
         <v>21</v>
       </c>
       <c r="B205" s="8">
-        <v>46077</v>
+        <v>46167</v>
       </c>
       <c r="C205" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -4644,10 +4644,10 @@
         <v>21</v>
       </c>
       <c r="B206" s="5">
-        <v>46035</v>
+        <v>46077</v>
       </c>
       <c r="C206" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -4655,10 +4655,10 @@
         <v>21</v>
       </c>
       <c r="B207" s="8">
-        <v>46085</v>
+        <v>46035</v>
       </c>
       <c r="C207" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4666,10 +4666,10 @@
         <v>21</v>
       </c>
       <c r="B208" s="5">
-        <v>46120</v>
+        <v>46085</v>
       </c>
       <c r="C208" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4677,10 +4677,10 @@
         <v>21</v>
       </c>
       <c r="B209" s="8">
-        <v>46114</v>
+        <v>46120</v>
       </c>
       <c r="C209" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4688,10 +4688,10 @@
         <v>21</v>
       </c>
       <c r="B210" s="5">
-        <v>46094</v>
+        <v>46114</v>
       </c>
       <c r="C210" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -4699,10 +4699,10 @@
         <v>21</v>
       </c>
       <c r="B211" s="8">
-        <v>46080</v>
+        <v>46094</v>
       </c>
       <c r="C211" s="9">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -4710,10 +4710,10 @@
         <v>21</v>
       </c>
       <c r="B212" s="5">
-        <v>46127</v>
+        <v>46080</v>
       </c>
       <c r="C212" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4721,7 +4721,7 @@
         <v>21</v>
       </c>
       <c r="B213" s="8">
-        <v>46091</v>
+        <v>46127</v>
       </c>
       <c r="C213" s="9">
         <v>2</v>
@@ -4732,10 +4732,10 @@
         <v>21</v>
       </c>
       <c r="B214" s="5">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="C214" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4743,10 +4743,10 @@
         <v>21</v>
       </c>
       <c r="B215" s="8">
-        <v>46020</v>
+        <v>46090</v>
       </c>
       <c r="C215" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4754,10 +4754,10 @@
         <v>21</v>
       </c>
       <c r="B216" s="5">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="C216" s="6">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4765,10 +4765,10 @@
         <v>21</v>
       </c>
       <c r="B217" s="8">
-        <v>46078</v>
+        <v>46015</v>
       </c>
       <c r="C217" s="9">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -4776,10 +4776,10 @@
         <v>21</v>
       </c>
       <c r="B218" s="5">
-        <v>46148</v>
+        <v>46078</v>
       </c>
       <c r="C218" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -4787,7 +4787,7 @@
         <v>21</v>
       </c>
       <c r="B219" s="8">
-        <v>46105</v>
+        <v>46148</v>
       </c>
       <c r="C219" s="9">
         <v>2</v>
@@ -4798,10 +4798,10 @@
         <v>21</v>
       </c>
       <c r="B220" s="5">
-        <v>46087</v>
+        <v>46105</v>
       </c>
       <c r="C220" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -4809,7 +4809,7 @@
         <v>21</v>
       </c>
       <c r="B221" s="8">
-        <v>46107</v>
+        <v>46087</v>
       </c>
       <c r="C221" s="9">
         <v>3</v>
@@ -4820,10 +4820,10 @@
         <v>21</v>
       </c>
       <c r="B222" s="5">
-        <v>46086</v>
+        <v>46107</v>
       </c>
       <c r="C222" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -4831,10 +4831,10 @@
         <v>21</v>
       </c>
       <c r="B223" s="8">
-        <v>46106</v>
+        <v>46086</v>
       </c>
       <c r="C223" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -4842,10 +4842,10 @@
         <v>21</v>
       </c>
       <c r="B224" s="5">
-        <v>46150</v>
+        <v>46106</v>
       </c>
       <c r="C224" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -4853,7 +4853,7 @@
         <v>21</v>
       </c>
       <c r="B225" s="8">
-        <v>46104</v>
+        <v>46150</v>
       </c>
       <c r="C225" s="9">
         <v>3</v>
@@ -4864,10 +4864,10 @@
         <v>21</v>
       </c>
       <c r="B226" s="5">
-        <v>46118</v>
+        <v>46104</v>
       </c>
       <c r="C226" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -4875,10 +4875,10 @@
         <v>21</v>
       </c>
       <c r="B227" s="8">
-        <v>46076</v>
+        <v>46118</v>
       </c>
       <c r="C227" s="9">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -4886,10 +4886,10 @@
         <v>21</v>
       </c>
       <c r="B228" s="5">
-        <v>46154</v>
+        <v>46076</v>
       </c>
       <c r="C228" s="6">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -4897,10 +4897,10 @@
         <v>21</v>
       </c>
       <c r="B229" s="8">
-        <v>46093</v>
+        <v>46154</v>
       </c>
       <c r="C229" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -4908,10 +4908,10 @@
         <v>21</v>
       </c>
       <c r="B230" s="5">
-        <v>46122</v>
+        <v>46093</v>
       </c>
       <c r="C230" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -4919,10 +4919,10 @@
         <v>21</v>
       </c>
       <c r="B231" s="8">
-        <v>46092</v>
+        <v>46122</v>
       </c>
       <c r="C231" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -4930,10 +4930,10 @@
         <v>21</v>
       </c>
       <c r="B232" s="5">
-        <v>46156</v>
+        <v>46092</v>
       </c>
       <c r="C232" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -4941,10 +4941,10 @@
         <v>21</v>
       </c>
       <c r="B233" s="8">
-        <v>46133</v>
+        <v>46156</v>
       </c>
       <c r="C233" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -4952,7 +4952,7 @@
         <v>21</v>
       </c>
       <c r="B234" s="5">
-        <v>46126</v>
+        <v>46133</v>
       </c>
       <c r="C234" s="6">
         <v>1</v>
@@ -4963,10 +4963,10 @@
         <v>21</v>
       </c>
       <c r="B235" s="8">
-        <v>46022</v>
+        <v>46126</v>
       </c>
       <c r="C235" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -4974,7 +4974,7 @@
         <v>21</v>
       </c>
       <c r="B236" s="5">
-        <v>46100</v>
+        <v>46022</v>
       </c>
       <c r="C236" s="6">
         <v>2</v>
@@ -4985,10 +4985,10 @@
         <v>21</v>
       </c>
       <c r="B237" s="8">
-        <v>46101</v>
+        <v>46100</v>
       </c>
       <c r="C237" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -4996,10 +4996,10 @@
         <v>21</v>
       </c>
       <c r="B238" s="5">
-        <v>46097</v>
+        <v>46101</v>
       </c>
       <c r="C238" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -5007,10 +5007,10 @@
         <v>21</v>
       </c>
       <c r="B239" s="8">
-        <v>46108</v>
+        <v>46097</v>
       </c>
       <c r="C239" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -5018,10 +5018,10 @@
         <v>21</v>
       </c>
       <c r="B240" s="5">
-        <v>46098</v>
+        <v>46108</v>
       </c>
       <c r="C240" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -5029,10 +5029,10 @@
         <v>21</v>
       </c>
       <c r="B241" s="8">
-        <v>46113</v>
+        <v>46098</v>
       </c>
       <c r="C241" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -5040,7 +5040,7 @@
         <v>21</v>
       </c>
       <c r="B242" s="5">
-        <v>46142</v>
+        <v>46113</v>
       </c>
       <c r="C242" s="6">
         <v>1</v>
@@ -5051,7 +5051,7 @@
         <v>21</v>
       </c>
       <c r="B243" s="8">
-        <v>46153</v>
+        <v>46142</v>
       </c>
       <c r="C243" s="9">
         <v>1</v>
@@ -5062,7 +5062,7 @@
         <v>21</v>
       </c>
       <c r="B244" s="5">
-        <v>46031</v>
+        <v>46153</v>
       </c>
       <c r="C244" s="6">
         <v>1</v>
@@ -5073,9 +5073,20 @@
         <v>21</v>
       </c>
       <c r="B245" s="8">
+        <v>46031</v>
+      </c>
+      <c r="C245" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B246" s="5">
         <v>46155</v>
       </c>
-      <c r="C245" s="9">
+      <c r="C246" s="6">
         <v>1</v>
       </c>
     </row>
@@ -5380,7 +5391,7 @@
         <v>3</v>
       </c>
       <c r="E17">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -5635,7 +5646,7 @@
         <v>248</v>
       </c>
       <c r="E32">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -5669,7 +5680,7 @@
         <v>8</v>
       </c>
       <c r="E34">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -5764,7 +5775,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0916EAC6-1E7F-4924-9D0E-33749FD3E143}">
-  <dimension ref="A1:C353"/>
+  <dimension ref="A1:C354"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
@@ -6209,7 +6220,7 @@
         <v>80</v>
       </c>
       <c r="C40">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -7878,7 +7889,7 @@
         <v>16</v>
       </c>
       <c r="B192" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="C192">
         <v>11</v>
@@ -7889,7 +7900,7 @@
         <v>16</v>
       </c>
       <c r="B193" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C193">
         <v>11</v>
@@ -7900,7 +7911,7 @@
         <v>16</v>
       </c>
       <c r="B194" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C194">
         <v>11</v>
@@ -8010,7 +8021,7 @@
         <v>16</v>
       </c>
       <c r="B204" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C204">
         <v>5</v>
@@ -8032,7 +8043,7 @@
         <v>16</v>
       </c>
       <c r="B206" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C206">
         <v>5</v>
@@ -8054,7 +8065,7 @@
         <v>16</v>
       </c>
       <c r="B208" t="s">
-        <v>60</v>
+        <v>197</v>
       </c>
       <c r="C208">
         <v>4</v>
@@ -8065,7 +8076,7 @@
         <v>16</v>
       </c>
       <c r="B209" t="s">
-        <v>199</v>
+        <v>60</v>
       </c>
       <c r="C209">
         <v>4</v>
@@ -8087,7 +8098,7 @@
         <v>16</v>
       </c>
       <c r="B211" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C211">
         <v>4</v>
@@ -8120,7 +8131,7 @@
         <v>16</v>
       </c>
       <c r="B214" t="s">
-        <v>201</v>
+        <v>59</v>
       </c>
       <c r="C214">
         <v>3</v>
@@ -8131,7 +8142,7 @@
         <v>16</v>
       </c>
       <c r="B215" t="s">
-        <v>114</v>
+        <v>201</v>
       </c>
       <c r="C215">
         <v>3</v>
@@ -8142,7 +8153,7 @@
         <v>16</v>
       </c>
       <c r="B216" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="C216">
         <v>3</v>
@@ -8164,7 +8175,7 @@
         <v>16</v>
       </c>
       <c r="B218" t="s">
-        <v>44</v>
+        <v>114</v>
       </c>
       <c r="C218">
         <v>3</v>
@@ -8175,7 +8186,7 @@
         <v>16</v>
       </c>
       <c r="B219" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="C219">
         <v>3</v>
@@ -8208,7 +8219,7 @@
         <v>16</v>
       </c>
       <c r="B222" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C222">
         <v>3</v>
@@ -8219,7 +8230,7 @@
         <v>16</v>
       </c>
       <c r="B223" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="C223">
         <v>2</v>
@@ -8230,7 +8241,7 @@
         <v>16</v>
       </c>
       <c r="B224" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C224">
         <v>2</v>
@@ -8241,7 +8252,7 @@
         <v>16</v>
       </c>
       <c r="B225" t="s">
-        <v>202</v>
+        <v>64</v>
       </c>
       <c r="C225">
         <v>2</v>
@@ -8252,7 +8263,7 @@
         <v>16</v>
       </c>
       <c r="B226" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C226">
         <v>2</v>
@@ -8263,7 +8274,7 @@
         <v>16</v>
       </c>
       <c r="B227" t="s">
-        <v>64</v>
+        <v>204</v>
       </c>
       <c r="C227">
         <v>2</v>
@@ -8274,7 +8285,7 @@
         <v>16</v>
       </c>
       <c r="B228" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C228">
         <v>2</v>
@@ -8285,7 +8296,7 @@
         <v>16</v>
       </c>
       <c r="B229" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="C229">
         <v>2</v>
@@ -8296,7 +8307,7 @@
         <v>16</v>
       </c>
       <c r="B230" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C230">
         <v>2</v>
@@ -8307,7 +8318,7 @@
         <v>16</v>
       </c>
       <c r="B231" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="C231">
         <v>1</v>
@@ -8318,7 +8329,7 @@
         <v>16</v>
       </c>
       <c r="B232" t="s">
-        <v>225</v>
+        <v>119</v>
       </c>
       <c r="C232">
         <v>1</v>
@@ -8329,7 +8340,7 @@
         <v>16</v>
       </c>
       <c r="B233" t="s">
-        <v>115</v>
+        <v>236</v>
       </c>
       <c r="C233">
         <v>1</v>
@@ -8351,7 +8362,7 @@
         <v>16</v>
       </c>
       <c r="B235" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="C235">
         <v>1</v>
@@ -8362,7 +8373,7 @@
         <v>16</v>
       </c>
       <c r="B236" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C236">
         <v>1</v>
@@ -8373,7 +8384,7 @@
         <v>16</v>
       </c>
       <c r="B237" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -8384,7 +8395,7 @@
         <v>16</v>
       </c>
       <c r="B238" t="s">
-        <v>70</v>
+        <v>215</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -8395,7 +8406,7 @@
         <v>16</v>
       </c>
       <c r="B239" t="s">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -8406,7 +8417,7 @@
         <v>16</v>
       </c>
       <c r="B240" t="s">
-        <v>121</v>
+        <v>216</v>
       </c>
       <c r="C240">
         <v>1</v>
@@ -8417,7 +8428,7 @@
         <v>16</v>
       </c>
       <c r="B241" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -8428,7 +8439,7 @@
         <v>16</v>
       </c>
       <c r="B242" t="s">
-        <v>58</v>
+        <v>242</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -8439,7 +8450,7 @@
         <v>16</v>
       </c>
       <c r="B243" t="s">
-        <v>231</v>
+        <v>218</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -8450,7 +8461,7 @@
         <v>16</v>
       </c>
       <c r="B244" t="s">
-        <v>217</v>
+        <v>58</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -8461,7 +8472,7 @@
         <v>16</v>
       </c>
       <c r="B245" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -8472,7 +8483,7 @@
         <v>16</v>
       </c>
       <c r="B246" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
       <c r="C246">
         <v>1</v>
@@ -8483,7 +8494,7 @@
         <v>16</v>
       </c>
       <c r="B247" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="C247">
         <v>1</v>
@@ -8494,7 +8505,7 @@
         <v>16</v>
       </c>
       <c r="B248" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C248">
         <v>1</v>
@@ -8505,7 +8516,7 @@
         <v>16</v>
       </c>
       <c r="B249" t="s">
-        <v>241</v>
+        <v>69</v>
       </c>
       <c r="C249">
         <v>1</v>
@@ -8516,7 +8527,7 @@
         <v>16</v>
       </c>
       <c r="B250" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -8527,7 +8538,7 @@
         <v>16</v>
       </c>
       <c r="B251" t="s">
-        <v>240</v>
+        <v>126</v>
       </c>
       <c r="C251">
         <v>1</v>
@@ -8538,7 +8549,7 @@
         <v>16</v>
       </c>
       <c r="B252" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -8549,7 +8560,7 @@
         <v>16</v>
       </c>
       <c r="B253" t="s">
-        <v>249</v>
+        <v>225</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -8560,7 +8571,7 @@
         <v>16</v>
       </c>
       <c r="B254" t="s">
-        <v>242</v>
+        <v>209</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -8571,7 +8582,7 @@
         <v>16</v>
       </c>
       <c r="B255" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -8582,7 +8593,7 @@
         <v>16</v>
       </c>
       <c r="B256" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -8593,7 +8604,7 @@
         <v>16</v>
       </c>
       <c r="B257" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -8604,7 +8615,7 @@
         <v>16</v>
       </c>
       <c r="B258" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="C258">
         <v>1</v>
@@ -8615,7 +8626,7 @@
         <v>16</v>
       </c>
       <c r="B259" t="s">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="C259">
         <v>1</v>
@@ -8626,7 +8637,7 @@
         <v>16</v>
       </c>
       <c r="B260" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="C260">
         <v>1</v>
@@ -8637,7 +8648,7 @@
         <v>16</v>
       </c>
       <c r="B261" t="s">
-        <v>126</v>
+        <v>226</v>
       </c>
       <c r="C261">
         <v>1</v>
@@ -8648,7 +8659,7 @@
         <v>16</v>
       </c>
       <c r="B262" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C262">
         <v>1</v>
@@ -8659,7 +8670,7 @@
         <v>16</v>
       </c>
       <c r="B263" t="s">
-        <v>219</v>
+        <v>243</v>
       </c>
       <c r="C263">
         <v>1</v>
@@ -8670,7 +8681,7 @@
         <v>16</v>
       </c>
       <c r="B264" t="s">
-        <v>69</v>
+        <v>115</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -8681,7 +8692,7 @@
         <v>16</v>
       </c>
       <c r="B265" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="C265">
         <v>1</v>
@@ -8692,7 +8703,7 @@
         <v>16</v>
       </c>
       <c r="B266" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="C266">
         <v>1</v>
@@ -8703,7 +8714,7 @@
         <v>16</v>
       </c>
       <c r="B267" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -8714,7 +8725,7 @@
         <v>16</v>
       </c>
       <c r="B268" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="C268">
         <v>1</v>
@@ -8725,7 +8736,7 @@
         <v>16</v>
       </c>
       <c r="B269" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="C269">
         <v>1</v>
@@ -8736,7 +8747,7 @@
         <v>16</v>
       </c>
       <c r="B270" t="s">
-        <v>119</v>
+        <v>232</v>
       </c>
       <c r="C270">
         <v>1</v>
@@ -8747,7 +8758,7 @@
         <v>16</v>
       </c>
       <c r="B271" t="s">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="C271">
         <v>1</v>
@@ -8758,7 +8769,7 @@
         <v>16</v>
       </c>
       <c r="B272" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="C272">
         <v>1</v>
@@ -8769,7 +8780,7 @@
         <v>16</v>
       </c>
       <c r="B273" t="s">
-        <v>243</v>
+        <v>210</v>
       </c>
       <c r="C273">
         <v>1</v>
@@ -8780,7 +8791,7 @@
         <v>16</v>
       </c>
       <c r="B274" t="s">
-        <v>209</v>
+        <v>70</v>
       </c>
       <c r="C274">
         <v>1</v>
@@ -8788,13 +8799,13 @@
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B275" t="s">
         <v>121</v>
       </c>
       <c r="C275">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -8802,10 +8813,10 @@
         <v>21</v>
       </c>
       <c r="B276" t="s">
-        <v>189</v>
+        <v>121</v>
       </c>
       <c r="C276">
-        <v>11</v>
+        <v>39</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -8813,10 +8824,10 @@
         <v>21</v>
       </c>
       <c r="B277" t="s">
-        <v>132</v>
+        <v>189</v>
       </c>
       <c r="C277">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -8824,10 +8835,10 @@
         <v>21</v>
       </c>
       <c r="B278" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="C278">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -8835,7 +8846,7 @@
         <v>21</v>
       </c>
       <c r="B279" t="s">
-        <v>202</v>
+        <v>103</v>
       </c>
       <c r="C279">
         <v>7</v>
@@ -8846,10 +8857,10 @@
         <v>21</v>
       </c>
       <c r="B280" t="s">
-        <v>244</v>
+        <v>202</v>
       </c>
       <c r="C280">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -8857,7 +8868,7 @@
         <v>21</v>
       </c>
       <c r="B281" t="s">
-        <v>120</v>
+        <v>244</v>
       </c>
       <c r="C281">
         <v>6</v>
@@ -8868,10 +8879,10 @@
         <v>21</v>
       </c>
       <c r="B282" t="s">
-        <v>246</v>
+        <v>120</v>
       </c>
       <c r="C282">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -8879,7 +8890,7 @@
         <v>21</v>
       </c>
       <c r="B283" t="s">
-        <v>142</v>
+        <v>246</v>
       </c>
       <c r="C283">
         <v>5</v>
@@ -8890,7 +8901,7 @@
         <v>21</v>
       </c>
       <c r="B284" t="s">
-        <v>245</v>
+        <v>142</v>
       </c>
       <c r="C284">
         <v>5</v>
@@ -8901,7 +8912,7 @@
         <v>21</v>
       </c>
       <c r="B285" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C285">
         <v>5</v>
@@ -8912,10 +8923,10 @@
         <v>21</v>
       </c>
       <c r="B286" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C286">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -8923,7 +8934,7 @@
         <v>21</v>
       </c>
       <c r="B287" t="s">
-        <v>128</v>
+        <v>248</v>
       </c>
       <c r="C287">
         <v>4</v>
@@ -8934,7 +8945,7 @@
         <v>21</v>
       </c>
       <c r="B288" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="C288">
         <v>4</v>
@@ -8945,7 +8956,7 @@
         <v>21</v>
       </c>
       <c r="B289" t="s">
-        <v>133</v>
+        <v>101</v>
       </c>
       <c r="C289">
         <v>4</v>
@@ -8956,10 +8967,10 @@
         <v>21</v>
       </c>
       <c r="B290" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="C290">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -8967,7 +8978,7 @@
         <v>21</v>
       </c>
       <c r="B291" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="C291">
         <v>3</v>
@@ -8978,7 +8989,7 @@
         <v>21</v>
       </c>
       <c r="B292" t="s">
-        <v>249</v>
+        <v>81</v>
       </c>
       <c r="C292">
         <v>3</v>
@@ -8989,7 +9000,7 @@
         <v>21</v>
       </c>
       <c r="B293" t="s">
-        <v>163</v>
+        <v>249</v>
       </c>
       <c r="C293">
         <v>3</v>
@@ -9000,7 +9011,7 @@
         <v>21</v>
       </c>
       <c r="B294" t="s">
-        <v>251</v>
+        <v>163</v>
       </c>
       <c r="C294">
         <v>3</v>
@@ -9011,7 +9022,7 @@
         <v>21</v>
       </c>
       <c r="B295" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C295">
         <v>3</v>
@@ -9022,7 +9033,7 @@
         <v>21</v>
       </c>
       <c r="B296" t="s">
-        <v>44</v>
+        <v>252</v>
       </c>
       <c r="C296">
         <v>3</v>
@@ -9033,7 +9044,7 @@
         <v>21</v>
       </c>
       <c r="B297" t="s">
-        <v>253</v>
+        <v>44</v>
       </c>
       <c r="C297">
         <v>3</v>
@@ -9044,7 +9055,7 @@
         <v>21</v>
       </c>
       <c r="B298" t="s">
-        <v>126</v>
+        <v>253</v>
       </c>
       <c r="C298">
         <v>3</v>
@@ -9055,7 +9066,7 @@
         <v>21</v>
       </c>
       <c r="B299" t="s">
-        <v>196</v>
+        <v>126</v>
       </c>
       <c r="C299">
         <v>3</v>
@@ -9066,10 +9077,10 @@
         <v>21</v>
       </c>
       <c r="B300" t="s">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="C300">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -9077,7 +9088,7 @@
         <v>21</v>
       </c>
       <c r="B301" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="C301">
         <v>2</v>
@@ -9088,7 +9099,7 @@
         <v>21</v>
       </c>
       <c r="B302" t="s">
-        <v>271</v>
+        <v>198</v>
       </c>
       <c r="C302">
         <v>2</v>
@@ -9099,7 +9110,7 @@
         <v>21</v>
       </c>
       <c r="B303" t="s">
-        <v>136</v>
+        <v>271</v>
       </c>
       <c r="C303">
         <v>2</v>
@@ -9110,7 +9121,7 @@
         <v>21</v>
       </c>
       <c r="B304" t="s">
-        <v>257</v>
+        <v>136</v>
       </c>
       <c r="C304">
         <v>2</v>
@@ -9121,7 +9132,7 @@
         <v>21</v>
       </c>
       <c r="B305" t="s">
-        <v>116</v>
+        <v>257</v>
       </c>
       <c r="C305">
         <v>2</v>
@@ -9132,7 +9143,7 @@
         <v>21</v>
       </c>
       <c r="B306" t="s">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="C306">
         <v>2</v>
@@ -9143,7 +9154,7 @@
         <v>21</v>
       </c>
       <c r="B307" t="s">
-        <v>256</v>
+        <v>77</v>
       </c>
       <c r="C307">
         <v>2</v>
@@ -9154,7 +9165,7 @@
         <v>21</v>
       </c>
       <c r="B308" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C308">
         <v>2</v>
@@ -9165,7 +9176,7 @@
         <v>21</v>
       </c>
       <c r="B309" t="s">
-        <v>173</v>
+        <v>255</v>
       </c>
       <c r="C309">
         <v>2</v>
@@ -9176,7 +9187,7 @@
         <v>21</v>
       </c>
       <c r="B310" t="s">
-        <v>85</v>
+        <v>173</v>
       </c>
       <c r="C310">
         <v>2</v>
@@ -9187,7 +9198,7 @@
         <v>21</v>
       </c>
       <c r="B311" t="s">
-        <v>250</v>
+        <v>85</v>
       </c>
       <c r="C311">
         <v>2</v>
@@ -9198,7 +9209,7 @@
         <v>21</v>
       </c>
       <c r="B312" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C312">
         <v>2</v>
@@ -9209,7 +9220,7 @@
         <v>21</v>
       </c>
       <c r="B313" t="s">
-        <v>54</v>
+        <v>254</v>
       </c>
       <c r="C313">
         <v>2</v>
@@ -9220,7 +9231,7 @@
         <v>21</v>
       </c>
       <c r="B314" t="s">
-        <v>199</v>
+        <v>54</v>
       </c>
       <c r="C314">
         <v>2</v>
@@ -9231,7 +9242,7 @@
         <v>21</v>
       </c>
       <c r="B315" t="s">
-        <v>62</v>
+        <v>199</v>
       </c>
       <c r="C315">
         <v>2</v>
@@ -9242,7 +9253,7 @@
         <v>21</v>
       </c>
       <c r="B316" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C316">
         <v>2</v>
@@ -9253,10 +9264,10 @@
         <v>21</v>
       </c>
       <c r="B317" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="C317">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
@@ -9264,7 +9275,7 @@
         <v>21</v>
       </c>
       <c r="B318" t="s">
-        <v>214</v>
+        <v>63</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -9275,7 +9286,7 @@
         <v>21</v>
       </c>
       <c r="B319" t="s">
-        <v>269</v>
+        <v>214</v>
       </c>
       <c r="C319">
         <v>1</v>
@@ -9286,7 +9297,7 @@
         <v>21</v>
       </c>
       <c r="B320" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="C320">
         <v>1</v>
@@ -9297,7 +9308,7 @@
         <v>21</v>
       </c>
       <c r="B321" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="C321">
         <v>1</v>
@@ -9308,7 +9319,7 @@
         <v>21</v>
       </c>
       <c r="B322" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="C322">
         <v>1</v>
@@ -9319,7 +9330,7 @@
         <v>21</v>
       </c>
       <c r="B323" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C323">
         <v>1</v>
@@ -9330,7 +9341,7 @@
         <v>21</v>
       </c>
       <c r="B324" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="C324">
         <v>1</v>
@@ -9341,7 +9352,7 @@
         <v>21</v>
       </c>
       <c r="B325" t="s">
-        <v>137</v>
+        <v>279</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -9352,7 +9363,7 @@
         <v>21</v>
       </c>
       <c r="B326" t="s">
-        <v>266</v>
+        <v>137</v>
       </c>
       <c r="C326">
         <v>1</v>
@@ -9363,7 +9374,7 @@
         <v>21</v>
       </c>
       <c r="B327" t="s">
-        <v>92</v>
+        <v>266</v>
       </c>
       <c r="C327">
         <v>1</v>
@@ -9374,7 +9385,7 @@
         <v>21</v>
       </c>
       <c r="B328" t="s">
-        <v>267</v>
+        <v>92</v>
       </c>
       <c r="C328">
         <v>1</v>
@@ -9385,7 +9396,7 @@
         <v>21</v>
       </c>
       <c r="B329" t="s">
-        <v>125</v>
+        <v>267</v>
       </c>
       <c r="C329">
         <v>1</v>
@@ -9396,7 +9407,7 @@
         <v>21</v>
       </c>
       <c r="B330" t="s">
-        <v>280</v>
+        <v>125</v>
       </c>
       <c r="C330">
         <v>1</v>
@@ -9407,7 +9418,7 @@
         <v>21</v>
       </c>
       <c r="B331" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C331">
         <v>1</v>
@@ -9418,7 +9429,7 @@
         <v>21</v>
       </c>
       <c r="B332" t="s">
-        <v>185</v>
+        <v>278</v>
       </c>
       <c r="C332">
         <v>1</v>
@@ -9429,7 +9440,7 @@
         <v>21</v>
       </c>
       <c r="B333" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="C333">
         <v>1</v>
@@ -9440,7 +9451,7 @@
         <v>21</v>
       </c>
       <c r="B334" t="s">
-        <v>49</v>
+        <v>165</v>
       </c>
       <c r="C334">
         <v>1</v>
@@ -9451,7 +9462,7 @@
         <v>21</v>
       </c>
       <c r="B335" t="s">
-        <v>115</v>
+        <v>49</v>
       </c>
       <c r="C335">
         <v>1</v>
@@ -9462,7 +9473,7 @@
         <v>21</v>
       </c>
       <c r="B336" t="s">
-        <v>270</v>
+        <v>115</v>
       </c>
       <c r="C336">
         <v>1</v>
@@ -9473,7 +9484,7 @@
         <v>21</v>
       </c>
       <c r="B337" t="s">
-        <v>138</v>
+        <v>270</v>
       </c>
       <c r="C337">
         <v>1</v>
@@ -9484,7 +9495,7 @@
         <v>21</v>
       </c>
       <c r="B338" t="s">
-        <v>273</v>
+        <v>138</v>
       </c>
       <c r="C338">
         <v>1</v>
@@ -9495,7 +9506,7 @@
         <v>21</v>
       </c>
       <c r="B339" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="C339">
         <v>1</v>
@@ -9506,7 +9517,7 @@
         <v>21</v>
       </c>
       <c r="B340" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="C340">
         <v>1</v>
@@ -9517,7 +9528,7 @@
         <v>21</v>
       </c>
       <c r="B341" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="C341">
         <v>1</v>
@@ -9528,7 +9539,7 @@
         <v>21</v>
       </c>
       <c r="B342" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="C342">
         <v>1</v>
@@ -9539,7 +9550,7 @@
         <v>21</v>
       </c>
       <c r="B343" t="s">
-        <v>172</v>
+        <v>272</v>
       </c>
       <c r="C343">
         <v>1</v>
@@ -9550,7 +9561,7 @@
         <v>21</v>
       </c>
       <c r="B344" t="s">
-        <v>277</v>
+        <v>172</v>
       </c>
       <c r="C344">
         <v>1</v>
@@ -9561,7 +9572,7 @@
         <v>21</v>
       </c>
       <c r="B345" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="C345">
         <v>1</v>
@@ -9572,7 +9583,7 @@
         <v>21</v>
       </c>
       <c r="B346" t="s">
-        <v>276</v>
+        <v>258</v>
       </c>
       <c r="C346">
         <v>1</v>
@@ -9583,7 +9594,7 @@
         <v>21</v>
       </c>
       <c r="B347" t="s">
-        <v>148</v>
+        <v>276</v>
       </c>
       <c r="C347">
         <v>1</v>
@@ -9594,7 +9605,7 @@
         <v>21</v>
       </c>
       <c r="B348" t="s">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c r="C348">
         <v>1</v>
@@ -9605,7 +9616,7 @@
         <v>21</v>
       </c>
       <c r="B349" t="s">
-        <v>260</v>
+        <v>174</v>
       </c>
       <c r="C349">
         <v>1</v>
@@ -9616,7 +9627,7 @@
         <v>21</v>
       </c>
       <c r="B350" t="s">
-        <v>281</v>
+        <v>260</v>
       </c>
       <c r="C350">
         <v>1</v>
@@ -9627,7 +9638,7 @@
         <v>21</v>
       </c>
       <c r="B351" t="s">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="C351">
         <v>1</v>
@@ -9638,7 +9649,7 @@
         <v>21</v>
       </c>
       <c r="B352" t="s">
-        <v>282</v>
+        <v>259</v>
       </c>
       <c r="C352">
         <v>1</v>
@@ -9649,9 +9660,20 @@
         <v>21</v>
       </c>
       <c r="B353" t="s">
+        <v>282</v>
+      </c>
+      <c r="C353">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>21</v>
+      </c>
+      <c r="B354" t="s">
         <v>268</v>
       </c>
-      <c r="C353">
+      <c r="C354">
         <v>1</v>
       </c>
     </row>
@@ -9940,7 +9962,7 @@
         <v>287</v>
       </c>
       <c r="C25">
-        <v>873</v>
+        <v>876</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="150" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95AF4B72-74CA-4F31-9868-91B2ADF691C9}"/>
+  <xr:revisionPtr revIDLastSave="164" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F7610F2-617E-4FA8-BA0B-F94CF87C6183}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" tabRatio="731" firstSheet="1" activeTab="7" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1320" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1321" uniqueCount="300">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -1447,10 +1447,10 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3">
-        <v>1.03</v>
+        <v>1.0609999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1481,10 +1481,10 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E5">
-        <v>1.294</v>
+        <v>1.2649999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1685,10 +1685,10 @@
         <v>68</v>
       </c>
       <c r="D17">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E17">
-        <v>1.044</v>
+        <v>1.0289999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -1940,10 +1940,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E32">
-        <v>1.0660000000000001</v>
+        <v>1.0629999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -1957,10 +1957,10 @@
         <v>329</v>
       </c>
       <c r="D33">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E33">
-        <v>1.03</v>
+        <v>1.036</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2008,10 +2008,10 @@
         <v>250</v>
       </c>
       <c r="D36">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E36">
-        <v>1.028</v>
+        <v>1.024</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2042,10 +2042,10 @@
         <v>226</v>
       </c>
       <c r="D38">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E38">
-        <v>1.075</v>
+        <v>1.071</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -2289,7 +2289,7 @@
         <v>34</v>
       </c>
       <c r="C4">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2333,7 +2333,7 @@
         <v>34</v>
       </c>
       <c r="C8">
-        <v>593</v>
+        <v>595</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2344,7 +2344,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2355,7 +2355,7 @@
         <v>35</v>
       </c>
       <c r="C10">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -2366,7 +2366,7 @@
         <v>34</v>
       </c>
       <c r="C11">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
   </sheetData>
@@ -2376,7 +2376,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD19485A-0629-47F9-A5AD-80ABA7A6E076}">
-  <dimension ref="A1:C246"/>
+  <dimension ref="A1:C247"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -2425,7 +2425,7 @@
         <v>46000</v>
       </c>
       <c r="C4" s="6">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2939,10 +2939,10 @@
         <v>16</v>
       </c>
       <c r="B51" s="8">
-        <v>46156</v>
+        <v>46177</v>
       </c>
       <c r="C51" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -2950,7 +2950,7 @@
         <v>16</v>
       </c>
       <c r="B52" s="5">
-        <v>46092</v>
+        <v>46156</v>
       </c>
       <c r="C52" s="6">
         <v>1</v>
@@ -2961,7 +2961,7 @@
         <v>16</v>
       </c>
       <c r="B53" s="8">
-        <v>46101</v>
+        <v>46092</v>
       </c>
       <c r="C53" s="9">
         <v>1</v>
@@ -2969,13 +2969,13 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B54" s="5">
-        <v>46007</v>
+        <v>46101</v>
       </c>
       <c r="C54" s="6">
-        <v>78</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -2983,10 +2983,10 @@
         <v>14</v>
       </c>
       <c r="B55" s="8">
-        <v>46009</v>
+        <v>46007</v>
       </c>
       <c r="C55" s="9">
-        <v>34</v>
+        <v>78</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -2994,10 +2994,10 @@
         <v>14</v>
       </c>
       <c r="B56" s="5">
-        <v>46000</v>
+        <v>46009</v>
       </c>
       <c r="C56" s="6">
-        <v>80</v>
+        <v>34</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -3005,10 +3005,10 @@
         <v>14</v>
       </c>
       <c r="B57" s="8">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C57" s="9">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -3016,10 +3016,10 @@
         <v>14</v>
       </c>
       <c r="B58" s="5">
-        <v>46006</v>
+        <v>46001</v>
       </c>
       <c r="C58" s="6">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -3027,10 +3027,10 @@
         <v>14</v>
       </c>
       <c r="B59" s="8">
-        <v>46010</v>
+        <v>46006</v>
       </c>
       <c r="C59" s="9">
-        <v>24</v>
+        <v>79</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -3038,10 +3038,10 @@
         <v>14</v>
       </c>
       <c r="B60" s="5">
-        <v>46014</v>
+        <v>46010</v>
       </c>
       <c r="C60" s="6">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -3049,10 +3049,10 @@
         <v>14</v>
       </c>
       <c r="B61" s="8">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="C61" s="9">
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -3060,10 +3060,10 @@
         <v>14</v>
       </c>
       <c r="B62" s="5">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C62" s="6">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -3071,10 +3071,10 @@
         <v>14</v>
       </c>
       <c r="B63" s="8">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="C63" s="9">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -3082,10 +3082,10 @@
         <v>14</v>
       </c>
       <c r="B64" s="5">
-        <v>46013</v>
+        <v>46003</v>
       </c>
       <c r="C64" s="6">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -3093,10 +3093,10 @@
         <v>14</v>
       </c>
       <c r="B65" s="8">
-        <v>46022</v>
+        <v>46013</v>
       </c>
       <c r="C65" s="9">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -3104,10 +3104,10 @@
         <v>14</v>
       </c>
       <c r="B66" s="5">
-        <v>46080</v>
+        <v>46022</v>
       </c>
       <c r="C66" s="6">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -3115,10 +3115,10 @@
         <v>14</v>
       </c>
       <c r="B67" s="8">
-        <v>46084</v>
+        <v>46080</v>
       </c>
       <c r="C67" s="9">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -3126,10 +3126,10 @@
         <v>14</v>
       </c>
       <c r="B68" s="5">
-        <v>46125</v>
+        <v>46084</v>
       </c>
       <c r="C68" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -3137,10 +3137,10 @@
         <v>14</v>
       </c>
       <c r="B69" s="8">
-        <v>46091</v>
+        <v>46125</v>
       </c>
       <c r="C69" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -3148,10 +3148,10 @@
         <v>14</v>
       </c>
       <c r="B70" s="5">
-        <v>46083</v>
+        <v>46091</v>
       </c>
       <c r="C70" s="6">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -3159,10 +3159,10 @@
         <v>14</v>
       </c>
       <c r="B71" s="8">
-        <v>46105</v>
+        <v>46083</v>
       </c>
       <c r="C71" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -3170,10 +3170,10 @@
         <v>14</v>
       </c>
       <c r="B72" s="5">
-        <v>46077</v>
+        <v>46105</v>
       </c>
       <c r="C72" s="6">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -3181,10 +3181,10 @@
         <v>14</v>
       </c>
       <c r="B73" s="8">
-        <v>46118</v>
+        <v>46077</v>
       </c>
       <c r="C73" s="9">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -3192,10 +3192,10 @@
         <v>14</v>
       </c>
       <c r="B74" s="5">
-        <v>46078</v>
+        <v>46118</v>
       </c>
       <c r="C74" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -3203,10 +3203,10 @@
         <v>14</v>
       </c>
       <c r="B75" s="8">
-        <v>46099</v>
+        <v>46078</v>
       </c>
       <c r="C75" s="9">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -3214,10 +3214,10 @@
         <v>14</v>
       </c>
       <c r="B76" s="5">
-        <v>46104</v>
+        <v>46099</v>
       </c>
       <c r="C76" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -3225,10 +3225,10 @@
         <v>14</v>
       </c>
       <c r="B77" s="8">
-        <v>46107</v>
+        <v>46104</v>
       </c>
       <c r="C77" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -3236,7 +3236,7 @@
         <v>14</v>
       </c>
       <c r="B78" s="5">
-        <v>46020</v>
+        <v>46107</v>
       </c>
       <c r="C78" s="6">
         <v>2</v>
@@ -3247,10 +3247,10 @@
         <v>14</v>
       </c>
       <c r="B79" s="8">
-        <v>46076</v>
+        <v>46020</v>
       </c>
       <c r="C79" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -3258,10 +3258,10 @@
         <v>14</v>
       </c>
       <c r="B80" s="5">
-        <v>46111</v>
+        <v>46076</v>
       </c>
       <c r="C80" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -3269,10 +3269,10 @@
         <v>14</v>
       </c>
       <c r="B81" s="8">
-        <v>46087</v>
+        <v>46111</v>
       </c>
       <c r="C81" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -3280,7 +3280,7 @@
         <v>14</v>
       </c>
       <c r="B82" s="5">
-        <v>46140</v>
+        <v>46087</v>
       </c>
       <c r="C82" s="6">
         <v>2</v>
@@ -3291,10 +3291,10 @@
         <v>14</v>
       </c>
       <c r="B83" s="8">
-        <v>46113</v>
+        <v>46140</v>
       </c>
       <c r="C83" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -3302,10 +3302,10 @@
         <v>14</v>
       </c>
       <c r="B84" s="5">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="C84" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -3313,10 +3313,10 @@
         <v>14</v>
       </c>
       <c r="B85" s="8">
-        <v>46108</v>
+        <v>46119</v>
       </c>
       <c r="C85" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -3324,7 +3324,7 @@
         <v>14</v>
       </c>
       <c r="B86" s="5">
-        <v>46098</v>
+        <v>46108</v>
       </c>
       <c r="C86" s="6">
         <v>1</v>
@@ -3335,7 +3335,7 @@
         <v>14</v>
       </c>
       <c r="B87" s="8">
-        <v>46141</v>
+        <v>46098</v>
       </c>
       <c r="C87" s="9">
         <v>1</v>
@@ -3346,7 +3346,7 @@
         <v>14</v>
       </c>
       <c r="B88" s="5">
-        <v>46114</v>
+        <v>46141</v>
       </c>
       <c r="C88" s="6">
         <v>1</v>
@@ -3357,10 +3357,10 @@
         <v>14</v>
       </c>
       <c r="B89" s="8">
-        <v>46079</v>
+        <v>46114</v>
       </c>
       <c r="C89" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -3368,10 +3368,10 @@
         <v>14</v>
       </c>
       <c r="B90" s="5">
-        <v>46139</v>
+        <v>46079</v>
       </c>
       <c r="C90" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -3379,10 +3379,10 @@
         <v>14</v>
       </c>
       <c r="B91" s="8">
-        <v>46148</v>
+        <v>46139</v>
       </c>
       <c r="C91" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -3390,10 +3390,10 @@
         <v>14</v>
       </c>
       <c r="B92" s="5">
-        <v>46174</v>
+        <v>46148</v>
       </c>
       <c r="C92" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -3668,7 +3668,7 @@
         <v>46084</v>
       </c>
       <c r="C117" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -3819,10 +3819,10 @@
         <v>3</v>
       </c>
       <c r="B131" s="8">
-        <v>46161</v>
+        <v>46177</v>
       </c>
       <c r="C131" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -3830,10 +3830,10 @@
         <v>3</v>
       </c>
       <c r="B132" s="5">
-        <v>46129</v>
+        <v>46161</v>
       </c>
       <c r="C132" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -3841,7 +3841,7 @@
         <v>3</v>
       </c>
       <c r="B133" s="8">
-        <v>46080</v>
+        <v>46129</v>
       </c>
       <c r="C133" s="9">
         <v>1</v>
@@ -3852,7 +3852,7 @@
         <v>3</v>
       </c>
       <c r="B134" s="5">
-        <v>46101</v>
+        <v>46080</v>
       </c>
       <c r="C134" s="6">
         <v>1</v>
@@ -3863,7 +3863,7 @@
         <v>3</v>
       </c>
       <c r="B135" s="8">
-        <v>46155</v>
+        <v>46101</v>
       </c>
       <c r="C135" s="9">
         <v>1</v>
@@ -3874,7 +3874,7 @@
         <v>3</v>
       </c>
       <c r="B136" s="5">
-        <v>46150</v>
+        <v>46155</v>
       </c>
       <c r="C136" s="6">
         <v>1</v>
@@ -3885,7 +3885,7 @@
         <v>3</v>
       </c>
       <c r="B137" s="8">
-        <v>46141</v>
+        <v>46150</v>
       </c>
       <c r="C137" s="9">
         <v>1</v>
@@ -3896,7 +3896,7 @@
         <v>3</v>
       </c>
       <c r="B138" s="5">
-        <v>46085</v>
+        <v>46141</v>
       </c>
       <c r="C138" s="6">
         <v>1</v>
@@ -3907,7 +3907,7 @@
         <v>3</v>
       </c>
       <c r="B139" s="8">
-        <v>46148</v>
+        <v>46085</v>
       </c>
       <c r="C139" s="9">
         <v>1</v>
@@ -3918,10 +3918,10 @@
         <v>3</v>
       </c>
       <c r="B140" s="5">
-        <v>46118</v>
+        <v>46148</v>
       </c>
       <c r="C140" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -3929,21 +3929,21 @@
         <v>3</v>
       </c>
       <c r="B141" s="8">
-        <v>46079</v>
+        <v>46118</v>
       </c>
       <c r="C141" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B142" s="5">
-        <v>46003</v>
+        <v>46079</v>
       </c>
       <c r="C142" s="6">
-        <v>92</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -3951,10 +3951,10 @@
         <v>15</v>
       </c>
       <c r="B143" s="8">
-        <v>46000</v>
+        <v>46003</v>
       </c>
       <c r="C143" s="9">
-        <v>132</v>
+        <v>92</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -3962,10 +3962,10 @@
         <v>15</v>
       </c>
       <c r="B144" s="5">
-        <v>46006</v>
+        <v>46000</v>
       </c>
       <c r="C144" s="6">
-        <v>173</v>
+        <v>132</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -3973,10 +3973,10 @@
         <v>15</v>
       </c>
       <c r="B145" s="8">
-        <v>46001</v>
+        <v>46006</v>
       </c>
       <c r="C145" s="9">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -3984,10 +3984,10 @@
         <v>15</v>
       </c>
       <c r="B146" s="5">
-        <v>46014</v>
+        <v>46001</v>
       </c>
       <c r="C146" s="6">
-        <v>16</v>
+        <v>174</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -3995,10 +3995,10 @@
         <v>15</v>
       </c>
       <c r="B147" s="8">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="C147" s="9">
-        <v>171</v>
+        <v>16</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -4006,10 +4006,10 @@
         <v>15</v>
       </c>
       <c r="B148" s="5">
-        <v>46009</v>
+        <v>46002</v>
       </c>
       <c r="C148" s="6">
-        <v>19</v>
+        <v>171</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -4017,7 +4017,7 @@
         <v>15</v>
       </c>
       <c r="B149" s="8">
-        <v>46010</v>
+        <v>46009</v>
       </c>
       <c r="C149" s="9">
         <v>19</v>
@@ -4028,10 +4028,10 @@
         <v>15</v>
       </c>
       <c r="B150" s="5">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="C150" s="6">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -4039,10 +4039,10 @@
         <v>15</v>
       </c>
       <c r="B151" s="8">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="C151" s="9">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -4050,10 +4050,10 @@
         <v>15</v>
       </c>
       <c r="B152" s="5">
-        <v>46013</v>
+        <v>46007</v>
       </c>
       <c r="C152" s="6">
-        <v>12</v>
+        <v>43</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -4061,10 +4061,10 @@
         <v>15</v>
       </c>
       <c r="B153" s="8">
-        <v>46080</v>
+        <v>46013</v>
       </c>
       <c r="C153" s="9">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -4072,10 +4072,10 @@
         <v>15</v>
       </c>
       <c r="B154" s="5">
-        <v>46090</v>
+        <v>46080</v>
       </c>
       <c r="C154" s="6">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -4083,10 +4083,10 @@
         <v>15</v>
       </c>
       <c r="B155" s="8">
-        <v>46079</v>
+        <v>46090</v>
       </c>
       <c r="C155" s="9">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -4094,10 +4094,10 @@
         <v>15</v>
       </c>
       <c r="B156" s="5">
-        <v>46015</v>
+        <v>46079</v>
       </c>
       <c r="C156" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -4105,10 +4105,10 @@
         <v>15</v>
       </c>
       <c r="B157" s="8">
-        <v>46085</v>
+        <v>46015</v>
       </c>
       <c r="C157" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -4116,10 +4116,10 @@
         <v>15</v>
       </c>
       <c r="B158" s="5">
-        <v>46098</v>
+        <v>46085</v>
       </c>
       <c r="C158" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -4127,10 +4127,10 @@
         <v>15</v>
       </c>
       <c r="B159" s="8">
-        <v>46021</v>
+        <v>46098</v>
       </c>
       <c r="C159" s="9">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -4138,10 +4138,10 @@
         <v>15</v>
       </c>
       <c r="B160" s="5">
-        <v>46078</v>
+        <v>46021</v>
       </c>
       <c r="C160" s="6">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -4149,10 +4149,10 @@
         <v>15</v>
       </c>
       <c r="B161" s="8">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="C161" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -4160,10 +4160,10 @@
         <v>15</v>
       </c>
       <c r="B162" s="5">
-        <v>46128</v>
+        <v>46084</v>
       </c>
       <c r="C162" s="6">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -4171,10 +4171,10 @@
         <v>15</v>
       </c>
       <c r="B163" s="8">
-        <v>46083</v>
+        <v>46128</v>
       </c>
       <c r="C163" s="9">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -4182,10 +4182,10 @@
         <v>15</v>
       </c>
       <c r="B164" s="5">
-        <v>46153</v>
+        <v>46083</v>
       </c>
       <c r="C164" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -4193,10 +4193,10 @@
         <v>15</v>
       </c>
       <c r="B165" s="8">
-        <v>46076</v>
+        <v>46153</v>
       </c>
       <c r="C165" s="9">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -4204,10 +4204,10 @@
         <v>15</v>
       </c>
       <c r="B166" s="5">
-        <v>46099</v>
+        <v>46076</v>
       </c>
       <c r="C166" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -4215,10 +4215,10 @@
         <v>15</v>
       </c>
       <c r="B167" s="8">
-        <v>46154</v>
+        <v>46099</v>
       </c>
       <c r="C167" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -4226,7 +4226,7 @@
         <v>15</v>
       </c>
       <c r="B168" s="5">
-        <v>46092</v>
+        <v>46154</v>
       </c>
       <c r="C168" s="6">
         <v>1</v>
@@ -4237,10 +4237,10 @@
         <v>15</v>
       </c>
       <c r="B169" s="8">
-        <v>46031</v>
+        <v>46092</v>
       </c>
       <c r="C169" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -4248,7 +4248,7 @@
         <v>15</v>
       </c>
       <c r="B170" s="5">
-        <v>46120</v>
+        <v>46031</v>
       </c>
       <c r="C170" s="6">
         <v>2</v>
@@ -4259,10 +4259,10 @@
         <v>15</v>
       </c>
       <c r="B171" s="8">
-        <v>46077</v>
+        <v>46120</v>
       </c>
       <c r="C171" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -4270,10 +4270,10 @@
         <v>15</v>
       </c>
       <c r="B172" s="5">
-        <v>46114</v>
+        <v>46077</v>
       </c>
       <c r="C172" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -4281,7 +4281,7 @@
         <v>15</v>
       </c>
       <c r="B173" s="8">
-        <v>46037</v>
+        <v>46114</v>
       </c>
       <c r="C173" s="9">
         <v>1</v>
@@ -4292,10 +4292,10 @@
         <v>15</v>
       </c>
       <c r="B174" s="5">
-        <v>46020</v>
+        <v>46037</v>
       </c>
       <c r="C174" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -4303,10 +4303,10 @@
         <v>15</v>
       </c>
       <c r="B175" s="8">
-        <v>46106</v>
+        <v>46020</v>
       </c>
       <c r="C175" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -4314,7 +4314,7 @@
         <v>15</v>
       </c>
       <c r="B176" s="5">
-        <v>46155</v>
+        <v>46106</v>
       </c>
       <c r="C176" s="6">
         <v>1</v>
@@ -4325,7 +4325,7 @@
         <v>15</v>
       </c>
       <c r="B177" s="8">
-        <v>46112</v>
+        <v>46155</v>
       </c>
       <c r="C177" s="9">
         <v>1</v>
@@ -4336,7 +4336,7 @@
         <v>15</v>
       </c>
       <c r="B178" s="5">
-        <v>46132</v>
+        <v>46112</v>
       </c>
       <c r="C178" s="6">
         <v>1</v>
@@ -4347,7 +4347,7 @@
         <v>15</v>
       </c>
       <c r="B179" s="8">
-        <v>46108</v>
+        <v>46132</v>
       </c>
       <c r="C179" s="9">
         <v>1</v>
@@ -4358,7 +4358,7 @@
         <v>15</v>
       </c>
       <c r="B180" s="5">
-        <v>46148</v>
+        <v>46108</v>
       </c>
       <c r="C180" s="6">
         <v>1</v>
@@ -4369,7 +4369,7 @@
         <v>15</v>
       </c>
       <c r="B181" s="8">
-        <v>46118</v>
+        <v>46148</v>
       </c>
       <c r="C181" s="9">
         <v>1</v>
@@ -4380,7 +4380,7 @@
         <v>15</v>
       </c>
       <c r="B182" s="5">
-        <v>46035</v>
+        <v>46118</v>
       </c>
       <c r="C182" s="6">
         <v>1</v>
@@ -4391,7 +4391,7 @@
         <v>15</v>
       </c>
       <c r="B183" s="8">
-        <v>46093</v>
+        <v>46035</v>
       </c>
       <c r="C183" s="9">
         <v>1</v>
@@ -4402,7 +4402,7 @@
         <v>15</v>
       </c>
       <c r="B184" s="5">
-        <v>46022</v>
+        <v>46093</v>
       </c>
       <c r="C184" s="6">
         <v>1</v>
@@ -4413,7 +4413,7 @@
         <v>15</v>
       </c>
       <c r="B185" s="8">
-        <v>46087</v>
+        <v>46022</v>
       </c>
       <c r="C185" s="9">
         <v>1</v>
@@ -4424,10 +4424,10 @@
         <v>15</v>
       </c>
       <c r="B186" s="5">
-        <v>46030</v>
+        <v>46087</v>
       </c>
       <c r="C186" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -4435,10 +4435,10 @@
         <v>15</v>
       </c>
       <c r="B187" s="8">
-        <v>46101</v>
+        <v>46030</v>
       </c>
       <c r="C187" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -4446,7 +4446,7 @@
         <v>15</v>
       </c>
       <c r="B188" s="5">
-        <v>46142</v>
+        <v>46101</v>
       </c>
       <c r="C188" s="6">
         <v>1</v>
@@ -4454,13 +4454,13 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B189" s="8">
-        <v>46001</v>
+        <v>46142</v>
       </c>
       <c r="C189" s="9">
-        <v>153</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -4468,10 +4468,10 @@
         <v>21</v>
       </c>
       <c r="B190" s="5">
-        <v>46008</v>
+        <v>46001</v>
       </c>
       <c r="C190" s="6">
-        <v>38</v>
+        <v>153</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -4479,10 +4479,10 @@
         <v>21</v>
       </c>
       <c r="B191" s="8">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="C191" s="9">
-        <v>70</v>
+        <v>38</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -4490,10 +4490,10 @@
         <v>21</v>
       </c>
       <c r="B192" s="5">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="C192" s="6">
-        <v>111</v>
+        <v>70</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -4501,10 +4501,10 @@
         <v>21</v>
       </c>
       <c r="B193" s="8">
-        <v>46006</v>
+        <v>46002</v>
       </c>
       <c r="C193" s="9">
-        <v>147</v>
+        <v>111</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -4512,10 +4512,10 @@
         <v>21</v>
       </c>
       <c r="B194" s="5">
-        <v>46007</v>
+        <v>46006</v>
       </c>
       <c r="C194" s="6">
-        <v>45</v>
+        <v>146</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -4523,10 +4523,10 @@
         <v>21</v>
       </c>
       <c r="B195" s="8">
-        <v>46000</v>
+        <v>46007</v>
       </c>
       <c r="C195" s="9">
-        <v>127</v>
+        <v>45</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -4534,10 +4534,10 @@
         <v>21</v>
       </c>
       <c r="B196" s="5">
-        <v>46084</v>
+        <v>46000</v>
       </c>
       <c r="C196" s="6">
-        <v>10</v>
+        <v>127</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -4545,10 +4545,10 @@
         <v>21</v>
       </c>
       <c r="B197" s="8">
-        <v>46014</v>
+        <v>46084</v>
       </c>
       <c r="C197" s="9">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -4556,10 +4556,10 @@
         <v>21</v>
       </c>
       <c r="B198" s="5">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="C198" s="6">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -4567,10 +4567,10 @@
         <v>21</v>
       </c>
       <c r="B199" s="8">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="C199" s="9">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -4578,10 +4578,10 @@
         <v>21</v>
       </c>
       <c r="B200" s="5">
-        <v>46021</v>
+        <v>46010</v>
       </c>
       <c r="C200" s="6">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -4589,10 +4589,10 @@
         <v>21</v>
       </c>
       <c r="B201" s="8">
-        <v>46009</v>
+        <v>46021</v>
       </c>
       <c r="C201" s="9">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -4600,10 +4600,10 @@
         <v>21</v>
       </c>
       <c r="B202" s="5">
-        <v>46083</v>
+        <v>46009</v>
       </c>
       <c r="C202" s="6">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -4611,10 +4611,10 @@
         <v>21</v>
       </c>
       <c r="B203" s="8">
-        <v>46157</v>
+        <v>46083</v>
       </c>
       <c r="C203" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -4622,10 +4622,10 @@
         <v>21</v>
       </c>
       <c r="B204" s="5">
-        <v>46079</v>
+        <v>46157</v>
       </c>
       <c r="C204" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -4633,10 +4633,10 @@
         <v>21</v>
       </c>
       <c r="B205" s="8">
-        <v>46167</v>
+        <v>46079</v>
       </c>
       <c r="C205" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -4644,10 +4644,10 @@
         <v>21</v>
       </c>
       <c r="B206" s="5">
-        <v>46077</v>
+        <v>46167</v>
       </c>
       <c r="C206" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -4655,10 +4655,10 @@
         <v>21</v>
       </c>
       <c r="B207" s="8">
-        <v>46035</v>
+        <v>46077</v>
       </c>
       <c r="C207" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4666,10 +4666,10 @@
         <v>21</v>
       </c>
       <c r="B208" s="5">
-        <v>46085</v>
+        <v>46035</v>
       </c>
       <c r="C208" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4677,10 +4677,10 @@
         <v>21</v>
       </c>
       <c r="B209" s="8">
-        <v>46120</v>
+        <v>46085</v>
       </c>
       <c r="C209" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4688,10 +4688,10 @@
         <v>21</v>
       </c>
       <c r="B210" s="5">
-        <v>46114</v>
+        <v>46120</v>
       </c>
       <c r="C210" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -4699,10 +4699,10 @@
         <v>21</v>
       </c>
       <c r="B211" s="8">
-        <v>46094</v>
+        <v>46114</v>
       </c>
       <c r="C211" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -4710,10 +4710,10 @@
         <v>21</v>
       </c>
       <c r="B212" s="5">
-        <v>46080</v>
+        <v>46094</v>
       </c>
       <c r="C212" s="6">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4721,10 +4721,10 @@
         <v>21</v>
       </c>
       <c r="B213" s="8">
-        <v>46127</v>
+        <v>46080</v>
       </c>
       <c r="C213" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4732,7 +4732,7 @@
         <v>21</v>
       </c>
       <c r="B214" s="5">
-        <v>46091</v>
+        <v>46127</v>
       </c>
       <c r="C214" s="6">
         <v>2</v>
@@ -4743,10 +4743,10 @@
         <v>21</v>
       </c>
       <c r="B215" s="8">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="C215" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4754,10 +4754,10 @@
         <v>21</v>
       </c>
       <c r="B216" s="5">
-        <v>46020</v>
+        <v>46090</v>
       </c>
       <c r="C216" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4765,10 +4765,10 @@
         <v>21</v>
       </c>
       <c r="B217" s="8">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="C217" s="9">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -4776,10 +4776,10 @@
         <v>21</v>
       </c>
       <c r="B218" s="5">
-        <v>46078</v>
+        <v>46015</v>
       </c>
       <c r="C218" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -4787,10 +4787,10 @@
         <v>21</v>
       </c>
       <c r="B219" s="8">
-        <v>46148</v>
+        <v>46078</v>
       </c>
       <c r="C219" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4798,7 +4798,7 @@
         <v>21</v>
       </c>
       <c r="B220" s="5">
-        <v>46105</v>
+        <v>46148</v>
       </c>
       <c r="C220" s="6">
         <v>2</v>
@@ -4809,10 +4809,10 @@
         <v>21</v>
       </c>
       <c r="B221" s="8">
-        <v>46087</v>
+        <v>46105</v>
       </c>
       <c r="C221" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -4820,7 +4820,7 @@
         <v>21</v>
       </c>
       <c r="B222" s="5">
-        <v>46107</v>
+        <v>46087</v>
       </c>
       <c r="C222" s="6">
         <v>3</v>
@@ -4831,10 +4831,10 @@
         <v>21</v>
       </c>
       <c r="B223" s="8">
-        <v>46086</v>
+        <v>46107</v>
       </c>
       <c r="C223" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -4842,10 +4842,10 @@
         <v>21</v>
       </c>
       <c r="B224" s="5">
-        <v>46106</v>
+        <v>46086</v>
       </c>
       <c r="C224" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -4853,10 +4853,10 @@
         <v>21</v>
       </c>
       <c r="B225" s="8">
-        <v>46150</v>
+        <v>46106</v>
       </c>
       <c r="C225" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -4864,7 +4864,7 @@
         <v>21</v>
       </c>
       <c r="B226" s="5">
-        <v>46104</v>
+        <v>46150</v>
       </c>
       <c r="C226" s="6">
         <v>3</v>
@@ -4875,10 +4875,10 @@
         <v>21</v>
       </c>
       <c r="B227" s="8">
-        <v>46118</v>
+        <v>46104</v>
       </c>
       <c r="C227" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -4886,10 +4886,10 @@
         <v>21</v>
       </c>
       <c r="B228" s="5">
-        <v>46076</v>
+        <v>46118</v>
       </c>
       <c r="C228" s="6">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -4897,10 +4897,10 @@
         <v>21</v>
       </c>
       <c r="B229" s="8">
-        <v>46154</v>
+        <v>46076</v>
       </c>
       <c r="C229" s="9">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -4908,10 +4908,10 @@
         <v>21</v>
       </c>
       <c r="B230" s="5">
-        <v>46093</v>
+        <v>46154</v>
       </c>
       <c r="C230" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -4919,10 +4919,10 @@
         <v>21</v>
       </c>
       <c r="B231" s="8">
-        <v>46122</v>
+        <v>46093</v>
       </c>
       <c r="C231" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -4930,10 +4930,10 @@
         <v>21</v>
       </c>
       <c r="B232" s="5">
-        <v>46092</v>
+        <v>46122</v>
       </c>
       <c r="C232" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -4941,10 +4941,10 @@
         <v>21</v>
       </c>
       <c r="B233" s="8">
-        <v>46156</v>
+        <v>46092</v>
       </c>
       <c r="C233" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -4952,10 +4952,10 @@
         <v>21</v>
       </c>
       <c r="B234" s="5">
-        <v>46133</v>
+        <v>46156</v>
       </c>
       <c r="C234" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -4963,7 +4963,7 @@
         <v>21</v>
       </c>
       <c r="B235" s="8">
-        <v>46126</v>
+        <v>46133</v>
       </c>
       <c r="C235" s="9">
         <v>1</v>
@@ -4974,10 +4974,10 @@
         <v>21</v>
       </c>
       <c r="B236" s="5">
-        <v>46022</v>
+        <v>46126</v>
       </c>
       <c r="C236" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -4985,7 +4985,7 @@
         <v>21</v>
       </c>
       <c r="B237" s="8">
-        <v>46100</v>
+        <v>46022</v>
       </c>
       <c r="C237" s="9">
         <v>2</v>
@@ -4996,10 +4996,10 @@
         <v>21</v>
       </c>
       <c r="B238" s="5">
-        <v>46101</v>
+        <v>46100</v>
       </c>
       <c r="C238" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -5007,10 +5007,10 @@
         <v>21</v>
       </c>
       <c r="B239" s="8">
-        <v>46097</v>
+        <v>46101</v>
       </c>
       <c r="C239" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -5018,10 +5018,10 @@
         <v>21</v>
       </c>
       <c r="B240" s="5">
-        <v>46108</v>
+        <v>46097</v>
       </c>
       <c r="C240" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -5029,10 +5029,10 @@
         <v>21</v>
       </c>
       <c r="B241" s="8">
-        <v>46098</v>
+        <v>46108</v>
       </c>
       <c r="C241" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -5040,10 +5040,10 @@
         <v>21</v>
       </c>
       <c r="B242" s="5">
-        <v>46113</v>
+        <v>46098</v>
       </c>
       <c r="C242" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -5051,7 +5051,7 @@
         <v>21</v>
       </c>
       <c r="B243" s="8">
-        <v>46142</v>
+        <v>46113</v>
       </c>
       <c r="C243" s="9">
         <v>1</v>
@@ -5062,7 +5062,7 @@
         <v>21</v>
       </c>
       <c r="B244" s="5">
-        <v>46153</v>
+        <v>46142</v>
       </c>
       <c r="C244" s="6">
         <v>1</v>
@@ -5073,7 +5073,7 @@
         <v>21</v>
       </c>
       <c r="B245" s="8">
-        <v>46031</v>
+        <v>46153</v>
       </c>
       <c r="C245" s="9">
         <v>1</v>
@@ -5084,9 +5084,20 @@
         <v>21</v>
       </c>
       <c r="B246" s="5">
+        <v>46031</v>
+      </c>
+      <c r="C246" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B247" s="8">
         <v>46155</v>
       </c>
-      <c r="C246" s="6">
+      <c r="C247" s="9">
         <v>1</v>
       </c>
     </row>
@@ -5153,7 +5164,7 @@
         <v>4</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -5187,7 +5198,7 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -5391,7 +5402,7 @@
         <v>3</v>
       </c>
       <c r="E17">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -5640,7 +5651,7 @@
         <v>17</v>
       </c>
       <c r="C32">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D32">
         <v>248</v>
@@ -5663,7 +5674,7 @@
         <v>8</v>
       </c>
       <c r="E33">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -5714,7 +5725,7 @@
         <v>87</v>
       </c>
       <c r="E36">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -5742,7 +5753,7 @@
         <v>19</v>
       </c>
       <c r="C38">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D38">
         <v>10</v>
@@ -6220,7 +6231,7 @@
         <v>80</v>
       </c>
       <c r="C40">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -7870,7 +7881,7 @@
         <v>193</v>
       </c>
       <c r="C190">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -8912,7 +8923,7 @@
         <v>21</v>
       </c>
       <c r="B285" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C285">
         <v>5</v>
@@ -8923,7 +8934,7 @@
         <v>21</v>
       </c>
       <c r="B286" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C286">
         <v>5</v>
@@ -8934,7 +8945,7 @@
         <v>21</v>
       </c>
       <c r="B287" t="s">
-        <v>248</v>
+        <v>101</v>
       </c>
       <c r="C287">
         <v>4</v>
@@ -8956,7 +8967,7 @@
         <v>21</v>
       </c>
       <c r="B289" t="s">
-        <v>101</v>
+        <v>248</v>
       </c>
       <c r="C289">
         <v>4</v>
@@ -8967,10 +8978,10 @@
         <v>21</v>
       </c>
       <c r="B290" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="C290">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -8978,7 +8989,7 @@
         <v>21</v>
       </c>
       <c r="B291" t="s">
-        <v>127</v>
+        <v>249</v>
       </c>
       <c r="C291">
         <v>3</v>
@@ -8989,7 +9000,7 @@
         <v>21</v>
       </c>
       <c r="B292" t="s">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="C292">
         <v>3</v>
@@ -9000,7 +9011,7 @@
         <v>21</v>
       </c>
       <c r="B293" t="s">
-        <v>249</v>
+        <v>196</v>
       </c>
       <c r="C293">
         <v>3</v>
@@ -9011,7 +9022,7 @@
         <v>21</v>
       </c>
       <c r="B294" t="s">
-        <v>163</v>
+        <v>127</v>
       </c>
       <c r="C294">
         <v>3</v>
@@ -9022,7 +9033,7 @@
         <v>21</v>
       </c>
       <c r="B295" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C295">
         <v>3</v>
@@ -9044,7 +9055,7 @@
         <v>21</v>
       </c>
       <c r="B297" t="s">
-        <v>44</v>
+        <v>163</v>
       </c>
       <c r="C297">
         <v>3</v>
@@ -9055,7 +9066,7 @@
         <v>21</v>
       </c>
       <c r="B298" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C298">
         <v>3</v>
@@ -9066,7 +9077,7 @@
         <v>21</v>
       </c>
       <c r="B299" t="s">
-        <v>126</v>
+        <v>44</v>
       </c>
       <c r="C299">
         <v>3</v>
@@ -9077,7 +9088,7 @@
         <v>21</v>
       </c>
       <c r="B300" t="s">
-        <v>196</v>
+        <v>133</v>
       </c>
       <c r="C300">
         <v>3</v>
@@ -9088,7 +9099,7 @@
         <v>21</v>
       </c>
       <c r="B301" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
       <c r="C301">
         <v>2</v>
@@ -9099,7 +9110,7 @@
         <v>21</v>
       </c>
       <c r="B302" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="C302">
         <v>2</v>
@@ -9110,7 +9121,7 @@
         <v>21</v>
       </c>
       <c r="B303" t="s">
-        <v>271</v>
+        <v>136</v>
       </c>
       <c r="C303">
         <v>2</v>
@@ -9121,7 +9132,7 @@
         <v>21</v>
       </c>
       <c r="B304" t="s">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="C304">
         <v>2</v>
@@ -9132,7 +9143,7 @@
         <v>21</v>
       </c>
       <c r="B305" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C305">
         <v>2</v>
@@ -9143,7 +9154,7 @@
         <v>21</v>
       </c>
       <c r="B306" t="s">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="C306">
         <v>2</v>
@@ -9154,7 +9165,7 @@
         <v>21</v>
       </c>
       <c r="B307" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C307">
         <v>2</v>
@@ -9176,7 +9187,7 @@
         <v>21</v>
       </c>
       <c r="B309" t="s">
-        <v>255</v>
+        <v>54</v>
       </c>
       <c r="C309">
         <v>2</v>
@@ -9187,7 +9198,7 @@
         <v>21</v>
       </c>
       <c r="B310" t="s">
-        <v>173</v>
+        <v>85</v>
       </c>
       <c r="C310">
         <v>2</v>
@@ -9198,7 +9209,7 @@
         <v>21</v>
       </c>
       <c r="B311" t="s">
-        <v>85</v>
+        <v>271</v>
       </c>
       <c r="C311">
         <v>2</v>
@@ -9209,7 +9220,7 @@
         <v>21</v>
       </c>
       <c r="B312" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="C312">
         <v>2</v>
@@ -9220,7 +9231,7 @@
         <v>21</v>
       </c>
       <c r="B313" t="s">
-        <v>254</v>
+        <v>198</v>
       </c>
       <c r="C313">
         <v>2</v>
@@ -9231,7 +9242,7 @@
         <v>21</v>
       </c>
       <c r="B314" t="s">
-        <v>54</v>
+        <v>254</v>
       </c>
       <c r="C314">
         <v>2</v>
@@ -9264,7 +9275,7 @@
         <v>21</v>
       </c>
       <c r="B317" t="s">
-        <v>70</v>
+        <v>250</v>
       </c>
       <c r="C317">
         <v>2</v>
@@ -9275,7 +9286,7 @@
         <v>21</v>
       </c>
       <c r="B318" t="s">
-        <v>63</v>
+        <v>281</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -9286,7 +9297,7 @@
         <v>21</v>
       </c>
       <c r="B319" t="s">
-        <v>214</v>
+        <v>138</v>
       </c>
       <c r="C319">
         <v>1</v>
@@ -9308,7 +9319,7 @@
         <v>21</v>
       </c>
       <c r="B321" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="C321">
         <v>1</v>
@@ -9330,7 +9341,7 @@
         <v>21</v>
       </c>
       <c r="B323" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="C323">
         <v>1</v>
@@ -9341,7 +9352,7 @@
         <v>21</v>
       </c>
       <c r="B324" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="C324">
         <v>1</v>
@@ -9352,7 +9363,7 @@
         <v>21</v>
       </c>
       <c r="B325" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -9363,7 +9374,7 @@
         <v>21</v>
       </c>
       <c r="B326" t="s">
-        <v>137</v>
+        <v>172</v>
       </c>
       <c r="C326">
         <v>1</v>
@@ -9374,7 +9385,7 @@
         <v>21</v>
       </c>
       <c r="B327" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="C327">
         <v>1</v>
@@ -9385,7 +9396,7 @@
         <v>21</v>
       </c>
       <c r="B328" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="C328">
         <v>1</v>
@@ -9396,7 +9407,7 @@
         <v>21</v>
       </c>
       <c r="B329" t="s">
-        <v>267</v>
+        <v>137</v>
       </c>
       <c r="C329">
         <v>1</v>
@@ -9407,7 +9418,7 @@
         <v>21</v>
       </c>
       <c r="B330" t="s">
-        <v>125</v>
+        <v>280</v>
       </c>
       <c r="C330">
         <v>1</v>
@@ -9418,7 +9429,7 @@
         <v>21</v>
       </c>
       <c r="B331" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="C331">
         <v>1</v>
@@ -9451,7 +9462,7 @@
         <v>21</v>
       </c>
       <c r="B334" t="s">
-        <v>165</v>
+        <v>264</v>
       </c>
       <c r="C334">
         <v>1</v>
@@ -9462,7 +9473,7 @@
         <v>21</v>
       </c>
       <c r="B335" t="s">
-        <v>49</v>
+        <v>148</v>
       </c>
       <c r="C335">
         <v>1</v>
@@ -9473,7 +9484,7 @@
         <v>21</v>
       </c>
       <c r="B336" t="s">
-        <v>115</v>
+        <v>49</v>
       </c>
       <c r="C336">
         <v>1</v>
@@ -9484,7 +9495,7 @@
         <v>21</v>
       </c>
       <c r="B337" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="C337">
         <v>1</v>
@@ -9495,7 +9506,7 @@
         <v>21</v>
       </c>
       <c r="B338" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="C338">
         <v>1</v>
@@ -9550,7 +9561,7 @@
         <v>21</v>
       </c>
       <c r="B343" t="s">
-        <v>272</v>
+        <v>214</v>
       </c>
       <c r="C343">
         <v>1</v>
@@ -9561,7 +9572,7 @@
         <v>21</v>
       </c>
       <c r="B344" t="s">
-        <v>172</v>
+        <v>125</v>
       </c>
       <c r="C344">
         <v>1</v>
@@ -9594,7 +9605,7 @@
         <v>21</v>
       </c>
       <c r="B347" t="s">
-        <v>276</v>
+        <v>92</v>
       </c>
       <c r="C347">
         <v>1</v>
@@ -9605,7 +9616,7 @@
         <v>21</v>
       </c>
       <c r="B348" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="C348">
         <v>1</v>
@@ -9627,7 +9638,7 @@
         <v>21</v>
       </c>
       <c r="B350" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="C350">
         <v>1</v>
@@ -9638,7 +9649,7 @@
         <v>21</v>
       </c>
       <c r="B351" t="s">
-        <v>281</v>
+        <v>260</v>
       </c>
       <c r="C351">
         <v>1</v>
@@ -9660,7 +9671,7 @@
         <v>21</v>
       </c>
       <c r="B353" t="s">
-        <v>282</v>
+        <v>263</v>
       </c>
       <c r="C353">
         <v>1</v>
@@ -9720,7 +9731,7 @@
         <v>287</v>
       </c>
       <c r="C3">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -9731,7 +9742,7 @@
         <v>288</v>
       </c>
       <c r="C4">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -9830,7 +9841,7 @@
         <v>290</v>
       </c>
       <c r="C13">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -9962,7 +9973,7 @@
         <v>287</v>
       </c>
       <c r="C25">
-        <v>876</v>
+        <v>878</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -9995,7 +10006,7 @@
         <v>288</v>
       </c>
       <c r="C28">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -10061,7 +10072,7 @@
         <v>290</v>
       </c>
       <c r="C34">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="164" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F7610F2-617E-4FA8-BA0B-F94CF87C6183}"/>
+  <xr:revisionPtr revIDLastSave="179" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC55ECF7-3F82-4AF5-BAE6-62D195D4A831}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" tabRatio="731" firstSheet="1" activeTab="7" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" tabRatio="731" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="mat_2026" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1321" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1321" uniqueCount="299">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -710,9 +710,6 @@
   </si>
   <si>
     <t>Liceo Polivalente Rigoberto Fontt</t>
-  </si>
-  <si>
-    <t>Colegio Dalmacia</t>
   </si>
   <si>
     <t>Colegio Chillán</t>
@@ -1923,10 +1920,10 @@
         <v>138</v>
       </c>
       <c r="D31">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E31">
-        <v>1.0509999999999999</v>
+        <v>1.0580000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1940,10 +1937,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E32">
-        <v>1.0629999999999999</v>
+        <v>1.0609999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2311,7 +2308,7 @@
         <v>35</v>
       </c>
       <c r="C6">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2344,7 +2341,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2376,7 +2373,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD19485A-0629-47F9-A5AD-80ABA7A6E076}">
-  <dimension ref="A1:C247"/>
+  <dimension ref="A1:C249"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -2425,7 +2422,7 @@
         <v>46000</v>
       </c>
       <c r="C4" s="6">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2491,7 +2488,7 @@
         <v>46007</v>
       </c>
       <c r="C10" s="6">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -2730,10 +2727,10 @@
         <v>16</v>
       </c>
       <c r="B32" s="5">
-        <v>46084</v>
+        <v>46181</v>
       </c>
       <c r="C32" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -2741,10 +2738,10 @@
         <v>16</v>
       </c>
       <c r="B33" s="8">
-        <v>46160</v>
+        <v>46084</v>
       </c>
       <c r="C33" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -2752,10 +2749,10 @@
         <v>16</v>
       </c>
       <c r="B34" s="5">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="C34" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -2763,10 +2760,10 @@
         <v>16</v>
       </c>
       <c r="B35" s="8">
-        <v>46099</v>
+        <v>46167</v>
       </c>
       <c r="C35" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -2774,10 +2771,10 @@
         <v>16</v>
       </c>
       <c r="B36" s="5">
-        <v>46128</v>
+        <v>46099</v>
       </c>
       <c r="C36" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -2785,10 +2782,10 @@
         <v>16</v>
       </c>
       <c r="B37" s="8">
-        <v>46141</v>
+        <v>46128</v>
       </c>
       <c r="C37" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -2796,10 +2793,10 @@
         <v>16</v>
       </c>
       <c r="B38" s="5">
-        <v>46132</v>
+        <v>46141</v>
       </c>
       <c r="C38" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -2807,10 +2804,10 @@
         <v>16</v>
       </c>
       <c r="B39" s="8">
-        <v>46127</v>
+        <v>46132</v>
       </c>
       <c r="C39" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -2818,7 +2815,7 @@
         <v>16</v>
       </c>
       <c r="B40" s="5">
-        <v>46091</v>
+        <v>46127</v>
       </c>
       <c r="C40" s="6">
         <v>2</v>
@@ -2829,10 +2826,10 @@
         <v>16</v>
       </c>
       <c r="B41" s="8">
-        <v>46104</v>
+        <v>46091</v>
       </c>
       <c r="C41" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -2840,7 +2837,7 @@
         <v>16</v>
       </c>
       <c r="B42" s="5">
-        <v>46140</v>
+        <v>46104</v>
       </c>
       <c r="C42" s="6">
         <v>1</v>
@@ -2851,7 +2848,7 @@
         <v>16</v>
       </c>
       <c r="B43" s="8">
-        <v>46106</v>
+        <v>46140</v>
       </c>
       <c r="C43" s="9">
         <v>1</v>
@@ -2862,7 +2859,7 @@
         <v>16</v>
       </c>
       <c r="B44" s="5">
-        <v>46113</v>
+        <v>46106</v>
       </c>
       <c r="C44" s="6">
         <v>1</v>
@@ -2873,10 +2870,10 @@
         <v>16</v>
       </c>
       <c r="B45" s="8">
-        <v>46090</v>
+        <v>46113</v>
       </c>
       <c r="C45" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -2884,10 +2881,10 @@
         <v>16</v>
       </c>
       <c r="B46" s="5">
-        <v>46139</v>
+        <v>46090</v>
       </c>
       <c r="C46" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -2895,7 +2892,7 @@
         <v>16</v>
       </c>
       <c r="B47" s="8">
-        <v>46148</v>
+        <v>46139</v>
       </c>
       <c r="C47" s="9">
         <v>1</v>
@@ -2906,7 +2903,7 @@
         <v>16</v>
       </c>
       <c r="B48" s="5">
-        <v>46175</v>
+        <v>46148</v>
       </c>
       <c r="C48" s="6">
         <v>1</v>
@@ -2917,7 +2914,7 @@
         <v>16</v>
       </c>
       <c r="B49" s="8">
-        <v>46125</v>
+        <v>46175</v>
       </c>
       <c r="C49" s="9">
         <v>1</v>
@@ -2928,7 +2925,7 @@
         <v>16</v>
       </c>
       <c r="B50" s="5">
-        <v>46093</v>
+        <v>46125</v>
       </c>
       <c r="C50" s="6">
         <v>1</v>
@@ -2939,10 +2936,10 @@
         <v>16</v>
       </c>
       <c r="B51" s="8">
-        <v>46177</v>
+        <v>46093</v>
       </c>
       <c r="C51" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -2950,10 +2947,10 @@
         <v>16</v>
       </c>
       <c r="B52" s="5">
-        <v>46156</v>
+        <v>46177</v>
       </c>
       <c r="C52" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -2961,7 +2958,7 @@
         <v>16</v>
       </c>
       <c r="B53" s="8">
-        <v>46092</v>
+        <v>46156</v>
       </c>
       <c r="C53" s="9">
         <v>1</v>
@@ -2972,7 +2969,7 @@
         <v>16</v>
       </c>
       <c r="B54" s="5">
-        <v>46101</v>
+        <v>46092</v>
       </c>
       <c r="C54" s="6">
         <v>1</v>
@@ -2980,13 +2977,13 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B55" s="8">
-        <v>46007</v>
+        <v>46101</v>
       </c>
       <c r="C55" s="9">
-        <v>78</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -2994,10 +2991,10 @@
         <v>14</v>
       </c>
       <c r="B56" s="5">
-        <v>46009</v>
+        <v>46007</v>
       </c>
       <c r="C56" s="6">
-        <v>34</v>
+        <v>78</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -3005,10 +3002,10 @@
         <v>14</v>
       </c>
       <c r="B57" s="8">
-        <v>46000</v>
+        <v>46009</v>
       </c>
       <c r="C57" s="9">
-        <v>80</v>
+        <v>34</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -3016,10 +3013,10 @@
         <v>14</v>
       </c>
       <c r="B58" s="5">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C58" s="6">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -3027,10 +3024,10 @@
         <v>14</v>
       </c>
       <c r="B59" s="8">
-        <v>46006</v>
+        <v>46001</v>
       </c>
       <c r="C59" s="9">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -3038,10 +3035,10 @@
         <v>14</v>
       </c>
       <c r="B60" s="5">
-        <v>46010</v>
+        <v>46006</v>
       </c>
       <c r="C60" s="6">
-        <v>24</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -3049,10 +3046,10 @@
         <v>14</v>
       </c>
       <c r="B61" s="8">
-        <v>46014</v>
+        <v>46010</v>
       </c>
       <c r="C61" s="9">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -3060,10 +3057,10 @@
         <v>14</v>
       </c>
       <c r="B62" s="5">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="C62" s="6">
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -3071,10 +3068,10 @@
         <v>14</v>
       </c>
       <c r="B63" s="8">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C63" s="9">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -3082,10 +3079,10 @@
         <v>14</v>
       </c>
       <c r="B64" s="5">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="C64" s="6">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -3093,10 +3090,10 @@
         <v>14</v>
       </c>
       <c r="B65" s="8">
-        <v>46013</v>
+        <v>46003</v>
       </c>
       <c r="C65" s="9">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -3104,10 +3101,10 @@
         <v>14</v>
       </c>
       <c r="B66" s="5">
-        <v>46022</v>
+        <v>46013</v>
       </c>
       <c r="C66" s="6">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -3115,10 +3112,10 @@
         <v>14</v>
       </c>
       <c r="B67" s="8">
-        <v>46080</v>
+        <v>46022</v>
       </c>
       <c r="C67" s="9">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -3126,10 +3123,10 @@
         <v>14</v>
       </c>
       <c r="B68" s="5">
-        <v>46084</v>
+        <v>46080</v>
       </c>
       <c r="C68" s="6">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -3137,10 +3134,10 @@
         <v>14</v>
       </c>
       <c r="B69" s="8">
-        <v>46125</v>
+        <v>46084</v>
       </c>
       <c r="C69" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -3148,10 +3145,10 @@
         <v>14</v>
       </c>
       <c r="B70" s="5">
-        <v>46091</v>
+        <v>46125</v>
       </c>
       <c r="C70" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -3159,10 +3156,10 @@
         <v>14</v>
       </c>
       <c r="B71" s="8">
-        <v>46083</v>
+        <v>46091</v>
       </c>
       <c r="C71" s="9">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -3170,10 +3167,10 @@
         <v>14</v>
       </c>
       <c r="B72" s="5">
-        <v>46105</v>
+        <v>46083</v>
       </c>
       <c r="C72" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -3181,10 +3178,10 @@
         <v>14</v>
       </c>
       <c r="B73" s="8">
-        <v>46077</v>
+        <v>46105</v>
       </c>
       <c r="C73" s="9">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -3192,10 +3189,10 @@
         <v>14</v>
       </c>
       <c r="B74" s="5">
-        <v>46118</v>
+        <v>46077</v>
       </c>
       <c r="C74" s="6">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -3203,10 +3200,10 @@
         <v>14</v>
       </c>
       <c r="B75" s="8">
-        <v>46078</v>
+        <v>46118</v>
       </c>
       <c r="C75" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -3214,10 +3211,10 @@
         <v>14</v>
       </c>
       <c r="B76" s="5">
-        <v>46099</v>
+        <v>46078</v>
       </c>
       <c r="C76" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -3225,10 +3222,10 @@
         <v>14</v>
       </c>
       <c r="B77" s="8">
-        <v>46104</v>
+        <v>46099</v>
       </c>
       <c r="C77" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -3236,10 +3233,10 @@
         <v>14</v>
       </c>
       <c r="B78" s="5">
-        <v>46107</v>
+        <v>46104</v>
       </c>
       <c r="C78" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -3247,7 +3244,7 @@
         <v>14</v>
       </c>
       <c r="B79" s="8">
-        <v>46020</v>
+        <v>46107</v>
       </c>
       <c r="C79" s="9">
         <v>2</v>
@@ -3258,10 +3255,10 @@
         <v>14</v>
       </c>
       <c r="B80" s="5">
-        <v>46076</v>
+        <v>46020</v>
       </c>
       <c r="C80" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -3269,10 +3266,10 @@
         <v>14</v>
       </c>
       <c r="B81" s="8">
-        <v>46111</v>
+        <v>46076</v>
       </c>
       <c r="C81" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -3280,10 +3277,10 @@
         <v>14</v>
       </c>
       <c r="B82" s="5">
-        <v>46087</v>
+        <v>46111</v>
       </c>
       <c r="C82" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -3291,7 +3288,7 @@
         <v>14</v>
       </c>
       <c r="B83" s="8">
-        <v>46140</v>
+        <v>46087</v>
       </c>
       <c r="C83" s="9">
         <v>2</v>
@@ -3302,10 +3299,10 @@
         <v>14</v>
       </c>
       <c r="B84" s="5">
-        <v>46113</v>
+        <v>46140</v>
       </c>
       <c r="C84" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -3313,10 +3310,10 @@
         <v>14</v>
       </c>
       <c r="B85" s="8">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="C85" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -3324,10 +3321,10 @@
         <v>14</v>
       </c>
       <c r="B86" s="5">
-        <v>46108</v>
+        <v>46119</v>
       </c>
       <c r="C86" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -3335,7 +3332,7 @@
         <v>14</v>
       </c>
       <c r="B87" s="8">
-        <v>46098</v>
+        <v>46108</v>
       </c>
       <c r="C87" s="9">
         <v>1</v>
@@ -3346,7 +3343,7 @@
         <v>14</v>
       </c>
       <c r="B88" s="5">
-        <v>46141</v>
+        <v>46098</v>
       </c>
       <c r="C88" s="6">
         <v>1</v>
@@ -3357,7 +3354,7 @@
         <v>14</v>
       </c>
       <c r="B89" s="8">
-        <v>46114</v>
+        <v>46141</v>
       </c>
       <c r="C89" s="9">
         <v>1</v>
@@ -3368,10 +3365,10 @@
         <v>14</v>
       </c>
       <c r="B90" s="5">
-        <v>46079</v>
+        <v>46114</v>
       </c>
       <c r="C90" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -3379,10 +3376,10 @@
         <v>14</v>
       </c>
       <c r="B91" s="8">
-        <v>46139</v>
+        <v>46079</v>
       </c>
       <c r="C91" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -3390,10 +3387,10 @@
         <v>14</v>
       </c>
       <c r="B92" s="5">
-        <v>46148</v>
+        <v>46139</v>
       </c>
       <c r="C92" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -3401,10 +3398,10 @@
         <v>14</v>
       </c>
       <c r="B93" s="8">
-        <v>46092</v>
+        <v>46148</v>
       </c>
       <c r="C93" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -3412,10 +3409,10 @@
         <v>14</v>
       </c>
       <c r="B94" s="5">
-        <v>46021</v>
+        <v>46092</v>
       </c>
       <c r="C94" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -3423,10 +3420,10 @@
         <v>14</v>
       </c>
       <c r="B95" s="8">
-        <v>46086</v>
+        <v>46021</v>
       </c>
       <c r="C95" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -3434,10 +3431,10 @@
         <v>14</v>
       </c>
       <c r="B96" s="5">
-        <v>46147</v>
+        <v>46086</v>
       </c>
       <c r="C96" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -3445,7 +3442,7 @@
         <v>14</v>
       </c>
       <c r="B97" s="8">
-        <v>46134</v>
+        <v>46147</v>
       </c>
       <c r="C97" s="9">
         <v>1</v>
@@ -3453,13 +3450,13 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B98" s="5">
-        <v>46003</v>
+        <v>46134</v>
       </c>
       <c r="C98" s="6">
-        <v>95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -3467,10 +3464,10 @@
         <v>3</v>
       </c>
       <c r="B99" s="8">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="C99" s="9">
-        <v>115</v>
+        <v>95</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -3478,10 +3475,10 @@
         <v>3</v>
       </c>
       <c r="B100" s="5">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C100" s="6">
-        <v>15</v>
+        <v>115</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -3489,10 +3486,10 @@
         <v>3</v>
       </c>
       <c r="B101" s="8">
-        <v>46000</v>
+        <v>46008</v>
       </c>
       <c r="C101" s="9">
-        <v>98</v>
+        <v>15</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -3500,10 +3497,10 @@
         <v>3</v>
       </c>
       <c r="B102" s="5">
-        <v>46007</v>
+        <v>46000</v>
       </c>
       <c r="C102" s="6">
-        <v>40</v>
+        <v>98</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -3511,10 +3508,10 @@
         <v>3</v>
       </c>
       <c r="B103" s="8">
-        <v>46001</v>
+        <v>46007</v>
       </c>
       <c r="C103" s="9">
-        <v>91</v>
+        <v>40</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -3522,10 +3519,10 @@
         <v>3</v>
       </c>
       <c r="B104" s="5">
-        <v>46010</v>
+        <v>46001</v>
       </c>
       <c r="C104" s="6">
-        <v>9</v>
+        <v>91</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -3533,10 +3530,10 @@
         <v>3</v>
       </c>
       <c r="B105" s="8">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="C105" s="9">
-        <v>84</v>
+        <v>9</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -3544,10 +3541,10 @@
         <v>3</v>
       </c>
       <c r="B106" s="5">
-        <v>46009</v>
+        <v>46006</v>
       </c>
       <c r="C106" s="6">
-        <v>2</v>
+        <v>84</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -3555,10 +3552,10 @@
         <v>3</v>
       </c>
       <c r="B107" s="8">
-        <v>46015</v>
+        <v>46009</v>
       </c>
       <c r="C107" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -3566,10 +3563,10 @@
         <v>3</v>
       </c>
       <c r="B108" s="5">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="C108" s="6">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -3577,10 +3574,10 @@
         <v>3</v>
       </c>
       <c r="B109" s="8">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="C109" s="9">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -3588,10 +3585,10 @@
         <v>3</v>
       </c>
       <c r="B110" s="5">
-        <v>46021</v>
+        <v>46013</v>
       </c>
       <c r="C110" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -3599,10 +3596,10 @@
         <v>3</v>
       </c>
       <c r="B111" s="8">
-        <v>46077</v>
+        <v>46021</v>
       </c>
       <c r="C111" s="9">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -3610,10 +3607,10 @@
         <v>3</v>
       </c>
       <c r="B112" s="5">
-        <v>46167</v>
+        <v>46077</v>
       </c>
       <c r="C112" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -3621,10 +3618,10 @@
         <v>3</v>
       </c>
       <c r="B113" s="8">
-        <v>46090</v>
+        <v>46167</v>
       </c>
       <c r="C113" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -3632,10 +3629,10 @@
         <v>3</v>
       </c>
       <c r="B114" s="5">
-        <v>46170</v>
+        <v>46090</v>
       </c>
       <c r="C114" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -3643,7 +3640,7 @@
         <v>3</v>
       </c>
       <c r="B115" s="8">
-        <v>46093</v>
+        <v>46170</v>
       </c>
       <c r="C115" s="9">
         <v>1</v>
@@ -3654,10 +3651,10 @@
         <v>3</v>
       </c>
       <c r="B116" s="5">
-        <v>46078</v>
+        <v>46093</v>
       </c>
       <c r="C116" s="6">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -3665,7 +3662,7 @@
         <v>3</v>
       </c>
       <c r="B117" s="8">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="C117" s="9">
         <v>7</v>
@@ -3676,10 +3673,10 @@
         <v>3</v>
       </c>
       <c r="B118" s="5">
-        <v>46134</v>
+        <v>46084</v>
       </c>
       <c r="C118" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -3687,10 +3684,10 @@
         <v>3</v>
       </c>
       <c r="B119" s="8">
-        <v>46083</v>
+        <v>46134</v>
       </c>
       <c r="C119" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -3698,10 +3695,10 @@
         <v>3</v>
       </c>
       <c r="B120" s="5">
-        <v>46022</v>
+        <v>46083</v>
       </c>
       <c r="C120" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -3709,10 +3706,10 @@
         <v>3</v>
       </c>
       <c r="B121" s="8">
-        <v>46114</v>
+        <v>46022</v>
       </c>
       <c r="C121" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -3720,10 +3717,10 @@
         <v>3</v>
       </c>
       <c r="B122" s="5">
-        <v>46135</v>
+        <v>46114</v>
       </c>
       <c r="C122" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -3731,10 +3728,10 @@
         <v>3</v>
       </c>
       <c r="B123" s="8">
-        <v>46168</v>
+        <v>46135</v>
       </c>
       <c r="C123" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -3742,7 +3739,7 @@
         <v>3</v>
       </c>
       <c r="B124" s="5">
-        <v>46126</v>
+        <v>46168</v>
       </c>
       <c r="C124" s="6">
         <v>3</v>
@@ -3753,7 +3750,7 @@
         <v>3</v>
       </c>
       <c r="B125" s="8">
-        <v>46120</v>
+        <v>46126</v>
       </c>
       <c r="C125" s="9">
         <v>3</v>
@@ -3764,10 +3761,10 @@
         <v>3</v>
       </c>
       <c r="B126" s="5">
-        <v>46127</v>
+        <v>46120</v>
       </c>
       <c r="C126" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -3775,7 +3772,7 @@
         <v>3</v>
       </c>
       <c r="B127" s="8">
-        <v>46087</v>
+        <v>46127</v>
       </c>
       <c r="C127" s="9">
         <v>1</v>
@@ -3786,7 +3783,7 @@
         <v>3</v>
       </c>
       <c r="B128" s="5">
-        <v>46108</v>
+        <v>46087</v>
       </c>
       <c r="C128" s="6">
         <v>1</v>
@@ -3797,7 +3794,7 @@
         <v>3</v>
       </c>
       <c r="B129" s="8">
-        <v>46020</v>
+        <v>46108</v>
       </c>
       <c r="C129" s="9">
         <v>1</v>
@@ -3808,7 +3805,7 @@
         <v>3</v>
       </c>
       <c r="B130" s="5">
-        <v>46097</v>
+        <v>46020</v>
       </c>
       <c r="C130" s="6">
         <v>1</v>
@@ -3819,7 +3816,7 @@
         <v>3</v>
       </c>
       <c r="B131" s="8">
-        <v>46177</v>
+        <v>46097</v>
       </c>
       <c r="C131" s="9">
         <v>1</v>
@@ -3830,10 +3827,10 @@
         <v>3</v>
       </c>
       <c r="B132" s="5">
-        <v>46161</v>
+        <v>46177</v>
       </c>
       <c r="C132" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -3841,10 +3838,10 @@
         <v>3</v>
       </c>
       <c r="B133" s="8">
-        <v>46129</v>
+        <v>46161</v>
       </c>
       <c r="C133" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -3852,7 +3849,7 @@
         <v>3</v>
       </c>
       <c r="B134" s="5">
-        <v>46080</v>
+        <v>46129</v>
       </c>
       <c r="C134" s="6">
         <v>1</v>
@@ -3863,7 +3860,7 @@
         <v>3</v>
       </c>
       <c r="B135" s="8">
-        <v>46101</v>
+        <v>46080</v>
       </c>
       <c r="C135" s="9">
         <v>1</v>
@@ -3874,7 +3871,7 @@
         <v>3</v>
       </c>
       <c r="B136" s="5">
-        <v>46155</v>
+        <v>46101</v>
       </c>
       <c r="C136" s="6">
         <v>1</v>
@@ -3885,7 +3882,7 @@
         <v>3</v>
       </c>
       <c r="B137" s="8">
-        <v>46150</v>
+        <v>46155</v>
       </c>
       <c r="C137" s="9">
         <v>1</v>
@@ -3896,7 +3893,7 @@
         <v>3</v>
       </c>
       <c r="B138" s="5">
-        <v>46141</v>
+        <v>46150</v>
       </c>
       <c r="C138" s="6">
         <v>1</v>
@@ -3907,7 +3904,7 @@
         <v>3</v>
       </c>
       <c r="B139" s="8">
-        <v>46085</v>
+        <v>46141</v>
       </c>
       <c r="C139" s="9">
         <v>1</v>
@@ -3918,7 +3915,7 @@
         <v>3</v>
       </c>
       <c r="B140" s="5">
-        <v>46148</v>
+        <v>46085</v>
       </c>
       <c r="C140" s="6">
         <v>1</v>
@@ -3929,10 +3926,10 @@
         <v>3</v>
       </c>
       <c r="B141" s="8">
-        <v>46118</v>
+        <v>46148</v>
       </c>
       <c r="C141" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -3940,21 +3937,21 @@
         <v>3</v>
       </c>
       <c r="B142" s="5">
-        <v>46079</v>
+        <v>46118</v>
       </c>
       <c r="C142" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B143" s="8">
-        <v>46003</v>
+        <v>46079</v>
       </c>
       <c r="C143" s="9">
-        <v>92</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -3962,10 +3959,10 @@
         <v>15</v>
       </c>
       <c r="B144" s="5">
-        <v>46000</v>
+        <v>46003</v>
       </c>
       <c r="C144" s="6">
-        <v>132</v>
+        <v>92</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -3973,10 +3970,10 @@
         <v>15</v>
       </c>
       <c r="B145" s="8">
-        <v>46006</v>
+        <v>46000</v>
       </c>
       <c r="C145" s="9">
-        <v>173</v>
+        <v>132</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -3984,10 +3981,10 @@
         <v>15</v>
       </c>
       <c r="B146" s="5">
-        <v>46001</v>
+        <v>46006</v>
       </c>
       <c r="C146" s="6">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -3995,10 +3992,10 @@
         <v>15</v>
       </c>
       <c r="B147" s="8">
-        <v>46014</v>
+        <v>46001</v>
       </c>
       <c r="C147" s="9">
-        <v>16</v>
+        <v>174</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -4006,10 +4003,10 @@
         <v>15</v>
       </c>
       <c r="B148" s="5">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="C148" s="6">
-        <v>171</v>
+        <v>16</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -4017,10 +4014,10 @@
         <v>15</v>
       </c>
       <c r="B149" s="8">
-        <v>46009</v>
+        <v>46002</v>
       </c>
       <c r="C149" s="9">
-        <v>19</v>
+        <v>171</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -4028,7 +4025,7 @@
         <v>15</v>
       </c>
       <c r="B150" s="5">
-        <v>46010</v>
+        <v>46009</v>
       </c>
       <c r="C150" s="6">
         <v>19</v>
@@ -4039,10 +4036,10 @@
         <v>15</v>
       </c>
       <c r="B151" s="8">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="C151" s="9">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -4050,10 +4047,10 @@
         <v>15</v>
       </c>
       <c r="B152" s="5">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="C152" s="6">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -4061,10 +4058,10 @@
         <v>15</v>
       </c>
       <c r="B153" s="8">
-        <v>46013</v>
+        <v>46007</v>
       </c>
       <c r="C153" s="9">
-        <v>12</v>
+        <v>43</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -4072,10 +4069,10 @@
         <v>15</v>
       </c>
       <c r="B154" s="5">
-        <v>46080</v>
+        <v>46013</v>
       </c>
       <c r="C154" s="6">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -4083,10 +4080,10 @@
         <v>15</v>
       </c>
       <c r="B155" s="8">
-        <v>46090</v>
+        <v>46080</v>
       </c>
       <c r="C155" s="9">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -4094,10 +4091,10 @@
         <v>15</v>
       </c>
       <c r="B156" s="5">
-        <v>46079</v>
+        <v>46090</v>
       </c>
       <c r="C156" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -4105,10 +4102,10 @@
         <v>15</v>
       </c>
       <c r="B157" s="8">
-        <v>46015</v>
+        <v>46079</v>
       </c>
       <c r="C157" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -4116,10 +4113,10 @@
         <v>15</v>
       </c>
       <c r="B158" s="5">
-        <v>46085</v>
+        <v>46015</v>
       </c>
       <c r="C158" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -4127,10 +4124,10 @@
         <v>15</v>
       </c>
       <c r="B159" s="8">
-        <v>46098</v>
+        <v>46085</v>
       </c>
       <c r="C159" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -4138,10 +4135,10 @@
         <v>15</v>
       </c>
       <c r="B160" s="5">
-        <v>46021</v>
+        <v>46098</v>
       </c>
       <c r="C160" s="6">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -4149,10 +4146,10 @@
         <v>15</v>
       </c>
       <c r="B161" s="8">
-        <v>46078</v>
+        <v>46021</v>
       </c>
       <c r="C161" s="9">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -4160,10 +4157,10 @@
         <v>15</v>
       </c>
       <c r="B162" s="5">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="C162" s="6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -4171,10 +4168,10 @@
         <v>15</v>
       </c>
       <c r="B163" s="8">
-        <v>46128</v>
+        <v>46084</v>
       </c>
       <c r="C163" s="9">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -4182,10 +4179,10 @@
         <v>15</v>
       </c>
       <c r="B164" s="5">
-        <v>46083</v>
+        <v>46128</v>
       </c>
       <c r="C164" s="6">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -4193,10 +4190,10 @@
         <v>15</v>
       </c>
       <c r="B165" s="8">
-        <v>46153</v>
+        <v>46083</v>
       </c>
       <c r="C165" s="9">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -4204,10 +4201,10 @@
         <v>15</v>
       </c>
       <c r="B166" s="5">
-        <v>46076</v>
+        <v>46153</v>
       </c>
       <c r="C166" s="6">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -4215,10 +4212,10 @@
         <v>15</v>
       </c>
       <c r="B167" s="8">
-        <v>46099</v>
+        <v>46076</v>
       </c>
       <c r="C167" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -4226,10 +4223,10 @@
         <v>15</v>
       </c>
       <c r="B168" s="5">
-        <v>46154</v>
+        <v>46099</v>
       </c>
       <c r="C168" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -4237,7 +4234,7 @@
         <v>15</v>
       </c>
       <c r="B169" s="8">
-        <v>46092</v>
+        <v>46154</v>
       </c>
       <c r="C169" s="9">
         <v>1</v>
@@ -4248,10 +4245,10 @@
         <v>15</v>
       </c>
       <c r="B170" s="5">
-        <v>46031</v>
+        <v>46092</v>
       </c>
       <c r="C170" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -4259,7 +4256,7 @@
         <v>15</v>
       </c>
       <c r="B171" s="8">
-        <v>46120</v>
+        <v>46031</v>
       </c>
       <c r="C171" s="9">
         <v>2</v>
@@ -4270,10 +4267,10 @@
         <v>15</v>
       </c>
       <c r="B172" s="5">
-        <v>46077</v>
+        <v>46120</v>
       </c>
       <c r="C172" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -4281,10 +4278,10 @@
         <v>15</v>
       </c>
       <c r="B173" s="8">
-        <v>46114</v>
+        <v>46077</v>
       </c>
       <c r="C173" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -4292,7 +4289,7 @@
         <v>15</v>
       </c>
       <c r="B174" s="5">
-        <v>46037</v>
+        <v>46114</v>
       </c>
       <c r="C174" s="6">
         <v>1</v>
@@ -4303,10 +4300,10 @@
         <v>15</v>
       </c>
       <c r="B175" s="8">
-        <v>46020</v>
+        <v>46037</v>
       </c>
       <c r="C175" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -4314,10 +4311,10 @@
         <v>15</v>
       </c>
       <c r="B176" s="5">
-        <v>46106</v>
+        <v>46020</v>
       </c>
       <c r="C176" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -4325,7 +4322,7 @@
         <v>15</v>
       </c>
       <c r="B177" s="8">
-        <v>46155</v>
+        <v>46106</v>
       </c>
       <c r="C177" s="9">
         <v>1</v>
@@ -4336,7 +4333,7 @@
         <v>15</v>
       </c>
       <c r="B178" s="5">
-        <v>46112</v>
+        <v>46155</v>
       </c>
       <c r="C178" s="6">
         <v>1</v>
@@ -4347,7 +4344,7 @@
         <v>15</v>
       </c>
       <c r="B179" s="8">
-        <v>46132</v>
+        <v>46112</v>
       </c>
       <c r="C179" s="9">
         <v>1</v>
@@ -4358,7 +4355,7 @@
         <v>15</v>
       </c>
       <c r="B180" s="5">
-        <v>46108</v>
+        <v>46132</v>
       </c>
       <c r="C180" s="6">
         <v>1</v>
@@ -4369,7 +4366,7 @@
         <v>15</v>
       </c>
       <c r="B181" s="8">
-        <v>46148</v>
+        <v>46108</v>
       </c>
       <c r="C181" s="9">
         <v>1</v>
@@ -4380,7 +4377,7 @@
         <v>15</v>
       </c>
       <c r="B182" s="5">
-        <v>46118</v>
+        <v>46148</v>
       </c>
       <c r="C182" s="6">
         <v>1</v>
@@ -4391,7 +4388,7 @@
         <v>15</v>
       </c>
       <c r="B183" s="8">
-        <v>46035</v>
+        <v>46118</v>
       </c>
       <c r="C183" s="9">
         <v>1</v>
@@ -4402,7 +4399,7 @@
         <v>15</v>
       </c>
       <c r="B184" s="5">
-        <v>46093</v>
+        <v>46035</v>
       </c>
       <c r="C184" s="6">
         <v>1</v>
@@ -4413,7 +4410,7 @@
         <v>15</v>
       </c>
       <c r="B185" s="8">
-        <v>46022</v>
+        <v>46093</v>
       </c>
       <c r="C185" s="9">
         <v>1</v>
@@ -4424,7 +4421,7 @@
         <v>15</v>
       </c>
       <c r="B186" s="5">
-        <v>46087</v>
+        <v>46022</v>
       </c>
       <c r="C186" s="6">
         <v>1</v>
@@ -4435,10 +4432,10 @@
         <v>15</v>
       </c>
       <c r="B187" s="8">
-        <v>46030</v>
+        <v>46087</v>
       </c>
       <c r="C187" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -4446,10 +4443,10 @@
         <v>15</v>
       </c>
       <c r="B188" s="5">
-        <v>46101</v>
+        <v>46030</v>
       </c>
       <c r="C188" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -4457,7 +4454,7 @@
         <v>15</v>
       </c>
       <c r="B189" s="8">
-        <v>46142</v>
+        <v>46176</v>
       </c>
       <c r="C189" s="9">
         <v>1</v>
@@ -4465,24 +4462,24 @@
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B190" s="5">
-        <v>46001</v>
+        <v>46101</v>
       </c>
       <c r="C190" s="6">
-        <v>153</v>
+        <v>1</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B191" s="8">
-        <v>46008</v>
+        <v>46142</v>
       </c>
       <c r="C191" s="9">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -4490,10 +4487,10 @@
         <v>21</v>
       </c>
       <c r="B192" s="5">
-        <v>46003</v>
+        <v>46001</v>
       </c>
       <c r="C192" s="6">
-        <v>70</v>
+        <v>153</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -4501,10 +4498,10 @@
         <v>21</v>
       </c>
       <c r="B193" s="8">
-        <v>46002</v>
+        <v>46008</v>
       </c>
       <c r="C193" s="9">
-        <v>111</v>
+        <v>38</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -4512,10 +4509,10 @@
         <v>21</v>
       </c>
       <c r="B194" s="5">
-        <v>46006</v>
+        <v>46003</v>
       </c>
       <c r="C194" s="6">
-        <v>146</v>
+        <v>70</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -4523,10 +4520,10 @@
         <v>21</v>
       </c>
       <c r="B195" s="8">
-        <v>46007</v>
+        <v>46002</v>
       </c>
       <c r="C195" s="9">
-        <v>45</v>
+        <v>111</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -4534,10 +4531,10 @@
         <v>21</v>
       </c>
       <c r="B196" s="5">
-        <v>46000</v>
+        <v>46006</v>
       </c>
       <c r="C196" s="6">
-        <v>127</v>
+        <v>146</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -4545,10 +4542,10 @@
         <v>21</v>
       </c>
       <c r="B197" s="8">
-        <v>46084</v>
+        <v>46007</v>
       </c>
       <c r="C197" s="9">
-        <v>10</v>
+        <v>45</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -4556,10 +4553,10 @@
         <v>21</v>
       </c>
       <c r="B198" s="5">
-        <v>46014</v>
+        <v>46000</v>
       </c>
       <c r="C198" s="6">
-        <v>21</v>
+        <v>127</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -4567,10 +4564,10 @@
         <v>21</v>
       </c>
       <c r="B199" s="8">
-        <v>46013</v>
+        <v>46084</v>
       </c>
       <c r="C199" s="9">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -4578,10 +4575,10 @@
         <v>21</v>
       </c>
       <c r="B200" s="5">
-        <v>46010</v>
+        <v>46014</v>
       </c>
       <c r="C200" s="6">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -4589,10 +4586,10 @@
         <v>21</v>
       </c>
       <c r="B201" s="8">
-        <v>46021</v>
+        <v>46013</v>
       </c>
       <c r="C201" s="9">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -4600,10 +4597,10 @@
         <v>21</v>
       </c>
       <c r="B202" s="5">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="C202" s="6">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -4611,10 +4608,10 @@
         <v>21</v>
       </c>
       <c r="B203" s="8">
-        <v>46083</v>
+        <v>46021</v>
       </c>
       <c r="C203" s="9">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -4622,10 +4619,10 @@
         <v>21</v>
       </c>
       <c r="B204" s="5">
-        <v>46157</v>
+        <v>46009</v>
       </c>
       <c r="C204" s="6">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -4633,10 +4630,10 @@
         <v>21</v>
       </c>
       <c r="B205" s="8">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="C205" s="9">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -4644,10 +4641,10 @@
         <v>21</v>
       </c>
       <c r="B206" s="5">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="C206" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -4655,10 +4652,10 @@
         <v>21</v>
       </c>
       <c r="B207" s="8">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="C207" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4666,10 +4663,10 @@
         <v>21</v>
       </c>
       <c r="B208" s="5">
-        <v>46035</v>
+        <v>46167</v>
       </c>
       <c r="C208" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4677,10 +4674,10 @@
         <v>21</v>
       </c>
       <c r="B209" s="8">
-        <v>46085</v>
+        <v>46077</v>
       </c>
       <c r="C209" s="9">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4688,7 +4685,7 @@
         <v>21</v>
       </c>
       <c r="B210" s="5">
-        <v>46120</v>
+        <v>46035</v>
       </c>
       <c r="C210" s="6">
         <v>2</v>
@@ -4699,10 +4696,10 @@
         <v>21</v>
       </c>
       <c r="B211" s="8">
-        <v>46114</v>
+        <v>46085</v>
       </c>
       <c r="C211" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -4710,10 +4707,10 @@
         <v>21</v>
       </c>
       <c r="B212" s="5">
-        <v>46094</v>
+        <v>46120</v>
       </c>
       <c r="C212" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4721,10 +4718,10 @@
         <v>21</v>
       </c>
       <c r="B213" s="8">
-        <v>46080</v>
+        <v>46114</v>
       </c>
       <c r="C213" s="9">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4732,10 +4729,10 @@
         <v>21</v>
       </c>
       <c r="B214" s="5">
-        <v>46127</v>
+        <v>46094</v>
       </c>
       <c r="C214" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4743,10 +4740,10 @@
         <v>21</v>
       </c>
       <c r="B215" s="8">
-        <v>46091</v>
+        <v>46080</v>
       </c>
       <c r="C215" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4754,10 +4751,10 @@
         <v>21</v>
       </c>
       <c r="B216" s="5">
-        <v>46090</v>
+        <v>46127</v>
       </c>
       <c r="C216" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4765,7 +4762,7 @@
         <v>21</v>
       </c>
       <c r="B217" s="8">
-        <v>46020</v>
+        <v>46091</v>
       </c>
       <c r="C217" s="9">
         <v>2</v>
@@ -4776,10 +4773,10 @@
         <v>21</v>
       </c>
       <c r="B218" s="5">
-        <v>46015</v>
+        <v>46090</v>
       </c>
       <c r="C218" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -4787,10 +4784,10 @@
         <v>21</v>
       </c>
       <c r="B219" s="8">
-        <v>46078</v>
+        <v>46020</v>
       </c>
       <c r="C219" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4798,10 +4795,10 @@
         <v>21</v>
       </c>
       <c r="B220" s="5">
-        <v>46148</v>
+        <v>46015</v>
       </c>
       <c r="C220" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -4809,10 +4806,10 @@
         <v>21</v>
       </c>
       <c r="B221" s="8">
-        <v>46105</v>
+        <v>46078</v>
       </c>
       <c r="C221" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -4820,10 +4817,10 @@
         <v>21</v>
       </c>
       <c r="B222" s="5">
-        <v>46087</v>
+        <v>46148</v>
       </c>
       <c r="C222" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -4831,10 +4828,10 @@
         <v>21</v>
       </c>
       <c r="B223" s="8">
-        <v>46107</v>
+        <v>46105</v>
       </c>
       <c r="C223" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -4842,10 +4839,10 @@
         <v>21</v>
       </c>
       <c r="B224" s="5">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="C224" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -4853,10 +4850,10 @@
         <v>21</v>
       </c>
       <c r="B225" s="8">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="C225" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -4864,10 +4861,10 @@
         <v>21</v>
       </c>
       <c r="B226" s="5">
-        <v>46150</v>
+        <v>46086</v>
       </c>
       <c r="C226" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -4875,10 +4872,10 @@
         <v>21</v>
       </c>
       <c r="B227" s="8">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="C227" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -4886,10 +4883,10 @@
         <v>21</v>
       </c>
       <c r="B228" s="5">
-        <v>46118</v>
+        <v>46150</v>
       </c>
       <c r="C228" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -4897,10 +4894,10 @@
         <v>21</v>
       </c>
       <c r="B229" s="8">
-        <v>46076</v>
+        <v>46104</v>
       </c>
       <c r="C229" s="9">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -4908,7 +4905,7 @@
         <v>21</v>
       </c>
       <c r="B230" s="5">
-        <v>46154</v>
+        <v>46118</v>
       </c>
       <c r="C230" s="6">
         <v>1</v>
@@ -4919,10 +4916,10 @@
         <v>21</v>
       </c>
       <c r="B231" s="8">
-        <v>46093</v>
+        <v>46076</v>
       </c>
       <c r="C231" s="9">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -4930,7 +4927,7 @@
         <v>21</v>
       </c>
       <c r="B232" s="5">
-        <v>46122</v>
+        <v>46154</v>
       </c>
       <c r="C232" s="6">
         <v>1</v>
@@ -4941,7 +4938,7 @@
         <v>21</v>
       </c>
       <c r="B233" s="8">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="C233" s="9">
         <v>3</v>
@@ -4952,10 +4949,10 @@
         <v>21</v>
       </c>
       <c r="B234" s="5">
-        <v>46156</v>
+        <v>46122</v>
       </c>
       <c r="C234" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -4963,10 +4960,10 @@
         <v>21</v>
       </c>
       <c r="B235" s="8">
-        <v>46133</v>
+        <v>46092</v>
       </c>
       <c r="C235" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -4974,10 +4971,10 @@
         <v>21</v>
       </c>
       <c r="B236" s="5">
-        <v>46126</v>
+        <v>46156</v>
       </c>
       <c r="C236" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -4985,10 +4982,10 @@
         <v>21</v>
       </c>
       <c r="B237" s="8">
-        <v>46022</v>
+        <v>46133</v>
       </c>
       <c r="C237" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -4996,10 +4993,10 @@
         <v>21</v>
       </c>
       <c r="B238" s="5">
-        <v>46100</v>
+        <v>46126</v>
       </c>
       <c r="C238" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -5007,10 +5004,10 @@
         <v>21</v>
       </c>
       <c r="B239" s="8">
-        <v>46101</v>
+        <v>46022</v>
       </c>
       <c r="C239" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -5018,10 +5015,10 @@
         <v>21</v>
       </c>
       <c r="B240" s="5">
-        <v>46097</v>
+        <v>46100</v>
       </c>
       <c r="C240" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -5029,7 +5026,7 @@
         <v>21</v>
       </c>
       <c r="B241" s="8">
-        <v>46108</v>
+        <v>46101</v>
       </c>
       <c r="C241" s="9">
         <v>1</v>
@@ -5040,10 +5037,10 @@
         <v>21</v>
       </c>
       <c r="B242" s="5">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="C242" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -5051,7 +5048,7 @@
         <v>21</v>
       </c>
       <c r="B243" s="8">
-        <v>46113</v>
+        <v>46108</v>
       </c>
       <c r="C243" s="9">
         <v>1</v>
@@ -5062,10 +5059,10 @@
         <v>21</v>
       </c>
       <c r="B244" s="5">
-        <v>46142</v>
+        <v>46098</v>
       </c>
       <c r="C244" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -5073,7 +5070,7 @@
         <v>21</v>
       </c>
       <c r="B245" s="8">
-        <v>46153</v>
+        <v>46113</v>
       </c>
       <c r="C245" s="9">
         <v>1</v>
@@ -5084,7 +5081,7 @@
         <v>21</v>
       </c>
       <c r="B246" s="5">
-        <v>46031</v>
+        <v>46142</v>
       </c>
       <c r="C246" s="6">
         <v>1</v>
@@ -5095,9 +5092,31 @@
         <v>21</v>
       </c>
       <c r="B247" s="8">
+        <v>46153</v>
+      </c>
+      <c r="C247" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B248" s="5">
+        <v>46031</v>
+      </c>
+      <c r="C248" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B249" s="8">
         <v>46155</v>
       </c>
-      <c r="C247" s="9">
+      <c r="C249" s="9">
         <v>1</v>
       </c>
     </row>
@@ -5640,7 +5659,7 @@
         <v>4</v>
       </c>
       <c r="E31">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -5654,7 +5673,7 @@
         <v>83</v>
       </c>
       <c r="D32">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E32">
         <v>90</v>
@@ -5685,13 +5704,13 @@
         <v>19</v>
       </c>
       <c r="C34">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D34">
         <v>8</v>
       </c>
       <c r="E34">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -5786,7 +5805,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0916EAC6-1E7F-4924-9D0E-33749FD3E143}">
-  <dimension ref="A1:C354"/>
+  <dimension ref="A1:C353"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
@@ -5799,7 +5818,7 @@
         <v>37</v>
       </c>
       <c r="B1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C1" t="s">
         <v>36</v>
@@ -6943,7 +6962,7 @@
         <v>15</v>
       </c>
       <c r="B105" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="C105">
         <v>6</v>
@@ -6954,10 +6973,10 @@
         <v>15</v>
       </c>
       <c r="B106" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="C106">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -6965,7 +6984,7 @@
         <v>15</v>
       </c>
       <c r="B107" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C107">
         <v>4</v>
@@ -6976,7 +6995,7 @@
         <v>15</v>
       </c>
       <c r="B108" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C108">
         <v>4</v>
@@ -6987,7 +7006,7 @@
         <v>15</v>
       </c>
       <c r="B109" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C109">
         <v>4</v>
@@ -7020,7 +7039,7 @@
         <v>15</v>
       </c>
       <c r="B112" t="s">
-        <v>81</v>
+        <v>127</v>
       </c>
       <c r="C112">
         <v>3</v>
@@ -7031,7 +7050,7 @@
         <v>15</v>
       </c>
       <c r="B113" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="C113">
         <v>3</v>
@@ -7042,7 +7061,7 @@
         <v>15</v>
       </c>
       <c r="B114" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C114">
         <v>3</v>
@@ -7053,7 +7072,7 @@
         <v>15</v>
       </c>
       <c r="B115" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C115">
         <v>3</v>
@@ -8087,7 +8106,7 @@
         <v>16</v>
       </c>
       <c r="B209" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="C209">
         <v>4</v>
@@ -8098,7 +8117,7 @@
         <v>16</v>
       </c>
       <c r="B210" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C210">
         <v>4</v>
@@ -8120,7 +8139,7 @@
         <v>16</v>
       </c>
       <c r="B212" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="C212">
         <v>4</v>
@@ -8131,7 +8150,7 @@
         <v>16</v>
       </c>
       <c r="B213" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="C213">
         <v>4</v>
@@ -8142,10 +8161,10 @@
         <v>16</v>
       </c>
       <c r="B214" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="C214">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -8153,7 +8172,7 @@
         <v>16</v>
       </c>
       <c r="B215" t="s">
-        <v>201</v>
+        <v>118</v>
       </c>
       <c r="C215">
         <v>3</v>
@@ -8164,7 +8183,7 @@
         <v>16</v>
       </c>
       <c r="B216" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="C216">
         <v>3</v>
@@ -8175,7 +8194,7 @@
         <v>16</v>
       </c>
       <c r="B217" t="s">
-        <v>118</v>
+        <v>201</v>
       </c>
       <c r="C217">
         <v>3</v>
@@ -8197,7 +8216,7 @@
         <v>16</v>
       </c>
       <c r="B219" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="C219">
         <v>3</v>
@@ -8208,7 +8227,7 @@
         <v>16</v>
       </c>
       <c r="B220" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C220">
         <v>3</v>
@@ -8219,7 +8238,7 @@
         <v>16</v>
       </c>
       <c r="B221" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C221">
         <v>3</v>
@@ -8329,7 +8348,7 @@
         <v>16</v>
       </c>
       <c r="B231" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="C231">
         <v>1</v>
@@ -8340,7 +8359,7 @@
         <v>16</v>
       </c>
       <c r="B232" t="s">
-        <v>119</v>
+        <v>224</v>
       </c>
       <c r="C232">
         <v>1</v>
@@ -8351,7 +8370,7 @@
         <v>16</v>
       </c>
       <c r="B233" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="C233">
         <v>1</v>
@@ -8362,7 +8381,7 @@
         <v>16</v>
       </c>
       <c r="B234" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="C234">
         <v>1</v>
@@ -8373,7 +8392,7 @@
         <v>16</v>
       </c>
       <c r="B235" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="C235">
         <v>1</v>
@@ -8384,7 +8403,7 @@
         <v>16</v>
       </c>
       <c r="B236" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="C236">
         <v>1</v>
@@ -8395,7 +8414,7 @@
         <v>16</v>
       </c>
       <c r="B237" t="s">
-        <v>214</v>
+        <v>239</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -8406,7 +8425,7 @@
         <v>16</v>
       </c>
       <c r="B238" t="s">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -8417,7 +8436,7 @@
         <v>16</v>
       </c>
       <c r="B239" t="s">
-        <v>240</v>
+        <v>119</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -8428,7 +8447,7 @@
         <v>16</v>
       </c>
       <c r="B240" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C240">
         <v>1</v>
@@ -8439,7 +8458,7 @@
         <v>16</v>
       </c>
       <c r="B241" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -8450,7 +8469,7 @@
         <v>16</v>
       </c>
       <c r="B242" t="s">
-        <v>242</v>
+        <v>58</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -8461,7 +8480,7 @@
         <v>16</v>
       </c>
       <c r="B243" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -8472,7 +8491,7 @@
         <v>16</v>
       </c>
       <c r="B244" t="s">
-        <v>58</v>
+        <v>217</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -8483,7 +8502,7 @@
         <v>16</v>
       </c>
       <c r="B245" t="s">
-        <v>249</v>
+        <v>222</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -8494,7 +8513,7 @@
         <v>16</v>
       </c>
       <c r="B246" t="s">
-        <v>217</v>
+        <v>69</v>
       </c>
       <c r="C246">
         <v>1</v>
@@ -8505,7 +8524,7 @@
         <v>16</v>
       </c>
       <c r="B247" t="s">
-        <v>211</v>
+        <v>115</v>
       </c>
       <c r="C247">
         <v>1</v>
@@ -8516,7 +8535,7 @@
         <v>16</v>
       </c>
       <c r="B248" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C248">
         <v>1</v>
@@ -8527,7 +8546,7 @@
         <v>16</v>
       </c>
       <c r="B249" t="s">
-        <v>69</v>
+        <v>226</v>
       </c>
       <c r="C249">
         <v>1</v>
@@ -8538,7 +8557,7 @@
         <v>16</v>
       </c>
       <c r="B250" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -8549,7 +8568,7 @@
         <v>16</v>
       </c>
       <c r="B251" t="s">
-        <v>126</v>
+        <v>223</v>
       </c>
       <c r="C251">
         <v>1</v>
@@ -8560,7 +8579,7 @@
         <v>16</v>
       </c>
       <c r="B252" t="s">
-        <v>230</v>
+        <v>126</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -8571,7 +8590,7 @@
         <v>16</v>
       </c>
       <c r="B253" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -8582,7 +8601,7 @@
         <v>16</v>
       </c>
       <c r="B254" t="s">
-        <v>209</v>
+        <v>235</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -8593,7 +8612,7 @@
         <v>16</v>
       </c>
       <c r="B255" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -8604,7 +8623,7 @@
         <v>16</v>
       </c>
       <c r="B256" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -8615,7 +8634,7 @@
         <v>16</v>
       </c>
       <c r="B257" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -8626,7 +8645,7 @@
         <v>16</v>
       </c>
       <c r="B258" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C258">
         <v>1</v>
@@ -8637,7 +8656,7 @@
         <v>16</v>
       </c>
       <c r="B259" t="s">
-        <v>231</v>
+        <v>208</v>
       </c>
       <c r="C259">
         <v>1</v>
@@ -8648,7 +8667,7 @@
         <v>16</v>
       </c>
       <c r="B260" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C260">
         <v>1</v>
@@ -8659,7 +8678,7 @@
         <v>16</v>
       </c>
       <c r="B261" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C261">
         <v>1</v>
@@ -8670,7 +8689,7 @@
         <v>16</v>
       </c>
       <c r="B262" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C262">
         <v>1</v>
@@ -8681,7 +8700,7 @@
         <v>16</v>
       </c>
       <c r="B263" t="s">
-        <v>243</v>
+        <v>219</v>
       </c>
       <c r="C263">
         <v>1</v>
@@ -8692,7 +8711,7 @@
         <v>16</v>
       </c>
       <c r="B264" t="s">
-        <v>115</v>
+        <v>233</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -8703,7 +8722,7 @@
         <v>16</v>
       </c>
       <c r="B265" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="C265">
         <v>1</v>
@@ -8714,7 +8733,7 @@
         <v>16</v>
       </c>
       <c r="B266" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C266">
         <v>1</v>
@@ -8725,7 +8744,7 @@
         <v>16</v>
       </c>
       <c r="B267" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -8736,7 +8755,7 @@
         <v>16</v>
       </c>
       <c r="B268" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="C268">
         <v>1</v>
@@ -8747,7 +8766,7 @@
         <v>16</v>
       </c>
       <c r="B269" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="C269">
         <v>1</v>
@@ -8758,7 +8777,7 @@
         <v>16</v>
       </c>
       <c r="B270" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="C270">
         <v>1</v>
@@ -8769,7 +8788,7 @@
         <v>16</v>
       </c>
       <c r="B271" t="s">
-        <v>241</v>
+        <v>216</v>
       </c>
       <c r="C271">
         <v>1</v>
@@ -8780,7 +8799,7 @@
         <v>16</v>
       </c>
       <c r="B272" t="s">
-        <v>245</v>
+        <v>70</v>
       </c>
       <c r="C272">
         <v>1</v>
@@ -8791,7 +8810,7 @@
         <v>16</v>
       </c>
       <c r="B273" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C273">
         <v>1</v>
@@ -8802,7 +8821,7 @@
         <v>16</v>
       </c>
       <c r="B274" t="s">
-        <v>70</v>
+        <v>121</v>
       </c>
       <c r="C274">
         <v>1</v>
@@ -8810,13 +8829,13 @@
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B275" t="s">
         <v>121</v>
       </c>
       <c r="C275">
-        <v>1</v>
+        <v>39</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -8824,10 +8843,10 @@
         <v>21</v>
       </c>
       <c r="B276" t="s">
-        <v>121</v>
+        <v>189</v>
       </c>
       <c r="C276">
-        <v>39</v>
+        <v>11</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -8835,10 +8854,10 @@
         <v>21</v>
       </c>
       <c r="B277" t="s">
-        <v>189</v>
+        <v>132</v>
       </c>
       <c r="C277">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -8846,10 +8865,10 @@
         <v>21</v>
       </c>
       <c r="B278" t="s">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="C278">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -8857,7 +8876,7 @@
         <v>21</v>
       </c>
       <c r="B279" t="s">
-        <v>103</v>
+        <v>202</v>
       </c>
       <c r="C279">
         <v>7</v>
@@ -8868,10 +8887,10 @@
         <v>21</v>
       </c>
       <c r="B280" t="s">
-        <v>202</v>
+        <v>243</v>
       </c>
       <c r="C280">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -8879,7 +8898,7 @@
         <v>21</v>
       </c>
       <c r="B281" t="s">
-        <v>244</v>
+        <v>120</v>
       </c>
       <c r="C281">
         <v>6</v>
@@ -8890,10 +8909,10 @@
         <v>21</v>
       </c>
       <c r="B282" t="s">
-        <v>120</v>
+        <v>245</v>
       </c>
       <c r="C282">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -8901,7 +8920,7 @@
         <v>21</v>
       </c>
       <c r="B283" t="s">
-        <v>246</v>
+        <v>142</v>
       </c>
       <c r="C283">
         <v>5</v>
@@ -8912,7 +8931,7 @@
         <v>21</v>
       </c>
       <c r="B284" t="s">
-        <v>142</v>
+        <v>246</v>
       </c>
       <c r="C284">
         <v>5</v>
@@ -8923,7 +8942,7 @@
         <v>21</v>
       </c>
       <c r="B285" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C285">
         <v>5</v>
@@ -8934,10 +8953,10 @@
         <v>21</v>
       </c>
       <c r="B286" t="s">
-        <v>245</v>
+        <v>101</v>
       </c>
       <c r="C286">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -8945,7 +8964,7 @@
         <v>21</v>
       </c>
       <c r="B287" t="s">
-        <v>101</v>
+        <v>128</v>
       </c>
       <c r="C287">
         <v>4</v>
@@ -8956,7 +8975,7 @@
         <v>21</v>
       </c>
       <c r="B288" t="s">
-        <v>128</v>
+        <v>247</v>
       </c>
       <c r="C288">
         <v>4</v>
@@ -8967,10 +8986,10 @@
         <v>21</v>
       </c>
       <c r="B289" t="s">
-        <v>248</v>
+        <v>81</v>
       </c>
       <c r="C289">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -8978,7 +8997,7 @@
         <v>21</v>
       </c>
       <c r="B290" t="s">
-        <v>81</v>
+        <v>248</v>
       </c>
       <c r="C290">
         <v>3</v>
@@ -8989,7 +9008,7 @@
         <v>21</v>
       </c>
       <c r="B291" t="s">
-        <v>249</v>
+        <v>126</v>
       </c>
       <c r="C291">
         <v>3</v>
@@ -9000,7 +9019,7 @@
         <v>21</v>
       </c>
       <c r="B292" t="s">
-        <v>126</v>
+        <v>196</v>
       </c>
       <c r="C292">
         <v>3</v>
@@ -9011,7 +9030,7 @@
         <v>21</v>
       </c>
       <c r="B293" t="s">
-        <v>196</v>
+        <v>127</v>
       </c>
       <c r="C293">
         <v>3</v>
@@ -9022,7 +9041,7 @@
         <v>21</v>
       </c>
       <c r="B294" t="s">
-        <v>127</v>
+        <v>252</v>
       </c>
       <c r="C294">
         <v>3</v>
@@ -9033,7 +9052,7 @@
         <v>21</v>
       </c>
       <c r="B295" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C295">
         <v>3</v>
@@ -9044,7 +9063,7 @@
         <v>21</v>
       </c>
       <c r="B296" t="s">
-        <v>252</v>
+        <v>163</v>
       </c>
       <c r="C296">
         <v>3</v>
@@ -9055,7 +9074,7 @@
         <v>21</v>
       </c>
       <c r="B297" t="s">
-        <v>163</v>
+        <v>250</v>
       </c>
       <c r="C297">
         <v>3</v>
@@ -9066,7 +9085,7 @@
         <v>21</v>
       </c>
       <c r="B298" t="s">
-        <v>251</v>
+        <v>44</v>
       </c>
       <c r="C298">
         <v>3</v>
@@ -9077,7 +9096,7 @@
         <v>21</v>
       </c>
       <c r="B299" t="s">
-        <v>44</v>
+        <v>133</v>
       </c>
       <c r="C299">
         <v>3</v>
@@ -9088,10 +9107,10 @@
         <v>21</v>
       </c>
       <c r="B300" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="C300">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
@@ -9099,7 +9118,7 @@
         <v>21</v>
       </c>
       <c r="B301" t="s">
-        <v>116</v>
+        <v>171</v>
       </c>
       <c r="C301">
         <v>2</v>
@@ -9110,7 +9129,7 @@
         <v>21</v>
       </c>
       <c r="B302" t="s">
-        <v>171</v>
+        <v>136</v>
       </c>
       <c r="C302">
         <v>2</v>
@@ -9121,7 +9140,7 @@
         <v>21</v>
       </c>
       <c r="B303" t="s">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="C303">
         <v>2</v>
@@ -9132,7 +9151,7 @@
         <v>21</v>
       </c>
       <c r="B304" t="s">
-        <v>173</v>
+        <v>254</v>
       </c>
       <c r="C304">
         <v>2</v>
@@ -9143,7 +9162,7 @@
         <v>21</v>
       </c>
       <c r="B305" t="s">
-        <v>255</v>
+        <v>77</v>
       </c>
       <c r="C305">
         <v>2</v>
@@ -9154,7 +9173,7 @@
         <v>21</v>
       </c>
       <c r="B306" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C306">
         <v>2</v>
@@ -9165,7 +9184,7 @@
         <v>21</v>
       </c>
       <c r="B307" t="s">
-        <v>70</v>
+        <v>255</v>
       </c>
       <c r="C307">
         <v>2</v>
@@ -9176,7 +9195,7 @@
         <v>21</v>
       </c>
       <c r="B308" t="s">
-        <v>256</v>
+        <v>54</v>
       </c>
       <c r="C308">
         <v>2</v>
@@ -9187,7 +9206,7 @@
         <v>21</v>
       </c>
       <c r="B309" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="C309">
         <v>2</v>
@@ -9198,7 +9217,7 @@
         <v>21</v>
       </c>
       <c r="B310" t="s">
-        <v>85</v>
+        <v>270</v>
       </c>
       <c r="C310">
         <v>2</v>
@@ -9209,7 +9228,7 @@
         <v>21</v>
       </c>
       <c r="B311" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="C311">
         <v>2</v>
@@ -9220,7 +9239,7 @@
         <v>21</v>
       </c>
       <c r="B312" t="s">
-        <v>257</v>
+        <v>198</v>
       </c>
       <c r="C312">
         <v>2</v>
@@ -9231,7 +9250,7 @@
         <v>21</v>
       </c>
       <c r="B313" t="s">
-        <v>198</v>
+        <v>253</v>
       </c>
       <c r="C313">
         <v>2</v>
@@ -9242,7 +9261,7 @@
         <v>21</v>
       </c>
       <c r="B314" t="s">
-        <v>254</v>
+        <v>199</v>
       </c>
       <c r="C314">
         <v>2</v>
@@ -9253,7 +9272,7 @@
         <v>21</v>
       </c>
       <c r="B315" t="s">
-        <v>199</v>
+        <v>62</v>
       </c>
       <c r="C315">
         <v>2</v>
@@ -9264,7 +9283,7 @@
         <v>21</v>
       </c>
       <c r="B316" t="s">
-        <v>62</v>
+        <v>249</v>
       </c>
       <c r="C316">
         <v>2</v>
@@ -9275,10 +9294,10 @@
         <v>21</v>
       </c>
       <c r="B317" t="s">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="C317">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
@@ -9286,7 +9305,7 @@
         <v>21</v>
       </c>
       <c r="B318" t="s">
-        <v>281</v>
+        <v>138</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -9297,7 +9316,7 @@
         <v>21</v>
       </c>
       <c r="B319" t="s">
-        <v>138</v>
+        <v>268</v>
       </c>
       <c r="C319">
         <v>1</v>
@@ -9308,7 +9327,7 @@
         <v>21</v>
       </c>
       <c r="B320" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C320">
         <v>1</v>
@@ -9319,7 +9338,7 @@
         <v>21</v>
       </c>
       <c r="B321" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C321">
         <v>1</v>
@@ -9341,7 +9360,7 @@
         <v>21</v>
       </c>
       <c r="B323" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C323">
         <v>1</v>
@@ -9352,7 +9371,7 @@
         <v>21</v>
       </c>
       <c r="B324" t="s">
-        <v>279</v>
+        <v>266</v>
       </c>
       <c r="C324">
         <v>1</v>
@@ -9363,7 +9382,7 @@
         <v>21</v>
       </c>
       <c r="B325" t="s">
-        <v>267</v>
+        <v>172</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -9374,7 +9393,7 @@
         <v>21</v>
       </c>
       <c r="B326" t="s">
-        <v>172</v>
+        <v>281</v>
       </c>
       <c r="C326">
         <v>1</v>
@@ -9385,7 +9404,7 @@
         <v>21</v>
       </c>
       <c r="B327" t="s">
-        <v>282</v>
+        <v>63</v>
       </c>
       <c r="C327">
         <v>1</v>
@@ -9396,7 +9415,7 @@
         <v>21</v>
       </c>
       <c r="B328" t="s">
-        <v>63</v>
+        <v>137</v>
       </c>
       <c r="C328">
         <v>1</v>
@@ -9407,7 +9426,7 @@
         <v>21</v>
       </c>
       <c r="B329" t="s">
-        <v>137</v>
+        <v>279</v>
       </c>
       <c r="C329">
         <v>1</v>
@@ -9418,7 +9437,7 @@
         <v>21</v>
       </c>
       <c r="B330" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="C330">
         <v>1</v>
@@ -9429,7 +9448,7 @@
         <v>21</v>
       </c>
       <c r="B331" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="C331">
         <v>1</v>
@@ -9440,7 +9459,7 @@
         <v>21</v>
       </c>
       <c r="B332" t="s">
-        <v>278</v>
+        <v>185</v>
       </c>
       <c r="C332">
         <v>1</v>
@@ -9451,7 +9470,7 @@
         <v>21</v>
       </c>
       <c r="B333" t="s">
-        <v>185</v>
+        <v>263</v>
       </c>
       <c r="C333">
         <v>1</v>
@@ -9462,7 +9481,7 @@
         <v>21</v>
       </c>
       <c r="B334" t="s">
-        <v>264</v>
+        <v>148</v>
       </c>
       <c r="C334">
         <v>1</v>
@@ -9473,7 +9492,7 @@
         <v>21</v>
       </c>
       <c r="B335" t="s">
-        <v>148</v>
+        <v>49</v>
       </c>
       <c r="C335">
         <v>1</v>
@@ -9484,7 +9503,7 @@
         <v>21</v>
       </c>
       <c r="B336" t="s">
-        <v>49</v>
+        <v>261</v>
       </c>
       <c r="C336">
         <v>1</v>
@@ -9495,7 +9514,7 @@
         <v>21</v>
       </c>
       <c r="B337" t="s">
-        <v>262</v>
+        <v>115</v>
       </c>
       <c r="C337">
         <v>1</v>
@@ -9506,7 +9525,7 @@
         <v>21</v>
       </c>
       <c r="B338" t="s">
-        <v>115</v>
+        <v>272</v>
       </c>
       <c r="C338">
         <v>1</v>
@@ -9517,7 +9536,7 @@
         <v>21</v>
       </c>
       <c r="B339" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="C339">
         <v>1</v>
@@ -9528,7 +9547,7 @@
         <v>21</v>
       </c>
       <c r="B340" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="C340">
         <v>1</v>
@@ -9539,7 +9558,7 @@
         <v>21</v>
       </c>
       <c r="B341" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="C341">
         <v>1</v>
@@ -9550,7 +9569,7 @@
         <v>21</v>
       </c>
       <c r="B342" t="s">
-        <v>261</v>
+        <v>214</v>
       </c>
       <c r="C342">
         <v>1</v>
@@ -9561,7 +9580,7 @@
         <v>21</v>
       </c>
       <c r="B343" t="s">
-        <v>214</v>
+        <v>125</v>
       </c>
       <c r="C343">
         <v>1</v>
@@ -9572,7 +9591,7 @@
         <v>21</v>
       </c>
       <c r="B344" t="s">
-        <v>125</v>
+        <v>276</v>
       </c>
       <c r="C344">
         <v>1</v>
@@ -9583,7 +9602,7 @@
         <v>21</v>
       </c>
       <c r="B345" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="C345">
         <v>1</v>
@@ -9594,7 +9613,7 @@
         <v>21</v>
       </c>
       <c r="B346" t="s">
-        <v>258</v>
+        <v>92</v>
       </c>
       <c r="C346">
         <v>1</v>
@@ -9605,7 +9624,7 @@
         <v>21</v>
       </c>
       <c r="B347" t="s">
-        <v>92</v>
+        <v>165</v>
       </c>
       <c r="C347">
         <v>1</v>
@@ -9616,7 +9635,7 @@
         <v>21</v>
       </c>
       <c r="B348" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="C348">
         <v>1</v>
@@ -9627,7 +9646,7 @@
         <v>21</v>
       </c>
       <c r="B349" t="s">
-        <v>174</v>
+        <v>269</v>
       </c>
       <c r="C349">
         <v>1</v>
@@ -9638,7 +9657,7 @@
         <v>21</v>
       </c>
       <c r="B350" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="C350">
         <v>1</v>
@@ -9649,7 +9668,7 @@
         <v>21</v>
       </c>
       <c r="B351" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C351">
         <v>1</v>
@@ -9660,7 +9679,7 @@
         <v>21</v>
       </c>
       <c r="B352" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C352">
         <v>1</v>
@@ -9671,20 +9690,9 @@
         <v>21</v>
       </c>
       <c r="B353" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C353">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A354" t="s">
-        <v>21</v>
-      </c>
-      <c r="B354" t="s">
-        <v>268</v>
-      </c>
-      <c r="C354">
         <v>1</v>
       </c>
     </row>
@@ -9706,10 +9714,10 @@
         <v>37</v>
       </c>
       <c r="B1" t="s">
+        <v>283</v>
+      </c>
+      <c r="C1" t="s">
         <v>284</v>
-      </c>
-      <c r="C1" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -9717,7 +9725,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C2">
         <v>63</v>
@@ -9728,7 +9736,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C3">
         <v>512</v>
@@ -9739,7 +9747,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C4">
         <v>37</v>
@@ -9750,7 +9758,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C5">
         <v>11</v>
@@ -9761,7 +9769,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C6">
         <v>7</v>
@@ -9772,7 +9780,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -9783,7 +9791,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -9794,7 +9802,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C9">
         <v>29</v>
@@ -9805,7 +9813,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C10">
         <v>559</v>
@@ -9816,7 +9824,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C11">
         <v>23</v>
@@ -9827,7 +9835,7 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C12">
         <v>30</v>
@@ -9838,7 +9846,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C13">
         <v>25</v>
@@ -9849,10 +9857,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C14">
-        <v>881</v>
+        <v>882</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -9860,7 +9868,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C15">
         <v>4</v>
@@ -9871,7 +9879,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C16">
         <v>13</v>
@@ -9882,7 +9890,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C17">
         <v>22</v>
@@ -9893,7 +9901,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C18">
         <v>33</v>
@@ -9904,7 +9912,7 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C19">
         <v>11</v>
@@ -9915,7 +9923,7 @@
         <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C20">
         <v>2</v>
@@ -9926,7 +9934,7 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C21">
         <v>4</v>
@@ -9937,7 +9945,7 @@
         <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C22">
         <v>2</v>
@@ -9948,7 +9956,7 @@
         <v>15</v>
       </c>
       <c r="B23" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C23">
         <v>2</v>
@@ -9959,7 +9967,7 @@
         <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C24">
         <v>41</v>
@@ -9970,10 +9978,10 @@
         <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C25">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -9981,7 +9989,7 @@
         <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C26">
         <v>25</v>
@@ -9992,7 +10000,7 @@
         <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C27">
         <v>111</v>
@@ -10003,7 +10011,7 @@
         <v>16</v>
       </c>
       <c r="B28" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C28">
         <v>139</v>
@@ -10014,7 +10022,7 @@
         <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C29">
         <v>77</v>
@@ -10025,7 +10033,7 @@
         <v>16</v>
       </c>
       <c r="B30" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C30">
         <v>10</v>
@@ -10036,7 +10044,7 @@
         <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -10047,7 +10055,7 @@
         <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C32">
         <v>7</v>
@@ -10058,7 +10066,7 @@
         <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -10069,7 +10077,7 @@
         <v>21</v>
       </c>
       <c r="B34" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C34">
         <v>706</v>
@@ -10080,7 +10088,7 @@
         <v>21</v>
       </c>
       <c r="B35" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C35">
         <v>9</v>
@@ -10091,7 +10099,7 @@
         <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C36">
         <v>22</v>
@@ -10102,7 +10110,7 @@
         <v>21</v>
       </c>
       <c r="B37" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C37">
         <v>61</v>
@@ -10113,7 +10121,7 @@
         <v>21</v>
       </c>
       <c r="B38" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C38">
         <v>24</v>
@@ -10124,7 +10132,7 @@
         <v>21</v>
       </c>
       <c r="B39" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C39">
         <v>55</v>
@@ -10135,7 +10143,7 @@
         <v>21</v>
       </c>
       <c r="B40" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C40">
         <v>3</v>
@@ -10146,7 +10154,7 @@
         <v>21</v>
       </c>
       <c r="B41" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C41">
         <v>14</v>
@@ -10157,7 +10165,7 @@
         <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C42">
         <v>14</v>
@@ -10168,7 +10176,7 @@
         <v>21</v>
       </c>
       <c r="B43" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C43">
         <v>6</v>
@@ -10197,7 +10205,7 @@
         <v>22</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -10304,7 +10312,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C11" s="9">
         <v>1</v>
@@ -10414,7 +10422,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C21" s="9">
         <v>2</v>
@@ -10524,7 +10532,7 @@
         <v>15</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C31" s="9">
         <v>2</v>

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="179" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC55ECF7-3F82-4AF5-BAE6-62D195D4A831}"/>
+  <xr:revisionPtr revIDLastSave="194" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{608AAFB9-F37D-490B-B00D-E06F6E440669}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" tabRatio="731" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" tabRatio="731" firstSheet="1" activeTab="7" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
-    <sheet name="mat_2026" sheetId="1" r:id="rId1"/>
-    <sheet name="proyeccion_2026" sheetId="2" r:id="rId2"/>
+    <sheet name="proyeccion_2026" sheetId="2" r:id="rId1"/>
+    <sheet name="mat_2026" sheetId="1" r:id="rId2"/>
     <sheet name="genero" sheetId="3" r:id="rId3"/>
     <sheet name="mat_time" sheetId="4" r:id="rId4"/>
     <sheet name="origen_estudiantes" sheetId="5" r:id="rId5"/>
@@ -23,7 +23,7 @@
     <sheet name="cantidad_cursos" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">mat_2026!$A$1:$E$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">mat_2026!$A$1:$E$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">origen_colegios!$A$1:$C$354</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1321" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1317" uniqueCount="298">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -671,9 +671,6 @@
   </si>
   <si>
     <t>Escuela Particular La Merced</t>
-  </si>
-  <si>
-    <t>Liceo Neandro Schilling</t>
   </si>
   <si>
     <t>Centro Educacional Principado de Asturias</t>
@@ -1387,687 +1384,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8FC1322-F2C4-4535-882A-673ED2A7B0F2}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="3"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2">
-        <v>19</v>
-      </c>
-      <c r="D2">
-        <v>24</v>
-      </c>
-      <c r="E2">
-        <v>1.2629999999999999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3">
-        <v>33</v>
-      </c>
-      <c r="D3">
-        <v>35</v>
-      </c>
-      <c r="E3">
-        <v>1.0609999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4">
-        <v>46</v>
-      </c>
-      <c r="D4">
-        <v>52</v>
-      </c>
-      <c r="E4">
-        <v>1.1299999999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5">
-        <v>34</v>
-      </c>
-      <c r="D5">
-        <v>43</v>
-      </c>
-      <c r="E5">
-        <v>1.2649999999999999</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6">
-        <v>58</v>
-      </c>
-      <c r="D6">
-        <v>62</v>
-      </c>
-      <c r="E6">
-        <v>1.069</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7">
-        <v>61</v>
-      </c>
-      <c r="D7">
-        <v>66</v>
-      </c>
-      <c r="E7">
-        <v>1.0820000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8">
-        <v>75</v>
-      </c>
-      <c r="D8">
-        <v>80</v>
-      </c>
-      <c r="E8">
-        <v>1.0669999999999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9">
-        <v>108</v>
-      </c>
-      <c r="D9">
-        <v>109</v>
-      </c>
-      <c r="E9">
-        <v>1.0089999999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10">
-        <v>64</v>
-      </c>
-      <c r="D10">
-        <v>70</v>
-      </c>
-      <c r="E10">
-        <v>1.0940000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11">
-        <v>88</v>
-      </c>
-      <c r="D11">
-        <v>93</v>
-      </c>
-      <c r="E11">
-        <v>1.0569999999999999</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12">
-        <v>31</v>
-      </c>
-      <c r="D12">
-        <v>43</v>
-      </c>
-      <c r="E12">
-        <v>1.387</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13">
-        <v>35</v>
-      </c>
-      <c r="D13">
-        <v>39</v>
-      </c>
-      <c r="E13">
-        <v>1.1140000000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14">
-        <v>62</v>
-      </c>
-      <c r="D14">
-        <v>65</v>
-      </c>
-      <c r="E14">
-        <v>1.048</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15">
-        <v>40</v>
-      </c>
-      <c r="D15">
-        <v>42</v>
-      </c>
-      <c r="E15">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16">
-        <v>63</v>
-      </c>
-      <c r="D16">
-        <v>61</v>
-      </c>
-      <c r="E16">
-        <v>0.96799999999999997</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17">
-        <v>68</v>
-      </c>
-      <c r="D17">
-        <v>70</v>
-      </c>
-      <c r="E17">
-        <v>1.0289999999999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18">
-        <v>75</v>
-      </c>
-      <c r="D18">
-        <v>83</v>
-      </c>
-      <c r="E18">
-        <v>1.107</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19">
-        <v>89</v>
-      </c>
-      <c r="D19">
-        <v>89</v>
-      </c>
-      <c r="E19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20">
-        <v>85</v>
-      </c>
-      <c r="D20">
-        <v>85</v>
-      </c>
-      <c r="E20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21">
-        <v>88</v>
-      </c>
-      <c r="D21">
-        <v>89</v>
-      </c>
-      <c r="E21">
-        <v>1.0109999999999999</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>4</v>
-      </c>
-      <c r="C22">
-        <v>28</v>
-      </c>
-      <c r="D22">
-        <v>36</v>
-      </c>
-      <c r="E22">
-        <v>1.286</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23">
-        <v>38</v>
-      </c>
-      <c r="D23">
-        <v>41</v>
-      </c>
-      <c r="E23">
-        <v>1.079</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24">
-        <v>65</v>
-      </c>
-      <c r="D24">
-        <v>74</v>
-      </c>
-      <c r="E24">
-        <v>1.1379999999999999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>5</v>
-      </c>
-      <c r="C25">
-        <v>91</v>
-      </c>
-      <c r="D25">
-        <v>93</v>
-      </c>
-      <c r="E25">
-        <v>1.022</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26">
-        <v>83</v>
-      </c>
-      <c r="D26">
-        <v>82</v>
-      </c>
-      <c r="E26">
-        <v>0.98799999999999999</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>12</v>
-      </c>
-      <c r="C27">
-        <v>109</v>
-      </c>
-      <c r="D27">
-        <v>106</v>
-      </c>
-      <c r="E27">
-        <v>0.97199999999999998</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28">
-        <v>140</v>
-      </c>
-      <c r="D28">
-        <v>146</v>
-      </c>
-      <c r="E28">
-        <v>1.0429999999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>13</v>
-      </c>
-      <c r="C29">
-        <v>128</v>
-      </c>
-      <c r="D29">
-        <v>134</v>
-      </c>
-      <c r="E29">
-        <v>1.0469999999999999</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30">
-        <v>119</v>
-      </c>
-      <c r="D30">
-        <v>117</v>
-      </c>
-      <c r="E30">
-        <v>0.98299999999999998</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31">
-        <v>138</v>
-      </c>
-      <c r="D31">
-        <v>146</v>
-      </c>
-      <c r="E31">
-        <v>1.0580000000000001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>16</v>
-      </c>
-      <c r="B32" t="s">
-        <v>17</v>
-      </c>
-      <c r="C32">
-        <v>396</v>
-      </c>
-      <c r="D32">
-        <v>420</v>
-      </c>
-      <c r="E32">
-        <v>1.0609999999999999</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>16</v>
-      </c>
-      <c r="B33" t="s">
-        <v>18</v>
-      </c>
-      <c r="C33">
-        <v>329</v>
-      </c>
-      <c r="D33">
-        <v>341</v>
-      </c>
-      <c r="E33">
-        <v>1.036</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>16</v>
-      </c>
-      <c r="B34" t="s">
-        <v>19</v>
-      </c>
-      <c r="C34">
-        <v>323</v>
-      </c>
-      <c r="D34">
-        <v>310</v>
-      </c>
-      <c r="E34">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>16</v>
-      </c>
-      <c r="B35" t="s">
-        <v>20</v>
-      </c>
-      <c r="C35">
-        <v>218</v>
-      </c>
-      <c r="D35">
-        <v>218</v>
-      </c>
-      <c r="E35">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>21</v>
-      </c>
-      <c r="B36" t="s">
-        <v>17</v>
-      </c>
-      <c r="C36">
-        <v>250</v>
-      </c>
-      <c r="D36">
-        <v>256</v>
-      </c>
-      <c r="E36">
-        <v>1.024</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>21</v>
-      </c>
-      <c r="B37" t="s">
-        <v>18</v>
-      </c>
-      <c r="C37">
-        <v>217</v>
-      </c>
-      <c r="D37">
-        <v>217</v>
-      </c>
-      <c r="E37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>21</v>
-      </c>
-      <c r="B38" t="s">
-        <v>19</v>
-      </c>
-      <c r="C38">
-        <v>226</v>
-      </c>
-      <c r="D38">
-        <v>242</v>
-      </c>
-      <c r="E38">
-        <v>1.071</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>21</v>
-      </c>
-      <c r="B39" t="s">
-        <v>20</v>
-      </c>
-      <c r="C39">
-        <v>214</v>
-      </c>
-      <c r="D39">
-        <v>199</v>
-      </c>
-      <c r="E39">
-        <v>0.93</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB2C3402-0C17-4819-BE0C-D68186D5792E}">
   <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2230,6 +1546,687 @@
       <c r="F7" s="2">
         <f t="shared" si="1"/>
         <v>4.8701298701299134E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8FC1322-F2C4-4535-882A-673ED2A7B0F2}">
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>19</v>
+      </c>
+      <c r="D2">
+        <v>24</v>
+      </c>
+      <c r="E2">
+        <v>1.2629999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>33</v>
+      </c>
+      <c r="D3">
+        <v>34</v>
+      </c>
+      <c r="E3">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>46</v>
+      </c>
+      <c r="D4">
+        <v>52</v>
+      </c>
+      <c r="E4">
+        <v>1.1299999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>34</v>
+      </c>
+      <c r="D5">
+        <v>43</v>
+      </c>
+      <c r="E5">
+        <v>1.2649999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <v>58</v>
+      </c>
+      <c r="D6">
+        <v>62</v>
+      </c>
+      <c r="E6">
+        <v>1.069</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>61</v>
+      </c>
+      <c r="D7">
+        <v>66</v>
+      </c>
+      <c r="E7">
+        <v>1.0820000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>75</v>
+      </c>
+      <c r="D8">
+        <v>80</v>
+      </c>
+      <c r="E8">
+        <v>1.0669999999999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9">
+        <v>108</v>
+      </c>
+      <c r="D9">
+        <v>109</v>
+      </c>
+      <c r="E9">
+        <v>1.0089999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>64</v>
+      </c>
+      <c r="D10">
+        <v>70</v>
+      </c>
+      <c r="E10">
+        <v>1.0940000000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11">
+        <v>88</v>
+      </c>
+      <c r="D11">
+        <v>93</v>
+      </c>
+      <c r="E11">
+        <v>1.0569999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12">
+        <v>31</v>
+      </c>
+      <c r="D12">
+        <v>42</v>
+      </c>
+      <c r="E12">
+        <v>1.355</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13">
+        <v>35</v>
+      </c>
+      <c r="D13">
+        <v>39</v>
+      </c>
+      <c r="E13">
+        <v>1.1140000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14">
+        <v>62</v>
+      </c>
+      <c r="D14">
+        <v>64</v>
+      </c>
+      <c r="E14">
+        <v>1.032</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15">
+        <v>40</v>
+      </c>
+      <c r="D15">
+        <v>42</v>
+      </c>
+      <c r="E15">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16">
+        <v>63</v>
+      </c>
+      <c r="D16">
+        <v>61</v>
+      </c>
+      <c r="E16">
+        <v>0.96799999999999997</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17">
+        <v>68</v>
+      </c>
+      <c r="D17">
+        <v>71</v>
+      </c>
+      <c r="E17">
+        <v>1.044</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18">
+        <v>75</v>
+      </c>
+      <c r="D18">
+        <v>83</v>
+      </c>
+      <c r="E18">
+        <v>1.107</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19">
+        <v>89</v>
+      </c>
+      <c r="D19">
+        <v>89</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20">
+        <v>85</v>
+      </c>
+      <c r="D20">
+        <v>85</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21">
+        <v>88</v>
+      </c>
+      <c r="D21">
+        <v>89</v>
+      </c>
+      <c r="E21">
+        <v>1.0109999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>4</v>
+      </c>
+      <c r="C22">
+        <v>28</v>
+      </c>
+      <c r="D22">
+        <v>36</v>
+      </c>
+      <c r="E22">
+        <v>1.286</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23">
+        <v>38</v>
+      </c>
+      <c r="D23">
+        <v>41</v>
+      </c>
+      <c r="E23">
+        <v>1.079</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24">
+        <v>65</v>
+      </c>
+      <c r="D24">
+        <v>74</v>
+      </c>
+      <c r="E24">
+        <v>1.1379999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25">
+        <v>91</v>
+      </c>
+      <c r="D25">
+        <v>93</v>
+      </c>
+      <c r="E25">
+        <v>1.022</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26">
+        <v>83</v>
+      </c>
+      <c r="D26">
+        <v>83</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27">
+        <v>109</v>
+      </c>
+      <c r="D27">
+        <v>105</v>
+      </c>
+      <c r="E27">
+        <v>0.96299999999999997</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28">
+        <v>140</v>
+      </c>
+      <c r="D28">
+        <v>146</v>
+      </c>
+      <c r="E28">
+        <v>1.0429999999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>13</v>
+      </c>
+      <c r="C29">
+        <v>128</v>
+      </c>
+      <c r="D29">
+        <v>134</v>
+      </c>
+      <c r="E29">
+        <v>1.0469999999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30">
+        <v>119</v>
+      </c>
+      <c r="D30">
+        <v>117</v>
+      </c>
+      <c r="E30">
+        <v>0.98299999999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31">
+        <v>138</v>
+      </c>
+      <c r="D31">
+        <v>146</v>
+      </c>
+      <c r="E31">
+        <v>1.0580000000000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32">
+        <v>396</v>
+      </c>
+      <c r="D32">
+        <v>422</v>
+      </c>
+      <c r="E32">
+        <v>1.0660000000000001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33">
+        <v>329</v>
+      </c>
+      <c r="D33">
+        <v>339</v>
+      </c>
+      <c r="E33">
+        <v>1.03</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>16</v>
+      </c>
+      <c r="B34" t="s">
+        <v>19</v>
+      </c>
+      <c r="C34">
+        <v>323</v>
+      </c>
+      <c r="D34">
+        <v>310</v>
+      </c>
+      <c r="E34">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B35" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35">
+        <v>218</v>
+      </c>
+      <c r="D35">
+        <v>218</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>21</v>
+      </c>
+      <c r="B36" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36">
+        <v>250</v>
+      </c>
+      <c r="D36">
+        <v>257</v>
+      </c>
+      <c r="E36">
+        <v>1.028</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37">
+        <v>217</v>
+      </c>
+      <c r="D37">
+        <v>217</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>21</v>
+      </c>
+      <c r="B38" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38">
+        <v>226</v>
+      </c>
+      <c r="D38">
+        <v>242</v>
+      </c>
+      <c r="E38">
+        <v>1.071</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" t="s">
+        <v>20</v>
+      </c>
+      <c r="C39">
+        <v>214</v>
+      </c>
+      <c r="D39">
+        <v>199</v>
+      </c>
+      <c r="E39">
+        <v>0.93</v>
       </c>
     </row>
   </sheetData>
@@ -2264,7 +2261,7 @@
         <v>34</v>
       </c>
       <c r="C2">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2297,7 +2294,7 @@
         <v>35</v>
       </c>
       <c r="C5">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2330,7 +2327,7 @@
         <v>34</v>
       </c>
       <c r="C8">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2341,7 +2338,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2363,7 +2360,7 @@
         <v>34</v>
       </c>
       <c r="C11">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
   </sheetData>
@@ -2373,7 +2370,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD19485A-0629-47F9-A5AD-80ABA7A6E076}">
-  <dimension ref="A1:C249"/>
+  <dimension ref="A1:C251"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -2411,7 +2408,7 @@
         <v>46008</v>
       </c>
       <c r="C3" s="9">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2477,7 +2474,7 @@
         <v>46013</v>
       </c>
       <c r="C9" s="9">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2609,7 +2606,7 @@
         <v>46080</v>
       </c>
       <c r="C21" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -2716,10 +2713,10 @@
         <v>16</v>
       </c>
       <c r="B31" s="8">
-        <v>46098</v>
+        <v>46182</v>
       </c>
       <c r="C31" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -2727,10 +2724,10 @@
         <v>16</v>
       </c>
       <c r="B32" s="5">
-        <v>46181</v>
+        <v>46098</v>
       </c>
       <c r="C32" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -2738,10 +2735,10 @@
         <v>16</v>
       </c>
       <c r="B33" s="8">
-        <v>46084</v>
+        <v>46181</v>
       </c>
       <c r="C33" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -2749,10 +2746,10 @@
         <v>16</v>
       </c>
       <c r="B34" s="5">
-        <v>46160</v>
+        <v>46084</v>
       </c>
       <c r="C34" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -2760,10 +2757,10 @@
         <v>16</v>
       </c>
       <c r="B35" s="8">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="C35" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -2771,10 +2768,10 @@
         <v>16</v>
       </c>
       <c r="B36" s="5">
-        <v>46099</v>
+        <v>46167</v>
       </c>
       <c r="C36" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -2782,10 +2779,10 @@
         <v>16</v>
       </c>
       <c r="B37" s="8">
-        <v>46128</v>
+        <v>46099</v>
       </c>
       <c r="C37" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -2793,10 +2790,10 @@
         <v>16</v>
       </c>
       <c r="B38" s="5">
-        <v>46141</v>
+        <v>46128</v>
       </c>
       <c r="C38" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -2804,10 +2801,10 @@
         <v>16</v>
       </c>
       <c r="B39" s="8">
-        <v>46132</v>
+        <v>46141</v>
       </c>
       <c r="C39" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -2815,10 +2812,10 @@
         <v>16</v>
       </c>
       <c r="B40" s="5">
-        <v>46127</v>
+        <v>46132</v>
       </c>
       <c r="C40" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -2826,7 +2823,7 @@
         <v>16</v>
       </c>
       <c r="B41" s="8">
-        <v>46091</v>
+        <v>46127</v>
       </c>
       <c r="C41" s="9">
         <v>2</v>
@@ -2837,10 +2834,10 @@
         <v>16</v>
       </c>
       <c r="B42" s="5">
-        <v>46104</v>
+        <v>46091</v>
       </c>
       <c r="C42" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -2848,7 +2845,7 @@
         <v>16</v>
       </c>
       <c r="B43" s="8">
-        <v>46140</v>
+        <v>46104</v>
       </c>
       <c r="C43" s="9">
         <v>1</v>
@@ -2859,7 +2856,7 @@
         <v>16</v>
       </c>
       <c r="B44" s="5">
-        <v>46106</v>
+        <v>46140</v>
       </c>
       <c r="C44" s="6">
         <v>1</v>
@@ -2870,7 +2867,7 @@
         <v>16</v>
       </c>
       <c r="B45" s="8">
-        <v>46113</v>
+        <v>46106</v>
       </c>
       <c r="C45" s="9">
         <v>1</v>
@@ -2881,10 +2878,10 @@
         <v>16</v>
       </c>
       <c r="B46" s="5">
-        <v>46090</v>
+        <v>46113</v>
       </c>
       <c r="C46" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -2892,10 +2889,10 @@
         <v>16</v>
       </c>
       <c r="B47" s="8">
-        <v>46139</v>
+        <v>46090</v>
       </c>
       <c r="C47" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -2903,7 +2900,7 @@
         <v>16</v>
       </c>
       <c r="B48" s="5">
-        <v>46148</v>
+        <v>46139</v>
       </c>
       <c r="C48" s="6">
         <v>1</v>
@@ -2914,7 +2911,7 @@
         <v>16</v>
       </c>
       <c r="B49" s="8">
-        <v>46175</v>
+        <v>46148</v>
       </c>
       <c r="C49" s="9">
         <v>1</v>
@@ -2925,7 +2922,7 @@
         <v>16</v>
       </c>
       <c r="B50" s="5">
-        <v>46125</v>
+        <v>46175</v>
       </c>
       <c r="C50" s="6">
         <v>1</v>
@@ -2936,7 +2933,7 @@
         <v>16</v>
       </c>
       <c r="B51" s="8">
-        <v>46093</v>
+        <v>46125</v>
       </c>
       <c r="C51" s="9">
         <v>1</v>
@@ -2947,10 +2944,10 @@
         <v>16</v>
       </c>
       <c r="B52" s="5">
-        <v>46177</v>
+        <v>46093</v>
       </c>
       <c r="C52" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
@@ -2958,10 +2955,10 @@
         <v>16</v>
       </c>
       <c r="B53" s="8">
-        <v>46156</v>
+        <v>46177</v>
       </c>
       <c r="C53" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -2969,7 +2966,7 @@
         <v>16</v>
       </c>
       <c r="B54" s="5">
-        <v>46092</v>
+        <v>46156</v>
       </c>
       <c r="C54" s="6">
         <v>1</v>
@@ -2980,7 +2977,7 @@
         <v>16</v>
       </c>
       <c r="B55" s="8">
-        <v>46101</v>
+        <v>46092</v>
       </c>
       <c r="C55" s="9">
         <v>1</v>
@@ -2988,13 +2985,13 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B56" s="5">
-        <v>46007</v>
+        <v>46101</v>
       </c>
       <c r="C56" s="6">
-        <v>78</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -3002,10 +2999,10 @@
         <v>14</v>
       </c>
       <c r="B57" s="8">
-        <v>46009</v>
+        <v>46007</v>
       </c>
       <c r="C57" s="9">
-        <v>34</v>
+        <v>78</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -3013,10 +3010,10 @@
         <v>14</v>
       </c>
       <c r="B58" s="5">
-        <v>46000</v>
+        <v>46009</v>
       </c>
       <c r="C58" s="6">
-        <v>80</v>
+        <v>34</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -3024,10 +3021,10 @@
         <v>14</v>
       </c>
       <c r="B59" s="8">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C59" s="9">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -3035,10 +3032,10 @@
         <v>14</v>
       </c>
       <c r="B60" s="5">
-        <v>46006</v>
+        <v>46001</v>
       </c>
       <c r="C60" s="6">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -3046,10 +3043,10 @@
         <v>14</v>
       </c>
       <c r="B61" s="8">
-        <v>46010</v>
+        <v>46006</v>
       </c>
       <c r="C61" s="9">
-        <v>24</v>
+        <v>79</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -3057,10 +3054,10 @@
         <v>14</v>
       </c>
       <c r="B62" s="5">
-        <v>46014</v>
+        <v>46010</v>
       </c>
       <c r="C62" s="6">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -3068,10 +3065,10 @@
         <v>14</v>
       </c>
       <c r="B63" s="8">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="C63" s="9">
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -3079,10 +3076,10 @@
         <v>14</v>
       </c>
       <c r="B64" s="5">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C64" s="6">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -3090,10 +3087,10 @@
         <v>14</v>
       </c>
       <c r="B65" s="8">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="C65" s="9">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -3101,10 +3098,10 @@
         <v>14</v>
       </c>
       <c r="B66" s="5">
-        <v>46013</v>
+        <v>46003</v>
       </c>
       <c r="C66" s="6">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -3112,10 +3109,10 @@
         <v>14</v>
       </c>
       <c r="B67" s="8">
-        <v>46022</v>
+        <v>46013</v>
       </c>
       <c r="C67" s="9">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -3123,10 +3120,10 @@
         <v>14</v>
       </c>
       <c r="B68" s="5">
-        <v>46080</v>
+        <v>46022</v>
       </c>
       <c r="C68" s="6">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -3134,10 +3131,10 @@
         <v>14</v>
       </c>
       <c r="B69" s="8">
-        <v>46084</v>
+        <v>46080</v>
       </c>
       <c r="C69" s="9">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -3145,10 +3142,10 @@
         <v>14</v>
       </c>
       <c r="B70" s="5">
-        <v>46125</v>
+        <v>46084</v>
       </c>
       <c r="C70" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -3156,10 +3153,10 @@
         <v>14</v>
       </c>
       <c r="B71" s="8">
-        <v>46091</v>
+        <v>46125</v>
       </c>
       <c r="C71" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -3167,10 +3164,10 @@
         <v>14</v>
       </c>
       <c r="B72" s="5">
-        <v>46083</v>
+        <v>46091</v>
       </c>
       <c r="C72" s="6">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -3178,10 +3175,10 @@
         <v>14</v>
       </c>
       <c r="B73" s="8">
-        <v>46105</v>
+        <v>46083</v>
       </c>
       <c r="C73" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -3189,10 +3186,10 @@
         <v>14</v>
       </c>
       <c r="B74" s="5">
-        <v>46077</v>
+        <v>46105</v>
       </c>
       <c r="C74" s="6">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -3200,10 +3197,10 @@
         <v>14</v>
       </c>
       <c r="B75" s="8">
-        <v>46118</v>
+        <v>46077</v>
       </c>
       <c r="C75" s="9">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -3211,10 +3208,10 @@
         <v>14</v>
       </c>
       <c r="B76" s="5">
-        <v>46078</v>
+        <v>46118</v>
       </c>
       <c r="C76" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -3222,10 +3219,10 @@
         <v>14</v>
       </c>
       <c r="B77" s="8">
-        <v>46099</v>
+        <v>46078</v>
       </c>
       <c r="C77" s="9">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -3233,10 +3230,10 @@
         <v>14</v>
       </c>
       <c r="B78" s="5">
-        <v>46104</v>
+        <v>46099</v>
       </c>
       <c r="C78" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -3244,10 +3241,10 @@
         <v>14</v>
       </c>
       <c r="B79" s="8">
-        <v>46107</v>
+        <v>46104</v>
       </c>
       <c r="C79" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -3409,7 +3406,7 @@
         <v>14</v>
       </c>
       <c r="B94" s="5">
-        <v>46092</v>
+        <v>46174</v>
       </c>
       <c r="C94" s="6">
         <v>1</v>
@@ -3420,10 +3417,10 @@
         <v>14</v>
       </c>
       <c r="B95" s="8">
-        <v>46021</v>
+        <v>46092</v>
       </c>
       <c r="C95" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -3431,10 +3428,10 @@
         <v>14</v>
       </c>
       <c r="B96" s="5">
-        <v>46086</v>
+        <v>46021</v>
       </c>
       <c r="C96" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -3442,10 +3439,10 @@
         <v>14</v>
       </c>
       <c r="B97" s="8">
-        <v>46147</v>
+        <v>46086</v>
       </c>
       <c r="C97" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -3453,7 +3450,7 @@
         <v>14</v>
       </c>
       <c r="B98" s="5">
-        <v>46134</v>
+        <v>46147</v>
       </c>
       <c r="C98" s="6">
         <v>1</v>
@@ -3461,13 +3458,13 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B99" s="8">
-        <v>46003</v>
+        <v>46134</v>
       </c>
       <c r="C99" s="9">
-        <v>95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -3475,10 +3472,10 @@
         <v>3</v>
       </c>
       <c r="B100" s="5">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="C100" s="6">
-        <v>115</v>
+        <v>95</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -3486,10 +3483,10 @@
         <v>3</v>
       </c>
       <c r="B101" s="8">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C101" s="9">
-        <v>15</v>
+        <v>115</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -3497,10 +3494,10 @@
         <v>3</v>
       </c>
       <c r="B102" s="5">
-        <v>46000</v>
+        <v>46008</v>
       </c>
       <c r="C102" s="6">
-        <v>98</v>
+        <v>14</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -3508,10 +3505,10 @@
         <v>3</v>
       </c>
       <c r="B103" s="8">
-        <v>46007</v>
+        <v>46000</v>
       </c>
       <c r="C103" s="9">
-        <v>40</v>
+        <v>98</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -3519,10 +3516,10 @@
         <v>3</v>
       </c>
       <c r="B104" s="5">
-        <v>46001</v>
+        <v>46007</v>
       </c>
       <c r="C104" s="6">
-        <v>91</v>
+        <v>40</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -3530,10 +3527,10 @@
         <v>3</v>
       </c>
       <c r="B105" s="8">
-        <v>46010</v>
+        <v>46001</v>
       </c>
       <c r="C105" s="9">
-        <v>9</v>
+        <v>91</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -3541,10 +3538,10 @@
         <v>3</v>
       </c>
       <c r="B106" s="5">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="C106" s="6">
-        <v>84</v>
+        <v>9</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -3552,10 +3549,10 @@
         <v>3</v>
       </c>
       <c r="B107" s="8">
-        <v>46009</v>
+        <v>46006</v>
       </c>
       <c r="C107" s="9">
-        <v>2</v>
+        <v>84</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -3563,10 +3560,10 @@
         <v>3</v>
       </c>
       <c r="B108" s="5">
-        <v>46015</v>
+        <v>46009</v>
       </c>
       <c r="C108" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -3574,10 +3571,10 @@
         <v>3</v>
       </c>
       <c r="B109" s="8">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="C109" s="9">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -3585,10 +3582,10 @@
         <v>3</v>
       </c>
       <c r="B110" s="5">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="C110" s="6">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -3596,10 +3593,10 @@
         <v>3</v>
       </c>
       <c r="B111" s="8">
-        <v>46021</v>
+        <v>46013</v>
       </c>
       <c r="C111" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -3607,10 +3604,10 @@
         <v>3</v>
       </c>
       <c r="B112" s="5">
-        <v>46077</v>
+        <v>46021</v>
       </c>
       <c r="C112" s="6">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -3618,10 +3615,10 @@
         <v>3</v>
       </c>
       <c r="B113" s="8">
-        <v>46167</v>
+        <v>46077</v>
       </c>
       <c r="C113" s="9">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -3629,10 +3626,10 @@
         <v>3</v>
       </c>
       <c r="B114" s="5">
-        <v>46090</v>
+        <v>46167</v>
       </c>
       <c r="C114" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -3640,10 +3637,10 @@
         <v>3</v>
       </c>
       <c r="B115" s="8">
-        <v>46170</v>
+        <v>46090</v>
       </c>
       <c r="C115" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -3651,7 +3648,7 @@
         <v>3</v>
       </c>
       <c r="B116" s="5">
-        <v>46093</v>
+        <v>46170</v>
       </c>
       <c r="C116" s="6">
         <v>1</v>
@@ -3662,10 +3659,10 @@
         <v>3</v>
       </c>
       <c r="B117" s="8">
-        <v>46078</v>
+        <v>46093</v>
       </c>
       <c r="C117" s="9">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -3673,7 +3670,7 @@
         <v>3</v>
       </c>
       <c r="B118" s="5">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="C118" s="6">
         <v>7</v>
@@ -3684,10 +3681,10 @@
         <v>3</v>
       </c>
       <c r="B119" s="8">
-        <v>46134</v>
+        <v>46084</v>
       </c>
       <c r="C119" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -3695,10 +3692,10 @@
         <v>3</v>
       </c>
       <c r="B120" s="5">
-        <v>46083</v>
+        <v>46134</v>
       </c>
       <c r="C120" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -3706,10 +3703,10 @@
         <v>3</v>
       </c>
       <c r="B121" s="8">
-        <v>46022</v>
+        <v>46083</v>
       </c>
       <c r="C121" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -3717,10 +3714,10 @@
         <v>3</v>
       </c>
       <c r="B122" s="5">
-        <v>46114</v>
+        <v>46022</v>
       </c>
       <c r="C122" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -3728,10 +3725,10 @@
         <v>3</v>
       </c>
       <c r="B123" s="8">
-        <v>46135</v>
+        <v>46114</v>
       </c>
       <c r="C123" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -3739,10 +3736,10 @@
         <v>3</v>
       </c>
       <c r="B124" s="5">
-        <v>46168</v>
+        <v>46135</v>
       </c>
       <c r="C124" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -3750,7 +3747,7 @@
         <v>3</v>
       </c>
       <c r="B125" s="8">
-        <v>46126</v>
+        <v>46168</v>
       </c>
       <c r="C125" s="9">
         <v>3</v>
@@ -3761,7 +3758,7 @@
         <v>3</v>
       </c>
       <c r="B126" s="5">
-        <v>46120</v>
+        <v>46126</v>
       </c>
       <c r="C126" s="6">
         <v>3</v>
@@ -3772,10 +3769,10 @@
         <v>3</v>
       </c>
       <c r="B127" s="8">
-        <v>46127</v>
+        <v>46120</v>
       </c>
       <c r="C127" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -3783,7 +3780,7 @@
         <v>3</v>
       </c>
       <c r="B128" s="5">
-        <v>46087</v>
+        <v>46127</v>
       </c>
       <c r="C128" s="6">
         <v>1</v>
@@ -3794,7 +3791,7 @@
         <v>3</v>
       </c>
       <c r="B129" s="8">
-        <v>46108</v>
+        <v>46087</v>
       </c>
       <c r="C129" s="9">
         <v>1</v>
@@ -3805,7 +3802,7 @@
         <v>3</v>
       </c>
       <c r="B130" s="5">
-        <v>46020</v>
+        <v>46108</v>
       </c>
       <c r="C130" s="6">
         <v>1</v>
@@ -3816,7 +3813,7 @@
         <v>3</v>
       </c>
       <c r="B131" s="8">
-        <v>46097</v>
+        <v>46020</v>
       </c>
       <c r="C131" s="9">
         <v>1</v>
@@ -3827,7 +3824,7 @@
         <v>3</v>
       </c>
       <c r="B132" s="5">
-        <v>46177</v>
+        <v>46097</v>
       </c>
       <c r="C132" s="6">
         <v>1</v>
@@ -3838,10 +3835,10 @@
         <v>3</v>
       </c>
       <c r="B133" s="8">
-        <v>46161</v>
+        <v>46177</v>
       </c>
       <c r="C133" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -3849,10 +3846,10 @@
         <v>3</v>
       </c>
       <c r="B134" s="5">
-        <v>46129</v>
+        <v>46161</v>
       </c>
       <c r="C134" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -3860,7 +3857,7 @@
         <v>3</v>
       </c>
       <c r="B135" s="8">
-        <v>46080</v>
+        <v>46129</v>
       </c>
       <c r="C135" s="9">
         <v>1</v>
@@ -3871,7 +3868,7 @@
         <v>3</v>
       </c>
       <c r="B136" s="5">
-        <v>46101</v>
+        <v>46080</v>
       </c>
       <c r="C136" s="6">
         <v>1</v>
@@ -3882,7 +3879,7 @@
         <v>3</v>
       </c>
       <c r="B137" s="8">
-        <v>46155</v>
+        <v>46101</v>
       </c>
       <c r="C137" s="9">
         <v>1</v>
@@ -3893,7 +3890,7 @@
         <v>3</v>
       </c>
       <c r="B138" s="5">
-        <v>46150</v>
+        <v>46155</v>
       </c>
       <c r="C138" s="6">
         <v>1</v>
@@ -3904,7 +3901,7 @@
         <v>3</v>
       </c>
       <c r="B139" s="8">
-        <v>46141</v>
+        <v>46150</v>
       </c>
       <c r="C139" s="9">
         <v>1</v>
@@ -3915,7 +3912,7 @@
         <v>3</v>
       </c>
       <c r="B140" s="5">
-        <v>46085</v>
+        <v>46141</v>
       </c>
       <c r="C140" s="6">
         <v>1</v>
@@ -3926,7 +3923,7 @@
         <v>3</v>
       </c>
       <c r="B141" s="8">
-        <v>46148</v>
+        <v>46085</v>
       </c>
       <c r="C141" s="9">
         <v>1</v>
@@ -3937,10 +3934,10 @@
         <v>3</v>
       </c>
       <c r="B142" s="5">
-        <v>46118</v>
+        <v>46148</v>
       </c>
       <c r="C142" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -3948,21 +3945,21 @@
         <v>3</v>
       </c>
       <c r="B143" s="8">
-        <v>46079</v>
+        <v>46118</v>
       </c>
       <c r="C143" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B144" s="5">
-        <v>46003</v>
+        <v>46079</v>
       </c>
       <c r="C144" s="6">
-        <v>92</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -3970,10 +3967,10 @@
         <v>15</v>
       </c>
       <c r="B145" s="8">
-        <v>46000</v>
+        <v>46003</v>
       </c>
       <c r="C145" s="9">
-        <v>132</v>
+        <v>92</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -3981,10 +3978,10 @@
         <v>15</v>
       </c>
       <c r="B146" s="5">
-        <v>46006</v>
+        <v>46000</v>
       </c>
       <c r="C146" s="6">
-        <v>173</v>
+        <v>132</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -3992,10 +3989,10 @@
         <v>15</v>
       </c>
       <c r="B147" s="8">
-        <v>46001</v>
+        <v>46006</v>
       </c>
       <c r="C147" s="9">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -4003,10 +4000,10 @@
         <v>15</v>
       </c>
       <c r="B148" s="5">
-        <v>46014</v>
+        <v>46001</v>
       </c>
       <c r="C148" s="6">
-        <v>16</v>
+        <v>174</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -4014,10 +4011,10 @@
         <v>15</v>
       </c>
       <c r="B149" s="8">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="C149" s="9">
-        <v>171</v>
+        <v>16</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -4025,10 +4022,10 @@
         <v>15</v>
       </c>
       <c r="B150" s="5">
-        <v>46009</v>
+        <v>46002</v>
       </c>
       <c r="C150" s="6">
-        <v>19</v>
+        <v>171</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -4036,7 +4033,7 @@
         <v>15</v>
       </c>
       <c r="B151" s="8">
-        <v>46010</v>
+        <v>46009</v>
       </c>
       <c r="C151" s="9">
         <v>19</v>
@@ -4047,10 +4044,10 @@
         <v>15</v>
       </c>
       <c r="B152" s="5">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="C152" s="6">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -4058,10 +4055,10 @@
         <v>15</v>
       </c>
       <c r="B153" s="8">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="C153" s="9">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -4069,10 +4066,10 @@
         <v>15</v>
       </c>
       <c r="B154" s="5">
-        <v>46013</v>
+        <v>46007</v>
       </c>
       <c r="C154" s="6">
-        <v>12</v>
+        <v>43</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -4080,10 +4077,10 @@
         <v>15</v>
       </c>
       <c r="B155" s="8">
-        <v>46080</v>
+        <v>46013</v>
       </c>
       <c r="C155" s="9">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -4091,10 +4088,10 @@
         <v>15</v>
       </c>
       <c r="B156" s="5">
-        <v>46090</v>
+        <v>46080</v>
       </c>
       <c r="C156" s="6">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -4102,10 +4099,10 @@
         <v>15</v>
       </c>
       <c r="B157" s="8">
-        <v>46079</v>
+        <v>46090</v>
       </c>
       <c r="C157" s="9">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -4113,10 +4110,10 @@
         <v>15</v>
       </c>
       <c r="B158" s="5">
-        <v>46015</v>
+        <v>46079</v>
       </c>
       <c r="C158" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -4124,10 +4121,10 @@
         <v>15</v>
       </c>
       <c r="B159" s="8">
-        <v>46085</v>
+        <v>46015</v>
       </c>
       <c r="C159" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -4135,10 +4132,10 @@
         <v>15</v>
       </c>
       <c r="B160" s="5">
-        <v>46098</v>
+        <v>46085</v>
       </c>
       <c r="C160" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -4146,10 +4143,10 @@
         <v>15</v>
       </c>
       <c r="B161" s="8">
-        <v>46021</v>
+        <v>46098</v>
       </c>
       <c r="C161" s="9">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -4157,10 +4154,10 @@
         <v>15</v>
       </c>
       <c r="B162" s="5">
-        <v>46078</v>
+        <v>46021</v>
       </c>
       <c r="C162" s="6">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -4168,10 +4165,10 @@
         <v>15</v>
       </c>
       <c r="B163" s="8">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="C163" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -4179,10 +4176,10 @@
         <v>15</v>
       </c>
       <c r="B164" s="5">
-        <v>46128</v>
+        <v>46084</v>
       </c>
       <c r="C164" s="6">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -4190,10 +4187,10 @@
         <v>15</v>
       </c>
       <c r="B165" s="8">
-        <v>46083</v>
+        <v>46128</v>
       </c>
       <c r="C165" s="9">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -4201,10 +4198,10 @@
         <v>15</v>
       </c>
       <c r="B166" s="5">
-        <v>46153</v>
+        <v>46083</v>
       </c>
       <c r="C166" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -4410,7 +4407,7 @@
         <v>15</v>
       </c>
       <c r="B185" s="8">
-        <v>46093</v>
+        <v>46181</v>
       </c>
       <c r="C185" s="9">
         <v>1</v>
@@ -4421,7 +4418,7 @@
         <v>15</v>
       </c>
       <c r="B186" s="5">
-        <v>46022</v>
+        <v>46093</v>
       </c>
       <c r="C186" s="6">
         <v>1</v>
@@ -4432,7 +4429,7 @@
         <v>15</v>
       </c>
       <c r="B187" s="8">
-        <v>46087</v>
+        <v>46022</v>
       </c>
       <c r="C187" s="9">
         <v>1</v>
@@ -4443,10 +4440,10 @@
         <v>15</v>
       </c>
       <c r="B188" s="5">
-        <v>46030</v>
+        <v>46087</v>
       </c>
       <c r="C188" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -4454,10 +4451,10 @@
         <v>15</v>
       </c>
       <c r="B189" s="8">
-        <v>46176</v>
+        <v>46030</v>
       </c>
       <c r="C189" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -4465,7 +4462,7 @@
         <v>15</v>
       </c>
       <c r="B190" s="5">
-        <v>46101</v>
+        <v>46176</v>
       </c>
       <c r="C190" s="6">
         <v>1</v>
@@ -4476,7 +4473,7 @@
         <v>15</v>
       </c>
       <c r="B191" s="8">
-        <v>46142</v>
+        <v>46101</v>
       </c>
       <c r="C191" s="9">
         <v>1</v>
@@ -4484,13 +4481,13 @@
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B192" s="5">
-        <v>46001</v>
+        <v>46142</v>
       </c>
       <c r="C192" s="6">
-        <v>153</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -4498,10 +4495,10 @@
         <v>21</v>
       </c>
       <c r="B193" s="8">
-        <v>46008</v>
+        <v>46001</v>
       </c>
       <c r="C193" s="9">
-        <v>38</v>
+        <v>153</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -4509,10 +4506,10 @@
         <v>21</v>
       </c>
       <c r="B194" s="5">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="C194" s="6">
-        <v>70</v>
+        <v>38</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -4520,10 +4517,10 @@
         <v>21</v>
       </c>
       <c r="B195" s="8">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="C195" s="9">
-        <v>111</v>
+        <v>70</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -4531,10 +4528,10 @@
         <v>21</v>
       </c>
       <c r="B196" s="5">
-        <v>46006</v>
+        <v>46002</v>
       </c>
       <c r="C196" s="6">
-        <v>146</v>
+        <v>111</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -4542,10 +4539,10 @@
         <v>21</v>
       </c>
       <c r="B197" s="8">
-        <v>46007</v>
+        <v>46006</v>
       </c>
       <c r="C197" s="9">
-        <v>45</v>
+        <v>146</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -4553,10 +4550,10 @@
         <v>21</v>
       </c>
       <c r="B198" s="5">
-        <v>46000</v>
+        <v>46007</v>
       </c>
       <c r="C198" s="6">
-        <v>127</v>
+        <v>45</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -4564,10 +4561,10 @@
         <v>21</v>
       </c>
       <c r="B199" s="8">
-        <v>46084</v>
+        <v>46000</v>
       </c>
       <c r="C199" s="9">
-        <v>10</v>
+        <v>127</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -4575,10 +4572,10 @@
         <v>21</v>
       </c>
       <c r="B200" s="5">
-        <v>46014</v>
+        <v>46084</v>
       </c>
       <c r="C200" s="6">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -4586,10 +4583,10 @@
         <v>21</v>
       </c>
       <c r="B201" s="8">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="C201" s="9">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -4597,10 +4594,10 @@
         <v>21</v>
       </c>
       <c r="B202" s="5">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="C202" s="6">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -4608,10 +4605,10 @@
         <v>21</v>
       </c>
       <c r="B203" s="8">
-        <v>46021</v>
+        <v>46010</v>
       </c>
       <c r="C203" s="9">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -4619,10 +4616,10 @@
         <v>21</v>
       </c>
       <c r="B204" s="5">
-        <v>46009</v>
+        <v>46021</v>
       </c>
       <c r="C204" s="6">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -4630,10 +4627,10 @@
         <v>21</v>
       </c>
       <c r="B205" s="8">
-        <v>46083</v>
+        <v>46009</v>
       </c>
       <c r="C205" s="9">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -4641,10 +4638,10 @@
         <v>21</v>
       </c>
       <c r="B206" s="5">
-        <v>46157</v>
+        <v>46083</v>
       </c>
       <c r="C206" s="6">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -4652,10 +4649,10 @@
         <v>21</v>
       </c>
       <c r="B207" s="8">
-        <v>46079</v>
+        <v>46157</v>
       </c>
       <c r="C207" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4663,10 +4660,10 @@
         <v>21</v>
       </c>
       <c r="B208" s="5">
-        <v>46167</v>
+        <v>46079</v>
       </c>
       <c r="C208" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4674,10 +4671,10 @@
         <v>21</v>
       </c>
       <c r="B209" s="8">
-        <v>46077</v>
+        <v>46167</v>
       </c>
       <c r="C209" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4685,10 +4682,10 @@
         <v>21</v>
       </c>
       <c r="B210" s="5">
-        <v>46035</v>
+        <v>46077</v>
       </c>
       <c r="C210" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -4696,10 +4693,10 @@
         <v>21</v>
       </c>
       <c r="B211" s="8">
-        <v>46085</v>
+        <v>46035</v>
       </c>
       <c r="C211" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -4707,10 +4704,10 @@
         <v>21</v>
       </c>
       <c r="B212" s="5">
-        <v>46120</v>
+        <v>46085</v>
       </c>
       <c r="C212" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4718,10 +4715,10 @@
         <v>21</v>
       </c>
       <c r="B213" s="8">
-        <v>46114</v>
+        <v>46120</v>
       </c>
       <c r="C213" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4729,10 +4726,10 @@
         <v>21</v>
       </c>
       <c r="B214" s="5">
-        <v>46094</v>
+        <v>46114</v>
       </c>
       <c r="C214" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4740,10 +4737,10 @@
         <v>21</v>
       </c>
       <c r="B215" s="8">
-        <v>46080</v>
+        <v>46094</v>
       </c>
       <c r="C215" s="9">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4751,10 +4748,10 @@
         <v>21</v>
       </c>
       <c r="B216" s="5">
-        <v>46127</v>
+        <v>46080</v>
       </c>
       <c r="C216" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4762,7 +4759,7 @@
         <v>21</v>
       </c>
       <c r="B217" s="8">
-        <v>46091</v>
+        <v>46127</v>
       </c>
       <c r="C217" s="9">
         <v>2</v>
@@ -4773,10 +4770,10 @@
         <v>21</v>
       </c>
       <c r="B218" s="5">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="C218" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -4784,10 +4781,10 @@
         <v>21</v>
       </c>
       <c r="B219" s="8">
-        <v>46020</v>
+        <v>46090</v>
       </c>
       <c r="C219" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4795,10 +4792,10 @@
         <v>21</v>
       </c>
       <c r="B220" s="5">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="C220" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -4806,10 +4803,10 @@
         <v>21</v>
       </c>
       <c r="B221" s="8">
-        <v>46078</v>
+        <v>46015</v>
       </c>
       <c r="C221" s="9">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -4817,10 +4814,10 @@
         <v>21</v>
       </c>
       <c r="B222" s="5">
-        <v>46148</v>
+        <v>46078</v>
       </c>
       <c r="C222" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -4828,7 +4825,7 @@
         <v>21</v>
       </c>
       <c r="B223" s="8">
-        <v>46105</v>
+        <v>46148</v>
       </c>
       <c r="C223" s="9">
         <v>2</v>
@@ -4839,10 +4836,10 @@
         <v>21</v>
       </c>
       <c r="B224" s="5">
-        <v>46087</v>
+        <v>46105</v>
       </c>
       <c r="C224" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -4850,7 +4847,7 @@
         <v>21</v>
       </c>
       <c r="B225" s="8">
-        <v>46107</v>
+        <v>46087</v>
       </c>
       <c r="C225" s="9">
         <v>3</v>
@@ -4861,10 +4858,10 @@
         <v>21</v>
       </c>
       <c r="B226" s="5">
-        <v>46086</v>
+        <v>46107</v>
       </c>
       <c r="C226" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -4872,10 +4869,10 @@
         <v>21</v>
       </c>
       <c r="B227" s="8">
-        <v>46106</v>
+        <v>46086</v>
       </c>
       <c r="C227" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -4883,10 +4880,10 @@
         <v>21</v>
       </c>
       <c r="B228" s="5">
-        <v>46150</v>
+        <v>46106</v>
       </c>
       <c r="C228" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -4894,7 +4891,7 @@
         <v>21</v>
       </c>
       <c r="B229" s="8">
-        <v>46104</v>
+        <v>46150</v>
       </c>
       <c r="C229" s="9">
         <v>3</v>
@@ -4905,10 +4902,10 @@
         <v>21</v>
       </c>
       <c r="B230" s="5">
-        <v>46118</v>
+        <v>46104</v>
       </c>
       <c r="C230" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -4916,10 +4913,10 @@
         <v>21</v>
       </c>
       <c r="B231" s="8">
-        <v>46076</v>
+        <v>46118</v>
       </c>
       <c r="C231" s="9">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -4927,10 +4924,10 @@
         <v>21</v>
       </c>
       <c r="B232" s="5">
-        <v>46154</v>
+        <v>46076</v>
       </c>
       <c r="C232" s="6">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -4938,10 +4935,10 @@
         <v>21</v>
       </c>
       <c r="B233" s="8">
-        <v>46093</v>
+        <v>46182</v>
       </c>
       <c r="C233" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -4949,7 +4946,7 @@
         <v>21</v>
       </c>
       <c r="B234" s="5">
-        <v>46122</v>
+        <v>46154</v>
       </c>
       <c r="C234" s="6">
         <v>1</v>
@@ -4960,7 +4957,7 @@
         <v>21</v>
       </c>
       <c r="B235" s="8">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="C235" s="9">
         <v>3</v>
@@ -4971,10 +4968,10 @@
         <v>21</v>
       </c>
       <c r="B236" s="5">
-        <v>46156</v>
+        <v>46122</v>
       </c>
       <c r="C236" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -4982,10 +4979,10 @@
         <v>21</v>
       </c>
       <c r="B237" s="8">
-        <v>46133</v>
+        <v>46092</v>
       </c>
       <c r="C237" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -4993,10 +4990,10 @@
         <v>21</v>
       </c>
       <c r="B238" s="5">
-        <v>46126</v>
+        <v>46156</v>
       </c>
       <c r="C238" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -5004,10 +5001,10 @@
         <v>21</v>
       </c>
       <c r="B239" s="8">
-        <v>46022</v>
+        <v>46133</v>
       </c>
       <c r="C239" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -5015,10 +5012,10 @@
         <v>21</v>
       </c>
       <c r="B240" s="5">
-        <v>46100</v>
+        <v>46126</v>
       </c>
       <c r="C240" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -5026,10 +5023,10 @@
         <v>21</v>
       </c>
       <c r="B241" s="8">
-        <v>46101</v>
+        <v>46022</v>
       </c>
       <c r="C241" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -5037,10 +5034,10 @@
         <v>21</v>
       </c>
       <c r="B242" s="5">
-        <v>46097</v>
+        <v>46100</v>
       </c>
       <c r="C242" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -5048,7 +5045,7 @@
         <v>21</v>
       </c>
       <c r="B243" s="8">
-        <v>46108</v>
+        <v>46101</v>
       </c>
       <c r="C243" s="9">
         <v>1</v>
@@ -5059,10 +5056,10 @@
         <v>21</v>
       </c>
       <c r="B244" s="5">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="C244" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -5070,7 +5067,7 @@
         <v>21</v>
       </c>
       <c r="B245" s="8">
-        <v>46113</v>
+        <v>46108</v>
       </c>
       <c r="C245" s="9">
         <v>1</v>
@@ -5081,10 +5078,10 @@
         <v>21</v>
       </c>
       <c r="B246" s="5">
-        <v>46142</v>
+        <v>46098</v>
       </c>
       <c r="C246" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -5092,7 +5089,7 @@
         <v>21</v>
       </c>
       <c r="B247" s="8">
-        <v>46153</v>
+        <v>46113</v>
       </c>
       <c r="C247" s="9">
         <v>1</v>
@@ -5103,7 +5100,7 @@
         <v>21</v>
       </c>
       <c r="B248" s="5">
-        <v>46031</v>
+        <v>46142</v>
       </c>
       <c r="C248" s="6">
         <v>1</v>
@@ -5114,9 +5111,31 @@
         <v>21</v>
       </c>
       <c r="B249" s="8">
+        <v>46153</v>
+      </c>
+      <c r="C249" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B250" s="5">
+        <v>46031</v>
+      </c>
+      <c r="C250" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B251" s="8">
         <v>46155</v>
       </c>
-      <c r="C249" s="9">
+      <c r="C251" s="9">
         <v>1</v>
       </c>
     </row>
@@ -5180,7 +5199,7 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E3">
         <v>5</v>
@@ -5336,7 +5355,7 @@
         <v>27</v>
       </c>
       <c r="E12">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -5370,7 +5389,7 @@
         <v>6</v>
       </c>
       <c r="E14">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -5421,7 +5440,7 @@
         <v>3</v>
       </c>
       <c r="E17">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -5574,7 +5593,7 @@
         <v>3</v>
       </c>
       <c r="E26">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -5591,7 +5610,7 @@
         <v>2</v>
       </c>
       <c r="E27">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -5676,7 +5695,7 @@
         <v>247</v>
       </c>
       <c r="E32">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -5687,13 +5706,13 @@
         <v>18</v>
       </c>
       <c r="C33">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D33">
         <v>8</v>
       </c>
       <c r="E33">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -5704,13 +5723,13 @@
         <v>19</v>
       </c>
       <c r="C34">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D34">
         <v>8</v>
       </c>
       <c r="E34">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -5744,7 +5763,7 @@
         <v>87</v>
       </c>
       <c r="E36">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -5805,7 +5824,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0916EAC6-1E7F-4924-9D0E-33749FD3E143}">
-  <dimension ref="A1:C353"/>
+  <dimension ref="A1:C351"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
@@ -5818,7 +5837,7 @@
         <v>37</v>
       </c>
       <c r="B1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C1" t="s">
         <v>36</v>
@@ -6005,7 +6024,7 @@
         <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -6016,7 +6035,7 @@
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -6027,7 +6046,7 @@
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -6049,7 +6068,7 @@
         <v>3</v>
       </c>
       <c r="B22" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -6071,7 +6090,7 @@
         <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -6093,7 +6112,7 @@
         <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -6104,7 +6123,7 @@
         <v>3</v>
       </c>
       <c r="B27" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -6115,7 +6134,7 @@
         <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C28">
         <v>1</v>
@@ -6126,7 +6145,7 @@
         <v>3</v>
       </c>
       <c r="B29" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C29">
         <v>1</v>
@@ -6137,7 +6156,7 @@
         <v>3</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -6148,7 +6167,7 @@
         <v>3</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C31">
         <v>1</v>
@@ -6159,7 +6178,7 @@
         <v>3</v>
       </c>
       <c r="B32" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -6170,7 +6189,7 @@
         <v>3</v>
       </c>
       <c r="B33" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -6181,7 +6200,7 @@
         <v>3</v>
       </c>
       <c r="B34" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -6192,7 +6211,7 @@
         <v>3</v>
       </c>
       <c r="B35" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -6203,7 +6222,7 @@
         <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -6214,7 +6233,7 @@
         <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="C37">
         <v>1</v>
@@ -6225,7 +6244,7 @@
         <v>3</v>
       </c>
       <c r="B38" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -6233,13 +6252,13 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B39" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -6247,7 +6266,7 @@
         <v>14</v>
       </c>
       <c r="B40" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="C40">
         <v>9</v>
@@ -6258,10 +6277,10 @@
         <v>14</v>
       </c>
       <c r="B41" t="s">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="C41">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -6269,10 +6288,10 @@
         <v>14</v>
       </c>
       <c r="B42" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="C42">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -6280,7 +6299,7 @@
         <v>14</v>
       </c>
       <c r="B43" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C43">
         <v>5</v>
@@ -6291,7 +6310,7 @@
         <v>14</v>
       </c>
       <c r="B44" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C44">
         <v>5</v>
@@ -6302,10 +6321,10 @@
         <v>14</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="C45">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -6313,7 +6332,7 @@
         <v>14</v>
       </c>
       <c r="B46" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="C46">
         <v>4</v>
@@ -6324,10 +6343,10 @@
         <v>14</v>
       </c>
       <c r="B47" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="C47">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -6335,7 +6354,7 @@
         <v>14</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="C48">
         <v>3</v>
@@ -6346,10 +6365,10 @@
         <v>14</v>
       </c>
       <c r="B49" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="C49">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -6357,7 +6376,7 @@
         <v>14</v>
       </c>
       <c r="B50" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="C50">
         <v>2</v>
@@ -6368,7 +6387,7 @@
         <v>14</v>
       </c>
       <c r="B51" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="C51">
         <v>2</v>
@@ -6379,7 +6398,7 @@
         <v>14</v>
       </c>
       <c r="B52" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="C52">
         <v>2</v>
@@ -6390,7 +6409,7 @@
         <v>14</v>
       </c>
       <c r="B53" t="s">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="C53">
         <v>2</v>
@@ -6401,7 +6420,7 @@
         <v>14</v>
       </c>
       <c r="B54" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="C54">
         <v>2</v>
@@ -6412,7 +6431,7 @@
         <v>14</v>
       </c>
       <c r="B55" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="C55">
         <v>2</v>
@@ -6423,7 +6442,7 @@
         <v>14</v>
       </c>
       <c r="B56" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C56">
         <v>2</v>
@@ -6434,7 +6453,7 @@
         <v>14</v>
       </c>
       <c r="B57" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C57">
         <v>2</v>
@@ -6445,7 +6464,7 @@
         <v>14</v>
       </c>
       <c r="B58" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C58">
         <v>2</v>
@@ -6456,7 +6475,7 @@
         <v>14</v>
       </c>
       <c r="B59" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C59">
         <v>2</v>
@@ -6467,7 +6486,7 @@
         <v>14</v>
       </c>
       <c r="B60" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C60">
         <v>2</v>
@@ -6478,7 +6497,7 @@
         <v>14</v>
       </c>
       <c r="B61" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C61">
         <v>2</v>
@@ -6489,7 +6508,7 @@
         <v>14</v>
       </c>
       <c r="B62" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C62">
         <v>2</v>
@@ -6500,10 +6519,10 @@
         <v>14</v>
       </c>
       <c r="B63" t="s">
-        <v>68</v>
+        <v>115</v>
       </c>
       <c r="C63">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -6511,7 +6530,7 @@
         <v>14</v>
       </c>
       <c r="B64" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -6522,7 +6541,7 @@
         <v>14</v>
       </c>
       <c r="B65" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -6533,7 +6552,7 @@
         <v>14</v>
       </c>
       <c r="B66" t="s">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -6544,7 +6563,7 @@
         <v>14</v>
       </c>
       <c r="B67" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -6555,7 +6574,7 @@
         <v>14</v>
       </c>
       <c r="B68" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -6566,7 +6585,7 @@
         <v>14</v>
       </c>
       <c r="B69" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -6577,7 +6596,7 @@
         <v>14</v>
       </c>
       <c r="B70" t="s">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -6588,7 +6607,7 @@
         <v>14</v>
       </c>
       <c r="B71" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -6599,7 +6618,7 @@
         <v>14</v>
       </c>
       <c r="B72" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -6610,7 +6629,7 @@
         <v>14</v>
       </c>
       <c r="B73" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -6621,7 +6640,7 @@
         <v>14</v>
       </c>
       <c r="B74" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -6632,7 +6651,7 @@
         <v>14</v>
       </c>
       <c r="B75" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -6643,7 +6662,7 @@
         <v>14</v>
       </c>
       <c r="B76" t="s">
-        <v>112</v>
+        <v>59</v>
       </c>
       <c r="C76">
         <v>1</v>
@@ -6654,7 +6673,7 @@
         <v>14</v>
       </c>
       <c r="B77" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="C77">
         <v>1</v>
@@ -6665,7 +6684,7 @@
         <v>14</v>
       </c>
       <c r="B78" t="s">
-        <v>71</v>
+        <v>102</v>
       </c>
       <c r="C78">
         <v>1</v>
@@ -6676,7 +6695,7 @@
         <v>14</v>
       </c>
       <c r="B79" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -6687,7 +6706,7 @@
         <v>14</v>
       </c>
       <c r="B80" t="s">
-        <v>57</v>
+        <v>109</v>
       </c>
       <c r="C80">
         <v>1</v>
@@ -6698,7 +6717,7 @@
         <v>14</v>
       </c>
       <c r="B81" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -6709,7 +6728,7 @@
         <v>14</v>
       </c>
       <c r="B82" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="C82">
         <v>1</v>
@@ -6720,7 +6739,7 @@
         <v>14</v>
       </c>
       <c r="B83" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -6731,7 +6750,7 @@
         <v>14</v>
       </c>
       <c r="B84" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="C84">
         <v>1</v>
@@ -6742,7 +6761,7 @@
         <v>14</v>
       </c>
       <c r="B85" t="s">
-        <v>107</v>
+        <v>51</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -6753,7 +6772,7 @@
         <v>14</v>
       </c>
       <c r="B86" t="s">
-        <v>51</v>
+        <v>111</v>
       </c>
       <c r="C86">
         <v>1</v>
@@ -6764,7 +6783,7 @@
         <v>14</v>
       </c>
       <c r="B87" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="C87">
         <v>1</v>
@@ -6775,7 +6794,7 @@
         <v>14</v>
       </c>
       <c r="B88" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -6786,7 +6805,7 @@
         <v>14</v>
       </c>
       <c r="B89" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -6797,7 +6816,7 @@
         <v>14</v>
       </c>
       <c r="B90" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="C90">
         <v>1</v>
@@ -6808,7 +6827,7 @@
         <v>14</v>
       </c>
       <c r="B91" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="C91">
         <v>1</v>
@@ -6819,7 +6838,7 @@
         <v>14</v>
       </c>
       <c r="B92" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="C92">
         <v>1</v>
@@ -6830,7 +6849,7 @@
         <v>14</v>
       </c>
       <c r="B93" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="C93">
         <v>1</v>
@@ -6841,7 +6860,7 @@
         <v>14</v>
       </c>
       <c r="B94" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="C94">
         <v>1</v>
@@ -6852,7 +6871,7 @@
         <v>14</v>
       </c>
       <c r="B95" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="C95">
         <v>1</v>
@@ -6863,7 +6882,7 @@
         <v>14</v>
       </c>
       <c r="B96" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C96">
         <v>1</v>
@@ -6874,7 +6893,7 @@
         <v>14</v>
       </c>
       <c r="B97" t="s">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="C97">
         <v>1</v>
@@ -6885,7 +6904,7 @@
         <v>14</v>
       </c>
       <c r="B98" t="s">
-        <v>79</v>
+        <v>118</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -6893,13 +6912,13 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B99" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C99">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -6907,10 +6926,10 @@
         <v>15</v>
       </c>
       <c r="B100" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C100">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -6918,10 +6937,10 @@
         <v>15</v>
       </c>
       <c r="B101" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C101">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -6929,10 +6948,10 @@
         <v>15</v>
       </c>
       <c r="B102" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C102">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -6940,10 +6959,10 @@
         <v>15</v>
       </c>
       <c r="B103" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C103">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -6951,7 +6970,7 @@
         <v>15</v>
       </c>
       <c r="B104" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="C104">
         <v>6</v>
@@ -6962,7 +6981,7 @@
         <v>15</v>
       </c>
       <c r="B105" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="C105">
         <v>6</v>
@@ -6973,10 +6992,10 @@
         <v>15</v>
       </c>
       <c r="B106" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C106">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -6984,7 +7003,7 @@
         <v>15</v>
       </c>
       <c r="B107" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C107">
         <v>4</v>
@@ -6995,7 +7014,7 @@
         <v>15</v>
       </c>
       <c r="B108" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C108">
         <v>4</v>
@@ -7006,7 +7025,7 @@
         <v>15</v>
       </c>
       <c r="B109" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="C109">
         <v>4</v>
@@ -7017,7 +7036,7 @@
         <v>15</v>
       </c>
       <c r="B110" t="s">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="C110">
         <v>4</v>
@@ -7028,10 +7047,10 @@
         <v>15</v>
       </c>
       <c r="B111" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C111">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -7039,7 +7058,7 @@
         <v>15</v>
       </c>
       <c r="B112" t="s">
-        <v>127</v>
+        <v>81</v>
       </c>
       <c r="C112">
         <v>3</v>
@@ -7050,7 +7069,7 @@
         <v>15</v>
       </c>
       <c r="B113" t="s">
-        <v>81</v>
+        <v>131</v>
       </c>
       <c r="C113">
         <v>3</v>
@@ -7061,7 +7080,7 @@
         <v>15</v>
       </c>
       <c r="B114" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C114">
         <v>3</v>
@@ -7072,7 +7091,7 @@
         <v>15</v>
       </c>
       <c r="B115" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C115">
         <v>3</v>
@@ -7083,7 +7102,7 @@
         <v>15</v>
       </c>
       <c r="B116" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C116">
         <v>3</v>
@@ -7094,10 +7113,10 @@
         <v>15</v>
       </c>
       <c r="B117" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="C117">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -7105,7 +7124,7 @@
         <v>15</v>
       </c>
       <c r="B118" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C118">
         <v>2</v>
@@ -7116,7 +7135,7 @@
         <v>15</v>
       </c>
       <c r="B119" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C119">
         <v>2</v>
@@ -7127,7 +7146,7 @@
         <v>15</v>
       </c>
       <c r="B120" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C120">
         <v>2</v>
@@ -7138,7 +7157,7 @@
         <v>15</v>
       </c>
       <c r="B121" t="s">
-        <v>137</v>
+        <v>62</v>
       </c>
       <c r="C121">
         <v>2</v>
@@ -7149,7 +7168,7 @@
         <v>15</v>
       </c>
       <c r="B122" t="s">
-        <v>62</v>
+        <v>139</v>
       </c>
       <c r="C122">
         <v>2</v>
@@ -7160,7 +7179,7 @@
         <v>15</v>
       </c>
       <c r="B123" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C123">
         <v>2</v>
@@ -7171,7 +7190,7 @@
         <v>15</v>
       </c>
       <c r="B124" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C124">
         <v>2</v>
@@ -7182,7 +7201,7 @@
         <v>15</v>
       </c>
       <c r="B125" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C125">
         <v>2</v>
@@ -7193,7 +7212,7 @@
         <v>15</v>
       </c>
       <c r="B126" t="s">
-        <v>136</v>
+        <v>49</v>
       </c>
       <c r="C126">
         <v>2</v>
@@ -7204,10 +7223,10 @@
         <v>15</v>
       </c>
       <c r="B127" t="s">
-        <v>49</v>
+        <v>169</v>
       </c>
       <c r="C127">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -7215,7 +7234,7 @@
         <v>15</v>
       </c>
       <c r="B128" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="C128">
         <v>1</v>
@@ -7226,7 +7245,7 @@
         <v>15</v>
       </c>
       <c r="B129" t="s">
-        <v>152</v>
+        <v>175</v>
       </c>
       <c r="C129">
         <v>1</v>
@@ -7237,7 +7256,7 @@
         <v>15</v>
       </c>
       <c r="B130" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="C130">
         <v>1</v>
@@ -7248,7 +7267,7 @@
         <v>15</v>
       </c>
       <c r="B131" t="s">
-        <v>187</v>
+        <v>83</v>
       </c>
       <c r="C131">
         <v>1</v>
@@ -7259,7 +7278,7 @@
         <v>15</v>
       </c>
       <c r="B132" t="s">
-        <v>83</v>
+        <v>146</v>
       </c>
       <c r="C132">
         <v>1</v>
@@ -7270,7 +7289,7 @@
         <v>15</v>
       </c>
       <c r="B133" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="C133">
         <v>1</v>
@@ -7281,7 +7300,7 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>157</v>
+        <v>188</v>
       </c>
       <c r="C134">
         <v>1</v>
@@ -7292,7 +7311,7 @@
         <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="C135">
         <v>1</v>
@@ -7303,7 +7322,7 @@
         <v>15</v>
       </c>
       <c r="B136" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="C136">
         <v>1</v>
@@ -7314,7 +7333,7 @@
         <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="C137">
         <v>1</v>
@@ -7325,7 +7344,7 @@
         <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>186</v>
+        <v>150</v>
       </c>
       <c r="C138">
         <v>1</v>
@@ -7336,7 +7355,7 @@
         <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="C139">
         <v>1</v>
@@ -7347,7 +7366,7 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="C140">
         <v>1</v>
@@ -7358,7 +7377,7 @@
         <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="C141">
         <v>1</v>
@@ -7369,7 +7388,7 @@
         <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="C142">
         <v>1</v>
@@ -7380,7 +7399,7 @@
         <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="C143">
         <v>1</v>
@@ -7391,7 +7410,7 @@
         <v>15</v>
       </c>
       <c r="B144" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C144">
         <v>1</v>
@@ -7402,7 +7421,7 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="C145">
         <v>1</v>
@@ -7413,7 +7432,7 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="C146">
         <v>1</v>
@@ -7424,7 +7443,7 @@
         <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>159</v>
+        <v>181</v>
       </c>
       <c r="C147">
         <v>1</v>
@@ -7435,7 +7454,7 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="C148">
         <v>1</v>
@@ -7446,7 +7465,7 @@
         <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>161</v>
+        <v>185</v>
       </c>
       <c r="C149">
         <v>1</v>
@@ -7457,7 +7476,7 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C150">
         <v>1</v>
@@ -7468,7 +7487,7 @@
         <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C151">
         <v>1</v>
@@ -7479,7 +7498,7 @@
         <v>15</v>
       </c>
       <c r="B152" t="s">
-        <v>183</v>
+        <v>148</v>
       </c>
       <c r="C152">
         <v>1</v>
@@ -7490,7 +7509,7 @@
         <v>15</v>
       </c>
       <c r="B153" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C153">
         <v>1</v>
@@ -7501,7 +7520,7 @@
         <v>15</v>
       </c>
       <c r="B154" t="s">
-        <v>147</v>
+        <v>166</v>
       </c>
       <c r="C154">
         <v>1</v>
@@ -7512,7 +7531,7 @@
         <v>15</v>
       </c>
       <c r="B155" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="C155">
         <v>1</v>
@@ -7523,7 +7542,7 @@
         <v>15</v>
       </c>
       <c r="B156" t="s">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="C156">
         <v>1</v>
@@ -7534,7 +7553,7 @@
         <v>15</v>
       </c>
       <c r="B157" t="s">
-        <v>168</v>
+        <v>143</v>
       </c>
       <c r="C157">
         <v>1</v>
@@ -7545,7 +7564,7 @@
         <v>15</v>
       </c>
       <c r="B158" t="s">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="C158">
         <v>1</v>
@@ -7556,7 +7575,7 @@
         <v>15</v>
       </c>
       <c r="B159" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="C159">
         <v>1</v>
@@ -7567,7 +7586,7 @@
         <v>15</v>
       </c>
       <c r="B160" t="s">
-        <v>156</v>
+        <v>97</v>
       </c>
       <c r="C160">
         <v>1</v>
@@ -7578,7 +7597,7 @@
         <v>15</v>
       </c>
       <c r="B161" t="s">
-        <v>97</v>
+        <v>164</v>
       </c>
       <c r="C161">
         <v>1</v>
@@ -7589,7 +7608,7 @@
         <v>15</v>
       </c>
       <c r="B162" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="C162">
         <v>1</v>
@@ -7600,7 +7619,7 @@
         <v>15</v>
       </c>
       <c r="B163" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -7611,7 +7630,7 @@
         <v>15</v>
       </c>
       <c r="B164" t="s">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="C164">
         <v>1</v>
@@ -7622,7 +7641,7 @@
         <v>15</v>
       </c>
       <c r="B165" t="s">
-        <v>182</v>
+        <v>163</v>
       </c>
       <c r="C165">
         <v>1</v>
@@ -7633,7 +7652,7 @@
         <v>15</v>
       </c>
       <c r="B166" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C166">
         <v>1</v>
@@ -7644,7 +7663,7 @@
         <v>15</v>
       </c>
       <c r="B167" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -7655,7 +7674,7 @@
         <v>15</v>
       </c>
       <c r="B168" t="s">
-        <v>160</v>
+        <v>88</v>
       </c>
       <c r="C168">
         <v>1</v>
@@ -7666,7 +7685,7 @@
         <v>15</v>
       </c>
       <c r="B169" t="s">
-        <v>88</v>
+        <v>151</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -7677,7 +7696,7 @@
         <v>15</v>
       </c>
       <c r="B170" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -7688,7 +7707,7 @@
         <v>15</v>
       </c>
       <c r="B171" t="s">
-        <v>145</v>
+        <v>67</v>
       </c>
       <c r="C171">
         <v>1</v>
@@ -7699,7 +7718,7 @@
         <v>15</v>
       </c>
       <c r="B172" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C172">
         <v>1</v>
@@ -7710,7 +7729,7 @@
         <v>15</v>
       </c>
       <c r="B173" t="s">
-        <v>70</v>
+        <v>144</v>
       </c>
       <c r="C173">
         <v>1</v>
@@ -7721,7 +7740,7 @@
         <v>15</v>
       </c>
       <c r="B174" t="s">
-        <v>144</v>
+        <v>68</v>
       </c>
       <c r="C174">
         <v>1</v>
@@ -7732,7 +7751,7 @@
         <v>15</v>
       </c>
       <c r="B175" t="s">
-        <v>68</v>
+        <v>173</v>
       </c>
       <c r="C175">
         <v>1</v>
@@ -7743,7 +7762,7 @@
         <v>15</v>
       </c>
       <c r="B176" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -7754,7 +7773,7 @@
         <v>15</v>
       </c>
       <c r="B177" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -7765,7 +7784,7 @@
         <v>15</v>
       </c>
       <c r="B178" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -7776,7 +7795,7 @@
         <v>15</v>
       </c>
       <c r="B179" t="s">
-        <v>178</v>
+        <v>142</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -7787,7 +7806,7 @@
         <v>15</v>
       </c>
       <c r="B180" t="s">
-        <v>142</v>
+        <v>189</v>
       </c>
       <c r="C180">
         <v>1</v>
@@ -7798,7 +7817,7 @@
         <v>15</v>
       </c>
       <c r="B181" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C181">
         <v>1</v>
@@ -7809,7 +7828,7 @@
         <v>15</v>
       </c>
       <c r="B182" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C182">
         <v>1</v>
@@ -7820,7 +7839,7 @@
         <v>15</v>
       </c>
       <c r="B183" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C183">
         <v>1</v>
@@ -7828,13 +7847,13 @@
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B184" t="s">
-        <v>192</v>
+        <v>49</v>
       </c>
       <c r="C184">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -7842,10 +7861,10 @@
         <v>16</v>
       </c>
       <c r="B185" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C185">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -7853,10 +7872,10 @@
         <v>16</v>
       </c>
       <c r="B186" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C186">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -7864,10 +7883,10 @@
         <v>16</v>
       </c>
       <c r="B187" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="C187">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -7875,10 +7894,10 @@
         <v>16</v>
       </c>
       <c r="B188" t="s">
-        <v>66</v>
+        <v>116</v>
       </c>
       <c r="C188">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -7886,10 +7905,10 @@
         <v>16</v>
       </c>
       <c r="B189" t="s">
-        <v>116</v>
+        <v>193</v>
       </c>
       <c r="C189">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -7897,10 +7916,10 @@
         <v>16</v>
       </c>
       <c r="B190" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C190">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -7919,7 +7938,7 @@
         <v>16</v>
       </c>
       <c r="B192" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C192">
         <v>11</v>
@@ -7930,7 +7949,7 @@
         <v>16</v>
       </c>
       <c r="B193" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="C193">
         <v>11</v>
@@ -7941,7 +7960,7 @@
         <v>16</v>
       </c>
       <c r="B194" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="C194">
         <v>11</v>
@@ -7952,7 +7971,7 @@
         <v>16</v>
       </c>
       <c r="B195" t="s">
-        <v>195</v>
+        <v>45</v>
       </c>
       <c r="C195">
         <v>10</v>
@@ -7963,10 +7982,10 @@
         <v>16</v>
       </c>
       <c r="B196" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C196">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -7974,7 +7993,7 @@
         <v>16</v>
       </c>
       <c r="B197" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="C197">
         <v>9</v>
@@ -7985,10 +8004,10 @@
         <v>16</v>
       </c>
       <c r="B198" t="s">
-        <v>72</v>
+        <v>196</v>
       </c>
       <c r="C198">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -7996,10 +8015,10 @@
         <v>16</v>
       </c>
       <c r="B199" t="s">
-        <v>196</v>
+        <v>85</v>
       </c>
       <c r="C199">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -8007,7 +8026,7 @@
         <v>16</v>
       </c>
       <c r="B200" t="s">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="C200">
         <v>7</v>
@@ -8018,10 +8037,10 @@
         <v>16</v>
       </c>
       <c r="B201" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C201">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -8029,7 +8048,7 @@
         <v>16</v>
       </c>
       <c r="B202" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="C202">
         <v>6</v>
@@ -8040,10 +8059,10 @@
         <v>16</v>
       </c>
       <c r="B203" t="s">
-        <v>48</v>
+        <v>200</v>
       </c>
       <c r="C203">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -8051,7 +8070,7 @@
         <v>16</v>
       </c>
       <c r="B204" t="s">
-        <v>200</v>
+        <v>71</v>
       </c>
       <c r="C204">
         <v>5</v>
@@ -8062,7 +8081,7 @@
         <v>16</v>
       </c>
       <c r="B205" t="s">
-        <v>71</v>
+        <v>198</v>
       </c>
       <c r="C205">
         <v>5</v>
@@ -8073,7 +8092,7 @@
         <v>16</v>
       </c>
       <c r="B206" t="s">
-        <v>198</v>
+        <v>73</v>
       </c>
       <c r="C206">
         <v>5</v>
@@ -8084,10 +8103,10 @@
         <v>16</v>
       </c>
       <c r="B207" t="s">
-        <v>73</v>
+        <v>197</v>
       </c>
       <c r="C207">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -8095,7 +8114,7 @@
         <v>16</v>
       </c>
       <c r="B208" t="s">
-        <v>197</v>
+        <v>47</v>
       </c>
       <c r="C208">
         <v>4</v>
@@ -8106,7 +8125,7 @@
         <v>16</v>
       </c>
       <c r="B209" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C209">
         <v>4</v>
@@ -8117,7 +8136,7 @@
         <v>16</v>
       </c>
       <c r="B210" t="s">
-        <v>44</v>
+        <v>199</v>
       </c>
       <c r="C210">
         <v>4</v>
@@ -8128,7 +8147,7 @@
         <v>16</v>
       </c>
       <c r="B211" t="s">
-        <v>199</v>
+        <v>60</v>
       </c>
       <c r="C211">
         <v>4</v>
@@ -8139,7 +8158,7 @@
         <v>16</v>
       </c>
       <c r="B212" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="C212">
         <v>4</v>
@@ -8150,7 +8169,7 @@
         <v>16</v>
       </c>
       <c r="B213" t="s">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="C213">
         <v>4</v>
@@ -8161,10 +8180,10 @@
         <v>16</v>
       </c>
       <c r="B214" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="C214">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -8172,7 +8191,7 @@
         <v>16</v>
       </c>
       <c r="B215" t="s">
-        <v>118</v>
+        <v>59</v>
       </c>
       <c r="C215">
         <v>3</v>
@@ -8183,7 +8202,7 @@
         <v>16</v>
       </c>
       <c r="B216" t="s">
-        <v>59</v>
+        <v>201</v>
       </c>
       <c r="C216">
         <v>3</v>
@@ -8194,7 +8213,7 @@
         <v>16</v>
       </c>
       <c r="B217" t="s">
-        <v>201</v>
+        <v>114</v>
       </c>
       <c r="C217">
         <v>3</v>
@@ -8205,7 +8224,7 @@
         <v>16</v>
       </c>
       <c r="B218" t="s">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="C218">
         <v>3</v>
@@ -8216,7 +8235,7 @@
         <v>16</v>
       </c>
       <c r="B219" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C219">
         <v>3</v>
@@ -8227,7 +8246,7 @@
         <v>16</v>
       </c>
       <c r="B220" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C220">
         <v>3</v>
@@ -8238,7 +8257,7 @@
         <v>16</v>
       </c>
       <c r="B221" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C221">
         <v>3</v>
@@ -8249,10 +8268,10 @@
         <v>16</v>
       </c>
       <c r="B222" t="s">
-        <v>68</v>
+        <v>189</v>
       </c>
       <c r="C222">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -8260,7 +8279,7 @@
         <v>16</v>
       </c>
       <c r="B223" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="C223">
         <v>2</v>
@@ -8271,7 +8290,7 @@
         <v>16</v>
       </c>
       <c r="B224" t="s">
-        <v>203</v>
+        <v>64</v>
       </c>
       <c r="C224">
         <v>2</v>
@@ -8282,7 +8301,7 @@
         <v>16</v>
       </c>
       <c r="B225" t="s">
-        <v>64</v>
+        <v>205</v>
       </c>
       <c r="C225">
         <v>2</v>
@@ -8293,7 +8312,7 @@
         <v>16</v>
       </c>
       <c r="B226" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C226">
         <v>2</v>
@@ -8304,7 +8323,7 @@
         <v>16</v>
       </c>
       <c r="B227" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C227">
         <v>2</v>
@@ -8315,7 +8334,7 @@
         <v>16</v>
       </c>
       <c r="B228" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C228">
         <v>2</v>
@@ -8326,7 +8345,7 @@
         <v>16</v>
       </c>
       <c r="B229" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C229">
         <v>2</v>
@@ -8337,10 +8356,10 @@
         <v>16</v>
       </c>
       <c r="B230" t="s">
-        <v>207</v>
+        <v>234</v>
       </c>
       <c r="C230">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -8348,7 +8367,7 @@
         <v>16</v>
       </c>
       <c r="B231" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C231">
         <v>1</v>
@@ -8359,7 +8378,7 @@
         <v>16</v>
       </c>
       <c r="B232" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="C232">
         <v>1</v>
@@ -8370,7 +8389,7 @@
         <v>16</v>
       </c>
       <c r="B233" t="s">
-        <v>248</v>
+        <v>231</v>
       </c>
       <c r="C233">
         <v>1</v>
@@ -8381,7 +8400,7 @@
         <v>16</v>
       </c>
       <c r="B234" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="C234">
         <v>1</v>
@@ -8392,7 +8411,7 @@
         <v>16</v>
       </c>
       <c r="B235" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="C235">
         <v>1</v>
@@ -8403,7 +8422,7 @@
         <v>16</v>
       </c>
       <c r="B236" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="C236">
         <v>1</v>
@@ -8414,7 +8433,7 @@
         <v>16</v>
       </c>
       <c r="B237" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -8425,7 +8444,7 @@
         <v>16</v>
       </c>
       <c r="B238" t="s">
-        <v>240</v>
+        <v>119</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -8436,7 +8455,7 @@
         <v>16</v>
       </c>
       <c r="B239" t="s">
-        <v>119</v>
+        <v>210</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -8447,7 +8466,7 @@
         <v>16</v>
       </c>
       <c r="B240" t="s">
-        <v>210</v>
+        <v>241</v>
       </c>
       <c r="C240">
         <v>1</v>
@@ -8458,7 +8477,7 @@
         <v>16</v>
       </c>
       <c r="B241" t="s">
-        <v>242</v>
+        <v>58</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -8469,7 +8488,7 @@
         <v>16</v>
       </c>
       <c r="B242" t="s">
-        <v>58</v>
+        <v>229</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -8480,7 +8499,7 @@
         <v>16</v>
       </c>
       <c r="B243" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -8491,7 +8510,7 @@
         <v>16</v>
       </c>
       <c r="B244" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -8502,7 +8521,7 @@
         <v>16</v>
       </c>
       <c r="B245" t="s">
-        <v>222</v>
+        <v>69</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -8513,7 +8532,7 @@
         <v>16</v>
       </c>
       <c r="B246" t="s">
-        <v>69</v>
+        <v>115</v>
       </c>
       <c r="C246">
         <v>1</v>
@@ -8524,7 +8543,7 @@
         <v>16</v>
       </c>
       <c r="B247" t="s">
-        <v>115</v>
+        <v>237</v>
       </c>
       <c r="C247">
         <v>1</v>
@@ -8535,7 +8554,7 @@
         <v>16</v>
       </c>
       <c r="B248" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="C248">
         <v>1</v>
@@ -8557,7 +8576,7 @@
         <v>16</v>
       </c>
       <c r="B250" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -8568,7 +8587,7 @@
         <v>16</v>
       </c>
       <c r="B251" t="s">
-        <v>223</v>
+        <v>126</v>
       </c>
       <c r="C251">
         <v>1</v>
@@ -8579,7 +8598,7 @@
         <v>16</v>
       </c>
       <c r="B252" t="s">
-        <v>126</v>
+        <v>220</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -8590,7 +8609,7 @@
         <v>16</v>
       </c>
       <c r="B253" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -8601,7 +8620,7 @@
         <v>16</v>
       </c>
       <c r="B254" t="s">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -8612,7 +8631,7 @@
         <v>16</v>
       </c>
       <c r="B255" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -8623,7 +8642,7 @@
         <v>16</v>
       </c>
       <c r="B256" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -8634,7 +8653,7 @@
         <v>16</v>
       </c>
       <c r="B257" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -8645,7 +8664,7 @@
         <v>16</v>
       </c>
       <c r="B258" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C258">
         <v>1</v>
@@ -8656,7 +8675,7 @@
         <v>16</v>
       </c>
       <c r="B259" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C259">
         <v>1</v>
@@ -8667,7 +8686,7 @@
         <v>16</v>
       </c>
       <c r="B260" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="C260">
         <v>1</v>
@@ -8678,7 +8697,7 @@
         <v>16</v>
       </c>
       <c r="B261" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="C261">
         <v>1</v>
@@ -8689,7 +8708,7 @@
         <v>16</v>
       </c>
       <c r="B262" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C262">
         <v>1</v>
@@ -8700,7 +8719,7 @@
         <v>16</v>
       </c>
       <c r="B263" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="C263">
         <v>1</v>
@@ -8711,7 +8730,7 @@
         <v>16</v>
       </c>
       <c r="B264" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -8722,7 +8741,7 @@
         <v>16</v>
       </c>
       <c r="B265" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C265">
         <v>1</v>
@@ -8733,7 +8752,7 @@
         <v>16</v>
       </c>
       <c r="B266" t="s">
-        <v>236</v>
+        <v>208</v>
       </c>
       <c r="C266">
         <v>1</v>
@@ -8744,7 +8763,7 @@
         <v>16</v>
       </c>
       <c r="B267" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -8755,7 +8774,7 @@
         <v>16</v>
       </c>
       <c r="B268" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="C268">
         <v>1</v>
@@ -8766,7 +8785,7 @@
         <v>16</v>
       </c>
       <c r="B269" t="s">
-        <v>215</v>
+        <v>243</v>
       </c>
       <c r="C269">
         <v>1</v>
@@ -8777,7 +8796,7 @@
         <v>16</v>
       </c>
       <c r="B270" t="s">
-        <v>244</v>
+        <v>209</v>
       </c>
       <c r="C270">
         <v>1</v>
@@ -8788,7 +8807,7 @@
         <v>16</v>
       </c>
       <c r="B271" t="s">
-        <v>216</v>
+        <v>70</v>
       </c>
       <c r="C271">
         <v>1</v>
@@ -8799,7 +8818,7 @@
         <v>16</v>
       </c>
       <c r="B272" t="s">
-        <v>70</v>
+        <v>121</v>
       </c>
       <c r="C272">
         <v>1</v>
@@ -8807,24 +8826,24 @@
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B273" t="s">
-        <v>211</v>
+        <v>121</v>
       </c>
       <c r="C273">
-        <v>1</v>
+        <v>39</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B274" t="s">
-        <v>121</v>
+        <v>189</v>
       </c>
       <c r="C274">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -8832,10 +8851,10 @@
         <v>21</v>
       </c>
       <c r="B275" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="C275">
-        <v>39</v>
+        <v>11</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -8843,10 +8862,10 @@
         <v>21</v>
       </c>
       <c r="B276" t="s">
-        <v>189</v>
+        <v>103</v>
       </c>
       <c r="C276">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -8854,10 +8873,10 @@
         <v>21</v>
       </c>
       <c r="B277" t="s">
-        <v>132</v>
+        <v>202</v>
       </c>
       <c r="C277">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -8865,10 +8884,10 @@
         <v>21</v>
       </c>
       <c r="B278" t="s">
-        <v>103</v>
+        <v>242</v>
       </c>
       <c r="C278">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -8876,10 +8895,10 @@
         <v>21</v>
       </c>
       <c r="B279" t="s">
-        <v>202</v>
+        <v>120</v>
       </c>
       <c r="C279">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -8887,10 +8906,10 @@
         <v>21</v>
       </c>
       <c r="B280" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C280">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
@@ -8898,10 +8917,10 @@
         <v>21</v>
       </c>
       <c r="B281" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="C281">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -8920,7 +8939,7 @@
         <v>21</v>
       </c>
       <c r="B283" t="s">
-        <v>142</v>
+        <v>243</v>
       </c>
       <c r="C283">
         <v>5</v>
@@ -8931,10 +8950,10 @@
         <v>21</v>
       </c>
       <c r="B284" t="s">
-        <v>246</v>
+        <v>101</v>
       </c>
       <c r="C284">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
@@ -8942,10 +8961,10 @@
         <v>21</v>
       </c>
       <c r="B285" t="s">
-        <v>244</v>
+        <v>128</v>
       </c>
       <c r="C285">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -8953,7 +8972,7 @@
         <v>21</v>
       </c>
       <c r="B286" t="s">
-        <v>101</v>
+        <v>246</v>
       </c>
       <c r="C286">
         <v>4</v>
@@ -8964,10 +8983,10 @@
         <v>21</v>
       </c>
       <c r="B287" t="s">
-        <v>128</v>
+        <v>81</v>
       </c>
       <c r="C287">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
@@ -8978,7 +8997,7 @@
         <v>247</v>
       </c>
       <c r="C288">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
@@ -8986,7 +9005,7 @@
         <v>21</v>
       </c>
       <c r="B289" t="s">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="C289">
         <v>3</v>
@@ -8997,7 +9016,7 @@
         <v>21</v>
       </c>
       <c r="B290" t="s">
-        <v>248</v>
+        <v>196</v>
       </c>
       <c r="C290">
         <v>3</v>
@@ -9008,7 +9027,7 @@
         <v>21</v>
       </c>
       <c r="B291" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C291">
         <v>3</v>
@@ -9019,7 +9038,7 @@
         <v>21</v>
       </c>
       <c r="B292" t="s">
-        <v>196</v>
+        <v>251</v>
       </c>
       <c r="C292">
         <v>3</v>
@@ -9030,7 +9049,7 @@
         <v>21</v>
       </c>
       <c r="B293" t="s">
-        <v>127</v>
+        <v>250</v>
       </c>
       <c r="C293">
         <v>3</v>
@@ -9041,7 +9060,7 @@
         <v>21</v>
       </c>
       <c r="B294" t="s">
-        <v>252</v>
+        <v>163</v>
       </c>
       <c r="C294">
         <v>3</v>
@@ -9052,7 +9071,7 @@
         <v>21</v>
       </c>
       <c r="B295" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C295">
         <v>3</v>
@@ -9063,7 +9082,7 @@
         <v>21</v>
       </c>
       <c r="B296" t="s">
-        <v>163</v>
+        <v>44</v>
       </c>
       <c r="C296">
         <v>3</v>
@@ -9074,7 +9093,7 @@
         <v>21</v>
       </c>
       <c r="B297" t="s">
-        <v>250</v>
+        <v>133</v>
       </c>
       <c r="C297">
         <v>3</v>
@@ -9085,10 +9104,10 @@
         <v>21</v>
       </c>
       <c r="B298" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="C298">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
@@ -9096,10 +9115,10 @@
         <v>21</v>
       </c>
       <c r="B299" t="s">
-        <v>133</v>
+        <v>171</v>
       </c>
       <c r="C299">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
@@ -9107,7 +9126,7 @@
         <v>21</v>
       </c>
       <c r="B300" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="C300">
         <v>2</v>
@@ -9118,7 +9137,7 @@
         <v>21</v>
       </c>
       <c r="B301" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C301">
         <v>2</v>
@@ -9129,7 +9148,7 @@
         <v>21</v>
       </c>
       <c r="B302" t="s">
-        <v>136</v>
+        <v>253</v>
       </c>
       <c r="C302">
         <v>2</v>
@@ -9140,7 +9159,7 @@
         <v>21</v>
       </c>
       <c r="B303" t="s">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="C303">
         <v>2</v>
@@ -9151,7 +9170,7 @@
         <v>21</v>
       </c>
       <c r="B304" t="s">
-        <v>254</v>
+        <v>70</v>
       </c>
       <c r="C304">
         <v>2</v>
@@ -9162,7 +9181,7 @@
         <v>21</v>
       </c>
       <c r="B305" t="s">
-        <v>77</v>
+        <v>254</v>
       </c>
       <c r="C305">
         <v>2</v>
@@ -9173,7 +9192,7 @@
         <v>21</v>
       </c>
       <c r="B306" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="C306">
         <v>2</v>
@@ -9184,7 +9203,7 @@
         <v>21</v>
       </c>
       <c r="B307" t="s">
-        <v>255</v>
+        <v>85</v>
       </c>
       <c r="C307">
         <v>2</v>
@@ -9195,7 +9214,7 @@
         <v>21</v>
       </c>
       <c r="B308" t="s">
-        <v>54</v>
+        <v>269</v>
       </c>
       <c r="C308">
         <v>2</v>
@@ -9206,7 +9225,7 @@
         <v>21</v>
       </c>
       <c r="B309" t="s">
-        <v>85</v>
+        <v>255</v>
       </c>
       <c r="C309">
         <v>2</v>
@@ -9217,7 +9236,7 @@
         <v>21</v>
       </c>
       <c r="B310" t="s">
-        <v>270</v>
+        <v>198</v>
       </c>
       <c r="C310">
         <v>2</v>
@@ -9228,7 +9247,7 @@
         <v>21</v>
       </c>
       <c r="B311" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C311">
         <v>2</v>
@@ -9239,7 +9258,7 @@
         <v>21</v>
       </c>
       <c r="B312" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C312">
         <v>2</v>
@@ -9250,7 +9269,7 @@
         <v>21</v>
       </c>
       <c r="B313" t="s">
-        <v>253</v>
+        <v>62</v>
       </c>
       <c r="C313">
         <v>2</v>
@@ -9261,7 +9280,7 @@
         <v>21</v>
       </c>
       <c r="B314" t="s">
-        <v>199</v>
+        <v>248</v>
       </c>
       <c r="C314">
         <v>2</v>
@@ -9272,10 +9291,10 @@
         <v>21</v>
       </c>
       <c r="B315" t="s">
-        <v>62</v>
+        <v>279</v>
       </c>
       <c r="C315">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
@@ -9283,10 +9302,10 @@
         <v>21</v>
       </c>
       <c r="B316" t="s">
-        <v>249</v>
+        <v>138</v>
       </c>
       <c r="C316">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
@@ -9294,7 +9313,7 @@
         <v>21</v>
       </c>
       <c r="B317" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="C317">
         <v>1</v>
@@ -9305,7 +9324,7 @@
         <v>21</v>
       </c>
       <c r="B318" t="s">
-        <v>138</v>
+        <v>270</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -9316,7 +9335,7 @@
         <v>21</v>
       </c>
       <c r="B319" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C319">
         <v>1</v>
@@ -9327,7 +9346,7 @@
         <v>21</v>
       </c>
       <c r="B320" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C320">
         <v>1</v>
@@ -9338,7 +9357,7 @@
         <v>21</v>
       </c>
       <c r="B321" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="C321">
         <v>1</v>
@@ -9349,7 +9368,7 @@
         <v>21</v>
       </c>
       <c r="B322" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="C322">
         <v>1</v>
@@ -9360,7 +9379,7 @@
         <v>21</v>
       </c>
       <c r="B323" t="s">
-        <v>278</v>
+        <v>172</v>
       </c>
       <c r="C323">
         <v>1</v>
@@ -9371,7 +9390,7 @@
         <v>21</v>
       </c>
       <c r="B324" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="C324">
         <v>1</v>
@@ -9382,7 +9401,7 @@
         <v>21</v>
       </c>
       <c r="B325" t="s">
-        <v>172</v>
+        <v>63</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -9393,7 +9412,7 @@
         <v>21</v>
       </c>
       <c r="B326" t="s">
-        <v>281</v>
+        <v>137</v>
       </c>
       <c r="C326">
         <v>1</v>
@@ -9404,7 +9423,7 @@
         <v>21</v>
       </c>
       <c r="B327" t="s">
-        <v>63</v>
+        <v>278</v>
       </c>
       <c r="C327">
         <v>1</v>
@@ -9415,7 +9434,7 @@
         <v>21</v>
       </c>
       <c r="B328" t="s">
-        <v>137</v>
+        <v>264</v>
       </c>
       <c r="C328">
         <v>1</v>
@@ -9426,7 +9445,7 @@
         <v>21</v>
       </c>
       <c r="B329" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C329">
         <v>1</v>
@@ -9437,7 +9456,7 @@
         <v>21</v>
       </c>
       <c r="B330" t="s">
-        <v>265</v>
+        <v>185</v>
       </c>
       <c r="C330">
         <v>1</v>
@@ -9448,7 +9467,7 @@
         <v>21</v>
       </c>
       <c r="B331" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="C331">
         <v>1</v>
@@ -9459,7 +9478,7 @@
         <v>21</v>
       </c>
       <c r="B332" t="s">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="C332">
         <v>1</v>
@@ -9470,7 +9489,7 @@
         <v>21</v>
       </c>
       <c r="B333" t="s">
-        <v>263</v>
+        <v>49</v>
       </c>
       <c r="C333">
         <v>1</v>
@@ -9481,7 +9500,7 @@
         <v>21</v>
       </c>
       <c r="B334" t="s">
-        <v>148</v>
+        <v>260</v>
       </c>
       <c r="C334">
         <v>1</v>
@@ -9492,7 +9511,7 @@
         <v>21</v>
       </c>
       <c r="B335" t="s">
-        <v>49</v>
+        <v>115</v>
       </c>
       <c r="C335">
         <v>1</v>
@@ -9503,7 +9522,7 @@
         <v>21</v>
       </c>
       <c r="B336" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="C336">
         <v>1</v>
@@ -9514,7 +9533,7 @@
         <v>21</v>
       </c>
       <c r="B337" t="s">
-        <v>115</v>
+        <v>263</v>
       </c>
       <c r="C337">
         <v>1</v>
@@ -9536,7 +9555,7 @@
         <v>21</v>
       </c>
       <c r="B339" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C339">
         <v>1</v>
@@ -9547,7 +9566,7 @@
         <v>21</v>
       </c>
       <c r="B340" t="s">
-        <v>273</v>
+        <v>213</v>
       </c>
       <c r="C340">
         <v>1</v>
@@ -9558,7 +9577,7 @@
         <v>21</v>
       </c>
       <c r="B341" t="s">
-        <v>260</v>
+        <v>125</v>
       </c>
       <c r="C341">
         <v>1</v>
@@ -9569,7 +9588,7 @@
         <v>21</v>
       </c>
       <c r="B342" t="s">
-        <v>214</v>
+        <v>275</v>
       </c>
       <c r="C342">
         <v>1</v>
@@ -9580,7 +9599,7 @@
         <v>21</v>
       </c>
       <c r="B343" t="s">
-        <v>125</v>
+        <v>256</v>
       </c>
       <c r="C343">
         <v>1</v>
@@ -9591,7 +9610,7 @@
         <v>21</v>
       </c>
       <c r="B344" t="s">
-        <v>276</v>
+        <v>92</v>
       </c>
       <c r="C344">
         <v>1</v>
@@ -9602,7 +9621,7 @@
         <v>21</v>
       </c>
       <c r="B345" t="s">
-        <v>257</v>
+        <v>165</v>
       </c>
       <c r="C345">
         <v>1</v>
@@ -9613,7 +9632,7 @@
         <v>21</v>
       </c>
       <c r="B346" t="s">
-        <v>92</v>
+        <v>174</v>
       </c>
       <c r="C346">
         <v>1</v>
@@ -9624,7 +9643,7 @@
         <v>21</v>
       </c>
       <c r="B347" t="s">
-        <v>165</v>
+        <v>268</v>
       </c>
       <c r="C347">
         <v>1</v>
@@ -9635,7 +9654,7 @@
         <v>21</v>
       </c>
       <c r="B348" t="s">
-        <v>174</v>
+        <v>258</v>
       </c>
       <c r="C348">
         <v>1</v>
@@ -9646,7 +9665,7 @@
         <v>21</v>
       </c>
       <c r="B349" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="C349">
         <v>1</v>
@@ -9657,7 +9676,7 @@
         <v>21</v>
       </c>
       <c r="B350" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C350">
         <v>1</v>
@@ -9668,31 +9687,9 @@
         <v>21</v>
       </c>
       <c r="B351" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="C351">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A352" t="s">
-        <v>21</v>
-      </c>
-      <c r="B352" t="s">
-        <v>262</v>
-      </c>
-      <c r="C352">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A353" t="s">
-        <v>21</v>
-      </c>
-      <c r="B353" t="s">
-        <v>267</v>
-      </c>
-      <c r="C353">
         <v>1</v>
       </c>
     </row>
@@ -9703,7 +9700,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23700CF0-069F-497B-B50D-FB3ED3120196}">
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -9714,10 +9711,10 @@
         <v>37</v>
       </c>
       <c r="B1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C1" t="s">
         <v>283</v>
-      </c>
-      <c r="C1" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -9725,7 +9722,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C2">
         <v>63</v>
@@ -9736,7 +9733,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C3">
         <v>512</v>
@@ -9747,7 +9744,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C4">
         <v>37</v>
@@ -9758,7 +9755,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C5">
         <v>11</v>
@@ -9769,7 +9766,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C6">
         <v>7</v>
@@ -9780,7 +9777,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -9788,13 +9785,13 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -9805,7 +9802,7 @@
         <v>285</v>
       </c>
       <c r="C9">
-        <v>29</v>
+        <v>559</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -9813,10 +9810,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C10">
-        <v>559</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -9824,10 +9821,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C11">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
@@ -9835,21 +9832,21 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C12">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C13">
-        <v>25</v>
+        <v>882</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -9857,10 +9854,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C14">
-        <v>882</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -9868,10 +9865,10 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="C15">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -9879,10 +9876,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C16">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -9890,10 +9887,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C17">
-        <v>22</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -9901,10 +9898,10 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C18">
-        <v>33</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -9912,10 +9909,10 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="C19">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -9923,10 +9920,10 @@
         <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -9934,10 +9931,10 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="C21">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -9945,7 +9942,7 @@
         <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C22">
         <v>2</v>
@@ -9953,13 +9950,13 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -9967,10 +9964,10 @@
         <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C24">
-        <v>41</v>
+        <v>875</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -9978,10 +9975,10 @@
         <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="C25">
-        <v>877</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -9989,10 +9986,10 @@
         <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="C26">
-        <v>25</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -10000,10 +9997,10 @@
         <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C27">
-        <v>111</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -10014,7 +10011,7 @@
         <v>287</v>
       </c>
       <c r="C28">
-        <v>139</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -10022,10 +10019,10 @@
         <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="C29">
-        <v>77</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -10033,10 +10030,10 @@
         <v>16</v>
       </c>
       <c r="B30" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="C30">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -10044,10 +10041,10 @@
         <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -10055,21 +10052,21 @@
         <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C32">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B33" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>706</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -10077,10 +10074,10 @@
         <v>21</v>
       </c>
       <c r="B34" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C34">
-        <v>706</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -10088,10 +10085,10 @@
         <v>21</v>
       </c>
       <c r="B35" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C35">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -10099,10 +10096,10 @@
         <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C36">
-        <v>22</v>
+        <v>61</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -10110,10 +10107,10 @@
         <v>21</v>
       </c>
       <c r="B37" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C37">
-        <v>61</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -10121,10 +10118,10 @@
         <v>21</v>
       </c>
       <c r="B38" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="C38">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -10132,10 +10129,10 @@
         <v>21</v>
       </c>
       <c r="B39" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="C39">
-        <v>55</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -10143,10 +10140,10 @@
         <v>21</v>
       </c>
       <c r="B40" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="C40">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -10154,7 +10151,7 @@
         <v>21</v>
       </c>
       <c r="B41" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="C41">
         <v>14</v>
@@ -10165,20 +10162,9 @@
         <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C42">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>21</v>
-      </c>
-      <c r="B43" t="s">
-        <v>288</v>
-      </c>
-      <c r="C43">
         <v>6</v>
       </c>
     </row>
@@ -10205,7 +10191,7 @@
         <v>22</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -10312,7 +10298,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C11" s="9">
         <v>1</v>
@@ -10422,7 +10408,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C21" s="9">
         <v>2</v>
@@ -10532,7 +10518,7 @@
         <v>15</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C31" s="9">
         <v>2</v>

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="194" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{608AAFB9-F37D-490B-B00D-E06F6E440669}"/>
+  <xr:revisionPtr revIDLastSave="205" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6690877-4635-491B-9952-57FFBED5698B}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-135" windowWidth="20730" windowHeight="11040" tabRatio="731" firstSheet="1" activeTab="7" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="731" firstSheet="1" activeTab="7" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="proyeccion_2026" sheetId="2" r:id="rId1"/>
@@ -24,7 +24,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">mat_2026!$A$1:$E$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">origen_colegios!$A$1:$C$354</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">origen_colegios!$A$1:$C$352</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1317" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="296">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -676,9 +676,6 @@
     <t>Centro Educacional Principado de Asturias</t>
   </si>
   <si>
-    <t>Proyecto Virtual (sin RBD tradicional)</t>
-  </si>
-  <si>
     <t>Colegio Excelsior</t>
   </si>
   <si>
@@ -764,9 +761,6 @@
   </si>
   <si>
     <t>Colegio Nuevo Horizonte</t>
-  </si>
-  <si>
-    <t>OTRO</t>
   </si>
   <si>
     <t>Colegio Adventista de San Felipe</t>
@@ -1866,10 +1860,10 @@
         <v>75</v>
       </c>
       <c r="D18">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E18">
-        <v>1.107</v>
+        <v>1.1200000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -1900,10 +1894,10 @@
         <v>85</v>
       </c>
       <c r="D20">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>1.012</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -2104,10 +2098,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E32">
-        <v>1.0660000000000001</v>
+        <v>1.0629999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2155,10 +2149,10 @@
         <v>218</v>
       </c>
       <c r="D35">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -2172,10 +2166,10 @@
         <v>250</v>
       </c>
       <c r="D36">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E36">
-        <v>1.028</v>
+        <v>1.024</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2283,7 +2277,7 @@
         <v>34</v>
       </c>
       <c r="C4">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2294,7 +2288,7 @@
         <v>35</v>
       </c>
       <c r="C5">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2327,7 +2321,7 @@
         <v>34</v>
       </c>
       <c r="C8">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2349,7 +2343,7 @@
         <v>35</v>
       </c>
       <c r="C10">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -2370,7 +2364,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD19485A-0629-47F9-A5AD-80ABA7A6E076}">
-  <dimension ref="A1:C251"/>
+  <dimension ref="A1:C254"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -2452,7 +2446,7 @@
         <v>46014</v>
       </c>
       <c r="C7" s="9">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -2474,7 +2468,7 @@
         <v>46013</v>
       </c>
       <c r="C9" s="9">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2529,7 +2523,7 @@
         <v>46010</v>
       </c>
       <c r="C14" s="6">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -2889,10 +2883,10 @@
         <v>16</v>
       </c>
       <c r="B47" s="8">
-        <v>46090</v>
+        <v>46184</v>
       </c>
       <c r="C47" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -2900,10 +2894,10 @@
         <v>16</v>
       </c>
       <c r="B48" s="5">
-        <v>46139</v>
+        <v>46090</v>
       </c>
       <c r="C48" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -2911,7 +2905,7 @@
         <v>16</v>
       </c>
       <c r="B49" s="8">
-        <v>46148</v>
+        <v>46139</v>
       </c>
       <c r="C49" s="9">
         <v>1</v>
@@ -2922,7 +2916,7 @@
         <v>16</v>
       </c>
       <c r="B50" s="5">
-        <v>46175</v>
+        <v>46148</v>
       </c>
       <c r="C50" s="6">
         <v>1</v>
@@ -2933,7 +2927,7 @@
         <v>16</v>
       </c>
       <c r="B51" s="8">
-        <v>46125</v>
+        <v>46175</v>
       </c>
       <c r="C51" s="9">
         <v>1</v>
@@ -2944,7 +2938,7 @@
         <v>16</v>
       </c>
       <c r="B52" s="5">
-        <v>46093</v>
+        <v>46125</v>
       </c>
       <c r="C52" s="6">
         <v>1</v>
@@ -2955,10 +2949,10 @@
         <v>16</v>
       </c>
       <c r="B53" s="8">
-        <v>46177</v>
+        <v>46093</v>
       </c>
       <c r="C53" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -2966,10 +2960,10 @@
         <v>16</v>
       </c>
       <c r="B54" s="5">
-        <v>46156</v>
+        <v>46177</v>
       </c>
       <c r="C54" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -2977,7 +2971,7 @@
         <v>16</v>
       </c>
       <c r="B55" s="8">
-        <v>46092</v>
+        <v>46156</v>
       </c>
       <c r="C55" s="9">
         <v>1</v>
@@ -2988,7 +2982,7 @@
         <v>16</v>
       </c>
       <c r="B56" s="5">
-        <v>46101</v>
+        <v>46092</v>
       </c>
       <c r="C56" s="6">
         <v>1</v>
@@ -2996,13 +2990,13 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B57" s="8">
-        <v>46007</v>
+        <v>46101</v>
       </c>
       <c r="C57" s="9">
-        <v>78</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
@@ -3010,10 +3004,10 @@
         <v>14</v>
       </c>
       <c r="B58" s="5">
-        <v>46009</v>
+        <v>46007</v>
       </c>
       <c r="C58" s="6">
-        <v>34</v>
+        <v>78</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -3021,10 +3015,10 @@
         <v>14</v>
       </c>
       <c r="B59" s="8">
-        <v>46000</v>
+        <v>46009</v>
       </c>
       <c r="C59" s="9">
-        <v>80</v>
+        <v>34</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -3032,10 +3026,10 @@
         <v>14</v>
       </c>
       <c r="B60" s="5">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C60" s="6">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -3043,10 +3037,10 @@
         <v>14</v>
       </c>
       <c r="B61" s="8">
-        <v>46006</v>
+        <v>46001</v>
       </c>
       <c r="C61" s="9">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -3054,10 +3048,10 @@
         <v>14</v>
       </c>
       <c r="B62" s="5">
-        <v>46010</v>
+        <v>46006</v>
       </c>
       <c r="C62" s="6">
-        <v>24</v>
+        <v>79</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -3065,10 +3059,10 @@
         <v>14</v>
       </c>
       <c r="B63" s="8">
-        <v>46014</v>
+        <v>46010</v>
       </c>
       <c r="C63" s="9">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -3076,10 +3070,10 @@
         <v>14</v>
       </c>
       <c r="B64" s="5">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="C64" s="6">
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -3087,10 +3081,10 @@
         <v>14</v>
       </c>
       <c r="B65" s="8">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C65" s="9">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -3098,10 +3092,10 @@
         <v>14</v>
       </c>
       <c r="B66" s="5">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="C66" s="6">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -3109,10 +3103,10 @@
         <v>14</v>
       </c>
       <c r="B67" s="8">
-        <v>46013</v>
+        <v>46003</v>
       </c>
       <c r="C67" s="9">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -3120,10 +3114,10 @@
         <v>14</v>
       </c>
       <c r="B68" s="5">
-        <v>46022</v>
+        <v>46013</v>
       </c>
       <c r="C68" s="6">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -3131,10 +3125,10 @@
         <v>14</v>
       </c>
       <c r="B69" s="8">
-        <v>46080</v>
+        <v>46022</v>
       </c>
       <c r="C69" s="9">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -3142,10 +3136,10 @@
         <v>14</v>
       </c>
       <c r="B70" s="5">
-        <v>46084</v>
+        <v>46080</v>
       </c>
       <c r="C70" s="6">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -3153,10 +3147,10 @@
         <v>14</v>
       </c>
       <c r="B71" s="8">
-        <v>46125</v>
+        <v>46084</v>
       </c>
       <c r="C71" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -3164,10 +3158,10 @@
         <v>14</v>
       </c>
       <c r="B72" s="5">
-        <v>46091</v>
+        <v>46125</v>
       </c>
       <c r="C72" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -3175,10 +3169,10 @@
         <v>14</v>
       </c>
       <c r="B73" s="8">
-        <v>46083</v>
+        <v>46091</v>
       </c>
       <c r="C73" s="9">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -3186,10 +3180,10 @@
         <v>14</v>
       </c>
       <c r="B74" s="5">
-        <v>46105</v>
+        <v>46083</v>
       </c>
       <c r="C74" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -3197,10 +3191,10 @@
         <v>14</v>
       </c>
       <c r="B75" s="8">
-        <v>46077</v>
+        <v>46105</v>
       </c>
       <c r="C75" s="9">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -3208,10 +3202,10 @@
         <v>14</v>
       </c>
       <c r="B76" s="5">
-        <v>46118</v>
+        <v>46077</v>
       </c>
       <c r="C76" s="6">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -3219,10 +3213,10 @@
         <v>14</v>
       </c>
       <c r="B77" s="8">
-        <v>46078</v>
+        <v>46118</v>
       </c>
       <c r="C77" s="9">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -3230,10 +3224,10 @@
         <v>14</v>
       </c>
       <c r="B78" s="5">
-        <v>46099</v>
+        <v>46078</v>
       </c>
       <c r="C78" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -3241,10 +3235,10 @@
         <v>14</v>
       </c>
       <c r="B79" s="8">
-        <v>46104</v>
+        <v>46099</v>
       </c>
       <c r="C79" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -3252,10 +3246,10 @@
         <v>14</v>
       </c>
       <c r="B80" s="5">
-        <v>46020</v>
+        <v>46104</v>
       </c>
       <c r="C80" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -3263,10 +3257,10 @@
         <v>14</v>
       </c>
       <c r="B81" s="8">
-        <v>46076</v>
+        <v>46020</v>
       </c>
       <c r="C81" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -3274,10 +3268,10 @@
         <v>14</v>
       </c>
       <c r="B82" s="5">
-        <v>46111</v>
+        <v>46076</v>
       </c>
       <c r="C82" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -3285,10 +3279,10 @@
         <v>14</v>
       </c>
       <c r="B83" s="8">
-        <v>46087</v>
+        <v>46111</v>
       </c>
       <c r="C83" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -3296,7 +3290,7 @@
         <v>14</v>
       </c>
       <c r="B84" s="5">
-        <v>46140</v>
+        <v>46087</v>
       </c>
       <c r="C84" s="6">
         <v>2</v>
@@ -3307,10 +3301,10 @@
         <v>14</v>
       </c>
       <c r="B85" s="8">
-        <v>46113</v>
+        <v>46140</v>
       </c>
       <c r="C85" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -3318,10 +3312,10 @@
         <v>14</v>
       </c>
       <c r="B86" s="5">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="C86" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -3329,10 +3323,10 @@
         <v>14</v>
       </c>
       <c r="B87" s="8">
-        <v>46108</v>
+        <v>46119</v>
       </c>
       <c r="C87" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -3340,7 +3334,7 @@
         <v>14</v>
       </c>
       <c r="B88" s="5">
-        <v>46098</v>
+        <v>46108</v>
       </c>
       <c r="C88" s="6">
         <v>1</v>
@@ -3351,7 +3345,7 @@
         <v>14</v>
       </c>
       <c r="B89" s="8">
-        <v>46141</v>
+        <v>46098</v>
       </c>
       <c r="C89" s="9">
         <v>1</v>
@@ -3362,7 +3356,7 @@
         <v>14</v>
       </c>
       <c r="B90" s="5">
-        <v>46114</v>
+        <v>46141</v>
       </c>
       <c r="C90" s="6">
         <v>1</v>
@@ -3373,10 +3367,10 @@
         <v>14</v>
       </c>
       <c r="B91" s="8">
-        <v>46079</v>
+        <v>46114</v>
       </c>
       <c r="C91" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -3384,10 +3378,10 @@
         <v>14</v>
       </c>
       <c r="B92" s="5">
-        <v>46139</v>
+        <v>46079</v>
       </c>
       <c r="C92" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -3395,10 +3389,10 @@
         <v>14</v>
       </c>
       <c r="B93" s="8">
-        <v>46148</v>
+        <v>46139</v>
       </c>
       <c r="C93" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -3406,10 +3400,10 @@
         <v>14</v>
       </c>
       <c r="B94" s="5">
-        <v>46174</v>
+        <v>46148</v>
       </c>
       <c r="C94" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -3417,7 +3411,7 @@
         <v>14</v>
       </c>
       <c r="B95" s="8">
-        <v>46092</v>
+        <v>46185</v>
       </c>
       <c r="C95" s="9">
         <v>1</v>
@@ -3428,10 +3422,10 @@
         <v>14</v>
       </c>
       <c r="B96" s="5">
-        <v>46021</v>
+        <v>46174</v>
       </c>
       <c r="C96" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -3439,10 +3433,10 @@
         <v>14</v>
       </c>
       <c r="B97" s="8">
-        <v>46086</v>
+        <v>46092</v>
       </c>
       <c r="C97" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -3450,10 +3444,10 @@
         <v>14</v>
       </c>
       <c r="B98" s="5">
-        <v>46147</v>
+        <v>46021</v>
       </c>
       <c r="C98" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -3461,43 +3455,43 @@
         <v>14</v>
       </c>
       <c r="B99" s="8">
-        <v>46134</v>
+        <v>46086</v>
       </c>
       <c r="C99" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B100" s="5">
-        <v>46003</v>
+        <v>46147</v>
       </c>
       <c r="C100" s="6">
-        <v>95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B101" s="8">
-        <v>46002</v>
+        <v>46134</v>
       </c>
       <c r="C101" s="9">
-        <v>115</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B102" s="5">
-        <v>46008</v>
+        <v>46182</v>
       </c>
       <c r="C102" s="6">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -3505,10 +3499,10 @@
         <v>3</v>
       </c>
       <c r="B103" s="8">
-        <v>46000</v>
+        <v>46003</v>
       </c>
       <c r="C103" s="9">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -3516,10 +3510,10 @@
         <v>3</v>
       </c>
       <c r="B104" s="5">
-        <v>46007</v>
+        <v>46002</v>
       </c>
       <c r="C104" s="6">
-        <v>40</v>
+        <v>115</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -3527,10 +3521,10 @@
         <v>3</v>
       </c>
       <c r="B105" s="8">
-        <v>46001</v>
+        <v>46008</v>
       </c>
       <c r="C105" s="9">
-        <v>91</v>
+        <v>14</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -3538,10 +3532,10 @@
         <v>3</v>
       </c>
       <c r="B106" s="5">
-        <v>46010</v>
+        <v>46000</v>
       </c>
       <c r="C106" s="6">
-        <v>9</v>
+        <v>98</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -3549,10 +3543,10 @@
         <v>3</v>
       </c>
       <c r="B107" s="8">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="C107" s="9">
-        <v>84</v>
+        <v>40</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -3560,10 +3554,10 @@
         <v>3</v>
       </c>
       <c r="B108" s="5">
-        <v>46009</v>
+        <v>46001</v>
       </c>
       <c r="C108" s="6">
-        <v>2</v>
+        <v>91</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -3571,10 +3565,10 @@
         <v>3</v>
       </c>
       <c r="B109" s="8">
-        <v>46015</v>
+        <v>46010</v>
       </c>
       <c r="C109" s="9">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -3582,10 +3576,10 @@
         <v>3</v>
       </c>
       <c r="B110" s="5">
-        <v>46014</v>
+        <v>46006</v>
       </c>
       <c r="C110" s="6">
-        <v>8</v>
+        <v>84</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -3593,10 +3587,10 @@
         <v>3</v>
       </c>
       <c r="B111" s="8">
-        <v>46013</v>
+        <v>46009</v>
       </c>
       <c r="C111" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -3604,10 +3598,10 @@
         <v>3</v>
       </c>
       <c r="B112" s="5">
-        <v>46021</v>
+        <v>46015</v>
       </c>
       <c r="C112" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -3615,7 +3609,7 @@
         <v>3</v>
       </c>
       <c r="B113" s="8">
-        <v>46077</v>
+        <v>46014</v>
       </c>
       <c r="C113" s="9">
         <v>8</v>
@@ -3626,10 +3620,10 @@
         <v>3</v>
       </c>
       <c r="B114" s="5">
-        <v>46167</v>
+        <v>46013</v>
       </c>
       <c r="C114" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -3637,10 +3631,10 @@
         <v>3</v>
       </c>
       <c r="B115" s="8">
-        <v>46090</v>
+        <v>46021</v>
       </c>
       <c r="C115" s="9">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -3648,10 +3642,10 @@
         <v>3</v>
       </c>
       <c r="B116" s="5">
-        <v>46170</v>
+        <v>46077</v>
       </c>
       <c r="C116" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -3659,7 +3653,7 @@
         <v>3</v>
       </c>
       <c r="B117" s="8">
-        <v>46093</v>
+        <v>46167</v>
       </c>
       <c r="C117" s="9">
         <v>1</v>
@@ -3670,10 +3664,10 @@
         <v>3</v>
       </c>
       <c r="B118" s="5">
-        <v>46078</v>
+        <v>46090</v>
       </c>
       <c r="C118" s="6">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -3681,10 +3675,10 @@
         <v>3</v>
       </c>
       <c r="B119" s="8">
-        <v>46084</v>
+        <v>46170</v>
       </c>
       <c r="C119" s="9">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -3692,10 +3686,10 @@
         <v>3</v>
       </c>
       <c r="B120" s="5">
-        <v>46134</v>
+        <v>46093</v>
       </c>
       <c r="C120" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -3703,10 +3697,10 @@
         <v>3</v>
       </c>
       <c r="B121" s="8">
-        <v>46083</v>
+        <v>46078</v>
       </c>
       <c r="C121" s="9">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -3714,10 +3708,10 @@
         <v>3</v>
       </c>
       <c r="B122" s="5">
-        <v>46022</v>
+        <v>46084</v>
       </c>
       <c r="C122" s="6">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -3725,7 +3719,7 @@
         <v>3</v>
       </c>
       <c r="B123" s="8">
-        <v>46114</v>
+        <v>46134</v>
       </c>
       <c r="C123" s="9">
         <v>2</v>
@@ -3736,10 +3730,10 @@
         <v>3</v>
       </c>
       <c r="B124" s="5">
-        <v>46135</v>
+        <v>46083</v>
       </c>
       <c r="C124" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -3747,10 +3741,10 @@
         <v>3</v>
       </c>
       <c r="B125" s="8">
-        <v>46168</v>
+        <v>46022</v>
       </c>
       <c r="C125" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
@@ -3758,10 +3752,10 @@
         <v>3</v>
       </c>
       <c r="B126" s="5">
-        <v>46126</v>
+        <v>46114</v>
       </c>
       <c r="C126" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -3769,10 +3763,10 @@
         <v>3</v>
       </c>
       <c r="B127" s="8">
-        <v>46120</v>
+        <v>46135</v>
       </c>
       <c r="C127" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -3780,10 +3774,10 @@
         <v>3</v>
       </c>
       <c r="B128" s="5">
-        <v>46127</v>
+        <v>46168</v>
       </c>
       <c r="C128" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -3791,10 +3785,10 @@
         <v>3</v>
       </c>
       <c r="B129" s="8">
-        <v>46087</v>
+        <v>46126</v>
       </c>
       <c r="C129" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -3802,10 +3796,10 @@
         <v>3</v>
       </c>
       <c r="B130" s="5">
-        <v>46108</v>
+        <v>46120</v>
       </c>
       <c r="C130" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -3813,7 +3807,7 @@
         <v>3</v>
       </c>
       <c r="B131" s="8">
-        <v>46020</v>
+        <v>46127</v>
       </c>
       <c r="C131" s="9">
         <v>1</v>
@@ -3824,7 +3818,7 @@
         <v>3</v>
       </c>
       <c r="B132" s="5">
-        <v>46097</v>
+        <v>46087</v>
       </c>
       <c r="C132" s="6">
         <v>1</v>
@@ -3835,7 +3829,7 @@
         <v>3</v>
       </c>
       <c r="B133" s="8">
-        <v>46177</v>
+        <v>46108</v>
       </c>
       <c r="C133" s="9">
         <v>1</v>
@@ -3846,10 +3840,10 @@
         <v>3</v>
       </c>
       <c r="B134" s="5">
-        <v>46161</v>
+        <v>46020</v>
       </c>
       <c r="C134" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -3857,7 +3851,7 @@
         <v>3</v>
       </c>
       <c r="B135" s="8">
-        <v>46129</v>
+        <v>46097</v>
       </c>
       <c r="C135" s="9">
         <v>1</v>
@@ -3868,7 +3862,7 @@
         <v>3</v>
       </c>
       <c r="B136" s="5">
-        <v>46080</v>
+        <v>46177</v>
       </c>
       <c r="C136" s="6">
         <v>1</v>
@@ -3879,10 +3873,10 @@
         <v>3</v>
       </c>
       <c r="B137" s="8">
-        <v>46101</v>
+        <v>46161</v>
       </c>
       <c r="C137" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -3890,7 +3884,7 @@
         <v>3</v>
       </c>
       <c r="B138" s="5">
-        <v>46155</v>
+        <v>46129</v>
       </c>
       <c r="C138" s="6">
         <v>1</v>
@@ -3901,7 +3895,7 @@
         <v>3</v>
       </c>
       <c r="B139" s="8">
-        <v>46150</v>
+        <v>46080</v>
       </c>
       <c r="C139" s="9">
         <v>1</v>
@@ -3912,7 +3906,7 @@
         <v>3</v>
       </c>
       <c r="B140" s="5">
-        <v>46141</v>
+        <v>46101</v>
       </c>
       <c r="C140" s="6">
         <v>1</v>
@@ -3923,7 +3917,7 @@
         <v>3</v>
       </c>
       <c r="B141" s="8">
-        <v>46085</v>
+        <v>46155</v>
       </c>
       <c r="C141" s="9">
         <v>1</v>
@@ -3934,7 +3928,7 @@
         <v>3</v>
       </c>
       <c r="B142" s="5">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="C142" s="6">
         <v>1</v>
@@ -3945,10 +3939,10 @@
         <v>3</v>
       </c>
       <c r="B143" s="8">
-        <v>46118</v>
+        <v>46141</v>
       </c>
       <c r="C143" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -3956,7 +3950,7 @@
         <v>3</v>
       </c>
       <c r="B144" s="5">
-        <v>46079</v>
+        <v>46085</v>
       </c>
       <c r="C144" s="6">
         <v>1</v>
@@ -3964,35 +3958,35 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B145" s="8">
-        <v>46003</v>
+        <v>46148</v>
       </c>
       <c r="C145" s="9">
-        <v>92</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B146" s="5">
-        <v>46000</v>
+        <v>46118</v>
       </c>
       <c r="C146" s="6">
-        <v>132</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B147" s="8">
-        <v>46006</v>
+        <v>46079</v>
       </c>
       <c r="C147" s="9">
-        <v>173</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -4000,10 +3994,10 @@
         <v>15</v>
       </c>
       <c r="B148" s="5">
-        <v>46001</v>
+        <v>46003</v>
       </c>
       <c r="C148" s="6">
-        <v>174</v>
+        <v>92</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -4011,10 +4005,10 @@
         <v>15</v>
       </c>
       <c r="B149" s="8">
-        <v>46014</v>
+        <v>46000</v>
       </c>
       <c r="C149" s="9">
-        <v>16</v>
+        <v>132</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -4022,10 +4016,10 @@
         <v>15</v>
       </c>
       <c r="B150" s="5">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="C150" s="6">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -4033,10 +4027,10 @@
         <v>15</v>
       </c>
       <c r="B151" s="8">
-        <v>46009</v>
+        <v>46001</v>
       </c>
       <c r="C151" s="9">
-        <v>19</v>
+        <v>174</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -4044,10 +4038,10 @@
         <v>15</v>
       </c>
       <c r="B152" s="5">
-        <v>46010</v>
+        <v>46014</v>
       </c>
       <c r="C152" s="6">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -4055,10 +4049,10 @@
         <v>15</v>
       </c>
       <c r="B153" s="8">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C153" s="9">
-        <v>25</v>
+        <v>171</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -4066,10 +4060,10 @@
         <v>15</v>
       </c>
       <c r="B154" s="5">
-        <v>46007</v>
+        <v>46009</v>
       </c>
       <c r="C154" s="6">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -4077,10 +4071,10 @@
         <v>15</v>
       </c>
       <c r="B155" s="8">
-        <v>46013</v>
+        <v>46010</v>
       </c>
       <c r="C155" s="9">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -4088,10 +4082,10 @@
         <v>15</v>
       </c>
       <c r="B156" s="5">
-        <v>46080</v>
+        <v>46008</v>
       </c>
       <c r="C156" s="6">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -4099,10 +4093,10 @@
         <v>15</v>
       </c>
       <c r="B157" s="8">
-        <v>46090</v>
+        <v>46007</v>
       </c>
       <c r="C157" s="9">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -4110,10 +4104,10 @@
         <v>15</v>
       </c>
       <c r="B158" s="5">
-        <v>46079</v>
+        <v>46013</v>
       </c>
       <c r="C158" s="6">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -4121,10 +4115,10 @@
         <v>15</v>
       </c>
       <c r="B159" s="8">
-        <v>46015</v>
+        <v>46080</v>
       </c>
       <c r="C159" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -4132,10 +4126,10 @@
         <v>15</v>
       </c>
       <c r="B160" s="5">
-        <v>46085</v>
+        <v>46090</v>
       </c>
       <c r="C160" s="6">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -4143,10 +4137,10 @@
         <v>15</v>
       </c>
       <c r="B161" s="8">
-        <v>46098</v>
+        <v>46079</v>
       </c>
       <c r="C161" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -4154,10 +4148,10 @@
         <v>15</v>
       </c>
       <c r="B162" s="5">
-        <v>46021</v>
+        <v>46015</v>
       </c>
       <c r="C162" s="6">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -4165,10 +4159,10 @@
         <v>15</v>
       </c>
       <c r="B163" s="8">
-        <v>46078</v>
+        <v>46085</v>
       </c>
       <c r="C163" s="9">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -4176,10 +4170,10 @@
         <v>15</v>
       </c>
       <c r="B164" s="5">
-        <v>46084</v>
+        <v>46098</v>
       </c>
       <c r="C164" s="6">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -4187,10 +4181,10 @@
         <v>15</v>
       </c>
       <c r="B165" s="8">
-        <v>46128</v>
+        <v>46021</v>
       </c>
       <c r="C165" s="9">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -4198,10 +4192,10 @@
         <v>15</v>
       </c>
       <c r="B166" s="5">
-        <v>46083</v>
+        <v>46078</v>
       </c>
       <c r="C166" s="6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -4209,10 +4203,10 @@
         <v>15</v>
       </c>
       <c r="B167" s="8">
-        <v>46076</v>
+        <v>46084</v>
       </c>
       <c r="C167" s="9">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -4220,10 +4214,10 @@
         <v>15</v>
       </c>
       <c r="B168" s="5">
-        <v>46099</v>
+        <v>46128</v>
       </c>
       <c r="C168" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -4231,10 +4225,10 @@
         <v>15</v>
       </c>
       <c r="B169" s="8">
-        <v>46154</v>
+        <v>46083</v>
       </c>
       <c r="C169" s="9">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -4242,10 +4236,10 @@
         <v>15</v>
       </c>
       <c r="B170" s="5">
-        <v>46092</v>
+        <v>46076</v>
       </c>
       <c r="C170" s="6">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -4253,7 +4247,7 @@
         <v>15</v>
       </c>
       <c r="B171" s="8">
-        <v>46031</v>
+        <v>46099</v>
       </c>
       <c r="C171" s="9">
         <v>2</v>
@@ -4264,10 +4258,10 @@
         <v>15</v>
       </c>
       <c r="B172" s="5">
-        <v>46120</v>
+        <v>46154</v>
       </c>
       <c r="C172" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -4275,10 +4269,10 @@
         <v>15</v>
       </c>
       <c r="B173" s="8">
-        <v>46077</v>
+        <v>46092</v>
       </c>
       <c r="C173" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -4286,10 +4280,10 @@
         <v>15</v>
       </c>
       <c r="B174" s="5">
-        <v>46114</v>
+        <v>46031</v>
       </c>
       <c r="C174" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -4297,10 +4291,10 @@
         <v>15</v>
       </c>
       <c r="B175" s="8">
-        <v>46037</v>
+        <v>46120</v>
       </c>
       <c r="C175" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -4308,10 +4302,10 @@
         <v>15</v>
       </c>
       <c r="B176" s="5">
-        <v>46020</v>
+        <v>46077</v>
       </c>
       <c r="C176" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -4319,7 +4313,7 @@
         <v>15</v>
       </c>
       <c r="B177" s="8">
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="C177" s="9">
         <v>1</v>
@@ -4330,7 +4324,7 @@
         <v>15</v>
       </c>
       <c r="B178" s="5">
-        <v>46155</v>
+        <v>46037</v>
       </c>
       <c r="C178" s="6">
         <v>1</v>
@@ -4341,10 +4335,10 @@
         <v>15</v>
       </c>
       <c r="B179" s="8">
-        <v>46112</v>
+        <v>46020</v>
       </c>
       <c r="C179" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -4352,7 +4346,7 @@
         <v>15</v>
       </c>
       <c r="B180" s="5">
-        <v>46132</v>
+        <v>46106</v>
       </c>
       <c r="C180" s="6">
         <v>1</v>
@@ -4363,7 +4357,7 @@
         <v>15</v>
       </c>
       <c r="B181" s="8">
-        <v>46108</v>
+        <v>46155</v>
       </c>
       <c r="C181" s="9">
         <v>1</v>
@@ -4374,7 +4368,7 @@
         <v>15</v>
       </c>
       <c r="B182" s="5">
-        <v>46148</v>
+        <v>46112</v>
       </c>
       <c r="C182" s="6">
         <v>1</v>
@@ -4385,7 +4379,7 @@
         <v>15</v>
       </c>
       <c r="B183" s="8">
-        <v>46118</v>
+        <v>46132</v>
       </c>
       <c r="C183" s="9">
         <v>1</v>
@@ -4396,7 +4390,7 @@
         <v>15</v>
       </c>
       <c r="B184" s="5">
-        <v>46035</v>
+        <v>46108</v>
       </c>
       <c r="C184" s="6">
         <v>1</v>
@@ -4407,7 +4401,7 @@
         <v>15</v>
       </c>
       <c r="B185" s="8">
-        <v>46181</v>
+        <v>46148</v>
       </c>
       <c r="C185" s="9">
         <v>1</v>
@@ -4418,7 +4412,7 @@
         <v>15</v>
       </c>
       <c r="B186" s="5">
-        <v>46093</v>
+        <v>46118</v>
       </c>
       <c r="C186" s="6">
         <v>1</v>
@@ -4429,7 +4423,7 @@
         <v>15</v>
       </c>
       <c r="B187" s="8">
-        <v>46022</v>
+        <v>46035</v>
       </c>
       <c r="C187" s="9">
         <v>1</v>
@@ -4440,7 +4434,7 @@
         <v>15</v>
       </c>
       <c r="B188" s="5">
-        <v>46087</v>
+        <v>46181</v>
       </c>
       <c r="C188" s="6">
         <v>1</v>
@@ -4451,10 +4445,10 @@
         <v>15</v>
       </c>
       <c r="B189" s="8">
-        <v>46030</v>
+        <v>46093</v>
       </c>
       <c r="C189" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
@@ -4462,7 +4456,7 @@
         <v>15</v>
       </c>
       <c r="B190" s="5">
-        <v>46176</v>
+        <v>46022</v>
       </c>
       <c r="C190" s="6">
         <v>1</v>
@@ -4473,7 +4467,7 @@
         <v>15</v>
       </c>
       <c r="B191" s="8">
-        <v>46101</v>
+        <v>46087</v>
       </c>
       <c r="C191" s="9">
         <v>1</v>
@@ -4484,43 +4478,43 @@
         <v>15</v>
       </c>
       <c r="B192" s="5">
-        <v>46142</v>
+        <v>46030</v>
       </c>
       <c r="C192" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B193" s="8">
-        <v>46001</v>
+        <v>46176</v>
       </c>
       <c r="C193" s="9">
-        <v>153</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B194" s="5">
-        <v>46008</v>
+        <v>46101</v>
       </c>
       <c r="C194" s="6">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B195" s="8">
-        <v>46003</v>
+        <v>46142</v>
       </c>
       <c r="C195" s="9">
-        <v>70</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -4528,10 +4522,10 @@
         <v>21</v>
       </c>
       <c r="B196" s="5">
-        <v>46002</v>
+        <v>46001</v>
       </c>
       <c r="C196" s="6">
-        <v>111</v>
+        <v>153</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -4539,10 +4533,10 @@
         <v>21</v>
       </c>
       <c r="B197" s="8">
-        <v>46006</v>
+        <v>46008</v>
       </c>
       <c r="C197" s="9">
-        <v>146</v>
+        <v>38</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -4550,10 +4544,10 @@
         <v>21</v>
       </c>
       <c r="B198" s="5">
-        <v>46007</v>
+        <v>46003</v>
       </c>
       <c r="C198" s="6">
-        <v>45</v>
+        <v>70</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -4561,10 +4555,10 @@
         <v>21</v>
       </c>
       <c r="B199" s="8">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="C199" s="9">
-        <v>127</v>
+        <v>111</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -4572,10 +4566,10 @@
         <v>21</v>
       </c>
       <c r="B200" s="5">
-        <v>46084</v>
+        <v>46006</v>
       </c>
       <c r="C200" s="6">
-        <v>10</v>
+        <v>146</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -4583,10 +4577,10 @@
         <v>21</v>
       </c>
       <c r="B201" s="8">
-        <v>46014</v>
+        <v>46007</v>
       </c>
       <c r="C201" s="9">
-        <v>21</v>
+        <v>45</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -4594,10 +4588,10 @@
         <v>21</v>
       </c>
       <c r="B202" s="5">
-        <v>46013</v>
+        <v>46000</v>
       </c>
       <c r="C202" s="6">
-        <v>27</v>
+        <v>127</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -4605,10 +4599,10 @@
         <v>21</v>
       </c>
       <c r="B203" s="8">
-        <v>46010</v>
+        <v>46084</v>
       </c>
       <c r="C203" s="9">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -4616,10 +4610,10 @@
         <v>21</v>
       </c>
       <c r="B204" s="5">
-        <v>46021</v>
+        <v>46013</v>
       </c>
       <c r="C204" s="6">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -4627,10 +4621,10 @@
         <v>21</v>
       </c>
       <c r="B205" s="8">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="C205" s="9">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -4638,10 +4632,10 @@
         <v>21</v>
       </c>
       <c r="B206" s="5">
-        <v>46083</v>
+        <v>46021</v>
       </c>
       <c r="C206" s="6">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -4649,10 +4643,10 @@
         <v>21</v>
       </c>
       <c r="B207" s="8">
-        <v>46157</v>
+        <v>46009</v>
       </c>
       <c r="C207" s="9">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4660,10 +4654,10 @@
         <v>21</v>
       </c>
       <c r="B208" s="5">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="C208" s="6">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4671,10 +4665,10 @@
         <v>21</v>
       </c>
       <c r="B209" s="8">
-        <v>46167</v>
+        <v>46014</v>
       </c>
       <c r="C209" s="9">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4682,10 +4676,10 @@
         <v>21</v>
       </c>
       <c r="B210" s="5">
-        <v>46077</v>
+        <v>46157</v>
       </c>
       <c r="C210" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -4693,10 +4687,10 @@
         <v>21</v>
       </c>
       <c r="B211" s="8">
-        <v>46035</v>
+        <v>46079</v>
       </c>
       <c r="C211" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -4704,10 +4698,10 @@
         <v>21</v>
       </c>
       <c r="B212" s="5">
-        <v>46085</v>
+        <v>46167</v>
       </c>
       <c r="C212" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4715,10 +4709,10 @@
         <v>21</v>
       </c>
       <c r="B213" s="8">
-        <v>46120</v>
+        <v>46077</v>
       </c>
       <c r="C213" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4726,10 +4720,10 @@
         <v>21</v>
       </c>
       <c r="B214" s="5">
-        <v>46114</v>
+        <v>46035</v>
       </c>
       <c r="C214" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4737,10 +4731,10 @@
         <v>21</v>
       </c>
       <c r="B215" s="8">
-        <v>46094</v>
+        <v>46085</v>
       </c>
       <c r="C215" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4748,10 +4742,10 @@
         <v>21</v>
       </c>
       <c r="B216" s="5">
-        <v>46080</v>
+        <v>46120</v>
       </c>
       <c r="C216" s="6">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4759,10 +4753,10 @@
         <v>21</v>
       </c>
       <c r="B217" s="8">
-        <v>46127</v>
+        <v>46114</v>
       </c>
       <c r="C217" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -4770,10 +4764,10 @@
         <v>21</v>
       </c>
       <c r="B218" s="5">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="C218" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -4781,10 +4775,10 @@
         <v>21</v>
       </c>
       <c r="B219" s="8">
-        <v>46090</v>
+        <v>46080</v>
       </c>
       <c r="C219" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4792,7 +4786,7 @@
         <v>21</v>
       </c>
       <c r="B220" s="5">
-        <v>46020</v>
+        <v>46127</v>
       </c>
       <c r="C220" s="6">
         <v>2</v>
@@ -4803,10 +4797,10 @@
         <v>21</v>
       </c>
       <c r="B221" s="8">
-        <v>46015</v>
+        <v>46091</v>
       </c>
       <c r="C221" s="9">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -4814,10 +4808,10 @@
         <v>21</v>
       </c>
       <c r="B222" s="5">
-        <v>46078</v>
+        <v>46090</v>
       </c>
       <c r="C222" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -4825,7 +4819,7 @@
         <v>21</v>
       </c>
       <c r="B223" s="8">
-        <v>46148</v>
+        <v>46020</v>
       </c>
       <c r="C223" s="9">
         <v>2</v>
@@ -4836,10 +4830,10 @@
         <v>21</v>
       </c>
       <c r="B224" s="5">
-        <v>46105</v>
+        <v>46015</v>
       </c>
       <c r="C224" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -4847,10 +4841,10 @@
         <v>21</v>
       </c>
       <c r="B225" s="8">
-        <v>46087</v>
+        <v>46078</v>
       </c>
       <c r="C225" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -4858,10 +4852,10 @@
         <v>21</v>
       </c>
       <c r="B226" s="5">
-        <v>46107</v>
+        <v>46148</v>
       </c>
       <c r="C226" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -4869,10 +4863,10 @@
         <v>21</v>
       </c>
       <c r="B227" s="8">
-        <v>46086</v>
+        <v>46105</v>
       </c>
       <c r="C227" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -4880,10 +4874,10 @@
         <v>21</v>
       </c>
       <c r="B228" s="5">
-        <v>46106</v>
+        <v>46087</v>
       </c>
       <c r="C228" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -4891,7 +4885,7 @@
         <v>21</v>
       </c>
       <c r="B229" s="8">
-        <v>46150</v>
+        <v>46107</v>
       </c>
       <c r="C229" s="9">
         <v>3</v>
@@ -4902,10 +4896,10 @@
         <v>21</v>
       </c>
       <c r="B230" s="5">
-        <v>46104</v>
+        <v>46086</v>
       </c>
       <c r="C230" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -4913,7 +4907,7 @@
         <v>21</v>
       </c>
       <c r="B231" s="8">
-        <v>46118</v>
+        <v>46106</v>
       </c>
       <c r="C231" s="9">
         <v>1</v>
@@ -4924,10 +4918,10 @@
         <v>21</v>
       </c>
       <c r="B232" s="5">
-        <v>46076</v>
+        <v>46150</v>
       </c>
       <c r="C232" s="6">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -4935,10 +4929,10 @@
         <v>21</v>
       </c>
       <c r="B233" s="8">
-        <v>46182</v>
+        <v>46104</v>
       </c>
       <c r="C233" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -4946,7 +4940,7 @@
         <v>21</v>
       </c>
       <c r="B234" s="5">
-        <v>46154</v>
+        <v>46118</v>
       </c>
       <c r="C234" s="6">
         <v>1</v>
@@ -4957,10 +4951,10 @@
         <v>21</v>
       </c>
       <c r="B235" s="8">
-        <v>46093</v>
+        <v>46076</v>
       </c>
       <c r="C235" s="9">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -4968,7 +4962,7 @@
         <v>21</v>
       </c>
       <c r="B236" s="5">
-        <v>46122</v>
+        <v>46182</v>
       </c>
       <c r="C236" s="6">
         <v>1</v>
@@ -4979,10 +4973,10 @@
         <v>21</v>
       </c>
       <c r="B237" s="8">
-        <v>46092</v>
+        <v>46154</v>
       </c>
       <c r="C237" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -4990,10 +4984,10 @@
         <v>21</v>
       </c>
       <c r="B238" s="5">
-        <v>46156</v>
+        <v>46093</v>
       </c>
       <c r="C238" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -5001,7 +4995,7 @@
         <v>21</v>
       </c>
       <c r="B239" s="8">
-        <v>46133</v>
+        <v>46122</v>
       </c>
       <c r="C239" s="9">
         <v>1</v>
@@ -5012,10 +5006,10 @@
         <v>21</v>
       </c>
       <c r="B240" s="5">
-        <v>46126</v>
+        <v>46092</v>
       </c>
       <c r="C240" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -5023,7 +5017,7 @@
         <v>21</v>
       </c>
       <c r="B241" s="8">
-        <v>46022</v>
+        <v>46156</v>
       </c>
       <c r="C241" s="9">
         <v>2</v>
@@ -5034,10 +5028,10 @@
         <v>21</v>
       </c>
       <c r="B242" s="5">
-        <v>46100</v>
+        <v>46133</v>
       </c>
       <c r="C242" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -5045,7 +5039,7 @@
         <v>21</v>
       </c>
       <c r="B243" s="8">
-        <v>46101</v>
+        <v>46126</v>
       </c>
       <c r="C243" s="9">
         <v>1</v>
@@ -5056,10 +5050,10 @@
         <v>21</v>
       </c>
       <c r="B244" s="5">
-        <v>46097</v>
+        <v>46022</v>
       </c>
       <c r="C244" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -5067,10 +5061,10 @@
         <v>21</v>
       </c>
       <c r="B245" s="8">
-        <v>46108</v>
+        <v>46100</v>
       </c>
       <c r="C245" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
@@ -5078,10 +5072,10 @@
         <v>21</v>
       </c>
       <c r="B246" s="5">
-        <v>46098</v>
+        <v>46101</v>
       </c>
       <c r="C246" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -5089,10 +5083,10 @@
         <v>21</v>
       </c>
       <c r="B247" s="8">
-        <v>46113</v>
+        <v>46097</v>
       </c>
       <c r="C247" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
@@ -5100,7 +5094,7 @@
         <v>21</v>
       </c>
       <c r="B248" s="5">
-        <v>46142</v>
+        <v>46108</v>
       </c>
       <c r="C248" s="6">
         <v>1</v>
@@ -5111,10 +5105,10 @@
         <v>21</v>
       </c>
       <c r="B249" s="8">
-        <v>46153</v>
+        <v>46098</v>
       </c>
       <c r="C249" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
@@ -5122,7 +5116,7 @@
         <v>21</v>
       </c>
       <c r="B250" s="5">
-        <v>46031</v>
+        <v>46113</v>
       </c>
       <c r="C250" s="6">
         <v>1</v>
@@ -5133,9 +5127,42 @@
         <v>21</v>
       </c>
       <c r="B251" s="8">
+        <v>46142</v>
+      </c>
+      <c r="C251" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B252" s="5">
+        <v>46153</v>
+      </c>
+      <c r="C252" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B253" s="8">
+        <v>46031</v>
+      </c>
+      <c r="C253" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B254" s="5">
         <v>46155</v>
       </c>
-      <c r="C251" s="9">
+      <c r="C254" s="6">
         <v>1</v>
       </c>
     </row>
@@ -5457,7 +5484,7 @@
         <v>1</v>
       </c>
       <c r="E18">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -5491,7 +5518,7 @@
         <v>9</v>
       </c>
       <c r="E20">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -5692,10 +5719,10 @@
         <v>83</v>
       </c>
       <c r="D32">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E32">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -5743,7 +5770,7 @@
         <v>209</v>
       </c>
       <c r="D35">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E35">
         <v>5</v>
@@ -5757,7 +5784,7 @@
         <v>17</v>
       </c>
       <c r="C36">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D36">
         <v>87</v>
@@ -5824,7 +5851,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0916EAC6-1E7F-4924-9D0E-33749FD3E143}">
-  <dimension ref="A1:C351"/>
+  <dimension ref="A1:C349"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
@@ -5837,7 +5864,7 @@
         <v>37</v>
       </c>
       <c r="B1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C1" t="s">
         <v>36</v>
@@ -6321,7 +6348,7 @@
         <v>14</v>
       </c>
       <c r="B45" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="C45">
         <v>4</v>
@@ -6332,7 +6359,7 @@
         <v>14</v>
       </c>
       <c r="B46" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="C46">
         <v>4</v>
@@ -6343,7 +6370,7 @@
         <v>14</v>
       </c>
       <c r="B47" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="C47">
         <v>3</v>
@@ -6354,7 +6381,7 @@
         <v>14</v>
       </c>
       <c r="B48" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C48">
         <v>3</v>
@@ -6365,10 +6392,10 @@
         <v>14</v>
       </c>
       <c r="B49" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="C49">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -6376,7 +6403,7 @@
         <v>14</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="C50">
         <v>2</v>
@@ -6387,7 +6414,7 @@
         <v>14</v>
       </c>
       <c r="B51" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C51">
         <v>2</v>
@@ -6398,7 +6425,7 @@
         <v>14</v>
       </c>
       <c r="B52" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C52">
         <v>2</v>
@@ -6409,7 +6436,7 @@
         <v>14</v>
       </c>
       <c r="B53" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C53">
         <v>2</v>
@@ -6420,7 +6447,7 @@
         <v>14</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C54">
         <v>2</v>
@@ -6431,7 +6458,7 @@
         <v>14</v>
       </c>
       <c r="B55" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C55">
         <v>2</v>
@@ -6442,7 +6469,7 @@
         <v>14</v>
       </c>
       <c r="B56" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C56">
         <v>2</v>
@@ -6453,7 +6480,7 @@
         <v>14</v>
       </c>
       <c r="B57" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C57">
         <v>2</v>
@@ -6464,7 +6491,7 @@
         <v>14</v>
       </c>
       <c r="B58" t="s">
-        <v>78</v>
+        <v>49</v>
       </c>
       <c r="C58">
         <v>2</v>
@@ -6475,7 +6502,7 @@
         <v>14</v>
       </c>
       <c r="B59" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C59">
         <v>2</v>
@@ -6486,7 +6513,7 @@
         <v>14</v>
       </c>
       <c r="B60" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C60">
         <v>2</v>
@@ -6508,7 +6535,7 @@
         <v>14</v>
       </c>
       <c r="B62" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="C62">
         <v>2</v>
@@ -6519,7 +6546,7 @@
         <v>14</v>
       </c>
       <c r="B63" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -6640,7 +6667,7 @@
         <v>14</v>
       </c>
       <c r="B74" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -6695,7 +6722,7 @@
         <v>14</v>
       </c>
       <c r="B79" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -6706,7 +6733,7 @@
         <v>14</v>
       </c>
       <c r="B80" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="C80">
         <v>1</v>
@@ -6739,7 +6766,7 @@
         <v>14</v>
       </c>
       <c r="B83" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -6772,7 +6799,7 @@
         <v>14</v>
       </c>
       <c r="B86" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C86">
         <v>1</v>
@@ -6794,7 +6821,7 @@
         <v>14</v>
       </c>
       <c r="B88" t="s">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -7949,7 +7976,7 @@
         <v>16</v>
       </c>
       <c r="B193" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="C193">
         <v>11</v>
@@ -7960,7 +7987,7 @@
         <v>16</v>
       </c>
       <c r="B194" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="C194">
         <v>11</v>
@@ -8059,7 +8086,7 @@
         <v>16</v>
       </c>
       <c r="B203" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C203">
         <v>5</v>
@@ -8070,7 +8097,7 @@
         <v>16</v>
       </c>
       <c r="B204" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="C204">
         <v>5</v>
@@ -8081,7 +8108,7 @@
         <v>16</v>
       </c>
       <c r="B205" t="s">
-        <v>198</v>
+        <v>71</v>
       </c>
       <c r="C205">
         <v>5</v>
@@ -8092,7 +8119,7 @@
         <v>16</v>
       </c>
       <c r="B206" t="s">
-        <v>73</v>
+        <v>200</v>
       </c>
       <c r="C206">
         <v>5</v>
@@ -8103,10 +8130,10 @@
         <v>16</v>
       </c>
       <c r="B207" t="s">
-        <v>197</v>
+        <v>73</v>
       </c>
       <c r="C207">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -8114,7 +8141,7 @@
         <v>16</v>
       </c>
       <c r="B208" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="C208">
         <v>4</v>
@@ -8125,7 +8152,7 @@
         <v>16</v>
       </c>
       <c r="B209" t="s">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="C209">
         <v>4</v>
@@ -8136,7 +8163,7 @@
         <v>16</v>
       </c>
       <c r="B210" t="s">
-        <v>199</v>
+        <v>47</v>
       </c>
       <c r="C210">
         <v>4</v>
@@ -8147,7 +8174,7 @@
         <v>16</v>
       </c>
       <c r="B211" t="s">
-        <v>60</v>
+        <v>197</v>
       </c>
       <c r="C211">
         <v>4</v>
@@ -8158,7 +8185,7 @@
         <v>16</v>
       </c>
       <c r="B212" t="s">
-        <v>78</v>
+        <v>199</v>
       </c>
       <c r="C212">
         <v>4</v>
@@ -8180,7 +8207,7 @@
         <v>16</v>
       </c>
       <c r="B214" t="s">
-        <v>118</v>
+        <v>201</v>
       </c>
       <c r="C214">
         <v>3</v>
@@ -8191,7 +8218,7 @@
         <v>16</v>
       </c>
       <c r="B215" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C215">
         <v>3</v>
@@ -8202,7 +8229,7 @@
         <v>16</v>
       </c>
       <c r="B216" t="s">
-        <v>201</v>
+        <v>59</v>
       </c>
       <c r="C216">
         <v>3</v>
@@ -8235,7 +8262,7 @@
         <v>16</v>
       </c>
       <c r="B219" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C219">
         <v>3</v>
@@ -8246,7 +8273,7 @@
         <v>16</v>
       </c>
       <c r="B220" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="C220">
         <v>3</v>
@@ -8257,7 +8284,7 @@
         <v>16</v>
       </c>
       <c r="B221" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C221">
         <v>3</v>
@@ -8268,7 +8295,7 @@
         <v>16</v>
       </c>
       <c r="B222" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="C222">
         <v>2</v>
@@ -8279,7 +8306,7 @@
         <v>16</v>
       </c>
       <c r="B223" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C223">
         <v>2</v>
@@ -8290,7 +8317,7 @@
         <v>16</v>
       </c>
       <c r="B224" t="s">
-        <v>64</v>
+        <v>203</v>
       </c>
       <c r="C224">
         <v>2</v>
@@ -8301,7 +8328,7 @@
         <v>16</v>
       </c>
       <c r="B225" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C225">
         <v>2</v>
@@ -8312,7 +8339,7 @@
         <v>16</v>
       </c>
       <c r="B226" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C226">
         <v>2</v>
@@ -8323,7 +8350,7 @@
         <v>16</v>
       </c>
       <c r="B227" t="s">
-        <v>206</v>
+        <v>64</v>
       </c>
       <c r="C227">
         <v>2</v>
@@ -8334,7 +8361,7 @@
         <v>16</v>
       </c>
       <c r="B228" t="s">
-        <v>202</v>
+        <v>189</v>
       </c>
       <c r="C228">
         <v>2</v>
@@ -8345,7 +8372,7 @@
         <v>16</v>
       </c>
       <c r="B229" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C229">
         <v>2</v>
@@ -8356,7 +8383,7 @@
         <v>16</v>
       </c>
       <c r="B230" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="C230">
         <v>1</v>
@@ -8367,7 +8394,7 @@
         <v>16</v>
       </c>
       <c r="B231" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C231">
         <v>1</v>
@@ -8378,7 +8405,7 @@
         <v>16</v>
       </c>
       <c r="B232" t="s">
-        <v>247</v>
+        <v>213</v>
       </c>
       <c r="C232">
         <v>1</v>
@@ -8389,7 +8416,7 @@
         <v>16</v>
       </c>
       <c r="B233" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C233">
         <v>1</v>
@@ -8400,7 +8427,7 @@
         <v>16</v>
       </c>
       <c r="B234" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C234">
         <v>1</v>
@@ -8411,7 +8438,7 @@
         <v>16</v>
       </c>
       <c r="B235" t="s">
-        <v>214</v>
+        <v>241</v>
       </c>
       <c r="C235">
         <v>1</v>
@@ -8422,7 +8449,7 @@
         <v>16</v>
       </c>
       <c r="B236" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C236">
         <v>1</v>
@@ -8433,7 +8460,7 @@
         <v>16</v>
       </c>
       <c r="B237" t="s">
-        <v>215</v>
+        <v>70</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -8444,7 +8471,7 @@
         <v>16</v>
       </c>
       <c r="B238" t="s">
-        <v>119</v>
+        <v>245</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -8455,7 +8482,7 @@
         <v>16</v>
       </c>
       <c r="B239" t="s">
-        <v>210</v>
+        <v>121</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -8466,7 +8493,7 @@
         <v>16</v>
       </c>
       <c r="B240" t="s">
-        <v>241</v>
+        <v>126</v>
       </c>
       <c r="C240">
         <v>1</v>
@@ -8488,7 +8515,7 @@
         <v>16</v>
       </c>
       <c r="B242" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -8499,7 +8526,7 @@
         <v>16</v>
       </c>
       <c r="B243" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -8510,7 +8537,7 @@
         <v>16</v>
       </c>
       <c r="B244" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -8521,7 +8548,7 @@
         <v>16</v>
       </c>
       <c r="B245" t="s">
-        <v>69</v>
+        <v>216</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -8532,7 +8559,7 @@
         <v>16</v>
       </c>
       <c r="B246" t="s">
-        <v>115</v>
+        <v>211</v>
       </c>
       <c r="C246">
         <v>1</v>
@@ -8543,7 +8570,7 @@
         <v>16</v>
       </c>
       <c r="B247" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C247">
         <v>1</v>
@@ -8554,7 +8581,7 @@
         <v>16</v>
       </c>
       <c r="B248" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C248">
         <v>1</v>
@@ -8565,7 +8592,7 @@
         <v>16</v>
       </c>
       <c r="B249" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="C249">
         <v>1</v>
@@ -8576,7 +8603,7 @@
         <v>16</v>
       </c>
       <c r="B250" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -8587,7 +8614,7 @@
         <v>16</v>
       </c>
       <c r="B251" t="s">
-        <v>126</v>
+        <v>209</v>
       </c>
       <c r="C251">
         <v>1</v>
@@ -8598,7 +8625,7 @@
         <v>16</v>
       </c>
       <c r="B252" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -8609,7 +8636,7 @@
         <v>16</v>
       </c>
       <c r="B253" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -8620,7 +8647,7 @@
         <v>16</v>
       </c>
       <c r="B254" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -8631,7 +8658,7 @@
         <v>16</v>
       </c>
       <c r="B255" t="s">
-        <v>218</v>
+        <v>69</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -8642,7 +8669,7 @@
         <v>16</v>
       </c>
       <c r="B256" t="s">
-        <v>217</v>
+        <v>115</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -8653,7 +8680,7 @@
         <v>16</v>
       </c>
       <c r="B257" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -8664,7 +8691,7 @@
         <v>16</v>
       </c>
       <c r="B258" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C258">
         <v>1</v>
@@ -8675,7 +8702,7 @@
         <v>16</v>
       </c>
       <c r="B259" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="C259">
         <v>1</v>
@@ -8686,7 +8713,7 @@
         <v>16</v>
       </c>
       <c r="B260" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C260">
         <v>1</v>
@@ -8697,7 +8724,7 @@
         <v>16</v>
       </c>
       <c r="B261" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="C261">
         <v>1</v>
@@ -8708,7 +8735,7 @@
         <v>16</v>
       </c>
       <c r="B262" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C262">
         <v>1</v>
@@ -8719,7 +8746,7 @@
         <v>16</v>
       </c>
       <c r="B263" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="C263">
         <v>1</v>
@@ -8730,7 +8757,7 @@
         <v>16</v>
       </c>
       <c r="B264" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -8741,7 +8768,7 @@
         <v>16</v>
       </c>
       <c r="B265" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C265">
         <v>1</v>
@@ -8752,7 +8779,7 @@
         <v>16</v>
       </c>
       <c r="B266" t="s">
-        <v>208</v>
+        <v>239</v>
       </c>
       <c r="C266">
         <v>1</v>
@@ -8763,7 +8790,7 @@
         <v>16</v>
       </c>
       <c r="B267" t="s">
-        <v>230</v>
+        <v>119</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -8774,7 +8801,7 @@
         <v>16</v>
       </c>
       <c r="B268" t="s">
-        <v>239</v>
+        <v>214</v>
       </c>
       <c r="C268">
         <v>1</v>
@@ -8785,7 +8812,7 @@
         <v>16</v>
       </c>
       <c r="B269" t="s">
-        <v>243</v>
+        <v>208</v>
       </c>
       <c r="C269">
         <v>1</v>
@@ -8796,7 +8823,7 @@
         <v>16</v>
       </c>
       <c r="B270" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="C270">
         <v>1</v>
@@ -8804,24 +8831,24 @@
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B271" t="s">
-        <v>70</v>
+        <v>121</v>
       </c>
       <c r="C271">
-        <v>1</v>
+        <v>39</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B272" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="C272">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
@@ -8829,10 +8856,10 @@
         <v>21</v>
       </c>
       <c r="B273" t="s">
-        <v>121</v>
+        <v>189</v>
       </c>
       <c r="C273">
-        <v>39</v>
+        <v>10</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
@@ -8840,10 +8867,10 @@
         <v>21</v>
       </c>
       <c r="B274" t="s">
-        <v>189</v>
+        <v>103</v>
       </c>
       <c r="C274">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
@@ -8851,10 +8878,10 @@
         <v>21</v>
       </c>
       <c r="B275" t="s">
-        <v>132</v>
+        <v>202</v>
       </c>
       <c r="C275">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -8862,10 +8889,10 @@
         <v>21</v>
       </c>
       <c r="B276" t="s">
-        <v>103</v>
+        <v>240</v>
       </c>
       <c r="C276">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
@@ -8873,10 +8900,10 @@
         <v>21</v>
       </c>
       <c r="B277" t="s">
-        <v>202</v>
+        <v>120</v>
       </c>
       <c r="C277">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -8887,7 +8914,7 @@
         <v>242</v>
       </c>
       <c r="C278">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
@@ -8895,10 +8922,10 @@
         <v>21</v>
       </c>
       <c r="B279" t="s">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="C279">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -8906,7 +8933,7 @@
         <v>21</v>
       </c>
       <c r="B280" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C280">
         <v>5</v>
@@ -8917,7 +8944,7 @@
         <v>21</v>
       </c>
       <c r="B281" t="s">
-        <v>142</v>
+        <v>241</v>
       </c>
       <c r="C281">
         <v>5</v>
@@ -8928,10 +8955,10 @@
         <v>21</v>
       </c>
       <c r="B282" t="s">
-        <v>245</v>
+        <v>101</v>
       </c>
       <c r="C282">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -8939,10 +8966,10 @@
         <v>21</v>
       </c>
       <c r="B283" t="s">
-        <v>243</v>
+        <v>128</v>
       </c>
       <c r="C283">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
@@ -8950,7 +8977,7 @@
         <v>21</v>
       </c>
       <c r="B284" t="s">
-        <v>101</v>
+        <v>244</v>
       </c>
       <c r="C284">
         <v>4</v>
@@ -8961,10 +8988,10 @@
         <v>21</v>
       </c>
       <c r="B285" t="s">
-        <v>128</v>
+        <v>81</v>
       </c>
       <c r="C285">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
@@ -8972,10 +8999,10 @@
         <v>21</v>
       </c>
       <c r="B286" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C286">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -8983,7 +9010,7 @@
         <v>21</v>
       </c>
       <c r="B287" t="s">
-        <v>81</v>
+        <v>126</v>
       </c>
       <c r="C287">
         <v>3</v>
@@ -8994,7 +9021,7 @@
         <v>21</v>
       </c>
       <c r="B288" t="s">
-        <v>247</v>
+        <v>196</v>
       </c>
       <c r="C288">
         <v>3</v>
@@ -9005,7 +9032,7 @@
         <v>21</v>
       </c>
       <c r="B289" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C289">
         <v>3</v>
@@ -9016,7 +9043,7 @@
         <v>21</v>
       </c>
       <c r="B290" t="s">
-        <v>196</v>
+        <v>249</v>
       </c>
       <c r="C290">
         <v>3</v>
@@ -9027,7 +9054,7 @@
         <v>21</v>
       </c>
       <c r="B291" t="s">
-        <v>127</v>
+        <v>248</v>
       </c>
       <c r="C291">
         <v>3</v>
@@ -9038,7 +9065,7 @@
         <v>21</v>
       </c>
       <c r="B292" t="s">
-        <v>251</v>
+        <v>163</v>
       </c>
       <c r="C292">
         <v>3</v>
@@ -9049,7 +9076,7 @@
         <v>21</v>
       </c>
       <c r="B293" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C293">
         <v>3</v>
@@ -9060,7 +9087,7 @@
         <v>21</v>
       </c>
       <c r="B294" t="s">
-        <v>163</v>
+        <v>44</v>
       </c>
       <c r="C294">
         <v>3</v>
@@ -9071,7 +9098,7 @@
         <v>21</v>
       </c>
       <c r="B295" t="s">
-        <v>249</v>
+        <v>133</v>
       </c>
       <c r="C295">
         <v>3</v>
@@ -9082,10 +9109,10 @@
         <v>21</v>
       </c>
       <c r="B296" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="C296">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -9093,10 +9120,10 @@
         <v>21</v>
       </c>
       <c r="B297" t="s">
-        <v>133</v>
+        <v>171</v>
       </c>
       <c r="C297">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
@@ -9104,7 +9131,7 @@
         <v>21</v>
       </c>
       <c r="B298" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="C298">
         <v>2</v>
@@ -9115,7 +9142,7 @@
         <v>21</v>
       </c>
       <c r="B299" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C299">
         <v>2</v>
@@ -9126,7 +9153,7 @@
         <v>21</v>
       </c>
       <c r="B300" t="s">
-        <v>136</v>
+        <v>251</v>
       </c>
       <c r="C300">
         <v>2</v>
@@ -9137,7 +9164,7 @@
         <v>21</v>
       </c>
       <c r="B301" t="s">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="C301">
         <v>2</v>
@@ -9148,7 +9175,7 @@
         <v>21</v>
       </c>
       <c r="B302" t="s">
-        <v>253</v>
+        <v>70</v>
       </c>
       <c r="C302">
         <v>2</v>
@@ -9159,7 +9186,7 @@
         <v>21</v>
       </c>
       <c r="B303" t="s">
-        <v>77</v>
+        <v>252</v>
       </c>
       <c r="C303">
         <v>2</v>
@@ -9170,7 +9197,7 @@
         <v>21</v>
       </c>
       <c r="B304" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="C304">
         <v>2</v>
@@ -9181,7 +9208,7 @@
         <v>21</v>
       </c>
       <c r="B305" t="s">
-        <v>254</v>
+        <v>85</v>
       </c>
       <c r="C305">
         <v>2</v>
@@ -9192,7 +9219,7 @@
         <v>21</v>
       </c>
       <c r="B306" t="s">
-        <v>54</v>
+        <v>267</v>
       </c>
       <c r="C306">
         <v>2</v>
@@ -9203,7 +9230,7 @@
         <v>21</v>
       </c>
       <c r="B307" t="s">
-        <v>85</v>
+        <v>253</v>
       </c>
       <c r="C307">
         <v>2</v>
@@ -9214,7 +9241,7 @@
         <v>21</v>
       </c>
       <c r="B308" t="s">
-        <v>269</v>
+        <v>198</v>
       </c>
       <c r="C308">
         <v>2</v>
@@ -9225,7 +9252,7 @@
         <v>21</v>
       </c>
       <c r="B309" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C309">
         <v>2</v>
@@ -9236,7 +9263,7 @@
         <v>21</v>
       </c>
       <c r="B310" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C310">
         <v>2</v>
@@ -9247,7 +9274,7 @@
         <v>21</v>
       </c>
       <c r="B311" t="s">
-        <v>252</v>
+        <v>62</v>
       </c>
       <c r="C311">
         <v>2</v>
@@ -9258,7 +9285,7 @@
         <v>21</v>
       </c>
       <c r="B312" t="s">
-        <v>199</v>
+        <v>246</v>
       </c>
       <c r="C312">
         <v>2</v>
@@ -9269,10 +9296,10 @@
         <v>21</v>
       </c>
       <c r="B313" t="s">
-        <v>62</v>
+        <v>277</v>
       </c>
       <c r="C313">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
@@ -9280,10 +9307,10 @@
         <v>21</v>
       </c>
       <c r="B314" t="s">
-        <v>248</v>
+        <v>138</v>
       </c>
       <c r="C314">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
@@ -9291,7 +9318,7 @@
         <v>21</v>
       </c>
       <c r="B315" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
       <c r="C315">
         <v>1</v>
@@ -9302,7 +9329,7 @@
         <v>21</v>
       </c>
       <c r="B316" t="s">
-        <v>138</v>
+        <v>268</v>
       </c>
       <c r="C316">
         <v>1</v>
@@ -9313,7 +9340,7 @@
         <v>21</v>
       </c>
       <c r="B317" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C317">
         <v>1</v>
@@ -9324,7 +9351,7 @@
         <v>21</v>
       </c>
       <c r="B318" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -9335,7 +9362,7 @@
         <v>21</v>
       </c>
       <c r="B319" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C319">
         <v>1</v>
@@ -9346,7 +9373,7 @@
         <v>21</v>
       </c>
       <c r="B320" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="C320">
         <v>1</v>
@@ -9357,7 +9384,7 @@
         <v>21</v>
       </c>
       <c r="B321" t="s">
-        <v>277</v>
+        <v>172</v>
       </c>
       <c r="C321">
         <v>1</v>
@@ -9368,7 +9395,7 @@
         <v>21</v>
       </c>
       <c r="B322" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="C322">
         <v>1</v>
@@ -9379,7 +9406,7 @@
         <v>21</v>
       </c>
       <c r="B323" t="s">
-        <v>172</v>
+        <v>63</v>
       </c>
       <c r="C323">
         <v>1</v>
@@ -9390,7 +9417,7 @@
         <v>21</v>
       </c>
       <c r="B324" t="s">
-        <v>280</v>
+        <v>137</v>
       </c>
       <c r="C324">
         <v>1</v>
@@ -9401,7 +9428,7 @@
         <v>21</v>
       </c>
       <c r="B325" t="s">
-        <v>63</v>
+        <v>276</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -9412,7 +9439,7 @@
         <v>21</v>
       </c>
       <c r="B326" t="s">
-        <v>137</v>
+        <v>262</v>
       </c>
       <c r="C326">
         <v>1</v>
@@ -9423,7 +9450,7 @@
         <v>21</v>
       </c>
       <c r="B327" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C327">
         <v>1</v>
@@ -9434,7 +9461,7 @@
         <v>21</v>
       </c>
       <c r="B328" t="s">
-        <v>264</v>
+        <v>185</v>
       </c>
       <c r="C328">
         <v>1</v>
@@ -9445,7 +9472,7 @@
         <v>21</v>
       </c>
       <c r="B329" t="s">
-        <v>276</v>
+        <v>260</v>
       </c>
       <c r="C329">
         <v>1</v>
@@ -9456,7 +9483,7 @@
         <v>21</v>
       </c>
       <c r="B330" t="s">
-        <v>185</v>
+        <v>148</v>
       </c>
       <c r="C330">
         <v>1</v>
@@ -9467,7 +9494,7 @@
         <v>21</v>
       </c>
       <c r="B331" t="s">
-        <v>262</v>
+        <v>49</v>
       </c>
       <c r="C331">
         <v>1</v>
@@ -9478,7 +9505,7 @@
         <v>21</v>
       </c>
       <c r="B332" t="s">
-        <v>148</v>
+        <v>258</v>
       </c>
       <c r="C332">
         <v>1</v>
@@ -9489,7 +9516,7 @@
         <v>21</v>
       </c>
       <c r="B333" t="s">
-        <v>49</v>
+        <v>115</v>
       </c>
       <c r="C333">
         <v>1</v>
@@ -9500,7 +9527,7 @@
         <v>21</v>
       </c>
       <c r="B334" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="C334">
         <v>1</v>
@@ -9511,7 +9538,7 @@
         <v>21</v>
       </c>
       <c r="B335" t="s">
-        <v>115</v>
+        <v>261</v>
       </c>
       <c r="C335">
         <v>1</v>
@@ -9522,7 +9549,7 @@
         <v>21</v>
       </c>
       <c r="B336" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C336">
         <v>1</v>
@@ -9533,7 +9560,7 @@
         <v>21</v>
       </c>
       <c r="B337" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="C337">
         <v>1</v>
@@ -9544,7 +9571,7 @@
         <v>21</v>
       </c>
       <c r="B338" t="s">
-        <v>272</v>
+        <v>212</v>
       </c>
       <c r="C338">
         <v>1</v>
@@ -9555,7 +9582,7 @@
         <v>21</v>
       </c>
       <c r="B339" t="s">
-        <v>259</v>
+        <v>125</v>
       </c>
       <c r="C339">
         <v>1</v>
@@ -9566,7 +9593,7 @@
         <v>21</v>
       </c>
       <c r="B340" t="s">
-        <v>213</v>
+        <v>273</v>
       </c>
       <c r="C340">
         <v>1</v>
@@ -9577,7 +9604,7 @@
         <v>21</v>
       </c>
       <c r="B341" t="s">
-        <v>125</v>
+        <v>254</v>
       </c>
       <c r="C341">
         <v>1</v>
@@ -9588,7 +9615,7 @@
         <v>21</v>
       </c>
       <c r="B342" t="s">
-        <v>275</v>
+        <v>92</v>
       </c>
       <c r="C342">
         <v>1</v>
@@ -9599,7 +9626,7 @@
         <v>21</v>
       </c>
       <c r="B343" t="s">
-        <v>256</v>
+        <v>165</v>
       </c>
       <c r="C343">
         <v>1</v>
@@ -9610,7 +9637,7 @@
         <v>21</v>
       </c>
       <c r="B344" t="s">
-        <v>92</v>
+        <v>174</v>
       </c>
       <c r="C344">
         <v>1</v>
@@ -9621,7 +9648,7 @@
         <v>21</v>
       </c>
       <c r="B345" t="s">
-        <v>165</v>
+        <v>266</v>
       </c>
       <c r="C345">
         <v>1</v>
@@ -9632,7 +9659,7 @@
         <v>21</v>
       </c>
       <c r="B346" t="s">
-        <v>174</v>
+        <v>256</v>
       </c>
       <c r="C346">
         <v>1</v>
@@ -9643,7 +9670,7 @@
         <v>21</v>
       </c>
       <c r="B347" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="C347">
         <v>1</v>
@@ -9654,7 +9681,7 @@
         <v>21</v>
       </c>
       <c r="B348" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C348">
         <v>1</v>
@@ -9665,31 +9692,9 @@
         <v>21</v>
       </c>
       <c r="B349" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="C349">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A350" t="s">
-        <v>21</v>
-      </c>
-      <c r="B350" t="s">
-        <v>261</v>
-      </c>
-      <c r="C350">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A351" t="s">
-        <v>21</v>
-      </c>
-      <c r="B351" t="s">
-        <v>266</v>
-      </c>
-      <c r="C351">
         <v>1</v>
       </c>
     </row>
@@ -9711,10 +9716,10 @@
         <v>37</v>
       </c>
       <c r="B1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -9722,7 +9727,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C2">
         <v>63</v>
@@ -9733,7 +9738,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C3">
         <v>512</v>
@@ -9744,7 +9749,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C4">
         <v>37</v>
@@ -9755,7 +9760,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C5">
         <v>11</v>
@@ -9766,7 +9771,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C6">
         <v>7</v>
@@ -9777,7 +9782,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -9788,10 +9793,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C8">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -9799,7 +9804,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C9">
         <v>559</v>
@@ -9810,7 +9815,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C10">
         <v>23</v>
@@ -9821,7 +9826,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C11">
         <v>30</v>
@@ -9832,10 +9837,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C12">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -9843,7 +9848,7 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C13">
         <v>882</v>
@@ -9854,7 +9859,7 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C14">
         <v>4</v>
@@ -9865,7 +9870,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C15">
         <v>13</v>
@@ -9876,7 +9881,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C16">
         <v>22</v>
@@ -9887,7 +9892,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C17">
         <v>33</v>
@@ -9898,7 +9903,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C18">
         <v>11</v>
@@ -9909,7 +9914,7 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C19">
         <v>2</v>
@@ -9920,7 +9925,7 @@
         <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C20">
         <v>4</v>
@@ -9931,7 +9936,7 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C21">
         <v>2</v>
@@ -9942,7 +9947,7 @@
         <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C22">
         <v>2</v>
@@ -9953,7 +9958,7 @@
         <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C23">
         <v>41</v>
@@ -9964,10 +9969,10 @@
         <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C24">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -9975,7 +9980,7 @@
         <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C25">
         <v>25</v>
@@ -9986,10 +9991,10 @@
         <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C26">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -9997,7 +10002,7 @@
         <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C27">
         <v>140</v>
@@ -10008,7 +10013,7 @@
         <v>16</v>
       </c>
       <c r="B28" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C28">
         <v>77</v>
@@ -10019,7 +10024,7 @@
         <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C29">
         <v>10</v>
@@ -10030,7 +10035,7 @@
         <v>16</v>
       </c>
       <c r="B30" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -10041,7 +10046,7 @@
         <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C31">
         <v>7</v>
@@ -10052,7 +10057,7 @@
         <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -10063,10 +10068,10 @@
         <v>21</v>
       </c>
       <c r="B33" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C33">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -10074,7 +10079,7 @@
         <v>21</v>
       </c>
       <c r="B34" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C34">
         <v>9</v>
@@ -10085,7 +10090,7 @@
         <v>21</v>
       </c>
       <c r="B35" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C35">
         <v>22</v>
@@ -10096,7 +10101,7 @@
         <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C36">
         <v>61</v>
@@ -10107,7 +10112,7 @@
         <v>21</v>
       </c>
       <c r="B37" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C37">
         <v>24</v>
@@ -10118,7 +10123,7 @@
         <v>21</v>
       </c>
       <c r="B38" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C38">
         <v>56</v>
@@ -10129,7 +10134,7 @@
         <v>21</v>
       </c>
       <c r="B39" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C39">
         <v>3</v>
@@ -10140,7 +10145,7 @@
         <v>21</v>
       </c>
       <c r="B40" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C40">
         <v>14</v>
@@ -10151,7 +10156,7 @@
         <v>21</v>
       </c>
       <c r="B41" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C41">
         <v>14</v>
@@ -10162,7 +10167,7 @@
         <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C42">
         <v>6</v>
@@ -10191,7 +10196,7 @@
         <v>22</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -10298,7 +10303,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C11" s="9">
         <v>1</v>
@@ -10408,7 +10413,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C21" s="9">
         <v>2</v>
@@ -10518,7 +10523,7 @@
         <v>15</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C31" s="9">
         <v>2</v>

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="205" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6690877-4635-491B-9952-57FFBED5698B}"/>
+  <xr:revisionPtr revIDLastSave="209" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36132FEB-14DF-4989-9BEE-28D9B6C90BD8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="731" firstSheet="1" activeTab="7" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="731" firstSheet="1" activeTab="2" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="proyeccion_2026" sheetId="2" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1317" uniqueCount="296">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -1809,10 +1809,10 @@
         <v>40</v>
       </c>
       <c r="D15">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E15">
-        <v>1.05</v>
+        <v>1.075</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -1911,10 +1911,10 @@
         <v>88</v>
       </c>
       <c r="D21">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E21">
-        <v>1.0109999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -2277,7 +2277,7 @@
         <v>34</v>
       </c>
       <c r="C4">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2288,7 +2288,7 @@
         <v>35</v>
       </c>
       <c r="C5">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2364,7 +2364,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD19485A-0629-47F9-A5AD-80ABA7A6E076}">
-  <dimension ref="A1:C254"/>
+  <dimension ref="A1:C255"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -3029,7 +3029,7 @@
         <v>46000</v>
       </c>
       <c r="C60" s="6">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -3455,10 +3455,10 @@
         <v>14</v>
       </c>
       <c r="B99" s="8">
-        <v>46086</v>
+        <v>46177</v>
       </c>
       <c r="C99" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -3466,10 +3466,10 @@
         <v>14</v>
       </c>
       <c r="B100" s="5">
-        <v>46147</v>
+        <v>46086</v>
       </c>
       <c r="C100" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -3477,7 +3477,7 @@
         <v>14</v>
       </c>
       <c r="B101" s="8">
-        <v>46134</v>
+        <v>46147</v>
       </c>
       <c r="C101" s="9">
         <v>1</v>
@@ -3488,7 +3488,7 @@
         <v>14</v>
       </c>
       <c r="B102" s="5">
-        <v>46182</v>
+        <v>46134</v>
       </c>
       <c r="C102" s="6">
         <v>1</v>
@@ -3496,13 +3496,13 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B103" s="8">
-        <v>46003</v>
+        <v>46182</v>
       </c>
       <c r="C103" s="9">
-        <v>95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -3510,10 +3510,10 @@
         <v>3</v>
       </c>
       <c r="B104" s="5">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="C104" s="6">
-        <v>115</v>
+        <v>95</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -3521,10 +3521,10 @@
         <v>3</v>
       </c>
       <c r="B105" s="8">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C105" s="9">
-        <v>14</v>
+        <v>115</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -3532,10 +3532,10 @@
         <v>3</v>
       </c>
       <c r="B106" s="5">
-        <v>46000</v>
+        <v>46008</v>
       </c>
       <c r="C106" s="6">
-        <v>98</v>
+        <v>14</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -3543,10 +3543,10 @@
         <v>3</v>
       </c>
       <c r="B107" s="8">
-        <v>46007</v>
+        <v>46000</v>
       </c>
       <c r="C107" s="9">
-        <v>40</v>
+        <v>98</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -3554,10 +3554,10 @@
         <v>3</v>
       </c>
       <c r="B108" s="5">
-        <v>46001</v>
+        <v>46007</v>
       </c>
       <c r="C108" s="6">
-        <v>91</v>
+        <v>40</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -3565,10 +3565,10 @@
         <v>3</v>
       </c>
       <c r="B109" s="8">
-        <v>46010</v>
+        <v>46001</v>
       </c>
       <c r="C109" s="9">
-        <v>9</v>
+        <v>91</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -3576,10 +3576,10 @@
         <v>3</v>
       </c>
       <c r="B110" s="5">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="C110" s="6">
-        <v>84</v>
+        <v>9</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -3587,10 +3587,10 @@
         <v>3</v>
       </c>
       <c r="B111" s="8">
-        <v>46009</v>
+        <v>46006</v>
       </c>
       <c r="C111" s="9">
-        <v>2</v>
+        <v>84</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -3598,10 +3598,10 @@
         <v>3</v>
       </c>
       <c r="B112" s="5">
-        <v>46015</v>
+        <v>46009</v>
       </c>
       <c r="C112" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -3609,10 +3609,10 @@
         <v>3</v>
       </c>
       <c r="B113" s="8">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="C113" s="9">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -3620,10 +3620,10 @@
         <v>3</v>
       </c>
       <c r="B114" s="5">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="C114" s="6">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -3631,10 +3631,10 @@
         <v>3</v>
       </c>
       <c r="B115" s="8">
-        <v>46021</v>
+        <v>46013</v>
       </c>
       <c r="C115" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -3642,10 +3642,10 @@
         <v>3</v>
       </c>
       <c r="B116" s="5">
-        <v>46077</v>
+        <v>46021</v>
       </c>
       <c r="C116" s="6">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -3653,10 +3653,10 @@
         <v>3</v>
       </c>
       <c r="B117" s="8">
-        <v>46167</v>
+        <v>46077</v>
       </c>
       <c r="C117" s="9">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -3664,10 +3664,10 @@
         <v>3</v>
       </c>
       <c r="B118" s="5">
-        <v>46090</v>
+        <v>46167</v>
       </c>
       <c r="C118" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -3675,10 +3675,10 @@
         <v>3</v>
       </c>
       <c r="B119" s="8">
-        <v>46170</v>
+        <v>46090</v>
       </c>
       <c r="C119" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -3686,7 +3686,7 @@
         <v>3</v>
       </c>
       <c r="B120" s="5">
-        <v>46093</v>
+        <v>46170</v>
       </c>
       <c r="C120" s="6">
         <v>1</v>
@@ -3697,10 +3697,10 @@
         <v>3</v>
       </c>
       <c r="B121" s="8">
-        <v>46078</v>
+        <v>46093</v>
       </c>
       <c r="C121" s="9">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -3708,7 +3708,7 @@
         <v>3</v>
       </c>
       <c r="B122" s="5">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="C122" s="6">
         <v>7</v>
@@ -3719,10 +3719,10 @@
         <v>3</v>
       </c>
       <c r="B123" s="8">
-        <v>46134</v>
+        <v>46084</v>
       </c>
       <c r="C123" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -3730,10 +3730,10 @@
         <v>3</v>
       </c>
       <c r="B124" s="5">
-        <v>46083</v>
+        <v>46134</v>
       </c>
       <c r="C124" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -3741,10 +3741,10 @@
         <v>3</v>
       </c>
       <c r="B125" s="8">
-        <v>46022</v>
+        <v>46083</v>
       </c>
       <c r="C125" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
@@ -3752,10 +3752,10 @@
         <v>3</v>
       </c>
       <c r="B126" s="5">
-        <v>46114</v>
+        <v>46022</v>
       </c>
       <c r="C126" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -3763,10 +3763,10 @@
         <v>3</v>
       </c>
       <c r="B127" s="8">
-        <v>46135</v>
+        <v>46114</v>
       </c>
       <c r="C127" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -3774,10 +3774,10 @@
         <v>3</v>
       </c>
       <c r="B128" s="5">
-        <v>46168</v>
+        <v>46135</v>
       </c>
       <c r="C128" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -3785,7 +3785,7 @@
         <v>3</v>
       </c>
       <c r="B129" s="8">
-        <v>46126</v>
+        <v>46168</v>
       </c>
       <c r="C129" s="9">
         <v>3</v>
@@ -3796,7 +3796,7 @@
         <v>3</v>
       </c>
       <c r="B130" s="5">
-        <v>46120</v>
+        <v>46126</v>
       </c>
       <c r="C130" s="6">
         <v>3</v>
@@ -3807,10 +3807,10 @@
         <v>3</v>
       </c>
       <c r="B131" s="8">
-        <v>46127</v>
+        <v>46120</v>
       </c>
       <c r="C131" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -3818,7 +3818,7 @@
         <v>3</v>
       </c>
       <c r="B132" s="5">
-        <v>46087</v>
+        <v>46127</v>
       </c>
       <c r="C132" s="6">
         <v>1</v>
@@ -3829,7 +3829,7 @@
         <v>3</v>
       </c>
       <c r="B133" s="8">
-        <v>46108</v>
+        <v>46087</v>
       </c>
       <c r="C133" s="9">
         <v>1</v>
@@ -3840,7 +3840,7 @@
         <v>3</v>
       </c>
       <c r="B134" s="5">
-        <v>46020</v>
+        <v>46108</v>
       </c>
       <c r="C134" s="6">
         <v>1</v>
@@ -3851,7 +3851,7 @@
         <v>3</v>
       </c>
       <c r="B135" s="8">
-        <v>46097</v>
+        <v>46020</v>
       </c>
       <c r="C135" s="9">
         <v>1</v>
@@ -3862,7 +3862,7 @@
         <v>3</v>
       </c>
       <c r="B136" s="5">
-        <v>46177</v>
+        <v>46097</v>
       </c>
       <c r="C136" s="6">
         <v>1</v>
@@ -3873,10 +3873,10 @@
         <v>3</v>
       </c>
       <c r="B137" s="8">
-        <v>46161</v>
+        <v>46177</v>
       </c>
       <c r="C137" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -3884,10 +3884,10 @@
         <v>3</v>
       </c>
       <c r="B138" s="5">
-        <v>46129</v>
+        <v>46161</v>
       </c>
       <c r="C138" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -3895,7 +3895,7 @@
         <v>3</v>
       </c>
       <c r="B139" s="8">
-        <v>46080</v>
+        <v>46129</v>
       </c>
       <c r="C139" s="9">
         <v>1</v>
@@ -3906,7 +3906,7 @@
         <v>3</v>
       </c>
       <c r="B140" s="5">
-        <v>46101</v>
+        <v>46080</v>
       </c>
       <c r="C140" s="6">
         <v>1</v>
@@ -3917,7 +3917,7 @@
         <v>3</v>
       </c>
       <c r="B141" s="8">
-        <v>46155</v>
+        <v>46101</v>
       </c>
       <c r="C141" s="9">
         <v>1</v>
@@ -3928,7 +3928,7 @@
         <v>3</v>
       </c>
       <c r="B142" s="5">
-        <v>46150</v>
+        <v>46155</v>
       </c>
       <c r="C142" s="6">
         <v>1</v>
@@ -3939,7 +3939,7 @@
         <v>3</v>
       </c>
       <c r="B143" s="8">
-        <v>46141</v>
+        <v>46150</v>
       </c>
       <c r="C143" s="9">
         <v>1</v>
@@ -3950,7 +3950,7 @@
         <v>3</v>
       </c>
       <c r="B144" s="5">
-        <v>46085</v>
+        <v>46141</v>
       </c>
       <c r="C144" s="6">
         <v>1</v>
@@ -3961,7 +3961,7 @@
         <v>3</v>
       </c>
       <c r="B145" s="8">
-        <v>46148</v>
+        <v>46085</v>
       </c>
       <c r="C145" s="9">
         <v>1</v>
@@ -3972,10 +3972,10 @@
         <v>3</v>
       </c>
       <c r="B146" s="5">
-        <v>46118</v>
+        <v>46148</v>
       </c>
       <c r="C146" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -3983,21 +3983,21 @@
         <v>3</v>
       </c>
       <c r="B147" s="8">
-        <v>46079</v>
+        <v>46118</v>
       </c>
       <c r="C147" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B148" s="5">
-        <v>46003</v>
+        <v>46079</v>
       </c>
       <c r="C148" s="6">
-        <v>92</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -4005,10 +4005,10 @@
         <v>15</v>
       </c>
       <c r="B149" s="8">
-        <v>46000</v>
+        <v>46003</v>
       </c>
       <c r="C149" s="9">
-        <v>132</v>
+        <v>92</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -4016,10 +4016,10 @@
         <v>15</v>
       </c>
       <c r="B150" s="5">
-        <v>46006</v>
+        <v>46000</v>
       </c>
       <c r="C150" s="6">
-        <v>173</v>
+        <v>132</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -4027,10 +4027,10 @@
         <v>15</v>
       </c>
       <c r="B151" s="8">
-        <v>46001</v>
+        <v>46006</v>
       </c>
       <c r="C151" s="9">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -4038,10 +4038,10 @@
         <v>15</v>
       </c>
       <c r="B152" s="5">
-        <v>46014</v>
+        <v>46001</v>
       </c>
       <c r="C152" s="6">
-        <v>16</v>
+        <v>174</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -4049,10 +4049,10 @@
         <v>15</v>
       </c>
       <c r="B153" s="8">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="C153" s="9">
-        <v>171</v>
+        <v>16</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -4060,10 +4060,10 @@
         <v>15</v>
       </c>
       <c r="B154" s="5">
-        <v>46009</v>
+        <v>46002</v>
       </c>
       <c r="C154" s="6">
-        <v>19</v>
+        <v>171</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -4071,7 +4071,7 @@
         <v>15</v>
       </c>
       <c r="B155" s="8">
-        <v>46010</v>
+        <v>46009</v>
       </c>
       <c r="C155" s="9">
         <v>19</v>
@@ -4082,10 +4082,10 @@
         <v>15</v>
       </c>
       <c r="B156" s="5">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="C156" s="6">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -4093,10 +4093,10 @@
         <v>15</v>
       </c>
       <c r="B157" s="8">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="C157" s="9">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -4104,10 +4104,10 @@
         <v>15</v>
       </c>
       <c r="B158" s="5">
-        <v>46013</v>
+        <v>46007</v>
       </c>
       <c r="C158" s="6">
-        <v>12</v>
+        <v>43</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -4115,10 +4115,10 @@
         <v>15</v>
       </c>
       <c r="B159" s="8">
-        <v>46080</v>
+        <v>46013</v>
       </c>
       <c r="C159" s="9">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -4126,10 +4126,10 @@
         <v>15</v>
       </c>
       <c r="B160" s="5">
-        <v>46090</v>
+        <v>46080</v>
       </c>
       <c r="C160" s="6">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -4137,10 +4137,10 @@
         <v>15</v>
       </c>
       <c r="B161" s="8">
-        <v>46079</v>
+        <v>46090</v>
       </c>
       <c r="C161" s="9">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -4148,10 +4148,10 @@
         <v>15</v>
       </c>
       <c r="B162" s="5">
-        <v>46015</v>
+        <v>46079</v>
       </c>
       <c r="C162" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -4159,10 +4159,10 @@
         <v>15</v>
       </c>
       <c r="B163" s="8">
-        <v>46085</v>
+        <v>46015</v>
       </c>
       <c r="C163" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -4170,10 +4170,10 @@
         <v>15</v>
       </c>
       <c r="B164" s="5">
-        <v>46098</v>
+        <v>46085</v>
       </c>
       <c r="C164" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -4181,10 +4181,10 @@
         <v>15</v>
       </c>
       <c r="B165" s="8">
-        <v>46021</v>
+        <v>46098</v>
       </c>
       <c r="C165" s="9">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -4192,10 +4192,10 @@
         <v>15</v>
       </c>
       <c r="B166" s="5">
-        <v>46078</v>
+        <v>46021</v>
       </c>
       <c r="C166" s="6">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -4203,10 +4203,10 @@
         <v>15</v>
       </c>
       <c r="B167" s="8">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="C167" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -4214,10 +4214,10 @@
         <v>15</v>
       </c>
       <c r="B168" s="5">
-        <v>46128</v>
+        <v>46084</v>
       </c>
       <c r="C168" s="6">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -4225,10 +4225,10 @@
         <v>15</v>
       </c>
       <c r="B169" s="8">
-        <v>46083</v>
+        <v>46128</v>
       </c>
       <c r="C169" s="9">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -4236,10 +4236,10 @@
         <v>15</v>
       </c>
       <c r="B170" s="5">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="C170" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -4247,10 +4247,10 @@
         <v>15</v>
       </c>
       <c r="B171" s="8">
-        <v>46099</v>
+        <v>46076</v>
       </c>
       <c r="C171" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -4258,10 +4258,10 @@
         <v>15</v>
       </c>
       <c r="B172" s="5">
-        <v>46154</v>
+        <v>46099</v>
       </c>
       <c r="C172" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -4269,7 +4269,7 @@
         <v>15</v>
       </c>
       <c r="B173" s="8">
-        <v>46092</v>
+        <v>46154</v>
       </c>
       <c r="C173" s="9">
         <v>1</v>
@@ -4280,10 +4280,10 @@
         <v>15</v>
       </c>
       <c r="B174" s="5">
-        <v>46031</v>
+        <v>46092</v>
       </c>
       <c r="C174" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -4291,7 +4291,7 @@
         <v>15</v>
       </c>
       <c r="B175" s="8">
-        <v>46120</v>
+        <v>46031</v>
       </c>
       <c r="C175" s="9">
         <v>2</v>
@@ -4302,10 +4302,10 @@
         <v>15</v>
       </c>
       <c r="B176" s="5">
-        <v>46077</v>
+        <v>46120</v>
       </c>
       <c r="C176" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -4313,10 +4313,10 @@
         <v>15</v>
       </c>
       <c r="B177" s="8">
-        <v>46114</v>
+        <v>46077</v>
       </c>
       <c r="C177" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -4324,7 +4324,7 @@
         <v>15</v>
       </c>
       <c r="B178" s="5">
-        <v>46037</v>
+        <v>46114</v>
       </c>
       <c r="C178" s="6">
         <v>1</v>
@@ -4335,10 +4335,10 @@
         <v>15</v>
       </c>
       <c r="B179" s="8">
-        <v>46020</v>
+        <v>46037</v>
       </c>
       <c r="C179" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -4346,10 +4346,10 @@
         <v>15</v>
       </c>
       <c r="B180" s="5">
-        <v>46106</v>
+        <v>46020</v>
       </c>
       <c r="C180" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -4357,7 +4357,7 @@
         <v>15</v>
       </c>
       <c r="B181" s="8">
-        <v>46155</v>
+        <v>46106</v>
       </c>
       <c r="C181" s="9">
         <v>1</v>
@@ -4368,7 +4368,7 @@
         <v>15</v>
       </c>
       <c r="B182" s="5">
-        <v>46112</v>
+        <v>46155</v>
       </c>
       <c r="C182" s="6">
         <v>1</v>
@@ -4379,7 +4379,7 @@
         <v>15</v>
       </c>
       <c r="B183" s="8">
-        <v>46132</v>
+        <v>46112</v>
       </c>
       <c r="C183" s="9">
         <v>1</v>
@@ -4390,7 +4390,7 @@
         <v>15</v>
       </c>
       <c r="B184" s="5">
-        <v>46108</v>
+        <v>46132</v>
       </c>
       <c r="C184" s="6">
         <v>1</v>
@@ -4401,7 +4401,7 @@
         <v>15</v>
       </c>
       <c r="B185" s="8">
-        <v>46148</v>
+        <v>46108</v>
       </c>
       <c r="C185" s="9">
         <v>1</v>
@@ -4412,7 +4412,7 @@
         <v>15</v>
       </c>
       <c r="B186" s="5">
-        <v>46118</v>
+        <v>46148</v>
       </c>
       <c r="C186" s="6">
         <v>1</v>
@@ -4423,7 +4423,7 @@
         <v>15</v>
       </c>
       <c r="B187" s="8">
-        <v>46035</v>
+        <v>46118</v>
       </c>
       <c r="C187" s="9">
         <v>1</v>
@@ -4434,7 +4434,7 @@
         <v>15</v>
       </c>
       <c r="B188" s="5">
-        <v>46181</v>
+        <v>46035</v>
       </c>
       <c r="C188" s="6">
         <v>1</v>
@@ -4445,7 +4445,7 @@
         <v>15</v>
       </c>
       <c r="B189" s="8">
-        <v>46093</v>
+        <v>46181</v>
       </c>
       <c r="C189" s="9">
         <v>1</v>
@@ -4456,7 +4456,7 @@
         <v>15</v>
       </c>
       <c r="B190" s="5">
-        <v>46022</v>
+        <v>46093</v>
       </c>
       <c r="C190" s="6">
         <v>1</v>
@@ -4467,7 +4467,7 @@
         <v>15</v>
       </c>
       <c r="B191" s="8">
-        <v>46087</v>
+        <v>46022</v>
       </c>
       <c r="C191" s="9">
         <v>1</v>
@@ -4478,10 +4478,10 @@
         <v>15</v>
       </c>
       <c r="B192" s="5">
-        <v>46030</v>
+        <v>46087</v>
       </c>
       <c r="C192" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -4489,10 +4489,10 @@
         <v>15</v>
       </c>
       <c r="B193" s="8">
-        <v>46176</v>
+        <v>46030</v>
       </c>
       <c r="C193" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -4500,7 +4500,7 @@
         <v>15</v>
       </c>
       <c r="B194" s="5">
-        <v>46101</v>
+        <v>46176</v>
       </c>
       <c r="C194" s="6">
         <v>1</v>
@@ -4511,7 +4511,7 @@
         <v>15</v>
       </c>
       <c r="B195" s="8">
-        <v>46142</v>
+        <v>46101</v>
       </c>
       <c r="C195" s="9">
         <v>1</v>
@@ -4519,13 +4519,13 @@
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B196" s="5">
-        <v>46001</v>
+        <v>46142</v>
       </c>
       <c r="C196" s="6">
-        <v>153</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -4533,10 +4533,10 @@
         <v>21</v>
       </c>
       <c r="B197" s="8">
-        <v>46008</v>
+        <v>46001</v>
       </c>
       <c r="C197" s="9">
-        <v>38</v>
+        <v>153</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
@@ -4544,10 +4544,10 @@
         <v>21</v>
       </c>
       <c r="B198" s="5">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="C198" s="6">
-        <v>70</v>
+        <v>38</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -4555,10 +4555,10 @@
         <v>21</v>
       </c>
       <c r="B199" s="8">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="C199" s="9">
-        <v>111</v>
+        <v>70</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -4566,10 +4566,10 @@
         <v>21</v>
       </c>
       <c r="B200" s="5">
-        <v>46006</v>
+        <v>46002</v>
       </c>
       <c r="C200" s="6">
-        <v>146</v>
+        <v>111</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -4577,10 +4577,10 @@
         <v>21</v>
       </c>
       <c r="B201" s="8">
-        <v>46007</v>
+        <v>46006</v>
       </c>
       <c r="C201" s="9">
-        <v>45</v>
+        <v>146</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -4588,10 +4588,10 @@
         <v>21</v>
       </c>
       <c r="B202" s="5">
-        <v>46000</v>
+        <v>46007</v>
       </c>
       <c r="C202" s="6">
-        <v>127</v>
+        <v>45</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -4599,10 +4599,10 @@
         <v>21</v>
       </c>
       <c r="B203" s="8">
-        <v>46084</v>
+        <v>46000</v>
       </c>
       <c r="C203" s="9">
-        <v>10</v>
+        <v>127</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -4610,10 +4610,10 @@
         <v>21</v>
       </c>
       <c r="B204" s="5">
-        <v>46013</v>
+        <v>46084</v>
       </c>
       <c r="C204" s="6">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -4621,10 +4621,10 @@
         <v>21</v>
       </c>
       <c r="B205" s="8">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="C205" s="9">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -4632,10 +4632,10 @@
         <v>21</v>
       </c>
       <c r="B206" s="5">
-        <v>46021</v>
+        <v>46010</v>
       </c>
       <c r="C206" s="6">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -4643,10 +4643,10 @@
         <v>21</v>
       </c>
       <c r="B207" s="8">
-        <v>46009</v>
+        <v>46021</v>
       </c>
       <c r="C207" s="9">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4654,10 +4654,10 @@
         <v>21</v>
       </c>
       <c r="B208" s="5">
-        <v>46083</v>
+        <v>46009</v>
       </c>
       <c r="C208" s="6">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4665,10 +4665,10 @@
         <v>21</v>
       </c>
       <c r="B209" s="8">
-        <v>46014</v>
+        <v>46083</v>
       </c>
       <c r="C209" s="9">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4676,10 +4676,10 @@
         <v>21</v>
       </c>
       <c r="B210" s="5">
-        <v>46157</v>
+        <v>46014</v>
       </c>
       <c r="C210" s="6">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -4687,10 +4687,10 @@
         <v>21</v>
       </c>
       <c r="B211" s="8">
-        <v>46079</v>
+        <v>46157</v>
       </c>
       <c r="C211" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -4698,10 +4698,10 @@
         <v>21</v>
       </c>
       <c r="B212" s="5">
-        <v>46167</v>
+        <v>46079</v>
       </c>
       <c r="C212" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4709,10 +4709,10 @@
         <v>21</v>
       </c>
       <c r="B213" s="8">
-        <v>46077</v>
+        <v>46167</v>
       </c>
       <c r="C213" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4720,10 +4720,10 @@
         <v>21</v>
       </c>
       <c r="B214" s="5">
-        <v>46035</v>
+        <v>46077</v>
       </c>
       <c r="C214" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4731,10 +4731,10 @@
         <v>21</v>
       </c>
       <c r="B215" s="8">
-        <v>46085</v>
+        <v>46035</v>
       </c>
       <c r="C215" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4742,10 +4742,10 @@
         <v>21</v>
       </c>
       <c r="B216" s="5">
-        <v>46120</v>
+        <v>46085</v>
       </c>
       <c r="C216" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4753,10 +4753,10 @@
         <v>21</v>
       </c>
       <c r="B217" s="8">
-        <v>46114</v>
+        <v>46120</v>
       </c>
       <c r="C217" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -4764,10 +4764,10 @@
         <v>21</v>
       </c>
       <c r="B218" s="5">
-        <v>46094</v>
+        <v>46114</v>
       </c>
       <c r="C218" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -4775,10 +4775,10 @@
         <v>21</v>
       </c>
       <c r="B219" s="8">
-        <v>46080</v>
+        <v>46094</v>
       </c>
       <c r="C219" s="9">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4786,10 +4786,10 @@
         <v>21</v>
       </c>
       <c r="B220" s="5">
-        <v>46127</v>
+        <v>46080</v>
       </c>
       <c r="C220" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -4797,7 +4797,7 @@
         <v>21</v>
       </c>
       <c r="B221" s="8">
-        <v>46091</v>
+        <v>46127</v>
       </c>
       <c r="C221" s="9">
         <v>2</v>
@@ -4808,10 +4808,10 @@
         <v>21</v>
       </c>
       <c r="B222" s="5">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="C222" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -4819,10 +4819,10 @@
         <v>21</v>
       </c>
       <c r="B223" s="8">
-        <v>46020</v>
+        <v>46090</v>
       </c>
       <c r="C223" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -4830,10 +4830,10 @@
         <v>21</v>
       </c>
       <c r="B224" s="5">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="C224" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -4841,10 +4841,10 @@
         <v>21</v>
       </c>
       <c r="B225" s="8">
-        <v>46078</v>
+        <v>46015</v>
       </c>
       <c r="C225" s="9">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -4852,10 +4852,10 @@
         <v>21</v>
       </c>
       <c r="B226" s="5">
-        <v>46148</v>
+        <v>46078</v>
       </c>
       <c r="C226" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -4863,7 +4863,7 @@
         <v>21</v>
       </c>
       <c r="B227" s="8">
-        <v>46105</v>
+        <v>46148</v>
       </c>
       <c r="C227" s="9">
         <v>2</v>
@@ -4874,10 +4874,10 @@
         <v>21</v>
       </c>
       <c r="B228" s="5">
-        <v>46087</v>
+        <v>46105</v>
       </c>
       <c r="C228" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -4885,7 +4885,7 @@
         <v>21</v>
       </c>
       <c r="B229" s="8">
-        <v>46107</v>
+        <v>46087</v>
       </c>
       <c r="C229" s="9">
         <v>3</v>
@@ -4896,10 +4896,10 @@
         <v>21</v>
       </c>
       <c r="B230" s="5">
-        <v>46086</v>
+        <v>46107</v>
       </c>
       <c r="C230" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -4907,10 +4907,10 @@
         <v>21</v>
       </c>
       <c r="B231" s="8">
-        <v>46106</v>
+        <v>46086</v>
       </c>
       <c r="C231" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -4918,10 +4918,10 @@
         <v>21</v>
       </c>
       <c r="B232" s="5">
-        <v>46150</v>
+        <v>46106</v>
       </c>
       <c r="C232" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -4929,7 +4929,7 @@
         <v>21</v>
       </c>
       <c r="B233" s="8">
-        <v>46104</v>
+        <v>46150</v>
       </c>
       <c r="C233" s="9">
         <v>3</v>
@@ -4940,10 +4940,10 @@
         <v>21</v>
       </c>
       <c r="B234" s="5">
-        <v>46118</v>
+        <v>46104</v>
       </c>
       <c r="C234" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -4951,10 +4951,10 @@
         <v>21</v>
       </c>
       <c r="B235" s="8">
-        <v>46076</v>
+        <v>46118</v>
       </c>
       <c r="C235" s="9">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -4962,10 +4962,10 @@
         <v>21</v>
       </c>
       <c r="B236" s="5">
-        <v>46182</v>
+        <v>46076</v>
       </c>
       <c r="C236" s="6">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -4973,7 +4973,7 @@
         <v>21</v>
       </c>
       <c r="B237" s="8">
-        <v>46154</v>
+        <v>46182</v>
       </c>
       <c r="C237" s="9">
         <v>1</v>
@@ -4984,10 +4984,10 @@
         <v>21</v>
       </c>
       <c r="B238" s="5">
-        <v>46093</v>
+        <v>46154</v>
       </c>
       <c r="C238" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -4995,10 +4995,10 @@
         <v>21</v>
       </c>
       <c r="B239" s="8">
-        <v>46122</v>
+        <v>46093</v>
       </c>
       <c r="C239" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -5006,10 +5006,10 @@
         <v>21</v>
       </c>
       <c r="B240" s="5">
-        <v>46092</v>
+        <v>46122</v>
       </c>
       <c r="C240" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -5017,10 +5017,10 @@
         <v>21</v>
       </c>
       <c r="B241" s="8">
-        <v>46156</v>
+        <v>46092</v>
       </c>
       <c r="C241" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -5028,10 +5028,10 @@
         <v>21</v>
       </c>
       <c r="B242" s="5">
-        <v>46133</v>
+        <v>46156</v>
       </c>
       <c r="C242" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -5039,7 +5039,7 @@
         <v>21</v>
       </c>
       <c r="B243" s="8">
-        <v>46126</v>
+        <v>46133</v>
       </c>
       <c r="C243" s="9">
         <v>1</v>
@@ -5050,10 +5050,10 @@
         <v>21</v>
       </c>
       <c r="B244" s="5">
-        <v>46022</v>
+        <v>46126</v>
       </c>
       <c r="C244" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -5061,7 +5061,7 @@
         <v>21</v>
       </c>
       <c r="B245" s="8">
-        <v>46100</v>
+        <v>46022</v>
       </c>
       <c r="C245" s="9">
         <v>2</v>
@@ -5072,10 +5072,10 @@
         <v>21</v>
       </c>
       <c r="B246" s="5">
-        <v>46101</v>
+        <v>46100</v>
       </c>
       <c r="C246" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -5083,10 +5083,10 @@
         <v>21</v>
       </c>
       <c r="B247" s="8">
-        <v>46097</v>
+        <v>46101</v>
       </c>
       <c r="C247" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
@@ -5094,10 +5094,10 @@
         <v>21</v>
       </c>
       <c r="B248" s="5">
-        <v>46108</v>
+        <v>46097</v>
       </c>
       <c r="C248" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -5105,10 +5105,10 @@
         <v>21</v>
       </c>
       <c r="B249" s="8">
-        <v>46098</v>
+        <v>46108</v>
       </c>
       <c r="C249" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
@@ -5116,10 +5116,10 @@
         <v>21</v>
       </c>
       <c r="B250" s="5">
-        <v>46113</v>
+        <v>46098</v>
       </c>
       <c r="C250" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -5127,7 +5127,7 @@
         <v>21</v>
       </c>
       <c r="B251" s="8">
-        <v>46142</v>
+        <v>46113</v>
       </c>
       <c r="C251" s="9">
         <v>1</v>
@@ -5138,7 +5138,7 @@
         <v>21</v>
       </c>
       <c r="B252" s="5">
-        <v>46153</v>
+        <v>46142</v>
       </c>
       <c r="C252" s="6">
         <v>1</v>
@@ -5149,7 +5149,7 @@
         <v>21</v>
       </c>
       <c r="B253" s="8">
-        <v>46031</v>
+        <v>46153</v>
       </c>
       <c r="C253" s="9">
         <v>1</v>
@@ -5160,9 +5160,20 @@
         <v>21</v>
       </c>
       <c r="B254" s="5">
+        <v>46031</v>
+      </c>
+      <c r="C254" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B255" s="8">
         <v>46155</v>
       </c>
-      <c r="C254" s="6">
+      <c r="C255" s="9">
         <v>1</v>
       </c>
     </row>
@@ -5433,7 +5444,7 @@
         <v>5</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -5529,7 +5540,7 @@
         <v>7</v>
       </c>
       <c r="C21">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D21">
         <v>6</v>

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="209" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36132FEB-14DF-4989-9BEE-28D9B6C90BD8}"/>
+  <xr:revisionPtr revIDLastSave="229" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2FCA052-7E6B-46AB-9697-B6753863B5EF}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="731" firstSheet="1" activeTab="2" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" tabRatio="731" firstSheet="1" activeTab="5" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="proyeccion_2026" sheetId="2" r:id="rId1"/>
@@ -24,7 +24,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">mat_2026!$A$1:$E$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">origen_colegios!$A$1:$C$352</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">origen_colegios!$A$1:$C$348</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1317" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1317" uniqueCount="295">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -287,9 +287,6 @@
   </si>
   <si>
     <t>Escuela Básica Cristo Redentor</t>
-  </si>
-  <si>
-    <t>EXTRANJERO</t>
   </si>
   <si>
     <t>Escuela General Bernardo O'Higgins</t>
@@ -1724,10 +1721,10 @@
         <v>64</v>
       </c>
       <c r="D10">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E10">
-        <v>1.0940000000000001</v>
+        <v>1.109</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1741,10 +1738,10 @@
         <v>88</v>
       </c>
       <c r="D11">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E11">
-        <v>1.0569999999999999</v>
+        <v>1.0680000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -2132,10 +2129,10 @@
         <v>323</v>
       </c>
       <c r="D34">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E34">
-        <v>0.96</v>
+        <v>0.96299999999999997</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -2166,10 +2163,10 @@
         <v>250</v>
       </c>
       <c r="D36">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E36">
-        <v>1.024</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2183,10 +2180,10 @@
         <v>217</v>
       </c>
       <c r="D37">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E37">
-        <v>1</v>
+        <v>0.995</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -2233,7 +2230,7 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -2255,7 +2252,7 @@
         <v>34</v>
       </c>
       <c r="C2">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2321,7 +2318,7 @@
         <v>34</v>
       </c>
       <c r="C8">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2354,7 +2351,7 @@
         <v>34</v>
       </c>
       <c r="C11">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
   </sheetData>
@@ -2364,7 +2361,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD19485A-0629-47F9-A5AD-80ABA7A6E076}">
-  <dimension ref="A1:C255"/>
+  <dimension ref="A1:C257"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -2993,7 +2990,7 @@
         <v>16</v>
       </c>
       <c r="B57" s="8">
-        <v>46101</v>
+        <v>46188</v>
       </c>
       <c r="C57" s="9">
         <v>1</v>
@@ -3001,13 +2998,13 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B58" s="5">
-        <v>46007</v>
+        <v>46101</v>
       </c>
       <c r="C58" s="6">
-        <v>78</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -3015,10 +3012,10 @@
         <v>14</v>
       </c>
       <c r="B59" s="8">
-        <v>46009</v>
+        <v>46007</v>
       </c>
       <c r="C59" s="9">
-        <v>34</v>
+        <v>78</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -3026,10 +3023,10 @@
         <v>14</v>
       </c>
       <c r="B60" s="5">
-        <v>46000</v>
+        <v>46009</v>
       </c>
       <c r="C60" s="6">
-        <v>79</v>
+        <v>34</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -3037,10 +3034,10 @@
         <v>14</v>
       </c>
       <c r="B61" s="8">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C61" s="9">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -3048,10 +3045,10 @@
         <v>14</v>
       </c>
       <c r="B62" s="5">
-        <v>46006</v>
+        <v>46001</v>
       </c>
       <c r="C62" s="6">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -3059,10 +3056,10 @@
         <v>14</v>
       </c>
       <c r="B63" s="8">
-        <v>46010</v>
+        <v>46006</v>
       </c>
       <c r="C63" s="9">
-        <v>24</v>
+        <v>79</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -3070,10 +3067,10 @@
         <v>14</v>
       </c>
       <c r="B64" s="5">
-        <v>46014</v>
+        <v>46010</v>
       </c>
       <c r="C64" s="6">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -3081,10 +3078,10 @@
         <v>14</v>
       </c>
       <c r="B65" s="8">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="C65" s="9">
-        <v>47</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -3092,10 +3089,10 @@
         <v>14</v>
       </c>
       <c r="B66" s="5">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C66" s="6">
-        <v>58</v>
+        <v>47</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -3103,10 +3100,10 @@
         <v>14</v>
       </c>
       <c r="B67" s="8">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="C67" s="9">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -3114,10 +3111,10 @@
         <v>14</v>
       </c>
       <c r="B68" s="5">
-        <v>46013</v>
+        <v>46003</v>
       </c>
       <c r="C68" s="6">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -3125,10 +3122,10 @@
         <v>14</v>
       </c>
       <c r="B69" s="8">
-        <v>46022</v>
+        <v>46013</v>
       </c>
       <c r="C69" s="9">
-        <v>2</v>
+        <v>30</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -3136,10 +3133,10 @@
         <v>14</v>
       </c>
       <c r="B70" s="5">
-        <v>46080</v>
+        <v>46022</v>
       </c>
       <c r="C70" s="6">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -3147,10 +3144,10 @@
         <v>14</v>
       </c>
       <c r="B71" s="8">
-        <v>46084</v>
+        <v>46080</v>
       </c>
       <c r="C71" s="9">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -3158,10 +3155,10 @@
         <v>14</v>
       </c>
       <c r="B72" s="5">
-        <v>46125</v>
+        <v>46084</v>
       </c>
       <c r="C72" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -3169,10 +3166,10 @@
         <v>14</v>
       </c>
       <c r="B73" s="8">
-        <v>46091</v>
+        <v>46125</v>
       </c>
       <c r="C73" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -3180,10 +3177,10 @@
         <v>14</v>
       </c>
       <c r="B74" s="5">
-        <v>46083</v>
+        <v>46091</v>
       </c>
       <c r="C74" s="6">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -3191,10 +3188,10 @@
         <v>14</v>
       </c>
       <c r="B75" s="8">
-        <v>46105</v>
+        <v>46083</v>
       </c>
       <c r="C75" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -3202,10 +3199,10 @@
         <v>14</v>
       </c>
       <c r="B76" s="5">
-        <v>46077</v>
+        <v>46105</v>
       </c>
       <c r="C76" s="6">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -3213,10 +3210,10 @@
         <v>14</v>
       </c>
       <c r="B77" s="8">
-        <v>46118</v>
+        <v>46077</v>
       </c>
       <c r="C77" s="9">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -3224,10 +3221,10 @@
         <v>14</v>
       </c>
       <c r="B78" s="5">
-        <v>46078</v>
+        <v>46118</v>
       </c>
       <c r="C78" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -3235,10 +3232,10 @@
         <v>14</v>
       </c>
       <c r="B79" s="8">
-        <v>46099</v>
+        <v>46078</v>
       </c>
       <c r="C79" s="9">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -3246,10 +3243,10 @@
         <v>14</v>
       </c>
       <c r="B80" s="5">
-        <v>46104</v>
+        <v>46099</v>
       </c>
       <c r="C80" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -3257,10 +3254,10 @@
         <v>14</v>
       </c>
       <c r="B81" s="8">
-        <v>46020</v>
+        <v>46104</v>
       </c>
       <c r="C81" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -3268,10 +3265,10 @@
         <v>14</v>
       </c>
       <c r="B82" s="5">
-        <v>46076</v>
+        <v>46020</v>
       </c>
       <c r="C82" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -3279,10 +3276,10 @@
         <v>14</v>
       </c>
       <c r="B83" s="8">
-        <v>46111</v>
+        <v>46076</v>
       </c>
       <c r="C83" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -3290,10 +3287,10 @@
         <v>14</v>
       </c>
       <c r="B84" s="5">
-        <v>46087</v>
+        <v>46111</v>
       </c>
       <c r="C84" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -3301,7 +3298,7 @@
         <v>14</v>
       </c>
       <c r="B85" s="8">
-        <v>46140</v>
+        <v>46087</v>
       </c>
       <c r="C85" s="9">
         <v>2</v>
@@ -3312,10 +3309,10 @@
         <v>14</v>
       </c>
       <c r="B86" s="5">
-        <v>46113</v>
+        <v>46140</v>
       </c>
       <c r="C86" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -3323,10 +3320,10 @@
         <v>14</v>
       </c>
       <c r="B87" s="8">
-        <v>46119</v>
+        <v>46113</v>
       </c>
       <c r="C87" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -3334,10 +3331,10 @@
         <v>14</v>
       </c>
       <c r="B88" s="5">
-        <v>46108</v>
+        <v>46119</v>
       </c>
       <c r="C88" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -3345,7 +3342,7 @@
         <v>14</v>
       </c>
       <c r="B89" s="8">
-        <v>46098</v>
+        <v>46108</v>
       </c>
       <c r="C89" s="9">
         <v>1</v>
@@ -3356,7 +3353,7 @@
         <v>14</v>
       </c>
       <c r="B90" s="5">
-        <v>46141</v>
+        <v>46098</v>
       </c>
       <c r="C90" s="6">
         <v>1</v>
@@ -3367,7 +3364,7 @@
         <v>14</v>
       </c>
       <c r="B91" s="8">
-        <v>46114</v>
+        <v>46141</v>
       </c>
       <c r="C91" s="9">
         <v>1</v>
@@ -3378,10 +3375,10 @@
         <v>14</v>
       </c>
       <c r="B92" s="5">
-        <v>46079</v>
+        <v>46114</v>
       </c>
       <c r="C92" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -3389,10 +3386,10 @@
         <v>14</v>
       </c>
       <c r="B93" s="8">
-        <v>46139</v>
+        <v>46079</v>
       </c>
       <c r="C93" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -3400,10 +3397,10 @@
         <v>14</v>
       </c>
       <c r="B94" s="5">
-        <v>46148</v>
+        <v>46139</v>
       </c>
       <c r="C94" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -3411,10 +3408,10 @@
         <v>14</v>
       </c>
       <c r="B95" s="8">
-        <v>46185</v>
+        <v>46148</v>
       </c>
       <c r="C95" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -3422,7 +3419,7 @@
         <v>14</v>
       </c>
       <c r="B96" s="5">
-        <v>46174</v>
+        <v>46185</v>
       </c>
       <c r="C96" s="6">
         <v>1</v>
@@ -3433,7 +3430,7 @@
         <v>14</v>
       </c>
       <c r="B97" s="8">
-        <v>46092</v>
+        <v>46174</v>
       </c>
       <c r="C97" s="9">
         <v>1</v>
@@ -3444,10 +3441,10 @@
         <v>14</v>
       </c>
       <c r="B98" s="5">
-        <v>46021</v>
+        <v>46092</v>
       </c>
       <c r="C98" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -3455,10 +3452,10 @@
         <v>14</v>
       </c>
       <c r="B99" s="8">
-        <v>46177</v>
+        <v>46021</v>
       </c>
       <c r="C99" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -3466,10 +3463,10 @@
         <v>14</v>
       </c>
       <c r="B100" s="5">
-        <v>46086</v>
+        <v>46177</v>
       </c>
       <c r="C100" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -3477,10 +3474,10 @@
         <v>14</v>
       </c>
       <c r="B101" s="8">
-        <v>46147</v>
+        <v>46086</v>
       </c>
       <c r="C101" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -3488,7 +3485,7 @@
         <v>14</v>
       </c>
       <c r="B102" s="5">
-        <v>46134</v>
+        <v>46147</v>
       </c>
       <c r="C102" s="6">
         <v>1</v>
@@ -3499,7 +3496,7 @@
         <v>14</v>
       </c>
       <c r="B103" s="8">
-        <v>46182</v>
+        <v>46134</v>
       </c>
       <c r="C103" s="9">
         <v>1</v>
@@ -3507,13 +3504,13 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B104" s="5">
-        <v>46003</v>
+        <v>46182</v>
       </c>
       <c r="C104" s="6">
-        <v>95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -3521,10 +3518,10 @@
         <v>3</v>
       </c>
       <c r="B105" s="8">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="C105" s="9">
-        <v>115</v>
+        <v>95</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -3532,10 +3529,10 @@
         <v>3</v>
       </c>
       <c r="B106" s="5">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C106" s="6">
-        <v>14</v>
+        <v>115</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -3543,10 +3540,10 @@
         <v>3</v>
       </c>
       <c r="B107" s="8">
-        <v>46000</v>
+        <v>46008</v>
       </c>
       <c r="C107" s="9">
-        <v>98</v>
+        <v>14</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -3554,10 +3551,10 @@
         <v>3</v>
       </c>
       <c r="B108" s="5">
-        <v>46007</v>
+        <v>46000</v>
       </c>
       <c r="C108" s="6">
-        <v>40</v>
+        <v>98</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -3565,10 +3562,10 @@
         <v>3</v>
       </c>
       <c r="B109" s="8">
-        <v>46001</v>
+        <v>46007</v>
       </c>
       <c r="C109" s="9">
-        <v>91</v>
+        <v>40</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -3576,10 +3573,10 @@
         <v>3</v>
       </c>
       <c r="B110" s="5">
-        <v>46010</v>
+        <v>46001</v>
       </c>
       <c r="C110" s="6">
-        <v>9</v>
+        <v>91</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -3587,10 +3584,10 @@
         <v>3</v>
       </c>
       <c r="B111" s="8">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="C111" s="9">
-        <v>84</v>
+        <v>9</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -3598,10 +3595,10 @@
         <v>3</v>
       </c>
       <c r="B112" s="5">
-        <v>46009</v>
+        <v>46006</v>
       </c>
       <c r="C112" s="6">
-        <v>2</v>
+        <v>84</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -3609,10 +3606,10 @@
         <v>3</v>
       </c>
       <c r="B113" s="8">
-        <v>46015</v>
+        <v>46009</v>
       </c>
       <c r="C113" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -3620,10 +3617,10 @@
         <v>3</v>
       </c>
       <c r="B114" s="5">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="C114" s="6">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -3631,10 +3628,10 @@
         <v>3</v>
       </c>
       <c r="B115" s="8">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="C115" s="9">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -3642,7 +3639,7 @@
         <v>3</v>
       </c>
       <c r="B116" s="5">
-        <v>46021</v>
+        <v>46013</v>
       </c>
       <c r="C116" s="6">
         <v>2</v>
@@ -3653,10 +3650,10 @@
         <v>3</v>
       </c>
       <c r="B117" s="8">
-        <v>46077</v>
+        <v>46021</v>
       </c>
       <c r="C117" s="9">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -3664,10 +3661,10 @@
         <v>3</v>
       </c>
       <c r="B118" s="5">
-        <v>46167</v>
+        <v>46077</v>
       </c>
       <c r="C118" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -3675,10 +3672,10 @@
         <v>3</v>
       </c>
       <c r="B119" s="8">
-        <v>46090</v>
+        <v>46167</v>
       </c>
       <c r="C119" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -3686,10 +3683,10 @@
         <v>3</v>
       </c>
       <c r="B120" s="5">
-        <v>46170</v>
+        <v>46090</v>
       </c>
       <c r="C120" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -3697,10 +3694,10 @@
         <v>3</v>
       </c>
       <c r="B121" s="8">
-        <v>46093</v>
+        <v>46189</v>
       </c>
       <c r="C121" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -3708,10 +3705,10 @@
         <v>3</v>
       </c>
       <c r="B122" s="5">
-        <v>46078</v>
+        <v>46170</v>
       </c>
       <c r="C122" s="6">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -3719,10 +3716,10 @@
         <v>3</v>
       </c>
       <c r="B123" s="8">
-        <v>46084</v>
+        <v>46093</v>
       </c>
       <c r="C123" s="9">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -3730,10 +3727,10 @@
         <v>3</v>
       </c>
       <c r="B124" s="5">
-        <v>46134</v>
+        <v>46078</v>
       </c>
       <c r="C124" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -3741,10 +3738,10 @@
         <v>3</v>
       </c>
       <c r="B125" s="8">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="C125" s="9">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
@@ -3752,10 +3749,10 @@
         <v>3</v>
       </c>
       <c r="B126" s="5">
-        <v>46022</v>
+        <v>46134</v>
       </c>
       <c r="C126" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -3763,10 +3760,10 @@
         <v>3</v>
       </c>
       <c r="B127" s="8">
-        <v>46114</v>
+        <v>46083</v>
       </c>
       <c r="C127" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -3774,7 +3771,7 @@
         <v>3</v>
       </c>
       <c r="B128" s="5">
-        <v>46135</v>
+        <v>46022</v>
       </c>
       <c r="C128" s="6">
         <v>1</v>
@@ -3785,10 +3782,10 @@
         <v>3</v>
       </c>
       <c r="B129" s="8">
-        <v>46168</v>
+        <v>46114</v>
       </c>
       <c r="C129" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -3796,10 +3793,10 @@
         <v>3</v>
       </c>
       <c r="B130" s="5">
-        <v>46126</v>
+        <v>46135</v>
       </c>
       <c r="C130" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -3807,7 +3804,7 @@
         <v>3</v>
       </c>
       <c r="B131" s="8">
-        <v>46120</v>
+        <v>46168</v>
       </c>
       <c r="C131" s="9">
         <v>3</v>
@@ -3818,10 +3815,10 @@
         <v>3</v>
       </c>
       <c r="B132" s="5">
-        <v>46127</v>
+        <v>46126</v>
       </c>
       <c r="C132" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -3829,10 +3826,10 @@
         <v>3</v>
       </c>
       <c r="B133" s="8">
-        <v>46087</v>
+        <v>46120</v>
       </c>
       <c r="C133" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -3840,7 +3837,7 @@
         <v>3</v>
       </c>
       <c r="B134" s="5">
-        <v>46108</v>
+        <v>46127</v>
       </c>
       <c r="C134" s="6">
         <v>1</v>
@@ -3851,7 +3848,7 @@
         <v>3</v>
       </c>
       <c r="B135" s="8">
-        <v>46020</v>
+        <v>46087</v>
       </c>
       <c r="C135" s="9">
         <v>1</v>
@@ -3862,7 +3859,7 @@
         <v>3</v>
       </c>
       <c r="B136" s="5">
-        <v>46097</v>
+        <v>46108</v>
       </c>
       <c r="C136" s="6">
         <v>1</v>
@@ -3873,7 +3870,7 @@
         <v>3</v>
       </c>
       <c r="B137" s="8">
-        <v>46177</v>
+        <v>46020</v>
       </c>
       <c r="C137" s="9">
         <v>1</v>
@@ -3884,10 +3881,10 @@
         <v>3</v>
       </c>
       <c r="B138" s="5">
-        <v>46161</v>
+        <v>46097</v>
       </c>
       <c r="C138" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -3895,7 +3892,7 @@
         <v>3</v>
       </c>
       <c r="B139" s="8">
-        <v>46129</v>
+        <v>46177</v>
       </c>
       <c r="C139" s="9">
         <v>1</v>
@@ -3906,10 +3903,10 @@
         <v>3</v>
       </c>
       <c r="B140" s="5">
-        <v>46080</v>
+        <v>46161</v>
       </c>
       <c r="C140" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -3917,7 +3914,7 @@
         <v>3</v>
       </c>
       <c r="B141" s="8">
-        <v>46101</v>
+        <v>46129</v>
       </c>
       <c r="C141" s="9">
         <v>1</v>
@@ -3928,7 +3925,7 @@
         <v>3</v>
       </c>
       <c r="B142" s="5">
-        <v>46155</v>
+        <v>46080</v>
       </c>
       <c r="C142" s="6">
         <v>1</v>
@@ -3939,7 +3936,7 @@
         <v>3</v>
       </c>
       <c r="B143" s="8">
-        <v>46150</v>
+        <v>46101</v>
       </c>
       <c r="C143" s="9">
         <v>1</v>
@@ -3950,7 +3947,7 @@
         <v>3</v>
       </c>
       <c r="B144" s="5">
-        <v>46141</v>
+        <v>46155</v>
       </c>
       <c r="C144" s="6">
         <v>1</v>
@@ -3961,7 +3958,7 @@
         <v>3</v>
       </c>
       <c r="B145" s="8">
-        <v>46085</v>
+        <v>46150</v>
       </c>
       <c r="C145" s="9">
         <v>1</v>
@@ -3972,7 +3969,7 @@
         <v>3</v>
       </c>
       <c r="B146" s="5">
-        <v>46148</v>
+        <v>46141</v>
       </c>
       <c r="C146" s="6">
         <v>1</v>
@@ -3983,10 +3980,10 @@
         <v>3</v>
       </c>
       <c r="B147" s="8">
-        <v>46118</v>
+        <v>46085</v>
       </c>
       <c r="C147" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -3994,7 +3991,7 @@
         <v>3</v>
       </c>
       <c r="B148" s="5">
-        <v>46079</v>
+        <v>46148</v>
       </c>
       <c r="C148" s="6">
         <v>1</v>
@@ -4002,24 +3999,24 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B149" s="8">
-        <v>46003</v>
+        <v>46118</v>
       </c>
       <c r="C149" s="9">
-        <v>92</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B150" s="5">
-        <v>46000</v>
+        <v>46079</v>
       </c>
       <c r="C150" s="6">
-        <v>132</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -4027,10 +4024,10 @@
         <v>15</v>
       </c>
       <c r="B151" s="8">
-        <v>46006</v>
+        <v>46003</v>
       </c>
       <c r="C151" s="9">
-        <v>173</v>
+        <v>92</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -4038,10 +4035,10 @@
         <v>15</v>
       </c>
       <c r="B152" s="5">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C152" s="6">
-        <v>174</v>
+        <v>132</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -4049,10 +4046,10 @@
         <v>15</v>
       </c>
       <c r="B153" s="8">
-        <v>46014</v>
+        <v>46006</v>
       </c>
       <c r="C153" s="9">
-        <v>16</v>
+        <v>173</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -4060,10 +4057,10 @@
         <v>15</v>
       </c>
       <c r="B154" s="5">
-        <v>46002</v>
+        <v>46001</v>
       </c>
       <c r="C154" s="6">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -4071,10 +4068,10 @@
         <v>15</v>
       </c>
       <c r="B155" s="8">
-        <v>46009</v>
+        <v>46014</v>
       </c>
       <c r="C155" s="9">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -4082,10 +4079,10 @@
         <v>15</v>
       </c>
       <c r="B156" s="5">
-        <v>46010</v>
+        <v>46002</v>
       </c>
       <c r="C156" s="6">
-        <v>19</v>
+        <v>171</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -4093,10 +4090,10 @@
         <v>15</v>
       </c>
       <c r="B157" s="8">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="C157" s="9">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -4104,10 +4101,10 @@
         <v>15</v>
       </c>
       <c r="B158" s="5">
-        <v>46007</v>
+        <v>46010</v>
       </c>
       <c r="C158" s="6">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -4115,10 +4112,10 @@
         <v>15</v>
       </c>
       <c r="B159" s="8">
-        <v>46013</v>
+        <v>46008</v>
       </c>
       <c r="C159" s="9">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -4126,10 +4123,10 @@
         <v>15</v>
       </c>
       <c r="B160" s="5">
-        <v>46080</v>
+        <v>46007</v>
       </c>
       <c r="C160" s="6">
-        <v>2</v>
+        <v>43</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -4137,10 +4134,10 @@
         <v>15</v>
       </c>
       <c r="B161" s="8">
-        <v>46090</v>
+        <v>46013</v>
       </c>
       <c r="C161" s="9">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -4148,10 +4145,10 @@
         <v>15</v>
       </c>
       <c r="B162" s="5">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="C162" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -4159,10 +4156,10 @@
         <v>15</v>
       </c>
       <c r="B163" s="8">
-        <v>46015</v>
+        <v>46090</v>
       </c>
       <c r="C163" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -4170,10 +4167,10 @@
         <v>15</v>
       </c>
       <c r="B164" s="5">
-        <v>46085</v>
+        <v>46079</v>
       </c>
       <c r="C164" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -4181,10 +4178,10 @@
         <v>15</v>
       </c>
       <c r="B165" s="8">
-        <v>46098</v>
+        <v>46015</v>
       </c>
       <c r="C165" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -4192,10 +4189,10 @@
         <v>15</v>
       </c>
       <c r="B166" s="5">
-        <v>46021</v>
+        <v>46085</v>
       </c>
       <c r="C166" s="6">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -4203,10 +4200,10 @@
         <v>15</v>
       </c>
       <c r="B167" s="8">
-        <v>46078</v>
+        <v>46098</v>
       </c>
       <c r="C167" s="9">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -4214,10 +4211,10 @@
         <v>15</v>
       </c>
       <c r="B168" s="5">
-        <v>46084</v>
+        <v>46021</v>
       </c>
       <c r="C168" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -4225,10 +4222,10 @@
         <v>15</v>
       </c>
       <c r="B169" s="8">
-        <v>46128</v>
+        <v>46078</v>
       </c>
       <c r="C169" s="9">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -4236,7 +4233,7 @@
         <v>15</v>
       </c>
       <c r="B170" s="5">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="C170" s="6">
         <v>8</v>
@@ -4247,10 +4244,10 @@
         <v>15</v>
       </c>
       <c r="B171" s="8">
-        <v>46076</v>
+        <v>46128</v>
       </c>
       <c r="C171" s="9">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -4258,10 +4255,10 @@
         <v>15</v>
       </c>
       <c r="B172" s="5">
-        <v>46099</v>
+        <v>46083</v>
       </c>
       <c r="C172" s="6">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -4269,10 +4266,10 @@
         <v>15</v>
       </c>
       <c r="B173" s="8">
-        <v>46154</v>
+        <v>46076</v>
       </c>
       <c r="C173" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -4280,10 +4277,10 @@
         <v>15</v>
       </c>
       <c r="B174" s="5">
-        <v>46092</v>
+        <v>46099</v>
       </c>
       <c r="C174" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -4291,10 +4288,10 @@
         <v>15</v>
       </c>
       <c r="B175" s="8">
-        <v>46031</v>
+        <v>46154</v>
       </c>
       <c r="C175" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -4302,10 +4299,10 @@
         <v>15</v>
       </c>
       <c r="B176" s="5">
-        <v>46120</v>
+        <v>46092</v>
       </c>
       <c r="C176" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -4313,10 +4310,10 @@
         <v>15</v>
       </c>
       <c r="B177" s="8">
-        <v>46077</v>
+        <v>46022</v>
       </c>
       <c r="C177" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -4324,10 +4321,10 @@
         <v>15</v>
       </c>
       <c r="B178" s="5">
-        <v>46114</v>
+        <v>46031</v>
       </c>
       <c r="C178" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -4335,10 +4332,10 @@
         <v>15</v>
       </c>
       <c r="B179" s="8">
-        <v>46037</v>
+        <v>46120</v>
       </c>
       <c r="C179" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -4346,10 +4343,10 @@
         <v>15</v>
       </c>
       <c r="B180" s="5">
-        <v>46020</v>
+        <v>46077</v>
       </c>
       <c r="C180" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -4357,7 +4354,7 @@
         <v>15</v>
       </c>
       <c r="B181" s="8">
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="C181" s="9">
         <v>1</v>
@@ -4368,7 +4365,7 @@
         <v>15</v>
       </c>
       <c r="B182" s="5">
-        <v>46155</v>
+        <v>46037</v>
       </c>
       <c r="C182" s="6">
         <v>1</v>
@@ -4379,10 +4376,10 @@
         <v>15</v>
       </c>
       <c r="B183" s="8">
-        <v>46112</v>
+        <v>46020</v>
       </c>
       <c r="C183" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -4390,7 +4387,7 @@
         <v>15</v>
       </c>
       <c r="B184" s="5">
-        <v>46132</v>
+        <v>46106</v>
       </c>
       <c r="C184" s="6">
         <v>1</v>
@@ -4401,7 +4398,7 @@
         <v>15</v>
       </c>
       <c r="B185" s="8">
-        <v>46108</v>
+        <v>46155</v>
       </c>
       <c r="C185" s="9">
         <v>1</v>
@@ -4412,7 +4409,7 @@
         <v>15</v>
       </c>
       <c r="B186" s="5">
-        <v>46148</v>
+        <v>46112</v>
       </c>
       <c r="C186" s="6">
         <v>1</v>
@@ -4423,7 +4420,7 @@
         <v>15</v>
       </c>
       <c r="B187" s="8">
-        <v>46118</v>
+        <v>46132</v>
       </c>
       <c r="C187" s="9">
         <v>1</v>
@@ -4434,7 +4431,7 @@
         <v>15</v>
       </c>
       <c r="B188" s="5">
-        <v>46035</v>
+        <v>46108</v>
       </c>
       <c r="C188" s="6">
         <v>1</v>
@@ -4445,7 +4442,7 @@
         <v>15</v>
       </c>
       <c r="B189" s="8">
-        <v>46181</v>
+        <v>46148</v>
       </c>
       <c r="C189" s="9">
         <v>1</v>
@@ -4456,7 +4453,7 @@
         <v>15</v>
       </c>
       <c r="B190" s="5">
-        <v>46093</v>
+        <v>46118</v>
       </c>
       <c r="C190" s="6">
         <v>1</v>
@@ -4467,7 +4464,7 @@
         <v>15</v>
       </c>
       <c r="B191" s="8">
-        <v>46022</v>
+        <v>46035</v>
       </c>
       <c r="C191" s="9">
         <v>1</v>
@@ -4478,7 +4475,7 @@
         <v>15</v>
       </c>
       <c r="B192" s="5">
-        <v>46087</v>
+        <v>46181</v>
       </c>
       <c r="C192" s="6">
         <v>1</v>
@@ -4489,10 +4486,10 @@
         <v>15</v>
       </c>
       <c r="B193" s="8">
-        <v>46030</v>
+        <v>46093</v>
       </c>
       <c r="C193" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
@@ -4500,7 +4497,7 @@
         <v>15</v>
       </c>
       <c r="B194" s="5">
-        <v>46176</v>
+        <v>46087</v>
       </c>
       <c r="C194" s="6">
         <v>1</v>
@@ -4511,10 +4508,10 @@
         <v>15</v>
       </c>
       <c r="B195" s="8">
-        <v>46101</v>
+        <v>46030</v>
       </c>
       <c r="C195" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -4522,7 +4519,7 @@
         <v>15</v>
       </c>
       <c r="B196" s="5">
-        <v>46142</v>
+        <v>46176</v>
       </c>
       <c r="C196" s="6">
         <v>1</v>
@@ -4530,24 +4527,24 @@
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B197" s="8">
-        <v>46001</v>
+        <v>46101</v>
       </c>
       <c r="C197" s="9">
-        <v>153</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B198" s="5">
-        <v>46008</v>
+        <v>46142</v>
       </c>
       <c r="C198" s="6">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -4555,10 +4552,10 @@
         <v>21</v>
       </c>
       <c r="B199" s="8">
-        <v>46003</v>
+        <v>46001</v>
       </c>
       <c r="C199" s="9">
-        <v>70</v>
+        <v>153</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -4566,10 +4563,10 @@
         <v>21</v>
       </c>
       <c r="B200" s="5">
-        <v>46002</v>
+        <v>46008</v>
       </c>
       <c r="C200" s="6">
-        <v>111</v>
+        <v>38</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -4577,10 +4574,10 @@
         <v>21</v>
       </c>
       <c r="B201" s="8">
-        <v>46006</v>
+        <v>46003</v>
       </c>
       <c r="C201" s="9">
-        <v>146</v>
+        <v>70</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -4588,10 +4585,10 @@
         <v>21</v>
       </c>
       <c r="B202" s="5">
-        <v>46007</v>
+        <v>46002</v>
       </c>
       <c r="C202" s="6">
-        <v>45</v>
+        <v>111</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -4599,10 +4596,10 @@
         <v>21</v>
       </c>
       <c r="B203" s="8">
-        <v>46000</v>
+        <v>46006</v>
       </c>
       <c r="C203" s="9">
-        <v>127</v>
+        <v>146</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -4610,10 +4607,10 @@
         <v>21</v>
       </c>
       <c r="B204" s="5">
-        <v>46084</v>
+        <v>46007</v>
       </c>
       <c r="C204" s="6">
-        <v>10</v>
+        <v>45</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -4621,10 +4618,10 @@
         <v>21</v>
       </c>
       <c r="B205" s="8">
-        <v>46013</v>
+        <v>46000</v>
       </c>
       <c r="C205" s="9">
-        <v>27</v>
+        <v>127</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -4632,10 +4629,10 @@
         <v>21</v>
       </c>
       <c r="B206" s="5">
-        <v>46010</v>
+        <v>46084</v>
       </c>
       <c r="C206" s="6">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -4643,10 +4640,10 @@
         <v>21</v>
       </c>
       <c r="B207" s="8">
-        <v>46021</v>
+        <v>46013</v>
       </c>
       <c r="C207" s="9">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4654,10 +4651,10 @@
         <v>21</v>
       </c>
       <c r="B208" s="5">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="C208" s="6">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4665,10 +4662,10 @@
         <v>21</v>
       </c>
       <c r="B209" s="8">
-        <v>46083</v>
+        <v>46021</v>
       </c>
       <c r="C209" s="9">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4676,10 +4673,10 @@
         <v>21</v>
       </c>
       <c r="B210" s="5">
-        <v>46014</v>
+        <v>46009</v>
       </c>
       <c r="C210" s="6">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -4687,10 +4684,10 @@
         <v>21</v>
       </c>
       <c r="B211" s="8">
-        <v>46157</v>
+        <v>46083</v>
       </c>
       <c r="C211" s="9">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -4698,10 +4695,10 @@
         <v>21</v>
       </c>
       <c r="B212" s="5">
-        <v>46079</v>
+        <v>46014</v>
       </c>
       <c r="C212" s="6">
-        <v>3</v>
+        <v>20</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4709,10 +4706,10 @@
         <v>21</v>
       </c>
       <c r="B213" s="8">
-        <v>46167</v>
+        <v>46157</v>
       </c>
       <c r="C213" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4720,10 +4717,10 @@
         <v>21</v>
       </c>
       <c r="B214" s="5">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="C214" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4731,10 +4728,10 @@
         <v>21</v>
       </c>
       <c r="B215" s="8">
-        <v>46035</v>
+        <v>46167</v>
       </c>
       <c r="C215" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4742,10 +4739,10 @@
         <v>21</v>
       </c>
       <c r="B216" s="5">
-        <v>46085</v>
+        <v>46035</v>
       </c>
       <c r="C216" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4753,10 +4750,10 @@
         <v>21</v>
       </c>
       <c r="B217" s="8">
-        <v>46120</v>
+        <v>46085</v>
       </c>
       <c r="C217" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -4764,10 +4761,10 @@
         <v>21</v>
       </c>
       <c r="B218" s="5">
-        <v>46114</v>
+        <v>46120</v>
       </c>
       <c r="C218" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -4775,10 +4772,10 @@
         <v>21</v>
       </c>
       <c r="B219" s="8">
-        <v>46094</v>
+        <v>46114</v>
       </c>
       <c r="C219" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4786,10 +4783,10 @@
         <v>21</v>
       </c>
       <c r="B220" s="5">
-        <v>46080</v>
+        <v>46094</v>
       </c>
       <c r="C220" s="6">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -4797,10 +4794,10 @@
         <v>21</v>
       </c>
       <c r="B221" s="8">
-        <v>46127</v>
+        <v>46080</v>
       </c>
       <c r="C221" s="9">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -4808,7 +4805,7 @@
         <v>21</v>
       </c>
       <c r="B222" s="5">
-        <v>46091</v>
+        <v>46127</v>
       </c>
       <c r="C222" s="6">
         <v>2</v>
@@ -4819,10 +4816,10 @@
         <v>21</v>
       </c>
       <c r="B223" s="8">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="C223" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -4830,10 +4827,10 @@
         <v>21</v>
       </c>
       <c r="B224" s="5">
-        <v>46020</v>
+        <v>46090</v>
       </c>
       <c r="C224" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -4841,10 +4838,10 @@
         <v>21</v>
       </c>
       <c r="B225" s="8">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="C225" s="9">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -4852,10 +4849,10 @@
         <v>21</v>
       </c>
       <c r="B226" s="5">
-        <v>46078</v>
+        <v>46015</v>
       </c>
       <c r="C226" s="6">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -4863,10 +4860,10 @@
         <v>21</v>
       </c>
       <c r="B227" s="8">
-        <v>46148</v>
+        <v>46078</v>
       </c>
       <c r="C227" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -4874,7 +4871,7 @@
         <v>21</v>
       </c>
       <c r="B228" s="5">
-        <v>46105</v>
+        <v>46148</v>
       </c>
       <c r="C228" s="6">
         <v>2</v>
@@ -4885,10 +4882,10 @@
         <v>21</v>
       </c>
       <c r="B229" s="8">
-        <v>46087</v>
+        <v>46105</v>
       </c>
       <c r="C229" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -4896,7 +4893,7 @@
         <v>21</v>
       </c>
       <c r="B230" s="5">
-        <v>46107</v>
+        <v>46087</v>
       </c>
       <c r="C230" s="6">
         <v>3</v>
@@ -4907,10 +4904,10 @@
         <v>21</v>
       </c>
       <c r="B231" s="8">
-        <v>46086</v>
+        <v>46107</v>
       </c>
       <c r="C231" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -4918,10 +4915,10 @@
         <v>21</v>
       </c>
       <c r="B232" s="5">
-        <v>46106</v>
+        <v>46086</v>
       </c>
       <c r="C232" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -4929,10 +4926,10 @@
         <v>21</v>
       </c>
       <c r="B233" s="8">
-        <v>46150</v>
+        <v>46106</v>
       </c>
       <c r="C233" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -4940,7 +4937,7 @@
         <v>21</v>
       </c>
       <c r="B234" s="5">
-        <v>46104</v>
+        <v>46150</v>
       </c>
       <c r="C234" s="6">
         <v>3</v>
@@ -4951,10 +4948,10 @@
         <v>21</v>
       </c>
       <c r="B235" s="8">
-        <v>46118</v>
+        <v>46104</v>
       </c>
       <c r="C235" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -4962,10 +4959,10 @@
         <v>21</v>
       </c>
       <c r="B236" s="5">
-        <v>46076</v>
+        <v>46118</v>
       </c>
       <c r="C236" s="6">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -4973,10 +4970,10 @@
         <v>21</v>
       </c>
       <c r="B237" s="8">
-        <v>46182</v>
+        <v>46076</v>
       </c>
       <c r="C237" s="9">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -4984,7 +4981,7 @@
         <v>21</v>
       </c>
       <c r="B238" s="5">
-        <v>46154</v>
+        <v>46182</v>
       </c>
       <c r="C238" s="6">
         <v>1</v>
@@ -4995,10 +4992,10 @@
         <v>21</v>
       </c>
       <c r="B239" s="8">
-        <v>46093</v>
+        <v>46077</v>
       </c>
       <c r="C239" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -5006,7 +5003,7 @@
         <v>21</v>
       </c>
       <c r="B240" s="5">
-        <v>46122</v>
+        <v>46154</v>
       </c>
       <c r="C240" s="6">
         <v>1</v>
@@ -5017,7 +5014,7 @@
         <v>21</v>
       </c>
       <c r="B241" s="8">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="C241" s="9">
         <v>3</v>
@@ -5028,10 +5025,10 @@
         <v>21</v>
       </c>
       <c r="B242" s="5">
-        <v>46156</v>
+        <v>46122</v>
       </c>
       <c r="C242" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -5039,10 +5036,10 @@
         <v>21</v>
       </c>
       <c r="B243" s="8">
-        <v>46133</v>
+        <v>46092</v>
       </c>
       <c r="C243" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
@@ -5050,10 +5047,10 @@
         <v>21</v>
       </c>
       <c r="B244" s="5">
-        <v>46126</v>
+        <v>46156</v>
       </c>
       <c r="C244" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -5061,10 +5058,10 @@
         <v>21</v>
       </c>
       <c r="B245" s="8">
-        <v>46022</v>
+        <v>46133</v>
       </c>
       <c r="C245" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
@@ -5072,10 +5069,10 @@
         <v>21</v>
       </c>
       <c r="B246" s="5">
-        <v>46100</v>
+        <v>46126</v>
       </c>
       <c r="C246" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -5083,10 +5080,10 @@
         <v>21</v>
       </c>
       <c r="B247" s="8">
-        <v>46101</v>
+        <v>46022</v>
       </c>
       <c r="C247" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
@@ -5094,10 +5091,10 @@
         <v>21</v>
       </c>
       <c r="B248" s="5">
-        <v>46097</v>
+        <v>46100</v>
       </c>
       <c r="C248" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -5105,7 +5102,7 @@
         <v>21</v>
       </c>
       <c r="B249" s="8">
-        <v>46108</v>
+        <v>46101</v>
       </c>
       <c r="C249" s="9">
         <v>1</v>
@@ -5116,10 +5113,10 @@
         <v>21</v>
       </c>
       <c r="B250" s="5">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="C250" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -5127,7 +5124,7 @@
         <v>21</v>
       </c>
       <c r="B251" s="8">
-        <v>46113</v>
+        <v>46108</v>
       </c>
       <c r="C251" s="9">
         <v>1</v>
@@ -5138,10 +5135,10 @@
         <v>21</v>
       </c>
       <c r="B252" s="5">
-        <v>46142</v>
+        <v>46098</v>
       </c>
       <c r="C252" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
@@ -5149,7 +5146,7 @@
         <v>21</v>
       </c>
       <c r="B253" s="8">
-        <v>46153</v>
+        <v>46113</v>
       </c>
       <c r="C253" s="9">
         <v>1</v>
@@ -5160,7 +5157,7 @@
         <v>21</v>
       </c>
       <c r="B254" s="5">
-        <v>46031</v>
+        <v>46142</v>
       </c>
       <c r="C254" s="6">
         <v>1</v>
@@ -5171,9 +5168,31 @@
         <v>21</v>
       </c>
       <c r="B255" s="8">
+        <v>46153</v>
+      </c>
+      <c r="C255" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B256" s="5">
+        <v>46031</v>
+      </c>
+      <c r="C256" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B257" s="8">
         <v>46155</v>
       </c>
-      <c r="C255" s="9">
+      <c r="C257" s="9">
         <v>1</v>
       </c>
     </row>
@@ -5359,7 +5378,7 @@
         <v>1</v>
       </c>
       <c r="E10">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -5376,7 +5395,7 @@
         <v>1</v>
       </c>
       <c r="E11">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -5767,7 +5786,7 @@
         <v>8</v>
       </c>
       <c r="E34">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -5798,7 +5817,7 @@
         <v>108</v>
       </c>
       <c r="D36">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E36">
         <v>61</v>
@@ -5818,7 +5837,7 @@
         <v>12</v>
       </c>
       <c r="E37">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -5862,7 +5881,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0916EAC6-1E7F-4924-9D0E-33749FD3E143}">
-  <dimension ref="A1:C349"/>
+  <dimension ref="A1:C348"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
@@ -5875,7 +5894,7 @@
         <v>37</v>
       </c>
       <c r="B1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C1" t="s">
         <v>36</v>
@@ -6084,7 +6103,7 @@
         <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -6150,7 +6169,7 @@
         <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -6238,7 +6257,7 @@
         <v>3</v>
       </c>
       <c r="B34" t="s">
-        <v>60</v>
+        <v>192</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -6260,7 +6279,7 @@
         <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="C36">
         <v>1</v>
@@ -6282,7 +6301,7 @@
         <v>3</v>
       </c>
       <c r="B38" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -6290,13 +6309,13 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="B39" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="C39">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -6315,7 +6334,7 @@
         <v>14</v>
       </c>
       <c r="B41" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C41">
         <v>5</v>
@@ -6359,7 +6378,7 @@
         <v>14</v>
       </c>
       <c r="B45" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C45">
         <v>4</v>
@@ -6414,7 +6433,7 @@
         <v>14</v>
       </c>
       <c r="B50" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C50">
         <v>2</v>
@@ -6425,7 +6444,7 @@
         <v>14</v>
       </c>
       <c r="B51" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C51">
         <v>2</v>
@@ -6447,7 +6466,7 @@
         <v>14</v>
       </c>
       <c r="B53" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C53">
         <v>2</v>
@@ -6469,7 +6488,7 @@
         <v>14</v>
       </c>
       <c r="B55" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C55">
         <v>2</v>
@@ -6480,7 +6499,7 @@
         <v>14</v>
       </c>
       <c r="B56" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C56">
         <v>2</v>
@@ -6513,7 +6532,7 @@
         <v>14</v>
       </c>
       <c r="B59" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C59">
         <v>2</v>
@@ -6524,7 +6543,7 @@
         <v>14</v>
       </c>
       <c r="B60" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C60">
         <v>2</v>
@@ -6546,7 +6565,7 @@
         <v>14</v>
       </c>
       <c r="B62" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C62">
         <v>2</v>
@@ -6557,7 +6576,7 @@
         <v>14</v>
       </c>
       <c r="B63" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -6568,7 +6587,7 @@
         <v>14</v>
       </c>
       <c r="B64" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -6590,7 +6609,7 @@
         <v>14</v>
       </c>
       <c r="B66" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -6601,7 +6620,7 @@
         <v>14</v>
       </c>
       <c r="B67" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -6612,7 +6631,7 @@
         <v>14</v>
       </c>
       <c r="B68" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -6634,7 +6653,7 @@
         <v>14</v>
       </c>
       <c r="B70" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -6645,7 +6664,7 @@
         <v>14</v>
       </c>
       <c r="B71" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -6656,7 +6675,7 @@
         <v>14</v>
       </c>
       <c r="B72" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -6667,7 +6686,7 @@
         <v>14</v>
       </c>
       <c r="B73" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -6678,7 +6697,7 @@
         <v>14</v>
       </c>
       <c r="B74" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -6689,7 +6708,7 @@
         <v>14</v>
       </c>
       <c r="B75" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -6722,7 +6741,7 @@
         <v>14</v>
       </c>
       <c r="B78" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C78">
         <v>1</v>
@@ -6733,7 +6752,7 @@
         <v>14</v>
       </c>
       <c r="B79" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -6744,7 +6763,7 @@
         <v>14</v>
       </c>
       <c r="B80" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C80">
         <v>1</v>
@@ -6755,7 +6774,7 @@
         <v>14</v>
       </c>
       <c r="B81" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -6766,7 +6785,7 @@
         <v>14</v>
       </c>
       <c r="B82" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C82">
         <v>1</v>
@@ -6777,7 +6796,7 @@
         <v>14</v>
       </c>
       <c r="B83" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -6788,7 +6807,7 @@
         <v>14</v>
       </c>
       <c r="B84" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C84">
         <v>1</v>
@@ -6810,7 +6829,7 @@
         <v>14</v>
       </c>
       <c r="B86" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C86">
         <v>1</v>
@@ -6821,7 +6840,7 @@
         <v>14</v>
       </c>
       <c r="B87" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C87">
         <v>1</v>
@@ -6843,7 +6862,7 @@
         <v>14</v>
       </c>
       <c r="B89" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -6854,7 +6873,7 @@
         <v>14</v>
       </c>
       <c r="B90" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C90">
         <v>1</v>
@@ -6865,7 +6884,7 @@
         <v>14</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C91">
         <v>1</v>
@@ -6876,7 +6895,7 @@
         <v>14</v>
       </c>
       <c r="B92" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C92">
         <v>1</v>
@@ -6887,7 +6906,7 @@
         <v>14</v>
       </c>
       <c r="B93" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C93">
         <v>1</v>
@@ -6909,7 +6928,7 @@
         <v>14</v>
       </c>
       <c r="B95" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C95">
         <v>1</v>
@@ -6920,7 +6939,7 @@
         <v>14</v>
       </c>
       <c r="B96" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C96">
         <v>1</v>
@@ -6942,7 +6961,7 @@
         <v>14</v>
       </c>
       <c r="B98" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -6953,7 +6972,7 @@
         <v>15</v>
       </c>
       <c r="B99" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C99">
         <v>14</v>
@@ -6964,7 +6983,7 @@
         <v>15</v>
       </c>
       <c r="B100" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C100">
         <v>14</v>
@@ -6975,7 +6994,7 @@
         <v>15</v>
       </c>
       <c r="B101" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C101">
         <v>10</v>
@@ -6986,7 +7005,7 @@
         <v>15</v>
       </c>
       <c r="B102" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C102">
         <v>8</v>
@@ -6997,7 +7016,7 @@
         <v>15</v>
       </c>
       <c r="B103" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C103">
         <v>6</v>
@@ -7008,7 +7027,7 @@
         <v>15</v>
       </c>
       <c r="B104" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C104">
         <v>6</v>
@@ -7019,7 +7038,7 @@
         <v>15</v>
       </c>
       <c r="B105" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C105">
         <v>6</v>
@@ -7030,7 +7049,7 @@
         <v>15</v>
       </c>
       <c r="B106" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C106">
         <v>4</v>
@@ -7041,7 +7060,7 @@
         <v>15</v>
       </c>
       <c r="B107" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C107">
         <v>4</v>
@@ -7052,7 +7071,7 @@
         <v>15</v>
       </c>
       <c r="B108" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C108">
         <v>4</v>
@@ -7063,7 +7082,7 @@
         <v>15</v>
       </c>
       <c r="B109" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C109">
         <v>4</v>
@@ -7074,7 +7093,7 @@
         <v>15</v>
       </c>
       <c r="B110" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C110">
         <v>4</v>
@@ -7085,7 +7104,7 @@
         <v>15</v>
       </c>
       <c r="B111" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C111">
         <v>3</v>
@@ -7096,7 +7115,7 @@
         <v>15</v>
       </c>
       <c r="B112" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C112">
         <v>3</v>
@@ -7107,7 +7126,7 @@
         <v>15</v>
       </c>
       <c r="B113" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C113">
         <v>3</v>
@@ -7118,7 +7137,7 @@
         <v>15</v>
       </c>
       <c r="B114" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C114">
         <v>3</v>
@@ -7129,7 +7148,7 @@
         <v>15</v>
       </c>
       <c r="B115" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C115">
         <v>3</v>
@@ -7140,7 +7159,7 @@
         <v>15</v>
       </c>
       <c r="B116" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C116">
         <v>3</v>
@@ -7151,7 +7170,7 @@
         <v>15</v>
       </c>
       <c r="B117" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C117">
         <v>2</v>
@@ -7162,7 +7181,7 @@
         <v>15</v>
       </c>
       <c r="B118" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C118">
         <v>2</v>
@@ -7173,7 +7192,7 @@
         <v>15</v>
       </c>
       <c r="B119" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C119">
         <v>2</v>
@@ -7184,7 +7203,7 @@
         <v>15</v>
       </c>
       <c r="B120" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C120">
         <v>2</v>
@@ -7206,7 +7225,7 @@
         <v>15</v>
       </c>
       <c r="B122" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C122">
         <v>2</v>
@@ -7217,7 +7236,7 @@
         <v>15</v>
       </c>
       <c r="B123" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C123">
         <v>2</v>
@@ -7228,7 +7247,7 @@
         <v>15</v>
       </c>
       <c r="B124" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C124">
         <v>2</v>
@@ -7239,7 +7258,7 @@
         <v>15</v>
       </c>
       <c r="B125" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C125">
         <v>2</v>
@@ -7261,7 +7280,7 @@
         <v>15</v>
       </c>
       <c r="B127" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C127">
         <v>1</v>
@@ -7272,7 +7291,7 @@
         <v>15</v>
       </c>
       <c r="B128" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C128">
         <v>1</v>
@@ -7283,7 +7302,7 @@
         <v>15</v>
       </c>
       <c r="B129" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C129">
         <v>1</v>
@@ -7294,7 +7313,7 @@
         <v>15</v>
       </c>
       <c r="B130" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C130">
         <v>1</v>
@@ -7305,7 +7324,7 @@
         <v>15</v>
       </c>
       <c r="B131" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C131">
         <v>1</v>
@@ -7316,7 +7335,7 @@
         <v>15</v>
       </c>
       <c r="B132" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C132">
         <v>1</v>
@@ -7327,7 +7346,7 @@
         <v>15</v>
       </c>
       <c r="B133" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C133">
         <v>1</v>
@@ -7338,7 +7357,7 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C134">
         <v>1</v>
@@ -7349,7 +7368,7 @@
         <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C135">
         <v>1</v>
@@ -7360,7 +7379,7 @@
         <v>15</v>
       </c>
       <c r="B136" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C136">
         <v>1</v>
@@ -7371,7 +7390,7 @@
         <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C137">
         <v>1</v>
@@ -7382,7 +7401,7 @@
         <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C138">
         <v>1</v>
@@ -7393,7 +7412,7 @@
         <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C139">
         <v>1</v>
@@ -7404,7 +7423,7 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C140">
         <v>1</v>
@@ -7415,7 +7434,7 @@
         <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C141">
         <v>1</v>
@@ -7426,7 +7445,7 @@
         <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C142">
         <v>1</v>
@@ -7437,7 +7456,7 @@
         <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C143">
         <v>1</v>
@@ -7448,7 +7467,7 @@
         <v>15</v>
       </c>
       <c r="B144" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C144">
         <v>1</v>
@@ -7459,7 +7478,7 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C145">
         <v>1</v>
@@ -7470,7 +7489,7 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C146">
         <v>1</v>
@@ -7481,7 +7500,7 @@
         <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C147">
         <v>1</v>
@@ -7492,7 +7511,7 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C148">
         <v>1</v>
@@ -7503,7 +7522,7 @@
         <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C149">
         <v>1</v>
@@ -7514,7 +7533,7 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C150">
         <v>1</v>
@@ -7525,7 +7544,7 @@
         <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C151">
         <v>1</v>
@@ -7536,7 +7555,7 @@
         <v>15</v>
       </c>
       <c r="B152" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C152">
         <v>1</v>
@@ -7547,7 +7566,7 @@
         <v>15</v>
       </c>
       <c r="B153" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C153">
         <v>1</v>
@@ -7558,7 +7577,7 @@
         <v>15</v>
       </c>
       <c r="B154" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C154">
         <v>1</v>
@@ -7569,7 +7588,7 @@
         <v>15</v>
       </c>
       <c r="B155" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C155">
         <v>1</v>
@@ -7580,7 +7599,7 @@
         <v>15</v>
       </c>
       <c r="B156" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C156">
         <v>1</v>
@@ -7591,7 +7610,7 @@
         <v>15</v>
       </c>
       <c r="B157" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C157">
         <v>1</v>
@@ -7602,7 +7621,7 @@
         <v>15</v>
       </c>
       <c r="B158" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C158">
         <v>1</v>
@@ -7613,7 +7632,7 @@
         <v>15</v>
       </c>
       <c r="B159" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C159">
         <v>1</v>
@@ -7624,7 +7643,7 @@
         <v>15</v>
       </c>
       <c r="B160" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C160">
         <v>1</v>
@@ -7635,7 +7654,7 @@
         <v>15</v>
       </c>
       <c r="B161" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C161">
         <v>1</v>
@@ -7646,7 +7665,7 @@
         <v>15</v>
       </c>
       <c r="B162" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C162">
         <v>1</v>
@@ -7657,7 +7676,7 @@
         <v>15</v>
       </c>
       <c r="B163" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -7668,7 +7687,7 @@
         <v>15</v>
       </c>
       <c r="B164" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C164">
         <v>1</v>
@@ -7679,7 +7698,7 @@
         <v>15</v>
       </c>
       <c r="B165" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C165">
         <v>1</v>
@@ -7690,7 +7709,7 @@
         <v>15</v>
       </c>
       <c r="B166" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C166">
         <v>1</v>
@@ -7701,7 +7720,7 @@
         <v>15</v>
       </c>
       <c r="B167" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -7712,7 +7731,7 @@
         <v>15</v>
       </c>
       <c r="B168" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C168">
         <v>1</v>
@@ -7723,7 +7742,7 @@
         <v>15</v>
       </c>
       <c r="B169" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -7734,7 +7753,7 @@
         <v>15</v>
       </c>
       <c r="B170" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -7767,7 +7786,7 @@
         <v>15</v>
       </c>
       <c r="B173" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C173">
         <v>1</v>
@@ -7789,7 +7808,7 @@
         <v>15</v>
       </c>
       <c r="B175" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C175">
         <v>1</v>
@@ -7800,7 +7819,7 @@
         <v>15</v>
       </c>
       <c r="B176" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -7811,7 +7830,7 @@
         <v>15</v>
       </c>
       <c r="B177" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -7822,7 +7841,7 @@
         <v>15</v>
       </c>
       <c r="B178" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -7833,7 +7852,7 @@
         <v>15</v>
       </c>
       <c r="B179" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -7844,7 +7863,7 @@
         <v>15</v>
       </c>
       <c r="B180" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C180">
         <v>1</v>
@@ -7855,7 +7874,7 @@
         <v>15</v>
       </c>
       <c r="B181" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C181">
         <v>1</v>
@@ -7866,7 +7885,7 @@
         <v>15</v>
       </c>
       <c r="B182" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C182">
         <v>1</v>
@@ -7877,7 +7896,7 @@
         <v>15</v>
       </c>
       <c r="B183" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C183">
         <v>1</v>
@@ -7932,7 +7951,7 @@
         <v>16</v>
       </c>
       <c r="B188" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C188">
         <v>14</v>
@@ -7943,7 +7962,7 @@
         <v>16</v>
       </c>
       <c r="B189" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C189">
         <v>13</v>
@@ -7954,7 +7973,7 @@
         <v>16</v>
       </c>
       <c r="B190" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C190">
         <v>12</v>
@@ -7965,7 +7984,7 @@
         <v>16</v>
       </c>
       <c r="B191" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C191">
         <v>12</v>
@@ -8042,7 +8061,7 @@
         <v>16</v>
       </c>
       <c r="B198" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C198">
         <v>8</v>
@@ -8053,7 +8072,7 @@
         <v>16</v>
       </c>
       <c r="B199" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C199">
         <v>7</v>
@@ -8075,7 +8094,7 @@
         <v>16</v>
       </c>
       <c r="B201" t="s">
-        <v>57</v>
+        <v>197</v>
       </c>
       <c r="C201">
         <v>6</v>
@@ -8086,7 +8105,7 @@
         <v>16</v>
       </c>
       <c r="B202" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C202">
         <v>6</v>
@@ -8097,10 +8116,10 @@
         <v>16</v>
       </c>
       <c r="B203" t="s">
-        <v>198</v>
+        <v>48</v>
       </c>
       <c r="C203">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -8130,7 +8149,7 @@
         <v>16</v>
       </c>
       <c r="B206" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C206">
         <v>5</v>
@@ -8185,7 +8204,7 @@
         <v>16</v>
       </c>
       <c r="B211" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C211">
         <v>4</v>
@@ -8196,7 +8215,7 @@
         <v>16</v>
       </c>
       <c r="B212" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C212">
         <v>4</v>
@@ -8207,7 +8226,7 @@
         <v>16</v>
       </c>
       <c r="B213" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C213">
         <v>4</v>
@@ -8218,7 +8237,7 @@
         <v>16</v>
       </c>
       <c r="B214" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C214">
         <v>3</v>
@@ -8251,7 +8270,7 @@
         <v>16</v>
       </c>
       <c r="B217" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C217">
         <v>3</v>
@@ -8273,7 +8292,7 @@
         <v>16</v>
       </c>
       <c r="B219" t="s">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="C219">
         <v>3</v>
@@ -8284,7 +8303,7 @@
         <v>16</v>
       </c>
       <c r="B220" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="C220">
         <v>3</v>
@@ -8295,10 +8314,10 @@
         <v>16</v>
       </c>
       <c r="B221" t="s">
-        <v>74</v>
+        <v>203</v>
       </c>
       <c r="C221">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -8306,7 +8325,7 @@
         <v>16</v>
       </c>
       <c r="B222" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C222">
         <v>2</v>
@@ -8317,7 +8336,7 @@
         <v>16</v>
       </c>
       <c r="B223" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C223">
         <v>2</v>
@@ -8328,7 +8347,7 @@
         <v>16</v>
       </c>
       <c r="B224" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C224">
         <v>2</v>
@@ -8339,7 +8358,7 @@
         <v>16</v>
       </c>
       <c r="B225" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C225">
         <v>2</v>
@@ -8350,7 +8369,7 @@
         <v>16</v>
       </c>
       <c r="B226" t="s">
-        <v>205</v>
+        <v>64</v>
       </c>
       <c r="C226">
         <v>2</v>
@@ -8361,7 +8380,7 @@
         <v>16</v>
       </c>
       <c r="B227" t="s">
-        <v>64</v>
+        <v>188</v>
       </c>
       <c r="C227">
         <v>2</v>
@@ -8372,7 +8391,7 @@
         <v>16</v>
       </c>
       <c r="B228" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="C228">
         <v>2</v>
@@ -8383,10 +8402,10 @@
         <v>16</v>
       </c>
       <c r="B229" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="C229">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -8394,7 +8413,7 @@
         <v>16</v>
       </c>
       <c r="B230" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C230">
         <v>1</v>
@@ -8405,7 +8424,7 @@
         <v>16</v>
       </c>
       <c r="B231" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="C231">
         <v>1</v>
@@ -8416,7 +8435,7 @@
         <v>16</v>
       </c>
       <c r="B232" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="C232">
         <v>1</v>
@@ -8427,7 +8446,7 @@
         <v>16</v>
       </c>
       <c r="B233" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C233">
         <v>1</v>
@@ -8438,7 +8457,7 @@
         <v>16</v>
       </c>
       <c r="B234" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="C234">
         <v>1</v>
@@ -8449,7 +8468,7 @@
         <v>16</v>
       </c>
       <c r="B235" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="C235">
         <v>1</v>
@@ -8460,7 +8479,7 @@
         <v>16</v>
       </c>
       <c r="B236" t="s">
-        <v>235</v>
+        <v>70</v>
       </c>
       <c r="C236">
         <v>1</v>
@@ -8471,7 +8490,7 @@
         <v>16</v>
       </c>
       <c r="B237" t="s">
-        <v>70</v>
+        <v>244</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -8482,7 +8501,7 @@
         <v>16</v>
       </c>
       <c r="B238" t="s">
-        <v>245</v>
+        <v>120</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -8493,7 +8512,7 @@
         <v>16</v>
       </c>
       <c r="B239" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -8504,7 +8523,7 @@
         <v>16</v>
       </c>
       <c r="B240" t="s">
-        <v>126</v>
+        <v>58</v>
       </c>
       <c r="C240">
         <v>1</v>
@@ -8515,7 +8534,7 @@
         <v>16</v>
       </c>
       <c r="B241" t="s">
-        <v>58</v>
+        <v>227</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -8526,7 +8545,7 @@
         <v>16</v>
       </c>
       <c r="B242" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -8537,7 +8556,7 @@
         <v>16</v>
       </c>
       <c r="B243" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -8548,7 +8567,7 @@
         <v>16</v>
       </c>
       <c r="B244" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -8559,7 +8578,7 @@
         <v>16</v>
       </c>
       <c r="B245" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -8570,7 +8589,7 @@
         <v>16</v>
       </c>
       <c r="B246" t="s">
-        <v>211</v>
+        <v>235</v>
       </c>
       <c r="C246">
         <v>1</v>
@@ -8581,7 +8600,7 @@
         <v>16</v>
       </c>
       <c r="B247" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="C247">
         <v>1</v>
@@ -8592,7 +8611,7 @@
         <v>16</v>
       </c>
       <c r="B248" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="C248">
         <v>1</v>
@@ -8603,7 +8622,7 @@
         <v>16</v>
       </c>
       <c r="B249" t="s">
-        <v>238</v>
+        <v>220</v>
       </c>
       <c r="C249">
         <v>1</v>
@@ -8614,7 +8633,7 @@
         <v>16</v>
       </c>
       <c r="B250" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -8625,7 +8644,7 @@
         <v>16</v>
       </c>
       <c r="B251" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="C251">
         <v>1</v>
@@ -8636,7 +8655,7 @@
         <v>16</v>
       </c>
       <c r="B252" t="s">
-        <v>233</v>
+        <v>211</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -8647,7 +8666,7 @@
         <v>16</v>
       </c>
       <c r="B253" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -8658,7 +8677,7 @@
         <v>16</v>
       </c>
       <c r="B254" t="s">
-        <v>210</v>
+        <v>69</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -8669,7 +8688,7 @@
         <v>16</v>
       </c>
       <c r="B255" t="s">
-        <v>69</v>
+        <v>114</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -8680,7 +8699,7 @@
         <v>16</v>
       </c>
       <c r="B256" t="s">
-        <v>115</v>
+        <v>233</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -8691,7 +8710,7 @@
         <v>16</v>
       </c>
       <c r="B257" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -8702,7 +8721,7 @@
         <v>16</v>
       </c>
       <c r="B258" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C258">
         <v>1</v>
@@ -8713,7 +8732,7 @@
         <v>16</v>
       </c>
       <c r="B259" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C259">
         <v>1</v>
@@ -8724,7 +8743,7 @@
         <v>16</v>
       </c>
       <c r="B260" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="C260">
         <v>1</v>
@@ -8735,7 +8754,7 @@
         <v>16</v>
       </c>
       <c r="B261" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C261">
         <v>1</v>
@@ -8746,7 +8765,7 @@
         <v>16</v>
       </c>
       <c r="B262" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="C262">
         <v>1</v>
@@ -8757,7 +8776,7 @@
         <v>16</v>
       </c>
       <c r="B263" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C263">
         <v>1</v>
@@ -8768,7 +8787,7 @@
         <v>16</v>
       </c>
       <c r="B264" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -8779,7 +8798,7 @@
         <v>16</v>
       </c>
       <c r="B265" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C265">
         <v>1</v>
@@ -8790,7 +8809,7 @@
         <v>16</v>
       </c>
       <c r="B266" t="s">
-        <v>239</v>
+        <v>118</v>
       </c>
       <c r="C266">
         <v>1</v>
@@ -8801,7 +8820,7 @@
         <v>16</v>
       </c>
       <c r="B267" t="s">
-        <v>119</v>
+        <v>213</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -8812,7 +8831,7 @@
         <v>16</v>
       </c>
       <c r="B268" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C268">
         <v>1</v>
@@ -8823,7 +8842,7 @@
         <v>16</v>
       </c>
       <c r="B269" t="s">
-        <v>208</v>
+        <v>236</v>
       </c>
       <c r="C269">
         <v>1</v>
@@ -8831,13 +8850,13 @@
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B270" t="s">
-        <v>237</v>
+        <v>120</v>
       </c>
       <c r="C270">
-        <v>1</v>
+        <v>38</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
@@ -8845,10 +8864,10 @@
         <v>21</v>
       </c>
       <c r="B271" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="C271">
-        <v>39</v>
+        <v>11</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
@@ -8856,10 +8875,10 @@
         <v>21</v>
       </c>
       <c r="B272" t="s">
-        <v>132</v>
+        <v>188</v>
       </c>
       <c r="C272">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
@@ -8867,10 +8886,10 @@
         <v>21</v>
       </c>
       <c r="B273" t="s">
-        <v>189</v>
+        <v>102</v>
       </c>
       <c r="C273">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
@@ -8878,7 +8897,7 @@
         <v>21</v>
       </c>
       <c r="B274" t="s">
-        <v>103</v>
+        <v>201</v>
       </c>
       <c r="C274">
         <v>7</v>
@@ -8889,10 +8908,10 @@
         <v>21</v>
       </c>
       <c r="B275" t="s">
-        <v>202</v>
+        <v>239</v>
       </c>
       <c r="C275">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -8900,7 +8919,7 @@
         <v>21</v>
       </c>
       <c r="B276" t="s">
-        <v>240</v>
+        <v>119</v>
       </c>
       <c r="C276">
         <v>6</v>
@@ -8911,10 +8930,10 @@
         <v>21</v>
       </c>
       <c r="B277" t="s">
-        <v>120</v>
+        <v>241</v>
       </c>
       <c r="C277">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -8922,7 +8941,7 @@
         <v>21</v>
       </c>
       <c r="B278" t="s">
-        <v>242</v>
+        <v>141</v>
       </c>
       <c r="C278">
         <v>5</v>
@@ -8933,7 +8952,7 @@
         <v>21</v>
       </c>
       <c r="B279" t="s">
-        <v>142</v>
+        <v>242</v>
       </c>
       <c r="C279">
         <v>5</v>
@@ -8944,7 +8963,7 @@
         <v>21</v>
       </c>
       <c r="B280" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C280">
         <v>5</v>
@@ -8955,10 +8974,10 @@
         <v>21</v>
       </c>
       <c r="B281" t="s">
-        <v>241</v>
+        <v>100</v>
       </c>
       <c r="C281">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -8966,7 +8985,7 @@
         <v>21</v>
       </c>
       <c r="B282" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="C282">
         <v>4</v>
@@ -8977,7 +8996,7 @@
         <v>21</v>
       </c>
       <c r="B283" t="s">
-        <v>128</v>
+        <v>243</v>
       </c>
       <c r="C283">
         <v>4</v>
@@ -8988,10 +9007,10 @@
         <v>21</v>
       </c>
       <c r="B284" t="s">
-        <v>244</v>
+        <v>80</v>
       </c>
       <c r="C284">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
@@ -8999,7 +9018,7 @@
         <v>21</v>
       </c>
       <c r="B285" t="s">
-        <v>81</v>
+        <v>244</v>
       </c>
       <c r="C285">
         <v>3</v>
@@ -9010,7 +9029,7 @@
         <v>21</v>
       </c>
       <c r="B286" t="s">
-        <v>245</v>
+        <v>125</v>
       </c>
       <c r="C286">
         <v>3</v>
@@ -9021,7 +9040,7 @@
         <v>21</v>
       </c>
       <c r="B287" t="s">
-        <v>126</v>
+        <v>195</v>
       </c>
       <c r="C287">
         <v>3</v>
@@ -9032,7 +9051,7 @@
         <v>21</v>
       </c>
       <c r="B288" t="s">
-        <v>196</v>
+        <v>126</v>
       </c>
       <c r="C288">
         <v>3</v>
@@ -9043,7 +9062,7 @@
         <v>21</v>
       </c>
       <c r="B289" t="s">
-        <v>127</v>
+        <v>248</v>
       </c>
       <c r="C289">
         <v>3</v>
@@ -9054,7 +9073,7 @@
         <v>21</v>
       </c>
       <c r="B290" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C290">
         <v>3</v>
@@ -9065,7 +9084,7 @@
         <v>21</v>
       </c>
       <c r="B291" t="s">
-        <v>248</v>
+        <v>162</v>
       </c>
       <c r="C291">
         <v>3</v>
@@ -9076,7 +9095,7 @@
         <v>21</v>
       </c>
       <c r="B292" t="s">
-        <v>163</v>
+        <v>246</v>
       </c>
       <c r="C292">
         <v>3</v>
@@ -9087,7 +9106,7 @@
         <v>21</v>
       </c>
       <c r="B293" t="s">
-        <v>247</v>
+        <v>44</v>
       </c>
       <c r="C293">
         <v>3</v>
@@ -9098,7 +9117,7 @@
         <v>21</v>
       </c>
       <c r="B294" t="s">
-        <v>44</v>
+        <v>132</v>
       </c>
       <c r="C294">
         <v>3</v>
@@ -9109,10 +9128,10 @@
         <v>21</v>
       </c>
       <c r="B295" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="C295">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -9120,7 +9139,7 @@
         <v>21</v>
       </c>
       <c r="B296" t="s">
-        <v>116</v>
+        <v>170</v>
       </c>
       <c r="C296">
         <v>2</v>
@@ -9131,7 +9150,7 @@
         <v>21</v>
       </c>
       <c r="B297" t="s">
-        <v>171</v>
+        <v>135</v>
       </c>
       <c r="C297">
         <v>2</v>
@@ -9142,7 +9161,7 @@
         <v>21</v>
       </c>
       <c r="B298" t="s">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="C298">
         <v>2</v>
@@ -9153,7 +9172,7 @@
         <v>21</v>
       </c>
       <c r="B299" t="s">
-        <v>173</v>
+        <v>250</v>
       </c>
       <c r="C299">
         <v>2</v>
@@ -9164,7 +9183,7 @@
         <v>21</v>
       </c>
       <c r="B300" t="s">
-        <v>251</v>
+        <v>77</v>
       </c>
       <c r="C300">
         <v>2</v>
@@ -9175,7 +9194,7 @@
         <v>21</v>
       </c>
       <c r="B301" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C301">
         <v>2</v>
@@ -9186,7 +9205,7 @@
         <v>21</v>
       </c>
       <c r="B302" t="s">
-        <v>70</v>
+        <v>251</v>
       </c>
       <c r="C302">
         <v>2</v>
@@ -9197,7 +9216,7 @@
         <v>21</v>
       </c>
       <c r="B303" t="s">
-        <v>252</v>
+        <v>54</v>
       </c>
       <c r="C303">
         <v>2</v>
@@ -9208,7 +9227,7 @@
         <v>21</v>
       </c>
       <c r="B304" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="C304">
         <v>2</v>
@@ -9219,7 +9238,7 @@
         <v>21</v>
       </c>
       <c r="B305" t="s">
-        <v>85</v>
+        <v>266</v>
       </c>
       <c r="C305">
         <v>2</v>
@@ -9230,7 +9249,7 @@
         <v>21</v>
       </c>
       <c r="B306" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="C306">
         <v>2</v>
@@ -9241,7 +9260,7 @@
         <v>21</v>
       </c>
       <c r="B307" t="s">
-        <v>253</v>
+        <v>197</v>
       </c>
       <c r="C307">
         <v>2</v>
@@ -9252,7 +9271,7 @@
         <v>21</v>
       </c>
       <c r="B308" t="s">
-        <v>198</v>
+        <v>249</v>
       </c>
       <c r="C308">
         <v>2</v>
@@ -9263,7 +9282,7 @@
         <v>21</v>
       </c>
       <c r="B309" t="s">
-        <v>250</v>
+        <v>62</v>
       </c>
       <c r="C309">
         <v>2</v>
@@ -9274,7 +9293,7 @@
         <v>21</v>
       </c>
       <c r="B310" t="s">
-        <v>199</v>
+        <v>245</v>
       </c>
       <c r="C310">
         <v>2</v>
@@ -9285,10 +9304,10 @@
         <v>21</v>
       </c>
       <c r="B311" t="s">
-        <v>62</v>
+        <v>253</v>
       </c>
       <c r="C311">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
@@ -9296,10 +9315,10 @@
         <v>21</v>
       </c>
       <c r="B312" t="s">
-        <v>246</v>
+        <v>114</v>
       </c>
       <c r="C312">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
@@ -9307,7 +9326,7 @@
         <v>21</v>
       </c>
       <c r="B313" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="C313">
         <v>1</v>
@@ -9318,7 +9337,7 @@
         <v>21</v>
       </c>
       <c r="B314" t="s">
-        <v>138</v>
+        <v>254</v>
       </c>
       <c r="C314">
         <v>1</v>
@@ -9329,7 +9348,7 @@
         <v>21</v>
       </c>
       <c r="B315" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="C315">
         <v>1</v>
@@ -9340,7 +9359,7 @@
         <v>21</v>
       </c>
       <c r="B316" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C316">
         <v>1</v>
@@ -9351,7 +9370,7 @@
         <v>21</v>
       </c>
       <c r="B317" t="s">
-        <v>271</v>
+        <v>198</v>
       </c>
       <c r="C317">
         <v>1</v>
@@ -9362,7 +9381,7 @@
         <v>21</v>
       </c>
       <c r="B318" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -9373,7 +9392,7 @@
         <v>21</v>
       </c>
       <c r="B319" t="s">
-        <v>275</v>
+        <v>49</v>
       </c>
       <c r="C319">
         <v>1</v>
@@ -9384,7 +9403,7 @@
         <v>21</v>
       </c>
       <c r="B320" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C320">
         <v>1</v>
@@ -9395,7 +9414,7 @@
         <v>21</v>
       </c>
       <c r="B321" t="s">
-        <v>172</v>
+        <v>260</v>
       </c>
       <c r="C321">
         <v>1</v>
@@ -9406,7 +9425,7 @@
         <v>21</v>
       </c>
       <c r="B322" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C322">
         <v>1</v>
@@ -9417,7 +9436,7 @@
         <v>21</v>
       </c>
       <c r="B323" t="s">
-        <v>63</v>
+        <v>124</v>
       </c>
       <c r="C323">
         <v>1</v>
@@ -9428,7 +9447,7 @@
         <v>21</v>
       </c>
       <c r="B324" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C324">
         <v>1</v>
@@ -9439,7 +9458,7 @@
         <v>21</v>
       </c>
       <c r="B325" t="s">
-        <v>276</v>
+        <v>164</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -9450,7 +9469,7 @@
         <v>21</v>
       </c>
       <c r="B326" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C326">
         <v>1</v>
@@ -9461,7 +9480,7 @@
         <v>21</v>
       </c>
       <c r="B327" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="C327">
         <v>1</v>
@@ -9472,7 +9491,7 @@
         <v>21</v>
       </c>
       <c r="B328" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C328">
         <v>1</v>
@@ -9483,7 +9502,7 @@
         <v>21</v>
       </c>
       <c r="B329" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C329">
         <v>1</v>
@@ -9494,7 +9513,7 @@
         <v>21</v>
       </c>
       <c r="B330" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C330">
         <v>1</v>
@@ -9505,7 +9524,7 @@
         <v>21</v>
       </c>
       <c r="B331" t="s">
-        <v>49</v>
+        <v>171</v>
       </c>
       <c r="C331">
         <v>1</v>
@@ -9516,7 +9535,7 @@
         <v>21</v>
       </c>
       <c r="B332" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C332">
         <v>1</v>
@@ -9527,7 +9546,7 @@
         <v>21</v>
       </c>
       <c r="B333" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="C333">
         <v>1</v>
@@ -9538,7 +9557,7 @@
         <v>21</v>
       </c>
       <c r="B334" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C334">
         <v>1</v>
@@ -9549,7 +9568,7 @@
         <v>21</v>
       </c>
       <c r="B335" t="s">
-        <v>261</v>
+        <v>63</v>
       </c>
       <c r="C335">
         <v>1</v>
@@ -9560,7 +9579,7 @@
         <v>21</v>
       </c>
       <c r="B336" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C336">
         <v>1</v>
@@ -9571,7 +9590,7 @@
         <v>21</v>
       </c>
       <c r="B337" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="C337">
         <v>1</v>
@@ -9582,7 +9601,7 @@
         <v>21</v>
       </c>
       <c r="B338" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C338">
         <v>1</v>
@@ -9593,7 +9612,7 @@
         <v>21</v>
       </c>
       <c r="B339" t="s">
-        <v>125</v>
+        <v>275</v>
       </c>
       <c r="C339">
         <v>1</v>
@@ -9604,7 +9623,7 @@
         <v>21</v>
       </c>
       <c r="B340" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C340">
         <v>1</v>
@@ -9615,7 +9634,7 @@
         <v>21</v>
       </c>
       <c r="B341" t="s">
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="C341">
         <v>1</v>
@@ -9626,7 +9645,7 @@
         <v>21</v>
       </c>
       <c r="B342" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C342">
         <v>1</v>
@@ -9637,7 +9656,7 @@
         <v>21</v>
       </c>
       <c r="B343" t="s">
-        <v>165</v>
+        <v>273</v>
       </c>
       <c r="C343">
         <v>1</v>
@@ -9648,7 +9667,7 @@
         <v>21</v>
       </c>
       <c r="B344" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C344">
         <v>1</v>
@@ -9659,7 +9678,7 @@
         <v>21</v>
       </c>
       <c r="B345" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="C345">
         <v>1</v>
@@ -9670,7 +9689,7 @@
         <v>21</v>
       </c>
       <c r="B346" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C346">
         <v>1</v>
@@ -9681,7 +9700,7 @@
         <v>21</v>
       </c>
       <c r="B347" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C347">
         <v>1</v>
@@ -9692,20 +9711,9 @@
         <v>21</v>
       </c>
       <c r="B348" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C348">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A349" t="s">
-        <v>21</v>
-      </c>
-      <c r="B349" t="s">
-        <v>264</v>
-      </c>
-      <c r="C349">
         <v>1</v>
       </c>
     </row>
@@ -9727,10 +9735,10 @@
         <v>37</v>
       </c>
       <c r="B1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C1" t="s">
         <v>280</v>
-      </c>
-      <c r="C1" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -9738,10 +9746,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C2">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -9749,10 +9757,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C3">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -9760,7 +9768,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C4">
         <v>37</v>
@@ -9771,10 +9779,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C5">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -9782,7 +9790,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C6">
         <v>7</v>
@@ -9793,7 +9801,7 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -9804,7 +9812,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C8">
         <v>29</v>
@@ -9815,10 +9823,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C9">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -9826,10 +9834,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C10">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -9837,7 +9845,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C11">
         <v>30</v>
@@ -9848,7 +9856,7 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C12">
         <v>26</v>
@@ -9859,7 +9867,7 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C13">
         <v>882</v>
@@ -9870,7 +9878,7 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C14">
         <v>4</v>
@@ -9881,7 +9889,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C15">
         <v>13</v>
@@ -9892,7 +9900,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C16">
         <v>22</v>
@@ -9903,7 +9911,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C17">
         <v>33</v>
@@ -9914,7 +9922,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C18">
         <v>11</v>
@@ -9925,7 +9933,7 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C19">
         <v>2</v>
@@ -9936,7 +9944,7 @@
         <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C20">
         <v>4</v>
@@ -9947,7 +9955,7 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C21">
         <v>2</v>
@@ -9958,7 +9966,7 @@
         <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C22">
         <v>2</v>
@@ -9969,7 +9977,7 @@
         <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C23">
         <v>41</v>
@@ -9980,10 +9988,10 @@
         <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C24">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -9991,7 +9999,7 @@
         <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C25">
         <v>25</v>
@@ -10002,7 +10010,7 @@
         <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C26">
         <v>111</v>
@@ -10013,7 +10021,7 @@
         <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C27">
         <v>140</v>
@@ -10024,7 +10032,7 @@
         <v>16</v>
       </c>
       <c r="B28" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C28">
         <v>77</v>
@@ -10035,7 +10043,7 @@
         <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C29">
         <v>10</v>
@@ -10046,7 +10054,7 @@
         <v>16</v>
       </c>
       <c r="B30" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -10057,7 +10065,7 @@
         <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C31">
         <v>7</v>
@@ -10068,7 +10076,7 @@
         <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -10079,10 +10087,10 @@
         <v>21</v>
       </c>
       <c r="B33" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C33">
-        <v>705</v>
+        <v>703</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -10090,7 +10098,7 @@
         <v>21</v>
       </c>
       <c r="B34" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C34">
         <v>9</v>
@@ -10101,7 +10109,7 @@
         <v>21</v>
       </c>
       <c r="B35" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C35">
         <v>22</v>
@@ -10112,10 +10120,10 @@
         <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C36">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -10123,7 +10131,7 @@
         <v>21</v>
       </c>
       <c r="B37" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C37">
         <v>24</v>
@@ -10134,7 +10142,7 @@
         <v>21</v>
       </c>
       <c r="B38" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C38">
         <v>56</v>
@@ -10145,7 +10153,7 @@
         <v>21</v>
       </c>
       <c r="B39" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C39">
         <v>3</v>
@@ -10156,7 +10164,7 @@
         <v>21</v>
       </c>
       <c r="B40" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C40">
         <v>14</v>
@@ -10167,10 +10175,10 @@
         <v>21</v>
       </c>
       <c r="B41" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C41">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -10178,7 +10186,7 @@
         <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C42">
         <v>6</v>
@@ -10207,7 +10215,7 @@
         <v>22</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -10314,7 +10322,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C11" s="9">
         <v>1</v>
@@ -10424,7 +10432,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C21" s="9">
         <v>2</v>
@@ -10534,7 +10542,7 @@
         <v>15</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C31" s="9">
         <v>2</v>

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="229" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2FCA052-7E6B-46AB-9697-B6753863B5EF}"/>
+  <xr:revisionPtr revIDLastSave="239" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9A76B9D-A797-47F3-8765-DB7ED151ABEB}"/>
   <bookViews>
-    <workbookView xWindow="-24120" yWindow="-795" windowWidth="24240" windowHeight="13020" tabRatio="731" firstSheet="1" activeTab="5" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="731" activeTab="1" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="proyeccion_2026" sheetId="2" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1317" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="295">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -352,9 +352,6 @@
     <t>Liceo Bicentenario Cordillera</t>
   </si>
   <si>
-    <t>Colegio Curimón</t>
-  </si>
-  <si>
     <t>Colegio Sunnyland School</t>
   </si>
   <si>
@@ -932,6 +929,9 @@
   </si>
   <si>
     <t>CURSOS</t>
+  </si>
+  <si>
+    <t>EXTRANJERO</t>
   </si>
 </sst>
 </file>
@@ -1840,10 +1840,10 @@
         <v>68</v>
       </c>
       <c r="D17">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E17">
-        <v>1.044</v>
+        <v>1.0289999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -1908,10 +1908,10 @@
         <v>88</v>
       </c>
       <c r="D21">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E21">
-        <v>1</v>
+        <v>1.0109999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -2095,10 +2095,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E32">
-        <v>1.0629999999999999</v>
+        <v>1.0580000000000001</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2112,10 +2112,10 @@
         <v>329</v>
       </c>
       <c r="D33">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E33">
-        <v>1.03</v>
+        <v>1.0269999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2163,10 +2163,10 @@
         <v>250</v>
       </c>
       <c r="D36">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E36">
-        <v>1.02</v>
+        <v>1.028</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2318,7 +2318,7 @@
         <v>34</v>
       </c>
       <c r="C8">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -2329,7 +2329,7 @@
         <v>35</v>
       </c>
       <c r="C9">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2340,7 +2340,7 @@
         <v>35</v>
       </c>
       <c r="C10">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -2351,7 +2351,7 @@
         <v>34</v>
       </c>
       <c r="C11">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
   </sheetData>
@@ -2361,7 +2361,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD19485A-0629-47F9-A5AD-80ABA7A6E076}">
-  <dimension ref="A1:C257"/>
+  <dimension ref="A1:C260"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -2465,7 +2465,7 @@
         <v>46013</v>
       </c>
       <c r="C9" s="9">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -2498,7 +2498,7 @@
         <v>46077</v>
       </c>
       <c r="C12" s="6">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -2773,7 +2773,7 @@
         <v>46099</v>
       </c>
       <c r="C37" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
@@ -3213,7 +3213,7 @@
         <v>46077</v>
       </c>
       <c r="C77" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -3485,7 +3485,7 @@
         <v>14</v>
       </c>
       <c r="B102" s="5">
-        <v>46147</v>
+        <v>46188</v>
       </c>
       <c r="C102" s="6">
         <v>1</v>
@@ -3496,7 +3496,7 @@
         <v>14</v>
       </c>
       <c r="B103" s="8">
-        <v>46134</v>
+        <v>46147</v>
       </c>
       <c r="C103" s="9">
         <v>1</v>
@@ -3507,7 +3507,7 @@
         <v>14</v>
       </c>
       <c r="B104" s="5">
-        <v>46182</v>
+        <v>46134</v>
       </c>
       <c r="C104" s="6">
         <v>1</v>
@@ -3515,13 +3515,13 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B105" s="8">
-        <v>46003</v>
+        <v>46182</v>
       </c>
       <c r="C105" s="9">
-        <v>95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -3529,10 +3529,10 @@
         <v>3</v>
       </c>
       <c r="B106" s="5">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="C106" s="6">
-        <v>115</v>
+        <v>95</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -3540,10 +3540,10 @@
         <v>3</v>
       </c>
       <c r="B107" s="8">
-        <v>46008</v>
+        <v>46002</v>
       </c>
       <c r="C107" s="9">
-        <v>14</v>
+        <v>115</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -3551,10 +3551,10 @@
         <v>3</v>
       </c>
       <c r="B108" s="5">
-        <v>46000</v>
+        <v>46008</v>
       </c>
       <c r="C108" s="6">
-        <v>98</v>
+        <v>14</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -3562,10 +3562,10 @@
         <v>3</v>
       </c>
       <c r="B109" s="8">
-        <v>46007</v>
+        <v>46000</v>
       </c>
       <c r="C109" s="9">
-        <v>40</v>
+        <v>98</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -3573,10 +3573,10 @@
         <v>3</v>
       </c>
       <c r="B110" s="5">
-        <v>46001</v>
+        <v>46007</v>
       </c>
       <c r="C110" s="6">
-        <v>91</v>
+        <v>40</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -3584,10 +3584,10 @@
         <v>3</v>
       </c>
       <c r="B111" s="8">
-        <v>46010</v>
+        <v>46001</v>
       </c>
       <c r="C111" s="9">
-        <v>9</v>
+        <v>91</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -3595,10 +3595,10 @@
         <v>3</v>
       </c>
       <c r="B112" s="5">
-        <v>46006</v>
+        <v>46010</v>
       </c>
       <c r="C112" s="6">
-        <v>84</v>
+        <v>9</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -3606,10 +3606,10 @@
         <v>3</v>
       </c>
       <c r="B113" s="8">
-        <v>46009</v>
+        <v>46006</v>
       </c>
       <c r="C113" s="9">
-        <v>2</v>
+        <v>84</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -3617,10 +3617,10 @@
         <v>3</v>
       </c>
       <c r="B114" s="5">
-        <v>46015</v>
+        <v>46009</v>
       </c>
       <c r="C114" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -3628,10 +3628,10 @@
         <v>3</v>
       </c>
       <c r="B115" s="8">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="C115" s="9">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -3639,10 +3639,10 @@
         <v>3</v>
       </c>
       <c r="B116" s="5">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="C116" s="6">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -3650,7 +3650,7 @@
         <v>3</v>
       </c>
       <c r="B117" s="8">
-        <v>46021</v>
+        <v>46013</v>
       </c>
       <c r="C117" s="9">
         <v>2</v>
@@ -3661,10 +3661,10 @@
         <v>3</v>
       </c>
       <c r="B118" s="5">
-        <v>46077</v>
+        <v>46021</v>
       </c>
       <c r="C118" s="6">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -3672,10 +3672,10 @@
         <v>3</v>
       </c>
       <c r="B119" s="8">
-        <v>46167</v>
+        <v>46077</v>
       </c>
       <c r="C119" s="9">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -3683,10 +3683,10 @@
         <v>3</v>
       </c>
       <c r="B120" s="5">
-        <v>46090</v>
+        <v>46167</v>
       </c>
       <c r="C120" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -3694,10 +3694,10 @@
         <v>3</v>
       </c>
       <c r="B121" s="8">
-        <v>46189</v>
+        <v>46090</v>
       </c>
       <c r="C121" s="9">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -3705,10 +3705,10 @@
         <v>3</v>
       </c>
       <c r="B122" s="5">
-        <v>46170</v>
+        <v>46189</v>
       </c>
       <c r="C122" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -3716,7 +3716,7 @@
         <v>3</v>
       </c>
       <c r="B123" s="8">
-        <v>46093</v>
+        <v>46170</v>
       </c>
       <c r="C123" s="9">
         <v>1</v>
@@ -3727,10 +3727,10 @@
         <v>3</v>
       </c>
       <c r="B124" s="5">
-        <v>46078</v>
+        <v>46093</v>
       </c>
       <c r="C124" s="6">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -3738,7 +3738,7 @@
         <v>3</v>
       </c>
       <c r="B125" s="8">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="C125" s="9">
         <v>7</v>
@@ -3749,10 +3749,10 @@
         <v>3</v>
       </c>
       <c r="B126" s="5">
-        <v>46134</v>
+        <v>46084</v>
       </c>
       <c r="C126" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -3760,10 +3760,10 @@
         <v>3</v>
       </c>
       <c r="B127" s="8">
-        <v>46083</v>
+        <v>46134</v>
       </c>
       <c r="C127" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -3771,10 +3771,10 @@
         <v>3</v>
       </c>
       <c r="B128" s="5">
-        <v>46022</v>
+        <v>46083</v>
       </c>
       <c r="C128" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -3782,10 +3782,10 @@
         <v>3</v>
       </c>
       <c r="B129" s="8">
-        <v>46114</v>
+        <v>46022</v>
       </c>
       <c r="C129" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -3793,10 +3793,10 @@
         <v>3</v>
       </c>
       <c r="B130" s="5">
-        <v>46135</v>
+        <v>46114</v>
       </c>
       <c r="C130" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -3804,10 +3804,10 @@
         <v>3</v>
       </c>
       <c r="B131" s="8">
-        <v>46168</v>
+        <v>46135</v>
       </c>
       <c r="C131" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -3815,7 +3815,7 @@
         <v>3</v>
       </c>
       <c r="B132" s="5">
-        <v>46126</v>
+        <v>46168</v>
       </c>
       <c r="C132" s="6">
         <v>3</v>
@@ -3826,7 +3826,7 @@
         <v>3</v>
       </c>
       <c r="B133" s="8">
-        <v>46120</v>
+        <v>46126</v>
       </c>
       <c r="C133" s="9">
         <v>3</v>
@@ -3837,10 +3837,10 @@
         <v>3</v>
       </c>
       <c r="B134" s="5">
-        <v>46127</v>
+        <v>46120</v>
       </c>
       <c r="C134" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -3848,7 +3848,7 @@
         <v>3</v>
       </c>
       <c r="B135" s="8">
-        <v>46087</v>
+        <v>46127</v>
       </c>
       <c r="C135" s="9">
         <v>1</v>
@@ -3859,7 +3859,7 @@
         <v>3</v>
       </c>
       <c r="B136" s="5">
-        <v>46108</v>
+        <v>46087</v>
       </c>
       <c r="C136" s="6">
         <v>1</v>
@@ -3870,7 +3870,7 @@
         <v>3</v>
       </c>
       <c r="B137" s="8">
-        <v>46020</v>
+        <v>46108</v>
       </c>
       <c r="C137" s="9">
         <v>1</v>
@@ -3881,7 +3881,7 @@
         <v>3</v>
       </c>
       <c r="B138" s="5">
-        <v>46097</v>
+        <v>46020</v>
       </c>
       <c r="C138" s="6">
         <v>1</v>
@@ -3892,7 +3892,7 @@
         <v>3</v>
       </c>
       <c r="B139" s="8">
-        <v>46177</v>
+        <v>46097</v>
       </c>
       <c r="C139" s="9">
         <v>1</v>
@@ -3903,10 +3903,10 @@
         <v>3</v>
       </c>
       <c r="B140" s="5">
-        <v>46161</v>
+        <v>46177</v>
       </c>
       <c r="C140" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -3914,10 +3914,10 @@
         <v>3</v>
       </c>
       <c r="B141" s="8">
-        <v>46129</v>
+        <v>46161</v>
       </c>
       <c r="C141" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -3925,7 +3925,7 @@
         <v>3</v>
       </c>
       <c r="B142" s="5">
-        <v>46080</v>
+        <v>46129</v>
       </c>
       <c r="C142" s="6">
         <v>1</v>
@@ -3936,7 +3936,7 @@
         <v>3</v>
       </c>
       <c r="B143" s="8">
-        <v>46101</v>
+        <v>46080</v>
       </c>
       <c r="C143" s="9">
         <v>1</v>
@@ -3947,7 +3947,7 @@
         <v>3</v>
       </c>
       <c r="B144" s="5">
-        <v>46155</v>
+        <v>46101</v>
       </c>
       <c r="C144" s="6">
         <v>1</v>
@@ -3958,7 +3958,7 @@
         <v>3</v>
       </c>
       <c r="B145" s="8">
-        <v>46150</v>
+        <v>46155</v>
       </c>
       <c r="C145" s="9">
         <v>1</v>
@@ -3969,7 +3969,7 @@
         <v>3</v>
       </c>
       <c r="B146" s="5">
-        <v>46141</v>
+        <v>46150</v>
       </c>
       <c r="C146" s="6">
         <v>1</v>
@@ -3980,7 +3980,7 @@
         <v>3</v>
       </c>
       <c r="B147" s="8">
-        <v>46085</v>
+        <v>46141</v>
       </c>
       <c r="C147" s="9">
         <v>1</v>
@@ -3991,7 +3991,7 @@
         <v>3</v>
       </c>
       <c r="B148" s="5">
-        <v>46148</v>
+        <v>46085</v>
       </c>
       <c r="C148" s="6">
         <v>1</v>
@@ -4002,10 +4002,10 @@
         <v>3</v>
       </c>
       <c r="B149" s="8">
-        <v>46118</v>
+        <v>46148</v>
       </c>
       <c r="C149" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -4013,21 +4013,21 @@
         <v>3</v>
       </c>
       <c r="B150" s="5">
-        <v>46079</v>
+        <v>46118</v>
       </c>
       <c r="C150" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B151" s="8">
-        <v>46003</v>
+        <v>46079</v>
       </c>
       <c r="C151" s="9">
-        <v>92</v>
+        <v>1</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -4035,10 +4035,10 @@
         <v>15</v>
       </c>
       <c r="B152" s="5">
-        <v>46000</v>
+        <v>46003</v>
       </c>
       <c r="C152" s="6">
-        <v>132</v>
+        <v>92</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -4046,10 +4046,10 @@
         <v>15</v>
       </c>
       <c r="B153" s="8">
-        <v>46006</v>
+        <v>46000</v>
       </c>
       <c r="C153" s="9">
-        <v>173</v>
+        <v>132</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -4057,10 +4057,10 @@
         <v>15</v>
       </c>
       <c r="B154" s="5">
-        <v>46001</v>
+        <v>46006</v>
       </c>
       <c r="C154" s="6">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -4068,10 +4068,10 @@
         <v>15</v>
       </c>
       <c r="B155" s="8">
-        <v>46014</v>
+        <v>46001</v>
       </c>
       <c r="C155" s="9">
-        <v>16</v>
+        <v>174</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -4079,10 +4079,10 @@
         <v>15</v>
       </c>
       <c r="B156" s="5">
-        <v>46002</v>
+        <v>46014</v>
       </c>
       <c r="C156" s="6">
-        <v>171</v>
+        <v>16</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -4090,10 +4090,10 @@
         <v>15</v>
       </c>
       <c r="B157" s="8">
-        <v>46009</v>
+        <v>46002</v>
       </c>
       <c r="C157" s="9">
-        <v>19</v>
+        <v>171</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -4101,7 +4101,7 @@
         <v>15</v>
       </c>
       <c r="B158" s="5">
-        <v>46010</v>
+        <v>46009</v>
       </c>
       <c r="C158" s="6">
         <v>19</v>
@@ -4112,10 +4112,10 @@
         <v>15</v>
       </c>
       <c r="B159" s="8">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="C159" s="9">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -4123,10 +4123,10 @@
         <v>15</v>
       </c>
       <c r="B160" s="5">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="C160" s="6">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -4134,10 +4134,10 @@
         <v>15</v>
       </c>
       <c r="B161" s="8">
-        <v>46013</v>
+        <v>46007</v>
       </c>
       <c r="C161" s="9">
-        <v>12</v>
+        <v>43</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -4145,10 +4145,10 @@
         <v>15</v>
       </c>
       <c r="B162" s="5">
-        <v>46080</v>
+        <v>46013</v>
       </c>
       <c r="C162" s="6">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -4156,10 +4156,10 @@
         <v>15</v>
       </c>
       <c r="B163" s="8">
-        <v>46090</v>
+        <v>46080</v>
       </c>
       <c r="C163" s="9">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -4167,10 +4167,10 @@
         <v>15</v>
       </c>
       <c r="B164" s="5">
-        <v>46079</v>
+        <v>46090</v>
       </c>
       <c r="C164" s="6">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -4178,10 +4178,10 @@
         <v>15</v>
       </c>
       <c r="B165" s="8">
-        <v>46015</v>
+        <v>46079</v>
       </c>
       <c r="C165" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -4189,10 +4189,10 @@
         <v>15</v>
       </c>
       <c r="B166" s="5">
-        <v>46085</v>
+        <v>46015</v>
       </c>
       <c r="C166" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -4200,10 +4200,10 @@
         <v>15</v>
       </c>
       <c r="B167" s="8">
-        <v>46098</v>
+        <v>46085</v>
       </c>
       <c r="C167" s="9">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -4211,10 +4211,10 @@
         <v>15</v>
       </c>
       <c r="B168" s="5">
-        <v>46021</v>
+        <v>46098</v>
       </c>
       <c r="C168" s="6">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -4222,10 +4222,10 @@
         <v>15</v>
       </c>
       <c r="B169" s="8">
-        <v>46078</v>
+        <v>46021</v>
       </c>
       <c r="C169" s="9">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -4233,10 +4233,10 @@
         <v>15</v>
       </c>
       <c r="B170" s="5">
-        <v>46084</v>
+        <v>46078</v>
       </c>
       <c r="C170" s="6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -4244,10 +4244,10 @@
         <v>15</v>
       </c>
       <c r="B171" s="8">
-        <v>46128</v>
+        <v>46084</v>
       </c>
       <c r="C171" s="9">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -4255,10 +4255,10 @@
         <v>15</v>
       </c>
       <c r="B172" s="5">
-        <v>46083</v>
+        <v>46128</v>
       </c>
       <c r="C172" s="6">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -4266,10 +4266,10 @@
         <v>15</v>
       </c>
       <c r="B173" s="8">
-        <v>46076</v>
+        <v>46083</v>
       </c>
       <c r="C173" s="9">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -4277,10 +4277,10 @@
         <v>15</v>
       </c>
       <c r="B174" s="5">
-        <v>46099</v>
+        <v>46076</v>
       </c>
       <c r="C174" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -4288,10 +4288,10 @@
         <v>15</v>
       </c>
       <c r="B175" s="8">
-        <v>46154</v>
+        <v>46099</v>
       </c>
       <c r="C175" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -4299,7 +4299,7 @@
         <v>15</v>
       </c>
       <c r="B176" s="5">
-        <v>46092</v>
+        <v>46154</v>
       </c>
       <c r="C176" s="6">
         <v>1</v>
@@ -4310,7 +4310,7 @@
         <v>15</v>
       </c>
       <c r="B177" s="8">
-        <v>46022</v>
+        <v>46092</v>
       </c>
       <c r="C177" s="9">
         <v>1</v>
@@ -4321,10 +4321,10 @@
         <v>15</v>
       </c>
       <c r="B178" s="5">
-        <v>46031</v>
+        <v>46022</v>
       </c>
       <c r="C178" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -4332,7 +4332,7 @@
         <v>15</v>
       </c>
       <c r="B179" s="8">
-        <v>46120</v>
+        <v>46031</v>
       </c>
       <c r="C179" s="9">
         <v>2</v>
@@ -4343,10 +4343,10 @@
         <v>15</v>
       </c>
       <c r="B180" s="5">
-        <v>46077</v>
+        <v>46120</v>
       </c>
       <c r="C180" s="6">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -4354,10 +4354,10 @@
         <v>15</v>
       </c>
       <c r="B181" s="8">
-        <v>46114</v>
+        <v>46077</v>
       </c>
       <c r="C181" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -4365,7 +4365,7 @@
         <v>15</v>
       </c>
       <c r="B182" s="5">
-        <v>46037</v>
+        <v>46114</v>
       </c>
       <c r="C182" s="6">
         <v>1</v>
@@ -4376,10 +4376,10 @@
         <v>15</v>
       </c>
       <c r="B183" s="8">
-        <v>46020</v>
+        <v>46037</v>
       </c>
       <c r="C183" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -4387,10 +4387,10 @@
         <v>15</v>
       </c>
       <c r="B184" s="5">
-        <v>46106</v>
+        <v>46020</v>
       </c>
       <c r="C184" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -4398,7 +4398,7 @@
         <v>15</v>
       </c>
       <c r="B185" s="8">
-        <v>46155</v>
+        <v>46106</v>
       </c>
       <c r="C185" s="9">
         <v>1</v>
@@ -4409,7 +4409,7 @@
         <v>15</v>
       </c>
       <c r="B186" s="5">
-        <v>46112</v>
+        <v>46155</v>
       </c>
       <c r="C186" s="6">
         <v>1</v>
@@ -4420,7 +4420,7 @@
         <v>15</v>
       </c>
       <c r="B187" s="8">
-        <v>46132</v>
+        <v>46112</v>
       </c>
       <c r="C187" s="9">
         <v>1</v>
@@ -4431,7 +4431,7 @@
         <v>15</v>
       </c>
       <c r="B188" s="5">
-        <v>46108</v>
+        <v>46132</v>
       </c>
       <c r="C188" s="6">
         <v>1</v>
@@ -4442,7 +4442,7 @@
         <v>15</v>
       </c>
       <c r="B189" s="8">
-        <v>46148</v>
+        <v>46108</v>
       </c>
       <c r="C189" s="9">
         <v>1</v>
@@ -4453,7 +4453,7 @@
         <v>15</v>
       </c>
       <c r="B190" s="5">
-        <v>46118</v>
+        <v>46148</v>
       </c>
       <c r="C190" s="6">
         <v>1</v>
@@ -4464,7 +4464,7 @@
         <v>15</v>
       </c>
       <c r="B191" s="8">
-        <v>46035</v>
+        <v>46118</v>
       </c>
       <c r="C191" s="9">
         <v>1</v>
@@ -4475,7 +4475,7 @@
         <v>15</v>
       </c>
       <c r="B192" s="5">
-        <v>46181</v>
+        <v>46035</v>
       </c>
       <c r="C192" s="6">
         <v>1</v>
@@ -4486,7 +4486,7 @@
         <v>15</v>
       </c>
       <c r="B193" s="8">
-        <v>46093</v>
+        <v>46181</v>
       </c>
       <c r="C193" s="9">
         <v>1</v>
@@ -4497,7 +4497,7 @@
         <v>15</v>
       </c>
       <c r="B194" s="5">
-        <v>46087</v>
+        <v>46093</v>
       </c>
       <c r="C194" s="6">
         <v>1</v>
@@ -4508,10 +4508,10 @@
         <v>15</v>
       </c>
       <c r="B195" s="8">
-        <v>46030</v>
+        <v>46087</v>
       </c>
       <c r="C195" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -4519,10 +4519,10 @@
         <v>15</v>
       </c>
       <c r="B196" s="5">
-        <v>46176</v>
+        <v>46030</v>
       </c>
       <c r="C196" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -4530,7 +4530,7 @@
         <v>15</v>
       </c>
       <c r="B197" s="8">
-        <v>46101</v>
+        <v>46176</v>
       </c>
       <c r="C197" s="9">
         <v>1</v>
@@ -4541,7 +4541,7 @@
         <v>15</v>
       </c>
       <c r="B198" s="5">
-        <v>46142</v>
+        <v>46101</v>
       </c>
       <c r="C198" s="6">
         <v>1</v>
@@ -4549,13 +4549,13 @@
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B199" s="8">
-        <v>46001</v>
+        <v>46142</v>
       </c>
       <c r="C199" s="9">
-        <v>153</v>
+        <v>1</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -4563,10 +4563,10 @@
         <v>21</v>
       </c>
       <c r="B200" s="5">
-        <v>46008</v>
+        <v>46001</v>
       </c>
       <c r="C200" s="6">
-        <v>38</v>
+        <v>153</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
@@ -4574,10 +4574,10 @@
         <v>21</v>
       </c>
       <c r="B201" s="8">
-        <v>46003</v>
+        <v>46008</v>
       </c>
       <c r="C201" s="9">
-        <v>70</v>
+        <v>38</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -4585,10 +4585,10 @@
         <v>21</v>
       </c>
       <c r="B202" s="5">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="C202" s="6">
-        <v>111</v>
+        <v>70</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -4596,10 +4596,10 @@
         <v>21</v>
       </c>
       <c r="B203" s="8">
-        <v>46006</v>
+        <v>46002</v>
       </c>
       <c r="C203" s="9">
-        <v>146</v>
+        <v>111</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -4607,10 +4607,10 @@
         <v>21</v>
       </c>
       <c r="B204" s="5">
-        <v>46007</v>
+        <v>46006</v>
       </c>
       <c r="C204" s="6">
-        <v>45</v>
+        <v>146</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -4618,10 +4618,10 @@
         <v>21</v>
       </c>
       <c r="B205" s="8">
-        <v>46000</v>
+        <v>46007</v>
       </c>
       <c r="C205" s="9">
-        <v>127</v>
+        <v>45</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -4629,10 +4629,10 @@
         <v>21</v>
       </c>
       <c r="B206" s="5">
-        <v>46084</v>
+        <v>46000</v>
       </c>
       <c r="C206" s="6">
-        <v>10</v>
+        <v>127</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -4640,10 +4640,10 @@
         <v>21</v>
       </c>
       <c r="B207" s="8">
-        <v>46013</v>
+        <v>46084</v>
       </c>
       <c r="C207" s="9">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4651,10 +4651,10 @@
         <v>21</v>
       </c>
       <c r="B208" s="5">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="C208" s="6">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4662,10 +4662,10 @@
         <v>21</v>
       </c>
       <c r="B209" s="8">
-        <v>46021</v>
+        <v>46010</v>
       </c>
       <c r="C209" s="9">
-        <v>6</v>
+        <v>19</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4673,10 +4673,10 @@
         <v>21</v>
       </c>
       <c r="B210" s="5">
-        <v>46009</v>
+        <v>46021</v>
       </c>
       <c r="C210" s="6">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -4684,10 +4684,10 @@
         <v>21</v>
       </c>
       <c r="B211" s="8">
-        <v>46083</v>
+        <v>46009</v>
       </c>
       <c r="C211" s="9">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -4695,10 +4695,10 @@
         <v>21</v>
       </c>
       <c r="B212" s="5">
-        <v>46014</v>
+        <v>46083</v>
       </c>
       <c r="C212" s="6">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4706,10 +4706,10 @@
         <v>21</v>
       </c>
       <c r="B213" s="8">
-        <v>46157</v>
+        <v>46014</v>
       </c>
       <c r="C213" s="9">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4717,10 +4717,10 @@
         <v>21</v>
       </c>
       <c r="B214" s="5">
-        <v>46079</v>
+        <v>46157</v>
       </c>
       <c r="C214" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4728,10 +4728,10 @@
         <v>21</v>
       </c>
       <c r="B215" s="8">
-        <v>46167</v>
+        <v>46079</v>
       </c>
       <c r="C215" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4739,10 +4739,10 @@
         <v>21</v>
       </c>
       <c r="B216" s="5">
-        <v>46035</v>
+        <v>46167</v>
       </c>
       <c r="C216" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4750,10 +4750,10 @@
         <v>21</v>
       </c>
       <c r="B217" s="8">
-        <v>46085</v>
+        <v>46035</v>
       </c>
       <c r="C217" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -4761,10 +4761,10 @@
         <v>21</v>
       </c>
       <c r="B218" s="5">
-        <v>46120</v>
+        <v>46085</v>
       </c>
       <c r="C218" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -4772,10 +4772,10 @@
         <v>21</v>
       </c>
       <c r="B219" s="8">
-        <v>46114</v>
+        <v>46120</v>
       </c>
       <c r="C219" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4783,10 +4783,10 @@
         <v>21</v>
       </c>
       <c r="B220" s="5">
-        <v>46094</v>
+        <v>46114</v>
       </c>
       <c r="C220" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -4794,10 +4794,10 @@
         <v>21</v>
       </c>
       <c r="B221" s="8">
-        <v>46080</v>
+        <v>46094</v>
       </c>
       <c r="C221" s="9">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -4805,10 +4805,10 @@
         <v>21</v>
       </c>
       <c r="B222" s="5">
-        <v>46127</v>
+        <v>46080</v>
       </c>
       <c r="C222" s="6">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -4816,7 +4816,7 @@
         <v>21</v>
       </c>
       <c r="B223" s="8">
-        <v>46091</v>
+        <v>46127</v>
       </c>
       <c r="C223" s="9">
         <v>2</v>
@@ -4827,10 +4827,10 @@
         <v>21</v>
       </c>
       <c r="B224" s="5">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="C224" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -4838,10 +4838,10 @@
         <v>21</v>
       </c>
       <c r="B225" s="8">
-        <v>46020</v>
+        <v>46090</v>
       </c>
       <c r="C225" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -4849,10 +4849,10 @@
         <v>21</v>
       </c>
       <c r="B226" s="5">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="C226" s="6">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -4860,10 +4860,10 @@
         <v>21</v>
       </c>
       <c r="B227" s="8">
-        <v>46078</v>
+        <v>46015</v>
       </c>
       <c r="C227" s="9">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -4871,10 +4871,10 @@
         <v>21</v>
       </c>
       <c r="B228" s="5">
-        <v>46148</v>
+        <v>46078</v>
       </c>
       <c r="C228" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -4882,7 +4882,7 @@
         <v>21</v>
       </c>
       <c r="B229" s="8">
-        <v>46105</v>
+        <v>46148</v>
       </c>
       <c r="C229" s="9">
         <v>2</v>
@@ -4893,10 +4893,10 @@
         <v>21</v>
       </c>
       <c r="B230" s="5">
-        <v>46087</v>
+        <v>46105</v>
       </c>
       <c r="C230" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -4904,7 +4904,7 @@
         <v>21</v>
       </c>
       <c r="B231" s="8">
-        <v>46107</v>
+        <v>46087</v>
       </c>
       <c r="C231" s="9">
         <v>3</v>
@@ -4915,10 +4915,10 @@
         <v>21</v>
       </c>
       <c r="B232" s="5">
-        <v>46086</v>
+        <v>46107</v>
       </c>
       <c r="C232" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -4926,10 +4926,10 @@
         <v>21</v>
       </c>
       <c r="B233" s="8">
-        <v>46106</v>
+        <v>46086</v>
       </c>
       <c r="C233" s="9">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -4937,10 +4937,10 @@
         <v>21</v>
       </c>
       <c r="B234" s="5">
-        <v>46150</v>
+        <v>46106</v>
       </c>
       <c r="C234" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -4948,7 +4948,7 @@
         <v>21</v>
       </c>
       <c r="B235" s="8">
-        <v>46104</v>
+        <v>46150</v>
       </c>
       <c r="C235" s="9">
         <v>3</v>
@@ -4959,10 +4959,10 @@
         <v>21</v>
       </c>
       <c r="B236" s="5">
-        <v>46118</v>
+        <v>46104</v>
       </c>
       <c r="C236" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -4970,10 +4970,10 @@
         <v>21</v>
       </c>
       <c r="B237" s="8">
-        <v>46076</v>
+        <v>46118</v>
       </c>
       <c r="C237" s="9">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -4981,10 +4981,10 @@
         <v>21</v>
       </c>
       <c r="B238" s="5">
-        <v>46182</v>
+        <v>46076</v>
       </c>
       <c r="C238" s="6">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -4992,10 +4992,10 @@
         <v>21</v>
       </c>
       <c r="B239" s="8">
-        <v>46077</v>
+        <v>46182</v>
       </c>
       <c r="C239" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -5003,7 +5003,7 @@
         <v>21</v>
       </c>
       <c r="B240" s="5">
-        <v>46154</v>
+        <v>46188</v>
       </c>
       <c r="C240" s="6">
         <v>1</v>
@@ -5014,10 +5014,10 @@
         <v>21</v>
       </c>
       <c r="B241" s="8">
-        <v>46093</v>
+        <v>46077</v>
       </c>
       <c r="C241" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -5025,7 +5025,7 @@
         <v>21</v>
       </c>
       <c r="B242" s="5">
-        <v>46122</v>
+        <v>46154</v>
       </c>
       <c r="C242" s="6">
         <v>1</v>
@@ -5036,7 +5036,7 @@
         <v>21</v>
       </c>
       <c r="B243" s="8">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="C243" s="9">
         <v>3</v>
@@ -5047,10 +5047,10 @@
         <v>21</v>
       </c>
       <c r="B244" s="5">
-        <v>46156</v>
+        <v>46122</v>
       </c>
       <c r="C244" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -5058,10 +5058,10 @@
         <v>21</v>
       </c>
       <c r="B245" s="8">
-        <v>46133</v>
+        <v>46092</v>
       </c>
       <c r="C245" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
@@ -5069,10 +5069,10 @@
         <v>21</v>
       </c>
       <c r="B246" s="5">
-        <v>46126</v>
+        <v>46156</v>
       </c>
       <c r="C246" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -5080,10 +5080,10 @@
         <v>21</v>
       </c>
       <c r="B247" s="8">
-        <v>46022</v>
+        <v>46133</v>
       </c>
       <c r="C247" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
@@ -5091,10 +5091,10 @@
         <v>21</v>
       </c>
       <c r="B248" s="5">
-        <v>46100</v>
+        <v>46189</v>
       </c>
       <c r="C248" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -5102,7 +5102,7 @@
         <v>21</v>
       </c>
       <c r="B249" s="8">
-        <v>46101</v>
+        <v>46126</v>
       </c>
       <c r="C249" s="9">
         <v>1</v>
@@ -5113,10 +5113,10 @@
         <v>21</v>
       </c>
       <c r="B250" s="5">
-        <v>46097</v>
+        <v>46022</v>
       </c>
       <c r="C250" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -5124,10 +5124,10 @@
         <v>21</v>
       </c>
       <c r="B251" s="8">
-        <v>46108</v>
+        <v>46100</v>
       </c>
       <c r="C251" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -5135,10 +5135,10 @@
         <v>21</v>
       </c>
       <c r="B252" s="5">
-        <v>46098</v>
+        <v>46101</v>
       </c>
       <c r="C252" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
@@ -5146,10 +5146,10 @@
         <v>21</v>
       </c>
       <c r="B253" s="8">
-        <v>46113</v>
+        <v>46097</v>
       </c>
       <c r="C253" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
@@ -5157,7 +5157,7 @@
         <v>21</v>
       </c>
       <c r="B254" s="5">
-        <v>46142</v>
+        <v>46108</v>
       </c>
       <c r="C254" s="6">
         <v>1</v>
@@ -5168,10 +5168,10 @@
         <v>21</v>
       </c>
       <c r="B255" s="8">
-        <v>46153</v>
+        <v>46098</v>
       </c>
       <c r="C255" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
@@ -5179,7 +5179,7 @@
         <v>21</v>
       </c>
       <c r="B256" s="5">
-        <v>46031</v>
+        <v>46113</v>
       </c>
       <c r="C256" s="6">
         <v>1</v>
@@ -5190,9 +5190,42 @@
         <v>21</v>
       </c>
       <c r="B257" s="8">
+        <v>46142</v>
+      </c>
+      <c r="C257" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B258" s="5">
+        <v>46153</v>
+      </c>
+      <c r="C258" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B259" s="8">
+        <v>46031</v>
+      </c>
+      <c r="C259" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B260" s="5">
         <v>46155</v>
       </c>
-      <c r="C257" s="9">
+      <c r="C260" s="6">
         <v>1</v>
       </c>
     </row>
@@ -5497,7 +5530,7 @@
         <v>3</v>
       </c>
       <c r="E17">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -5559,13 +5592,13 @@
         <v>7</v>
       </c>
       <c r="C21">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D21">
         <v>6</v>
       </c>
       <c r="E21">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -5752,7 +5785,7 @@
         <v>245</v>
       </c>
       <c r="E32">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -5769,7 +5802,7 @@
         <v>8</v>
       </c>
       <c r="E33">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -5820,7 +5853,7 @@
         <v>86</v>
       </c>
       <c r="E36">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -5881,7 +5914,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0916EAC6-1E7F-4924-9D0E-33749FD3E143}">
-  <dimension ref="A1:C348"/>
+  <dimension ref="A1:C349"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
@@ -5894,7 +5927,7 @@
         <v>37</v>
       </c>
       <c r="B1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C1" t="s">
         <v>36</v>
@@ -6257,7 +6290,7 @@
         <v>3</v>
       </c>
       <c r="B34" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -6323,10 +6356,10 @@
         <v>14</v>
       </c>
       <c r="B40" t="s">
-        <v>43</v>
+        <v>294</v>
       </c>
       <c r="C40">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -6334,10 +6367,10 @@
         <v>14</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="C41">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -6345,7 +6378,7 @@
         <v>14</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="C42">
         <v>5</v>
@@ -6356,7 +6389,7 @@
         <v>14</v>
       </c>
       <c r="B43" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C43">
         <v>5</v>
@@ -6378,10 +6411,10 @@
         <v>14</v>
       </c>
       <c r="B45" t="s">
-        <v>81</v>
+        <v>53</v>
       </c>
       <c r="C45">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
@@ -6400,10 +6433,10 @@
         <v>14</v>
       </c>
       <c r="B47" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="C47">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -6411,7 +6444,7 @@
         <v>14</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="C48">
         <v>3</v>
@@ -6422,7 +6455,7 @@
         <v>14</v>
       </c>
       <c r="B49" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="C49">
         <v>3</v>
@@ -6433,10 +6466,10 @@
         <v>14</v>
       </c>
       <c r="B50" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="C50">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -6444,7 +6477,7 @@
         <v>14</v>
       </c>
       <c r="B51" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="C51">
         <v>2</v>
@@ -6455,7 +6488,7 @@
         <v>14</v>
       </c>
       <c r="B52" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="C52">
         <v>2</v>
@@ -6466,7 +6499,7 @@
         <v>14</v>
       </c>
       <c r="B53" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="C53">
         <v>2</v>
@@ -6477,7 +6510,7 @@
         <v>14</v>
       </c>
       <c r="B54" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="C54">
         <v>2</v>
@@ -6499,7 +6532,7 @@
         <v>14</v>
       </c>
       <c r="B56" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="C56">
         <v>2</v>
@@ -6510,7 +6543,7 @@
         <v>14</v>
       </c>
       <c r="B57" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C57">
         <v>2</v>
@@ -6521,7 +6554,7 @@
         <v>14</v>
       </c>
       <c r="B58" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="C58">
         <v>2</v>
@@ -6532,7 +6565,7 @@
         <v>14</v>
       </c>
       <c r="B59" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C59">
         <v>2</v>
@@ -6543,7 +6576,7 @@
         <v>14</v>
       </c>
       <c r="B60" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="C60">
         <v>2</v>
@@ -6554,7 +6587,7 @@
         <v>14</v>
       </c>
       <c r="B61" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="C61">
         <v>2</v>
@@ -6565,7 +6598,7 @@
         <v>14</v>
       </c>
       <c r="B62" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="C62">
         <v>2</v>
@@ -6576,10 +6609,10 @@
         <v>14</v>
       </c>
       <c r="B63" t="s">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="C63">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
@@ -6587,7 +6620,7 @@
         <v>14</v>
       </c>
       <c r="B64" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -6598,7 +6631,7 @@
         <v>14</v>
       </c>
       <c r="B65" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="C65">
         <v>1</v>
@@ -6609,7 +6642,7 @@
         <v>14</v>
       </c>
       <c r="B66" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -6620,7 +6653,7 @@
         <v>14</v>
       </c>
       <c r="B67" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -6631,7 +6664,7 @@
         <v>14</v>
       </c>
       <c r="B68" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="C68">
         <v>1</v>
@@ -6642,7 +6675,7 @@
         <v>14</v>
       </c>
       <c r="B69" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="C69">
         <v>1</v>
@@ -6653,7 +6686,7 @@
         <v>14</v>
       </c>
       <c r="B70" t="s">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="C70">
         <v>1</v>
@@ -6664,7 +6697,7 @@
         <v>14</v>
       </c>
       <c r="B71" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -6675,7 +6708,7 @@
         <v>14</v>
       </c>
       <c r="B72" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C72">
         <v>1</v>
@@ -6686,7 +6719,7 @@
         <v>14</v>
       </c>
       <c r="B73" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -6697,7 +6730,7 @@
         <v>14</v>
       </c>
       <c r="B74" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C74">
         <v>1</v>
@@ -6708,7 +6741,7 @@
         <v>14</v>
       </c>
       <c r="B75" t="s">
-        <v>111</v>
+        <v>66</v>
       </c>
       <c r="C75">
         <v>1</v>
@@ -6719,7 +6752,7 @@
         <v>14</v>
       </c>
       <c r="B76" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="C76">
         <v>1</v>
@@ -6730,7 +6763,7 @@
         <v>14</v>
       </c>
       <c r="B77" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="C77">
         <v>1</v>
@@ -6741,7 +6774,7 @@
         <v>14</v>
       </c>
       <c r="B78" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="C78">
         <v>1</v>
@@ -6752,7 +6785,7 @@
         <v>14</v>
       </c>
       <c r="B79" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="C79">
         <v>1</v>
@@ -6763,7 +6796,7 @@
         <v>14</v>
       </c>
       <c r="B80" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="C80">
         <v>1</v>
@@ -6774,7 +6807,7 @@
         <v>14</v>
       </c>
       <c r="B81" t="s">
-        <v>95</v>
+        <v>57</v>
       </c>
       <c r="C81">
         <v>1</v>
@@ -6785,7 +6818,7 @@
         <v>14</v>
       </c>
       <c r="B82" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C82">
         <v>1</v>
@@ -6796,7 +6829,7 @@
         <v>14</v>
       </c>
       <c r="B83" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -6807,7 +6840,7 @@
         <v>14</v>
       </c>
       <c r="B84" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C84">
         <v>1</v>
@@ -6818,7 +6851,7 @@
         <v>14</v>
       </c>
       <c r="B85" t="s">
-        <v>51</v>
+        <v>107</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -6829,7 +6862,7 @@
         <v>14</v>
       </c>
       <c r="B86" t="s">
-        <v>102</v>
+        <v>191</v>
       </c>
       <c r="C86">
         <v>1</v>
@@ -6840,7 +6873,7 @@
         <v>14</v>
       </c>
       <c r="B87" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C87">
         <v>1</v>
@@ -6851,7 +6884,7 @@
         <v>14</v>
       </c>
       <c r="B88" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -6862,7 +6895,7 @@
         <v>14</v>
       </c>
       <c r="B89" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -6873,7 +6906,7 @@
         <v>14</v>
       </c>
       <c r="B90" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="C90">
         <v>1</v>
@@ -6884,7 +6917,7 @@
         <v>14</v>
       </c>
       <c r="B91" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="C91">
         <v>1</v>
@@ -6895,7 +6928,7 @@
         <v>14</v>
       </c>
       <c r="B92" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="C92">
         <v>1</v>
@@ -6906,7 +6939,7 @@
         <v>14</v>
       </c>
       <c r="B93" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="C93">
         <v>1</v>
@@ -6917,7 +6950,7 @@
         <v>14</v>
       </c>
       <c r="B94" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="C94">
         <v>1</v>
@@ -6939,7 +6972,7 @@
         <v>14</v>
       </c>
       <c r="B96" t="s">
-        <v>116</v>
+        <v>93</v>
       </c>
       <c r="C96">
         <v>1</v>
@@ -6950,7 +6983,7 @@
         <v>14</v>
       </c>
       <c r="B97" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="C97">
         <v>1</v>
@@ -6961,7 +6994,7 @@
         <v>14</v>
       </c>
       <c r="B98" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -6969,13 +7002,13 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B99" t="s">
-        <v>118</v>
+        <v>59</v>
       </c>
       <c r="C99">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -6983,7 +7016,7 @@
         <v>15</v>
       </c>
       <c r="B100" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C100">
         <v>14</v>
@@ -6994,10 +7027,10 @@
         <v>15</v>
       </c>
       <c r="B101" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C101">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -7005,10 +7038,10 @@
         <v>15</v>
       </c>
       <c r="B102" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C102">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -7016,10 +7049,10 @@
         <v>15</v>
       </c>
       <c r="B103" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C103">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -7027,7 +7060,7 @@
         <v>15</v>
       </c>
       <c r="B104" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="C104">
         <v>6</v>
@@ -7038,7 +7071,7 @@
         <v>15</v>
       </c>
       <c r="B105" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="C105">
         <v>6</v>
@@ -7049,10 +7082,10 @@
         <v>15</v>
       </c>
       <c r="B106" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C106">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -7060,7 +7093,7 @@
         <v>15</v>
       </c>
       <c r="B107" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C107">
         <v>4</v>
@@ -7071,7 +7104,7 @@
         <v>15</v>
       </c>
       <c r="B108" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C108">
         <v>4</v>
@@ -7082,7 +7115,7 @@
         <v>15</v>
       </c>
       <c r="B109" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="C109">
         <v>4</v>
@@ -7093,7 +7126,7 @@
         <v>15</v>
       </c>
       <c r="B110" t="s">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c r="C110">
         <v>4</v>
@@ -7104,10 +7137,10 @@
         <v>15</v>
       </c>
       <c r="B111" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C111">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -7115,7 +7148,7 @@
         <v>15</v>
       </c>
       <c r="B112" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="C112">
         <v>3</v>
@@ -7126,7 +7159,7 @@
         <v>15</v>
       </c>
       <c r="B113" t="s">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="C113">
         <v>3</v>
@@ -7137,7 +7170,7 @@
         <v>15</v>
       </c>
       <c r="B114" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C114">
         <v>3</v>
@@ -7148,7 +7181,7 @@
         <v>15</v>
       </c>
       <c r="B115" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C115">
         <v>3</v>
@@ -7159,7 +7192,7 @@
         <v>15</v>
       </c>
       <c r="B116" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C116">
         <v>3</v>
@@ -7170,10 +7203,10 @@
         <v>15</v>
       </c>
       <c r="B117" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="C117">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -7181,7 +7214,7 @@
         <v>15</v>
       </c>
       <c r="B118" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C118">
         <v>2</v>
@@ -7192,7 +7225,7 @@
         <v>15</v>
       </c>
       <c r="B119" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C119">
         <v>2</v>
@@ -7203,7 +7236,7 @@
         <v>15</v>
       </c>
       <c r="B120" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C120">
         <v>2</v>
@@ -7214,7 +7247,7 @@
         <v>15</v>
       </c>
       <c r="B121" t="s">
-        <v>62</v>
+        <v>135</v>
       </c>
       <c r="C121">
         <v>2</v>
@@ -7225,7 +7258,7 @@
         <v>15</v>
       </c>
       <c r="B122" t="s">
-        <v>138</v>
+        <v>62</v>
       </c>
       <c r="C122">
         <v>2</v>
@@ -7236,7 +7269,7 @@
         <v>15</v>
       </c>
       <c r="B123" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C123">
         <v>2</v>
@@ -7247,7 +7280,7 @@
         <v>15</v>
       </c>
       <c r="B124" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C124">
         <v>2</v>
@@ -7258,7 +7291,7 @@
         <v>15</v>
       </c>
       <c r="B125" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C125">
         <v>2</v>
@@ -7269,7 +7302,7 @@
         <v>15</v>
       </c>
       <c r="B126" t="s">
-        <v>49</v>
+        <v>134</v>
       </c>
       <c r="C126">
         <v>2</v>
@@ -7280,10 +7313,10 @@
         <v>15</v>
       </c>
       <c r="B127" t="s">
-        <v>168</v>
+        <v>49</v>
       </c>
       <c r="C127">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -7291,7 +7324,7 @@
         <v>15</v>
       </c>
       <c r="B128" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="C128">
         <v>1</v>
@@ -7302,7 +7335,7 @@
         <v>15</v>
       </c>
       <c r="B129" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="C129">
         <v>1</v>
@@ -7313,7 +7346,7 @@
         <v>15</v>
       </c>
       <c r="B130" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="C130">
         <v>1</v>
@@ -7324,7 +7357,7 @@
         <v>15</v>
       </c>
       <c r="B131" t="s">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="C131">
         <v>1</v>
@@ -7335,7 +7368,7 @@
         <v>15</v>
       </c>
       <c r="B132" t="s">
-        <v>145</v>
+        <v>82</v>
       </c>
       <c r="C132">
         <v>1</v>
@@ -7346,7 +7379,7 @@
         <v>15</v>
       </c>
       <c r="B133" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
       <c r="C133">
         <v>1</v>
@@ -7357,7 +7390,7 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>187</v>
+        <v>155</v>
       </c>
       <c r="C134">
         <v>1</v>
@@ -7368,7 +7401,7 @@
         <v>15</v>
       </c>
       <c r="B135" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="C135">
         <v>1</v>
@@ -7379,7 +7412,7 @@
         <v>15</v>
       </c>
       <c r="B136" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="C136">
         <v>1</v>
@@ -7390,7 +7423,7 @@
         <v>15</v>
       </c>
       <c r="B137" t="s">
-        <v>185</v>
+        <v>163</v>
       </c>
       <c r="C137">
         <v>1</v>
@@ -7401,7 +7434,7 @@
         <v>15</v>
       </c>
       <c r="B138" t="s">
-        <v>149</v>
+        <v>184</v>
       </c>
       <c r="C138">
         <v>1</v>
@@ -7412,7 +7445,7 @@
         <v>15</v>
       </c>
       <c r="B139" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="C139">
         <v>1</v>
@@ -7423,7 +7456,7 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="C140">
         <v>1</v>
@@ -7434,7 +7467,7 @@
         <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="C141">
         <v>1</v>
@@ -7445,7 +7478,7 @@
         <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="C142">
         <v>1</v>
@@ -7456,7 +7489,7 @@
         <v>15</v>
       </c>
       <c r="B143" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="C143">
         <v>1</v>
@@ -7467,7 +7500,7 @@
         <v>15</v>
       </c>
       <c r="B144" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C144">
         <v>1</v>
@@ -7478,7 +7511,7 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C145">
         <v>1</v>
@@ -7489,7 +7522,7 @@
         <v>15</v>
       </c>
       <c r="B146" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="C146">
         <v>1</v>
@@ -7500,7 +7533,7 @@
         <v>15</v>
       </c>
       <c r="B147" t="s">
-        <v>180</v>
+        <v>157</v>
       </c>
       <c r="C147">
         <v>1</v>
@@ -7511,7 +7544,7 @@
         <v>15</v>
       </c>
       <c r="B148" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="C148">
         <v>1</v>
@@ -7522,7 +7555,7 @@
         <v>15</v>
       </c>
       <c r="B149" t="s">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="C149">
         <v>1</v>
@@ -7555,7 +7588,7 @@
         <v>15</v>
       </c>
       <c r="B152" t="s">
-        <v>147</v>
+        <v>181</v>
       </c>
       <c r="C152">
         <v>1</v>
@@ -7577,7 +7610,7 @@
         <v>15</v>
       </c>
       <c r="B154" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="C154">
         <v>1</v>
@@ -7588,7 +7621,7 @@
         <v>15</v>
       </c>
       <c r="B155" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="C155">
         <v>1</v>
@@ -7599,7 +7632,7 @@
         <v>15</v>
       </c>
       <c r="B156" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="C156">
         <v>1</v>
@@ -7610,7 +7643,7 @@
         <v>15</v>
       </c>
       <c r="B157" t="s">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="C157">
         <v>1</v>
@@ -7621,7 +7654,7 @@
         <v>15</v>
       </c>
       <c r="B158" t="s">
-        <v>169</v>
+        <v>141</v>
       </c>
       <c r="C158">
         <v>1</v>
@@ -7632,7 +7665,7 @@
         <v>15</v>
       </c>
       <c r="B159" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="C159">
         <v>1</v>
@@ -7643,7 +7676,7 @@
         <v>15</v>
       </c>
       <c r="B160" t="s">
-        <v>96</v>
+        <v>154</v>
       </c>
       <c r="C160">
         <v>1</v>
@@ -7654,7 +7687,7 @@
         <v>15</v>
       </c>
       <c r="B161" t="s">
-        <v>163</v>
+        <v>96</v>
       </c>
       <c r="C161">
         <v>1</v>
@@ -7665,7 +7698,7 @@
         <v>15</v>
       </c>
       <c r="B162" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="C162">
         <v>1</v>
@@ -7676,7 +7709,7 @@
         <v>15</v>
       </c>
       <c r="B163" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -7687,7 +7720,7 @@
         <v>15</v>
       </c>
       <c r="B164" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="C164">
         <v>1</v>
@@ -7698,7 +7731,7 @@
         <v>15</v>
       </c>
       <c r="B165" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="C165">
         <v>1</v>
@@ -7709,7 +7742,7 @@
         <v>15</v>
       </c>
       <c r="B166" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C166">
         <v>1</v>
@@ -7720,7 +7753,7 @@
         <v>15</v>
       </c>
       <c r="B167" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -7731,7 +7764,7 @@
         <v>15</v>
       </c>
       <c r="B168" t="s">
-        <v>87</v>
+        <v>158</v>
       </c>
       <c r="C168">
         <v>1</v>
@@ -7742,7 +7775,7 @@
         <v>15</v>
       </c>
       <c r="B169" t="s">
-        <v>150</v>
+        <v>87</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -7753,7 +7786,7 @@
         <v>15</v>
       </c>
       <c r="B170" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -7764,7 +7797,7 @@
         <v>15</v>
       </c>
       <c r="B171" t="s">
-        <v>67</v>
+        <v>143</v>
       </c>
       <c r="C171">
         <v>1</v>
@@ -7775,7 +7808,7 @@
         <v>15</v>
       </c>
       <c r="B172" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C172">
         <v>1</v>
@@ -7786,7 +7819,7 @@
         <v>15</v>
       </c>
       <c r="B173" t="s">
-        <v>143</v>
+        <v>70</v>
       </c>
       <c r="C173">
         <v>1</v>
@@ -7797,7 +7830,7 @@
         <v>15</v>
       </c>
       <c r="B174" t="s">
-        <v>68</v>
+        <v>142</v>
       </c>
       <c r="C174">
         <v>1</v>
@@ -7808,7 +7841,7 @@
         <v>15</v>
       </c>
       <c r="B175" t="s">
-        <v>172</v>
+        <v>68</v>
       </c>
       <c r="C175">
         <v>1</v>
@@ -7819,7 +7852,7 @@
         <v>15</v>
       </c>
       <c r="B176" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -7830,7 +7863,7 @@
         <v>15</v>
       </c>
       <c r="B177" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -7841,7 +7874,7 @@
         <v>15</v>
       </c>
       <c r="B178" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -7852,7 +7885,7 @@
         <v>15</v>
       </c>
       <c r="B179" t="s">
-        <v>141</v>
+        <v>176</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -7863,7 +7896,7 @@
         <v>15</v>
       </c>
       <c r="B180" t="s">
-        <v>188</v>
+        <v>140</v>
       </c>
       <c r="C180">
         <v>1</v>
@@ -7874,7 +7907,7 @@
         <v>15</v>
       </c>
       <c r="B181" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C181">
         <v>1</v>
@@ -7885,7 +7918,7 @@
         <v>15</v>
       </c>
       <c r="B182" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C182">
         <v>1</v>
@@ -7896,7 +7929,7 @@
         <v>15</v>
       </c>
       <c r="B183" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C183">
         <v>1</v>
@@ -7904,13 +7937,13 @@
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B184" t="s">
-        <v>49</v>
+        <v>190</v>
       </c>
       <c r="C184">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -7918,10 +7951,10 @@
         <v>16</v>
       </c>
       <c r="B185" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C185">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -7929,10 +7962,10 @@
         <v>16</v>
       </c>
       <c r="B186" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C186">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -7940,10 +7973,10 @@
         <v>16</v>
       </c>
       <c r="B187" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="C187">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -7951,10 +7984,10 @@
         <v>16</v>
       </c>
       <c r="B188" t="s">
-        <v>115</v>
+        <v>66</v>
       </c>
       <c r="C188">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
@@ -7962,7 +7995,7 @@
         <v>16</v>
       </c>
       <c r="B189" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C189">
         <v>13</v>
@@ -7973,10 +8006,10 @@
         <v>16</v>
       </c>
       <c r="B190" t="s">
-        <v>194</v>
+        <v>114</v>
       </c>
       <c r="C190">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -7995,10 +8028,10 @@
         <v>16</v>
       </c>
       <c r="B192" t="s">
-        <v>50</v>
+        <v>192</v>
       </c>
       <c r="C192">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -8006,7 +8039,7 @@
         <v>16</v>
       </c>
       <c r="B193" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="C193">
         <v>11</v>
@@ -8017,7 +8050,7 @@
         <v>16</v>
       </c>
       <c r="B194" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="C194">
         <v>11</v>
@@ -8028,10 +8061,10 @@
         <v>16</v>
       </c>
       <c r="B195" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C195">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -8039,10 +8072,10 @@
         <v>16</v>
       </c>
       <c r="B196" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C196">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -8050,7 +8083,7 @@
         <v>16</v>
       </c>
       <c r="B197" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="C197">
         <v>9</v>
@@ -8061,10 +8094,10 @@
         <v>16</v>
       </c>
       <c r="B198" t="s">
-        <v>195</v>
+        <v>72</v>
       </c>
       <c r="C198">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -8072,10 +8105,10 @@
         <v>16</v>
       </c>
       <c r="B199" t="s">
-        <v>84</v>
+        <v>194</v>
       </c>
       <c r="C199">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
@@ -8094,10 +8127,10 @@
         <v>16</v>
       </c>
       <c r="B201" t="s">
-        <v>197</v>
+        <v>84</v>
       </c>
       <c r="C201">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
@@ -8105,7 +8138,7 @@
         <v>16</v>
       </c>
       <c r="B202" t="s">
-        <v>57</v>
+        <v>196</v>
       </c>
       <c r="C202">
         <v>6</v>
@@ -8116,7 +8149,7 @@
         <v>16</v>
       </c>
       <c r="B203" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C203">
         <v>6</v>
@@ -8127,7 +8160,7 @@
         <v>16</v>
       </c>
       <c r="B204" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C204">
         <v>5</v>
@@ -8149,7 +8182,7 @@
         <v>16</v>
       </c>
       <c r="B206" t="s">
-        <v>199</v>
+        <v>44</v>
       </c>
       <c r="C206">
         <v>5</v>
@@ -8160,7 +8193,7 @@
         <v>16</v>
       </c>
       <c r="B207" t="s">
-        <v>73</v>
+        <v>198</v>
       </c>
       <c r="C207">
         <v>5</v>
@@ -8171,10 +8204,10 @@
         <v>16</v>
       </c>
       <c r="B208" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C208">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -8204,7 +8237,7 @@
         <v>16</v>
       </c>
       <c r="B211" t="s">
-        <v>196</v>
+        <v>91</v>
       </c>
       <c r="C211">
         <v>4</v>
@@ -8215,7 +8248,7 @@
         <v>16</v>
       </c>
       <c r="B212" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C212">
         <v>4</v>
@@ -8226,7 +8259,7 @@
         <v>16</v>
       </c>
       <c r="B213" t="s">
-        <v>91</v>
+        <v>197</v>
       </c>
       <c r="C213">
         <v>4</v>
@@ -8237,10 +8270,10 @@
         <v>16</v>
       </c>
       <c r="B214" t="s">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="C214">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -8248,7 +8281,7 @@
         <v>16</v>
       </c>
       <c r="B215" t="s">
-        <v>68</v>
+        <v>294</v>
       </c>
       <c r="C215">
         <v>3</v>
@@ -8259,7 +8292,7 @@
         <v>16</v>
       </c>
       <c r="B216" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="C216">
         <v>3</v>
@@ -8270,7 +8303,7 @@
         <v>16</v>
       </c>
       <c r="B217" t="s">
-        <v>113</v>
+        <v>199</v>
       </c>
       <c r="C217">
         <v>3</v>
@@ -8281,7 +8314,7 @@
         <v>16</v>
       </c>
       <c r="B218" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="C218">
         <v>3</v>
@@ -8292,7 +8325,7 @@
         <v>16</v>
       </c>
       <c r="B219" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C219">
         <v>3</v>
@@ -8303,7 +8336,7 @@
         <v>16</v>
       </c>
       <c r="B220" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C220">
         <v>3</v>
@@ -8314,10 +8347,10 @@
         <v>16</v>
       </c>
       <c r="B221" t="s">
-        <v>203</v>
+        <v>116</v>
       </c>
       <c r="C221">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -8325,10 +8358,10 @@
         <v>16</v>
       </c>
       <c r="B222" t="s">
-        <v>206</v>
+        <v>74</v>
       </c>
       <c r="C222">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -8336,7 +8369,7 @@
         <v>16</v>
       </c>
       <c r="B223" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C223">
         <v>2</v>
@@ -8347,7 +8380,7 @@
         <v>16</v>
       </c>
       <c r="B224" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C224">
         <v>2</v>
@@ -8358,7 +8391,7 @@
         <v>16</v>
       </c>
       <c r="B225" t="s">
-        <v>204</v>
+        <v>64</v>
       </c>
       <c r="C225">
         <v>2</v>
@@ -8369,7 +8402,7 @@
         <v>16</v>
       </c>
       <c r="B226" t="s">
-        <v>64</v>
+        <v>203</v>
       </c>
       <c r="C226">
         <v>2</v>
@@ -8380,7 +8413,7 @@
         <v>16</v>
       </c>
       <c r="B227" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="C227">
         <v>2</v>
@@ -8391,7 +8424,7 @@
         <v>16</v>
       </c>
       <c r="B228" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C228">
         <v>2</v>
@@ -8402,10 +8435,10 @@
         <v>16</v>
       </c>
       <c r="B229" t="s">
-        <v>223</v>
+        <v>187</v>
       </c>
       <c r="C229">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -8413,10 +8446,10 @@
         <v>16</v>
       </c>
       <c r="B230" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="C230">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -8424,7 +8457,7 @@
         <v>16</v>
       </c>
       <c r="B231" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="C231">
         <v>1</v>
@@ -8435,7 +8468,7 @@
         <v>16</v>
       </c>
       <c r="B232" t="s">
-        <v>229</v>
+        <v>206</v>
       </c>
       <c r="C232">
         <v>1</v>
@@ -8446,7 +8479,7 @@
         <v>16</v>
       </c>
       <c r="B233" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="C233">
         <v>1</v>
@@ -8457,7 +8490,7 @@
         <v>16</v>
       </c>
       <c r="B234" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="C234">
         <v>1</v>
@@ -8468,7 +8501,7 @@
         <v>16</v>
       </c>
       <c r="B235" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="C235">
         <v>1</v>
@@ -8479,7 +8512,7 @@
         <v>16</v>
       </c>
       <c r="B236" t="s">
-        <v>70</v>
+        <v>239</v>
       </c>
       <c r="C236">
         <v>1</v>
@@ -8490,7 +8523,7 @@
         <v>16</v>
       </c>
       <c r="B237" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -8501,7 +8534,7 @@
         <v>16</v>
       </c>
       <c r="B238" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -8512,7 +8545,7 @@
         <v>16</v>
       </c>
       <c r="B239" t="s">
-        <v>125</v>
+        <v>231</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -8534,7 +8567,7 @@
         <v>16</v>
       </c>
       <c r="B241" t="s">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -8545,7 +8578,7 @@
         <v>16</v>
       </c>
       <c r="B242" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -8556,7 +8589,7 @@
         <v>16</v>
       </c>
       <c r="B243" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -8567,7 +8600,7 @@
         <v>16</v>
       </c>
       <c r="B244" t="s">
-        <v>215</v>
+        <v>124</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -8578,7 +8611,7 @@
         <v>16</v>
       </c>
       <c r="B245" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -8589,7 +8622,7 @@
         <v>16</v>
       </c>
       <c r="B246" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C246">
         <v>1</v>
@@ -8600,7 +8633,7 @@
         <v>16</v>
       </c>
       <c r="B247" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="C247">
         <v>1</v>
@@ -8611,7 +8644,7 @@
         <v>16</v>
       </c>
       <c r="B248" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="C248">
         <v>1</v>
@@ -8622,7 +8655,7 @@
         <v>16</v>
       </c>
       <c r="B249" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C249">
         <v>1</v>
@@ -8633,7 +8666,7 @@
         <v>16</v>
       </c>
       <c r="B250" t="s">
-        <v>208</v>
+        <v>69</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -8644,7 +8677,7 @@
         <v>16</v>
       </c>
       <c r="B251" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="C251">
         <v>1</v>
@@ -8655,7 +8688,7 @@
         <v>16</v>
       </c>
       <c r="B252" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -8666,7 +8699,7 @@
         <v>16</v>
       </c>
       <c r="B253" t="s">
-        <v>209</v>
+        <v>113</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -8677,7 +8710,7 @@
         <v>16</v>
       </c>
       <c r="B254" t="s">
-        <v>69</v>
+        <v>218</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -8688,7 +8721,7 @@
         <v>16</v>
       </c>
       <c r="B255" t="s">
-        <v>114</v>
+        <v>224</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -8699,7 +8732,7 @@
         <v>16</v>
       </c>
       <c r="B256" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -8710,7 +8743,7 @@
         <v>16</v>
       </c>
       <c r="B257" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -8721,7 +8754,7 @@
         <v>16</v>
       </c>
       <c r="B258" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C258">
         <v>1</v>
@@ -8732,7 +8765,7 @@
         <v>16</v>
       </c>
       <c r="B259" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="C259">
         <v>1</v>
@@ -8743,7 +8776,7 @@
         <v>16</v>
       </c>
       <c r="B260" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C260">
         <v>1</v>
@@ -8754,7 +8787,7 @@
         <v>16</v>
       </c>
       <c r="B261" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C261">
         <v>1</v>
@@ -8765,7 +8798,7 @@
         <v>16</v>
       </c>
       <c r="B262" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C262">
         <v>1</v>
@@ -8776,7 +8809,7 @@
         <v>16</v>
       </c>
       <c r="B263" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="C263">
         <v>1</v>
@@ -8787,7 +8820,7 @@
         <v>16</v>
       </c>
       <c r="B264" t="s">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -8798,7 +8831,7 @@
         <v>16</v>
       </c>
       <c r="B265" t="s">
-        <v>238</v>
+        <v>209</v>
       </c>
       <c r="C265">
         <v>1</v>
@@ -8809,7 +8842,7 @@
         <v>16</v>
       </c>
       <c r="B266" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C266">
         <v>1</v>
@@ -8820,7 +8853,7 @@
         <v>16</v>
       </c>
       <c r="B267" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -8831,7 +8864,7 @@
         <v>16</v>
       </c>
       <c r="B268" t="s">
-        <v>207</v>
+        <v>235</v>
       </c>
       <c r="C268">
         <v>1</v>
@@ -8842,7 +8875,7 @@
         <v>16</v>
       </c>
       <c r="B269" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="C269">
         <v>1</v>
@@ -8850,13 +8883,13 @@
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B270" t="s">
-        <v>120</v>
+        <v>243</v>
       </c>
       <c r="C270">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
@@ -8864,10 +8897,10 @@
         <v>21</v>
       </c>
       <c r="B271" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="C271">
-        <v>11</v>
+        <v>38</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
@@ -8875,10 +8908,10 @@
         <v>21</v>
       </c>
       <c r="B272" t="s">
-        <v>188</v>
+        <v>130</v>
       </c>
       <c r="C272">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
@@ -8886,10 +8919,10 @@
         <v>21</v>
       </c>
       <c r="B273" t="s">
-        <v>102</v>
+        <v>187</v>
       </c>
       <c r="C273">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
@@ -8897,7 +8930,7 @@
         <v>21</v>
       </c>
       <c r="B274" t="s">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="C274">
         <v>7</v>
@@ -8908,10 +8941,10 @@
         <v>21</v>
       </c>
       <c r="B275" t="s">
-        <v>239</v>
+        <v>200</v>
       </c>
       <c r="C275">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -8919,7 +8952,7 @@
         <v>21</v>
       </c>
       <c r="B276" t="s">
-        <v>119</v>
+        <v>238</v>
       </c>
       <c r="C276">
         <v>6</v>
@@ -8930,10 +8963,10 @@
         <v>21</v>
       </c>
       <c r="B277" t="s">
-        <v>241</v>
+        <v>118</v>
       </c>
       <c r="C277">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -8941,7 +8974,7 @@
         <v>21</v>
       </c>
       <c r="B278" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C278">
         <v>5</v>
@@ -8952,7 +8985,7 @@
         <v>21</v>
       </c>
       <c r="B279" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C279">
         <v>5</v>
@@ -8963,7 +8996,7 @@
         <v>21</v>
       </c>
       <c r="B280" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C280">
         <v>5</v>
@@ -8974,10 +9007,10 @@
         <v>21</v>
       </c>
       <c r="B281" t="s">
-        <v>100</v>
+        <v>239</v>
       </c>
       <c r="C281">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
@@ -8985,7 +9018,7 @@
         <v>21</v>
       </c>
       <c r="B282" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C282">
         <v>4</v>
@@ -8996,7 +9029,7 @@
         <v>21</v>
       </c>
       <c r="B283" t="s">
-        <v>243</v>
+        <v>100</v>
       </c>
       <c r="C283">
         <v>4</v>
@@ -9007,10 +9040,10 @@
         <v>21</v>
       </c>
       <c r="B284" t="s">
-        <v>80</v>
+        <v>242</v>
       </c>
       <c r="C284">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
@@ -9018,7 +9051,7 @@
         <v>21</v>
       </c>
       <c r="B285" t="s">
-        <v>244</v>
+        <v>124</v>
       </c>
       <c r="C285">
         <v>3</v>
@@ -9029,7 +9062,7 @@
         <v>21</v>
       </c>
       <c r="B286" t="s">
-        <v>125</v>
+        <v>247</v>
       </c>
       <c r="C286">
         <v>3</v>
@@ -9040,7 +9073,7 @@
         <v>21</v>
       </c>
       <c r="B287" t="s">
-        <v>195</v>
+        <v>44</v>
       </c>
       <c r="C287">
         <v>3</v>
@@ -9051,7 +9084,7 @@
         <v>21</v>
       </c>
       <c r="B288" t="s">
-        <v>126</v>
+        <v>246</v>
       </c>
       <c r="C288">
         <v>3</v>
@@ -9062,7 +9095,7 @@
         <v>21</v>
       </c>
       <c r="B289" t="s">
-        <v>248</v>
+        <v>161</v>
       </c>
       <c r="C289">
         <v>3</v>
@@ -9073,7 +9106,7 @@
         <v>21</v>
       </c>
       <c r="B290" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C290">
         <v>3</v>
@@ -9084,7 +9117,7 @@
         <v>21</v>
       </c>
       <c r="B291" t="s">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c r="C291">
         <v>3</v>
@@ -9095,7 +9128,7 @@
         <v>21</v>
       </c>
       <c r="B292" t="s">
-        <v>246</v>
+        <v>125</v>
       </c>
       <c r="C292">
         <v>3</v>
@@ -9106,7 +9139,7 @@
         <v>21</v>
       </c>
       <c r="B293" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="C293">
         <v>3</v>
@@ -9117,7 +9150,7 @@
         <v>21</v>
       </c>
       <c r="B294" t="s">
-        <v>132</v>
+        <v>245</v>
       </c>
       <c r="C294">
         <v>3</v>
@@ -9128,10 +9161,10 @@
         <v>21</v>
       </c>
       <c r="B295" t="s">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="C295">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -9139,10 +9172,10 @@
         <v>21</v>
       </c>
       <c r="B296" t="s">
-        <v>170</v>
+        <v>131</v>
       </c>
       <c r="C296">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -9150,7 +9183,7 @@
         <v>21</v>
       </c>
       <c r="B297" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C297">
         <v>2</v>
@@ -9161,7 +9194,7 @@
         <v>21</v>
       </c>
       <c r="B298" t="s">
-        <v>172</v>
+        <v>265</v>
       </c>
       <c r="C298">
         <v>2</v>
@@ -9172,7 +9205,7 @@
         <v>21</v>
       </c>
       <c r="B299" t="s">
-        <v>250</v>
+        <v>54</v>
       </c>
       <c r="C299">
         <v>2</v>
@@ -9183,7 +9216,7 @@
         <v>21</v>
       </c>
       <c r="B300" t="s">
-        <v>77</v>
+        <v>171</v>
       </c>
       <c r="C300">
         <v>2</v>
@@ -9194,7 +9227,7 @@
         <v>21</v>
       </c>
       <c r="B301" t="s">
-        <v>70</v>
+        <v>196</v>
       </c>
       <c r="C301">
         <v>2</v>
@@ -9205,7 +9238,7 @@
         <v>21</v>
       </c>
       <c r="B302" t="s">
-        <v>251</v>
+        <v>77</v>
       </c>
       <c r="C302">
         <v>2</v>
@@ -9216,7 +9249,7 @@
         <v>21</v>
       </c>
       <c r="B303" t="s">
-        <v>54</v>
+        <v>70</v>
       </c>
       <c r="C303">
         <v>2</v>
@@ -9227,7 +9260,7 @@
         <v>21</v>
       </c>
       <c r="B304" t="s">
-        <v>84</v>
+        <v>250</v>
       </c>
       <c r="C304">
         <v>2</v>
@@ -9238,7 +9271,7 @@
         <v>21</v>
       </c>
       <c r="B305" t="s">
-        <v>266</v>
+        <v>169</v>
       </c>
       <c r="C305">
         <v>2</v>
@@ -9249,7 +9282,7 @@
         <v>21</v>
       </c>
       <c r="B306" t="s">
-        <v>252</v>
+        <v>84</v>
       </c>
       <c r="C306">
         <v>2</v>
@@ -9260,7 +9293,7 @@
         <v>21</v>
       </c>
       <c r="B307" t="s">
-        <v>197</v>
+        <v>249</v>
       </c>
       <c r="C307">
         <v>2</v>
@@ -9271,7 +9304,7 @@
         <v>21</v>
       </c>
       <c r="B308" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C308">
         <v>2</v>
@@ -9282,7 +9315,7 @@
         <v>21</v>
       </c>
       <c r="B309" t="s">
-        <v>62</v>
+        <v>114</v>
       </c>
       <c r="C309">
         <v>2</v>
@@ -9293,7 +9326,7 @@
         <v>21</v>
       </c>
       <c r="B310" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C310">
         <v>2</v>
@@ -9304,10 +9337,10 @@
         <v>21</v>
       </c>
       <c r="B311" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="C311">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
@@ -9315,7 +9348,7 @@
         <v>21</v>
       </c>
       <c r="B312" t="s">
-        <v>114</v>
+        <v>252</v>
       </c>
       <c r="C312">
         <v>1</v>
@@ -9326,7 +9359,7 @@
         <v>21</v>
       </c>
       <c r="B313" t="s">
-        <v>259</v>
+        <v>123</v>
       </c>
       <c r="C313">
         <v>1</v>
@@ -9337,7 +9370,7 @@
         <v>21</v>
       </c>
       <c r="B314" t="s">
-        <v>254</v>
+        <v>49</v>
       </c>
       <c r="C314">
         <v>1</v>
@@ -9348,7 +9381,7 @@
         <v>21</v>
       </c>
       <c r="B315" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="C315">
         <v>1</v>
@@ -9359,7 +9392,7 @@
         <v>21</v>
       </c>
       <c r="B316" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="C316">
         <v>1</v>
@@ -9370,7 +9403,7 @@
         <v>21</v>
       </c>
       <c r="B317" t="s">
-        <v>198</v>
+        <v>266</v>
       </c>
       <c r="C317">
         <v>1</v>
@@ -9381,7 +9414,7 @@
         <v>21</v>
       </c>
       <c r="B318" t="s">
-        <v>271</v>
+        <v>197</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -9392,7 +9425,7 @@
         <v>21</v>
       </c>
       <c r="B319" t="s">
-        <v>49</v>
+        <v>163</v>
       </c>
       <c r="C319">
         <v>1</v>
@@ -9403,7 +9436,7 @@
         <v>21</v>
       </c>
       <c r="B320" t="s">
-        <v>262</v>
+        <v>113</v>
       </c>
       <c r="C320">
         <v>1</v>
@@ -9414,7 +9447,7 @@
         <v>21</v>
       </c>
       <c r="B321" t="s">
-        <v>260</v>
+        <v>135</v>
       </c>
       <c r="C321">
         <v>1</v>
@@ -9425,7 +9458,7 @@
         <v>21</v>
       </c>
       <c r="B322" t="s">
-        <v>277</v>
+        <v>259</v>
       </c>
       <c r="C322">
         <v>1</v>
@@ -9436,7 +9469,7 @@
         <v>21</v>
       </c>
       <c r="B323" t="s">
-        <v>124</v>
+        <v>276</v>
       </c>
       <c r="C323">
         <v>1</v>
@@ -9447,7 +9480,7 @@
         <v>21</v>
       </c>
       <c r="B324" t="s">
-        <v>136</v>
+        <v>274</v>
       </c>
       <c r="C324">
         <v>1</v>
@@ -9458,7 +9491,7 @@
         <v>21</v>
       </c>
       <c r="B325" t="s">
-        <v>164</v>
+        <v>260</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -9469,7 +9502,7 @@
         <v>21</v>
       </c>
       <c r="B326" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="C326">
         <v>1</v>
@@ -9480,7 +9513,7 @@
         <v>21</v>
       </c>
       <c r="B327" t="s">
-        <v>265</v>
+        <v>146</v>
       </c>
       <c r="C327">
         <v>1</v>
@@ -9491,7 +9524,7 @@
         <v>21</v>
       </c>
       <c r="B328" t="s">
-        <v>184</v>
+        <v>261</v>
       </c>
       <c r="C328">
         <v>1</v>
@@ -9502,7 +9535,7 @@
         <v>21</v>
       </c>
       <c r="B329" t="s">
-        <v>264</v>
+        <v>183</v>
       </c>
       <c r="C329">
         <v>1</v>
@@ -9513,7 +9546,7 @@
         <v>21</v>
       </c>
       <c r="B330" t="s">
-        <v>147</v>
+        <v>263</v>
       </c>
       <c r="C330">
         <v>1</v>
@@ -9524,7 +9557,7 @@
         <v>21</v>
       </c>
       <c r="B331" t="s">
-        <v>171</v>
+        <v>254</v>
       </c>
       <c r="C331">
         <v>1</v>
@@ -9535,7 +9568,7 @@
         <v>21</v>
       </c>
       <c r="B332" t="s">
-        <v>257</v>
+        <v>170</v>
       </c>
       <c r="C332">
         <v>1</v>
@@ -9546,7 +9579,7 @@
         <v>21</v>
       </c>
       <c r="B333" t="s">
-        <v>137</v>
+        <v>253</v>
       </c>
       <c r="C333">
         <v>1</v>
@@ -9557,7 +9590,7 @@
         <v>21</v>
       </c>
       <c r="B334" t="s">
-        <v>268</v>
+        <v>136</v>
       </c>
       <c r="C334">
         <v>1</v>
@@ -9568,7 +9601,7 @@
         <v>21</v>
       </c>
       <c r="B335" t="s">
-        <v>63</v>
+        <v>267</v>
       </c>
       <c r="C335">
         <v>1</v>
@@ -9579,7 +9612,7 @@
         <v>21</v>
       </c>
       <c r="B336" t="s">
-        <v>269</v>
+        <v>63</v>
       </c>
       <c r="C336">
         <v>1</v>
@@ -9590,7 +9623,7 @@
         <v>21</v>
       </c>
       <c r="B337" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C337">
         <v>1</v>
@@ -9601,7 +9634,7 @@
         <v>21</v>
       </c>
       <c r="B338" t="s">
-        <v>211</v>
+        <v>269</v>
       </c>
       <c r="C338">
         <v>1</v>
@@ -9612,7 +9645,7 @@
         <v>21</v>
       </c>
       <c r="B339" t="s">
-        <v>275</v>
+        <v>210</v>
       </c>
       <c r="C339">
         <v>1</v>
@@ -9623,7 +9656,7 @@
         <v>21</v>
       </c>
       <c r="B340" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="C340">
         <v>1</v>
@@ -9634,7 +9667,7 @@
         <v>21</v>
       </c>
       <c r="B341" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="C341">
         <v>1</v>
@@ -9645,7 +9678,7 @@
         <v>21</v>
       </c>
       <c r="B342" t="s">
-        <v>91</v>
+        <v>256</v>
       </c>
       <c r="C342">
         <v>1</v>
@@ -9656,7 +9689,7 @@
         <v>21</v>
       </c>
       <c r="B343" t="s">
-        <v>273</v>
+        <v>91</v>
       </c>
       <c r="C343">
         <v>1</v>
@@ -9667,7 +9700,7 @@
         <v>21</v>
       </c>
       <c r="B344" t="s">
-        <v>173</v>
+        <v>272</v>
       </c>
       <c r="C344">
         <v>1</v>
@@ -9678,7 +9711,7 @@
         <v>21</v>
       </c>
       <c r="B345" t="s">
-        <v>274</v>
+        <v>172</v>
       </c>
       <c r="C345">
         <v>1</v>
@@ -9689,7 +9722,7 @@
         <v>21</v>
       </c>
       <c r="B346" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="C346">
         <v>1</v>
@@ -9700,7 +9733,7 @@
         <v>21</v>
       </c>
       <c r="B347" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C347">
         <v>1</v>
@@ -9711,9 +9744,20 @@
         <v>21</v>
       </c>
       <c r="B348" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C348">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A349" t="s">
+        <v>21</v>
+      </c>
+      <c r="B349" t="s">
+        <v>262</v>
+      </c>
+      <c r="C349">
         <v>1</v>
       </c>
     </row>
@@ -9735,10 +9779,10 @@
         <v>37</v>
       </c>
       <c r="B1" t="s">
+        <v>278</v>
+      </c>
+      <c r="C1" t="s">
         <v>279</v>
-      </c>
-      <c r="C1" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -9746,7 +9790,7 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C2">
         <v>65</v>
@@ -9757,10 +9801,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C3">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -9768,7 +9812,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C4">
         <v>37</v>
@@ -9779,7 +9823,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C5">
         <v>12</v>
@@ -9790,7 +9834,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C6">
         <v>7</v>
@@ -9801,10 +9845,10 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C7">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -9812,7 +9856,7 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C8">
         <v>29</v>
@@ -9823,7 +9867,7 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C9">
         <v>558</v>
@@ -9834,7 +9878,7 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C10">
         <v>24</v>
@@ -9845,7 +9889,7 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C11">
         <v>30</v>
@@ -9856,7 +9900,7 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C12">
         <v>26</v>
@@ -9867,7 +9911,7 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C13">
         <v>882</v>
@@ -9878,7 +9922,7 @@
         <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C14">
         <v>4</v>
@@ -9889,7 +9933,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C15">
         <v>13</v>
@@ -9900,7 +9944,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C16">
         <v>22</v>
@@ -9911,7 +9955,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C17">
         <v>33</v>
@@ -9922,7 +9966,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C18">
         <v>11</v>
@@ -9933,7 +9977,7 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C19">
         <v>2</v>
@@ -9944,7 +9988,7 @@
         <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C20">
         <v>4</v>
@@ -9955,7 +9999,7 @@
         <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C21">
         <v>2</v>
@@ -9966,7 +10010,7 @@
         <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C22">
         <v>2</v>
@@ -9977,7 +10021,7 @@
         <v>16</v>
       </c>
       <c r="B23" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C23">
         <v>41</v>
@@ -9988,10 +10032,10 @@
         <v>16</v>
       </c>
       <c r="B24" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C24">
-        <v>875</v>
+        <v>872</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -9999,7 +10043,7 @@
         <v>16</v>
       </c>
       <c r="B25" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C25">
         <v>25</v>
@@ -10010,7 +10054,7 @@
         <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C26">
         <v>111</v>
@@ -10021,7 +10065,7 @@
         <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C27">
         <v>140</v>
@@ -10032,7 +10076,7 @@
         <v>16</v>
       </c>
       <c r="B28" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C28">
         <v>77</v>
@@ -10043,7 +10087,7 @@
         <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C29">
         <v>10</v>
@@ -10054,7 +10098,7 @@
         <v>16</v>
       </c>
       <c r="B30" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C30">
         <v>1</v>
@@ -10065,7 +10109,7 @@
         <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C31">
         <v>7</v>
@@ -10076,7 +10120,7 @@
         <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -10087,10 +10131,10 @@
         <v>21</v>
       </c>
       <c r="B33" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C33">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -10098,7 +10142,7 @@
         <v>21</v>
       </c>
       <c r="B34" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C34">
         <v>9</v>
@@ -10109,7 +10153,7 @@
         <v>21</v>
       </c>
       <c r="B35" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C35">
         <v>22</v>
@@ -10120,7 +10164,7 @@
         <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C36">
         <v>62</v>
@@ -10131,7 +10175,7 @@
         <v>21</v>
       </c>
       <c r="B37" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C37">
         <v>24</v>
@@ -10142,7 +10186,7 @@
         <v>21</v>
       </c>
       <c r="B38" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C38">
         <v>56</v>
@@ -10153,7 +10197,7 @@
         <v>21</v>
       </c>
       <c r="B39" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C39">
         <v>3</v>
@@ -10164,7 +10208,7 @@
         <v>21</v>
       </c>
       <c r="B40" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C40">
         <v>14</v>
@@ -10175,10 +10219,10 @@
         <v>21</v>
       </c>
       <c r="B41" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C41">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -10186,7 +10230,7 @@
         <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C42">
         <v>6</v>
@@ -10215,7 +10259,7 @@
         <v>22</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -10322,7 +10366,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C11" s="9">
         <v>1</v>
@@ -10432,7 +10476,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C21" s="9">
         <v>2</v>
@@ -10542,7 +10586,7 @@
         <v>15</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C31" s="9">
         <v>2</v>

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -1,30 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="239" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9A76B9D-A797-47F3-8765-DB7ED151ABEB}"/>
+  <xr:revisionPtr revIDLastSave="267" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F039489E-4DB0-48AD-A970-C9178D6FBF19}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="731" activeTab="1" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="731" firstSheet="1" activeTab="6" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="proyeccion_2026" sheetId="2" r:id="rId1"/>
     <sheet name="mat_2026" sheetId="1" r:id="rId2"/>
-    <sheet name="genero" sheetId="3" r:id="rId3"/>
-    <sheet name="mat_time" sheetId="4" r:id="rId4"/>
-    <sheet name="origen_estudiantes" sheetId="5" r:id="rId5"/>
-    <sheet name="origen_colegios" sheetId="6" r:id="rId6"/>
+    <sheet name="mat_time" sheetId="4" r:id="rId3"/>
+    <sheet name="origen_estudiantes" sheetId="5" r:id="rId4"/>
+    <sheet name="origen_colegios" sheetId="6" r:id="rId5"/>
+    <sheet name="genero" sheetId="3" r:id="rId6"/>
     <sheet name="com_est" sheetId="7" r:id="rId7"/>
     <sheet name="cantidad_cursos" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">mat_2026!$A$1:$E$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">origen_colegios!$A$1:$C$348</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">origen_colegios!$A$1:$C$348</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1325" uniqueCount="295">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -1053,10 +1053,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1546,6 +1542,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8FC1322-F2C4-4535-882A-673ED2A7B0F2}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
   <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1704,10 +1703,10 @@
         <v>108</v>
       </c>
       <c r="D9">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E9">
-        <v>1.0089999999999999</v>
+        <v>1.0189999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1721,10 +1720,10 @@
         <v>64</v>
       </c>
       <c r="D10">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E10">
-        <v>1.109</v>
+        <v>1.125</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -1925,10 +1924,10 @@
         <v>28</v>
       </c>
       <c r="D22">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E22">
-        <v>1.286</v>
+        <v>1.321</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1959,10 +1958,10 @@
         <v>65</v>
       </c>
       <c r="D24">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E24">
-        <v>1.1379999999999999</v>
+        <v>1.1539999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -2226,142 +2225,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AA5CF5E-5BFB-4AEA-AE46-C69F6039886F}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="20.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11">
-        <v>426</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD19485A-0629-47F9-A5AD-80ABA7A6E076}">
-  <dimension ref="A1:C260"/>
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:C263"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -3870,7 +3738,7 @@
         <v>3</v>
       </c>
       <c r="B137" s="8">
-        <v>46108</v>
+        <v>46209</v>
       </c>
       <c r="C137" s="9">
         <v>1</v>
@@ -3881,7 +3749,7 @@
         <v>3</v>
       </c>
       <c r="B138" s="5">
-        <v>46020</v>
+        <v>46108</v>
       </c>
       <c r="C138" s="6">
         <v>1</v>
@@ -3892,7 +3760,7 @@
         <v>3</v>
       </c>
       <c r="B139" s="8">
-        <v>46097</v>
+        <v>46020</v>
       </c>
       <c r="C139" s="9">
         <v>1</v>
@@ -3903,7 +3771,7 @@
         <v>3</v>
       </c>
       <c r="B140" s="5">
-        <v>46177</v>
+        <v>46097</v>
       </c>
       <c r="C140" s="6">
         <v>1</v>
@@ -3914,10 +3782,10 @@
         <v>3</v>
       </c>
       <c r="B141" s="8">
-        <v>46161</v>
+        <v>46177</v>
       </c>
       <c r="C141" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -3925,10 +3793,10 @@
         <v>3</v>
       </c>
       <c r="B142" s="5">
-        <v>46129</v>
+        <v>46161</v>
       </c>
       <c r="C142" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -3936,7 +3804,7 @@
         <v>3</v>
       </c>
       <c r="B143" s="8">
-        <v>46080</v>
+        <v>46129</v>
       </c>
       <c r="C143" s="9">
         <v>1</v>
@@ -3947,7 +3815,7 @@
         <v>3</v>
       </c>
       <c r="B144" s="5">
-        <v>46101</v>
+        <v>46080</v>
       </c>
       <c r="C144" s="6">
         <v>1</v>
@@ -3958,7 +3826,7 @@
         <v>3</v>
       </c>
       <c r="B145" s="8">
-        <v>46155</v>
+        <v>46101</v>
       </c>
       <c r="C145" s="9">
         <v>1</v>
@@ -3969,7 +3837,7 @@
         <v>3</v>
       </c>
       <c r="B146" s="5">
-        <v>46150</v>
+        <v>46155</v>
       </c>
       <c r="C146" s="6">
         <v>1</v>
@@ -3980,7 +3848,7 @@
         <v>3</v>
       </c>
       <c r="B147" s="8">
-        <v>46141</v>
+        <v>46150</v>
       </c>
       <c r="C147" s="9">
         <v>1</v>
@@ -3991,7 +3859,7 @@
         <v>3</v>
       </c>
       <c r="B148" s="5">
-        <v>46085</v>
+        <v>46141</v>
       </c>
       <c r="C148" s="6">
         <v>1</v>
@@ -4002,7 +3870,7 @@
         <v>3</v>
       </c>
       <c r="B149" s="8">
-        <v>46148</v>
+        <v>46085</v>
       </c>
       <c r="C149" s="9">
         <v>1</v>
@@ -4013,10 +3881,10 @@
         <v>3</v>
       </c>
       <c r="B150" s="5">
-        <v>46118</v>
+        <v>46148</v>
       </c>
       <c r="C150" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -4024,32 +3892,32 @@
         <v>3</v>
       </c>
       <c r="B151" s="8">
-        <v>46079</v>
+        <v>46118</v>
       </c>
       <c r="C151" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B152" s="5">
-        <v>46003</v>
+        <v>46192</v>
       </c>
       <c r="C152" s="6">
-        <v>92</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B153" s="8">
-        <v>46000</v>
+        <v>46079</v>
       </c>
       <c r="C153" s="9">
-        <v>132</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -4057,10 +3925,10 @@
         <v>15</v>
       </c>
       <c r="B154" s="5">
-        <v>46006</v>
+        <v>46003</v>
       </c>
       <c r="C154" s="6">
-        <v>173</v>
+        <v>92</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -4068,10 +3936,10 @@
         <v>15</v>
       </c>
       <c r="B155" s="8">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="C155" s="9">
-        <v>174</v>
+        <v>132</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -4079,10 +3947,10 @@
         <v>15</v>
       </c>
       <c r="B156" s="5">
-        <v>46014</v>
+        <v>46006</v>
       </c>
       <c r="C156" s="6">
-        <v>16</v>
+        <v>173</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
@@ -4090,10 +3958,10 @@
         <v>15</v>
       </c>
       <c r="B157" s="8">
-        <v>46002</v>
+        <v>46001</v>
       </c>
       <c r="C157" s="9">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
@@ -4101,10 +3969,10 @@
         <v>15</v>
       </c>
       <c r="B158" s="5">
-        <v>46009</v>
+        <v>46014</v>
       </c>
       <c r="C158" s="6">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
@@ -4112,10 +3980,10 @@
         <v>15</v>
       </c>
       <c r="B159" s="8">
-        <v>46010</v>
+        <v>46002</v>
       </c>
       <c r="C159" s="9">
-        <v>19</v>
+        <v>171</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -4123,10 +3991,10 @@
         <v>15</v>
       </c>
       <c r="B160" s="5">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="C160" s="6">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -4134,10 +4002,10 @@
         <v>15</v>
       </c>
       <c r="B161" s="8">
-        <v>46007</v>
+        <v>46010</v>
       </c>
       <c r="C161" s="9">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -4145,10 +4013,10 @@
         <v>15</v>
       </c>
       <c r="B162" s="5">
-        <v>46013</v>
+        <v>46008</v>
       </c>
       <c r="C162" s="6">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -4156,10 +4024,10 @@
         <v>15</v>
       </c>
       <c r="B163" s="8">
-        <v>46080</v>
+        <v>46007</v>
       </c>
       <c r="C163" s="9">
-        <v>2</v>
+        <v>43</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -4167,10 +4035,10 @@
         <v>15</v>
       </c>
       <c r="B164" s="5">
-        <v>46090</v>
+        <v>46013</v>
       </c>
       <c r="C164" s="6">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -4178,10 +4046,10 @@
         <v>15</v>
       </c>
       <c r="B165" s="8">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="C165" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -4189,10 +4057,10 @@
         <v>15</v>
       </c>
       <c r="B166" s="5">
-        <v>46015</v>
+        <v>46209</v>
       </c>
       <c r="C166" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -4200,10 +4068,10 @@
         <v>15</v>
       </c>
       <c r="B167" s="8">
-        <v>46085</v>
+        <v>46090</v>
       </c>
       <c r="C167" s="9">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -4211,10 +4079,10 @@
         <v>15</v>
       </c>
       <c r="B168" s="5">
-        <v>46098</v>
+        <v>46079</v>
       </c>
       <c r="C168" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -4222,10 +4090,10 @@
         <v>15</v>
       </c>
       <c r="B169" s="8">
-        <v>46021</v>
+        <v>46015</v>
       </c>
       <c r="C169" s="9">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -4233,10 +4101,10 @@
         <v>15</v>
       </c>
       <c r="B170" s="5">
-        <v>46078</v>
+        <v>46085</v>
       </c>
       <c r="C170" s="6">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -4244,10 +4112,10 @@
         <v>15</v>
       </c>
       <c r="B171" s="8">
-        <v>46084</v>
+        <v>46098</v>
       </c>
       <c r="C171" s="9">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -4255,10 +4123,10 @@
         <v>15</v>
       </c>
       <c r="B172" s="5">
-        <v>46128</v>
+        <v>46021</v>
       </c>
       <c r="C172" s="6">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -4266,10 +4134,10 @@
         <v>15</v>
       </c>
       <c r="B173" s="8">
-        <v>46083</v>
+        <v>46078</v>
       </c>
       <c r="C173" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -4277,10 +4145,10 @@
         <v>15</v>
       </c>
       <c r="B174" s="5">
-        <v>46076</v>
+        <v>46084</v>
       </c>
       <c r="C174" s="6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
@@ -4288,10 +4156,10 @@
         <v>15</v>
       </c>
       <c r="B175" s="8">
-        <v>46099</v>
+        <v>46128</v>
       </c>
       <c r="C175" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -4299,10 +4167,10 @@
         <v>15</v>
       </c>
       <c r="B176" s="5">
-        <v>46154</v>
+        <v>46083</v>
       </c>
       <c r="C176" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -4310,10 +4178,10 @@
         <v>15</v>
       </c>
       <c r="B177" s="8">
-        <v>46092</v>
+        <v>46076</v>
       </c>
       <c r="C177" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
@@ -4321,10 +4189,10 @@
         <v>15</v>
       </c>
       <c r="B178" s="5">
-        <v>46022</v>
+        <v>46099</v>
       </c>
       <c r="C178" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -4332,10 +4200,10 @@
         <v>15</v>
       </c>
       <c r="B179" s="8">
-        <v>46031</v>
+        <v>46154</v>
       </c>
       <c r="C179" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
@@ -4343,10 +4211,10 @@
         <v>15</v>
       </c>
       <c r="B180" s="5">
-        <v>46120</v>
+        <v>46092</v>
       </c>
       <c r="C180" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -4354,10 +4222,10 @@
         <v>15</v>
       </c>
       <c r="B181" s="8">
-        <v>46077</v>
+        <v>46022</v>
       </c>
       <c r="C181" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -4365,10 +4233,10 @@
         <v>15</v>
       </c>
       <c r="B182" s="5">
-        <v>46114</v>
+        <v>46031</v>
       </c>
       <c r="C182" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -4376,10 +4244,10 @@
         <v>15</v>
       </c>
       <c r="B183" s="8">
-        <v>46037</v>
+        <v>46120</v>
       </c>
       <c r="C183" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -4387,10 +4255,10 @@
         <v>15</v>
       </c>
       <c r="B184" s="5">
-        <v>46020</v>
+        <v>46077</v>
       </c>
       <c r="C184" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -4398,7 +4266,7 @@
         <v>15</v>
       </c>
       <c r="B185" s="8">
-        <v>46106</v>
+        <v>46114</v>
       </c>
       <c r="C185" s="9">
         <v>1</v>
@@ -4409,7 +4277,7 @@
         <v>15</v>
       </c>
       <c r="B186" s="5">
-        <v>46155</v>
+        <v>46037</v>
       </c>
       <c r="C186" s="6">
         <v>1</v>
@@ -4420,10 +4288,10 @@
         <v>15</v>
       </c>
       <c r="B187" s="8">
-        <v>46112</v>
+        <v>46020</v>
       </c>
       <c r="C187" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
@@ -4431,7 +4299,7 @@
         <v>15</v>
       </c>
       <c r="B188" s="5">
-        <v>46132</v>
+        <v>46106</v>
       </c>
       <c r="C188" s="6">
         <v>1</v>
@@ -4442,7 +4310,7 @@
         <v>15</v>
       </c>
       <c r="B189" s="8">
-        <v>46108</v>
+        <v>46155</v>
       </c>
       <c r="C189" s="9">
         <v>1</v>
@@ -4453,7 +4321,7 @@
         <v>15</v>
       </c>
       <c r="B190" s="5">
-        <v>46148</v>
+        <v>46112</v>
       </c>
       <c r="C190" s="6">
         <v>1</v>
@@ -4464,7 +4332,7 @@
         <v>15</v>
       </c>
       <c r="B191" s="8">
-        <v>46118</v>
+        <v>46132</v>
       </c>
       <c r="C191" s="9">
         <v>1</v>
@@ -4475,7 +4343,7 @@
         <v>15</v>
       </c>
       <c r="B192" s="5">
-        <v>46035</v>
+        <v>46108</v>
       </c>
       <c r="C192" s="6">
         <v>1</v>
@@ -4486,7 +4354,7 @@
         <v>15</v>
       </c>
       <c r="B193" s="8">
-        <v>46181</v>
+        <v>46148</v>
       </c>
       <c r="C193" s="9">
         <v>1</v>
@@ -4497,7 +4365,7 @@
         <v>15</v>
       </c>
       <c r="B194" s="5">
-        <v>46093</v>
+        <v>46118</v>
       </c>
       <c r="C194" s="6">
         <v>1</v>
@@ -4508,7 +4376,7 @@
         <v>15</v>
       </c>
       <c r="B195" s="8">
-        <v>46087</v>
+        <v>46035</v>
       </c>
       <c r="C195" s="9">
         <v>1</v>
@@ -4519,10 +4387,10 @@
         <v>15</v>
       </c>
       <c r="B196" s="5">
-        <v>46030</v>
+        <v>46181</v>
       </c>
       <c r="C196" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -4530,7 +4398,7 @@
         <v>15</v>
       </c>
       <c r="B197" s="8">
-        <v>46176</v>
+        <v>46093</v>
       </c>
       <c r="C197" s="9">
         <v>1</v>
@@ -4541,7 +4409,7 @@
         <v>15</v>
       </c>
       <c r="B198" s="5">
-        <v>46101</v>
+        <v>46087</v>
       </c>
       <c r="C198" s="6">
         <v>1</v>
@@ -4552,43 +4420,43 @@
         <v>15</v>
       </c>
       <c r="B199" s="8">
-        <v>46142</v>
+        <v>46030</v>
       </c>
       <c r="C199" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B200" s="5">
-        <v>46001</v>
+        <v>46176</v>
       </c>
       <c r="C200" s="6">
-        <v>153</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B201" s="8">
-        <v>46008</v>
+        <v>46101</v>
       </c>
       <c r="C201" s="9">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B202" s="5">
-        <v>46003</v>
+        <v>46142</v>
       </c>
       <c r="C202" s="6">
-        <v>70</v>
+        <v>1</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
@@ -4596,10 +4464,10 @@
         <v>21</v>
       </c>
       <c r="B203" s="8">
-        <v>46002</v>
+        <v>46001</v>
       </c>
       <c r="C203" s="9">
-        <v>111</v>
+        <v>153</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -4607,10 +4475,10 @@
         <v>21</v>
       </c>
       <c r="B204" s="5">
-        <v>46006</v>
+        <v>46008</v>
       </c>
       <c r="C204" s="6">
-        <v>146</v>
+        <v>38</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
@@ -4618,10 +4486,10 @@
         <v>21</v>
       </c>
       <c r="B205" s="8">
-        <v>46007</v>
+        <v>46003</v>
       </c>
       <c r="C205" s="9">
-        <v>45</v>
+        <v>70</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
@@ -4629,10 +4497,10 @@
         <v>21</v>
       </c>
       <c r="B206" s="5">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="C206" s="6">
-        <v>127</v>
+        <v>111</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
@@ -4640,10 +4508,10 @@
         <v>21</v>
       </c>
       <c r="B207" s="8">
-        <v>46084</v>
+        <v>46006</v>
       </c>
       <c r="C207" s="9">
-        <v>10</v>
+        <v>146</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -4651,10 +4519,10 @@
         <v>21</v>
       </c>
       <c r="B208" s="5">
-        <v>46013</v>
+        <v>46007</v>
       </c>
       <c r="C208" s="6">
-        <v>26</v>
+        <v>45</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
@@ -4662,10 +4530,10 @@
         <v>21</v>
       </c>
       <c r="B209" s="8">
-        <v>46010</v>
+        <v>46000</v>
       </c>
       <c r="C209" s="9">
-        <v>19</v>
+        <v>127</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
@@ -4673,10 +4541,10 @@
         <v>21</v>
       </c>
       <c r="B210" s="5">
-        <v>46021</v>
+        <v>46084</v>
       </c>
       <c r="C210" s="6">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -4684,10 +4552,10 @@
         <v>21</v>
       </c>
       <c r="B211" s="8">
-        <v>46009</v>
+        <v>46013</v>
       </c>
       <c r="C211" s="9">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
@@ -4695,10 +4563,10 @@
         <v>21</v>
       </c>
       <c r="B212" s="5">
-        <v>46083</v>
+        <v>46010</v>
       </c>
       <c r="C212" s="6">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4706,10 +4574,10 @@
         <v>21</v>
       </c>
       <c r="B213" s="8">
-        <v>46014</v>
+        <v>46021</v>
       </c>
       <c r="C213" s="9">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4717,10 +4585,10 @@
         <v>21</v>
       </c>
       <c r="B214" s="5">
-        <v>46157</v>
+        <v>46009</v>
       </c>
       <c r="C214" s="6">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4728,10 +4596,10 @@
         <v>21</v>
       </c>
       <c r="B215" s="8">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="C215" s="9">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4739,10 +4607,10 @@
         <v>21</v>
       </c>
       <c r="B216" s="5">
-        <v>46167</v>
+        <v>46014</v>
       </c>
       <c r="C216" s="6">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4750,7 +4618,7 @@
         <v>21</v>
       </c>
       <c r="B217" s="8">
-        <v>46035</v>
+        <v>46157</v>
       </c>
       <c r="C217" s="9">
         <v>2</v>
@@ -4761,7 +4629,7 @@
         <v>21</v>
       </c>
       <c r="B218" s="5">
-        <v>46085</v>
+        <v>46079</v>
       </c>
       <c r="C218" s="6">
         <v>3</v>
@@ -4772,10 +4640,10 @@
         <v>21</v>
       </c>
       <c r="B219" s="8">
-        <v>46120</v>
+        <v>46167</v>
       </c>
       <c r="C219" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4783,10 +4651,10 @@
         <v>21</v>
       </c>
       <c r="B220" s="5">
-        <v>46114</v>
+        <v>46035</v>
       </c>
       <c r="C220" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -4794,10 +4662,10 @@
         <v>21</v>
       </c>
       <c r="B221" s="8">
-        <v>46094</v>
+        <v>46085</v>
       </c>
       <c r="C221" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -4805,10 +4673,10 @@
         <v>21</v>
       </c>
       <c r="B222" s="5">
-        <v>46080</v>
+        <v>46120</v>
       </c>
       <c r="C222" s="6">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -4816,10 +4684,10 @@
         <v>21</v>
       </c>
       <c r="B223" s="8">
-        <v>46127</v>
+        <v>46114</v>
       </c>
       <c r="C223" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -4827,10 +4695,10 @@
         <v>21</v>
       </c>
       <c r="B224" s="5">
-        <v>46091</v>
+        <v>46094</v>
       </c>
       <c r="C224" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -4838,10 +4706,10 @@
         <v>21</v>
       </c>
       <c r="B225" s="8">
-        <v>46090</v>
+        <v>46080</v>
       </c>
       <c r="C225" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -4849,7 +4717,7 @@
         <v>21</v>
       </c>
       <c r="B226" s="5">
-        <v>46020</v>
+        <v>46127</v>
       </c>
       <c r="C226" s="6">
         <v>2</v>
@@ -4860,10 +4728,10 @@
         <v>21</v>
       </c>
       <c r="B227" s="8">
-        <v>46015</v>
+        <v>46091</v>
       </c>
       <c r="C227" s="9">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -4871,10 +4739,10 @@
         <v>21</v>
       </c>
       <c r="B228" s="5">
-        <v>46078</v>
+        <v>46090</v>
       </c>
       <c r="C228" s="6">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -4882,7 +4750,7 @@
         <v>21</v>
       </c>
       <c r="B229" s="8">
-        <v>46148</v>
+        <v>46020</v>
       </c>
       <c r="C229" s="9">
         <v>2</v>
@@ -4893,10 +4761,10 @@
         <v>21</v>
       </c>
       <c r="B230" s="5">
-        <v>46105</v>
+        <v>46015</v>
       </c>
       <c r="C230" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -4904,10 +4772,10 @@
         <v>21</v>
       </c>
       <c r="B231" s="8">
-        <v>46087</v>
+        <v>46078</v>
       </c>
       <c r="C231" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -4915,10 +4783,10 @@
         <v>21</v>
       </c>
       <c r="B232" s="5">
-        <v>46107</v>
+        <v>46148</v>
       </c>
       <c r="C232" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -4926,10 +4794,10 @@
         <v>21</v>
       </c>
       <c r="B233" s="8">
-        <v>46086</v>
+        <v>46105</v>
       </c>
       <c r="C233" s="9">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -4937,10 +4805,10 @@
         <v>21</v>
       </c>
       <c r="B234" s="5">
-        <v>46106</v>
+        <v>46087</v>
       </c>
       <c r="C234" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -4948,7 +4816,7 @@
         <v>21</v>
       </c>
       <c r="B235" s="8">
-        <v>46150</v>
+        <v>46107</v>
       </c>
       <c r="C235" s="9">
         <v>3</v>
@@ -4959,10 +4827,10 @@
         <v>21</v>
       </c>
       <c r="B236" s="5">
-        <v>46104</v>
+        <v>46086</v>
       </c>
       <c r="C236" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -4970,7 +4838,7 @@
         <v>21</v>
       </c>
       <c r="B237" s="8">
-        <v>46118</v>
+        <v>46106</v>
       </c>
       <c r="C237" s="9">
         <v>1</v>
@@ -4981,10 +4849,10 @@
         <v>21</v>
       </c>
       <c r="B238" s="5">
-        <v>46076</v>
+        <v>46150</v>
       </c>
       <c r="C238" s="6">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -4992,10 +4860,10 @@
         <v>21</v>
       </c>
       <c r="B239" s="8">
-        <v>46182</v>
+        <v>46104</v>
       </c>
       <c r="C239" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -5003,7 +4871,7 @@
         <v>21</v>
       </c>
       <c r="B240" s="5">
-        <v>46188</v>
+        <v>46118</v>
       </c>
       <c r="C240" s="6">
         <v>1</v>
@@ -5014,10 +4882,10 @@
         <v>21</v>
       </c>
       <c r="B241" s="8">
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="C241" s="9">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -5025,7 +4893,7 @@
         <v>21</v>
       </c>
       <c r="B242" s="5">
-        <v>46154</v>
+        <v>46182</v>
       </c>
       <c r="C242" s="6">
         <v>1</v>
@@ -5036,10 +4904,10 @@
         <v>21</v>
       </c>
       <c r="B243" s="8">
-        <v>46093</v>
+        <v>46188</v>
       </c>
       <c r="C243" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
@@ -5047,10 +4915,10 @@
         <v>21</v>
       </c>
       <c r="B244" s="5">
-        <v>46122</v>
+        <v>46077</v>
       </c>
       <c r="C244" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -5058,10 +4926,10 @@
         <v>21</v>
       </c>
       <c r="B245" s="8">
-        <v>46092</v>
+        <v>46154</v>
       </c>
       <c r="C245" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
@@ -5069,10 +4937,10 @@
         <v>21</v>
       </c>
       <c r="B246" s="5">
-        <v>46156</v>
+        <v>46093</v>
       </c>
       <c r="C246" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -5080,7 +4948,7 @@
         <v>21</v>
       </c>
       <c r="B247" s="8">
-        <v>46133</v>
+        <v>46122</v>
       </c>
       <c r="C247" s="9">
         <v>1</v>
@@ -5091,10 +4959,10 @@
         <v>21</v>
       </c>
       <c r="B248" s="5">
-        <v>46189</v>
+        <v>46092</v>
       </c>
       <c r="C248" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -5102,10 +4970,10 @@
         <v>21</v>
       </c>
       <c r="B249" s="8">
-        <v>46126</v>
+        <v>46156</v>
       </c>
       <c r="C249" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
@@ -5113,10 +4981,10 @@
         <v>21</v>
       </c>
       <c r="B250" s="5">
-        <v>46022</v>
+        <v>46133</v>
       </c>
       <c r="C250" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -5124,10 +4992,10 @@
         <v>21</v>
       </c>
       <c r="B251" s="8">
-        <v>46100</v>
+        <v>46189</v>
       </c>
       <c r="C251" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -5135,7 +5003,7 @@
         <v>21</v>
       </c>
       <c r="B252" s="5">
-        <v>46101</v>
+        <v>46126</v>
       </c>
       <c r="C252" s="6">
         <v>1</v>
@@ -5146,10 +5014,10 @@
         <v>21</v>
       </c>
       <c r="B253" s="8">
-        <v>46097</v>
+        <v>46022</v>
       </c>
       <c r="C253" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
@@ -5157,10 +5025,10 @@
         <v>21</v>
       </c>
       <c r="B254" s="5">
-        <v>46108</v>
+        <v>46100</v>
       </c>
       <c r="C254" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
@@ -5168,10 +5036,10 @@
         <v>21</v>
       </c>
       <c r="B255" s="8">
-        <v>46098</v>
+        <v>46101</v>
       </c>
       <c r="C255" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
@@ -5179,10 +5047,10 @@
         <v>21</v>
       </c>
       <c r="B256" s="5">
-        <v>46113</v>
+        <v>46097</v>
       </c>
       <c r="C256" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
@@ -5190,7 +5058,7 @@
         <v>21</v>
       </c>
       <c r="B257" s="8">
-        <v>46142</v>
+        <v>46108</v>
       </c>
       <c r="C257" s="9">
         <v>1</v>
@@ -5201,10 +5069,10 @@
         <v>21</v>
       </c>
       <c r="B258" s="5">
-        <v>46153</v>
+        <v>46098</v>
       </c>
       <c r="C258" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
@@ -5212,7 +5080,7 @@
         <v>21</v>
       </c>
       <c r="B259" s="8">
-        <v>46031</v>
+        <v>46113</v>
       </c>
       <c r="C259" s="9">
         <v>1</v>
@@ -5223,9 +5091,42 @@
         <v>21</v>
       </c>
       <c r="B260" s="5">
+        <v>46142</v>
+      </c>
+      <c r="C260" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B261" s="8">
+        <v>46153</v>
+      </c>
+      <c r="C261" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B262" s="5">
+        <v>46031</v>
+      </c>
+      <c r="C262" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B263" s="8">
         <v>46155</v>
       </c>
-      <c r="C260" s="6">
+      <c r="C263" s="9">
         <v>1</v>
       </c>
     </row>
@@ -5234,8 +5135,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF41E2F3-2E0F-49EB-BAE8-83F2CBABFF5B}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
   <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5394,7 +5298,7 @@
         <v>5</v>
       </c>
       <c r="E9">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -5411,7 +5315,7 @@
         <v>1</v>
       </c>
       <c r="E10">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -5615,7 +5519,7 @@
         <v>25</v>
       </c>
       <c r="E22">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -5643,7 +5547,7 @@
         <v>8</v>
       </c>
       <c r="C24">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D24">
         <v>12</v>
@@ -5912,8 +5816,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0916EAC6-1E7F-4924-9D0E-33749FD3E143}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
   <dimension ref="A1:C349"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7104,7 +7011,7 @@
         <v>15</v>
       </c>
       <c r="B108" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="C108">
         <v>4</v>
@@ -7126,7 +7033,7 @@
         <v>15</v>
       </c>
       <c r="B110" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="C110">
         <v>4</v>
@@ -7148,10 +7055,10 @@
         <v>15</v>
       </c>
       <c r="B112" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C112">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -7159,7 +7066,7 @@
         <v>15</v>
       </c>
       <c r="B113" t="s">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="C113">
         <v>3</v>
@@ -7181,7 +7088,7 @@
         <v>15</v>
       </c>
       <c r="B115" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C115">
         <v>3</v>
@@ -7203,7 +7110,7 @@
         <v>15</v>
       </c>
       <c r="B117" t="s">
-        <v>128</v>
+        <v>80</v>
       </c>
       <c r="C117">
         <v>3</v>
@@ -7214,7 +7121,7 @@
         <v>15</v>
       </c>
       <c r="B118" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C118">
         <v>2</v>
@@ -7225,7 +7132,7 @@
         <v>15</v>
       </c>
       <c r="B119" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C119">
         <v>2</v>
@@ -7236,7 +7143,7 @@
         <v>15</v>
       </c>
       <c r="B120" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C120">
         <v>2</v>
@@ -7258,7 +7165,7 @@
         <v>15</v>
       </c>
       <c r="B122" t="s">
-        <v>62</v>
+        <v>138</v>
       </c>
       <c r="C122">
         <v>2</v>
@@ -7280,7 +7187,7 @@
         <v>15</v>
       </c>
       <c r="B124" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C124">
         <v>2</v>
@@ -7302,7 +7209,7 @@
         <v>15</v>
       </c>
       <c r="B126" t="s">
-        <v>134</v>
+        <v>62</v>
       </c>
       <c r="C126">
         <v>2</v>
@@ -7335,7 +7242,7 @@
         <v>15</v>
       </c>
       <c r="B129" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="C129">
         <v>1</v>
@@ -7390,7 +7297,7 @@
         <v>15</v>
       </c>
       <c r="B134" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C134">
         <v>1</v>
@@ -7456,7 +7363,7 @@
         <v>15</v>
       </c>
       <c r="B140" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="C140">
         <v>1</v>
@@ -7511,7 +7418,7 @@
         <v>15</v>
       </c>
       <c r="B145" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="C145">
         <v>1</v>
@@ -7566,7 +7473,7 @@
         <v>15</v>
       </c>
       <c r="B150" t="s">
-        <v>183</v>
+        <v>67</v>
       </c>
       <c r="C150">
         <v>1</v>
@@ -7577,7 +7484,7 @@
         <v>15</v>
       </c>
       <c r="B151" t="s">
-        <v>182</v>
+        <v>161</v>
       </c>
       <c r="C151">
         <v>1</v>
@@ -7588,7 +7495,7 @@
         <v>15</v>
       </c>
       <c r="B152" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="C152">
         <v>1</v>
@@ -7599,7 +7506,7 @@
         <v>15</v>
       </c>
       <c r="B153" t="s">
-        <v>146</v>
+        <v>165</v>
       </c>
       <c r="C153">
         <v>1</v>
@@ -7698,7 +7605,7 @@
         <v>15</v>
       </c>
       <c r="B162" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C162">
         <v>1</v>
@@ -7709,7 +7616,7 @@
         <v>15</v>
       </c>
       <c r="B163" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -7731,7 +7638,7 @@
         <v>15</v>
       </c>
       <c r="B165" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="C165">
         <v>1</v>
@@ -7742,7 +7649,7 @@
         <v>15</v>
       </c>
       <c r="B166" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="C166">
         <v>1</v>
@@ -7753,7 +7660,7 @@
         <v>15</v>
       </c>
       <c r="B167" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -7775,7 +7682,7 @@
         <v>15</v>
       </c>
       <c r="B169" t="s">
-        <v>87</v>
+        <v>178</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -7797,7 +7704,7 @@
         <v>15</v>
       </c>
       <c r="B171" t="s">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="C171">
         <v>1</v>
@@ -7808,7 +7715,7 @@
         <v>15</v>
       </c>
       <c r="B172" t="s">
-        <v>67</v>
+        <v>162</v>
       </c>
       <c r="C172">
         <v>1</v>
@@ -7841,7 +7748,7 @@
         <v>15</v>
       </c>
       <c r="B175" t="s">
-        <v>68</v>
+        <v>147</v>
       </c>
       <c r="C175">
         <v>1</v>
@@ -7852,7 +7759,7 @@
         <v>15</v>
       </c>
       <c r="B176" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -7874,7 +7781,7 @@
         <v>15</v>
       </c>
       <c r="B178" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -7885,7 +7792,7 @@
         <v>15</v>
       </c>
       <c r="B179" t="s">
-        <v>176</v>
+        <v>68</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -9759,6 +9666,143 @@
       </c>
       <c r="C349">
         <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AA5CF5E-5BFB-4AEA-AE46-C69F6039886F}">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11">
+        <v>426</v>
       </c>
     </row>
   </sheetData>
@@ -9768,6 +9812,9 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23700CF0-069F-497B-B50D-FB3ED3120196}">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+  </sheetPr>
   <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -9804,7 +9851,7 @@
         <v>281</v>
       </c>
       <c r="C3">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -9914,7 +9961,7 @@
         <v>284</v>
       </c>
       <c r="C13">
-        <v>882</v>
+        <v>884</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -9936,7 +9983,7 @@
         <v>281</v>
       </c>
       <c r="C15">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -9958,7 +10005,7 @@
         <v>285</v>
       </c>
       <c r="C17">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -10243,6 +10290,9 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A394073B-D687-4CC9-855F-76C313D18351}">
+  <sheetPr>
+    <tabColor rgb="FFFFC000"/>
+  </sheetPr>
   <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>

--- a/src/pages/data/mat_2026.xlsx
+++ b/src/pages/data/mat_2026.xlsx
@@ -1,30 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/03459c2b1820bce1/Documentos/Proyect_Phyton/Proyect_multi_page/src/pages/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="239" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F9A76B9D-A797-47F3-8765-DB7ED151ABEB}"/>
+  <xr:revisionPtr revIDLastSave="287" documentId="13_ncr:1_{A55B11BD-6DE3-4270-9793-04ABEC3F3BB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{735711F1-9E87-4BCA-B09D-39CEB67597FA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="731" activeTab="1" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="20640" windowHeight="11040" tabRatio="731" activeTab="6" xr2:uid="{36BD599D-36E1-42BF-8C27-3007C624F7E1}"/>
   </bookViews>
   <sheets>
     <sheet name="proyeccion_2026" sheetId="2" r:id="rId1"/>
     <sheet name="mat_2026" sheetId="1" r:id="rId2"/>
-    <sheet name="genero" sheetId="3" r:id="rId3"/>
-    <sheet name="mat_time" sheetId="4" r:id="rId4"/>
-    <sheet name="origen_estudiantes" sheetId="5" r:id="rId5"/>
-    <sheet name="origen_colegios" sheetId="6" r:id="rId6"/>
+    <sheet name="mat_time" sheetId="4" r:id="rId3"/>
+    <sheet name="origen_estudiantes" sheetId="5" r:id="rId4"/>
+    <sheet name="origen_colegios" sheetId="6" r:id="rId5"/>
+    <sheet name="genero" sheetId="3" r:id="rId6"/>
     <sheet name="com_est" sheetId="7" r:id="rId7"/>
     <sheet name="cantidad_cursos" sheetId="8" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">mat_2026!$A$1:$E$39</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">origen_colegios!$A$1:$C$348</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">origen_colegios!$A$1:$C$348</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="295">
   <si>
     <t>SAE_2026</t>
   </si>
@@ -1053,10 +1053,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1585,10 +1581,10 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E2">
-        <v>1.2629999999999999</v>
+        <v>1.3160000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -1636,10 +1632,10 @@
         <v>34</v>
       </c>
       <c r="D5">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E5">
-        <v>1.2649999999999999</v>
+        <v>1.294</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -1653,10 +1649,10 @@
         <v>58</v>
       </c>
       <c r="D6">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E6">
-        <v>1.069</v>
+        <v>1.0860000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -1704,10 +1700,10 @@
         <v>108</v>
       </c>
       <c r="D9">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E9">
-        <v>1.0089999999999999</v>
+        <v>1.0189999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -1823,10 +1819,10 @@
         <v>63</v>
       </c>
       <c r="D16">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E16">
-        <v>0.96799999999999997</v>
+        <v>0.98399999999999999</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -1840,10 +1836,10 @@
         <v>68</v>
       </c>
       <c r="D17">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E17">
-        <v>1.0289999999999999</v>
+        <v>1.0589999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -1857,10 +1853,10 @@
         <v>75</v>
       </c>
       <c r="D18">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E18">
-        <v>1.1200000000000001</v>
+        <v>1.147</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -1874,10 +1870,10 @@
         <v>89</v>
       </c>
       <c r="D19">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0.98899999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1908,10 +1904,10 @@
         <v>88</v>
       </c>
       <c r="D21">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E21">
-        <v>1.0109999999999999</v>
+        <v>1.0229999999999999</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -1925,10 +1921,10 @@
         <v>28</v>
       </c>
       <c r="D22">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E22">
-        <v>1.286</v>
+        <v>1.321</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1959,10 +1955,10 @@
         <v>65</v>
       </c>
       <c r="D24">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E24">
-        <v>1.1379999999999999</v>
+        <v>1.169</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -1976,10 +1972,10 @@
         <v>91</v>
       </c>
       <c r="D25">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E25">
-        <v>1.022</v>
+        <v>1.0329999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -1993,10 +1989,10 @@
         <v>83</v>
       </c>
       <c r="D26">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>1.012</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -2010,10 +2006,10 @@
         <v>109</v>
       </c>
       <c r="D27">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E27">
-        <v>0.96299999999999997</v>
+        <v>0.97199999999999998</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -2044,10 +2040,10 @@
         <v>128</v>
       </c>
       <c r="D29">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E29">
-        <v>1.0469999999999999</v>
+        <v>1.0389999999999999</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -2061,10 +2057,10 @@
         <v>119</v>
       </c>
       <c r="D30">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E30">
-        <v>0.98299999999999998</v>
+        <v>0.99199999999999999</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -2078,10 +2074,10 @@
         <v>138</v>
       </c>
       <c r="D31">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E31">
-        <v>1.0580000000000001</v>
+        <v>1.0720000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -2095,10 +2091,10 @@
         <v>396</v>
       </c>
       <c r="D32">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E32">
-        <v>1.0580000000000001</v>
+        <v>1.056</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2112,10 +2108,10 @@
         <v>329</v>
       </c>
       <c r="D33">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="E33">
-        <v>1.0269999999999999</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2163,10 +2159,10 @@
         <v>250</v>
       </c>
       <c r="D36">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E36">
-        <v>1.028</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -2180,10 +2176,10 @@
         <v>217</v>
       </c>
       <c r="D37">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E37">
-        <v>0.995</v>
+        <v>1.0049999999999999</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -2197,10 +2193,10 @@
         <v>226</v>
       </c>
       <c r="D38">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E38">
-        <v>1.071</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -2226,142 +2222,8 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AA5CF5E-5BFB-4AEA-AE46-C69F6039886F}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="20.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11">
-        <v>426</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD19485A-0629-47F9-A5AD-80ABA7A6E076}">
-  <dimension ref="A1:C260"/>
+  <dimension ref="A1:C276"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -2649,10 +2511,10 @@
         <v>16</v>
       </c>
       <c r="B26" s="5">
-        <v>46020</v>
+        <v>46211</v>
       </c>
       <c r="C26" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -2660,10 +2522,10 @@
         <v>16</v>
       </c>
       <c r="B27" s="8">
-        <v>46076</v>
+        <v>46020</v>
       </c>
       <c r="C27" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -2671,10 +2533,10 @@
         <v>16</v>
       </c>
       <c r="B28" s="5">
-        <v>46136</v>
+        <v>46076</v>
       </c>
       <c r="C28" s="6">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
@@ -2682,10 +2544,10 @@
         <v>16</v>
       </c>
       <c r="B29" s="8">
-        <v>46078</v>
+        <v>46136</v>
       </c>
       <c r="C29" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -2693,10 +2555,10 @@
         <v>16</v>
       </c>
       <c r="B30" s="5">
-        <v>46176</v>
+        <v>46078</v>
       </c>
       <c r="C30" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -2704,10 +2566,10 @@
         <v>16</v>
       </c>
       <c r="B31" s="8">
-        <v>46182</v>
+        <v>46176</v>
       </c>
       <c r="C31" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -2715,10 +2577,10 @@
         <v>16</v>
       </c>
       <c r="B32" s="5">
-        <v>46098</v>
+        <v>46182</v>
       </c>
       <c r="C32" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -2726,7 +2588,7 @@
         <v>16</v>
       </c>
       <c r="B33" s="8">
-        <v>46181</v>
+        <v>46098</v>
       </c>
       <c r="C33" s="9">
         <v>3</v>
@@ -2737,10 +2599,10 @@
         <v>16</v>
       </c>
       <c r="B34" s="5">
-        <v>46084</v>
+        <v>46181</v>
       </c>
       <c r="C34" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
@@ -2748,10 +2610,10 @@
         <v>16</v>
       </c>
       <c r="B35" s="8">
-        <v>46160</v>
+        <v>46084</v>
       </c>
       <c r="C35" s="9">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -2759,10 +2621,10 @@
         <v>16</v>
       </c>
       <c r="B36" s="5">
-        <v>46167</v>
+        <v>46160</v>
       </c>
       <c r="C36" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
@@ -2770,7 +2632,7 @@
         <v>16</v>
       </c>
       <c r="B37" s="8">
-        <v>46099</v>
+        <v>46167</v>
       </c>
       <c r="C37" s="9">
         <v>2</v>
@@ -2781,10 +2643,10 @@
         <v>16</v>
       </c>
       <c r="B38" s="5">
-        <v>46128</v>
+        <v>46099</v>
       </c>
       <c r="C38" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
@@ -2792,10 +2654,10 @@
         <v>16</v>
       </c>
       <c r="B39" s="8">
-        <v>46141</v>
+        <v>46128</v>
       </c>
       <c r="C39" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -2803,10 +2665,10 @@
         <v>16</v>
       </c>
       <c r="B40" s="5">
-        <v>46132</v>
+        <v>46141</v>
       </c>
       <c r="C40" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -2814,10 +2676,10 @@
         <v>16</v>
       </c>
       <c r="B41" s="8">
-        <v>46127</v>
+        <v>46132</v>
       </c>
       <c r="C41" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -2825,7 +2687,7 @@
         <v>16</v>
       </c>
       <c r="B42" s="5">
-        <v>46091</v>
+        <v>46127</v>
       </c>
       <c r="C42" s="6">
         <v>2</v>
@@ -2836,10 +2698,10 @@
         <v>16</v>
       </c>
       <c r="B43" s="8">
-        <v>46104</v>
+        <v>46210</v>
       </c>
       <c r="C43" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
@@ -2847,10 +2709,10 @@
         <v>16</v>
       </c>
       <c r="B44" s="5">
-        <v>46140</v>
+        <v>46091</v>
       </c>
       <c r="C44" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -2858,7 +2720,7 @@
         <v>16</v>
       </c>
       <c r="B45" s="8">
-        <v>46106</v>
+        <v>46104</v>
       </c>
       <c r="C45" s="9">
         <v>1</v>
@@ -2869,7 +2731,7 @@
         <v>16</v>
       </c>
       <c r="B46" s="5">
-        <v>46113</v>
+        <v>46140</v>
       </c>
       <c r="C46" s="6">
         <v>1</v>
@@ -2880,7 +2742,7 @@
         <v>16</v>
       </c>
       <c r="B47" s="8">
-        <v>46184</v>
+        <v>46106</v>
       </c>
       <c r="C47" s="9">
         <v>1</v>
@@ -2891,10 +2753,10 @@
         <v>16</v>
       </c>
       <c r="B48" s="5">
-        <v>46090</v>
+        <v>46113</v>
       </c>
       <c r="C48" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
@@ -2902,7 +2764,7 @@
         <v>16</v>
       </c>
       <c r="B49" s="8">
-        <v>46139</v>
+        <v>46184</v>
       </c>
       <c r="C49" s="9">
         <v>1</v>
@@ -2913,10 +2775,10 @@
         <v>16</v>
       </c>
       <c r="B50" s="5">
-        <v>46148</v>
+        <v>46090</v>
       </c>
       <c r="C50" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -2924,7 +2786,7 @@
         <v>16</v>
       </c>
       <c r="B51" s="8">
-        <v>46175</v>
+        <v>46139</v>
       </c>
       <c r="C51" s="9">
         <v>1</v>
@@ -2935,7 +2797,7 @@
         <v>16</v>
       </c>
       <c r="B52" s="5">
-        <v>46125</v>
+        <v>46148</v>
       </c>
       <c r="C52" s="6">
         <v>1</v>
@@ -2946,7 +2808,7 @@
         <v>16</v>
       </c>
       <c r="B53" s="8">
-        <v>46093</v>
+        <v>46175</v>
       </c>
       <c r="C53" s="9">
         <v>1</v>
@@ -2957,10 +2819,10 @@
         <v>16</v>
       </c>
       <c r="B54" s="5">
-        <v>46177</v>
+        <v>46125</v>
       </c>
       <c r="C54" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -2968,7 +2830,7 @@
         <v>16</v>
       </c>
       <c r="B55" s="8">
-        <v>46156</v>
+        <v>46093</v>
       </c>
       <c r="C55" s="9">
         <v>1</v>
@@ -2979,10 +2841,10 @@
         <v>16</v>
       </c>
       <c r="B56" s="5">
-        <v>46092</v>
+        <v>46177</v>
       </c>
       <c r="C56" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
@@ -2990,7 +2852,7 @@
         <v>16</v>
       </c>
       <c r="B57" s="8">
-        <v>46188</v>
+        <v>46156</v>
       </c>
       <c r="C57" s="9">
         <v>1</v>
@@ -3001,7 +2863,7 @@
         <v>16</v>
       </c>
       <c r="B58" s="5">
-        <v>46101</v>
+        <v>46092</v>
       </c>
       <c r="C58" s="6">
         <v>1</v>
@@ -3009,24 +2871,24 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B59" s="8">
-        <v>46007</v>
+        <v>46188</v>
       </c>
       <c r="C59" s="9">
-        <v>78</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B60" s="5">
-        <v>46009</v>
+        <v>46101</v>
       </c>
       <c r="C60" s="6">
-        <v>34</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
@@ -3034,10 +2896,10 @@
         <v>14</v>
       </c>
       <c r="B61" s="8">
-        <v>46000</v>
+        <v>46007</v>
       </c>
       <c r="C61" s="9">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -3045,10 +2907,10 @@
         <v>14</v>
       </c>
       <c r="B62" s="5">
-        <v>46001</v>
+        <v>46009</v>
       </c>
       <c r="C62" s="6">
-        <v>83</v>
+        <v>34</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
@@ -3056,7 +2918,7 @@
         <v>14</v>
       </c>
       <c r="B63" s="8">
-        <v>46006</v>
+        <v>46000</v>
       </c>
       <c r="C63" s="9">
         <v>79</v>
@@ -3067,10 +2929,10 @@
         <v>14</v>
       </c>
       <c r="B64" s="5">
-        <v>46010</v>
+        <v>46001</v>
       </c>
       <c r="C64" s="6">
-        <v>24</v>
+        <v>82</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -3078,10 +2940,10 @@
         <v>14</v>
       </c>
       <c r="B65" s="8">
-        <v>46014</v>
+        <v>46006</v>
       </c>
       <c r="C65" s="9">
-        <v>20</v>
+        <v>79</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -3089,10 +2951,10 @@
         <v>14</v>
       </c>
       <c r="B66" s="5">
-        <v>46002</v>
+        <v>46010</v>
       </c>
       <c r="C66" s="6">
-        <v>47</v>
+        <v>24</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -3100,10 +2962,10 @@
         <v>14</v>
       </c>
       <c r="B67" s="8">
-        <v>46008</v>
+        <v>46014</v>
       </c>
       <c r="C67" s="9">
-        <v>58</v>
+        <v>20</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
@@ -3111,7 +2973,7 @@
         <v>14</v>
       </c>
       <c r="B68" s="5">
-        <v>46003</v>
+        <v>46002</v>
       </c>
       <c r="C68" s="6">
         <v>47</v>
@@ -3122,10 +2984,10 @@
         <v>14</v>
       </c>
       <c r="B69" s="8">
-        <v>46013</v>
+        <v>46008</v>
       </c>
       <c r="C69" s="9">
-        <v>30</v>
+        <v>58</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
@@ -3133,10 +2995,10 @@
         <v>14</v>
       </c>
       <c r="B70" s="5">
-        <v>46022</v>
+        <v>46003</v>
       </c>
       <c r="C70" s="6">
-        <v>2</v>
+        <v>47</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -3144,10 +3006,10 @@
         <v>14</v>
       </c>
       <c r="B71" s="8">
-        <v>46080</v>
+        <v>46013</v>
       </c>
       <c r="C71" s="9">
-        <v>8</v>
+        <v>30</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
@@ -3155,10 +3017,10 @@
         <v>14</v>
       </c>
       <c r="B72" s="5">
-        <v>46084</v>
+        <v>46022</v>
       </c>
       <c r="C72" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
@@ -3166,10 +3028,10 @@
         <v>14</v>
       </c>
       <c r="B73" s="8">
-        <v>46125</v>
+        <v>46080</v>
       </c>
       <c r="C73" s="9">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
@@ -3177,7 +3039,7 @@
         <v>14</v>
       </c>
       <c r="B74" s="5">
-        <v>46091</v>
+        <v>46084</v>
       </c>
       <c r="C74" s="6">
         <v>3</v>
@@ -3188,10 +3050,10 @@
         <v>14</v>
       </c>
       <c r="B75" s="8">
-        <v>46083</v>
+        <v>46125</v>
       </c>
       <c r="C75" s="9">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
@@ -3199,7 +3061,7 @@
         <v>14</v>
       </c>
       <c r="B76" s="5">
-        <v>46105</v>
+        <v>46209</v>
       </c>
       <c r="C76" s="6">
         <v>2</v>
@@ -3210,10 +3072,10 @@
         <v>14</v>
       </c>
       <c r="B77" s="8">
-        <v>46077</v>
+        <v>46091</v>
       </c>
       <c r="C77" s="9">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -3221,10 +3083,10 @@
         <v>14</v>
       </c>
       <c r="B78" s="5">
-        <v>46118</v>
+        <v>46083</v>
       </c>
       <c r="C78" s="6">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -3232,10 +3094,10 @@
         <v>14</v>
       </c>
       <c r="B79" s="8">
-        <v>46078</v>
+        <v>46105</v>
       </c>
       <c r="C79" s="9">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -3243,10 +3105,10 @@
         <v>14</v>
       </c>
       <c r="B80" s="5">
-        <v>46099</v>
+        <v>46210</v>
       </c>
       <c r="C80" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -3254,10 +3116,10 @@
         <v>14</v>
       </c>
       <c r="B81" s="8">
-        <v>46104</v>
+        <v>46211</v>
       </c>
       <c r="C81" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -3265,10 +3127,10 @@
         <v>14</v>
       </c>
       <c r="B82" s="5">
-        <v>46020</v>
+        <v>46077</v>
       </c>
       <c r="C82" s="6">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -3276,10 +3138,10 @@
         <v>14</v>
       </c>
       <c r="B83" s="8">
-        <v>46076</v>
+        <v>46118</v>
       </c>
       <c r="C83" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -3287,10 +3149,10 @@
         <v>14</v>
       </c>
       <c r="B84" s="5">
-        <v>46111</v>
+        <v>46078</v>
       </c>
       <c r="C84" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -3298,7 +3160,7 @@
         <v>14</v>
       </c>
       <c r="B85" s="8">
-        <v>46087</v>
+        <v>46099</v>
       </c>
       <c r="C85" s="9">
         <v>2</v>
@@ -3309,10 +3171,10 @@
         <v>14</v>
       </c>
       <c r="B86" s="5">
-        <v>46140</v>
+        <v>46104</v>
       </c>
       <c r="C86" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -3320,10 +3182,10 @@
         <v>14</v>
       </c>
       <c r="B87" s="8">
-        <v>46113</v>
+        <v>46020</v>
       </c>
       <c r="C87" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -3331,10 +3193,10 @@
         <v>14</v>
       </c>
       <c r="B88" s="5">
-        <v>46119</v>
+        <v>46076</v>
       </c>
       <c r="C88" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -3342,7 +3204,7 @@
         <v>14</v>
       </c>
       <c r="B89" s="8">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="C89" s="9">
         <v>1</v>
@@ -3353,10 +3215,10 @@
         <v>14</v>
       </c>
       <c r="B90" s="5">
-        <v>46098</v>
+        <v>46087</v>
       </c>
       <c r="C90" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -3364,10 +3226,10 @@
         <v>14</v>
       </c>
       <c r="B91" s="8">
-        <v>46141</v>
+        <v>46140</v>
       </c>
       <c r="C91" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -3375,10 +3237,10 @@
         <v>14</v>
       </c>
       <c r="B92" s="5">
-        <v>46114</v>
+        <v>46113</v>
       </c>
       <c r="C92" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -3386,10 +3248,10 @@
         <v>14</v>
       </c>
       <c r="B93" s="8">
-        <v>46079</v>
+        <v>46119</v>
       </c>
       <c r="C93" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -3397,7 +3259,7 @@
         <v>14</v>
       </c>
       <c r="B94" s="5">
-        <v>46139</v>
+        <v>46108</v>
       </c>
       <c r="C94" s="6">
         <v>1</v>
@@ -3408,10 +3270,10 @@
         <v>14</v>
       </c>
       <c r="B95" s="8">
-        <v>46148</v>
+        <v>46098</v>
       </c>
       <c r="C95" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -3419,7 +3281,7 @@
         <v>14</v>
       </c>
       <c r="B96" s="5">
-        <v>46185</v>
+        <v>46141</v>
       </c>
       <c r="C96" s="6">
         <v>1</v>
@@ -3430,7 +3292,7 @@
         <v>14</v>
       </c>
       <c r="B97" s="8">
-        <v>46174</v>
+        <v>46114</v>
       </c>
       <c r="C97" s="9">
         <v>1</v>
@@ -3441,10 +3303,10 @@
         <v>14</v>
       </c>
       <c r="B98" s="5">
-        <v>46092</v>
+        <v>46079</v>
       </c>
       <c r="C98" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -3452,10 +3314,10 @@
         <v>14</v>
       </c>
       <c r="B99" s="8">
-        <v>46021</v>
+        <v>46139</v>
       </c>
       <c r="C99" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -3463,10 +3325,10 @@
         <v>14</v>
       </c>
       <c r="B100" s="5">
-        <v>46177</v>
+        <v>46148</v>
       </c>
       <c r="C100" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -3474,10 +3336,10 @@
         <v>14</v>
       </c>
       <c r="B101" s="8">
-        <v>46086</v>
+        <v>46185</v>
       </c>
       <c r="C101" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -3485,7 +3347,7 @@
         <v>14</v>
       </c>
       <c r="B102" s="5">
-        <v>46188</v>
+        <v>46174</v>
       </c>
       <c r="C102" s="6">
         <v>1</v>
@@ -3496,7 +3358,7 @@
         <v>14</v>
       </c>
       <c r="B103" s="8">
-        <v>46147</v>
+        <v>46092</v>
       </c>
       <c r="C103" s="9">
         <v>1</v>
@@ -3507,10 +3369,10 @@
         <v>14</v>
       </c>
       <c r="B104" s="5">
-        <v>46134</v>
+        <v>46021</v>
       </c>
       <c r="C104" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -3518,7 +3380,7 @@
         <v>14</v>
       </c>
       <c r="B105" s="8">
-        <v>46182</v>
+        <v>46177</v>
       </c>
       <c r="C105" s="9">
         <v>1</v>
@@ -3526,68 +3388,68 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B106" s="5">
-        <v>46003</v>
+        <v>46086</v>
       </c>
       <c r="C106" s="6">
-        <v>95</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B107" s="8">
-        <v>46002</v>
+        <v>46188</v>
       </c>
       <c r="C107" s="9">
-        <v>115</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B108" s="5">
-        <v>46008</v>
+        <v>46147</v>
       </c>
       <c r="C108" s="6">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B109" s="8">
-        <v>46000</v>
+        <v>46134</v>
       </c>
       <c r="C109" s="9">
-        <v>98</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B110" s="5">
-        <v>46007</v>
+        <v>46182</v>
       </c>
       <c r="C110" s="6">
-        <v>40</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="B111" s="8">
-        <v>46001</v>
+        <v>46190</v>
       </c>
       <c r="C111" s="9">
-        <v>91</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -3595,10 +3457,10 @@
         <v>3</v>
       </c>
       <c r="B112" s="5">
-        <v>46010</v>
+        <v>46003</v>
       </c>
       <c r="C112" s="6">
-        <v>9</v>
+        <v>95</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -3606,10 +3468,10 @@
         <v>3</v>
       </c>
       <c r="B113" s="8">
-        <v>46006</v>
+        <v>46002</v>
       </c>
       <c r="C113" s="9">
-        <v>84</v>
+        <v>115</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -3617,10 +3479,10 @@
         <v>3</v>
       </c>
       <c r="B114" s="5">
-        <v>46009</v>
+        <v>46008</v>
       </c>
       <c r="C114" s="6">
-        <v>2</v>
+        <v>14</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -3628,10 +3490,10 @@
         <v>3</v>
       </c>
       <c r="B115" s="8">
-        <v>46015</v>
+        <v>46000</v>
       </c>
       <c r="C115" s="9">
-        <v>1</v>
+        <v>98</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -3639,10 +3501,10 @@
         <v>3</v>
       </c>
       <c r="B116" s="5">
-        <v>46014</v>
+        <v>46007</v>
       </c>
       <c r="C116" s="6">
-        <v>8</v>
+        <v>40</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -3650,10 +3512,10 @@
         <v>3</v>
       </c>
       <c r="B117" s="8">
-        <v>46013</v>
+        <v>46001</v>
       </c>
       <c r="C117" s="9">
-        <v>2</v>
+        <v>91</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -3661,10 +3523,10 @@
         <v>3</v>
       </c>
       <c r="B118" s="5">
-        <v>46021</v>
+        <v>46010</v>
       </c>
       <c r="C118" s="6">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -3672,10 +3534,10 @@
         <v>3</v>
       </c>
       <c r="B119" s="8">
-        <v>46077</v>
+        <v>46006</v>
       </c>
       <c r="C119" s="9">
-        <v>8</v>
+        <v>84</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -3683,10 +3545,10 @@
         <v>3</v>
       </c>
       <c r="B120" s="5">
-        <v>46167</v>
+        <v>46009</v>
       </c>
       <c r="C120" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -3694,10 +3556,10 @@
         <v>3</v>
       </c>
       <c r="B121" s="8">
-        <v>46090</v>
+        <v>46015</v>
       </c>
       <c r="C121" s="9">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -3705,10 +3567,10 @@
         <v>3</v>
       </c>
       <c r="B122" s="5">
-        <v>46189</v>
+        <v>46014</v>
       </c>
       <c r="C122" s="6">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -3716,10 +3578,10 @@
         <v>3</v>
       </c>
       <c r="B123" s="8">
-        <v>46170</v>
+        <v>46013</v>
       </c>
       <c r="C123" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -3727,10 +3589,10 @@
         <v>3</v>
       </c>
       <c r="B124" s="5">
-        <v>46093</v>
+        <v>46021</v>
       </c>
       <c r="C124" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -3738,10 +3600,10 @@
         <v>3</v>
       </c>
       <c r="B125" s="8">
-        <v>46078</v>
+        <v>46077</v>
       </c>
       <c r="C125" s="9">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
@@ -3749,10 +3611,10 @@
         <v>3</v>
       </c>
       <c r="B126" s="5">
-        <v>46084</v>
+        <v>46167</v>
       </c>
       <c r="C126" s="6">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -3760,10 +3622,10 @@
         <v>3</v>
       </c>
       <c r="B127" s="8">
-        <v>46134</v>
+        <v>46209</v>
       </c>
       <c r="C127" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -3771,10 +3633,10 @@
         <v>3</v>
       </c>
       <c r="B128" s="5">
-        <v>46083</v>
+        <v>46189</v>
       </c>
       <c r="C128" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -3782,7 +3644,7 @@
         <v>3</v>
       </c>
       <c r="B129" s="8">
-        <v>46022</v>
+        <v>46170</v>
       </c>
       <c r="C129" s="9">
         <v>1</v>
@@ -3793,10 +3655,10 @@
         <v>3</v>
       </c>
       <c r="B130" s="5">
-        <v>46114</v>
+        <v>46210</v>
       </c>
       <c r="C130" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -3804,7 +3666,7 @@
         <v>3</v>
       </c>
       <c r="B131" s="8">
-        <v>46135</v>
+        <v>46093</v>
       </c>
       <c r="C131" s="9">
         <v>1</v>
@@ -3815,10 +3677,10 @@
         <v>3</v>
       </c>
       <c r="B132" s="5">
-        <v>46168</v>
+        <v>46090</v>
       </c>
       <c r="C132" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -3826,10 +3688,10 @@
         <v>3</v>
       </c>
       <c r="B133" s="8">
-        <v>46126</v>
+        <v>46078</v>
       </c>
       <c r="C133" s="9">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -3837,10 +3699,10 @@
         <v>3</v>
       </c>
       <c r="B134" s="5">
-        <v>46120</v>
+        <v>46084</v>
       </c>
       <c r="C134" s="6">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -3848,10 +3710,10 @@
         <v>3</v>
       </c>
       <c r="B135" s="8">
-        <v>46127</v>
+        <v>46134</v>
       </c>
       <c r="C135" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -3859,10 +3721,10 @@
         <v>3</v>
       </c>
       <c r="B136" s="5">
-        <v>46087</v>
+        <v>46083</v>
       </c>
       <c r="C136" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -3870,7 +3732,7 @@
         <v>3</v>
       </c>
       <c r="B137" s="8">
-        <v>46108</v>
+        <v>46022</v>
       </c>
       <c r="C137" s="9">
         <v>1</v>
@@ -3881,10 +3743,10 @@
         <v>3</v>
       </c>
       <c r="B138" s="5">
-        <v>46020</v>
+        <v>46114</v>
       </c>
       <c r="C138" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -3892,7 +3754,7 @@
         <v>3</v>
       </c>
       <c r="B139" s="8">
-        <v>46097</v>
+        <v>46135</v>
       </c>
       <c r="C139" s="9">
         <v>1</v>
@@ -3903,10 +3765,10 @@
         <v>3</v>
       </c>
       <c r="B140" s="5">
-        <v>46177</v>
+        <v>46168</v>
       </c>
       <c r="C140" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -3914,10 +3776,10 @@
         <v>3</v>
       </c>
       <c r="B141" s="8">
-        <v>46161</v>
+        <v>46126</v>
       </c>
       <c r="C141" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -3925,10 +3787,10 @@
         <v>3</v>
       </c>
       <c r="B142" s="5">
-        <v>46129</v>
+        <v>46120</v>
       </c>
       <c r="C142" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -3936,7 +3798,7 @@
         <v>3</v>
       </c>
       <c r="B143" s="8">
-        <v>46080</v>
+        <v>46127</v>
       </c>
       <c r="C143" s="9">
         <v>1</v>
@@ -3947,7 +3809,7 @@
         <v>3</v>
       </c>
       <c r="B144" s="5">
-        <v>46101</v>
+        <v>46087</v>
       </c>
       <c r="C144" s="6">
         <v>1</v>
@@ -3958,7 +3820,7 @@
         <v>3</v>
       </c>
       <c r="B145" s="8">
-        <v>46155</v>
+        <v>46108</v>
       </c>
       <c r="C145" s="9">
         <v>1</v>
@@ -3969,7 +3831,7 @@
         <v>3</v>
       </c>
       <c r="B146" s="5">
-        <v>46150</v>
+        <v>46020</v>
       </c>
       <c r="C146" s="6">
         <v>1</v>
@@ -3980,7 +3842,7 @@
         <v>3</v>
       </c>
       <c r="B147" s="8">
-        <v>46141</v>
+        <v>46097</v>
       </c>
       <c r="C147" s="9">
         <v>1</v>
@@ -3991,7 +3853,7 @@
         <v>3</v>
       </c>
       <c r="B148" s="5">
-        <v>46085</v>
+        <v>46177</v>
       </c>
       <c r="C148" s="6">
         <v>1</v>
@@ -4002,10 +3864,10 @@
         <v>3</v>
       </c>
       <c r="B149" s="8">
-        <v>46148</v>
+        <v>46161</v>
       </c>
       <c r="C149" s="9">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -4013,10 +3875,10 @@
         <v>3</v>
       </c>
       <c r="B150" s="5">
-        <v>46118</v>
+        <v>46129</v>
       </c>
       <c r="C150" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -4024,7 +3886,7 @@
         <v>3</v>
       </c>
       <c r="B151" s="8">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="C151" s="9">
         <v>1</v>
@@ -4032,101 +3894,101 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B152" s="5">
-        <v>46003</v>
+        <v>46101</v>
       </c>
       <c r="C152" s="6">
-        <v>92</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B153" s="8">
-        <v>46000</v>
+        <v>46155</v>
       </c>
       <c r="C153" s="9">
-        <v>132</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B154" s="5">
-        <v>46006</v>
+        <v>46150</v>
       </c>
       <c r="C154" s="6">
-        <v>173</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B155" s="8">
-        <v>46001</v>
+        <v>46141</v>
       </c>
       <c r="C155" s="9">
-        <v>174</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B156" s="5">
-        <v>46014</v>
+        <v>46085</v>
       </c>
       <c r="C156" s="6">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B157" s="8">
-        <v>46002</v>
+        <v>46148</v>
       </c>
       <c r="C157" s="9">
-        <v>171</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B158" s="5">
-        <v>46009</v>
+        <v>46118</v>
       </c>
       <c r="C158" s="6">
-        <v>19</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B159" s="8">
-        <v>46010</v>
+        <v>46192</v>
       </c>
       <c r="C159" s="9">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B160" s="5">
-        <v>46008</v>
+        <v>46079</v>
       </c>
       <c r="C160" s="6">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -4134,10 +3996,10 @@
         <v>15</v>
       </c>
       <c r="B161" s="8">
-        <v>46007</v>
+        <v>46003</v>
       </c>
       <c r="C161" s="9">
-        <v>43</v>
+        <v>92</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -4145,10 +4007,10 @@
         <v>15</v>
       </c>
       <c r="B162" s="5">
-        <v>46013</v>
+        <v>46000</v>
       </c>
       <c r="C162" s="6">
-        <v>12</v>
+        <v>132</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -4156,10 +4018,10 @@
         <v>15</v>
       </c>
       <c r="B163" s="8">
-        <v>46080</v>
+        <v>46006</v>
       </c>
       <c r="C163" s="9">
-        <v>2</v>
+        <v>173</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
@@ -4167,10 +4029,10 @@
         <v>15</v>
       </c>
       <c r="B164" s="5">
-        <v>46090</v>
+        <v>46001</v>
       </c>
       <c r="C164" s="6">
-        <v>7</v>
+        <v>174</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
@@ -4178,10 +4040,10 @@
         <v>15</v>
       </c>
       <c r="B165" s="8">
-        <v>46079</v>
+        <v>46014</v>
       </c>
       <c r="C165" s="9">
-        <v>4</v>
+        <v>16</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
@@ -4189,10 +4051,10 @@
         <v>15</v>
       </c>
       <c r="B166" s="5">
-        <v>46015</v>
+        <v>46002</v>
       </c>
       <c r="C166" s="6">
-        <v>1</v>
+        <v>171</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
@@ -4200,10 +4062,10 @@
         <v>15</v>
       </c>
       <c r="B167" s="8">
-        <v>46085</v>
+        <v>46009</v>
       </c>
       <c r="C167" s="9">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
@@ -4211,10 +4073,10 @@
         <v>15</v>
       </c>
       <c r="B168" s="5">
-        <v>46098</v>
+        <v>46010</v>
       </c>
       <c r="C168" s="6">
-        <v>2</v>
+        <v>19</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -4222,10 +4084,10 @@
         <v>15</v>
       </c>
       <c r="B169" s="8">
-        <v>46021</v>
+        <v>46008</v>
       </c>
       <c r="C169" s="9">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
@@ -4233,10 +4095,10 @@
         <v>15</v>
       </c>
       <c r="B170" s="5">
-        <v>46078</v>
+        <v>46007</v>
       </c>
       <c r="C170" s="6">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
@@ -4244,10 +4106,10 @@
         <v>15</v>
       </c>
       <c r="B171" s="8">
-        <v>46084</v>
+        <v>46013</v>
       </c>
       <c r="C171" s="9">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
@@ -4255,10 +4117,10 @@
         <v>15</v>
       </c>
       <c r="B172" s="5">
-        <v>46128</v>
+        <v>46080</v>
       </c>
       <c r="C172" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
@@ -4266,10 +4128,10 @@
         <v>15</v>
       </c>
       <c r="B173" s="8">
-        <v>46083</v>
+        <v>46209</v>
       </c>
       <c r="C173" s="9">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
@@ -4277,7 +4139,7 @@
         <v>15</v>
       </c>
       <c r="B174" s="5">
-        <v>46076</v>
+        <v>46090</v>
       </c>
       <c r="C174" s="6">
         <v>7</v>
@@ -4288,10 +4150,10 @@
         <v>15</v>
       </c>
       <c r="B175" s="8">
-        <v>46099</v>
+        <v>46192</v>
       </c>
       <c r="C175" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -4299,10 +4161,10 @@
         <v>15</v>
       </c>
       <c r="B176" s="5">
-        <v>46154</v>
+        <v>46079</v>
       </c>
       <c r="C176" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
@@ -4310,7 +4172,7 @@
         <v>15</v>
       </c>
       <c r="B177" s="8">
-        <v>46092</v>
+        <v>46015</v>
       </c>
       <c r="C177" s="9">
         <v>1</v>
@@ -4321,10 +4183,10 @@
         <v>15</v>
       </c>
       <c r="B178" s="5">
-        <v>46022</v>
+        <v>46085</v>
       </c>
       <c r="C178" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
@@ -4332,7 +4194,7 @@
         <v>15</v>
       </c>
       <c r="B179" s="8">
-        <v>46031</v>
+        <v>46098</v>
       </c>
       <c r="C179" s="9">
         <v>2</v>
@@ -4343,10 +4205,10 @@
         <v>15</v>
       </c>
       <c r="B180" s="5">
-        <v>46120</v>
+        <v>46021</v>
       </c>
       <c r="C180" s="6">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -4354,10 +4216,10 @@
         <v>15</v>
       </c>
       <c r="B181" s="8">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="C181" s="9">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
@@ -4365,10 +4227,10 @@
         <v>15</v>
       </c>
       <c r="B182" s="5">
-        <v>46114</v>
+        <v>46084</v>
       </c>
       <c r="C182" s="6">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
@@ -4376,10 +4238,10 @@
         <v>15</v>
       </c>
       <c r="B183" s="8">
-        <v>46037</v>
+        <v>46128</v>
       </c>
       <c r="C183" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -4387,10 +4249,10 @@
         <v>15</v>
       </c>
       <c r="B184" s="5">
-        <v>46020</v>
+        <v>46083</v>
       </c>
       <c r="C184" s="6">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
@@ -4398,10 +4260,10 @@
         <v>15</v>
       </c>
       <c r="B185" s="8">
-        <v>46106</v>
+        <v>46076</v>
       </c>
       <c r="C185" s="9">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
@@ -4409,10 +4271,10 @@
         <v>15</v>
       </c>
       <c r="B186" s="5">
-        <v>46155</v>
+        <v>46099</v>
       </c>
       <c r="C186" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -4420,7 +4282,7 @@
         <v>15</v>
       </c>
       <c r="B187" s="8">
-        <v>46112</v>
+        <v>46154</v>
       </c>
       <c r="C187" s="9">
         <v>1</v>
@@ -4431,7 +4293,7 @@
         <v>15</v>
       </c>
       <c r="B188" s="5">
-        <v>46132</v>
+        <v>46092</v>
       </c>
       <c r="C188" s="6">
         <v>1</v>
@@ -4442,7 +4304,7 @@
         <v>15</v>
       </c>
       <c r="B189" s="8">
-        <v>46108</v>
+        <v>46022</v>
       </c>
       <c r="C189" s="9">
         <v>1</v>
@@ -4453,10 +4315,10 @@
         <v>15</v>
       </c>
       <c r="B190" s="5">
-        <v>46148</v>
+        <v>46031</v>
       </c>
       <c r="C190" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -4464,10 +4326,10 @@
         <v>15</v>
       </c>
       <c r="B191" s="8">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="C191" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
@@ -4475,10 +4337,10 @@
         <v>15</v>
       </c>
       <c r="B192" s="5">
-        <v>46035</v>
+        <v>46077</v>
       </c>
       <c r="C192" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
@@ -4486,7 +4348,7 @@
         <v>15</v>
       </c>
       <c r="B193" s="8">
-        <v>46181</v>
+        <v>46114</v>
       </c>
       <c r="C193" s="9">
         <v>1</v>
@@ -4497,7 +4359,7 @@
         <v>15</v>
       </c>
       <c r="B194" s="5">
-        <v>46093</v>
+        <v>46037</v>
       </c>
       <c r="C194" s="6">
         <v>1</v>
@@ -4508,10 +4370,10 @@
         <v>15</v>
       </c>
       <c r="B195" s="8">
-        <v>46087</v>
+        <v>46020</v>
       </c>
       <c r="C195" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
@@ -4519,10 +4381,10 @@
         <v>15</v>
       </c>
       <c r="B196" s="5">
-        <v>46030</v>
+        <v>46106</v>
       </c>
       <c r="C196" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
@@ -4530,7 +4392,7 @@
         <v>15</v>
       </c>
       <c r="B197" s="8">
-        <v>46176</v>
+        <v>46155</v>
       </c>
       <c r="C197" s="9">
         <v>1</v>
@@ -4541,10 +4403,10 @@
         <v>15</v>
       </c>
       <c r="B198" s="5">
-        <v>46101</v>
+        <v>46210</v>
       </c>
       <c r="C198" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -4552,7 +4414,7 @@
         <v>15</v>
       </c>
       <c r="B199" s="8">
-        <v>46142</v>
+        <v>46112</v>
       </c>
       <c r="C199" s="9">
         <v>1</v>
@@ -4560,145 +4422,145 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B200" s="5">
-        <v>46001</v>
+        <v>46132</v>
       </c>
       <c r="C200" s="6">
-        <v>153</v>
+        <v>1</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B201" s="8">
-        <v>46008</v>
+        <v>46108</v>
       </c>
       <c r="C201" s="9">
-        <v>38</v>
+        <v>1</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B202" s="5">
-        <v>46003</v>
+        <v>46148</v>
       </c>
       <c r="C202" s="6">
-        <v>70</v>
+        <v>1</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B203" s="8">
-        <v>46002</v>
+        <v>46118</v>
       </c>
       <c r="C203" s="9">
-        <v>111</v>
+        <v>1</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B204" s="5">
-        <v>46006</v>
+        <v>46035</v>
       </c>
       <c r="C204" s="6">
-        <v>146</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B205" s="8">
-        <v>46007</v>
+        <v>46181</v>
       </c>
       <c r="C205" s="9">
-        <v>45</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B206" s="5">
-        <v>46000</v>
+        <v>46093</v>
       </c>
       <c r="C206" s="6">
-        <v>127</v>
+        <v>1</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B207" s="8">
-        <v>46084</v>
+        <v>46087</v>
       </c>
       <c r="C207" s="9">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B208" s="5">
-        <v>46013</v>
+        <v>46030</v>
       </c>
       <c r="C208" s="6">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B209" s="8">
-        <v>46010</v>
+        <v>46204</v>
       </c>
       <c r="C209" s="9">
-        <v>19</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B210" s="5">
-        <v>46021</v>
+        <v>46176</v>
       </c>
       <c r="C210" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B211" s="8">
-        <v>46009</v>
+        <v>46101</v>
       </c>
       <c r="C211" s="9">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B212" s="5">
-        <v>46083</v>
+        <v>46142</v>
       </c>
       <c r="C212" s="6">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
@@ -4706,10 +4568,10 @@
         <v>21</v>
       </c>
       <c r="B213" s="8">
-        <v>46014</v>
+        <v>46001</v>
       </c>
       <c r="C213" s="9">
-        <v>20</v>
+        <v>153</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -4717,10 +4579,10 @@
         <v>21</v>
       </c>
       <c r="B214" s="5">
-        <v>46157</v>
+        <v>46008</v>
       </c>
       <c r="C214" s="6">
-        <v>2</v>
+        <v>38</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
@@ -4728,10 +4590,10 @@
         <v>21</v>
       </c>
       <c r="B215" s="8">
-        <v>46079</v>
+        <v>46003</v>
       </c>
       <c r="C215" s="9">
-        <v>3</v>
+        <v>70</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
@@ -4739,10 +4601,10 @@
         <v>21</v>
       </c>
       <c r="B216" s="5">
-        <v>46167</v>
+        <v>46002</v>
       </c>
       <c r="C216" s="6">
-        <v>1</v>
+        <v>111</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
@@ -4750,10 +4612,10 @@
         <v>21</v>
       </c>
       <c r="B217" s="8">
-        <v>46035</v>
+        <v>46006</v>
       </c>
       <c r="C217" s="9">
-        <v>2</v>
+        <v>146</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -4761,10 +4623,10 @@
         <v>21</v>
       </c>
       <c r="B218" s="5">
-        <v>46085</v>
+        <v>46007</v>
       </c>
       <c r="C218" s="6">
-        <v>3</v>
+        <v>45</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
@@ -4772,10 +4634,10 @@
         <v>21</v>
       </c>
       <c r="B219" s="8">
-        <v>46120</v>
+        <v>46000</v>
       </c>
       <c r="C219" s="9">
-        <v>2</v>
+        <v>127</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
@@ -4783,10 +4645,10 @@
         <v>21</v>
       </c>
       <c r="B220" s="5">
-        <v>46114</v>
+        <v>46084</v>
       </c>
       <c r="C220" s="6">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
@@ -4794,10 +4656,10 @@
         <v>21</v>
       </c>
       <c r="B221" s="8">
-        <v>46094</v>
+        <v>46013</v>
       </c>
       <c r="C221" s="9">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
@@ -4805,10 +4667,10 @@
         <v>21</v>
       </c>
       <c r="B222" s="5">
-        <v>46080</v>
+        <v>46010</v>
       </c>
       <c r="C222" s="6">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -4816,10 +4678,10 @@
         <v>21</v>
       </c>
       <c r="B223" s="8">
-        <v>46127</v>
+        <v>46021</v>
       </c>
       <c r="C223" s="9">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
@@ -4827,10 +4689,10 @@
         <v>21</v>
       </c>
       <c r="B224" s="5">
-        <v>46091</v>
+        <v>46009</v>
       </c>
       <c r="C224" s="6">
-        <v>2</v>
+        <v>25</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -4838,10 +4700,10 @@
         <v>21</v>
       </c>
       <c r="B225" s="8">
-        <v>46090</v>
+        <v>46083</v>
       </c>
       <c r="C225" s="9">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
@@ -4849,10 +4711,10 @@
         <v>21</v>
       </c>
       <c r="B226" s="5">
-        <v>46020</v>
+        <v>46014</v>
       </c>
       <c r="C226" s="6">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
@@ -4860,10 +4722,10 @@
         <v>21</v>
       </c>
       <c r="B227" s="8">
-        <v>46015</v>
+        <v>46157</v>
       </c>
       <c r="C227" s="9">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -4871,10 +4733,10 @@
         <v>21</v>
       </c>
       <c r="B228" s="5">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="C228" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
@@ -4882,10 +4744,10 @@
         <v>21</v>
       </c>
       <c r="B229" s="8">
-        <v>46148</v>
+        <v>46167</v>
       </c>
       <c r="C229" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -4893,7 +4755,7 @@
         <v>21</v>
       </c>
       <c r="B230" s="5">
-        <v>46105</v>
+        <v>46035</v>
       </c>
       <c r="C230" s="6">
         <v>2</v>
@@ -4904,7 +4766,7 @@
         <v>21</v>
       </c>
       <c r="B231" s="8">
-        <v>46087</v>
+        <v>46085</v>
       </c>
       <c r="C231" s="9">
         <v>3</v>
@@ -4915,10 +4777,10 @@
         <v>21</v>
       </c>
       <c r="B232" s="5">
-        <v>46107</v>
+        <v>46120</v>
       </c>
       <c r="C232" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
@@ -4926,10 +4788,10 @@
         <v>21</v>
       </c>
       <c r="B233" s="8">
-        <v>46086</v>
+        <v>46114</v>
       </c>
       <c r="C233" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
@@ -4937,10 +4799,10 @@
         <v>21</v>
       </c>
       <c r="B234" s="5">
-        <v>46106</v>
+        <v>46094</v>
       </c>
       <c r="C234" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
@@ -4948,10 +4810,10 @@
         <v>21</v>
       </c>
       <c r="B235" s="8">
-        <v>46150</v>
+        <v>46192</v>
       </c>
       <c r="C235" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -4959,10 +4821,10 @@
         <v>21</v>
       </c>
       <c r="B236" s="5">
-        <v>46104</v>
+        <v>46080</v>
       </c>
       <c r="C236" s="6">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -4970,10 +4832,10 @@
         <v>21</v>
       </c>
       <c r="B237" s="8">
-        <v>46118</v>
+        <v>46127</v>
       </c>
       <c r="C237" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
@@ -4981,10 +4843,10 @@
         <v>21</v>
       </c>
       <c r="B238" s="5">
-        <v>46076</v>
+        <v>46091</v>
       </c>
       <c r="C238" s="6">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
@@ -4992,7 +4854,7 @@
         <v>21</v>
       </c>
       <c r="B239" s="8">
-        <v>46182</v>
+        <v>46090</v>
       </c>
       <c r="C239" s="9">
         <v>1</v>
@@ -5003,10 +4865,10 @@
         <v>21</v>
       </c>
       <c r="B240" s="5">
-        <v>46188</v>
+        <v>46020</v>
       </c>
       <c r="C240" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -5014,10 +4876,10 @@
         <v>21</v>
       </c>
       <c r="B241" s="8">
-        <v>46077</v>
+        <v>46015</v>
       </c>
       <c r="C241" s="9">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
@@ -5025,10 +4887,10 @@
         <v>21</v>
       </c>
       <c r="B242" s="5">
-        <v>46154</v>
+        <v>46078</v>
       </c>
       <c r="C242" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
@@ -5036,10 +4898,10 @@
         <v>21</v>
       </c>
       <c r="B243" s="8">
-        <v>46093</v>
+        <v>46209</v>
       </c>
       <c r="C243" s="9">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
@@ -5047,10 +4909,10 @@
         <v>21</v>
       </c>
       <c r="B244" s="5">
-        <v>46122</v>
+        <v>46148</v>
       </c>
       <c r="C244" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
@@ -5058,10 +4920,10 @@
         <v>21</v>
       </c>
       <c r="B245" s="8">
-        <v>46092</v>
+        <v>46105</v>
       </c>
       <c r="C245" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
@@ -5069,10 +4931,10 @@
         <v>21</v>
       </c>
       <c r="B246" s="5">
-        <v>46156</v>
+        <v>46087</v>
       </c>
       <c r="C246" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -5080,10 +4942,10 @@
         <v>21</v>
       </c>
       <c r="B247" s="8">
-        <v>46133</v>
+        <v>46107</v>
       </c>
       <c r="C247" s="9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
@@ -5091,10 +4953,10 @@
         <v>21</v>
       </c>
       <c r="B248" s="5">
-        <v>46189</v>
+        <v>46086</v>
       </c>
       <c r="C248" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
@@ -5102,7 +4964,7 @@
         <v>21</v>
       </c>
       <c r="B249" s="8">
-        <v>46126</v>
+        <v>46106</v>
       </c>
       <c r="C249" s="9">
         <v>1</v>
@@ -5113,10 +4975,10 @@
         <v>21</v>
       </c>
       <c r="B250" s="5">
-        <v>46022</v>
+        <v>46150</v>
       </c>
       <c r="C250" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
@@ -5124,10 +4986,10 @@
         <v>21</v>
       </c>
       <c r="B251" s="8">
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="C251" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -5135,7 +4997,7 @@
         <v>21</v>
       </c>
       <c r="B252" s="5">
-        <v>46101</v>
+        <v>46118</v>
       </c>
       <c r="C252" s="6">
         <v>1</v>
@@ -5146,10 +5008,10 @@
         <v>21</v>
       </c>
       <c r="B253" s="8">
-        <v>46097</v>
+        <v>46076</v>
       </c>
       <c r="C253" s="9">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
@@ -5157,7 +5019,7 @@
         <v>21</v>
       </c>
       <c r="B254" s="5">
-        <v>46108</v>
+        <v>46182</v>
       </c>
       <c r="C254" s="6">
         <v>1</v>
@@ -5168,10 +5030,10 @@
         <v>21</v>
       </c>
       <c r="B255" s="8">
-        <v>46098</v>
+        <v>46188</v>
       </c>
       <c r="C255" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
@@ -5179,10 +5041,10 @@
         <v>21</v>
       </c>
       <c r="B256" s="5">
-        <v>46113</v>
+        <v>46077</v>
       </c>
       <c r="C256" s="6">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
@@ -5190,7 +5052,7 @@
         <v>21</v>
       </c>
       <c r="B257" s="8">
-        <v>46142</v>
+        <v>46154</v>
       </c>
       <c r="C257" s="9">
         <v>1</v>
@@ -5201,10 +5063,10 @@
         <v>21</v>
       </c>
       <c r="B258" s="5">
-        <v>46153</v>
+        <v>46093</v>
       </c>
       <c r="C258" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
@@ -5212,7 +5074,7 @@
         <v>21</v>
       </c>
       <c r="B259" s="8">
-        <v>46031</v>
+        <v>46122</v>
       </c>
       <c r="C259" s="9">
         <v>1</v>
@@ -5223,9 +5085,185 @@
         <v>21</v>
       </c>
       <c r="B260" s="5">
+        <v>46092</v>
+      </c>
+      <c r="C260" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B261" s="8">
+        <v>46156</v>
+      </c>
+      <c r="C261" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B262" s="5">
+        <v>46133</v>
+      </c>
+      <c r="C262" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B263" s="8">
+        <v>46189</v>
+      </c>
+      <c r="C263" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B264" s="5">
+        <v>46210</v>
+      </c>
+      <c r="C264" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B265" s="8">
+        <v>46126</v>
+      </c>
+      <c r="C265" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B266" s="5">
+        <v>46022</v>
+      </c>
+      <c r="C266" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B267" s="8">
+        <v>46100</v>
+      </c>
+      <c r="C267" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B268" s="5">
+        <v>46101</v>
+      </c>
+      <c r="C268" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B269" s="8">
+        <v>46097</v>
+      </c>
+      <c r="C269" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B270" s="5">
+        <v>46108</v>
+      </c>
+      <c r="C270" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B271" s="8">
+        <v>46098</v>
+      </c>
+      <c r="C271" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B272" s="5">
+        <v>46113</v>
+      </c>
+      <c r="C272" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B273" s="8">
+        <v>46142</v>
+      </c>
+      <c r="C273" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B274" s="5">
+        <v>46153</v>
+      </c>
+      <c r="C274" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B275" s="8">
+        <v>46031</v>
+      </c>
+      <c r="C275" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A276" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B276" s="5">
         <v>46155</v>
       </c>
-      <c r="C260" s="6">
+      <c r="C276" s="6">
         <v>1</v>
       </c>
     </row>
@@ -5234,7 +5272,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF41E2F3-2E0F-49EB-BAE8-83F2CBABFF5B}">
   <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5275,7 +5313,7 @@
         <v>14</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -5326,7 +5364,7 @@
         <v>1</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -5343,7 +5381,7 @@
         <v>1</v>
       </c>
       <c r="E6">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -5394,7 +5432,7 @@
         <v>5</v>
       </c>
       <c r="E9">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -5513,7 +5551,7 @@
         <v>3</v>
       </c>
       <c r="E16">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -5530,7 +5568,7 @@
         <v>3</v>
       </c>
       <c r="E17">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -5541,13 +5579,13 @@
         <v>10</v>
       </c>
       <c r="C18">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
       <c r="E18">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -5558,7 +5596,7 @@
         <v>13</v>
       </c>
       <c r="C19">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D19">
         <v>5</v>
@@ -5598,7 +5636,7 @@
         <v>6</v>
       </c>
       <c r="E21">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -5615,7 +5653,7 @@
         <v>25</v>
       </c>
       <c r="E22">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -5643,13 +5681,13 @@
         <v>8</v>
       </c>
       <c r="C24">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D24">
         <v>12</v>
       </c>
       <c r="E24">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -5666,7 +5704,7 @@
         <v>3</v>
       </c>
       <c r="E25">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -5683,7 +5721,7 @@
         <v>3</v>
       </c>
       <c r="E26">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -5697,7 +5735,7 @@
         <v>92</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27">
         <v>11</v>
@@ -5728,7 +5766,7 @@
         <v>13</v>
       </c>
       <c r="C29">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D29">
         <v>3</v>
@@ -5751,7 +5789,7 @@
         <v>7</v>
       </c>
       <c r="E30">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -5765,10 +5803,10 @@
         <v>117</v>
       </c>
       <c r="D31">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E31">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -5785,7 +5823,7 @@
         <v>245</v>
       </c>
       <c r="E32">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -5796,13 +5834,13 @@
 